--- a/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
+++ b/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
@@ -10,26 +10,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Controllo riparazione" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00 Nota" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 Archivi" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01B Archivi integrativi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Fonti seriali" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Atti giudiziari e normativi" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Atti parlamentari" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Bibliografia" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Archivi desecretati" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Archivi sudamericani" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Revisione manuale" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Residui numerici" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Diagnosi foglio 01" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro analitico-diagnostico" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01B Archivi integrativi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 Fonti seriali" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Atti giudiziari e normativi" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Atti parlamentari" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Bibliografia" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Archivi desecretati" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07 Archivi sudamericani" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Revisione manuale" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Residui numerici" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ZZ Diagnosi foglio 01" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00 Nota'!$A$1:$E$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'01 Archivi'!$A$1:$L$143</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'02 Fonti seriali'!$A$1:$I$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'03 Atti giudiziari e normativi'!$A$1:$K$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'04 Atti parlamentari'!$A$1:$H$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'05 Bibliografia'!$A$1:$I$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'06 Archivi desecretati'!$A$1:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Archivi sudamericani'!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'02 Fonti seriali'!$A$1:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'03 Atti giudiziari e normativi'!$A$1:$K$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'04 Atti parlamentari'!$A$1:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'05 Bibliografia'!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'06 Archivi desecretati'!$A$1:$J$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'07 Archivi sudamericani'!$A$1:$J$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1058,6 +1059,553 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Ente</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Strumento</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Sede e accesso</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Procedura</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Contenuto utile</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Sezione servita</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Verifica indipendente</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Data verifica indipendente</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>Sede consultata / esito</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>CIA</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>CREST — CIA Records Search Tool</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>In rete, nella FOIA Electronic Reading Room dell’Agenzia</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Consultazione libera; ricerca a testo pieno dal 2000; possibile la ricerca per raccolta, per categoria e per parola chiave. Avvertenza dell’Agenzia stessa: alcuni documenti non appartengono ad alcuna raccolta e sfuggono alle ricerche limitate per raccolta</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Sottoinsieme dei documenti dell’Agenzia riesaminati nel programma 25nnale, in formato elettronico. I documenti riesaminati manualmente confluiscono direttamente negli archivi nazionali nel formato originale</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II cap. III cond. 4 — l’asse americano</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO ALLA LETTERA — e manca la storia dell'apertura</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATE ESATTAMENTE LE 2 AFFERMAZIONI PORTANTI DELLA VOCE. Prima: il sistema e il deposito pubblicamente accessibile del SOTTOINSIEME dei documenti riesaminati nel programma venticinquennale in formato elettronico, mentre i documenti riesaminati manualmente confluiscono direttamente negli Archivi nazionali nel formato originale. Seconda: l'avvertenza dell'Agenzia, che la voce riporta correttamente, e che 'alcuni documenti non appartengono ad alcuna raccolta e possono sfuggire se si limita la ricerca a una o piu raccolte'. Confermata la ricerca a testo pieno dal 2000; il sistema e installato presso NARA II a College Park, Maryland. SCALA OMESSA: oltre 11 MILIONI DI PAGINE sono state rilasciate in formato elettronico e risiedono nella banca dati, dalle quali i ricercatori ne hanno stampate circa 1,1 milioni. STORIA DELL'APERTURA, OMESSA E RILEVANTISSIMA PER L'OPERA: prima della causa promossa da MuckRock il sistema era tecnicamente accessibile MA SOLTANTO DAL LUNEDI AL VENERDI, DALLE 9 ALLE 16 E 30, PRESSO LA SEDE DEGLI ARCHIVI NAZIONALI NEL MARYLAND. La messa in rete e il risultato di un contenzioso, non di una decisione amministrativa spontanea: e un caso documentato di apertura archivistica ottenuta per via giudiziaria, e va registrato accanto agli altri. DIFETTO DI NUMERAZIONE: la voce scrive 'programma 25nnale'; si legge VENTICINQUENNALE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Esecutivo statunitense</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ordine esecutivo 13526, già 12958 come modificato</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Prescrive la desecretazione automatica dei documenti non esentati di valore storico con più di 25 anni</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>È la norma che rende programmata, e non discrezionale, la desecretazione: fissa il termine oltre il quale un documento va rilasciato salvo eccezione motivata</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — il segreto come processo che costa</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — manca il meccanismo che rende la norma un processo</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>Confermato: l'ordine esecutivo 13526, gia 12958 come modificato, impone la desecretazione dei documenti non esentati di valore storico con 25 anni o piu. L'ordine fu emanato originariamente NELL'APRILE 1995 e, per effetto di modifica, fisso il 31 DICEMBRE 2006 come primo termine maggiore del programma venticinquennale; per l'Agenzia quel termine copriva i documenti dalla fondazione del servizio dopo la seconda guerra mondiale fino al 1981. MECCANISMO OMESSO, ED E IL PUNTO: l'obbligo SCORRE IN AVANTI DI UN ANNO ALLA VOLTA. Al 31 dicembre 2012 erano automaticamente desecretati i documenti permanenti fino al 31 dicembre 1987, salvo esenzione motivata. La voce coglie giustamente che la norma rende la desecretazione programmata e non discrezionale, ma non dice come: e lo scorrimento annuale a farne un processo continuo anziche una scadenza unica. Il servizio mantiene un centro di desecretazione che riesamina i documenti PRIMA che raggiungano il termine automatico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>National Security Archive, George Washington University</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Digital National Security Archive; Electronic Briefing Books</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>In rete; istituto non governativo fondato nel 1985</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Consultazione; sezione «Documents» ricercabile; guida alla presentazione di istanze di accesso</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Oltre 100.000 documenti desecretati su decisioni di politica estera statunitense, con cronologie, bibliografie e saggi introduttivi</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Tomo II capp. III-IV</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — e contiene la dimostrazione empirica piu utile che il corpus possa citare</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>Confermata la fondazione NEL 1985 da parte di giornalisti e studiosi per contrastare la crescente segretezza governativa; istituto di ricerca e biblioteca indipendente e non governativo presso la George Washington University, dal 1995 ospitato nella Gelman Library. Fondatore: Scott ARMSTRONG, gia cronista del Washington Post e collaboratore della commissione senatoriale sul Watergate; direttore: Tom BLANTON. PRECISAZIONE SULLA CIFRA: la voce indica 'oltre 100.000 documenti'. La banca dati dei documenti rilasciati dell'istituto reca oltre 100.000 record; il Digital National Security Archive, prodotto in collaborazione con ProQuest, ne reca OLTRE 150.000. La voce cita entrambi gli strumenti come uno solo: vanno distinti, perche il secondo E SU ABBONAMENTO mentre gli Electronic Briefing Books sono liberi. MISURE OMESSE: in 4 decenni l'istituto ha determinato la desecretazione di OLTRE 15 MILIONI DI PAGINE, presentando piu di 70.000 istanze e promuovendo oltre 50 CAUSE; le collezioni accessionate superano i 2 milioni di pagine in oltre 200 raccolte. Premio George Polk speciale nel 1999 per aver 'perforato i veli interessati della segretezza governativa'. DATO DI INDIPENDENZA, da registrare secondo il criterio gia applicato alle fonti finanziate: l'istituto NON RICEVE FINANZIAMENTI DAL GOVERNO STATUNITENSE e si sostiene con diritti d'autore e donazioni di fondazioni e privati. REPERTO METODOLOGICO DI PRIMO ORDINE, DA CITARE NELLA NOTA: l'istituto espone 2 versioni del medesimo scambio di messaggi del 1987 fra un ex segretario esecutivo del Consiglio di sicurezza nazionale e l'allora vice consigliere per la sicurezza nazionale: una dalla casella in arrivo, una da quella in uscita, ESAMINATE A 10 GIORNI DI DISTANZA DAL MEDESIMO REVISORE in risposta a una causa dell'istituto. LE DUE VERSIONI RECANO OMISSIS DIVERSI. E la dimostrazione empirica, su un caso unico e controllato, che l'espunzione non e una funzione del contenuto ma del revisore: 'la soggettivita di gran parte della segretezza di sicurezza nazionale e una delle ragioni per cui esistiamo'. COLLEGAMENTO CON IL FOGLIO 07: l'istituto ha presentato la documentazione desecretata nel processo argentino sull'operazione continentale, per il tramite del direttore del proprio progetto sul Cono Sud, Carlos OSORIO; e ha pubblicato raccolte su Cile, Guatemala ed El Salvador. Le 2 voci vanno messe in relazione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Wilson Center</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Digital Archive</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>In rete</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Consultazione libera</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Documenti già segreti provenienti da governi di tutto il mondo; comprende materiali sul crollo dell’impero coloniale portoghese</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Tomo II cap. IV</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>CONFERMATO — ma l'ambito dichiarato non e quello che la voce indica</t>
+        </is>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>Confermata alla lettera la descrizione generale: l'archivio digitale contiene documenti gia segreti provenienti da governi di tutto il mondo. AMBITO EFFETTIVO, che la voce non reca e che ne restringe l'uso: la raccolta riunisce la ricerca di 3 PROGETTI DEL CENTRO, dedicati alle storie interconnesse della GUERRA FREDDA, DELLA COREA e della PROLIFERAZIONE NUCLEARE. NON RISCONTRATO il contenuto che la voce indica come utile, cioe i materiali sul crollo dell'impero coloniale portoghese: non rientra in alcuno dei 3 progetti dichiarati e va verificato per ricerca diretta prima di essere citato. Confermata la libera consultazione; la risorsa e segnalata anche dalla biblioteca degli Archivi nazionali statunitensi. RESTA APERTA l'avvertenza gia annotata sul trasferimento di documenti verso l'archivio non governativo di Washington.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Dipartimento di Stato statunitense</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>FOIA Documents Search</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>In rete</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ricerca per parola chiave e per data</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Comprende i progetti di desecretazione dedicati a Cile, Argentina, El Salvador e Guatemala, e le trascrizioni telefoniche del segretario di Stato</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II cap. IV — l’asse sudamericano; è l’indirizzo più diretto per il lato lungo del triangolo</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — l'elenco delle raccolte e esatto, e 1 di esse rinvia al foglio 03</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>ELENCO CONFERMATO ALLA LETTERA: le raccolte comprendono i progetti di desecretazione dedicati a CILE, ARGENTINA, EL SALVADOR e GUATEMALA e le trascrizioni telefoniche del segretario di Stato, oltre alla corrispondenza elettronica di una segretaria di Stato successiva. Ricerca per parola chiave e per data confermata. MISURE, con divergenza da chiudere: una guida universitaria indica OLTRE 80MILA documenti ricercabili, un'altra 221.373. Le 2 cifre appartengono a rilevazioni di date diverse e vanno datate. DATI SOSTANZIALI OMESSI, tutti utili al Tomo sull'asse sudamericano: la raccolta cilena e l'esito di uno sforzo esteso all'intero governo e consta di OLTRE 23MILA DOCUMENTI sul periodo 1968-1991, prodotti da agenzia informativa, Difesa, Archivi nazionali, Consiglio di sicurezza, ufficio federale, Giustizia e Dipartimento di Stato; il progetto argentino rappresenta QUASI 20 ANNI di lavoro per rilasciare ogni informazione sulle violazioni dei diritti umani in Argentina FRA IL 1975 E IL 1983; le trascrizioni telefoniche coprono da settembre 1973 a dicembre 1976. L'ente stesso premette alla raccolta cilena l'avvertenza 'MATERIALE GRAFICO INCLUSO'. COLLEGAMENTO CON IL FOGLIO 03, VOCE 70: le trascrizioni dell'era Nixon sono state riesaminate SECONDO LA LEGGE DEL 1974 SULLA CONSERVAZIONE DELLE REGISTRAZIONI E DEI MATERIALI PRESIDENZIALI, quelle dell'era Ford secondo la legge sull'accesso. La legge che il repertorio censisce nel foglio degli atti e dunque la norma che regola la consultabilita di questa fonte: le 2 voci vanno messe in relazione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>FBI</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The Vault — Electronic Reading Room</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>In rete</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Consultazione libera</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Documenti desecretati dell’ufficio federale</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Tomo II</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — manca la scala</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>Confermato: la biblioteca elettronica dell'ufficio federale e descritta dall'ente stesso come la propria nuova biblioteca per l'accesso agli atti, contenente 6.700 DOCUMENTI e altri materiali digitalizzati da originali cartacei. La cifra manca alla voce ed e utile, perche colloca questa fonte 3 ordini di grandezza sotto le altre censite nel foglio: non e un archivio di massa ma una selezione.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Dipartimento di Stato statunitense</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Foreign Relations of the United States</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>In rete e a stampa</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Consultazione libera</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Serie documentaria ufficiale della politica estera, con annata pressoché completa dal 1861</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Tomo II</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — con un limite temporale da precisare</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>Confermata la serie documentaria ufficiale della politica estera. PRECISAZIONE SUL DATO DELLA VOCE: la formula 'annata pressoche completa dal 1861' corrisponde a quanto dichiarano le guide, che parlano di una serie quasi completa DAL 1861 AL 1960, con i volumi mancanti aggiunti via via che possono essere acquisiti e trattati. Il termine finale del 1960 riguarda la raccolta digitalizzata di riferimento e va indicato, perche per i decenni successivi la consultazione segue vie diverse. La serie prosegue oltre quella data nelle edizioni correnti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>NARA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>U.S. Declassified Documents Online e collezioni</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>In rete, in parte su abbonamento</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Consultazione</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Oltre 5100.000 pagine di documenti già classificati di Agenzia, Dipartimento di Stato, Difesa, Consiglio di sicurezza nazionale, Casa Bianca e ufficio federale</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Tomo II capp. III-IV</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>ERRORE DI ATTRIBUZIONE — LA RISORSA NON E DEGLI ARCHIVI NAZIONALI</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>ERRORE ACCERTATO: la voce attribuisce 'U.S. Declassified Documents Online' agli ARCHIVI NAZIONALI. La risorsa e un prodotto commerciale dell'editore GALE, gia denominato Declassified Documents Reference System. Non e un archivio pubblico ma una raccolta editoriale i cui curatori sorvegliano i rilasci delle biblioteche presidenziali e delle agenzie. Cio spiega l'annotazione 'in parte su abbonamento', che e esatta, ma l'ente va corretto: le voci di questo foglio devono distinguere gli enti che DETENGONO gli atti da quelli che li RIVENDONO. CIFRA CONFERMATA, E CONFERMA LA REGOLA DI DECODIFICA: la voce reca 'oltre 5100.000 pagine'; la forma corrotta si legge CINQUECENTOMILA, e la fonte reca esattamente 'over 500,000 pages of previously classified government documents'. E la sesta conferma esterna della regola. ELENCO DELLE AGENZIE ESATTO: agenzia informativa, Dipartimento di Stato, Difesa, Consiglio di sicurezza nazionale, Casa Bianca e ufficio federale, oltre ad altre. DIVERGENZE DI MISURA DA DATARE: una guida indica oltre 500mila PAGINE con copertura dal 1950 a oggi; un'altra circa 700mila DOCUMENTI dal 1900 al 2008. Pagine e documenti non sono la stessa unita e le 2 cifre non sono in conflitto, ma vanno indicate separatamente. MODALITA DI ACCRESCIMENTO: ogni inverno esce un supplemento annuale di 5.000 documenti, acquistabile a parte. INTEGRAZIONE PER LA VOCE 7: la serie diplomatica ufficiale, iniziata nel 1861, consta oggi di OLTRE 450 VOLUMI ed e prodotta dall'Ufficio dello storico del Dipartimento di Stato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>MuckRock</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Guida alla ricerca in CREST</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>In rete</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Consultazione libera</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Guida pratica alla ricerca nel repertorio dell’Agenzia; segnala che la guida ufficiale elenca 3 tipi di contenuto mentre i metadati ne rivelano oltre novanta</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Strumento operativo per il Cantiere Delta e per il Tomo II</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO ALLA LETTERA — 3 contro oltre 90</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="inlineStr">
+        <is>
+          <t>5.8.2026</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>LA CIFRA PIU SORPRENDENTE DELLA VOCE E ESATTA. La guida di MuckRock afferma: 'in un esempio egregio, la guida dell'Agenzia alla ricerca nei documenti elenca soltanto 3 TIPI DI CONTENUTO ricercabili, mentre un esame dei metadati raccolti da DATA.WORLD ne rivela ULTERIORI NOVANTA'. La voce lo rende correttamente. FONTE DEL DATO da aggiungere: i metadati furono compilati da Data.World, non dall'Agenzia. VALORE METODOLOGICO: e un caso misurato di divergenza fra cio che un ente dichiara di rendere ricercabile e cio che la struttura dei propri dati rende effettivamente ricercabile. Non e occultamento: e una guida incompleta. Ma per un'opera che studia le condizioni di osservabilita del proprio oggetto, la differenza fra 3 e oltre 90 e essa stessa un dato.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1375,7 +1923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1513,7 +2061,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4731,7 +5279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4990,7 +5538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6838,37 +7386,37 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Operazione «Feuerzauber» — attentato simulato al carcere di Celle</t>
+          <t>Struttura clandestina della Germania federale, 1950-1953 — organizzazione giovanile e suo «servizio tecnico»</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Bassa Sassonia, Germania; 25 luglio 1978, ore 2:54</t>
+          <t>Repubblica federale tedesca; deposito d’armi rinvenuto nell’Odenwald presso Francoforte</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fatti accertati e ammessi; commissione d’inchiesta del Parlamento regionale; relazione finale discussa in aula</t>
+          <t>Atti dell’inchiesta amministrativa e giudiziaria del 1952-1953; documentazione d’archivio ripresa dalla storiografia sulle organizzazioni stay-behind in Germania 1946-1990</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>UN SERVIZIO DI SICUREZZA DI UNO STATO DEMOCRATICO FECE ESPLODERE UNA BOMBA CONTRO IL MURO DI UN CARCERE E NE ATTRIBUÌ LA PATERNITÀ A UN’ORGANIZZAZIONE TERRORISTICA. L’ufficio regionale per la protezione della Costituzione, con il supporto dell’unità speciale antiterrorismo federale, provocò un foro di circa quaranta centimetri nella muraglia esterna, con danni minimi e nessuna evasione. Scopo dichiarato: infiltrare un informatore nell’organizzazione armata sotto falsa bandiera, arricchendone la biografia e dimostrando all’ambiente che gli informatori erano disposti ad azioni drastiche</t>
+          <t>L’associazione fu fondata nel giugno 1950 su iniziativa dell’ufficio di coordinamento politico del servizio informazioni statunitense e ne fu FINANZIATA AL CENTO PER CENTO, per almeno due milioni e mezzo di marchi, con vincolo di indirizzo sui contenuti politici. Il suo braccio paramilitare, il «servizio tecnico», ricevette fino a 50mila marchi mensili, armi ed esplosivi per brillamenti di ponti e atti di sabotaggio; era diretto da un ex appartenente alle Waffen-SS. La struttura fu scoperta nel 1952 quando un ex ufficiale delle SS si presentò spontaneamente alla polizia di Francoforte dichiarandosi membro. Nel settembre 1952 la perquisizione portò al rinvenimento di un deposito con mitragliatrici, granate, pezzi d’artiglieria leggera ed esplosivi. Associazione e servizio tecnico furono VIETATI all’inizio del 1953</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>LA MESSA IN SCENA FU COMPLETA: un’automobile predisposta con armi, munizioni e passaporti falsi, fermata ottanta chilometri più in là con il conducente già fuggito; ATTREZZI DA EVASIONE INTRODOTTI DI NASCOSTO NELLA CELLA DEL DETENUTO E POI «RITROVATI»; criminali arruolati come informatori, uno dei quali PRESENTATO AI MEDIA COME SOSPETTATO. L’azione, prevista per la notte precedente, fu rinviata perché DUE INNAMORATI PROVENIENTI DAL LUNA PARK VICINO ENTRARONO NELLA ZONA PERICOLOSA. Al detenuto furono in seguito respinte le richieste di alleviamento della detenzione CON RIFERIMENTO ALL’ATTENTATO</t>
+          <t>LE LISTE, E LA DIVERGENZA DA REGISTRARE: fra gli atti sequestrati furono trovate schede personali su 15 membri del partito comunista e ottanta del partito socialdemocratico; IL PRESIDENTE DELL’UFFICIO FEDERALE PER LA PROTEZIONE DELLA COSTITUZIONE DICHIARÒ IN SEGUITO CHE QUELLE SCHEDE ERANO SIMILI, PER IMPIANTO E STRUTTURA, A QUELLE IN USO PRESSO IL PROPRIO UFFICIO. Le compilò un ex maggiore della Wehrmacht. Alcune fonti riferiscono di una lista di quaranta dirigenti politici destinati a essere soppressi, in prevalenza socialdemocratici e con nomi di primo piano; una fonte storiografica critica avverte invece contro l’esagerazione, ritenendo che le liste riguardassero più probabilmente presunti comunisti che socialdemocratici. LA DIVERGENZA È DICHIARATA E VA RISOLTA SUGLI ATTI</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>LA RIVELAZIONE E L’ESITO: il 24 aprile 1986 due deputati regionali accennarono al fatto in aula; il giorno dopo, 3 settimane prima delle elezioni regionali, un quotidiano di Hannover ne rivelò le circostanze. Il presidente del Land rese una dichiarazione di governo IN CUI GIUSTIFICÒ L’OPERAZIONE. La commissione d’inchiesta NON POTÉ CONFERMARE i successi rivendicati e accertò che un investigatore privato poteva determinare da solo e senza controllo i concetti e le azioni fittizie degli informatori; il procedimento penale avviato fu ARCHIVIATO per mancanza di elementi di reato. Il pezzo di muro con il foro è oggi esposto davanti all’ingresso del carcere</t>
+          <t>IL DATO CHE VALE PIÙ DI TUTTI: il corpo di controspionaggio dell’esercito statunitense PRESE IN CUSTODIA I MEMBRI TEDESCHI E NEGÒ ALLE AUTORITÀ DELLA REPUBBLICA FEDERALE L’ACCESSO A ESSI NEI MESI SUCCESSIVI, PROPRIO PERCHÉ QUELLE AUTORITÀ INTENDEVANO INCRIMINARLI. Un partecipante fu condannato nel 1953 a 6 settimane per concorso in sequestro di persona</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — È IL PRECEDENTE DOCUMENTATO E AMMESSO DELLA CATEGORIA «SERVIZIO DEVIATO»; le fonti registrano che dopo le rivelazioni si sviluppò un durevole sospetto che attentati segnalati potessero essere azioni di Stato sotto falsa bandiera</t>
+          <t>Tomo II e Dominio 3 — è il precedente documentato della struttura clandestina con liste; Metodologia — un servizio straniero sottrae indagati alla giurisdizione del Paese ospite</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -6888,37 +7436,37 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Struttura clandestina della Germania federale, 1950-1953 — organizzazione giovanile e suo «servizio tecnico»</t>
+          <t>Archivio degli atti della Sicurezza di Stato — schedario microfilmato della direzione principale per l’informazione estera («Rosenholz»)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Repubblica federale tedesca; deposito d’armi rinvenuto nell’Odenwald presso Francoforte</t>
+          <t>Berlino; consultabile presso l’archivio dal marzo 2004</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Atti dell’inchiesta amministrativa e giudiziaria del 1952-1953; documentazione d’archivio ripresa dalla storiografia sulle organizzazioni stay-behind in Germania 1946-1990</t>
+          <t>Chiunque presenti istanza di accesso ai propri atti può prendere visione dei dati che lo riguardano; per la ricerca valgono le stesse regole degli altri atti della Sicurezza di Stato</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>L’associazione fu fondata nel giugno 1950 su iniziativa dell’ufficio di coordinamento politico del servizio informazioni statunitense e ne fu FINANZIATA AL CENTO PER CENTO, per almeno due milioni e mezzo di marchi, con vincolo di indirizzo sui contenuti politici. Il suo braccio paramilitare, il «servizio tecnico», ricevette fino a 50mila marchi mensili, armi ed esplosivi per brillamenti di ponti e atti di sabotaggio; era diretto da un ex appartenente alle Waffen-SS. La struttura fu scoperta nel 1952 quando un ex ufficiale delle SS si presentò spontaneamente alla polizia di Francoforte dichiarandosi membro. Nel settembre 1952 la perquisizione portò al rinvenimento di un deposito con mitragliatrici, granate, pezzi d’artiglieria leggera ed esplosivi. Associazione e servizio tecnico furono VIETATI all’inizio del 1953</t>
+          <t>TRECENTOTTANTUNO SUPPORTI OTTICI con circa 3150mila file: copie di circa DUECENTONOVANTATREMILA SCHEDE dello schedario nominativo della direzione per lo spionaggio estero. NON SONO FASCICOLI: SONO STRUMENTI DI CORREDO, schede e tabulati. Vi risultano registrate circa 150MILA PERSONE della Repubblica federale e CENTOSETTEMILA della Germania orientale</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>LE LISTE, E LA DIVERGENZA DA REGISTRARE: fra gli atti sequestrati furono trovate schede personali su 15 membri del partito comunista e ottanta del partito socialdemocratico; IL PRESIDENTE DELL’UFFICIO FEDERALE PER LA PROTEZIONE DELLA COSTITUZIONE DICHIARÒ IN SEGUITO CHE QUELLE SCHEDE ERANO SIMILI, PER IMPIANTO E STRUTTURA, A QUELLE IN USO PRESSO IL PROPRIO UFFICIO. Le compilò un ex maggiore della Wehrmacht. Alcune fonti riferiscono di una lista di quaranta dirigenti politici destinati a essere soppressi, in prevalenza socialdemocratici e con nomi di primo piano; una fonte storiografica critica avverte invece contro l’esagerazione, ritenendo che le liste riguardassero più probabilmente presunti comunisti che socialdemocratici. LA DIVERGENZA È DICHIARATA E VA RISOLTA SUGLI ATTI</t>
+          <t>LA PRIMA LEZIONE, CHE COINCIDE CON LA REGOLA DELLA CERNIERA: circa il NOVANTA PER CENTO delle persone schedate NON erano collaboratori informali del ministero, ma persone dell’ambiente dei collaboratori o registrate per altre ragioni; le fonti avvertono espressamente che dalla presenza di un fascicolo NON SI PUÒ INFERIRE L’ATTIVITÀ, poiché in parte si tratta di persone di contatto che di regola venivano attinte a loro insaputa. Le stime degli effettivi informatori indicano circa seimila cittadini federali e oltre ventimila cittadini della Germania orientale</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>IL DATO CHE VALE PIÙ DI TUTTI: il corpo di controspionaggio dell’esercito statunitense PRESE IN CUSTODIA I MEMBRI TEDESCHI E NEGÒ ALLE AUTORITÀ DELLA REPUBBLICA FEDERALE L’ACCESSO A ESSI NEI MESI SUCCESSIVI, PROPRIO PERCHÉ QUELLE AUTORITÀ INTENDEVANO INCRIMINARLI. Un partecipante fu condannato nel 1953 a 6 settimane per concorso in sequestro di persona</t>
+          <t>LA SECONDA LEZIONE, CHE COINCIDE CON LA CONTABILITÀ DELLE MANI: i microfilm giunsero al servizio informazioni statunitense PER VIA TUTTORA IGNOTA; furono restituiti in copia su supporto ottico a partire dal 1999 e fino al marzo 2003, A CONDIZIONE CHE FOSSERO CLASSIFICATI — condizione revocata nel giugno 2003. IN ALCUNI CASI È DIMOSTRABILE CHE L’AUTORITÀ AMERICANA IMPIEGÒ PROGRAMMI DI ELABORAZIONE DELL’IMMAGINE PER MIGLIORARE LA LEGGIBILITÀ DELLE SCHEDE DIGITALIZZATE, E CHE COSÌ FACENDO SINGOLE CIFRE O LETTERE RISULTARONO ALTERATE. L’archivio tedesco ha verificato i dati per errori di traduzione e di altra natura</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Tomo II e Dominio 3 — è il precedente documentato della struttura clandestina con liste; Metodologia — un servizio straniero sottrae indagati alla giurisdizione del Paese ospite</t>
+          <t>Tomo II; Metodologia — l’iscrizione non prova la condotta; e la copia migliorata è una copia alterata</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -6938,44 +7486,40 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Archivio degli atti della Sicurezza di Stato — schedario microfilmato della direzione principale per l’informazione estera («Rosenholz»)</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Berlino; consultabile presso l’archivio dal marzo 2004</t>
+          <t>Organo parlamentare di controllo sui servizi informativi federali — Germania</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Bundestag, Berlino</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Chiunque presenti istanza di accesso ai propri atti può prendere visione dei dati che lo riguardano; per la ricerca valgono le stesse regole degli altri atti della Sicurezza di Stato</t>
+          <t>Rango costituzionale dal 2009 con l’articolo 45d della Legge fondamentale; disciplina di dettaglio nella legge sul controllo parlamentare dell’attività informativa federale del 29 luglio 2009, riformata il 7 dicembre 2016</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>TRECENTOTTANTUNO SUPPORTI OTTICI con circa 3150mila file: copie di circa DUECENTONOVANTATREMILA SCHEDE dello schedario nominativo della direzione per lo spionaggio estero. NON SONO FASCICOLI: SONO STRUMENTI DI CORREDO, schede e tabulati. Vi risultano registrate circa 150MILA PERSONE della Repubblica federale e CENTOSETTEMILA della Germania orientale</t>
+          <t>GENEALOGIA: comitato informale di fiduciari dal 1956; commissione con base legislativa dal 1978; rifusione integrale nel 1999; ancoraggio costituzionale nel 2009; ulteriore sviluppo nel 2016 con l’istituzione di un COMMISSARIO PERMANENTE e l’aumento del personale di supporto. POTERI: il governo deve riferire d’ufficio o su richiesta; l’organo può PRENDERE VISIONE DI ATTI E BANCHE DATI, chiedere informazioni, OTTENERE ACCESSO AGLI UFFICI dei servizi, e INTERROGARE appartenenti ai servizi, dipendenti e membri del governo; può incaricare un ESPERTO con poteri estesi di accertare una singola vicenda. Poteri speciali sulle limitazioni del segreto postale e delle comunicazioni, con relazione semestrale del governo su tutte le misure di sorveglianza e nomina dei membri della commissione competente. Dal 1993 riferisce pubblicamente all’aula almeno a metà e a fine legislatura; DAL 2017 INTERROGA OGNI AUTUNNO I PRESIDENTI DEI SERVIZI IN AUDIZIONE PUBBLICA</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>LA PRIMA LEZIONE, CHE COINCIDE CON LA REGOLA DELLA CERNIERA: circa il NOVANTA PER CENTO delle persone schedate NON erano collaboratori informali del ministero, ma persone dell’ambiente dei collaboratori o registrate per altre ragioni; le fonti avvertono espressamente che dalla presenza di un fascicolo NON SI PUÒ INFERIRE L’ATTIVITÀ, poiché in parte si tratta di persone di contatto che di regola venivano attinte a loro insaputa. Le stime degli effettivi informatori indicano circa seimila cittadini federali e oltre ventimila cittadini della Germania orientale</t>
+          <t>I DUE LIMITI, DA REGISTRARE CON LA STESSA CURA. STRUTTURALE: in sede parlamentare si è osservato che, pur dopo il rafforzamento del 2009, un controllo sistematico risultava di fatto impraticabile, perché 9 DEPUTATI E UNA SEGRETERIA non bastano a controllare effettivamente il lavoro di QUASI 10MILA DIPENDENTI dei servizi federali. POLITICO: i membri sono eletti a maggioranza dei componenti dell’assemblea, e ciò ha comportato che deputati di alcuni gruppi non siano stati eletti nell’organo — negli anni Ottanta e Novanta, e ancora nel 2018 e nel 2025. LA MAGGIORANZA ELEGGE I CONTROLLORI, E HA ESCLUSO</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>LA SECONDA LEZIONE, CHE COINCIDE CON LA CONTABILITÀ DELLE MANI: i microfilm giunsero al servizio informazioni statunitense PER VIA TUTTORA IGNOTA; furono restituiti in copia su supporto ottico a partire dal 1999 e fino al marzo 2003, A CONDIZIONE CHE FOSSERO CLASSIFICATI — condizione revocata nel giugno 2003. IN ALCUNI CASI È DIMOSTRABILE CHE L’AUTORITÀ AMERICANA IMPIEGÒ PROGRAMMI DI ELABORAZIONE DELL’IMMAGINE PER MIGLIORARE LA LEGGIBILITÀ DELLE SCHEDE DIGITALIZZATE, E CHE COSÌ FACENDO SINGOLE CIFRE O LETTERE RISULTARONO ALTERATE. L’archivio tedesco ha verificato i dati per errori di traduzione e di altra natura</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II; Metodologia — l’iscrizione non prova la condotta; e la copia migliorata è una copia alterata</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
+          <t>Tomo III — è il termine di paragone della TERZA proposta del 1984 (centralità del Parlamento nei controlli) e insieme della QUARTA (strumenti effettivi in capo all’opposizione): il modello esiste, ha rango costituzionale, e presenta entrambi i limiti che la Nota italiana aveva previsto</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="8" t="inlineStr">
         <is>
@@ -6988,32 +7532,32 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Organo parlamentare di controllo sui servizi informativi federali — Germania</t>
+          <t>Serie tedesca delle commissioni indipendenti sulle continuità istituzionali dopo il 1945</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bundestag, Berlino</t>
+          <t>Repubblica federale tedesca</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Rango costituzionale dal 2009 con l’articolo 45d della Legge fondamentale; disciplina di dettaglio nella legge sul controllo parlamentare dell’attività informativa federale del 29 luglio 2009, riformata il 7 dicembre 2016</t>
+          <t>Commissioni istituite dai ministeri stessi, con studiosi esterni e accesso agli archivi interni; risultati pubblicati presso editori commerciali e diffusi anche in opuscoli scaricabili e in mostre itineranti</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>GENEALOGIA: comitato informale di fiduciari dal 1956; commissione con base legislativa dal 1978; rifusione integrale nel 1999; ancoraggio costituzionale nel 2009; ulteriore sviluppo nel 2016 con l’istituzione di un COMMISSARIO PERMANENTE e l’aumento del personale di supporto. POTERI: il governo deve riferire d’ufficio o su richiesta; l’organo può PRENDERE VISIONE DI ATTI E BANCHE DATI, chiedere informazioni, OTTENERE ACCESSO AGLI UFFICI dei servizi, e INTERROGARE appartenenti ai servizi, dipendenti e membri del governo; può incaricare un ESPERTO con poteri estesi di accertare una singola vicenda. Poteri speciali sulle limitazioni del segreto postale e delle comunicazioni, con relazione semestrale del governo su tutte le misure di sorveglianza e nomina dei membri della commissione competente. Dal 1993 riferisce pubblicamente all’aula almeno a metà e a fine legislatura; DAL 2017 INTERROGA OGNI AUTUNNO I PRESIDENTI DEI SERVIZI IN AUDIZIONE PUBBLICA</t>
+          <t>FENOMENO SISTEMICO, NON CASO ISOLATO: il ministero degli Esteri istituì una commissione indipendente sulla propria storia nel periodo nazionalsocialista e nella Repubblica federale, i cui risultati uscirono nel 2010; il ministero della Giustizia istituì nel 2012 una commissione scientifica indipendente sul modo in cui il dicastero trattò il proprio passato, che lavorò 4 ANNI e pubblicò nel 2016; il servizio informazioni estero istituì nel 2011 la propria commissione di storici. Nel 2016 è stato pubblicato anche un volume di rassegna su STATO E PROSPETTIVE DELLA RICERCA DI TUTTI GLI STUDI SULLE SUPREME AUTORITÀ DELLE DUE GERMANIE NEL DOPOGUERRA</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>I DUE LIMITI, DA REGISTRARE CON LA STESSA CURA. STRUTTURALE: in sede parlamentare si è osservato che, pur dopo il rafforzamento del 2009, un controllo sistematico risultava di fatto impraticabile, perché 9 DEPUTATI E UNA SEGRETERIA non bastano a controllare effettivamente il lavoro di QUASI 10MILA DIPENDENTI dei servizi federali. POLITICO: i membri sono eletti a maggioranza dei componenti dell’assemblea, e ciò ha comportato che deputati di alcuni gruppi non siano stati eletti nell’organo — negli anni Ottanta e Novanta, e ancora nel 2018 e nel 2025. LA MAGGIORANZA ELEGGE I CONTROLLORI, E HA ESCLUSO</t>
+          <t>LE RISULTANZE E LA CONSEGUENZA NORMATIVA: la commissione sulla giustizia accertò che ex funzionari del ministero del regime e dei tribunali speciali e militari furono REINTEGRATI NEL SERVIZIO DELLO STATO SENZA OBIEZIONI, che quei giuristi PLASMARONO LA GIURISPRUDENZA DEL DOPOGUERRA e che ebbero UN RUOLO CENTRALE NELL’AMNISTIA DEGLI AUTORI DI CRIMINI DEL REGIME. Il ministro annunciò nell’ottobre 2016 che l’ingiustizia commessa dai giuristi tedeschi nel novecento sarebbe divenuta MATERIA OBBLIGATORIA nella formazione giuridica; DAL 1° GENNAIO 2022 lo studio dell’ingiustizia nazionalsocialista e di quella della dittatura socialista è componente obbligatoria del corso di laurea e del tirocinio in giurisprudenza. Una mostra itinerante circola dall’estate 2017. IL RILIEVO CRITICO, da registrare: una recensione osserva che l’opera documenta ciò che non riuscì e non dedica pari fondatezza a ciò che riuscì, cioè alla costruzione effettiva dello Stato di diritto</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — è il termine di paragone della TERZA proposta del 1984 (centralità del Parlamento nei controlli) e insieme della QUARTA (strumenti effettivi in capo all’opposizione): il modello esiste, ha rango costituzionale, e presenta entrambi i limiti che la Nota italiana aveva previsto</t>
+          <t>Dominio 10 e Tomo III — IL REPERTORIO NON REGISTRA ALCUN EQUIVALENTE ITALIANO: nessuna commissione indipendente istituita da un ministero italiano sul proprio passato, e nessuna conseguente materia obbligatoria di formazione</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -7034,40 +7578,44 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Serie tedesca delle commissioni indipendenti sulle continuità istituzionali dopo il 1945</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Repubblica federale tedesca</t>
+          <t>Inchiesta pubblica britannica sulle attività sotto copertura della polizia</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Regno Unito; inchiesta di rango legislativo istituita nel 2015, presieduta da un ex giudice dell’Alta Corte; udienze avviate nel 2020; obiettivo di completamento delle indagini entro il 2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Commissioni istituite dai ministeri stessi, con studiosi esterni e accesso agli archivi interni; risultati pubblicati presso editori commerciali e diffusi anche in opuscoli scaricabili e in mostre itineranti</t>
+          <t>Atti, verbali e relazioni pubblicati sul sito dell’inchiesta; relazione interlocutoria della prima tranche pubblicata il 29 giugno 2023, relativa agli anni 1968-1982</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>FENOMENO SISTEMICO, NON CASO ISOLATO: il ministero degli Esteri istituì una commissione indipendente sulla propria storia nel periodo nazionalsocialista e nella Repubblica federale, i cui risultati uscirono nel 2010; il ministero della Giustizia istituì nel 2012 una commissione scientifica indipendente sul modo in cui il dicastero trattò il proprio passato, che lavorò 4 ANNI e pubblicò nel 2016; il servizio informazioni estero istituì nel 2011 la propria commissione di storici. Nel 2016 è stato pubblicato anche un volume di rassegna su STATO E PROSPETTIVE DELLA RICERCA DI TUTTI GLI STUDI SULLE SUPREME AUTORITÀ DELLE DUE GERMANIE NEL DOPOGUERRA</t>
+          <t>OGGETTO: due reparti sotto copertura — uno della polizia metropolitana attivo dal 1968 al 2008, fondato per raccogliere informazioni su una campagna contro la guerra del Vietnam, e uno di ordine pubblico attivo dal 1999 al 2010. FRA IL 1968 E IL 2008 IL PRIMO REPARTO INFILTRÒ E SORVEGLIÒ OLTRE MILLE GRUPPI, fra cui partiti politici, organizzazioni antirazziste e movimenti pacifisti, impiegando circa CENTOTRENTANOVE agenti, di regola per 4 ANNI ciascuno</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>LE RISULTANZE E LA CONSEGUENZA NORMATIVA: la commissione sulla giustizia accertò che ex funzionari del ministero del regime e dei tribunali speciali e militari furono REINTEGRATI NEL SERVIZIO DELLO STATO SENZA OBIEZIONI, che quei giuristi PLASMARONO LA GIURISPRUDENZA DEL DOPOGUERRA e che ebbero UN RUOLO CENTRALE NELL’AMNISTIA DEGLI AUTORI DI CRIMINI DEL REGIME. Il ministro annunciò nell’ottobre 2016 che l’ingiustizia commessa dai giuristi tedeschi nel novecento sarebbe divenuta MATERIA OBBLIGATORIA nella formazione giuridica; DAL 1° GENNAIO 2022 lo studio dell’ingiustizia nazionalsocialista e di quella della dittatura socialista è componente obbligatoria del corso di laurea e del tirocinio in giurisprudenza. Una mostra itinerante circola dall’estate 2017. IL RILIEVO CRITICO, da registrare: una recensione osserva che l’opera documenta ciò che non riuscì e non dedica pari fondatezza a ciò che riuscì, cioè alla costruzione effettiva dello Stato di diritto</t>
+          <t>LE PRATICHE ACCERTATE: gli agenti ASSUMEVANO L’IDENTITÀ DI BAMBINI DEFUNTI per costruirsi una biografia, ottenendo documenti a quei nomi; la pratica risulta impiegata fra il 1968 e il 1994 e fu attuata SENZA CONSULTARE I GENITORI; a 19 famiglie è stato in seguito comunicato che i loro figli morti avevano prestato il nome. Agenti intrecciarono RELAZIONI INTIME con donne ignare della loro identità, in alcuni casi generando figli; nella sola prima tranche ne sono accertati almeno 6. Furono sorvegliate ALMENO 17 FAMIGLIE che chiedevano giustizia per un congiunto ucciso, fra cui quella di un ragazzo assassinato per movente razzista mentre la famiglia chiedeva un’indagine adeguata</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Dominio 10 e Tomo III — IL REPERTORIO NON REGISTRA ALCUN EQUIVALENTE ITALIANO: nessuna commissione indipendente istituita da un ministero italiano sul proprio passato, e nessuna conseguente materia obbligatoria di formazione</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
+          <t>LE CONCLUSIONI DELLA PRIMA TRANCHE: le infiltrazioni nei gruppi della sinistra, PUR CONDOTTE CON APPROVAZIONE GOVERNATIVA, furono GIUDICATE INGIUSTIFICATE e avrebbero dovuto cessare rapidamente; l’infiltrazione risultò legalmente giustificata da ragioni di sicurezza pubblica IN SOLI 3 CASI SU CENTINAIA di gruppi presi di mira; gli agenti raccolsero una quantità definita «impressionante» di informazioni sulla vita privata — corporatura, programmi di vacanza, dati bancari; furono presi di mira sindacalisti, alcuni dei quali ne patirono ANNI DI DISOCCUPAZIONE. LA SPINA DOCUMENTALE: le relazioni annuali del reparto dettagliano le spese per alloggi e veicoli, CON APPROVAZIONE GOVERNATIVA CONCESSA DI ANNO IN ANNO. Il presidente ha osservato che, se quelle questioni fossero state affrontate, difficilmente si sarebbe potuti giungere a una conclusione diversa dalla chiusura del reparto</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 3 × Dominio 2 — È LA DOCUMENTAZIONE PIÙ COMPLETA ESISTENTE DELL’ARCO DI INFILTRAZIONE; e la scoperta si deve alle donne ingannate, organizzatesi in associazione, non a un controllo istituzionale</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
@@ -7080,37 +7628,37 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Inchiesta pubblica britannica sulle attività sotto copertura della polizia</t>
+          <t>Commissione ristretta del Senato degli Stati Uniti per lo studio delle operazioni governative in materia di attività d’intelligence</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Regno Unito; inchiesta di rango legislativo istituita nel 2015, presieduta da un ex giudice dell’Alta Corte; udienze avviate nel 2020; obiettivo di completamento delle indagini entro il 2026</t>
+          <t>Istituita con voto del 27 gennaio 1975, 82 VOTI CONTRO 4; relazione finale del 29 aprile 1976</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Atti, verbali e relazioni pubblicati sul sito dell’inchiesta; relazione interlocutoria della prima tranche pubblicata il 29 giugno 2023, relativa agli anni 1968-1982</t>
+          <t>Atti e relazioni pubblicati; documentazione parzialmente classificata</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>OGGETTO: due reparti sotto copertura — uno della polizia metropolitana attivo dal 1968 al 2008, fondato per raccogliere informazioni su una campagna contro la guerra del Vietnam, e uno di ordine pubblico attivo dal 1999 al 2010. FRA IL 1968 E IL 2008 IL PRIMO REPARTO INFILTRÒ E SORVEGLIÒ OLTRE MILLE GRUPPI, fra cui partiti politici, organizzazioni antirazziste e movimenti pacifisti, impiegando circa CENTOTRENTANOVE agenti, di regola per 4 ANNI ciascuno</t>
+          <t>16 MESI di lavoro; CENTODIECIMILA DOCUMENTI esaminati; OLTRE OTTOCENTO TESTIMONI; cento26 sedute plenarie e quarantasei di sottocommissione; relazione finale di DUEMILASETTECENTODUE PAGINE. Indagò sull’agenzia informativa estera, sul servizio investigativo federale, sull’agenzia per la sicurezza delle comunicazioni, sull’amministrazione fiscale e sull’intelligence militare, per il periodo dagli anni 50 ai primi anni Settanta</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>LE PRATICHE ACCERTATE: gli agenti ASSUMEVANO L’IDENTITÀ DI BAMBINI DEFUNTI per costruirsi una biografia, ottenendo documenti a quei nomi; la pratica risulta impiegata fra il 1968 e il 1994 e fu attuata SENZA CONSULTARE I GENITORI; a 19 famiglie è stato in seguito comunicato che i loro figli morti avevano prestato il nome. Agenti intrecciarono RELAZIONI INTIME con donne ignare della loro identità, in alcuni casi generando figli; nella sola prima tranche ne sono accertati almeno 6. Furono sorvegliate ALMENO 17 FAMIGLIE che chiedevano giustizia per un congiunto ucciso, fra cui quella di un ragazzo assassinato per movente razzista mentre la famiglia chiedeva un’indagine adeguata</t>
+          <t>ACCERTAMENTI PRINCIPALI: il programma di controspionaggio interno operò DAL 1956 AL 1971 contro partiti politici, movimenti per i diritti civili, femministi, ambientalisti, indipendentisti e anche contro organizzazioni di estrema destra, con sorveglianza, INFILTRAZIONE ORGANIZZATIVA, invii anonimi, molestie di polizia e DISINFORMAZIONE MEDIANTE STORIE FALSE PIANTATE SULLA STAMPA, allo scopo dichiarato di disgregare e screditare. L’agenzia per la sicurezza delle comunicazioni otteneva dal 1945 copia di PRATICAMENTE TUTTI I TELEGRAMMI in entrata e uscita dal Paese, forniti dalle compagnie SENZA MANDATO, per TRENT’ANNI; dagli anni Sessanta teneva liste di sorveglianza di cittadini</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>LE CONCLUSIONI DELLA PRIMA TRANCHE: le infiltrazioni nei gruppi della sinistra, PUR CONDOTTE CON APPROVAZIONE GOVERNATIVA, furono GIUDICATE INGIUSTIFICATE e avrebbero dovuto cessare rapidamente; l’infiltrazione risultò legalmente giustificata da ragioni di sicurezza pubblica IN SOLI 3 CASI SU CENTINAIA di gruppi presi di mira; gli agenti raccolsero una quantità definita «impressionante» di informazioni sulla vita privata — corporatura, programmi di vacanza, dati bancari; furono presi di mira sindacalisti, alcuni dei quali ne patirono ANNI DI DISOCCUPAZIONE. LA SPINA DOCUMENTALE: le relazioni annuali del reparto dettagliano le spese per alloggi e veicoli, CON APPROVAZIONE GOVERNATIVA CONCESSA DI ANNO IN ANNO. Il presidente ha osservato che, se quelle questioni fossero state affrontate, difficilmente si sarebbe potuti giungere a una conclusione diversa dalla chiusura del reparto</t>
+          <t>DUE FATTI CHE VANNO REGISTRATI INSIEME. PRIMO: il presidente in carica CERCÒ DI LIMITARE L’INDAGINE E CHIESE CHE FOSSE PUBBLICATA SOLTANTO UNA SINTESI; il comitato lo sfidò e pubblicò la relazione integrale. SECONDO: quanto al programma di sperimentazione sul controllo mentale, il direttore dell’agenzia AVEVA GIÀ ORDINATO NEL 1973 LA DISTRUZIONE DEI FASCICOLI, e ALCUNI DOCUMENTI SOPRAVVISSERO SOLTANTO PERCHÉ ERANO STATI ARCHIVIATI NEL POSTO SBAGLIATO: ciò che il comitato poté vedere era una frazione di ciò che era esistito. Milioni di pagine restano tuttora non rilasciate e molti documenti rilasciati sono pesantemente censurati</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Dominio 3 × Dominio 2 — È LA DOCUMENTAZIONE PIÙ COMPLETA ESISTENTE DELL’ARCO DI INFILTRAZIONE; e la scoperta si deve alle donne ingannate, organizzatesi in associazione, non a un controllo istituzionale</t>
+          <t>Dominio 3; Tomo III — dalla commissione nascono le commissioni parlamentari permanenti di vigilanza, la legge sulla sorveglianza per l’intelligence estera e il divieto di assassinî politici</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -7119,48 +7667,56 @@
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K44" s="8" t="inlineStr"/>
-      <c r="L44" s="8" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — data esatta; e vanno recati risoluzione, voto e composizione</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>DATA CONFERMATA: risoluzione approvata il 27 GENNAIO 1975 CON 82 VOTI CONTRO 4. Segnatura dell'atto: S. Res. 21, novantaquattresimo Congresso; la risoluzione era stata presentata il 21 GENNAIO 1975 dal senatore John PASTORE. Presidente Frank CHURCH, vicepresidente John TOWER; 11 COMPONENTI, 6 democratici e 5 repubblicani; alla Commissione furono attribuiti POTERI DI CITAZIONE IN GIUDIZIO. RELAZIONE FINALE DEL 29 APRILE 1976, in 14 VOLUMI, con 96 RACCOMANDAZIONI; furono pubblicati inoltre 7 VOLUMI DI AUDIZIONI e, prima della relazione finale, la relazione interim sui presunti complotti di assassinio di dirigenti stranieri. MANDATO, nei 4 punti fissati dalla risoluzione: se l'agenzia informativa avesse condotto operazioni interne illegali; la condotta di operazioni interne di informazione e controinformazione contro cittadini statunitensi da parte dell'ufficio federale o di altre agenzie; origini e destinazione del Piano Huston; la necessita di una disciplina legislativa delle agenzie. ORIGINE, da recare perche e un caso di apertura per pressione giornalistica: l'inchiesta segui l'articolo di Seymour HERSH pubblicato dal New York Times il 22 DICEMBRE 1974, secondo cui l'agenzia spiava da oltre un decennio gli attivisti contrari alla guerra in violazione del proprio statuto. ESITI NORMATIVI: legge sulla sorveglianza informativa estera; ordine esecutivo 11905 che vieto l'assassinio di dirigenti stranieri; istituzione della commissione permanente del Senato sull'informazione. FRASE DA CITARE: la Commissione osservo che NON ESISTE ALCUNA AUTORITA COSTITUZIONALE INTRINSECA, PER IL PRESIDENTE O PER QUALSIASI AGENZIA INFORMATIVA, DI VIOLARE LA LEGGE.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Commissione ristretta del Senato degli Stati Uniti per lo studio delle operazioni governative in materia di attività d’intelligence</t>
+          <t>Gruppo di lavoro interagenzia sui documenti relativi ai crimini di guerra nazisti e del governo imperiale giapponese</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Istituita con voto del 27 gennaio 1975, 82 VOTI CONTRO 4; relazione finale del 29 aprile 1976</t>
+          <t>Stati Uniti; documenti versati e consultabili presso l’Archivio nazionale a College Park, Maryland; relazioni e guide pubblicate in rete</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Atti e relazioni pubblicati; documentazione parzialmente classificata</t>
+          <t>Istituito dalla legge del 1998 sulla divulgazione dei crimini di guerra nazisti e da quella del 2000 sul governo imperiale giapponese; composto da rappresentanti di 7 AGENZIE dell’esecutivo e da 3 MEMBRI PUBBLICI di nomina presidenziale; attivo dal 1999 al 31 marzo 2007, con due proroghe; costo di circa TRENTA MILIONI DI DOLLARI</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>16 MESI di lavoro; CENTODIECIMILA DOCUMENTI esaminati; OLTRE OTTOCENTO TESTIMONI; cento26 sedute plenarie e quarantasei di sottocommissione; relazione finale di DUEMILASETTECENTODUE PAGINE. Indagò sull’agenzia informativa estera, sul servizio investigativo federale, sull’agenzia per la sicurezza delle comunicazioni, sull’amministrazione fiscale e sull’intelligence militare, per il periodo dagli anni 50 ai primi anni Settanta</t>
+          <t>OLTRE 8 MILIONI E MEZZO DI PAGINE aperte al pubblico: un milione e due100.000 pagine dell’ufficio dei servizi strategici bellici; settantaquattromila pagine di fascicoli nominativi e per materia dell’agenzia informativa; oltre 3150mila pagine di fascicoli del servizio investigativo federale; quasi 3100.000 pagine di fascicoli dell’intelligence militare. È LA PIÙ VASTA OPERAZIONE DI DECLASSIFICAZIONE SU SINGOLO TEMA DELLA STORIA STATUNITENSE</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ACCERTAMENTI PRINCIPALI: il programma di controspionaggio interno operò DAL 1956 AL 1971 contro partiti politici, movimenti per i diritti civili, femministi, ambientalisti, indipendentisti e anche contro organizzazioni di estrema destra, con sorveglianza, INFILTRAZIONE ORGANIZZATIVA, invii anonimi, molestie di polizia e DISINFORMAZIONE MEDIANTE STORIE FALSE PIANTATE SULLA STAMPA, allo scopo dichiarato di disgregare e screditare. L’agenzia per la sicurezza delle comunicazioni otteneva dal 1945 copia di PRATICAMENTE TUTTI I TELEGRAMMI in entrata e uscita dal Paese, forniti dalle compagnie SENZA MANDATO, per TRENT’ANNI; dagli anni Sessanta teneva liste di sorveglianza di cittadini</t>
+          <t>IL MANDATO CONTENEVA ESPRESSAMENTE IL PUNTO CHE INTERESSA QUEST’OPERA: la legge avviò la ricerca non solo sui crimini, ma «SU QUALSIASI INDIVIDUO CON UN PASSATO NAZISTA CHE POSSA ESSERE STATO IMPIEGATO COME FONTE INFORMATIVA E PROTETTO DALL’AZIONE PENALE DOPO LA GUERRA». Il rapporto sui fascicoli dell’agenzia informativa dichiara che essa ha localizzato e declassificato fascicoli su UN NUMERO CONSISTENTE DI INDIVIDUI SOSPETTATI DI ATTIVITÀ CRIMINALE PER IL REGIME O I SUOI ALLEATI E SATELLITI</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>DUE FATTI CHE VANNO REGISTRATI INSIEME. PRIMO: il presidente in carica CERCÒ DI LIMITARE L’INDAGINE E CHIESE CHE FOSSE PUBBLICATA SOLTANTO UNA SINTESI; il comitato lo sfidò e pubblicò la relazione integrale. SECONDO: quanto al programma di sperimentazione sul controllo mentale, il direttore dell’agenzia AVEVA GIÀ ORDINATO NEL 1973 LA DISTRUZIONE DEI FASCICOLI, e ALCUNI DOCUMENTI SOPRAVVISSERO SOLTANTO PERCHÉ ERANO STATI ARCHIVIATI NEL POSTO SBAGLIATO: ciò che il comitato poté vedere era una frazione di ciò che era esistito. Milioni di pagine restano tuttora non rilasciate e molti documenti rilasciati sono pesantemente censurati</t>
+          <t>LA CRONOLOGIA DELLA RESISTENZA, DA REGISTRARE: l’agenzia informativa mantenne obiezioni per anni; SOLTANTO NEL 2006, DOPO CHE IL CONGRESSO EBBE PROROGATO IL MANDATO NEL MARZO 2005, LE RITIRÒ, declassificando altri centosettantaquattro fascicoli per circa ventisettemila pagine. Servirono una legge, due proroghe, 7 anni e trenta milioni di dollari — e anche così l’adempimento fu graduale</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Dominio 3; Tomo III — dalla commissione nascono le commissioni parlamentari permanenti di vigilanza, la legge sulla sorveglianza per l’intelligence estera e il divieto di assassinî politici</t>
+          <t>Tomo II e corpus sulla diaspora postbellica — è lo strumento diretto per i materiali già presenti nel progetto; si lega alla struttura clandestina tedesca del 1952</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -7169,102 +7725,106 @@
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — data esatta; e vanno recati risoluzione, voto e composizione</t>
-        </is>
-      </c>
-      <c r="K45" s="11" t="inlineStr">
-        <is>
-          <t>6.8.2026</t>
-        </is>
-      </c>
-      <c r="L45" s="11" t="inlineStr">
-        <is>
-          <t>DATA CONFERMATA: risoluzione approvata il 27 GENNAIO 1975 CON 82 VOTI CONTRO 4. Segnatura dell'atto: S. Res. 21, novantaquattresimo Congresso; la risoluzione era stata presentata il 21 GENNAIO 1975 dal senatore John PASTORE. Presidente Frank CHURCH, vicepresidente John TOWER; 11 COMPONENTI, 6 democratici e 5 repubblicani; alla Commissione furono attribuiti POTERI DI CITAZIONE IN GIUDIZIO. RELAZIONE FINALE DEL 29 APRILE 1976, in 14 VOLUMI, con 96 RACCOMANDAZIONI; furono pubblicati inoltre 7 VOLUMI DI AUDIZIONI e, prima della relazione finale, la relazione interim sui presunti complotti di assassinio di dirigenti stranieri. MANDATO, nei 4 punti fissati dalla risoluzione: se l'agenzia informativa avesse condotto operazioni interne illegali; la condotta di operazioni interne di informazione e controinformazione contro cittadini statunitensi da parte dell'ufficio federale o di altre agenzie; origini e destinazione del Piano Huston; la necessita di una disciplina legislativa delle agenzie. ORIGINE, da recare perche e un caso di apertura per pressione giornalistica: l'inchiesta segui l'articolo di Seymour HERSH pubblicato dal New York Times il 22 DICEMBRE 1974, secondo cui l'agenzia spiava da oltre un decennio gli attivisti contrari alla guerra in violazione del proprio statuto. ESITI NORMATIVI: legge sulla sorveglianza informativa estera; ordine esecutivo 11905 che vieto l'assassinio di dirigenti stranieri; istituzione della commissione permanente del Senato sull'informazione. FRASE DA CITARE: la Commissione osservo che NON ESISTE ALCUNA AUTORITA COSTITUZIONALE INTRINSECA, PER IL PRESIDENTE O PER QUALSIASI AGENZIA INFORMATIVA, DI VIOLARE LA LEGGE.</t>
-        </is>
-      </c>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr"/>
+      <c r="L45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Effrazione dell’ufficio distaccato del servizio investigativo federale a Media, Pennsylvania — 8 marzo 1971</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Stati Uniti</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Commissione ristretta della Camera dei rappresentanti sull’intelligence — Stati Uniti, 1975-1976</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Istituita nel febbraio 1975, ricostituita nel luglio 1975 sotto nuova presidenza; mandato in scadenza il 31 gennaio 1976</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>LA RELAZIONE FINALE NON FU MAI PUBBLICATA UFFICIALMENTE. Ampi estratti apparvero il 16 febbraio 1976 su un settimanale newyorkese sotto il titolo «Il rapporto sulla CIA che il presidente Ford non vuole farvi leggere»; una copia integrale della bozza fu pubblicata in Inghilterra</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>7 dissidenti riuniti in una autodenominata commissione di cittadini per indagare sull’ufficio federale ENTRARONO CON EFFRAZIONE e sottrassero OLTRE MILLE DOCUMENTI RISERVATI, consegnandoli alla stampa. Ne derivò l’esposizione pubblica del programma di controspionaggio interno e, 4 anni dopo, l’istituzione della commissione senatoriale</t>
+          <t>Indagò sulle attività illegali dell’agenzia informativa, del servizio investigativo federale e dell’agenzia per la sicurezza delle comunicazioni, in parallelo alla commissione senatoriale e sugli stessi testimoni</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>IL DATO CHE CHIUDE IL REPERTORIO: PRIMA DI QUELL’EFFRAZIONE NON ESISTEVA ALCUNA VIGILANZA UFFICIALE SULLE AGENZIE DI INTELLIGENCE. L’ultima componente rimasta anonima ha rivelato la propria partecipazione SOLTANTO NEL 2024, 50tré anni dopo</t>
+          <t>L’ACCERTAMENTO CHE LA DISTINGUE, ED È IL DATO DI PRIM’ORDINE: mentre la commissione del Senato attribuì gran parte della responsabilità delle azioni coperte all’agenzia, QUESTA COMMISSIONE TROVÒ PROVE CHIARE CHE GLI ORDINI PROVENIVANO DALL’UFFICIO DEL PRESIDENTE — «l’agenzia non se ne va al galoppo a condurre operazioni per conto proprio» — RESPINGENDO LA TESI DELL’ELEFANTE IMPAZZITO. Il presidente della commissione denunciò l’ostruzione dell’esecutivo: gli investigatori incontravano «molto linguaggio di cooperazione e molta attività di non cooperazione», e lamentò dichiarazioni ingannevoli e documenti trattenuti su operazioni coperte in Africa</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — l’intero sistema di controllo democratico dell’intelligence statunitense nasce da un furto con scasso; e i documenti sul controllo mentale sopravvissero a un ordine di distruzione PER ERRORE DI ARCHIVIAZIONE</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
+          <t>LA SOPPRESSIONE: il 15 gennaio 1976 il presidente scrisse che la pubblicazione sarebbe stata pregiudizievole per la sicurezza nazionale; la commissione regolamento concesse la proroga per la stampa SOLO A CONDIZIONE CHE LA CASA BIANCA APPROVASSE LA DIFFUSIONE; il presidente sostenne allora che la relazione stessa fosse documento classificato. LA CAMERA VOTÒ 246 CONTRO 124 PER NON DIFFONDERLA (la data e il 29 GENNAIO 1976: DISCREPANZA CHIUSA, concordano la rivista interna dell’agenzia informativa statunitense e 3 fonti indipendenti; il voto fu di 246 contro 124). Il presidente della commissione osservò: «LA CAMERA HA APPENA VOTATO DI NON DIFFONDERE UN DOCUMENTO CHE NON AVEVA LETTO. LA NOSTRA COMMISSIONE HA VOTATO DI DIFFONDERE UN DOCUMENTO CHE AVEVA LETTO.» Il giornalista che ottenne la bozza dichiarò di non poter essere lui il responsabile della soppressione del rapporto; rifiutò di rivelare la fonte, fu chiamato a deporre davanti al Congresso e sfuggì per poco al carcere. Nella versione pubblicata furono omessi gli allegati su operazioni e fonti specifiche</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — DUE COMMISSIONI, STESSO ANNO, STESSA MATERIA: quella che pubblicò attribuiva la responsabilità all’agenzia; QUELLA CHE FU SOPPRESSA LA ATTRIBUIVA AL VERTICE POLITICO</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr"/>
-      <c r="L46" s="8" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — E LA RELAZIONE FU IMPEDITA DAL PRESIDENTE E PUBBLICATA DA UN GIORNALE</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>Segnatura: H. Res. 591, novantaquattresimo Congresso, 1975; presidente Otis PIKE. IL FATTO CHE LA VOCE DEVE RECARE, ED E IL PIU RILEVANTE DELL'INTERA SERIE STATUNITENSE: la Casa Bianca nego dapprima l'accesso alle informazioni, quasi provocando una crisi giudiziaria; sotto minaccia di essere citato in giudizio il Presidente consenti l'accesso ai documenti dell'agenzia IN PRESTITO. MA IMPEDI ALLA COMMISSIONE DI PUBBLICARE UFFICIALMENTE LA PROPRIA RELAZIONE FINALE, E LA CAMERA NON SUPERO IL VETO. AMPI STRALCI DELLA RELAZIONE FURONO PERO FATTI FILTRARE AL VILLAGE VOICE E PUBBLICATI IL 16 FEBBRAIO 1976. Nel 1977 la versione del giornale fu pubblicata in volume nel Regno Unito con introduzione di Philip AGEE. E dunque un caso in cui UN ACCERTAMENTO PARLAMENTARE ESISTE MA NON E ATTO UFFICIALE, ed e conoscibile soltanto attraverso una fuga di notizie e un'edizione estera. Per il metodo dell'opera lo statuto di quella relazione va marcato: cio che se ne cita non e un atto pubblicato ma un testo trafugato, per quanto autentico. DIFFERENZA DI CONDOTTA DA REGISTRARE: a differenza della commissione senatoriale e della commissione presidenziale, che lasciarono determinare la propria agenda dall'esecutivo, questa commissione RIFIUTO di farlo, e fu la sola a chiedere con citazione formale gli atti del Comitato dei Quaranta, il 6 NOVEMBRE 1975.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Gruppo di lavoro interagenzia sui documenti relativi ai crimini di guerra nazisti e del governo imperiale giapponese</t>
+          <t>Studio della commissione ristretta del Senato statunitense sul programma di detenzione e interrogatorio dell’agenzia informativa</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; documenti versati e consultabili presso l’Archivio nazionale a College Park, Maryland; relazioni e guide pubblicate in rete</t>
+          <t>Stati Uniti; rapporto ufficiale del Senato numero 113-288, ordinato alle stampe il 9 dicembre 2014</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Istituito dalla legge del 1998 sulla divulgazione dei crimini di guerra nazisti e da quella del 2000 sul governo imperiale giapponese; composto da rappresentanti di 7 AGENZIE dell’esecutivo e da 3 MEMBRI PUBBLICI di nomina presidenziale; attivo dal 1999 al 31 marzo 2007, con due proroghe; costo di circa TRENTA MILIONI DI DOLLARI</t>
+          <t>Pubblicato SOLTANTO il sommario esecutivo con premessa, risultanze e conclusioni — circa cinquecento25 pagine, parzialmente espunte. IL RAPPORTO INTEGRALE, DI SEIMILASETTECENTO PAGINE CON TRENTOTTOMILA NOTE, RESTA CLASSIFICATO</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>OLTRE 8 MILIONI E MEZZO DI PAGINE aperte al pubblico: un milione e due100.000 pagine dell’ufficio dei servizi strategici bellici; settantaquattromila pagine di fascicoli nominativi e per materia dell’agenzia informativa; oltre 3150mila pagine di fascicoli del servizio investigativo federale; quasi 3100.000 pagine di fascicoli dell’intelligence militare. È LA PIÙ VASTA OPERAZIONE DI DECLASSIFICAZIONE SU SINGOLO TEMA DELLA STORIA STATUNITENSE</t>
+          <t>Deliberata il 5 marzo 2009 con voto 14 a uno; 3 anni e mezzo di lavoro; il personale esaminò OLTRE 6 MILIONI E 3100.000 PAGINE di documenti dell’agenzia; studio approvato il 13 dicembre 2012 con 9 voti contro 6; declassificazione e diffusione deliberate il 3 aprile 2014 con 11 voti contro 3. Oggetto: la detenzione segreta all’estero di ALMENO 119 individui e l’uso di tecniche coercitive, in alcuni casi equivalenti a tortura</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>IL MANDATO CONTENEVA ESPRESSAMENTE IL PUNTO CHE INTERESSA QUEST’OPERA: la legge avviò la ricerca non solo sui crimini, ma «SU QUALSIASI INDIVIDUO CON UN PASSATO NAZISTA CHE POSSA ESSERE STATO IMPIEGATO COME FONTE INFORMATIVA E PROTETTO DALL’AZIONE PENALE DOPO LA GUERRA». Il rapporto sui fascicoli dell’agenzia informativa dichiara che essa ha localizzato e declassificato fascicoli su UN NUMERO CONSISTENTE DI INDIVIDUI SOSPETTATI DI ATTIVITÀ CRIMINALE PER IL REGIME O I SUOI ALLEATI E SATELLITI</t>
+          <t>RISULTANZE SULLE INFORMATIVE AL PARLAMENTO: la piena commissione NON FU INFORMATA sulle tecniche fino a poche ore prima che il programma fosse reso pubblico dal presidente il 6 settembre 2006; le informative contenevano NUMEROSE INESATTEZZE, comprese descrizioni inesatte di come le tecniche fossero applicate e di quali informazioni producessero; e l’agenzia comunicò all’ufficio legale del ministero della Giustizia, in sede classificata, CHE NESSUN SENATORE AVEVA SOLLEVATO OBIEZIONI, mentre diversi senatori le avevano espresse per iscritto</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>LA CRONOLOGIA DELLA RESISTENZA, DA REGISTRARE: l’agenzia informativa mantenne obiezioni per anni; SOLTANTO NEL 2006, DOPO CHE IL CONGRESSO EBBE PROROGATO IL MANDATO NEL MARZO 2005, LE RITIRÒ, declassificando altri centosettantaquattro fascicoli per circa ventisettemila pagine. Servirono una legge, due proroghe, 7 anni e trenta milioni di dollari — e anche così l’adempimento fu graduale</t>
+          <t>IL FATTO CENTRALE, ACCERTATO E AMMESSO: alla commissione era stato fornito, presso i locali dell’agenzia, un sistema informatico che l’agenzia assicurava separato e accessibile ai soli funzionari parlamentari. L’AGENZIA ACCEDETTE E PERQUISÌ I FILE DELLA COMMISSIONE. Il direttore negò pubblicamente — «nulla potrebbe essere più lontano dalla verità». L’11 marzo 2014 la presidente della commissione riferì in aula di essere stata informata della perquisizione il 15 gennaio 2014 e di temere UNA VIOLAZIONE DEI PRINCIPI DELLA SEPARAZIONE DEI POTERI; denunciò inoltre la rimozione di documenti e la richiesta di un’indagine federale sulla condotta degli investigatori parlamentari. IL 31 LUGLIO 2014 L’ISPETTORE GENERALE DELL’AGENZIA ACCERTÒ L’ACCESSO IMPROPRIO E IL DIRETTORE PRESENTÒ SCUSE; L’ISPETTORE RIMISE LA QUESTIONE AL MINISTERO DELLA GIUSTIZIA PER L’AZIONE PENALE, E IL MINISTERO RIFIUTÒ DI PROCEDERE</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Tomo II e corpus sulla diaspora postbellica — è lo strumento diretto per i materiali già presenti nel progetto; si lega alla struttura clandestina tedesca del 1952</t>
+          <t>Dominio 3 × Dominio 2 — un’agenzia perquisisce i computer del Parlamento che la sta indagando, l’accertamento arriva, le scuse pure, e la sanzione no</t>
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr">
@@ -7284,37 +7844,37 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Commissione ristretta della Camera dei rappresentanti sull’intelligence — Stati Uniti, 1975-1976</t>
+          <t>Legge statunitense del 1992 sulla raccolta dei documenti relativi all’assassinio del presidente Kennedy — legge pubblica 102-526</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Istituita nel febbraio 1975, ricostituita nel luglio 1975 sotto nuova presidenza; mandato in scadenza il 31 gennaio 1976</t>
+          <t>Stati Uniti; raccolta conservata presso l’Archivio nazionale; documenti pubblicati progressivamente in rete</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>LA RELAZIONE FINALE NON FU MAI PUBBLICATA UFFICIALMENTE. Ampi estratti apparvero il 16 febbraio 1976 su un settimanale newyorkese sotto il titolo «Il rapporto sulla CIA che il presidente Ford non vuole farvi leggere»; una copia integrale della bozza fu pubblicata in Inghilterra</t>
+          <t>Approvata dal Senato il 27 luglio 1992 per alzata di mano e dalla Camera il 30 settembre senza opposizione; firmata il 26 ottobre 1992. Titolo: legge per la SOLLECITA divulgazione dei documenti rilevanti</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Indagò sulle attività illegali dell’agenzia informativa, del servizio investigativo federale e dell’agenzia per la sicurezza delle comunicazioni, in parallelo alla commissione senatoriale e sugli stessi testimoni</t>
+          <t>LA RACCOLTA: DUECENTOSESSANTOTTOMILACENTO16 documenti per OLTRE 5 MILIONI DI PAGINE. Circa l’ottantotto per cento aperto integralmente; un ulteriore 11 per cento accessibile in parte, con le porzioni riservate rimosse</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>L’ACCERTAMENTO CHE LA DISTINGUE, ED È IL DATO DI PRIM’ORDINE: mentre la commissione del Senato attribuì gran parte della responsabilità delle azioni coperte all’agenzia, QUESTA COMMISSIONE TROVÒ PROVE CHIARE CHE GLI ORDINI PROVENIVANO DALL’UFFICIO DEL PRESIDENTE — «l’agenzia non se ne va al galoppo a condurre operazioni per conto proprio» — RESPINGENDO LA TESI DELL’ELEFANTE IMPAZZITO. Il presidente della commissione denunciò l’ostruzione dell’esecutivo: gli investigatori incontravano «molto linguaggio di cooperazione e molta attività di non cooperazione», e lamentò dichiarazioni ingannevoli e documenti trattenuti su operazioni coperte in Africa</t>
+          <t>LA CLAUSOLA CHE CONTA: la legge imponeva la divulgazione integrale di TUTTI i documenti ENTRO IL 26 OTTOBRE 2017, cioè 25 anni dopo l’entrata in vigore, SALVO CHE IL PRESIDENTE CERTIFICHI che il rinvio è reso necessario da un danno identificabile alla difesa militare, alle operazioni informative, all’applicazione della legge o alla condotta delle relazioni estere, E CHE TALE DANNO SIA DI GRAVITÀ TALE DA PREVALERE SULL’INTERESSE PUBBLICO ALLA DIVULGAZIONE</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>LA SOPPRESSIONE: il 15 gennaio 1976 il presidente scrisse che la pubblicazione sarebbe stata pregiudizievole per la sicurezza nazionale; la commissione regolamento concesse la proroga per la stampa SOLO A CONDIZIONE CHE LA CASA BIANCA APPROVASSE LA DIFFUSIONE; il presidente sostenne allora che la relazione stessa fosse documento classificato. LA CAMERA VOTÒ 246 CONTRO 124 PER NON DIFFONDERLA (la data e il 29 GENNAIO 1976: DISCREPANZA CHIUSA, concordano la rivista interna dell’agenzia informativa statunitense e 3 fonti indipendenti; il voto fu di 246 contro 124). Il presidente della commissione osservò: «LA CAMERA HA APPENA VOTATO DI NON DIFFONDERE UN DOCUMENTO CHE NON AVEVA LETTO. LA NOSTRA COMMISSIONE HA VOTATO DI DIFFONDERE UN DOCUMENTO CHE AVEVA LETTO.» Il giornalista che ottenne la bozza dichiarò di non poter essere lui il responsabile della soppressione del rapporto; rifiutò di rivelare la fonte, fu chiamato a deporre davanti al Congresso e sfuggì per poco al carcere. Nella versione pubblicata furono omessi gli allegati su operazioni e fonti specifiche</t>
+          <t>LA CRONOLOGIA DELLE PROROGHE, CHE È LA MISURA: certificazione temporanea del 31 ottobre 2017; certificazione del 26 aprile 2018, con rinvio fino al 26 ottobre 2021 e ordine alle agenzie di riesaminare ogni espunzione nel triennio; memorandum del 22 ottobre 2021, relativo a CIRCA 14MILA DOCUMENTI ANCORA CLASSIFICATI, con prima diffusione al 15 dicembre 2021 — in quella data furono pubblicati MILLEQUATTROCENTONOVANTUNO documenti integrali — e rinvio del resto al 15 dicembre 2022; ulteriori certificazioni nel 2022 e nel 2023; ordine esecutivo del gennaio 2025 esteso anche ai documenti su altri due assassinî. TRENTATRÉ ANNI DOPO LA LEGGE E 8 DOPO LA SCADENZA, IL PROCESSO È ANCORA IN CORSO</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — DUE COMMISSIONI, STESSO ANNO, STESSA MATERIA: quella che pubblicò attribuiva la responsabilità all’agenzia; QUELLA CHE FU SOPPRESSA LA ATTRIBUIVA AL VERTICE POLITICO</t>
+          <t>Tomo III — LA LEZIONE: una scadenza corredata di clausola di certificazione NON È UNA SCADENZA, ma un termine predefinito soggetto a rinnovo. Si legga accanto alla disposizione spagnola del 2022, che si diede un anno e non l’ha rispettato in 4</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -7323,56 +7883,48 @@
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — E LA RELAZIONE FU IMPEDITA DAL PRESIDENTE E PUBBLICATA DA UN GIORNALE</t>
-        </is>
-      </c>
-      <c r="K48" s="11" t="inlineStr">
-        <is>
-          <t>6.8.2026</t>
-        </is>
-      </c>
-      <c r="L48" s="11" t="inlineStr">
-        <is>
-          <t>Segnatura: H. Res. 591, novantaquattresimo Congresso, 1975; presidente Otis PIKE. IL FATTO CHE LA VOCE DEVE RECARE, ED E IL PIU RILEVANTE DELL'INTERA SERIE STATUNITENSE: la Casa Bianca nego dapprima l'accesso alle informazioni, quasi provocando una crisi giudiziaria; sotto minaccia di essere citato in giudizio il Presidente consenti l'accesso ai documenti dell'agenzia IN PRESTITO. MA IMPEDI ALLA COMMISSIONE DI PUBBLICARE UFFICIALMENTE LA PROPRIA RELAZIONE FINALE, E LA CAMERA NON SUPERO IL VETO. AMPI STRALCI DELLA RELAZIONE FURONO PERO FATTI FILTRARE AL VILLAGE VOICE E PUBBLICATI IL 16 FEBBRAIO 1976. Nel 1977 la versione del giornale fu pubblicata in volume nel Regno Unito con introduzione di Philip AGEE. E dunque un caso in cui UN ACCERTAMENTO PARLAMENTARE ESISTE MA NON E ATTO UFFICIALE, ed e conoscibile soltanto attraverso una fuga di notizie e un'edizione estera. Per il metodo dell'opera lo statuto di quella relazione va marcato: cio che se ne cita non e un atto pubblicato ma un testo trafugato, per quanto autentico. DIFFERENZA DI CONDOTTA DA REGISTRARE: a differenza della commissione senatoriale e della commissione presidenziale, che lasciarono determinare la propria agenda dall'esecutivo, questa commissione RIFIUTO di farlo, e fu la sola a chiedere con citazione formale gli atti del Comitato dei Quaranta, il 6 NOVEMBRE 1975.</t>
-        </is>
-      </c>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr"/>
+      <c r="L48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Studio della commissione ristretta del Senato statunitense sul programma di detenzione e interrogatorio dell’agenzia informativa</t>
+          <t>Progetto statunitense di declassificazione sul Cile, 1999-2000</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; rapporto ufficiale del Senato numero 113-288, ordinato alle stampe il 9 dicembre 2014</t>
+          <t>Stati Uniti; documenti pubblicati sul portale del Dipartimento di Stato e raccolti dall’archivio di sicurezza nazionale universitario</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Pubblicato SOLTANTO il sommario esecutivo con premessa, risultanze e conclusioni — circa cinquecento25 pagine, parzialmente espunte. IL RAPPORTO INTEGRALE, DI SEIMILASETTECENTO PAGINE CON TRENTOTTOMILA NOTE, RESTA CLASSIFICATO</t>
+          <t>Revisione discrezionale disposta dal presidente nel 1999 e coordinata dallo staff del Consiglio di sicurezza nazionale, su documenti relativi ad abusi dei diritti umani, terrorismo e altri atti di violenza politica prima e durante il regime militare</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Deliberata il 5 marzo 2009 con voto 14 a uno; 3 anni e mezzo di lavoro; il personale esaminò OLTRE 6 MILIONI E 3100.000 PAGINE di documenti dell’agenzia; studio approvato il 13 dicembre 2012 con 9 voti contro 6; declassificazione e diffusione deliberate il 3 aprile 2014 con 11 voti contro 3. Oggetto: la detenzione segreta all’estero di ALMENO 119 individui e l’uso di tecniche coercitive, in alcuni casi equivalenti a tortura</t>
+          <t>3 DIFFUSIONI. 30 GIUGNO 1999: circa CINQUEMILAOTTOCENTO documenti, sul periodo 1973-1978. 8 OTTOBRE 1999: oltre MILLECENTO documenti — circa 3150 del Dipartimento di Stato, centosessanta dell’agenzia informativa, quattrocentotrenta del servizio investigativo federale — sul periodo 1968-1973. 13 NOVEMBRE 2000: terza e ultima diffusione di OLTRE 16MILA DOCUMENTI per PIÙ DI 50MILA PAGINE: circa 13mila50 del Dipartimento di Stato, mille5150 dell’agenzia informativa, seicentoventi del servizio investigativo, trecentosettanta della Difesa, trecento10 dell’Archivio nazionale, cento10 del Consiglio di sicurezza, 50 della Giustizia. Vi rientrano SETTECENTO DOCUMENTI CHE LA DIREZIONE OPERAZIONI DELL’AGENZIA SI ERA RIFIUTATA DI RILASCIARE, relativi a operazioni coperte fra il 1968 e il 1975</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>RISULTANZE SULLE INFORMATIVE AL PARLAMENTO: la piena commissione NON FU INFORMATA sulle tecniche fino a poche ore prima che il programma fosse reso pubblico dal presidente il 6 settembre 2006; le informative contenevano NUMEROSE INESATTEZZE, comprese descrizioni inesatte di come le tecniche fossero applicate e di quali informazioni producessero; e l’agenzia comunicò all’ufficio legale del ministero della Giustizia, in sede classificata, CHE NESSUN SENATORE AVEVA SOLLEVATO OBIEZIONI, mentre diversi senatori le avevano espresse per iscritto</t>
+          <t>CONTENUTI PERTINENTI AL TOMO SECONDO: informative dell’agenzia al Dipartimento di Stato SULL’OPERAZIONE CONDOR e su assassinî pianificati all’estero; documenti che per la prima volta collegano il capo dello Stato a due agenti dei servizi poi legati all’assassinio di un ex ministro degli Esteri e della sua assistente nella capitale statunitense; rapporti sul capo della polizia segreta, sui suoi incontri con funzionari statunitensi e sui suoi sforzi per OSTACOLARE LE INDAGINI STATUNITENSI su quell’assassinio. Il 19 settembre 2000 l’agenzia riconobbe che il capo della polizia segreta era stato un proprio informatore</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>IL FATTO CENTRALE, ACCERTATO E AMMESSO: alla commissione era stato fornito, presso i locali dell’agenzia, un sistema informatico che l’agenzia assicurava separato e accessibile ai soli funzionari parlamentari. L’AGENZIA ACCEDETTE E PERQUISÌ I FILE DELLA COMMISSIONE. Il direttore negò pubblicamente — «nulla potrebbe essere più lontano dalla verità». L’11 marzo 2014 la presidente della commissione riferì in aula di essere stata informata della perquisizione il 15 gennaio 2014 e di temere UNA VIOLAZIONE DEI PRINCIPI DELLA SEPARAZIONE DEI POTERI; denunciò inoltre la rimozione di documenti e la richiesta di un’indagine federale sulla condotta degli investigatori parlamentari. IL 31 LUGLIO 2014 L’ISPETTORE GENERALE DELL’AGENZIA ACCERTÒ L’ACCESSO IMPROPRIO E IL DIRETTORE PRESENTÒ SCUSE; L’ISPETTORE RIMISE LA QUESTIONE AL MINISTERO DELLA GIUSTIZIA PER L’AZIONE PENALE, E IL MINISTERO RIFIUTÒ DI PROCEDERE</t>
+          <t>I DUE RILIEVI, DA REGISTRARE. CRITICO: molti documenti dell’agenzia restarono PESANTEMENTE ESPUNTI, e fu lamentata la scarsità di documentazione proprio sul sostegno informativo alla polizia segreta e sull’Operazione Condor. E IL MECCANISMO DI APERTURA, CHE NON COMPARE ALTROVE IN QUESTO REPERTORIO: la parte trattenuta nel 1999-2000 fu declassificata 17 ANNI DOPO, e soltanto perché IL GOVERNO DEL PAESE CHE AVEVA SUBÌTO NE FECE RICHIESTA; la consegna avvenne il 23 settembre 2016, e le famiglie delle vittime furono avvisate in anticipo</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Dominio 3 × Dominio 2 — un’agenzia perquisisce i computer del Parlamento che la sta indagando, l’accertamento arriva, le scuse pure, e la sanzione no</t>
+          <t>Tomo II — asse sudamericano; Metodologia — un archivio si apre anche su richiesta diplomatica del Paese offeso</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -7392,37 +7944,37 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Legge statunitense del 1992 sulla raccolta dei documenti relativi all’assassinio del presidente Kennedy — legge pubblica 102-526</t>
+          <t>Foreign Relations of the United States — serie documentaria ufficiale, volumi sull’Europa occidentale</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; raccolta conservata presso l’Archivio nazionale; documenti pubblicati progressivamente in rete</t>
+          <t>Consultabile integralmente in rete sul sito dell’ufficio dello storico del Dipartimento di Stato</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Approvata dal Senato il 27 luglio 1992 per alzata di mano e dalla Camera il 30 settembre senza opposizione; firmata il 26 ottobre 1992. Titolo: legge per la SOLLECITA divulgazione dei documenti rilevanti</t>
+          <t>Serie avviata nel 1861, oltre CINQUECENTO volumi; PER LEGGE deve costituire un resoconto «completo, accurato e affidabile» della politica estera e dell’attività diplomatica</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>LA RACCOLTA: DUECENTOSESSANTOTTOMILACENTO16 documenti per OLTRE 5 MILIONI DI PAGINE. Circa l’ottantotto per cento aperto integralmente; un ulteriore 11 per cento accessibile in parte, con le porzioni riservate rimosse</t>
+          <t>I DUE DOCUMENTI CHIAVE PER QUEST’OPERA. Volume dodicesimo della serie 1964-1968, pubblicato il 16 aprile 2001, documento 133: verbale della riunione del comitato interagenzia per le operazioni coperte del 22 AGOSTO 1967, voce «Italia — programma di azione coperta per l’esercizio 1968»; il comitato accolse con favore la RIDUZIONE ANTICIPATA del sostegno politico coperto ai partiti italiani, e il documento istruttorio del 4 agosto osservava che la prosecuzione di un programma di azione coperta su larga scala in Italia NON AVREBBE PIÙ AVUTO PERTINENZA, essendo conseguita l’unificazione socialista e disponendo i gruppi politici di fondi interni. Volume quarantunesimo della serie 1969-1976, documento 180: verbale della riunione dell’11 MARZO 1969, alla presenza fra gli altri del consigliere per la sicurezza nazionale e del direttore dell’agenzia informativa, con una ESPOSIZIONE DETTAGLIATA SU ORIGINI, RELAZIONI, LIVELLI DI FINANZIAMENTO E RISULTATI DEL PROGRAMMA DI SOSTEGNO POLITICO COPERTO A PARTITI E ORGANIZZAZIONI SINDACALI ITALIANI NEGLI ANNI 1948-1968</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LA CLAUSOLA CHE CONTA: la legge imponeva la divulgazione integrale di TUTTI i documenti ENTRO IL 26 OTTOBRE 2017, cioè 25 anni dopo l’entrata in vigore, SALVO CHE IL PRESIDENTE CERTIFICHI che il rinvio è reso necessario da un danno identificabile alla difesa militare, alle operazioni informative, all’applicazione della legge o alla condotta delle relazioni estere, E CHE TALE DANNO SIA DI GRAVITÀ TALE DA PREVALERE SULL’INTERESSE PUBBLICO ALLA DIVULGAZIONE</t>
+          <t>ESITO REGISTRATO NEL VERBALE: il sostegno era stato drasticamente ridotto e infine CESSATO DEL TUTTO ALLA FINE DELL’ESERCIZIO 1968, ritenendosi che gli italiani fossero in grado di finanziare da soli i propri partiti; i presenti furono unanimi nel ritenere che NON VI FOSSE REALE GIUSTIFICAZIONE PER UNA RIPRESA. Il presidente chiese all’agenzia un documento riepilogativo che coprisse anche IL FINANZIAMENTO SOVIETICO E COMUNISTA e le fonti disponibili ai partiti non comunisti. Uno studio dell’archivio universitario di sicurezza nazionale stima l’aiuto coperto all’Italia in circa 5 MILIONI DI DOLLARI ANNUI dalla fine degli anni Quaranta ai primi anni Sessanta</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>LA CRONOLOGIA DELLE PROROGHE, CHE È LA MISURA: certificazione temporanea del 31 ottobre 2017; certificazione del 26 aprile 2018, con rinvio fino al 26 ottobre 2021 e ordine alle agenzie di riesaminare ogni espunzione nel triennio; memorandum del 22 ottobre 2021, relativo a CIRCA 14MILA DOCUMENTI ANCORA CLASSIFICATI, con prima diffusione al 15 dicembre 2021 — in quella data furono pubblicati MILLEQUATTROCENTONOVANTUNO documenti integrali — e rinvio del resto al 15 dicembre 2022; ulteriori certificazioni nel 2022 e nel 2023; ordine esecutivo del gennaio 2025 esteso anche ai documenti su altri due assassinî. TRENTATRÉ ANNI DOPO LA LEGGE E 8 DOPO LA SCADENZA, IL PROCESSO È ANCORA IN CORSO</t>
+          <t>AVVERTENZA SULLA SERIE, DA REGISTRARE PERCHÉ RIGUARDA L’AFFIDABILITÀ DELLA FONTE: la storia ufficiale della serie stessa documenta che un volume relativo all’Iran FU PUBBLICATO PRIVO DELLA DOCUMENTAZIONE DI UNA RILEVANTE OPERAZIONE COPERTA NOTORIAMENTE AVVENUTA, e che ciò provocò una crisi e LE DIMISSIONI DEL PRESIDENTE DEL COMITATO SCIENTIFICO CONSULTIVO. La serie ufficiale ha dunque già omesso operazioni coperte: va usata come fonte primaria E verificata</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — LA LEZIONE: una scadenza corredata di clausola di certificazione NON È UNA SCADENZA, ma un termine predefinito soggetto a rinnovo. Si legga accanto alla disposizione spagnola del 2022, che si diede un anno e non l’ha rispettato in 4</t>
+          <t>Dominio 3 × Dominio 2 — è la fonte primaria statunitense sull’intervento politico in Italia, con numeri di documento</t>
         </is>
       </c>
       <c r="H50" s="3" t="inlineStr">
@@ -7442,44 +7994,40 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Progetto statunitense di declassificazione sul Cile, 1999-2000</t>
+          <t>Legge statunitense sulla libertà di informazione — 1966 e successive modifiche</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; documenti pubblicati sul portale del Dipartimento di Stato e raccolti dall’archivio di sicurezza nazionale universitario</t>
+          <t>Stati Uniti; si applica alle agenzie dell’esecutivo federale, NON al Congresso, alla magistratura né agli enti statali e locali</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Revisione discrezionale disposta dal presidente nel 1999 e coordinata dallo staff del Consiglio di sicurezza nazionale, su documenti relativi ad abusi dei diritti umani, terrorismo e altri atti di violenza politica prima e durante il regime militare</t>
+          <t>9 eccezioni tassative; richiesta esperibile da chiunque; dal 1974 con termini, penalità, esenzione dai costi per giornalisti e organizzazioni d’interesse pubblico, e SINDACATO GIURISDIZIONALE SUI DINIEGHI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3 DIFFUSIONI. 30 GIUGNO 1999: circa CINQUEMILAOTTOCENTO documenti, sul periodo 1973-1978. 8 OTTOBRE 1999: oltre MILLECENTO documenti — circa 3150 del Dipartimento di Stato, centosessanta dell’agenzia informativa, quattrocentotrenta del servizio investigativo federale — sul periodo 1968-1973. 13 NOVEMBRE 2000: terza e ultima diffusione di OLTRE 16MILA DOCUMENTI per PIÙ DI 50MILA PAGINE: circa 13mila50 del Dipartimento di Stato, mille5150 dell’agenzia informativa, seicentoventi del servizio investigativo, trecentosettanta della Difesa, trecento10 dell’Archivio nazionale, cento10 del Consiglio di sicurezza, 50 della Giustizia. Vi rientrano SETTECENTO DOCUMENTI CHE LA DIREZIONE OPERAZIONI DELL’AGENZIA SI ERA RIFIUTATA DI RILASCIARE, relativi a operazioni coperte fra il 1968 e il 1975</t>
+          <t>LA GENESI, CHE VA REGISTRATA PER INTERO. La proposta nacque da oltre un decennio di audizioni parlamentari; VENTISETTE AGENZIE GOVERNATIVE, COMPRESO IL MINISTERO DELLA GIUSTIZIA, SOSTENNERO CHE AVREBBE VIOLATO LA SEPARAZIONE DEI POTERI; il presidente vi si opponeva privatamente. Passò al Senato il 13 ottobre 1965 e alla Camera il 20 giugno 1966 CON TRECENTOSEI VOTI CONTRO NESSUNO. Fu firmata il 4 luglio 1966, MA IL PRESIDENTE RIFIUTÒ DI TENERE LA CERIMONIA PUBBLICA DI FIRMA che riservava alle leggi importanti, e la dichiarazione di firma insisteva sulle eccezioni di sicurezza nazionale e sul «margine di interpretazione». Entrò in vigore il 4 luglio 1967</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>CONTENUTI PERTINENTI AL TOMO SECONDO: informative dell’agenzia al Dipartimento di Stato SULL’OPERAZIONE CONDOR e su assassinî pianificati all’estero; documenti che per la prima volta collegano il capo dello Stato a due agenti dei servizi poi legati all’assassinio di un ex ministro degli Esteri e della sua assistente nella capitale statunitense; rapporti sul capo della polizia segreta, sui suoi incontri con funzionari statunitensi e sui suoi sforzi per OSTACOLARE LE INDAGINI STATUNITENSI su quell’assassinio. Il 19 settembre 2000 l’agenzia riconobbe che il capo della polizia segreta era stato un proprio informatore</t>
+          <t>LA LEGGE ERA PRIVA DI DENTI. Le agenzie arrivavano a chiedere UN DOLLARO A PAGINA E 7 DOLLARI L’ORA per la ricerca, quando il salario orario mediano era intorno ai 4 dollari. Dopo lo scandalo che travolse la presidenza, e fallito il negoziato con l’amministrazione, IL CONGRESSO APPROVÒ NEL 1974 LE MODIFICHE CHE LA RESERO EFFICACE. IL PRESIDENTE LE POSE IL VETO — spinto dal proprio capo di gabinetto, dal vice e dal capo dell’ufficio legale del ministero della Giustizia, preoccupati per le fughe di notizie e per la costituzionalità. IL CONGRESSO SUPERÒ IL VETO: la votazione al Senato sul veto presidenziale ebbe luogo il 21 novembre 1974, e le modifiche entrarono in vigore il 19 febbraio 1975</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>I DUE RILIEVI, DA REGISTRARE. CRITICO: molti documenti dell’agenzia restarono PESANTEMENTE ESPUNTI, e fu lamentata la scarsità di documentazione proprio sul sostegno informativo alla polizia segreta e sull’Operazione Condor. E IL MECCANISMO DI APERTURA, CHE NON COMPARE ALTROVE IN QUESTO REPERTORIO: la parte trattenuta nel 1999-2000 fu declassificata 17 ANNI DOPO, e soltanto perché IL GOVERNO DEL PAESE CHE AVEVA SUBÌTO NE FECE RICHIESTA; la consegna avvenne il 23 settembre 2016, e le famiglie delle vittime furono avvisate in anticipo</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — asse sudamericano; Metodologia — un archivio si apre anche su richiesta diplomatica del Paese offeso</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr">
+          <t>Metodologia — LO STRUMENTO CHE HA PRODOTTO BUONA PARTE DI QUESTO REPERTORIO FU AVVERSATO DA VENTISETTE AGENZIE, FIRMATO SENZA CERIMONIA, LASCIATO INEFFICACE PER 8 ANNI, E RESO OPERANTE SOLTANTO SUPERANDO UN VETO PRESIDENZIALE. Modifiche successive: 1976 sulle eccezioni, 1986, 1996 sui documenti elettronici, 2002 con limiti alle richieste di agenti stranieri ai servizi, 2007 e 2016</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H51" s="3" t="inlineStr"/>
       <c r="I51" s="3" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr">
         <is>
@@ -7492,37 +8040,37 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Foreign Relations of the United States — serie documentaria ufficiale, volumi sull’Europa occidentale</t>
+          <t>Compilazione interna dell’agenzia informativa statunitense sulle attività eccedenti il proprio statuto — «i gioielli di famiglia»</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Consultabile integralmente in rete sul sito dell’ufficio dello storico del Dipartimento di Stato</t>
+          <t>Stati Uniti; pubblicata sul sito dell’agenzia e raccolta dall’archivio universitario di sicurezza nazionale</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Serie avviata nel 1861, oltre CINQUECENTO volumi; PER LEGGE deve costituire un resoconto «completo, accurato e affidabile» della politica estera e dell’attività diplomatica</t>
+          <t>Pubblicata il 25 GIUGNO 2007, con espunzioni comprendenti PAGINE INTERE. L’archivio universitario aveva presentato la richiesta di accesso 15 ANNI PRIMA, nel 1992. TRENTAQUATTRO ANNI DALLA COMPILAZIONE</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>I DUE DOCUMENTI CHIAVE PER QUEST’OPERA. Volume dodicesimo della serie 1964-1968, pubblicato il 16 aprile 2001, documento 133: verbale della riunione del comitato interagenzia per le operazioni coperte del 22 AGOSTO 1967, voce «Italia — programma di azione coperta per l’esercizio 1968»; il comitato accolse con favore la RIDUZIONE ANTICIPATA del sostegno politico coperto ai partiti italiani, e il documento istruttorio del 4 agosto osservava che la prosecuzione di un programma di azione coperta su larga scala in Italia NON AVREBBE PIÙ AVUTO PERTINENZA, essendo conseguita l’unificazione socialista e disponendo i gruppi politici di fondi interni. Volume quarantunesimo della serie 1969-1976, documento 180: verbale della riunione dell’11 MARZO 1969, alla presenza fra gli altri del consigliere per la sicurezza nazionale e del direttore dell’agenzia informativa, con una ESPOSIZIONE DETTAGLIATA SU ORIGINI, RELAZIONI, LIVELLI DI FINANZIAMENTO E RISULTATI DEL PROGRAMMA DI SOSTEGNO POLITICO COPERTO A PARTITI E ORGANIZZAZIONI SINDACALI ITALIANI NEGLI ANNI 1948-1968</t>
+          <t>Nel maggio 1973 — DISCREPANZA CHIUSA COME DOPPIO ATTO: firma della direttiva ai vertici operativi il 7 MAGGIO, diramazione del memorandum a tutto il personale il 9 MAGGIO — il direttore firmò una direttiva che ordinava ai dirigenti di riferire su QUALSIASI ATTIVITÀ, PRESENTE O PASSATA, CHE POTESSE ESULARE DALLO STATUTO LEGALE DELL’AGENZIA. Ne risultò un raccoglitore a fogli mobili di 609TRÉ PAGINE di memorandum, passato al successore alla fine del 1973, che lo definì «gli scheletri nell’armadio». Il 31 dicembre 1974 il direttore e il consigliere generale ne informarono il vice ministro della Giustizia: il documento catalogava azioni DAL 1959 AL 1973 e furono individuati 18 PUNTI DI RILIEVO GIURIDICO</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>ESITO REGISTRATO NEL VERBALE: il sostegno era stato drasticamente ridotto e infine CESSATO DEL TUTTO ALLA FINE DELL’ESERCIZIO 1968, ritenendosi che gli italiani fossero in grado di finanziare da soli i propri partiti; i presenti furono unanimi nel ritenere che NON VI FOSSE REALE GIUSTIFICAZIONE PER UNA RIPRESA. Il presidente chiese all’agenzia un documento riepilogativo che coprisse anche IL FINANZIAMENTO SOVIETICO E COMUNISTA e le fonti disponibili ai partiti non comunisti. Uno studio dell’archivio universitario di sicurezza nazionale stima l’aiuto coperto all’Italia in circa 5 MILIONI DI DOLLARI ANNUI dalla fine degli anni Quaranta ai primi anni Sessanta</t>
+          <t>CONTENUTI DICHIARATI: la detenzione di un disertore sovietico, che «potrebbe essere considerata violazione delle leggi sul sequestro di persona»; intercettazioni di due editorialisti, approvate dal ministro della Giustizia e dal ministro della Difesa dell’epoca; sorveglianza fisica di un giornalista investigativo che aveva scritto sui tentativi di assassinio di un capo di Stato straniero, e di un cronista di un grande quotidiano; EFFRAZIONI nell’abitazione di un ex dipendente, nell’ufficio di un ex disertore, e ingresso senza mandato in un appartamento; APERTURA DELLA CORRISPONDENZA da e per l’Unione Sovietica DAL 1953 AL 1973 e da e per la Cina dal 1969 al 1972; sperimentazioni con sostanze psicoattive su soggetti inconsapevoli; piani di assassinio di capi di Stato stranieri; e la questione dell’addestramento di polizie straniere alla fabbricazione di ordigni e al sabotaggio</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>AVVERTENZA SULLA SERIE, DA REGISTRARE PERCHÉ RIGUARDA L’AFFIDABILITÀ DELLA FONTE: la storia ufficiale della serie stessa documenta che un volume relativo all’Iran FU PUBBLICATO PRIVO DELLA DOCUMENTAZIONE DI UNA RILEVANTE OPERAZIONE COPERTA NOTORIAMENTE AVVENUTA, e che ciò provocò una crisi e LE DIMISSIONI DEL PRESIDENTE DEL COMITATO SCIENTIFICO CONSULTIVO. La serie ufficiale ha dunque già omesso operazioni coperte: va usata come fonte primaria E verificata</t>
+          <t>LA GENESI, CHE VA REGISTRATA PERCHÉ NON FU UN ATTO DI COSCIENZA: la direttiva nacque dalle notizie di stampa sul coinvolgimento dell’agenzia nello scandalo che travolse la presidenza, e in particolare dal sostegno prestato a due suoi veterani coinvolti in un’effrazione. Il direttore, appena insediato, VOLLE SAPERE CHE COS’ALTRO NON GLI ERA STATO DETTO E POTEVA ESPORLO. Il successore presentò poi le attività ai parlamentari COME RISPOSTE ISOLATE A MINACCE PERCEPITE anziché come fallimenti istituzionali, e sostenne internamente che la soppressione totale rischiava un’esposizione maggiore attraverso le fughe di notizie. Gli investigatori parlamentari ebbero accesso al documento negli anni Settanta E LA SUA ESISTENZA ERA NOTA DA ANNI</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Dominio 3 × Dominio 2 — è la fonte primaria statunitense sull’intervento politico in Italia, con numeri di documento</t>
+          <t>Metodologia — un’istituzione cataloga le proprie illegalità per timore, non per dovere; il catalogo serve al Parlamento in 3 anni e al pubblico in trentaquattro</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -7542,40 +8090,44 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Legge statunitense sulla libertà di informazione — 1966 e successive modifiche</t>
+          <t>Progetto statunitense di declassificazione sull’Argentina, 2016-2019</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; si applica alle agenzie dell’esecutivo federale, NON al Congresso, alla magistratura né agli enti statali e locali</t>
+          <t>Stati Uniti; documenti raccolti sul portale della comunità informativa e consultabili liberamente</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>9 eccezioni tassative; richiesta esperibile da chiunque; dal 1974 con termini, penalità, esenzione dai costi per giornalisti e organizzazioni d’interesse pubblico, e SINDACATO GIURISDIZIONALE SUI DINIEGHI</t>
+          <t>Avviato su richiesta del governo argentino e di organizzazioni per i diritti umani; annuncio nel marzo 2016 a Buenos Aires, nel quarantennale del colpo di Stato del 1976; incarico presidenziale del 13 GIUGNO 2016 a OLTRE 16 agenzie e dipartimenti, comprese le biblioteche presidenziali, per i documenti relativi ad abusi commessi FRA IL 1° GENNAIO 1975 E IL 31 DICEMBRE 1984</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>LA GENESI, CHE VA REGISTRATA PER INTERO. La proposta nacque da oltre un decennio di audizioni parlamentari; VENTISETTE AGENZIE GOVERNATIVE, COMPRESO IL MINISTERO DELLA GIUSTIZIA, SOSTENNERO CHE AVREBBE VIOLATO LA SEPARAZIONE DEI POTERI; il presidente vi si opponeva privatamente. Passò al Senato il 13 ottobre 1965 e alla Camera il 20 giugno 1966 CON TRECENTOSEI VOTI CONTRO NESSUNO. Fu firmata il 4 luglio 1966, MA IL PRESIDENTE RIFIUTÒ DI TENERE LA CERIMONIA PUBBLICA DI FIRMA che riservava alle leggi importanti, e la dichiarazione di firma insisteva sulle eccezioni di sicurezza nazionale e sul «margine di interpretazione». Entrò in vigore il 4 luglio 1967</t>
+          <t>PER LA PRIMA VOLTA furono inclusi i documenti dell’agenzia informativa, del servizio investigativo federale, dell’agenzia informativa della difesa, dei dipartimenti militari e dello stato maggiore congiunto. 4 CONSEGNE: agosto 2016, trecentoquaranta documenti per mille507 pagine, consegnati di persona dal segretario di Stato; dicembre 2016, centosessantasette documenti per 5150 pagine; aprile 2017, novecentotrentadue documenti per circa tremilatrecento pagine, su supporto digitale; 12 APRILE 2019, consegna finale con oltre cinquemilaseicento nuovi documenti. TOTALE: SETTEMILATRENTACINQUE DOCUMENTI PRODOTTI, 49MILA PAGINE ESAMINATE, CIRCA TRENTADUEMILA ORE DI LAVORO E OLTRE TRECENTOTTANTA PERSONE in 16 agenzie; collezione complessiva di oltre 11milaseicento documenti. È definita la PIÙ GRANDE DECLASSIFICAZIONE DA GOVERNO A GOVERNO DELLA STORIA STATUNITENSE</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>LA LEGGE ERA PRIVA DI DENTI. Le agenzie arrivavano a chiedere UN DOLLARO A PAGINA E 7 DOLLARI L’ORA per la ricerca, quando il salario orario mediano era intorno ai 4 dollari. Dopo lo scandalo che travolse la presidenza, e fallito il negoziato con l’amministrazione, IL CONGRESSO APPROVÒ NEL 1974 LE MODIFICHE CHE LA RESERO EFFICACE. IL PRESIDENTE LE POSE IL VETO — spinto dal proprio capo di gabinetto, dal vice e dal capo dell’ufficio legale del ministero della Giustizia, preoccupati per le fughe di notizie e per la costituzionalità. IL CONGRESSO SUPERÒ IL VETO: la votazione al Senato sul veto presidenziale ebbe luogo il 21 novembre 1974, e le modifiche entrarono in vigore il 19 febbraio 1975</t>
+          <t>CONTENUTO PERTINENTE AL TOMO SECONDO: evidenza estesa sull’infrastruttura della repressione, SUL RUOLO DELL’ARGENTINA NELLA CAMPAGNA DI TERRORISMO INTERNAZIONALE NOTA COME OPERAZIONE CONDOR, e sulla sorte di centinaia di scomparsi. I documenti SONO OGGI UTILIZZATI PER PERSEGUIRE CRIMINI CONTRO I DIRITTI UMANI</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — LO STRUMENTO CHE HA PRODOTTO BUONA PARTE DI QUESTO REPERTORIO FU AVVERSATO DA VENTISETTE AGENZIE, FIRMATO SENZA CERIMONIA, LASCIATO INEFFICACE PER 8 ANNI, E RESO OPERANTE SOLTANTO SUPERANDO UN VETO PRESIDENZIALE. Modifiche successive: 1976 sulle eccezioni, 1986, 1996 sui documenti elettronici, 2002 con limiti alle richieste di agenti stranieri ai servizi, 2007 e 2016</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
+          <t>IL DETTAGLIO CHE VALE QUANTO LE CIFRE: è stato osservato che, grazie al meticoloso controllo di qualità esercitato da UN SINGOLO FUNZIONARIO responsabile dei documenti presso il Consiglio di sicurezza nazionale, i documenti rilasciati risultano ASSAI MENO CENSURATI delle precedenti declassificazioni speciali. IL GRADO DI LEGGIBILITÀ DI UN ARCHIVIO PUÒ DIPENDERE DA UNA PERSONA</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II — asse sudamericano; Metodologia — la variabile umana dentro la macchina</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="3" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr">
         <is>
@@ -7588,37 +8140,37 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Compilazione interna dell’agenzia informativa statunitense sulle attività eccedenti il proprio statuto — «i gioielli di famiglia»</t>
+          <t>Centro nazionale di declassificazione presso l’Archivio nazionale statunitense</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; pubblicata sul sito dell’agenzia e raccolta dall’archivio universitario di sicurezza nazionale</t>
+          <t>College Park, Maryland; relazioni semestrali e piani di priorità pubblicati in rete</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pubblicata il 25 GIUGNO 2007, con espunzioni comprendenti PAGINE INTERE. L’archivio universitario aveva presentato la richiesta di accesso 15 ANNI PRIMA, nel 1992. TRENTAQUATTRO ANNI DALLA COMPILAZIONE</t>
+          <t>Istituito con l’ordine esecutivo del 29 dicembre 2009 e reso operativo il giorno successivo; coordina il trattamento dei rinvii fra agenzie sui documenti classificati DI 25 ANNI O PIÙ e di valore storico permanente; il piano di priorità fu sottoposto a consultazione pubblica</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Nel maggio 1973 — DISCREPANZA CHIUSA COME DOPPIO ATTO: firma della direttiva ai vertici operativi il 7 MAGGIO, diramazione del memorandum a tutto il personale il 9 MAGGIO — il direttore firmò una direttiva che ordinava ai dirigenti di riferire su QUALSIASI ATTIVITÀ, PRESENTE O PASSATA, CHE POTESSE ESULARE DALLO STATUTO LEGALE DELL’AGENZIA. Ne risultò un raccoglitore a fogli mobili di 609TRÉ PAGINE di memorandum, passato al successore alla fine del 1973, che lo definì «gli scheletri nell’armadio». Il 31 dicembre 1974 il direttore e il consigliere generale ne informarono il vice ministro della Giustizia: il documento catalogava azioni DAL 1959 AL 1973 e furono individuati 18 PUNTI DI RILIEVO GIURIDICO</t>
+          <t>L’ARRETRATO: OLTRE QUATTROCENTO MILIONI DI PAGINE già acquisite dall’Archivio, di almeno 25 anni, sottoposte alla declassificazione automatica introdotta nel 1995 MA NON TRATTABILI per rinvii mancati e difetti nelle revisioni iniziali. Il memorandum presidenziale fissava la scadenza al 31 DICEMBRE 2013: 4 anni, cioè circa CENTO MILIONI DI PAGINE L’ANNO</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>CONTENUTI DICHIARATI: la detenzione di un disertore sovietico, che «potrebbe essere considerata violazione delle leggi sul sequestro di persona»; intercettazioni di due editorialisti, approvate dal ministro della Giustizia e dal ministro della Difesa dell’epoca; sorveglianza fisica di un giornalista investigativo che aveva scritto sui tentativi di assassinio di un capo di Stato straniero, e di un cronista di un grande quotidiano; EFFRAZIONI nell’abitazione di un ex dipendente, nell’ufficio di un ex disertore, e ingresso senza mandato in un appartamento; APERTURA DELLA CORRISPONDENZA da e per l’Unione Sovietica DAL 1953 AL 1973 e da e per la Cina dal 1969 al 1972; sperimentazioni con sostanze psicoattive su soggetti inconsapevoli; piani di assassinio di capi di Stato stranieri; e la questione dell’addestramento di polizie straniere alla fabbricazione di ordigni e al sabotaggio</t>
+          <t>IL DATO STRUTTURALE, CHE È LA MISURA PIÙ UTILE DELL’INTERO REPERTORIO: secondo una stima dello stesso Centro, ogni anno 15 MILIONI DI NUOVE PAGINE CLASSIFICATE vengono acquisite dall’Archivio, e SOLTANTO 11 MILIONI completano il processo di declassificazione e divengono pubbliche. IL SISTEMA PRODUCE OGNI ANNO 4 MILIONI DI PAGINE DI SEGRETO NETTO</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>LA GENESI, CHE VA REGISTRATA PERCHÉ NON FU UN ATTO DI COSCIENZA: la direttiva nacque dalle notizie di stampa sul coinvolgimento dell’agenzia nello scandalo che travolse la presidenza, e in particolare dal sostegno prestato a due suoi veterani coinvolti in un’effrazione. Il direttore, appena insediato, VOLLE SAPERE CHE COS’ALTRO NON GLI ERA STATO DETTO E POTEVA ESPORLO. Il successore presentò poi le attività ai parlamentari COME RISPOSTE ISOLATE A MINACCE PERCEPITE anziché come fallimenti istituzionali, e sostenne internamente che la soppressione totale rischiava un’esposizione maggiore attraverso le fughe di notizie. Gli investigatori parlamentari ebbero accesso al documento negli anni Settanta E LA SUA ESISTENZA ERA NOTA DA ANNI</t>
+          <t>L’ESITO, E LA SUA QUALIFICAZIONE. Il 31 dicembre 2013 il Centro dichiarò raggiunto l’obiettivo, con il «ritiro» di un arretrato di 3150DUE MILIONI DI PAGINE: tutte le serie classificate acquisite prima del 1° gennaio 2010 erano state declassificate dalle agenzie titolari O ESENTATE per ragioni di sicurezza nazionale. MA LA RELAZIONE STESSA AVVERTE che occorre ancora il trattamento archivistico — segregazione degli esentati, controllo di riservatezza, descrizione e conservazione — PER RENDERE EFFETTIVAMENTE ACCESSIBILI MOLTI DI QUEI DOCUMENTI, e che l’Archivio è vincolato da limitazioni di risorse di lunga data. Fra le difficoltà dichiarate: incoerenze delle revisioni precedenti, marcature di rinvio problematiche, e EMERGENZE CONSERVATIVE COME MUFFE E DOCUMENTI FRAGILI DA RISANARE</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — un’istituzione cataloga le proprie illegalità per timore, non per dovere; il catalogo serve al Parlamento in 3 anni e al pubblico in trentaquattro</t>
+          <t>Tomo III — LA DISTINZIONE DECISIVA: «declassificato» significa che l’agenzia ha deciso, NON che il cittadino possa leggere. Fra le due cose stanno la descrizione, la conservazione e il personale</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -7638,44 +8190,40 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Progetto statunitense di declassificazione sull’Argentina, 2016-2019</t>
+          <t>Collegio interagenzia di appello sulle classificazioni di sicurezza — Stati Uniti</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; documenti raccolti sul portale della comunità informativa e consultabili liberamente</t>
+          <t>Decisioni pubblicate su tabella consultabile nel portale della declassificazione dell’Archivio nazionale</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Avviato su richiesta del governo argentino e di organizzazioni per i diritti umani; annuncio nel marzo 2016 a Buenos Aires, nel quarantennale del colpo di Stato del 1976; incarico presidenziale del 13 GIUGNO 2016 a OLTRE 16 agenzie e dipartimenti, comprese le biblioteche presidenziali, per i documenti relativi ad abusi commessi FRA IL 1° GENNAIO 1975 E IL 31 DICEMBRE 1984</t>
+          <t>Istituito con l’ordine esecutivo del 17 aprile 1995, efficace dall’ottobre successivo; prima riunione nel MAGGIO 1996. Composto da rappresentanti di alto livello dei dipartimenti di Stato, Difesa e Giustizia, del Consiglio di sicurezza nazionale, dell’ufficio del direttore dell’intelligence nazionale e dell’Archivio nazionale. È SEDE DI APPELLO IMPARZIALE PER CHIUNQUE si sia visto respingere da un’agenzia una richiesta di revisione obbligatoria della classificazione</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PER LA PRIMA VOLTA furono inclusi i documenti dell’agenzia informativa, del servizio investigativo federale, dell’agenzia informativa della difesa, dei dipartimenti militari e dello stato maggiore congiunto. 4 CONSEGNE: agosto 2016, trecentoquaranta documenti per mille507 pagine, consegnati di persona dal segretario di Stato; dicembre 2016, centosessantasette documenti per 5150 pagine; aprile 2017, novecentotrentadue documenti per circa tremilatrecento pagine, su supporto digitale; 12 APRILE 2019, consegna finale con oltre cinquemilaseicento nuovi documenti. TOTALE: SETTEMILATRENTACINQUE DOCUMENTI PRODOTTI, 49MILA PAGINE ESAMINATE, CIRCA TRENTADUEMILA ORE DI LAVORO E OLTRE TRECENTOTTANTA PERSONE in 16 agenzie; collezione complessiva di oltre 11milaseicento documenti. È definita la PIÙ GRANDE DECLASSIFICAZIONE DA GOVERNO A GOVERNO DELLA STORIA STATUNITENSE</t>
+          <t>LE CIFRE, CHE SONO IL PUNTO. Su un totale di 2.4007 documenti decisi dal 1996, il collegio HA DECLASSIFICATO INFORMAZIONI ULTERIORI NEL SETTANTACINQUE PER CENTO DEI CASI: 6094 documenti — il 29 per cento — declassificati INTEGRALMENTE; millecentootto — il quarantasei per cento — in parte; e le decisioni delle agenzie CONFERMATE INTEGRALMENTE SOLTANTO IN SEICENTOCINQUE CASI, il 25 per cento. In un anno campione più recente, su centosessantatré documenti esaminati, le decisioni delle agenzie furono pienamente confermate SOLTANTO NELL’8 PER CENTO: il trentanove per cento fu declassificato in pieno e il 50tré in parte — CIOÈ IL NOVANTADUE PER CENTO RIBALTATO IN TUTTO O IN PARTE</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>CONTENUTO PERTINENTE AL TOMO SECONDO: evidenza estesa sull’infrastruttura della repressione, SUL RUOLO DELL’ARGENTINA NELLA CAMPAGNA DI TERRORISMO INTERNAZIONALE NOTA COME OPERAZIONE CONDOR, e sulla sorte di centinaia di scomparsi. I documenti SONO OGGI UTILIZZATI PER PERSEGUIRE CRIMINI CONTRO I DIRITTI UMANI</t>
+          <t>ALTRO DATO: nello stesso anno i dipendenti pubblici presentarono QUATTROCENTODUE contestazioni interne alla classificazione di singole informazioni; la classificazione fu confermata in due terzi dei casi e RIBALTATA IN TUTTO O IN PARTE IN UN TERZO. Dall’ordine esecutivo del 2009 le agenzie DEVONO tenere conto delle decisioni del collegio nelle proprie, e il collegio deve informarne funzionari e pubblico. Fra i documenti recentemente liberati in appello: porzioni di informative presidenziali quotidiane della fine degli anni Sessanta e una storia interna dell’agenzia informativa sul SOSTEGNO COPERTO A GRUPPI ANTICOMUNISTI STATUNITENSI FRA IL 1949 E IL 1967</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>IL DETTAGLIO CHE VALE QUANTO LE CIFRE: è stato osservato che, grazie al meticoloso controllo di qualità esercitato da UN SINGOLO FUNZIONARIO responsabile dei documenti presso il Consiglio di sicurezza nazionale, i documenti rilasciati risultano ASSAI MENO CENSURATI delle precedenti declassificazioni speciali. IL GRADO DI LEGGIBILITÀ DI UN ARCHIVIO PUÒ DIPENDERE DA UNA PERSONA</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — asse sudamericano; Metodologia — la variabile umana dentro la macchina</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
+          <t>Tomo III e Metodologia — LA SOVRACLASSIFICAZIONE NON È UN’IMPRESSIONE: È UN TASSO MISURATO, e a misurarlo è l’organo di appello dello Stato stesso. Quando un collegio indipendente riesamina i dinieghi che le agenzie hanno confermato, li ribalta in 3 casi su 4</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H55" s="3" t="inlineStr"/>
       <c r="I55" s="3" t="inlineStr"/>
       <c r="J55" s="8" t="inlineStr">
         <is>
@@ -7688,44 +8236,40 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Centro nazionale di declassificazione presso l’Archivio nazionale statunitense</t>
+          <t>Consiglio consultivo statunitense per la declassificazione nell’interesse pubblico — relazioni al presidente</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>College Park, Maryland; relazioni semestrali e piani di priorità pubblicati in rete</t>
+          <t>Istituito con legge pubblica 106-567; relazioni e pareri pubblicati sul portale dell’Archivio nazionale</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Istituito con l’ordine esecutivo del 29 dicembre 2009 e reso operativo il giorno successivo; coordina il trattamento dei rinvii fra agenzie sui documenti classificati DI 25 ANNI O PIÙ e di valore storico permanente; il piano di priorità fu sottoposto a consultazione pubblica</t>
+          <t>Relazioni del 2007 e 2008; RELAZIONE DEL 2012 sulla trasformazione del sistema di classificazione, con 14 raccomandazioni; supplemento del 2014 sulle priorità; documento tecnico del giugno 2016; RELAZIONE DEL MAGGIO 2020 «Una visione per l’era digitale»</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>L’ARRETRATO: OLTRE QUATTROCENTO MILIONI DI PAGINE già acquisite dall’Archivio, di almeno 25 anni, sottoposte alla declassificazione automatica introdotta nel 1995 MA NON TRATTABILI per rinvii mancati e difetti nelle revisioni iniziali. Il memorandum presidenziale fissava la scadenza al 31 DICEMBRE 2013: 4 anni, cioè circa CENTO MILIONI DI PAGINE L’ANNO</t>
+          <t>LE CONSTATAZIONI, CHE VANNO CITATE COME SONO. Nel 2016 il Consiglio dichiarò che il sistema di classificazione «NON È PIÙ IN GRADO DI TRATTARE L’ATTUALE VOLUME E LE FORME DELL’INFORMAZIONE, SPECIE DATA LA CRESCITA ESPONENZIALE DELL’INFORMAZIONE DIGITALE». Nel 2019 il direttore dell’ufficio di vigilanza sulla sicurezza delle informazioni scrisse al presidente che «L’ATTUALE ASSETTO È INSOSTENIBILE E RICHIEDE DISPERATAMENTE UNA MODERNIZZAZIONE». La relazione del 2020 afferma che il sistema RESTA INSOSTENIBILE nell’era digitale, e che via via che tutti i supporti divengono digitali LA TECNOLOGIA ANALOGICA E I DOCUMENTI CARTACEI DIVENTANO PRATICAMENTE INACCESSIBILI E DISFUNZIONALI</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>IL DATO STRUTTURALE, CHE È LA MISURA PIÙ UTILE DELL’INTERO REPERTORIO: secondo una stima dello stesso Centro, ogni anno 15 MILIONI DI NUOVE PAGINE CLASSIFICATE vengono acquisite dall’Archivio, e SOLTANTO 11 MILIONI completano il processo di declassificazione e divengono pubbliche. IL SISTEMA PRODUCE OGNI ANNO 4 MILIONI DI PAGINE DI SEGRETO NETTO</t>
+          <t>IL NUMERO CHE CHIUDE IL REPERTORIO: i costi del sistema di classificazione della sicurezza sono definiti «SBALORDITIVI» — stimati in 18 MILIARDI E TRECENTONOVANTA MILIONI DI DOLLARI nel solo esercizio 2017 — MENTRE LE RISORSE PER LA DECLASSIFICAZIONE RESTANO «MISERAMENTE SOTTOFINANZIATE». E l’argomento non è storiografico ma di sicurezza: la sovraclassificazione e l’arretrato «DANNO ORIGINE A FUGHE DI NOTIZIE E DIVULGAZIONI INAVVERTITE CHE DANNEGGIANO GLI IMPERATIVI DELLA SICUREZZA NAZIONALE», e le prassi correnti DIMINUISCONO LA FIDUCIA PUBBLICA nel sistema. La relazione avverte che occorre agire «PRIMA CHE IL CRESCENTE AFFLUSSO DI INFORMAZIONE ELETTRONICA CLASSIFICATA DIVENGA COMPLETAMENTE INGOVERNABILE». In audizione parlamentare nel 2020 si è osservato che, 4 anni dopo, poco indica che il problema sia avviato a soluzione</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>L’ESITO, E LA SUA QUALIFICAZIONE. Il 31 dicembre 2013 il Centro dichiarò raggiunto l’obiettivo, con il «ritiro» di un arretrato di 3150DUE MILIONI DI PAGINE: tutte le serie classificate acquisite prima del 1° gennaio 2010 erano state declassificate dalle agenzie titolari O ESENTATE per ragioni di sicurezza nazionale. MA LA RELAZIONE STESSA AVVERTE che occorre ancora il trattamento archivistico — segregazione degli esentati, controllo di riservatezza, descrizione e conservazione — PER RENDERE EFFETTIVAMENTE ACCESSIBILI MOLTI DI QUEI DOCUMENTI, e che l’Archivio è vincolato da limitazioni di risorse di lunga data. Fra le difficoltà dichiarate: incoerenze delle revisioni precedenti, marcature di rinvio problematiche, e EMERGENZE CONSERVATIVE COME MUFFE E DOCUMENTI FRAGILI DA RISANARE</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — LA DISTINZIONE DECISIVA: «declassificato» significa che l’agenzia ha deciso, NON che il cittadino possa leggere. Fra le due cose stanno la descrizione, la conservazione e il personale</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
+          <t>Tomo III e Metodologia — È LO STATO STESSO A DICHIARARE INSOSTENIBILE L’INTERO SISTEMA CHE QUESTO REPERTORIO HA CENSITO, e a dire che il segreto in eccesso non protegge la sicurezza: la danneggia</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H56" s="3" t="inlineStr"/>
       <c r="I56" s="3" t="inlineStr"/>
       <c r="J56" s="8" t="inlineStr">
         <is>
@@ -7738,40 +8282,44 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Collegio interagenzia di appello sulle classificazioni di sicurezza — Stati Uniti</t>
+          <t>Progetto crittanalitico statunitense sulle comunicazioni sovietiche — «Venona»</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Decisioni pubblicate su tabella consultabile nel portale della declassificazione dell’Archivio nazionale</t>
+          <t>Stati Uniti; documenti declassificati e pubblicati in rete dalle due agenzie che li custodivano</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Istituito con l’ordine esecutivo del 17 aprile 1995, efficace dall’ottobre successivo; prima riunione nel MAGGIO 1996. Composto da rappresentanti di alto livello dei dipartimenti di Stato, Difesa e Giustizia, del Consiglio di sicurezza nazionale, dell’ufficio del direttore dell’intelligence nazionale e dell’Archivio nazionale. È SEDE DI APPELLO IMPARZIALE PER CHIUNQUE si sia visto respingere da un’agenzia una richiesta di revisione obbligatoria della classificazione</t>
+          <t>Declassificazione avviata l’11 LUGLIO 1995 con cerimonia pubblica: prima tranche di 49 telegrammi tradotti e parzialmente decifrati sullo spionaggio atomico 1940-1948; seconda tranche sui messaggi della residenza di New York per il 1942-1943; terza con OLTRE CINQUECENTO traduzioni. Complessivamente, nel 1995-96, OLTRE DUEMILANOVECENTONOVANTA telegrammi interamente o parzialmente decifrati</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>LE CIFRE, CHE SONO IL PUNTO. Su un totale di 2.4007 documenti decisi dal 1996, il collegio HA DECLASSIFICATO INFORMAZIONI ULTERIORI NEL SETTANTACINQUE PER CENTO DEI CASI: 6094 documenti — il 29 per cento — declassificati INTEGRALMENTE; millecentootto — il quarantasei per cento — in parte; e le decisioni delle agenzie CONFERMATE INTEGRALMENTE SOLTANTO IN SEICENTOCINQUE CASI, il 25 per cento. In un anno campione più recente, su centosessantatré documenti esaminati, le decisioni delle agenzie furono pienamente confermate SOLTANTO NELL’8 PER CENTO: il trentanove per cento fu declassificato in pieno e il 50tré in parte — CIOÈ IL NOVANTADUE PER CENTO RIBALTATO IN TUTTO O IN PARTE</t>
+          <t>Avviato nel FEBBRAIO 1943 dal servizio informazioni di segnalazione dell’esercito per intercettare e decifrare le comunicazioni diplomatiche e spionistiche sovietiche cifrate con blocco monouso. IL METODO FUNZIONÒ PER UN ERRORE AVVERSARIO: parte del materiale chiave era stata RIUTILIZZATA, il che rese possibile la decifrazione, spesso solo parziale, DI UNA PICCOLA PARTE DEL TRAFFICO. Durò 37 ANNI, fino al 1980, e produsse circa TREMILA messaggi decifrati e tradotti su molte migliaia trasmessi; il tasso era irregolarissimo — per una serie del 1943 circa la metà, per gli altri anni nulla. Furono identificati OLTRE DUECENTO individui come agenti occulti; ne emersero una rete di spionaggio britannica e lo spionaggio sul progetto atomico. IL PROGETTO RESTÒ SEGRETO PER OLTRE 15 ANNI DOPO LA SUA CONCLUSIONE</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ALTRO DATO: nello stesso anno i dipendenti pubblici presentarono QUATTROCENTODUE contestazioni interne alla classificazione di singole informazioni; la classificazione fu confermata in due terzi dei casi e RIBALTATA IN TUTTO O IN PARTE IN UN TERZO. Dall’ordine esecutivo del 2009 le agenzie DEVONO tenere conto delle decisioni del collegio nelle proprie, e il collegio deve informarne funzionari e pubblico. Fra i documenti recentemente liberati in appello: porzioni di informative presidenziali quotidiane della fine degli anni Sessanta e una storia interna dell’agenzia informativa sul SOSTEGNO COPERTO A GRUPPI ANTICOMUNISTI STATUNITENSI FRA IL 1949 E IL 1967</t>
+          <t>AVVERTENZE DI STATUTO, INDISPENSABILI: le decifrazioni sono PARZIALI; furono usati centinaia di nomi in codice, alcuni dei quali compaiono una o due volte e RESTANO TUTTORA IGNOTI; e l’attribuzione dei nomi in codice a persone reali fu ottenuta DAL CONTESTO E DA INFORMAZIONI ESTERNE, non dal testo stesso — sicché alcune identificazioni restano probabili e non certe. L’agenzia preparò inoltre i documenti ESPUNGENDO nomi in codice, identificativi parziali e dettagli operativi ritenuti ancora sensibili</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Tomo III e Metodologia — LA SOVRACLASSIFICAZIONE NON È UN’IMPRESSIONE: È UN TASSO MISURATO, e a misurarlo è l’organo di appello dello Stato stesso. Quando un collegio indipendente riesamina i dinieghi che le agenzie hanno confermato, li ribalta in 3 casi su 4</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
+          <t>E IL FATTO CHE VALE PER IL METODO: uno degli agenti sovietici operanti nei servizi alleati ERA VISITATORE ABITUALE DEL CENTRO DI DECRITTAZIONE e ne osservava i lavori; avvertì Mosca, e due colleghi poterono fuggire. IL PROGETTO CHE SCOPRIVA LE SPIE ERA OSSERVATO DA UNA SPIA</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II — versante orientale: con lo schedario microfilmato e le carte manoscritte già censite, sono 3 MODI DI CONOSCERE L’EST DALL’OVEST, E NESSUNO DEI 3 È UN DOCUMENTO LETTO IN ORIGINALE</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr"/>
       <c r="I57" s="3" t="inlineStr"/>
       <c r="J57" s="8" t="inlineStr">
         <is>
@@ -7784,40 +8332,44 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Consiglio consultivo statunitense per la declassificazione nell’interesse pubblico — relazioni al presidente</t>
+          <t>Commissione ristretta del Senato statunitense — relazione interlocutoria sui presunti piani di assassinio di capi di Stato stranieri</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Istituito con legge pubblica 106-567; relazioni e pareri pubblicati sul portale dell’Archivio nazionale</t>
+          <t>Rapporto del Senato numero 94-165, novantaquattresimo Congresso; DUECENT85 PAGINE, con opinioni aggiuntive, supplementari e separate; votata e pubblicata il 20 NOVEMBRE 1975</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Relazioni del 2007 e 2008; RELAZIONE DEL 2012 sulla trasformazione del sistema di classificazione, con 14 raccomandazioni; supplemento del 2014 sulle priorità; documento tecnico del giugno 2016; RELAZIONE DEL MAGGIO 2020 «Una visione per l’era digitale»</t>
+          <t>Testo integrale liberamente consultabile in rete presso più archivi documentari</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>LE CONSTATAZIONI, CHE VANNO CITATE COME SONO. Nel 2016 il Consiglio dichiarò che il sistema di classificazione «NON È PIÙ IN GRADO DI TRATTARE L’ATTUALE VOLUME E LE FORME DELL’INFORMAZIONE, SPECIE DATA LA CRESCITA ESPONENZIALE DELL’INFORMAZIONE DIGITALE». Nel 2019 il direttore dell’ufficio di vigilanza sulla sicurezza delle informazioni scrisse al presidente che «L’ATTUALE ASSETTO È INSOSTENIBILE E RICHIEDE DISPERATAMENTE UNA MODERNIZZAZIONE». La relazione del 2020 afferma che il sistema RESTA INSOSTENIBILE nell’era digitale, e che via via che tutti i supporti divengono digitali LA TECNOLOGIA ANALOGICA E I DOCUMENTI CARTACEI DIVENTANO PRATICAMENTE INACCESSIBILI E DISFUNZIONALI</t>
+          <t>LA PUBBLICAZIONE FU CONTESTATA DALL’ESECUTIVO. Il 4 novembre 1975 OTIS PIKE, presidente della commissione respinse per iscritto il tentativo della Casa Bianca di sopprimerne le risultanze: «A mio avviso L’INTERESSE NAZIONALE È MEGLIO SERVITO FACENDO CONOSCERE AL POPOLO AMERICANO LA STORIA VERA E COMPLETA. Un principio fondamentale della nostra democrazia è che il popolo dev’essere informato degli errori del proprio governo, AFFINCHÉ ABBIA LA POSSIBILITÀ DI CORREGGERLI.» Espunti alcuni nomi di funzionari, la commissione votò la diffusione. L’introduzione afferma: «LE PROVE STABILISCONO CHE GLI STATI UNITI FURONO IMPLICATI IN DIVERSI PIANI DI ASSASSINIO»</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>IL NUMERO CHE CHIUDE IL REPERTORIO: i costi del sistema di classificazione della sicurezza sono definiti «SBALORDITIVI» — stimati in 18 MILIARDI E TRECENTONOVANTA MILIONI DI DOLLARI nel solo esercizio 2017 — MENTRE LE RISORSE PER LA DECLASSIFICAZIONE RESTANO «MISERAMENTE SOTTOFINANZIATE». E l’argomento non è storiografico ma di sicurezza: la sovraclassificazione e l’arretrato «DANNO ORIGINE A FUGHE DI NOTIZIE E DIVULGAZIONI INAVVERTITE CHE DANNEGGIANO GLI IMPERATIVI DELLA SICUREZZA NAZIONALE», e le prassi correnti DIMINUISCONO LA FIDUCIA PUBBLICA nel sistema. La relazione avverte che occorre agire «PRIMA CHE IL CRESCENTE AFFLUSSO DI INFORMAZIONE ELETTRONICA CLASSIFICATA DIVENGA COMPLETAMENTE INGOVERNABILE». In audizione parlamentare nel 2020 si è osservato che, 4 anni dopo, poco indica che il problema sia avviato a soluzione</t>
+          <t>MATERIA PERTINENTE AL DOMINIO 1 × DOMINIO 3: il rapporto dedica sezioni proprie ALL’USO DI FIGURE DEL SOTTOBOSCO CRIMINALE, articolato in due fasi, ai contatti con l’organizzazione criminale, e a un’intercettazione con coinvolgimento dell’agenzia informativa. Esamina inoltre espressamente LE ASSUNZIONI DEGLI OPERATIVI SULL’AUTORIZZAZIONE PRESIDENZIALE e L’IMPRESSIONE DEGLI ESECUTORI che l’operazione fosse autorizzata dal vertice</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Tomo III e Metodologia — È LO STATO STESSO A DICHIARARE INSOSTENIBILE L’INTERO SISTEMA CHE QUESTO REPERTORIO HA CENSITO, e a dire che il segreto in eccesso non protegge la sicurezza: la danneggia</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+          <t>IL PUNTO CHE VALE PER TUTTA L’OPERA. Il sistema della NEGABILITÀ PLAUSIBILE non fu una conseguenza: era COSTRUITO DENTRO i piani. Il rapporto contiene sezioni intitolate «IL PERICOLO INSITO NELL’ESTENDERE ECCESSIVAMENTE LA DOTTRINA DELLA NEGABILITÀ PLAUSIBILE» e «IL PERICOLO DI USARE LA CIRCONLOCUZIONE». E LA COMMISSIONE — con potere di citazione, ottocento testimoni e centodiecimila documenti — NON FU IN GRADO DI AFFERMARE CATEGORICAMENTE SE ALCUN PRESIDENTE AVESSE EFFETTIVAMENTE APPROVATO QUEI PIANI. NON PERCHÉ LE PROVE FOSSERO STATE DISTRUTTE, MA PERCHÉ IL SISTEMA ERA STATO PROGETTATO PER PRODURRE QUELL’AMBIGUITÀ</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — LA VOCE PIÙ IMPORTANTE DEL REPERTORIO: in questo campo l’assenza di un ordine tracciabile NON È UNA LACUNA DELLA PROVA, È UN PRODOTTO DEL PROGETTO. E la disciplina della commissione va imitata per intero: essa NON CONCLUSE «dunque il presidente autorizzò», ma «NON POSSIAMO DETERMINARLO»</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="3" t="inlineStr"/>
       <c r="J58" s="8" t="inlineStr">
         <is>
@@ -7830,44 +8382,40 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Progetto crittanalitico statunitense sulle comunicazioni sovietiche — «Venona»</t>
+          <t>Rapporti fra agenzia informativa statunitense e stampa — accertamento parlamentare del 1976 e inchiesta giornalistica del 1977</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; documenti declassificati e pubblicati in rete dalle due agenzie che li custodivano</t>
+          <t>Stati Uniti; relazione finale della commissione senatoriale, Libro primo su intelligence estera e militare, 1976, consultabile in rete; articolo di rivista del 20 ottobre 1977, 25MILA PAROLE, frutto di 6 mesi di lavoro</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Declassificazione avviata l’11 LUGLIO 1995 con cerimonia pubblica: prima tranche di 49 telegrammi tradotti e parzialmente decifrati sullo spionaggio atomico 1940-1948; seconda tranche sui messaggi della residenza di New York per il 1942-1943; terza con OLTRE CINQUECENTO traduzioni. Complessivamente, nel 1995-96, OLTRE DUEMILANOVECENTONOVANTA telegrammi interamente o parzialmente decifrati</t>
+          <t>L’ACCERTAMENTO UFFICIALE: la commissione concluse che l’agenzia manteneva RAPPORTI COPERTI CON CIRCA 50 GIORNALISTI O DIPENDENTI DI ORGANI DI INFORMAZIONE STATUNITENSI, e precisò che circa 50 di quei rapporti riguardavano persone CHE FORNIVANO CONSAPEVOLMENTE informazioni, mentre le restanti IGNORAVANO DI AVERE A CHE FARE CON L’AGENZIA. La relazione NON FECE NOMI e non descrisse l’intera estensione del fenomeno</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Avviato nel FEBBRAIO 1943 dal servizio informazioni di segnalazione dell’esercito per intercettare e decifrare le comunicazioni diplomatiche e spionistiche sovietiche cifrate con blocco monouso. IL METODO FUNZIONÒ PER UN ERRORE AVVERSARIO: parte del materiale chiave era stata RIUTILIZZATA, il che rese possibile la decifrazione, spesso solo parziale, DI UNA PICCOLA PARTE DEL TRAFFICO. Durò 37 ANNI, fino al 1980, e produsse circa TREMILA messaggi decifrati e tradotti su molte migliaia trasmessi; il tasso era irregolarissimo — per una serie del 1943 circa la metà, per gli altri anni nulla. Furono identificati OLTRE DUECENTO individui come agenti occulti; ne emersero una rete di spionaggio britannica e lo spionaggio sul progetto atomico. IL PROGETTO RESTÒ SEGRETO PER OLTRE 15 ANNI DOPO LA SUA CONCLUSIONE</t>
+          <t>LA TESI GIORNALISTICA, DA TENERE DISTINTA E MARCATA COME TALE: l’inchiesta del 1977 sostiene che OLTRE QUATTROCENTO giornalisti statunitensi avessero svolto incarichi riservati per l’agenzia nell’arco di 25 anni, dal 1953 al 1977, secondo documenti conservati presso la sede dell’agenzia; che i rapporti fossero taciti o espliciti, con «cooperazione, accomodamento e sovrapposizione»; e che i giornalisti prestassero servizi che andavano dalla semplice raccolta informativa al ruolo di intermediari con agenti nei Paesi dell’Est. Il sottotitolo dell’articolo ACCUSA LA COMMISSIONE DI AVER INSABBIATO. QUESTA È TESI D’AUTORE E NON ACCERTAMENTO</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>AVVERTENZE DI STATUTO, INDISPENSABILI: le decifrazioni sono PARZIALI; furono usati centinaia di nomi in codice, alcuni dei quali compaiono una o due volte e RESTANO TUTTORA IGNOTI; e l’attribuzione dei nomi in codice a persone reali fu ottenuta DAL CONTESTO E DA INFORMAZIONI ESTERNE, non dal testo stesso — sicché alcune identificazioni restano probabili e non certe. L’agenzia preparò inoltre i documenti ESPUNGENDO nomi in codice, identificativi parziali e dettagli operativi ritenuti ancora sensibili</t>
+          <t>IL DATO CHE VALE PIÙ DI ENTRAMBI, PERCHÉ RIGUARDA IL METODO DELL’INCHIESTA. Nel marzo 1976, in una riunione presso la sede dell’agenzia con il presidente e il vicepresidente della commissione, il direttore dello staff, il direttore dell’agenzia e il suo consigliere, FU CONCORDATO UN ACCESSO NEGOZIATO: l’agenzia rifiutò i fascicoli integrali e i nomi dei giornalisti e delle testate; due funzionari della commissione poterono esaminare versioni EPURATE dei fascicoli di 25 giornalisti scelti fra oltre quattrocento sintesi di un paragrafo ciascuna, CON I NOMI DELLE PERSONE E DELLE TESTATE OSCURATI; il presidente e il vicepresidente poterono vedere le versioni integre DI 5 SOLTANTO, al solo fine di attestare che nulla fosse nascosto oltre i nomi; E NESSUNO DEI 4 POTEVA RIFERIRNE AGLI ALTRI MEMBRI DELLA COMMISSIONE O DELLO STAFF. I fascicoli dei 25 erano SPESSI DA 8 A 28 CENTIMETRI. Pur con le omissioni, i parlamentari determinarono che si trattava di giornalisti dei SETTORI PIÙ IN VISTA DELLA STAMPA NAZIONALE, fra cui 4 o 5 dei maggiori quotidiani, le reti radiotelevisive e i due principali settimanali</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>E IL FATTO CHE VALE PER IL METODO: uno degli agenti sovietici operanti nei servizi alleati ERA VISITATORE ABITUALE DEL CENTRO DI DECRITTAZIONE e ne osservava i lavori; avvertì Mosca, e due colleghi poterono fuggire. IL PROGETTO CHE SCOPRIVA LE SPIE ERA OSSERVATO DA UNA SPIA</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — versante orientale: con lo schedario microfilmato e le carte manoscritte già censite, sono 3 MODI DI CONOSCERE L’EST DALL’OVEST, E NESSUNO DEI 3 È UN DOCUMENTO LETTO IN ORIGINALE</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
+          <t>Dominio 8 × Dominio 3 — e la lezione metodologica: LA CIFRA UFFICIALE È IL PRODOTTO DI UNA TRATTATIVA, NON DI UN CONTEGGIO. Chi cita «circa 50» cita ciò che fu concesso di verificare, non ciò che fu contato</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="3" t="inlineStr"/>
       <c r="J59" s="8" t="inlineStr">
         <is>
@@ -7880,90 +8428,98 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Commissione ristretta del Senato statunitense — relazione interlocutoria sui presunti piani di assassinio di capi di Stato stranieri</t>
+          <t>Commissione presidenziale statunitense sulle attività dell’agenzia informativa all’interno del Paese, 1975</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Rapporto del Senato numero 94-165, novantaquattresimo Congresso; DUECENT85 PAGINE, con opinioni aggiuntive, supplementari e separate; votata e pubblicata il 20 NOVEMBRE 1975</t>
+          <t>Nominata il 4 gennaio 1975 con ordine esecutivo, presieduta dal vicepresidente; relazione finale pubblicata l’11 giugno 1975</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Testo integrale liberamente consultabile in rete presso più archivi documentari</t>
+          <t>La SEZIONE SOPPRESSA — «Sintesi dei fatti: indagine sul coinvolgimento dell’agenzia in piani per assassinare capi di Stato stranieri», datata 5 giugno 1975, OTTANTASEI PAGINE — è stata pubblicata soltanto il 29 FEBBRAIO 2016 da un archivio universitario di sicurezza nazionale, insieme alle annotazioni a margine, ai memorandum dello staff che avvertivano delle conseguenze della cancellazione, e alle strategie della Casa Bianca per presentare al pubblico la relazione modificata</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>LA PUBBLICAZIONE FU CONTESTATA DALL’ESECUTIVO. Il 4 novembre 1975 OTIS PIKE, presidente della commissione respinse per iscritto il tentativo della Casa Bianca di sopprimerne le risultanze: «A mio avviso L’INTERESSE NAZIONALE È MEGLIO SERVITO FACENDO CONOSCERE AL POPOLO AMERICANO LA STORIA VERA E COMPLETA. Un principio fondamentale della nostra democrazia è che il popolo dev’essere informato degli errori del proprio governo, AFFINCHÉ ABBIA LA POSSIBILITÀ DI CORREGGERLI.» Espunti alcuni nomi di funzionari, la commissione votò la diffusione. L’introduzione afferma: «LE PROVE STABILISCONO CHE GLI STATI UNITI FURONO IMPLICATI IN DIVERSI PIANI DI ASSASSINIO»</t>
+          <t>UN’INTERA SEZIONE DI OTTANTASEI PAGINE FU RIMOSSA DALLA RELAZIONE FINALE PER ORDINE DELLA CASA BIANCA, sopra le obiezioni di alti funzionari e legali della commissione; l’editing fu condotto dal vice capo di gabinetto, con annotazioni a margine di suo pugno. La giustificazione addotta non fu di negare i fatti — già emersi — ma di proteggere metodi, fonti e tecniche. La sezione era fondata su ACCESSO LIMITATO AI DOCUMENTI e in larga misura su una dozzina di interviste ad alti responsabili</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MATERIA PERTINENTE AL DOMINIO 1 × DOMINIO 3: il rapporto dedica sezioni proprie ALL’USO DI FIGURE DEL SOTTOBOSCO CRIMINALE, articolato in due fasi, ai contatti con l’organizzazione criminale, e a un’intercettazione con coinvolgimento dell’agenzia informativa. Esamina inoltre espressamente LE ASSUNZIONI DEGLI OPERATIVI SULL’AUTORIZZAZIONE PRESIDENZIALE e L’IMPRESSIONE DEGLI ESECUTORI che l’operazione fosse autorizzata dal vertice</t>
+          <t>LA MODIFICA TESTUALE, DOCUMENTATA E ISTRUTTIVA: la bozza finale diceva che il presidente aveva chiesto alla commissione di indagare sui piani DOPO l’avvio dell’inchiesta, che lo staff non era riuscito a completarla, e che il presidente aveva poi chiesto che il materiale gli fosse consegnato. L’INTERVENTO INSERÌ UN DUBBIO, aggiungendo che non era chiaro se gli assassinî rientrassero nel mandato — RESUSCITANDO UNA QUESTIONE DI COMPETENZA GIÀ RISOLTA — E RIDUSSE IL PRESIDENTE A COMPARSA, affermando che egli aveva soltanto «concordato» con la decisione, anziché che era stato lui a rivelare l’esistenza dei piani e a dover modificare i termini di riferimento. Quanto agli ostacoli: a metà aprile 1975 il legale contava di chiudere la parte sugli assassinî entro il mese, ma l’agenzia RITARDÒ la consegna dei materiali e il segretario di Stato, che aveva promesso collaborazione, FORNÌ POCO</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>IL PUNTO CHE VALE PER TUTTA L’OPERA. Il sistema della NEGABILITÀ PLAUSIBILE non fu una conseguenza: era COSTRUITO DENTRO i piani. Il rapporto contiene sezioni intitolate «IL PERICOLO INSITO NELL’ESTENDERE ECCESSIVAMENTE LA DOTTRINA DELLA NEGABILITÀ PLAUSIBILE» e «IL PERICOLO DI USARE LA CIRCONLOCUZIONE». E LA COMMISSIONE — con potere di citazione, ottocento testimoni e centodiecimila documenti — NON FU IN GRADO DI AFFERMARE CATEGORICAMENTE SE ALCUN PRESIDENTE AVESSE EFFETTIVAMENTE APPROVATO QUEI PIANI. NON PERCHÉ LE PROVE FOSSERO STATE DISTRUTTE, MA PERCHÉ IL SISTEMA ERA STATO PROGETTATO PER PRODURRE QUELL’AMBIGUITÀ</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — LA VOCE PIÙ IMPORTANTE DEL REPERTORIO: in questo campo l’assenza di un ordine tracciabile NON È UNA LACUNA DELLA PROVA, È UN PRODOTTO DEL PROGETTO. E la disciplina della commissione va imitata per intero: essa NON CONCLUSE «dunque il presidente autorizzò», ma «NON POSSIAMO DETERMINARLO»</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
+          <t>IL TRITTICO DEL 1975, CHE È LA STRUTTURA PIÙ ISTRUTTIVA DELL’INTERO REPERTORIO. 3 INCHIESTE, UN ANNO, UNA MATERIA. Il Senato pubblicò contro l’opposizione presidenziale e concluse «non possiamo determinare». La Camera vide la propria relazione SOPPRESSA DALLA PROPRIA ASSEMBLEA con 246 voti contro 124, e fu quella che attribuiva la responsabilità al vertice politico. L’esecutivo fece EDITARE DALL’INTERNO la propria commissione, e il testo riemerse QUARANTUN ANNI DOPO. IN TUTTI E 3 I CASI CIÒ CHE FU SOPPRESSO ERA LA PARTE CHE PUNTAVA VERSO L’ALTO</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
+      <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="inlineStr"/>
-      <c r="L60" s="8" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>CONFERMATO — con una rettifica accertata dal Senato stesso</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>Commissione presidenziale sulle attivita dell'agenzia informativa all'interno degli Stati Uniti, nominata con ordine esecutivo del 4 GENNAIO 1975; relazione del giugno 1975. RETTIFICA ACCERTATA, da recare perche riguarda l'attendibilita della fonte: IL SENATO RILEVO CHE LA RELAZIONE DI QUESTA COMMISSIONE AVEVA QUALIFICATO ERRONEAMENTE COME 'RICHIAMI' PROVVEDIMENTI CHE IN REALTA NON LO ERANO E CHE NON EBBERO ALCUN EFFETTO NEGATIVO SULL'AVANZAMENTO DI CARRIERA DEI DESTINATARI NEGLI ANNI SUCCESSIVI. E un caso documentato di relazione ufficiale che attenua la portata di una sanzione, rilevato da un altro organo dello Stato: appartiene alla medesima famiglia dell'accertamento senza sanzione gia censita dal repertorio. COLLOCAZIONE NELLA SERIE: le 3 inchieste del 1975 sono note come l'ANNO DELL'INFORMAZIONE e vanno lette insieme, perche differiscono per autonomia dall'esecutivo: la commissione presidenziale e quella senatoriale lasciarono determinare l'agenda dall'esecutivo, quella della Camera no.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Rapporti fra agenzia informativa statunitense e stampa — accertamento parlamentare del 1976 e inchiesta giornalistica del 1977</t>
+          <t>Commissione ristretta della Camera statunitense sugli assassinî — relazione finale del gennaio 1979, e revisione scientifica del 1982</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; relazione finale della commissione senatoriale, Libro primo su intelligence estera e militare, 1976, consultabile in rete; articolo di rivista del 20 ottobre 1977, 25MILA PAROLE, frutto di 6 mesi di lavoro</t>
+          <t>Stati Uniti; relazione e 12 volumi di allegati per ciascun caso; le carte di lavoro sul primo caso furono declassificate negli anni Novanta in forza della legge del 1992</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>L’ACCERTAMENTO UFFICIALE: la commissione concluse che l’agenzia manteneva RAPPORTI COPERTI CON CIRCA 50 GIORNALISTI O DIPENDENTI DI ORGANI DI INFORMAZIONE STATUNITENSI, e precisò che circa 50 di quei rapporti riguardavano persone CHE FORNIVANO CONSAPEVOLMENTE informazioni, mentre le restanti IGNORAVANO DI AVERE A CHE FARE CON L’AGENZIA. La relazione NON FECE NOMI e non descrisse l’intera estensione del fenomeno</t>
+          <t>Il testo integrale è pubblicamente consultabile; l’organo di revisione istituito dalla legge del 1992 declassificò OLTRE SESSANTAMILA DOCUMENTI fra il 1994 e il 1998</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>LA TESI GIORNALISTICA, DA TENERE DISTINTA E MARCATA COME TALE: l’inchiesta del 1977 sostiene che OLTRE QUATTROCENTO giornalisti statunitensi avessero svolto incarichi riservati per l’agenzia nell’arco di 25 anni, dal 1953 al 1977, secondo documenti conservati presso la sede dell’agenzia; che i rapporti fossero taciti o espliciti, con «cooperazione, accomodamento e sovrapposizione»; e che i giornalisti prestassero servizi che andavano dalla semplice raccolta informativa al ruolo di intermediari con agenti nei Paesi dell’Est. Il sottotitolo dell’articolo ACCUSA LA COMMISSIONE DI AVER INSABBIATO. QUESTA È TESI D’AUTORE E NON ACCERTAMENTO</t>
+          <t>LA SEQUENZA, CHE È IL PUNTO. NEL DICEMBRE 1978 LA COMMISSIONE AVEVA GIÀ PREDISPOSTO UNA BOZZA DI RELAZIONE FINALE CHE CONCLUDEVA PER L’AUTORE SINGOLO. Resa disponibile un’analisi acustica di una registrazione radio, LA COMMISSIONE RIBALTÒ RAPIDAMENTE LA CONCLUSIONE e pubblicò che «prove scientifiche acustiche stabiliscono un’ALTA PROBABILITÀ che due uomini armati abbiano sparato», e che il fatto fosse PROBABILMENTE esito di una cospirazione. La catena delle stime: una società di consulenza indicò una probabilità del 50 per cento per un colpo ulteriore; due ricercatori universitari, riesaminando ed estendendo il lavoro, la portarono al NOVANTACINQUE. La commissione SUPERÒ INOLTRE LA DICHIARAZIONE DELL’AGENTE il cui microfono avrebbe registrato: egli affermava di non trovarsi sul posto, e la commissione stabilì che vi si trovava</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>IL DATO CHE VALE PIÙ DI ENTRAMBI, PERCHÉ RIGUARDA IL METODO DELL’INCHIESTA. Nel marzo 1976, in una riunione presso la sede dell’agenzia con il presidente e il vicepresidente della commissione, il direttore dello staff, il direttore dell’agenzia e il suo consigliere, FU CONCORDATO UN ACCESSO NEGOZIATO: l’agenzia rifiutò i fascicoli integrali e i nomi dei giornalisti e delle testate; due funzionari della commissione poterono esaminare versioni EPURATE dei fascicoli di 25 giornalisti scelti fra oltre quattrocento sintesi di un paragrafo ciascuna, CON I NOMI DELLE PERSONE E DELLE TESTATE OSCURATI; il presidente e il vicepresidente poterono vedere le versioni integre DI 5 SOLTANTO, al solo fine di attestare che nulla fosse nascosto oltre i nomi; E NESSUNO DEI 4 POTEVA RIFERIRNE AGLI ALTRI MEMBRI DELLA COMMISSIONE O DELLO STAFF. I fascicoli dei 25 erano SPESSI DA 8 A 28 CENTIMETRI. Pur con le omissioni, i parlamentari determinarono che si trattava di giornalisti dei SETTORI PIÙ IN VISTA DELLA STAMPA NAZIONALE, fra cui 4 o 5 dei maggiori quotidiani, le reti radiotelevisive e i due principali settimanali</t>
+          <t>I DISSENSI FURONO CONTEMPORANEI, NON POSTUMI: membri della commissione espressero opinioni dissenzienti negli allegati, obiettando che l’analisi acustica riceveva un PESO SPROPORZIONATO rispetto a prove fisiche contrarie; un consulente scrisse che il colpo dalla posizione contestata «non è escluso da alcuna delle testimonianze acustiche, MA NEPPURE È CONFERMATO»; e un membro scrisse: «ritengo che l’allegato A dimostrerà chiaramente UNA CORSA A CONCLUSIONI COSPIRATIVE»</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Dominio 8 × Dominio 3 — e la lezione metodologica: LA CIFRA UFFICIALE È IL PRODOTTO DI UNA TRATTATIVA, NON DI UN CONTEGGIO. Chi cita «circa 50» cita ciò che fu concesso di verificare, non ciò che fu contato</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
+          <t>LA REVISIONE: nel 1982 il comitato sull’acustica balistica dell’Accademia nazionale delle scienze, incaricato dal ministero della Giustizia, concluse che gli impulsi NON ERANO COLPI D’ARMA DA FUOCO e che il modello apparente era attribuibile a rumore casuale; l’errore più grave individuato fu che IL MOMENTO IN CUI I CONSULENTI RITENEVANO FOSSERO STATI ESPLOSI I COLPI ERA SBAGLIATO — la registrazione corrispondeva a CIRCA UN MINUTO DOPO. Nel 1988 una relazione parlamentare censurò la conclusione di probabile cospirazione. LA CONTROVERSIA TECNICA NON È CHIUSA: revisioni successive hanno rivendicato l’analisi originaria e sono state a loro volta riesaminate</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — È L’ERRORE OPPOSTO A TUTTI GLI ALTRI DEL REPERTORIO. Altrove l’organo ufficiale ha soppresso o concluso in difetto; qui HA RIBALTATO UNA BOZZA COMPLETA SULLA FORZA DI UN SOLO ACCERTAMENTO TECNICO, ha superato una testimonianza contraria, e ha pubblicato una conclusione che una revisione scientifica ha poi ricondotto al minuto sbagliato. È il «pollo induttivista» della Nota Metodologica, realizzato da una commissione parlamentare</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="3" t="inlineStr"/>
       <c r="J61" s="8" t="inlineStr">
         <is>
@@ -7976,32 +8532,32 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Commissione presidenziale statunitense sulle attività dell’agenzia informativa all’interno del Paese, 1975</t>
+          <t>Collegio di revisione istituito dalla legge statunitense del 1992 — relazione annuale 1995 e relazione finale 1998</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Nominata il 4 gennaio 1975 con ordine esecutivo, presieduta dal vicepresidente; relazione finale pubblicata l’11 giugno 1975</t>
+          <t>Stati Uniti; entrambe le relazioni sono pubblicamente consultabili</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>La SEZIONE SOPPRESSA — «Sintesi dei fatti: indagine sul coinvolgimento dell’agenzia in piani per assassinare capi di Stato stranieri», datata 5 giugno 1975, OTTANTASEI PAGINE — è stata pubblicata soltanto il 29 FEBBRAIO 2016 da un archivio universitario di sicurezza nazionale, insieme alle annotazioni a margine, ai memorandum dello staff che avvertivano delle conseguenze della cancellazione, e alle strategie della Casa Bianca per presentare al pubblico la relazione modificata</t>
+          <t>Il collegio impose a CIASCUNA AGENZIA una dichiarazione firmata SOTTO PENA DI FALSA TESTIMONIANZA, che descrivesse le ricerche compiute, i documenti individuati e le azioni intraprese per adempiere alla legge</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>UN’INTERA SEZIONE DI OTTANTASEI PAGINE FU RIMOSSA DALLA RELAZIONE FINALE PER ORDINE DELLA CASA BIANCA, sopra le obiezioni di alti funzionari e legali della commissione; l’editing fu condotto dal vice capo di gabinetto, con annotazioni a margine di suo pugno. La giustificazione addotta non fu di negare i fatti — già emersi — ma di proteggere metodi, fonti e tecniche. La sezione era fondata su ACCESSO LIMITATO AI DOCUMENTI e in larga misura su una dozzina di interviste ad alti responsabili</t>
+          <t>IL FATTO, RIPORTATO DALLE RELAZIONI STESSE: la legge entrò in vigore nell’ottobre 1992 e un mese dopo il servizio di protezione presidenziale avviò le proprie attività di adempimento. NEL GENNAIO 1995 QUEL SERVIZIO DISTRUSSE DUE SCATOLE DI RAPPORTI DI RICOGNIZIONE SULLA PROTEZIONE PRESIDENZIALE relativi al periodo 1961-1963 e ad alcuni viaggi dell’autunno 1963 — rapporti CHE ERANO GIÀ STATI ESAMINATI DALLA COMMISSIONE PARLAMENTARE DEL DECENNIO PRECEDENTE. LA DISTRUZIONE FU AUTORIZZATA DAL SERVIZIO DOPO L’ENTRATA IN VIGORE DELLA LEGGE ed eseguita presso il centro nazionale di conservazione POCO PRIMA CHE IL COLLEGIO NE CHIEDESSE L’ACCESSO</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>LA MODIFICA TESTUALE, DOCUMENTATA E ISTRUTTIVA: la bozza finale diceva che il presidente aveva chiesto alla commissione di indagare sui piani DOPO l’avvio dell’inchiesta, che lo staff non era riuscito a completarla, e che il presidente aveva poi chiesto che il materiale gli fosse consegnato. L’INTERVENTO INSERÌ UN DUBBIO, aggiungendo che non era chiaro se gli assassinî rientrassero nel mandato — RESUSCITANDO UNA QUESTIONE DI COMPETENZA GIÀ RISOLTA — E RIDUSSE IL PRESIDENTE A COMPARSA, affermando che egli aveva soltanto «concordato» con la decisione, anziché che era stato lui a rivelare l’esistenza dei piani e a dover modificare i termini di riferimento. Quanto agli ostacoli: a metà aprile 1975 il legale contava di chiudere la parte sugli assassinî entro il mese, ma l’agenzia RITARDÒ la consegna dei materiali e il segretario di Stato, che aveva promesso collaborazione, FORNÌ POCO</t>
+          <t>LA CRONOLOGIA CHE VA LETTA DI SEGUITO: il collegio apprese della distruzione CIRCA UNA SETTIMANA DOPO, mentre stava redigendo la richiesta di informazioni aggiuntive; riteneva quei fascicoli rilevanti perché riguardavano i viaggi del presidente NELLE SETTIMANE PRECEDENTI LA SUA MORTE; NEL MARZO 1995, in una riunione con il direttore del servizio, IL COLLEGIO FU ASSICURATO CHE IL SERVIZIO ERA IN PIENA OSSERVANZA DELLA LEGGE. Il collegio qualificò il fatto come «UN’APPARENTE VIOLAZIONE DELLA LEGGE» e chiese spiegazioni formali, che furono fornite per iscritto e in informativa orale. LA VICENDA NON DIVENNE DI PUBBLICO DOMINIO FINO AL 1998</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>IL TRITTICO DEL 1975, CHE È LA STRUTTURA PIÙ ISTRUTTIVA DELL’INTERO REPERTORIO. 3 INCHIESTE, UN ANNO, UNA MATERIA. Il Senato pubblicò contro l’opposizione presidenziale e concluse «non possiamo determinare». La Camera vide la propria relazione SOPPRESSA DALLA PROPRIA ASSEMBLEA con 246 voti contro 124, e fu quella che attribuiva la responsabilità al vertice politico. L’esecutivo fece EDITARE DALL’INTERNO la propria commissione, e il testo riemerse QUARANTUN ANNI DOPO. IN TUTTI E 3 I CASI CIÒ CHE FU SOPPRESSO ERA LA PARTE CHE PUNTAVA VERSO L’ALTO</t>
+          <t>Metodologia — È IL CORONAMENTO DEL REPERTORIO: UNA LEGGE CHE IMPONE LA CONSERVAZIONE NON CONSERVA. Ma fa una cosa sola, e non da poco: RENDE LA VIOLAZIONE NOMINABILE, DATABILE E SCRIVIBILE IN UN ATTO PUBBLICO — ed è esattamente ciò che il collegio ha fatto</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -8011,56 +8567,48 @@
       </c>
       <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — con una rettifica accertata dal Senato stesso</t>
-        </is>
-      </c>
-      <c r="K62" s="11" t="inlineStr">
-        <is>
-          <t>6.8.2026</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
-        <is>
-          <t>Commissione presidenziale sulle attivita dell'agenzia informativa all'interno degli Stati Uniti, nominata con ordine esecutivo del 4 GENNAIO 1975; relazione del giugno 1975. RETTIFICA ACCERTATA, da recare perche riguarda l'attendibilita della fonte: IL SENATO RILEVO CHE LA RELAZIONE DI QUESTA COMMISSIONE AVEVA QUALIFICATO ERRONEAMENTE COME 'RICHIAMI' PROVVEDIMENTI CHE IN REALTA NON LO ERANO E CHE NON EBBERO ALCUN EFFETTO NEGATIVO SULL'AVANZAMENTO DI CARRIERA DEI DESTINATARI NEGLI ANNI SUCCESSIVI. E un caso documentato di relazione ufficiale che attenua la portata di una sanzione, rilevato da un altro organo dello Stato: appartiene alla medesima famiglia dell'accertamento senza sanzione gia censita dal repertorio. COLLOCAZIONE NELLA SERIE: le 3 inchieste del 1975 sono note come l'ANNO DELL'INFORMAZIONE e vanno lette insieme, perche differiscono per autonomia dall'esecutivo: la commissione presidenziale e quella senatoriale lasciarono determinare l'agenda dall'esecutivo, quella della Camera no.</t>
-        </is>
-      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K62" s="8" t="inlineStr"/>
+      <c r="L62" s="8" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Commissione ristretta della Camera statunitense sugli assassinî — relazione finale del gennaio 1979, e revisione scientifica del 1982</t>
+          <t>Archivi statali russi — regime di accesso dal 1991 a oggi</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; relazione e 12 volumi di allegati per ciascun caso; le carte di lavoro sul primo caso furono declassificate negli anni Novanta in forza della legge del 1992</t>
+          <t>Mosca: Archivio di Stato della Federazione Russa; Archivio di Stato di storia socio-politica; Archivio di Stato di storia contemporanea; Archivio della politica estera; Archivio dell’economia</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Il testo integrale è pubblicamente consultabile; l’organo di revisione istituito dalla legge del 1992 declassificò OLTRE SESSANTAMILA DOCUMENTI fra il 1994 e il 1998</t>
+          <t>LA APERTURA. Dopo il fallito colpo di Stato dell’agosto 1991 FORZE INSORGENTI OCCUPARONO FISICAMENTE I PRINCIPALI ARCHIVI POLITICI PER IMPEDIRE LA DISTRUZIONE DI DOCUMENTI compromettenti. L’amministrazione archivistica sovietica fu sostituita da un organo riformatore diretto da uno storico, che promosse la MASSIMA DESECRETAZIONE; i regolamenti del 1991 e 1992 IMPOSERO L’ACCESSO SCIENTIFICO E PUBBLICO a materiali fino ad allora segreti. L’Archivio di Stato della Federazione fu istituito il 28 aprile 1992 e conserva CIRCA 7 MILIONI DI FASCICOLI</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>LA SEQUENZA, CHE È IL PUNTO. NEL DICEMBRE 1978 LA COMMISSIONE AVEVA GIÀ PREDISPOSTO UNA BOZZA DI RELAZIONE FINALE CHE CONCLUDEVA PER L’AUTORE SINGOLO. Resa disponibile un’analisi acustica di una registrazione radio, LA COMMISSIONE RIBALTÒ RAPIDAMENTE LA CONCLUSIONE e pubblicò che «prove scientifiche acustiche stabiliscono un’ALTA PROBABILITÀ che due uomini armati abbiano sparato», e che il fatto fosse PROBABILMENTE esito di una cospirazione. La catena delle stime: una società di consulenza indicò una probabilità del 50 per cento per un colpo ulteriore; due ricercatori universitari, riesaminando ed estendendo il lavoro, la portarono al NOVANTACINQUE. La commissione SUPERÒ INOLTRE LA DICHIARAZIONE DELL’AGENTE il cui microfono avrebbe registrato: egli affermava di non trovarsi sul posto, e la commissione stabilì che vi si trovava</t>
+          <t>I FONDI UTILI: la «collezione 89» dell’archivio di storia contemporanea raccoglie CIRCA TREMILA FASCICOLI declassificati per il periodo 1922-1991, desecretati principalmente NEL CORSO DELLA PREPARAZIONE DEL PROCESSO SUL PARTITO COMUNISTA nel 1992 da una commissione istituita dal presidente — ed è consultabile DA UN SOLO COMPUTER nella sala di lettura. L’archivio della politica estera declassifica per singolo Paese e «lentamente, con enfasi sul lentamente»: sono stati progressivamente rilasciati fondi su Stati Uniti, entrambe le Germanie, Polonia, Ungheria, Cecoslovacchia, Bulgaria, Romania, Cina e Giappone</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>I DISSENSI FURONO CONTEMPORANEI, NON POSTUMI: membri della commissione espressero opinioni dissenzienti negli allegati, obiettando che l’analisi acustica riceveva un PESO SPROPORZIONATO rispetto a prove fisiche contrarie; un consulente scrisse che il colpo dalla posizione contestata «non è escluso da alcuna delle testimonianze acustiche, MA NEPPURE È CONFERMATO»; e un membro scrisse: «ritengo che l’allegato A dimostrerà chiaramente UNA CORSA A CONCLUSIONI COSPIRATIVE»</t>
+          <t>LA RICHIUSURA, DA REGISTRARE PUNTO PER PUNTO. 5 trascrizioni integrali di sedute del massimo organo di partito risultano «DECLASSIFICATE NEL 2008 MA MAI RESE DISPONIBILI»; le annotazioni archivistiche ne indicano l’ampiezza — talvolta oltre duecento pagine — e la loro indisponibilità è stata definita UNA LACUNA CRUCIALE NEL DOCUMENTO STORICO. NEL 2016 IL DIRETTORE DELL’ARCHIVIO DI STATO, IN CARICA DAL 1992, FU RIMOSSO e riassegnato a consulente scientifico: aveva sovrinteso alla declassificazione di documenti sensibili, fra cui l’autorizzazione ai massimi livelli della repressione di Novočerkassk del 1962, in cui le forze di sicurezza uccisero 26 operai in sciopero</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>LA REVISIONE: nel 1982 il comitato sull’acustica balistica dell’Accademia nazionale delle scienze, incaricato dal ministero della Giustizia, concluse che gli impulsi NON ERANO COLPI D’ARMA DA FUOCO e che il modello apparente era attribuibile a rumore casuale; l’errore più grave individuato fu che IL MOMENTO IN CUI I CONSULENTI RITENEVANO FOSSERO STATI ESPLOSI I COLPI ERA SBAGLIATO — la registrazione corrispondeva a CIRCA UN MINUTO DOPO. Nel 1988 una relazione parlamentare censurò la conclusione di probabile cospirazione. LA CONTROVERSIA TECNICA NON È CHIUSA: revisioni successive hanno rivendicato l’analisi originaria e sono state a loro volta riesaminate</t>
+          <t>IL 28 DICEMBRE 2021 LA CORTE SUPREMA HA ORDINATO LA LIQUIDAZIONE DELL’ASSOCIAZIONE MEMORIAL INTERNAZIONALE, confermando una raccomandazione governativa dell’11 novembre, per asserita violazione della normativa sugli «agenti stranieri». Fondata nel 1987, l’associazione aveva costituito banche dati con nomi e dati biografici di OLTRE 3 MILIONI DI VITTIME della repressione, un archivio comprendente i FASCICOLI PERSONALI DI SESSANTAMILA VITTIME e materiali del movimento dissidente, e una biblioteca di oltre quarantamila volumi</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — È L’ERRORE OPPOSTO A TUTTI GLI ALTRI DEL REPERTORIO. Altrove l’organo ufficiale ha soppresso o concluso in difetto; qui HA RIBALTATO UNA BOZZA COMPLETA SULLA FORZA DI UN SOLO ACCERTAMENTO TECNICO, ha superato una testimonianza contraria, e ha pubblicato una conclusione che una revisione scientifica ha poi ricondotto al minuto sbagliato. È il «pollo induttivista» della Nota Metodologica, realizzato da una commissione parlamentare</t>
+          <t>Tomo II — CONSEGUENZA METODOLOGICA CHE VA DICHIARATA: il versante orientale NON PUÒ ESSERE DOCUMENTATO IN MODO SIMMETRICO A QUELLO OCCIDENTALE. Le 3 fonti orientali già censite sono copie, schedari e inferenze conservati in Occidente; e gli originali russi sono progressivamente meno accessibili. L’ASIMMETRIA NON È UN PREGIUDIZIO DEL RICERCATORE: È UN FATTO SULLE FONTI, E VA SCRITTO NEL TESTO</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
@@ -8080,40 +8628,44 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Collegio di revisione istituito dalla legge statunitense del 1992 — relazione annuale 1995 e relazione finale 1998</t>
+          <t>Memorandum dello Stato maggiore congiunto statunitense al ministro della Difesa, 13 marzo 1962 — «Giustificazione per l’intervento militare a Cuba»</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; entrambe le relazioni sono pubblicamente consultabili</t>
+          <t>Stati Uniti; originale presso l’Archivio nazionale a College Park</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Il collegio impose a CIASCUNA AGENZIA una dichiarazione firmata SOTTO PENA DI FALSA TESTIMONIANZA, che descrivesse le ricerche compiute, i documenti individuati e le azioni intraprese per adempiere alla legge</t>
+          <t>DECLASSIFICATO IL 18 NOVEMBRE 1997 dal collegio di revisione istituito con la legge del 1992, insieme a CIRCA MILLECINQUECENTO PAGINE di documenti militari per il 1962-1964. TRENTACINQUE ANNI DI CLASSIFICAZIONE</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>IL FATTO, RIPORTATO DALLE RELAZIONI STESSE: la legge entrò in vigore nell’ottobre 1992 e un mese dopo il servizio di protezione presidenziale avviò le proprie attività di adempimento. NEL GENNAIO 1995 QUEL SERVIZIO DISTRUSSE DUE SCATOLE DI RAPPORTI DI RICOGNIZIONE SULLA PROTEZIONE PRESIDENZIALE relativi al periodo 1961-1963 e ad alcuni viaggi dell’autunno 1963 — rapporti CHE ERANO GIÀ STATI ESAMINATI DALLA COMMISSIONE PARLAMENTARE DEL DECENNIO PRECEDENTE. LA DISTRUZIONE FU AUTORIZZATA DAL SERVIZIO DOPO L’ENTRATA IN VIGORE DELLA LEGGE ed eseguita presso il centro nazionale di conservazione POCO PRIMA CHE IL COLLEGIO NE CHIEDESSE L’ACCESSO</t>
+          <t>CHE COSA È: una raccolta di BOZZE di memorandum redatte dal dipartimento della Difesa e dal rappresentante dello Stato maggiore presso un gruppo di studio, presentata al ministro COME SOTTOPOSIZIONE PRELIMINARE A FINI DI PIANIFICAZIONE, CON UN SOLO PARAGRAFO APPROVATO, e firmata dal presidente dello Stato maggiore congiunto. Le proposte furono generate in risposta a una richiesta nel quadro di un’operazione coperta già in corso</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>LA CRONOLOGIA CHE VA LETTA DI SEGUITO: il collegio apprese della distruzione CIRCA UNA SETTIMANA DOPO, mentre stava redigendo la richiesta di informazioni aggiuntive; riteneva quei fascicoli rilevanti perché riguardavano i viaggi del presidente NELLE SETTIMANE PRECEDENTI LA SUA MORTE; NEL MARZO 1995, in una riunione con il direttore del servizio, IL COLLEGIO FU ASSICURATO CHE IL SERVIZIO ERA IN PIENA OSSERVANZA DELLA LEGGE. Il collegio qualificò il fatto come «UN’APPARENTE VIOLAZIONE DELLA LEGGE» e chiese spiegazioni formali, che furono fornite per iscritto e in informativa orale. LA VICENDA NON DIVENNE DI PUBBLICO DOMINIO FINO AL 1998</t>
+          <t>CHE COSA PROPONEVA: una serie di PRETESTI da fabbricare — attacchi simulati contro una base e contro navi, abbattimenti simulati di aerei, dirottamenti fabbricati, UNA CAMPAGNA DI TERRORE DA ATTRIBUIRE A CUBA IN CITTÀ STATUNITENSI, l’affondamento «reale o simulato» di un’imbarcazione di profughi, documenti falsi e interviste inscenate — allo scopo di porre gli Stati Uniti nella «APPARENTE POSIZIONE DI SUBIRE LAMENTELE DIFENDIBILI da parte di un governo avventato e irresponsabile»</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — È IL CORONAMENTO DEL REPERTORIO: UNA LEGGE CHE IMPONE LA CONSERVAZIONE NON CONSERVA. Ma fa una cosa sola, e non da poco: RENDE LA VIOLAZIONE NOMINABILE, DATABILE E SCRIVIBILE IN UN ATTO PUBBLICO — ed è esattamente ciò che il collegio ha fatto</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
+          <t>LO STATUTO, CHE VA DICHIARATO OGNI VOLTA CHE IL DOCUMENTO SI CITA. NON FU ATTUATO: la dirigenza civile lo respinse e nessuna delle operazioni proposte fu mai avviata; il firmatario fu rimosso dall’incarico nel dicembre 1962 e riassegnato a un comando alleato; nessuno fu perseguito. CHI LO CITA COME PROVA CHE OPERAZIONI DEL GENERE SIANO AVVENUTE NE FA UN USO SCORRETTO. Ciò che esso prova è diverso e sufficiente: CHE IL PIÙ ALTO COMANDO MILITARE DI UNA DEMOCRAZIA MISE PER ISCRITTO, IN FORMA DI PROPOSTA FORMALE, L’INSCENAMENTO DI ATTENTATI CONTRO I PROPRI CITTADINI DA ATTRIBUIRE A UNO STATO ESTERO</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 7 e Metodologia — INSIEME ALL’OPERAZIONE TEDESCA DEL 1978, GIÀ CENSITA, DELIMITA LA CATEGORIA: qui la proposta respinta e mai eseguita; là l’operazione eseguita, in scala minima, e in seguito ammessa. Fra questi due estremi documentati sta tutto ciò che sull’argomento si può affermare</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>verificato 4.8.2026</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="3" t="inlineStr"/>
       <c r="J64" s="8" t="inlineStr">
         <is>
@@ -8126,37 +8678,37 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Archivi statali russi — regime di accesso dal 1991 a oggi</t>
+          <t>Archivio storico della Polizia Nazionale del Guatemala</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Mosca: Archivio di Stato della Federazione Russa; Archivio di Stato di storia socio-politica; Archivio di Stato di storia contemporanea; Archivio della politica estera; Archivio dell’economia</t>
+          <t>Città del Guatemala, avenida La Pedrera; sala di lettura pubblica dal 2009; portale digitale ospitato da un ateneo statunitense dal dicembre 2011</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>LA APERTURA. Dopo il fallito colpo di Stato dell’agosto 1991 FORZE INSORGENTI OCCUPARONO FISICAMENTE I PRINCIPALI ARCHIVI POLITICI PER IMPEDIRE LA DISTRUZIONE DI DOCUMENTI compromettenti. L’amministrazione archivistica sovietica fu sostituita da un organo riformatore diretto da uno storico, che promosse la MASSIMA DESECRETAZIONE; i regolamenti del 1991 e 1992 IMPOSERO L’ACCESSO SCIENTIFICO E PUBBLICO a materiali fino ad allora segreti. L’Archivio di Stato della Federazione fu istituito il 28 aprile 1992 e conserva CIRCA 7 MILIONI DI FASCICOLI</t>
+          <t>ACCESSO DICHIARATO SENZA ALCUN REQUISITO: chiunque, da qualunque parte del mondo, può consultare la collezione digitalizzata; l’archivio evade inoltre richieste puntuali di pubblici ministeri, investigatori per i diritti umani, familiari degli scomparsi, studiosi e giornalisti. Copie digitali sicure sono conservate anche presso un governo europeo e presso l’ateneo statunitense</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>I FONDI UTILI: la «collezione 89» dell’archivio di storia contemporanea raccoglie CIRCA TREMILA FASCICOLI declassificati per il periodo 1922-1991, desecretati principalmente NEL CORSO DELLA PREPARAZIONE DEL PROCESSO SUL PARTITO COMUNISTA nel 1992 da una commissione istituita dal presidente — ed è consultabile DA UN SOLO COMPUTER nella sala di lettura. L’archivio della politica estera declassifica per singolo Paese e «lentamente, con enfasi sul lentamente»: sono stati progressivamente rilasciati fondi su Stati Uniti, entrambe le Germanie, Polonia, Ungheria, Cecoslovacchia, Bulgaria, Romania, Cina e Giappone</t>
+          <t>IL RINVENIMENTO. IL 5 LUGLIO 2005 funzionari dell’ufficio del difensore civico per i diritti umani entrarono in un DEPOSITO DI MUNIZIONI FATISCENTE E INFESTATO DAI RATTI, nel centro della capitale, PER INDAGARE SU DENUNCE RELATIVE A ESPLOSIVI CONSERVATI IMPROPRIAMENTE. Durante l’ispezione trovarono una vasta raccolta di documenti, in 5 EDIFICI e in avanzato stato di degrado: CIRCA OTTANTA MILIONI DI PAGINE, appartenenti alla polizia nazionale — istituzione così legata a repressione, rapimenti, sparizioni, tortura e assassinî che gli accordi di pace del 1996 ne imposero LO SCIOGLIMENTO TOTALE. I documenti coprono l’intera storia del corpo, dalla fondazione a fine ottocento allo scioglimento nel 1997</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>LA RICHIUSURA, DA REGISTRARE PUNTO PER PUNTO. 5 trascrizioni integrali di sedute del massimo organo di partito risultano «DECLASSIFICATE NEL 2008 MA MAI RESE DISPONIBILI»; le annotazioni archivistiche ne indicano l’ampiezza — talvolta oltre duecento pagine — e la loro indisponibilità è stata definita UNA LACUNA CRUCIALE NEL DOCUMENTO STORICO. NEL 2016 IL DIRETTORE DELL’ARCHIVIO DI STATO, IN CARICA DAL 1992, FU RIMOSSO e riassegnato a consulente scientifico: aveva sovrinteso alla declassificazione di documenti sensibili, fra cui l’autorizzazione ai massimi livelli della repressione di Novočerkassk del 1962, in cui le forze di sicurezza uccisero 26 operai in sciopero</t>
+          <t>LA MESSA IN SICUREZZA: nello stesso mese l’ufficio del difensore civico OTTENNE UN ORDINE GIUDIZIARIO che lo autorizzava a proteggere il sito e ad accedere ai documenti, IMPEDENDONE LA RIMOZIONE O LA DISTRUZIONE da parte di non autorizzati. Le condizioni erano di muffa, infestazioni e danni da acqua in magazzini non sorvegliati. Il salvataggio e la digitalizzazione iniziarono nel 2006 con sostegno internazionale, studenti universitari e volontari; dal 2009 l’archivio è passato sotto il ministero della Cultura. Digitalizzate circa VENTI MILIONI DI IMMAGINI al 2017, circa un quarto del totale; ventitré milioni citati nel 2019</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>IL 28 DICEMBRE 2021 LA CORTE SUPREMA HA ORDINATO LA LIQUIDAZIONE DELL’ASSOCIAZIONE MEMORIAL INTERNAZIONALE, confermando una raccomandazione governativa dell’11 novembre, per asserita violazione della normativa sugli «agenti stranieri». Fondata nel 1987, l’associazione aveva costituito banche dati con nomi e dati biografici di OLTRE 3 MILIONI DI VITTIME della repressione, un archivio comprendente i FASCICOLI PERSONALI DI SESSANTAMILA VITTIME e materiali del movimento dissidente, e una biblioteca di oltre quarantamila volumi</t>
+          <t>IL CONTENUTO E L’USO: registri di crimini e violenze, e REGISTRI DI CONTROLLO SOCIALE E SORVEGLIANZA, in specie di esponenti politici dell’opposizione; OLTRE 900.000 FASCICOLI PERSONALI con nomi, fotografie, impronte digitali e annotazioni sulle attività politiche. L’archivio ha prodotto PROVE UTILIZZATE IN PROCESSI, fra cui la condanna nel 2011 di due ex agenti per la sparizione di un sindacalista avvenuta nel 1984. MA IL RITROVAMENTO NON BASTA: nel 2019 furono lanciati appelli internazionali per proteggerlo, e nel ventennale, nell’agosto 2025, è stato descritto come «INVISIBILE, MESSO A TACERE E QUASI ABBANDONATO»</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Tomo II — CONSEGUENZA METODOLOGICA CHE VA DICHIARATA: il versante orientale NON PUÒ ESSERE DOCUMENTATO IN MODO SIMMETRICO A QUELLO OCCIDENTALE. Le 3 fonti orientali già censite sono copie, schedari e inferenze conservati in Occidente; e gli originali russi sono progressivamente meno accessibili. L’ASIMMETRIA NON È UN PREGIUDIZIO DEL RICERCATORE: È UN FATTO SULLE FONTI, E VA SCRITTO NEL TESTO</t>
+          <t>Metodologia — È IL CORONAMENTO DELLA SERIE: il più grande deposito pubblico di atti di polizia dell’America Latina fu trovato PER CASO, mentre si indagava su una denuncia per esplosivi mal conservati; fu salvato da UN ORDINE GIUDIZIARIO OTTENUTO IN POCHI GIORNI; e vent’anni dopo rischia l’abbandono. TROVARE UN ARCHIVIO E CONSERVARLO SONO DUE OPERE DISTINTE</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
@@ -8176,37 +8728,37 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Memorandum dello Stato maggiore congiunto statunitense al ministro della Difesa, 13 marzo 1962 — «Giustificazione per l’intervento militare a Cuba»</t>
+          <t>Direttive italiane di desecretazione e versamento — 2008, 2014, 2021 — e Sala delle Raccolte speciali dell’Archivio centrale dello Stato</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Stati Uniti; originale presso l’Archivio nazionale a College Park</t>
+          <t>Roma; consultazione ESCLUSIVAMENTE SU APPUNTAMENTO presso la Sala delle Raccolte speciali, al secondo piano dell’Istituto</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>DECLASSIFICATO IL 18 NOVEMBRE 1997 dal collegio di revisione istituito con la legge del 1992, insieme a CIRCA MILLECINQUECENTO PAGINE di documenti militari per il 1962-1964. TRENTACINQUE ANNI DI CLASSIFICAZIONE</t>
+          <t>LE DIRETTIVE: quella del 2008; quella del 22 APRILE 2014, in Gazzetta Ufficiale n. 100 del 2 maggio, che dispone CON PROCEDURA STRAORDINARIA il versamento all’Archivio centrale e agli Archivi di Stato della documentazione relativa a 9 STRAGI — Piazza Fontana 1969, Gioia Tauro 1970, Peteano 1972, Questura di Milano 1973, Piazza della Loggia 1974, Italicus 1974, Ustica 1980, stazione di Bologna 1980, Rapido 904 1984; quella del 2 DICEMBRE 2014, che invita a completare in via definitiva i versamenti SUL SEQUESTRO E L’UCCISIONE DI ALDO MORO; e quella dell’AGOSTO 2021, in Gazzetta Ufficiale n. 190 del 10 agosto, che ne amplia l’ambito</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CHE COSA È: una raccolta di BOZZE di memorandum redatte dal dipartimento della Difesa e dal rappresentante dello Stato maggiore presso un gruppo di studio, presentata al ministro COME SOTTOPOSIZIONE PRELIMINARE A FINI DI PIANIFICAZIONE, CON UN SOLO PARAGRAFO APPROVATO, e firmata dal presidente dello Stato maggiore congiunto. Le proposte furono generate in risposta a una richiesta nel quadro di un’operazione coperta già in corso</t>
+          <t>LA MISURA: i versamenti sono iniziati il 1° agosto 2014 e ammontano a SETTANTASETTE VERSAMENTI DA 1506 UFFICI PRODUTTORI, per CIRCA DUEMILA FALDONI, in formato cartaceo e digitale. Il Comitato ha sollecitato le amministrazioni I CUI VERSAMENTI RISULTANO ANCORA ESIGUI O DEL TUTTO ASSENTI, e la Direzione generale Archivi ha compilato UNA MAPPATURA PUNTUALE dei versamenti presso tutti gli Archivi di Stato, individuandone le carenze</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>CHE COSA PROPONEVA: una serie di PRETESTI da fabbricare — attacchi simulati contro una base e contro navi, abbattimenti simulati di aerei, dirottamenti fabbricati, UNA CAMPAGNA DI TERRORE DA ATTRIBUIRE A CUBA IN CITTÀ STATUNITENSI, l’affondamento «reale o simulato» di un’imbarcazione di profughi, documenti falsi e interviste inscenate — allo scopo di porre gli Stati Uniti nella «APPARENTE POSIZIONE DI SUBIRE LAMENTELE DIFENDIBILI da parte di un governo avventato e irresponsabile»</t>
+          <t>IL FONDO CHE INTERESSA DIRETTAMENTE QUEST’OPERA: nelle Raccolte speciali è confluita anche la documentazione del Ministero dell’Interno prodotta dalla DIVISIONE AFFARI RISERVATI della Pubblica Sicurezza, SEQUESTRATA NEL 1996 DALLA DIGOS DI ROMA presso un deposito di Circonvallazione Appia, e versata all’Archivio centrale IN CIRCA SETTECENTO FALDONI IL 14 LUGLIO 2017 — ventun anni dopo il sequestro. Una cospicua parte fu esaminata da diverse Procure nei processi sulle stragi e sul terrorismo. È DUNQUE ANCORA UNA PERQUISIZIONE ALL’ORIGINE</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>LO STATUTO, CHE VA DICHIARATO OGNI VOLTA CHE IL DOCUMENTO SI CITA. NON FU ATTUATO: la dirigenza civile lo respinse e nessuna delle operazioni proposte fu mai avviata; il firmatario fu rimosso dall’incarico nel dicembre 1962 e riassegnato a un comando alleato; nessuno fu perseguito. CHI LO CITA COME PROVA CHE OPERAZIONI DEL GENERE SIANO AVVENUTE NE FA UN USO SCORRETTO. Ciò che esso prova è diverso e sufficiente: CHE IL PIÙ ALTO COMANDO MILITARE DI UNA DEMOCRAZIA MISE PER ISCRITTO, IN FORMA DI PROPOSTA FORMALE, L’INSCENAMENTO DI ATTENTATI CONTRO I PROPRI CITTADINI DA ATTRIBUIRE A UNO STATO ESTERO</t>
+          <t>LE CRITICHE, DOCUMENTATE E DA REGISTRARE. Le associazioni dei familiari delle vittime e la rete degli archivi denunciano che «CHI DEVE FARLO NON VERSA I DOCUMENTI E CHI LO FA NE VERSA DI GIÀ NOTI, CHE QUINDI NON AGGIUNGONO NULLA», e chiedono: apertura degli ARCHIVI PERIFERICI, comprese le prefetture; prosecuzione della DIGITALIZZAZIONE, SINORA LIMITATA; applicazione della direttiva ANCHE DA PARTE DI CAMERA E SENATO; versamento dei documenti sulle STRUTTURE SEGRETE ED EVERSIVE per contestualizzare; che si eviti LO SMEMBRAMENTO degli archivi; e che DOPO TRENT’ANNI DAI FATTI SI VERSI TUTTO. Già a un anno dalla direttiva il sovrintendente dell’Archivio centrale poneva pubblicamente le domande: quante amministrazioni l’avessero recepita e attuata, COME FOSSERO STATI SELEZIONATI I DOCUMENTI, QUALI GARANZIE AVESSERO I CITTADINI CHE IL MATERIALE DEPOSITATO FOSSE COMPLETO, e se fossero valutati anche fatti non citati nella direttiva</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Dominio 7 e Metodologia — INSIEME ALL’OPERAZIONE TEDESCA DEL 1978, GIÀ CENSITA, DELIMITA LA CATEGORIA: qui la proposta respinta e mai eseguita; là l’operazione eseguita, in scala minima, e in seguito ammessa. Fra questi due estremi documentati sta tutto ciò che sull’argomento si può affermare</t>
+          <t>Tomo III — LA MISURA COMPARATIVA CHE CHIUDE LA TAVOLA: venti anni nel Regno Unito, 25 negli Stati Uniti con clausola di certificazione, 50 o cento in Francia con declassificazione preventiva reintrodotta, NESSUN TERMINE in Spagna, fino a centoventi anni in un caso tedesco. L’ITALIA NON HA UN TERMINE GENERALE: HA 3 DIRETTIVE STRAORDINARIE FONDATE SULL’EVENTO E NON SUL TEMPO. Il che comporta una conseguenza esatta: CIÒ CHE NON È NOMINATO NON È COPERTO</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -8226,37 +8778,37 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Archivio storico della Polizia Nazionale del Guatemala</t>
+          <t>Legge italiana 3 agosto 2007 numero 124, capo quinto — disciplina del segreto</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Città del Guatemala, avenida La Pedrera; sala di lettura pubblica dal 2009; portale digitale ospitato da un ateneo statunitense dal dicembre 2011</t>
+          <t>Italia; pubblicata nella Gazzetta Ufficiale del 13 agosto 2007, numero 187</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ACCESSO DICHIARATO SENZA ALCUN REQUISITO: chiunque, da qualunque parte del mondo, può consultare la collezione digitalizzata; l’archivio evade inoltre richieste puntuali di pubblici ministeri, investigatori per i diritti umani, familiari degli scomparsi, studiosi e giornalisti. Copie digitali sicure sono conservate anche presso un governo europeo e presso l’ateneo statunitense</t>
+          <t>RETTIFICA A QUANTO AFFERMATO IN VOCI PRECEDENTI DI QUESTO REPERTORIO: È ERRATO DIRE CHE L’ITALIA NON HA UN TERMINE. Prima del 2007 il vincolo del segreto di Stato NON AVEVA ALCUN LIMITE TEMPORALE; l’articolo 39 lo ha introdotto: 15 ANNI, prorogabili con provvedimento motivato del Presidente del Consiglio trasmesso al Comitato parlamentare per la sicurezza, PER UNA DURATA COMPLESSIVA MASSIMA DI TRENTA ANNI. Decorsi 15 anni, CHIUNQUE VI ABBIA INTERESSE può chiedere al Presidente del Consiglio l’accesso; entro trenta giorni questi consente l’accesso o dispone proroga motivata. Il vincolo può cessare anche prima, quando siano venute meno le esigenze</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>IL RINVENIMENTO. IL 5 LUGLIO 2005 funzionari dell’ufficio del difensore civico per i diritti umani entrarono in un DEPOSITO DI MUNIZIONI FATISCENTE E INFESTATO DAI RATTI, nel centro della capitale, PER INDAGARE SU DENUNCE RELATIVE A ESPLOSIVI CONSERVATI IMPROPRIAMENTE. Durante l’ispezione trovarono una vasta raccolta di documenti, in 5 EDIFICI e in avanzato stato di degrado: CIRCA OTTANTA MILIONI DI PAGINE, appartenenti alla polizia nazionale — istituzione così legata a repressione, rapimenti, sparizioni, tortura e assassinî che gli accordi di pace del 1996 ne imposero LO SCIOGLIMENTO TOTALE. I documenti coprono l’intera storia del corpo, dalla fondazione a fine ottocento allo scioglimento nel 1997</t>
+          <t>LA NORMA CHE RIGUARDA DIRETTAMENTE LA MATERIA DI QUEST’OPERA, E CHE NESSUN ALTRO ORDINAMENTO QUI CENSITO POSSIEDE IN QUESTA FORMA: NON POSSONO ESSERE COPERTI DAL SEGRETO DI STATO i fatti eversivi dell’ordine costituzionale, i fatti di terrorismo, i delitti di STRAGE COMUNE e di strage con finalità di attentare alla sicurezza dello Stato, l’ASSOCIAZIONE DI TIPO MAFIOSO e lo SCAMBIO ELETTORALE POLITICO-MAFIOSO. Non è un termine più breve: È UN’ESCLUSIONE DI MATERIA</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>LA MESSA IN SICUREZZA: nello stesso mese l’ufficio del difensore civico OTTENNE UN ORDINE GIUDIZIARIO che lo autorizzava a proteggere il sito e ad accedere ai documenti, IMPEDENDONE LA RIMOZIONE O LA DISTRUZIONE da parte di non autorizzati. Le condizioni erano di muffa, infestazioni e danni da acqua in magazzini non sorvegliati. Il salvataggio e la digitalizzazione iniziarono nel 2006 con sostegno internazionale, studenti universitari e volontari; dal 2009 l’archivio è passato sotto il ministero della Cultura. Digitalizzate circa VENTI MILIONI DI IMMAGINI al 2017, circa un quarto del totale; ventitré milioni citati nel 2019</t>
+          <t>LE GARANZIE PROCESSUALI: se un testimone oppone il segreto, l’autorità giudiziaria ne informa il Presidente del Consiglio; SE ENTRO TRENTA GIORNI NON GIUNGE CONFERMA, L’AUTORITÀ GIUDIZIARIA ACQUISISCE LA NOTIZIA. Se la conferma giunge, il Presidente deve darne comunicazione motivata al Comitato parlamentare, il quale, SE RITIENE INFONDATA L’OPPOSIZIONE, NE RIFERISCE A CIASCUNA DELLE CAMERE. E infine: IN NESSUN CASO IL SEGRETO DI STATO È OPPONIBILE ALLA CORTE COSTITUZIONALE</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>IL CONTENUTO E L’USO: registri di crimini e violenze, e REGISTRI DI CONTROLLO SOCIALE E SORVEGLIANZA, in specie di esponenti politici dell’opposizione; OLTRE 900.000 FASCICOLI PERSONALI con nomi, fotografie, impronte digitali e annotazioni sulle attività politiche. L’archivio ha prodotto PROVE UTILIZZATE IN PROCESSI, fra cui la condanna nel 2011 di due ex agenti per la sparizione di un sindacalista avvenuta nel 1984. MA IL RITROVAMENTO NON BASTA: nel 2019 furono lanciati appelli internazionali per proteggerlo, e nel ventennale, nell’agosto 2025, è stato descritto come «INVISIBILE, MESSO A TACERE E QUASI ABBANDONATO»</t>
+          <t>IL CONTRAPPESO, DA DICHIARARE: l’esclusione riguarda IL SEGRETO DI STATO IN SENSO PROPRIO, non le ordinarie classifiche di segretezza previste dall’articolo 42, né la materiale disponibilità dei documenti negli archivi delle amministrazioni. È PRECISAMENTE QUESTO IL VUOTO CHE LE DIRETTIVE STRAORDINARIE DEL 2008, 2014 E 2021 CERCANO DI COLMARE — e la doglianza delle associazioni dei familiari è che documenti i quali PER LEGGE NON POSSONO ESSERE SEGRETI CONTINUINO A NON ARRIVARE</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Metodologia — È IL CORONAMENTO DELLA SERIE: il più grande deposito pubblico di atti di polizia dell’America Latina fu trovato PER CASO, mentre si indagava su una denuncia per esplosivi mal conservati; fu salvato da UN ORDINE GIUDIZIARIO OTTENUTO IN POCHI GIORNI; e vent’anni dopo rischia l’abbandono. TROVARE UN ARCHIVIO E CONSERVARLO SONO DUE OPERE DISTINTE</t>
+          <t>Tomo III — LA MISURA ITALIANA CORRETTA: trenta anni di massimo, contro i 50 o cento francesi; PIÙ un divieto di materia che Regno Unito, Stati Uniti, Francia, Spagna e Germania non prevedono. E DUNQUE LA CONCLUSIONE CAMBIA: PER I FATTI DI CUI QUEST’OPERA SI OCCUPA, IL SEGRETO È VIETATO PER LEGGE, E I DOCUMENTI NON ARRIVANO LO STESSO. L’OSTACOLO NON È LA NORMA: È IL VERSAMENTO</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -8276,37 +8828,37 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Direttive italiane di desecretazione e versamento — 2008, 2014, 2021 — e Sala delle Raccolte speciali dell’Archivio centrale dello Stato</t>
+          <t>Comitato parlamentare italiano per la sicurezza della Repubblica — articoli 30-38 della legge 124/2007</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Roma; consultazione ESCLUSIVAMENTE SU APPUNTAMENTO presso la Sala delle Raccolte speciali, al secondo piano dell’Istituto</t>
+          <t>Roma, Palazzo San Macuto; sedute di regola secretate, salvo diversa decisione del Comitato; l’attività è ricostruibile dall’elenco dei documenti approvati e dagli ordini del giorno</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>LE DIRETTIVE: quella del 2008; quella del 22 APRILE 2014, in Gazzetta Ufficiale n. 100 del 2 maggio, che dispone CON PROCEDURA STRAORDINARIA il versamento all’Archivio centrale e agli Archivi di Stato della documentazione relativa a 9 STRAGI — Piazza Fontana 1969, Gioia Tauro 1970, Peteano 1972, Questura di Milano 1973, Piazza della Loggia 1974, Italicus 1974, Ustica 1980, stazione di Bologna 1980, Rapido 904 1984; quella del 2 DICEMBRE 2014, che invita a completare in via definitiva i versamenti SUL SEQUESTRO E L’UCCISIONE DI ALDO MORO; e quella dell’AGOSTO 2021, in Gazzetta Ufficiale n. 190 del 10 agosto, che ne amplia l’ambito</t>
+          <t>FUNZIONE DI LEGGE: verificare IN MODO SISTEMATICO E CONTINUATIVO che l’attività del Sistema di informazione per la sicurezza si svolga nel rispetto della Costituzione e delle leggi, nell’esclusivo interesse e per la difesa della Repubblica. RATIO DICHIARATA: compensare gli ampi poteri del Presidente del Consiglio in materia di intelligence. Controlla l’operato del Presidente del Consiglio, che è tenuto a fornire comunicazioni dettagliate; svolge audizioni; RELAZIONA ANNUALMENTE AL PARLAMENTO formulando proposte</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>LA MISURA: i versamenti sono iniziati il 1° agosto 2014 e ammontano a SETTANTASETTE VERSAMENTI DA 1506 UFFICI PRODUTTORI, per CIRCA DUEMILA FALDONI, in formato cartaceo e digitale. Il Comitato ha sollecitato le amministrazioni I CUI VERSAMENTI RISULTANO ANCORA ESIGUI O DEL TUTTO ASSENTI, e la Direzione generale Archivi ha compilato UNA MAPPATURA PUNTUALE dei versamenti presso tutti gli Archivi di Stato, individuandone le carenze</t>
+          <t>LA NORMA CHE RISPONDE ALLA QUARTA PROPOSTA DEL 1984. Il Comitato è composto da 5 DEPUTATI E 5 SENATORI — erano 4 e 4 nella legge del 1977 — nominati entro venti giorni dall’inizio di ogni legislatura dai Presidenti dei due rami in proporzione ai gruppi, MA GARANTENDO COMUNQUE LA RAPPRESENTANZA PARITARIA DELLA MAGGIORANZA E DELLE OPPOSIZIONI. E soprattutto: IL PRESIDENTE È ELETTO FRA I COMPONENTI APPARTENENTI ALL’OPPOSIZIONE, a maggioranza assoluta dei componenti con eventuale ballottaggio; per gli altri due membri dell’ufficio di presidenza vige il VOTO LIMITATO. Il principio era prassi parlamentare ed è stato SANCITO PER LEGGE nel 2007</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>IL FONDO CHE INTERESSA DIRETTAMENTE QUEST’OPERA: nelle Raccolte speciali è confluita anche la documentazione del Ministero dell’Interno prodotta dalla DIVISIONE AFFARI RISERVATI della Pubblica Sicurezza, SEQUESTRATA NEL 1996 DALLA DIGOS DI ROMA presso un deposito di Circonvallazione Appia, e versata all’Archivio centrale IN CIRCA SETTECENTO FALDONI IL 14 LUGLIO 2017 — ventun anni dopo il sequestro. Una cospicua parte fu esaminata da diverse Procure nei processi sulle stragi e sul terrorismo. È DUNQUE ANCORA UNA PERQUISIZIONE ALL’ORIGINE</t>
+          <t>IL CONFRONTO CHE NE DERIVA, E CHE ROVESCIA UNA GRADUATORIA: in Germania i membri dell’organo omologo sono eletti a maggioranza dei componenti dell’assemblea, E LA MAGGIORANZA HA PIÙ VOLTE ESCLUSO DEPUTATI DI GRUPPI DI OPPOSIZIONE. IN ITALIA LA PARITÀ È IMPOSTA DALLA LEGGE E LA PRESIDENZA SPETTA ALL’OPPOSIZIONE. SU QUESTO PUNTO SPECIFICO IL MODELLO ITALIANO È PIÙ FORTE DI QUELLO TEDESCO. Da verificare sulla norma il potere, riferito da fonte secondaria, di declassificare segreti di Stato ALL’UNANIMITÀ DEI COMPONENTI</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>LE CRITICHE, DOCUMENTATE E DA REGISTRARE. Le associazioni dei familiari delle vittime e la rete degli archivi denunciano che «CHI DEVE FARLO NON VERSA I DOCUMENTI E CHI LO FA NE VERSA DI GIÀ NOTI, CHE QUINDI NON AGGIUNGONO NULLA», e chiedono: apertura degli ARCHIVI PERIFERICI, comprese le prefetture; prosecuzione della DIGITALIZZAZIONE, SINORA LIMITATA; applicazione della direttiva ANCHE DA PARTE DI CAMERA E SENATO; versamento dei documenti sulle STRUTTURE SEGRETE ED EVERSIVE per contestualizzare; che si eviti LO SMEMBRAMENTO degli archivi; e che DOPO TRENT’ANNI DAI FATTI SI VERSI TUTTO. Già a un anno dalla direttiva il sovrintendente dell’Archivio centrale poneva pubblicamente le domande: quante amministrazioni l’avessero recepita e attuata, COME FOSSERO STATI SELEZIONATI I DOCUMENTI, QUALI GARANZIE AVESSERO I CITTADINI CHE IL MATERIALE DEPOSITATO FOSSE COMPLETO, e se fossero valutati anche fatti non citati nella direttiva</t>
+          <t>I CONTRAPPESI, DA REGISTRARE: la legge fu approvata sotto una legge elettorale con premio di maggioranza, in un assetto bipolare CHE OGGI DI FATTO NON ESISTE PIÙ; una proposta di legge in corso chiede di portare i componenti DA 10 A 12 affinché tutte le forze siano rappresentate, e i lavori parlamentari osservano che i mutati equilibri si sono riverberati SULLA COMPOSIZIONE E SULL’INDIVIDUAZIONE DEL GRUPPO CUI SPETTA LA PRESIDENZA. Inoltre le sedute sono di regola secretate</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — LA MISURA COMPARATIVA CHE CHIUDE LA TAVOLA: venti anni nel Regno Unito, 25 negli Stati Uniti con clausola di certificazione, 50 o cento in Francia con declassificazione preventiva reintrodotta, NESSUN TERMINE in Spagna, fino a centoventi anni in un caso tedesco. L’ITALIA NON HA UN TERMINE GENERALE: HA 3 DIRETTIVE STRAORDINARIE FONDATE SULL’EVENTO E NON SUL TEMPO. Il che comporta una conseguenza esatta: CIÒ CHE NON È NOMINATO NON È COPERTO</t>
+          <t>Tomo III — LA SECONDA PROPOSTA MISURATA, E QUESTA VOLTA ATTUATA: la quarta proposta della Commissione del 1984 chiedeva strumenti effettivi in capo all’opposizione. NEL 2007 IL LEGISLATORE LI HA SCRITTI IN LEGGE. Il tomo che misura le distanze deve registrare anche questa</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -8326,37 +8878,37 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Legge italiana 3 agosto 2007 numero 124, capo quinto — disciplina del segreto</t>
+          <t>Seconda Commissione parlamentare di inchiesta sul rapimento e sulla morte di Aldo Moro (2014-2018)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Italia; pubblicata nella Gazzetta Ufficiale del 13 agosto 2007, numero 187</t>
+          <t>Istituita con LEGGE 30 MAGGIO 2014, NUMERO 82; costituita il 2 ottobre 2014; atti e relazioni consultabili sui siti parlamentari e presso l’archivio della Camera</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>RETTIFICA A QUANTO AFFERMATO IN VOCI PRECEDENTI DI QUESTO REPERTORIO: È ERRATO DIRE CHE L’ITALIA NON HA UN TERMINE. Prima del 2007 il vincolo del segreto di Stato NON AVEVA ALCUN LIMITE TEMPORALE; l’articolo 39 lo ha introdotto: 15 ANNI, prorogabili con provvedimento motivato del Presidente del Consiglio trasmesso al Comitato parlamentare per la sicurezza, PER UNA DURATA COMPLESSIVA MASSIMA DI TRENTA ANNI. Decorsi 15 anni, CHIUNQUE VI ABBIA INTERESSE può chiedere al Presidente del Consiglio l’accesso; entro trenta giorni questi consente l’accesso o dispone proroga motivata. Il vincolo può cessare anche prima, quando siano venute meno le esigenze</t>
+          <t>TRENTA SENATORI E TRENTA DEPUTATI. Termine originario di 24 mesi dalla costituzione, PROROGATO AL TERMINE DELLA LEGISLATURA con l’articolo 12-bis del decreto-legge 30 dicembre 2015 numero 210, convertito dalla legge 25 febbraio 2016 numero 21. Nel corso dei lavori ha approvato PIÙ RELAZIONI, pubblicate nella serie Doc. XXIII</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>LA NORMA CHE RIGUARDA DIRETTAMENTE LA MATERIA DI QUEST’OPERA, E CHE NESSUN ALTRO ORDINAMENTO QUI CENSITO POSSIEDE IN QUESTA FORMA: NON POSSONO ESSERE COPERTI DAL SEGRETO DI STATO i fatti eversivi dell’ordine costituzionale, i fatti di terrorismo, i delitti di STRAGE COMUNE e di strage con finalità di attentare alla sicurezza dello Stato, l’ASSOCIAZIONE DI TIPO MAFIOSO e lo SCAMBIO ELETTORALE POLITICO-MAFIOSO. Non è un termine più breve: È UN’ESCLUSIONE DI MATERIA</t>
+          <t>IL MANDATO, ARTICOLO 1: accertare EVENTUALI NUOVI ELEMENTI che possano integrare le conoscenze acquisite dalle precedenti Commissioni sulla strage di via Fani, sul sequestro e sull’assassinio; e EVENTUALI RESPONSABILITÀ «RICONDUCIBILI AD APPARATI, STRUTTURE E ORGANIZZAZIONI COMUNQUE DENOMINATI OVVERO A PERSONE A ESSI APPARTENENTI O APPARTENUTE». È formula che copre espressamente gli apparati dello Stato</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>LE GARANZIE PROCESSUALI: se un testimone oppone il segreto, l’autorità giudiziaria ne informa il Presidente del Consiglio; SE ENTRO TRENTA GIORNI NON GIUNGE CONFERMA, L’AUTORITÀ GIUDIZIARIA ACQUISISCE LA NOTIZIA. Se la conferma giunge, il Presidente deve darne comunicazione motivata al Comitato parlamentare, il quale, SE RITIENE INFONDATA L’OPPOSIZIONE, NE RIFERISCE A CIASCUNA DELLE CAMERE. E infine: IN NESSUN CASO IL SEGRETO DI STATO È OPPONIBILE ALLA CORTE COSTITUZIONALE</t>
+          <t>I POTERI, CHE MISURANO LA TERZA PROPOSTA DEL 1984 SULLA CENTRALITÀ DEL PARLAMENTO: la Commissione si è avvalsa dei POTERI DELL’AUTORITÀ GIUDIZIARIA attribuiti dall’articolo 82 della Costituzione e confermati dall’articolo 5 della legge istitutiva; ha potuto disporre L’ESIBIZIONE E L’ACQUISIZIONE DI DOCUMENTI FORMATI O CUSTODITI DA SOGGETTI PRIVATI, e l’acquisizione di atti relativi a PROCEDIMENTI E INCHIESTE IN CORSO presso l’autorità giudiziaria. Ha inoltre SEGNALATO TEMPESTIVAMENTE A DIVERSI UFFICI GIUDIZIARI, in ossequio al principio di leale cooperazione fra poteri dello Stato, elementi emersi nell’inchiesta parlamentare</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>IL CONTRAPPESO, DA DICHIARARE: l’esclusione riguarda IL SEGRETO DI STATO IN SENSO PROPRIO, non le ordinarie classifiche di segretezza previste dall’articolo 42, né la materiale disponibilità dei documenti negli archivi delle amministrazioni. È PRECISAMENTE QUESTO IL VUOTO CHE LE DIRETTIVE STRAORDINARIE DEL 2008, 2014 E 2021 CERCANO DI COLMARE — e la doglianza delle associazioni dei familiari è che documenti i quali PER LEGGE NON POSSONO ESSERE SEGRETI CONTINUINO A NON ARRIVARE</t>
+          <t>DUE DATI OPERATIVI PER CHI DEVE LAVORARCI. PRIMO: in forza di deliberazione dell’Ufficio di presidenza del 21 ottobre 2014 L’ARCHIVIO DELLA PRIMA COMMISSIONE MORO, istituita nel novembre 1979 (estremi della legge istitutiva DA VERIFICARE), È STATO INTEGRALMENTE DIGITALIZZATO. SECONDO: il regime di divulgazione prevede che l’estrazione di copia dei documenti riservati sia PREVENTIVAMENTE AUTORIZZATA DAL PRESIDENTE e che NON SIA CONSENTITA LA COPIA DI DOCUMENTI SEGRETI. E l’autovalutazione dichiarata nella relazione del secondo anno va citata come modello di registro: «GLI ELEMENTI ACQUISITI NON CONSENTONO ANCORA UNA RILETTURA COMPLESSIVA DELLA VICENDA, MA EVIDENZIANO IMPORTANTI NOVITÀ»</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — LA MISURA ITALIANA CORRETTA: trenta anni di massimo, contro i 50 o cento francesi; PIÙ un divieto di materia che Regno Unito, Stati Uniti, Francia, Spagna e Germania non prevedono. E DUNQUE LA CONCLUSIONE CAMBIA: PER I FATTI DI CUI QUEST’OPERA SI OCCUPA, IL SEGRETO È VIETATO PER LEGGE, E I DOCUMENTI NON ARRIVANO LO STESSO. L’OSTACOLO NON È LA NORMA: È IL VERSAMENTO</t>
+          <t>Tomo I e Tomo III — è insieme la fonte istituzionale diretta del primo tomo e LA MISURA DELLA TERZA PROPOSTA: qui il Parlamento ha esercitato poteri giudiziari, acquisito atti da privati e da procedimenti in corso, e restituito elementi alle Procure</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
@@ -8376,37 +8928,37 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Comitato parlamentare italiano per la sicurezza della Repubblica — articoli 30-38 della legge 124/2007</t>
+          <t>Divieto italiano di incompatibilità successiva — articolo 53 comma 16-ter del decreto legislativo 165/2001, introdotto dalla legge 190/2012</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Roma, Palazzo San Macuto; sedute di regola secretate, salvo diversa decisione del Comitato; l’attività è ricostruibile dall’elenco dei documenti approvati e dagli ordini del giorno</t>
+          <t>Italia; linee guida dell’Autorità nazionale anticorruzione, delibera numero 493 del 25 settembre 2024; norma collegata: articolo 21 del decreto legislativo 39/2013</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>FUNZIONE DI LEGGE: verificare IN MODO SISTEMATICO E CONTINUATIVO che l’attività del Sistema di informazione per la sicurezza si svolga nel rispetto della Costituzione e delle leggi, nell’esclusivo interesse e per la difesa della Repubblica. RATIO DICHIARATA: compensare gli ampi poteri del Presidente del Consiglio in materia di intelligence. Controlla l’operato del Presidente del Consiglio, che è tenuto a fornire comunicazioni dettagliate; svolge audizioni; RELAZIONA ANNUALMENTE AL PARLAMENTO formulando proposte</t>
+          <t>LA NORMA CHE MISURA LA SECONDA PROPOSTA DEL 1984, QUELLA SUL CONTROLLO OLTRE LA CESSAZIONE DALL’INCARICO. I dipendenti che NEGLI ULTIMI 3 ANNI DI SERVIZIO abbiano esercitato POTERI AUTORITATIVI O NEGOZIALI per conto delle pubbliche amministrazioni non possono, NEI 3 ANNI SUCCESSIVI ALLA CESSAZIONE, svolgere attività lavorativa o professionale PRESSO I SOGGETTI PRIVATI DESTINATARI dell’attività svolta attraverso quei medesimi poteri. Il triennio è definito in dottrina PERIODO DI RAFFREDDAMENTO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>LA NORMA CHE RISPONDE ALLA QUARTA PROPOSTA DEL 1984. Il Comitato è composto da 5 DEPUTATI E 5 SENATORI — erano 4 e 4 nella legge del 1977 — nominati entro venti giorni dall’inizio di ogni legislatura dai Presidenti dei due rami in proporzione ai gruppi, MA GARANTENDO COMUNQUE LA RAPPRESENTANZA PARITARIA DELLA MAGGIORANZA E DELLE OPPOSIZIONI. E soprattutto: IL PRESIDENTE È ELETTO FRA I COMPONENTI APPARTENENTI ALL’OPPOSIZIONE, a maggioranza assoluta dei componenti con eventuale ballottaggio; per gli altri due membri dell’ufficio di presidenza vige il VOTO LIMITATO. Il principio era prassi parlamentare ed è stato SANCITO PER LEGGE nel 2007</t>
+          <t>AMBITO E SANZIONI: si applica ai dipendenti pubblici INCLUSI I TITOLARI DI INCARICHI DIRIGENZIALI E AMMINISTRATIVI DI VERTICE, nelle amministrazioni e negli enti pubblici economici e di diritto privato IN CONTROLLO PUBBLICO; copre l’esercizio di quei poteri SIA IN FORMA STABILE SIA OCCASIONALE. Conseguenze: NULLITÀ dei contratti conclusi e degli incarichi conferiti; OBBLIGO DI RESTITUZIONE DEI COMPENSI percepiti; e DIVIETO PER IL PRIVATO DI CONTRATTARE CON LE PUBBLICHE AMMINISTRAZIONI PER 3 ANNI</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>IL CONFRONTO CHE NE DERIVA, E CHE ROVESCIA UNA GRADUATORIA: in Germania i membri dell’organo omologo sono eletti a maggioranza dei componenti dell’assemblea, E LA MAGGIORANZA HA PIÙ VOLTE ESCLUSO DEPUTATI DI GRUPPI DI OPPOSIZIONE. IN ITALIA LA PARITÀ È IMPOSTA DALLA LEGGE E LA PRESIDENZA SPETTA ALL’OPPOSIZIONE. SU QUESTO PUNTO SPECIFICO IL MODELLO ITALIANO È PIÙ FORTE DI QUELLO TEDESCO. Da verificare sulla norma il potere, riferito da fonte secondaria, di declassificare segreti di Stato ALL’UNANIMITÀ DEI COMPONENTI</t>
+          <t>LA PRIMA DEBOLEZZA, CHE RIPETE UN PATTERN GIÀ REGISTRATO: LA LEGGE NON INDIVIDUA L’AUTORITÀ COMPETENTE a garantire l’esecuzione delle conseguenze sanzionatorie. È stata LA GIURISPRUDENZA AMMINISTRATIVA ad attribuirle all’Autorità nazionale anticorruzione, affermando che «una volta accertata l’effettiva violazione non può fondatamente dubitarsi che tale potere spetti» a quell’Autorità. ANCORA UNA VOLTA UN GIUDICE HA DOVUTO FORNIRE CIÒ CHE IL LEGISLATORE AVEVA OMESSO</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>I CONTRAPPESI, DA REGISTRARE: la legge fu approvata sotto una legge elettorale con premio di maggioranza, in un assetto bipolare CHE OGGI DI FATTO NON ESISTE PIÙ; una proposta di legge in corso chiede di portare i componenti DA 10 A 12 affinché tutte le forze siano rappresentate, e i lavori parlamentari osservano che i mutati equilibri si sono riverberati SULLA COMPOSIZIONE E SULL’INDIVIDUAZIONE DEL GRUPPO CUI SPETTA LA PRESIDENZA. Inoltre le sedute sono di regola secretate</t>
+          <t>LA SECONDA DEBOLEZZA, DA REGISTRARE PERCHÉ È SCRITTA IN LEGGE: PER I PROFESSIONISTI ASSUNTI A TEMPO DETERMINATO per l’espletamento delle attività del piano nazionale di ripresa e resilienza I DIVIETI DEL COMMA 16-TER NON SI APPLICANO</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — LA SECONDA PROPOSTA MISURATA, E QUESTA VOLTA ATTUATA: la quarta proposta della Commissione del 1984 chiedeva strumenti effettivi in capo all’opposizione. NEL 2007 IL LEGISLATORE LI HA SCRITTI IN LEGGE. Il tomo che misura le distanze deve registrare anche questa</t>
+          <t>Tomo III — CHIUDE IL QUADRO DELLE 4 PROPOSTE DEL 1984, E OGNUNA HA AVUTO SORTE DIVERSA. LA PRIMA: attuata al contrario, più discrezionalità anziché meno, e raddrizzata dalla Corte costituzionale. LA SECONDA: attuata 28 ANNI DOPO, e non da una legge sulla sicurezza ma da una legge anticorruzione, con l’autorità sanzionatoria fornita dalla giurisprudenza e un’esenzione espressa. LA TERZA: esercitata con poteri giudiziari da una Commissione bicamerale, che si è dichiarata essa stessa incompleta. LA QUARTA: scritta in legge nel 2007 in forma più forte di quella tedesca. IN DUE CASI SU 4 SONO STATI I GIUDICI A SUPPLIRE AL LEGISLATORE</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -8426,42 +8978,42 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Seconda Commissione parlamentare di inchiesta sul rapimento e sulla morte di Aldo Moro (2014-2018)</t>
+          <t>Relazione del Comitato parlamentare per la sicurezza della Repubblica sull’attivita febbraio-agosto 2022 — APPROVATA ALL’UNANIMITA</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Istituita con LEGGE 30 MAGGIO 2014, NUMERO 82; costituita il 2 ottobre 2014; atti e relazioni consultabili sui siti parlamentari e presso l’archivio della Camera</t>
+          <t>Italia; relazione trasmessa al Parlamento nell’agosto 2022, anticipata rispetto al documento annuale a causa dello scioglimento anticipato delle Camere; approvata ALL’UNANIMITA dall’organo la cui presidenza spetta per legge all’opposizione</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>TRENTA SENATORI E TRENTA DEPUTATI. Termine originario di 24 mesi dalla costituzione, PROROGATO AL TERMINE DELLA LEGISLATURA con l’articolo 12-bis del decreto-legge 30 dicembre 2015 numero 210, convertito dalla legge 25 febbraio 2016 numero 21. Nel corso dei lavori ha approvato PIÙ RELAZIONI, pubblicate nella serie Doc. XXIII</t>
+          <t>CIO CHE IL COMITATO ACCERTA: «il montaggio e la diffusione di fake news, le campagne social e l’utilizzo dei troll si affermano quali STRUMENTI SOFISTICATI E PERVASIVI DI INFLUENZA DA PARTE DELLA RUSSIA, MA ANCHE DA PARTE DI ALTRI ATTORI STATUALI» — nominando anche la Cina — «rischiando di inquinare e distorcere il dibattito pubblico italiano e quello dei Paesi occidentali». Sul meccanismo: la propaganda «si avvale di AGENZIE DI STAMPA ONLINE CONTROLLATE che pubblicano i propri contenuti in diverse lingue, compreso l’italiano, con DECINE DI MILIONI DI VISUALIZZAZIONI, NELLA MAGGIOR PARTE DEI CASI DEL PUBBLICO PIU GIOVANE»; sono «siti di cui SONO IGNOTI I SOSTENITORI E LE FONTI DI FINANZIAMENTO», i cui contenuti «rimbalzano presso taluni siti italiani, MOLTIPLICANDO L’ONDA MALEVOLA»</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>IL MANDATO, ARTICOLO 1: accertare EVENTUALI NUOVI ELEMENTI che possano integrare le conoscenze acquisite dalle precedenti Commissioni sulla strage di via Fani, sul sequestro e sull’assassinio; e EVENTUALI RESPONSABILITÀ «RICONDUCIBILI AD APPARATI, STRUTTURE E ORGANIZZAZIONI COMUNQUE DENOMINATI OVVERO A PERSONE A ESSI APPARTENENTI O APPARTENUTE». È formula che copre espressamente gli apparati dello Stato</t>
+          <t>L’AUTOVALUTAZIONE DELLO STATO SU SE STESSO, CHE E LA PARTE PIU UTILE: in Italia si ravvisa «UNA SOSTANZIALE DEBOLEZZA DEGLI INTERVENTI PER IL CONTRASTO ALLA DISINFORMAZIONE E ALLE DIVERSE FORME DI INGERENZA. UN CHIARO DEFICIT E RITARDO DEL NOSTRO PAESE RISPETTO AD IMPEGNI, STRUMENTI, STRATEGIE E MISURE CHE DA DIVERSO TEMPO SONO GIA OPERATIVI TANTO NEL CONTESTO INTERNAZIONALE». E la conclusione: «E QUINDI ORMAI NON PIU RINVIABILE UN MAGGIORE IMPEGNO DEL NOSTRO PAESE, anche non escludendo possibili interventi di ordine legislativo e normativo». Il Comitato avverte inoltre sui RAPPORTI FRA PARTITI ED ESPONENTI POLITICI ITALIANI E CONTROPARTI RUSSE, richiamando la risoluzione del Parlamento europeo del 9 MARZO 2022, frutto di un’indagine durata un anno e mezzo</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>I POTERI, CHE MISURANO LA TERZA PROPOSTA DEL 1984 SULLA CENTRALITÀ DEL PARLAMENTO: la Commissione si è avvalsa dei POTERI DELL’AUTORITÀ GIUDIZIARIA attribuiti dall’articolo 82 della Costituzione e confermati dall’articolo 5 della legge istitutiva; ha potuto disporre L’ESIBIZIONE E L’ACQUISIZIONE DI DOCUMENTI FORMATI O CUSTODITI DA SOGGETTI PRIVATI, e l’acquisizione di atti relativi a PROCEDIMENTI E INCHIESTE IN CORSO presso l’autorità giudiziaria. Ha inoltre SEGNALATO TEMPESTIVAMENTE A DIVERSI UFFICI GIUDIZIARI, in ossequio al principio di leale cooperazione fra poteri dello Stato, elementi emersi nell’inchiesta parlamentare</t>
+          <t>IL RITROVAMENTO CHE RIGUARDA DIRETTAMENTE QUEST’OPERA: la relazione da conto di DUE INDAGINI DEL COMITATO RIMASTE INCOMPIUTE PER LO SCIOGLIMENTO ANTICIPATO DELLE CAMERE. LA PRIMA E QUELLA «SULLE MODALITA DI ATTUAZIONE DELLA DESECRETAZIONE DEGLI ATTI PER UNA MIGLIORE CONSERVAZIONE E ACCESSIBILITA DEI DOCUMENTI». LA SECONDA E QUELLA «SULLE FORME DI DISINFORMAZIONE E DI INGERENZA STRANIERE». Le due inchieste parlamentari piu direttamente pertinenti a questo lavoro SONO STATE ENTRAMBE INTERROTTE NELL’AGOSTO 2022</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>DUE DATI OPERATIVI PER CHI DEVE LAVORARCI. PRIMO: in forza di deliberazione dell’Ufficio di presidenza del 21 ottobre 2014 L’ARCHIVIO DELLA PRIMA COMMISSIONE MORO, istituita nel novembre 1979 (estremi della legge istitutiva DA VERIFICARE), È STATO INTEGRALMENTE DIGITALIZZATO. SECONDO: il regime di divulgazione prevede che l’estrazione di copia dei documenti riservati sia PREVENTIVAMENTE AUTORIZZATA DAL PRESIDENTE e che NON SIA CONSENTITA LA COPIA DI DOCUMENTI SEGRETI. E l’autovalutazione dichiarata nella relazione del secondo anno va citata come modello di registro: «GLI ELEMENTI ACQUISITI NON CONSENTONO ANCORA UNA RILETTURA COMPLESSIVA DELLA VICENDA, MA EVIDENZIANO IMPORTANTI NOVITÀ»</t>
+          <t>CONTESTO DA REGISTRARE CON CAUTELA: il 18 agosto 2022, alla vigilia della riunione conclusiva, un alto esponente russo INVITO PUBBLICAMENTE «GLI EUROPEI A PUNIRE I PROPRI GOVERNI NELLE URNE», con riferimento ritenuto rivolto alle elezioni italiane imminenti. E DICHIARAZIONE PUBBLICA, NON OPERAZIONE COPERTA, e va citata come tale</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>Tomo I e Tomo III — è insieme la fonte istituzionale diretta del primo tomo e LA MISURA DELLA TERZA PROPOSTA: qui il Parlamento ha esercitato poteri giudiziari, acquisito atti da privati e da procedimenti in corso, e restituito elementi alle Procure</t>
+          <t>Tomo II e Tomo III — CHIUDE IL TRIANGOLO DELLE 3 SEDI: commissione bipartisan statunitense, magistratura milanese, organo parlamentare italiano. Tutte e 3 accertano influenza e contatti; NESSUNA RAGGIUNGE UN VERTICE; e nella terza L’INCHIESTA STESSA SI INTERROMPE. Il deficit dichiarato dall’organo di controllo e inoltre IL RISCONTRO ISTITUZIONALE della doglianza dei familiari delle vittime sul mancato versamento: DUE ORGANI DIVERSI, LA STESSA LACUNA</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
@@ -8476,42 +9028,42 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Divieto italiano di incompatibilità successiva — articolo 53 comma 16-ter del decreto legislativo 165/2001, introdotto dalla legge 190/2012</t>
+          <t>Risoluzione del Parlamento europeo del 9 MARZO 2022 sulle ingerenze straniere nei processi democratici dell’Unione, e la serie successiva</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Italia; linee guida dell’Autorità nazionale anticorruzione, delibera numero 493 del 25 settembre 2024; norma collegata: articolo 21 del decreto legislativo 39/2013</t>
+          <t>Relazione finale della commissione speciale INGE, documento A9-0022/2022, testo approvato TA-9-2022-0064; seguono la risoluzione del 1° GIUGNO 2023 (relazione finale della commissione INGE2), la risoluzione del 15 DICEMBRE 2022 sulla sospetta corruzione da parte di uno Stato terzo, quella del 13 LUGLIO 2023 sulla riforma delle norme in materia di trasparenza e integrita, la decisione del 13 SETTEMBRE 2023 di modifica del regolamento, e le proposte del 2024 sulle ingerenze nell’attivita del Parlamento stesso</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>LA NORMA CHE MISURA LA SECONDA PROPOSTA DEL 1984, QUELLA SUL CONTROLLO OLTRE LA CESSAZIONE DALL’INCARICO. I dipendenti che NEGLI ULTIMI 3 ANNI DI SERVIZIO abbiano esercitato POTERI AUTORITATIVI O NEGOZIALI per conto delle pubbliche amministrazioni non possono, NEI 3 ANNI SUCCESSIVI ALLA CESSAZIONE, svolgere attività lavorativa o professionale PRESSO I SOGGETTI PRIVATI DESTINATARI dell’attività svolta attraverso quei medesimi poteri. Il triennio è definito in dottrina PERIODO DI RAFFREDDAMENTO</t>
+          <t>L’ESITO DEL VOTO E LA CONCLUSIONE: 5150DUE FAVOREVOLI, OTTANTUNO CONTRARI, SESSANTA ASTENUTI. Il testo conclude che in Europa esiste UNA «LARGA IMPREPARAZIONE» sulla gravita della minaccia rappresentata dai regimi autocratici stranieri, in particolare Russia e Cina</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>AMBITO E SANZIONI: si applica ai dipendenti pubblici INCLUSI I TITOLARI DI INCARICHI DIRIGENZIALI E AMMINISTRATIVI DI VERTICE, nelle amministrazioni e negli enti pubblici economici e di diritto privato IN CONTROLLO PUBBLICO; copre l’esercizio di quei poteri SIA IN FORMA STABILE SIA OCCASIONALE. Conseguenze: NULLITÀ dei contratti conclusi e degli incarichi conferiti; OBBLIGO DI RESTITUZIONE DEI COMPENSI percepiti; e DIVIETO PER IL PRIVATO DI CONTRATTARE CON LE PUBBLICHE AMMINISTRAZIONI PER 3 ANNI</t>
+          <t>IL PASSAGGIO CHE CONFERMA LA TASSONOMIA A DUE ASSI, E VA CITATO NELLA SUA INTEREZZA: la relazione «CONDANNA IL FATTO CHE I PARTITI ESTREMISTI, POPULISTI, ANTIEUROPEI E ALCUNI ALTRI PARTITI E INDIVIDUI ABBIANO LEGAMI E SIANO ESPLICITAMENTE COMPLICI NEI TENTATIVI DI INTERFERIRE NEI PROCESSI DEMOCRATICI DELL’UNIONE». LA FORMULA «E ALCUNI ALTRI PARTITI E INDIVIDUI» E DECISIVA: IL PARLAMENTO EUROPEO NON CIRCOSCRIVE IL FENOMENO A UNA FAMIGLIA POLITICA. Riscontro ulteriore: al testo votarono a favore anche delegazioni nazionali di area conservatrice</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>LA PRIMA DEBOLEZZA, CHE RIPETE UN PATTERN GIÀ REGISTRATO: LA LEGGE NON INDIVIDUA L’AUTORITÀ COMPETENTE a garantire l’esecuzione delle conseguenze sanzionatorie. È stata LA GIURISPRUDENZA AMMINISTRATIVA ad attribuirle all’Autorità nazionale anticorruzione, affermando che «una volta accertata l’effettiva violazione non può fondatamente dubitarsi che tale potere spetti» a quell’Autorità. ANCORA UNA VOLTA UN GIUDICE HA DOVUTO FORNIRE CIÒ CHE IL LEGISLATORE AVEVA OMESSO</t>
+          <t>IL RIMEDIO PROPOSTO, CHE E LA RISPOSTA NORMATIVA ALLO SCHEMA DOCUMENTATO NEL CASO MOSCOVITA DEL 2018: «VIETARE DONAZIONI E FINANZIAMENTI A PARTITI, FONDAZIONI E AGLI ESPONENTI POLITICI CHE RICOPRONO CARICHE PUBBLICHE O ELETTIVE DA PARTE DI POTENZE STRANIERE» EXTRAEUROPEE. E la risoluzione del 2024 aggiunge che «CONTINUANO A EMERGERE PROVE DI INGERENZE RUSSE NEI PERIODI PRECEDENTI A TUTTE LE PRINCIPALI ELEZIONI NAZIONALI ED EUROPEE», chiedendo «UN’INDAGINE INTERNA APPROFONDITA» sui possibili casi di ingerenza E SULLA CONDOTTA SCORRETTA DEI PROPRI DEPUTATI</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>LA SECONDA DEBOLEZZA, DA REGISTRARE PERCHÉ È SCRITTA IN LEGGE: PER I PROFESSIONISTI ASSUNTI A TEMPO DETERMINATO per l’espletamento delle attività del piano nazionale di ripresa e resilienza I DIVIETI DEL COMMA 16-TER NON SI APPLICANO</t>
+          <t>DA REGISTRARE CON MISURA: secondo un’indagine di opinione del marzo 2023 i cittadini collocano fra le principali sfide ai sistemi democratici le informazioni false in rete, la propaganda da fonti straniere non democratiche E LE INGERENZE OCCULTE «ANCHE ATTRAVERSO IL FINANZIAMENTO DI ATTORI NAZIONALI». E PERCEZIONE, NON ACCERTAMENTO, e va citata come tale</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Tomo III — CHIUDE IL QUADRO DELLE 4 PROPOSTE DEL 1984, E OGNUNA HA AVUTO SORTE DIVERSA. LA PRIMA: attuata al contrario, più discrezionalità anziché meno, e raddrizzata dalla Corte costituzionale. LA SECONDA: attuata 28 ANNI DOPO, e non da una legge sulla sicurezza ma da una legge anticorruzione, con l’autorità sanzionatoria fornita dalla giurisprudenza e un’esenzione espressa. LA TERZA: esercitata con poteri giudiziari da una Commissione bicamerale, che si è dichiarata essa stessa incompleta. LA QUARTA: scritta in legge nel 2007 in forma più forte di quella tedesca. IN DUE CASI SU 4 SONO STATI I GIUDICI A SUPPLIRE AL LEGISLATORE</t>
+          <t>Tomo II e Apparato — CHIUDE IL QUADRILATERO ISTITUZIONALE: commissione bipartisan statunitense, magistratura italiana, comitato parlamentare italiano, Parlamento europeo. E FORNISCE LA CONFERMA EMPIRICA DELLA TASSONOMIA: il fenomeno e condannato senza essere attribuito a una famiglia politica, e la stessa risoluzione e votata anche da chi a quelle famiglie e contiguo. LA POSIZIONE ECCEZIONALISTA E RICORRENTE, NON EREDITARIA</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
@@ -8526,42 +9078,42 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Field Manual 30-31B, cosiddetto «direttiva Westmoreland» — STATUTO CONTESO, NON UTILIZZABILE COME PROVA</t>
+          <t>Articolo 18 della Costituzione e legge 25 GENNAIO 1982 numero 17 — L’ANCORAGGIO COSTITUZIONALE DELL’OPERA, E LA SUA RIDUZIONE</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Copia sequestrata a Licio Gelli a Castiglion Fibocchi il 17 marzo 1981 e pubblicata dalla Commissione parlamentare P2 nel Doc. XXIII n. 2-quater, Serie II, Volume VII, Tomo I, alle pagine 287-298, Roma 1987</t>
+          <t>Italia; legge pubblicata nella Gazzetta Ufficiale, serie generale numero 27, del 28 GENNAIO 1982, con rubrica «Norme di attuazione dell’articolo 18 della Costituzione in materia di associazioni segrete e scioglimento della associazione denominata Loggia P2»; emanata a seguito della conclusione dei lavori della Commissione parlamentare d’inchiesta</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>CHE COSA AFFERMA IL DOCUMENTO: che quando i governi dei Paesi ospiti mostrino passivita o indecisione di fronte alla sovversione comunista, gli apparati statunitensi possano promuovere azioni di provocazione, incoraggiando gruppi di estrema sinistra ad atti violenti o eseguendo direttamente azioni sotto falsa bandiera da attribuire loro. Reca data 18 marzo 1970 e la firma attribuita al capo di Stato maggiore dell’Esercito</t>
+          <t>LA NORMA COSTITUZIONALE: «I cittadini hanno diritto di associarsi liberamente, senza autorizzazione, per fini che non sono vietati ai singoli dalla legge penale. SONO PROIBITE LE ASSOCIAZIONI SEGRETE E QUELLE CHE PERSEGUONO, ANCHE INDIRETTAMENTE, SCOPI POLITICI MEDIANTE ORGANIZZAZIONI DI CARATTERE MILITARE». Il secondo comma reca UNA PROIBIZIONE DUPLICE E DISGIUNTA, e adopera il termine «proibizione» riferito anche alla persecuzione INDIRETTA della finalita vietata</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>GLI ELEMENTI A FAVORE DELLA FALSIFICAZIONE, CHE SONO SERI E PRECOCI: il SERVIZIO DI INTELLIGENCE DELLA DIFESA DANESE CONCLUSE GIA NEL 1976 che si trattava di un falso inserito in una campagna di disinformazione sovietica; UN TRANSFUGA DEL KGB LO DICHIARO FALSO DI ORIGINE SOVIETICA testimoniando davanti al Congresso statunitense; la commissione parlamentare statunitense sull’intelligence apri un’indagine sulle falsificazioni nel gennaio 1979; IL FM 30-31 PUBBLICAMENTE RILASCIATO HA IL SOLO SUPPLEMENTO A, NON IL B; il Dipartimento di Stato lo ha qualificato come falso sovietico trentennale in un comunicato del 20 gennaio 2006; un ex direttore centrale dell’intelligence dichiaro di non averne mai sentito parlare</t>
+          <t>LA DEFINIZIONE DI LEGGE, ARTICOLO PRIMO, CHE DESCRIVE LA LOGGIA COPERTA IN TERMINI GIURIDICI: sono segrete le associazioni che, ANCHE ALL’INTERNO DI ASSOCIAZIONI PALESI, occultando la loro esistenza ovvero tenendo segrete congiuntamente finalita e attivita sociali ovvero RENDENDO SCONOSCIUTI, IN TUTTO O IN PARTE E ANCHE RECIPROCAMENTE, I SOCI, SVOLGONO ATTIVITA DIRETTA A INTERFERIRE SULL’ESERCIZIO DELLE FUNZIONI DI ORGANI COSTITUZIONALI, di amministrazioni pubbliche anche ad ordinamento autonomo, di enti pubblici anche economici, nonche di servizi pubblici essenziali di interesse nazionale. SANZIONI: da uno a 5 anni per chi promuove, dirige o fa proselitismo, con interdizione quinquennale dai pubblici uffici; fino a due anni per chi partecipa. ARTICOLO TERZO: accertata con SENTENZA IRREVOCABILE la costituzione dell’associazione, il Presidente del Consiglio ne ordina con decreto LO SCIOGLIMENTO E LA CONFISCA DEI BENI; e in ogni stato e grado, se vi e pericolo nel ritardo, puo essere disposta in camera di consiglio LA SOSPENSIONE CAUTELARE DI OGNI ATTIVITA ASSOCIATIVA</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>GLI ELEMENTI CONTRARI, CHE NON SONO TRASCURABILI: fu sequestrato INSIEME AD ALTRI DOCUMENTI DI ORIGINE STATUNITENSE VERIFICATI; LA COMMISSIONE PARLAMENTARE ITALIANA LO PUBBLICO NEL 1987 COME DOCUMENTO GENUINO; un ex vicedirettore della CIA dichiaro di sospettarne l’autenticita, PRECISANDO PERO DI NON AVERLO MAI VISTO; il detentore affermo nel 1992 di averlo ricevuto da un amico della CIA; e NEL PROCESSO DI BOLOGNA DEL 2018 UN GENERALE DEL SISMI IN CONGEDO HA TESTIMONIATO che una copia non espunta esisteva negli archivi dell’intelligence militare italiana, ottenuta da autorita statunitensi SENZA ALCUNA ANNOTAZIONE che la indicasse come falsa</t>
+          <t>LA RIDUZIONE, CHE E IL FATTO PIU IMPORTANTE DI QUESTA VOCE. La Costituzione proibisce le associazioni segrete TOUT COURT, a prescindere dalla loro azione. LA MODIFICA INTRODOTTA IN SEDE PARLAMENTARE ALLA LEGGE DI ATTUAZIONE VIETO LE SOLE ASSOCIAZIONI SEGRETE CHE PERSEGUONO FINI ILLECITI, «RENDENDO IN QUESTO MODO LA SEGRETEZZA UN CARATTERE DI PER SE LEGITTIMO». La dottrina costituzionalistica conferma che la definizione «ATTUA SOLO IN PARTE IL DETTATO COSTITUZIONALE». Ne discende una conseguenza processuale diretta: dopo quella modifica NON BASTA PROVARE LA SEGRETEZZA, OCCORRE PROVARE L’INTERFERENZA — ed e esattamente il requisito la cui mancata prova ha condotto all’assoluzione registrata altrove in questo repertorio</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>LA REGOLA CHE NE DISCENDE PER L’OPERA, ED E TASSATIVA. IL DOCUMENTO NON PUO ESSERE USATO COME PROVA DI UNA DOTTRINA. Puo essere trattato SOLTANTO come oggetto di studio a statuto conteso, esponendo entrambi i fronti. E NON SERVE: la categoria della falsa bandiera e gia stabilita da altre fonti incontestate — la proposta statunitense del 13 marzo 1962, autentica e respinta, e l’operazione tedesca del 25 luglio 1978, eseguita e in seguito ammessa in sede parlamentare. UN’OPERA CHE POGGIA SU QUESTO DOCUMENTO REGALA AI PROPRI AVVERSARI LA SOLA OBIEZIONE REALMENTE LETALE</t>
+          <t>IL SEGUITO, ANCORA APERTO: nel LUGLIO 2018 e stato depositato un disegno di legge in materia di incompatibilita fra cariche e partecipazione ad associazioni che comportino VINCOLO DI OBBEDIENZA, al termine di un dibattito «SOSTANZIALMENTE INIZIATO DURANTE L’ITER DI APPROVAZIONE DELLA LEGGE STESSA». Va inoltre registrato che in sede costituente NON SI PREVIDE ALCUN REGIME GENERALE DI PUBBLICITA DELLE ASSOCIAZIONI che qualificasse come segrete quelle che vi si sottraessero</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Dominio 7 e Metodologia — NODO A MASSIMO RISCHIO. Il Volume Zero lo classifica gia Savona B: e giusto, MA INSUFFICIENTE. Va marcato CONTESO, con entrambe le serie di elementi esposte nel testo e non in nota</t>
+          <t>Dominio 4 e Tomo III — E L’ANCORAGGIO COSTITUZIONALE DELL’INTERA OPERA E INSIEME IL SUO CASO ESEMPLARE. LA NORMA CHE DOVEVA ATTUARE IL DIVIETO LO HA RISTRETTO, E LA RESTRIZIONE HA PRODOTTO L’ASSOLUZIONE. E la stessa figura gia registrata per la prima proposta del 1984: la disposizione attuativa che si muove in direzione contraria alla fonte che dichiara di attuare</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
@@ -8576,42 +9128,42 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Gladio — verifica delle cifre e delle date: RETTIFICHE AL VOLUME ZERO PARTE VII</t>
+          <t>Corte europea dei diritti dell’uomo, Grande Oriente d’Italia contro Italia — ricorso 29550/17, sentenza 19 DICEMBRE 2024</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Fonti: relazione Andreotti alla Commissione stragi (ottobre 1990); audizione del capo di Stato maggiore del SISMI del 29 novembre 1990; appunto interno SIFAR predisposto per la visita del capo di Stato maggiore a Capo Marrargiu (1965)</t>
+          <t>TESTO INTEGRALE IN TRADUZIONE ITALIANA UFFICIALE SUL SITO DEL MINISTERO DELLA GIUSTIZIA, sezione delle sentenze della Corte europea; comunicato stampa della cancelleria in lingua inglese. Ricorso proposto il 13 APRILE 2017, poche settimane dopo i fatti; decisione di Camera ALL’UNANIMITA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>LA DATA COSTITUTIVA: protocollo d’intesa fra servizio italiano e statunitense: LA RELAZIONE DEL GOVERNO AL PARLAMENTO LO DATA AL 26 NOVEMBRE 1956, LA COPIA DEL DOCUMENTO POI CONSEGNATA DAL GOVERNO ALLA COMMISSIONE E DATATA 28 NOVEMBRE 1956 — DISCREPANZA CHIUSA, MA NON RISOLTA IN FAVORE DI UNA DATA: e uno scarto fra il racconto dell’esecutivo e l’atto dell’esecutivo. E il protocollo NON E L’INIZIO: conteneva esplicito riferimento ad ACCORDI PREESISTENTI, e la sezione addestramento del SIFAR era stata costituita il 1° OTTOBRE 1956, prima del protocollo. Scrivere che Gladio nasce il 26 novembre 1956 e dunque inesatto: quella e la data in cui viene formalizzata</t>
+          <t>I FATTI ACCERTATI. Nel MARZO 2017, su ordine della Commissione parlamentare antimafia della 17sima legislatura, il nucleo speciale della Guardia di finanza per il contrasto alla criminalita organizzata perquisi la sede dell’obbedienza. L’associazione si era rifiutata di consegnare gli elenchi spontaneamente per due ragioni: NON RISULTAVA CHE ALCUN ISCRITTO FOSSE INDAGATO dalla magistratura, e la consegna avrebbe violato la normativa sulla protezione dei dati personali. LA PERQUISIZIONE DURO 14 ORE e si estese all’intera struttura, COMPRESI L’APPARTAMENTO PRIVATO DEL GRAN MAESTRO E IL CAPANNO DEGLI ATTREZZI. Furono sequestrati TRENTANOVE FALDONI di schede relative a SEIMILA ISCRITTI delle logge di Sicilia e Calabria</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>ERRORE DI FATTO DA CORREGGERE NEL VOLUME ZERO: il magistrato veneziano ottenne da Andreotti nel luglio 1990 l’accesso all’archivio del SISMI a FORTE BRASCHI, non a Forte Boccea. Forte Braschi e la sede del servizio; Forte Boccea ospita il carcere e il tribunale militari. LA PARTE VII INDICA IL FORTE SBAGLIATO</t>
+          <t>LA RISPOSTA ALLA DOMANDA SU DOVE SIANO I FASCICOLI, E VIENE DALLA SENTENZA: SI TRATTA DI «INTERFERENZA PERMANENTE IN QUANTO LA DOCUMENTAZIONE SEQUESTRATA NON E STATA DISTRUTTA AL TERMINE DELL’ATTIVITA DELLA COMMISSIONE». I trentanove faldoni non risultano dunque distrutti, e la Corte qualifica proprio questo come il carattere permanente della violazione. QUANTO AI TRENTACINQUEMILA NOMINATIVI DELLE 4 OBBEDIENZE, ESSI SONO L’OGGETTO DELL’INVITO DELL’APRILE 2017, NON DEL SEQUESTRO ACCERTATO: la sorte degli elenchi delle altre 3 obbedienze NON RISULTA DA QUESTE FONTI E RESTA DA VERIFICARE</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>LA CIFRA DEI TREMILA UOMINI VA DECLASSATA. Proviene da un APPUNTO INTERNO SIFAR PRIVO DI DATA, predisposto per una visita del 1965, che indica millecinquecento uomini inquadrati nelle forze speciali, altri millecinquecento disponibili per mobilitazione e seicento64 quadri formati in cento36 corsi. MA IL 29 NOVEMBRE 1990, DAVANTI ALLA COMMISSIONE, IL CAPO DI STATO MAGGIORE DEL SISMI INTERROGATO SU QUELLA DISCREPANZA RISPOSE CHE «PROBABILMENTE CHI LO HA COMPILATO VOLEVA FARE BELLA FIGURA», indicando come piu veritieri gli elenchi nominativi. Agli atti risulta inoltre che LA FORZA COMPLESSIVA PREVISTA DEI QUARANTA NUCLEI AMMONTAVA A CENTOSESSANTA UOMINI, e che «non si hanno in atti riscontri sulla forza effettiva della struttura esterna». LA PARTE VII CLASSIFICA I TREMILA COME SAVONA A: E UNA SOVRASTIMA DI GRADO</t>
+          <t>LE MOTIVAZIONI, CHE INTERESSANO IL TOMO TERZO. La Corte accerta violazione dell’articolo 8 della Convenzione, e conclude che il provvedimento fu adottato «IN ASSENZA DI PROVE O DI RAGIONEVOLI SOSPETTI DEL COINVOLGIMENTO NEI FATTI OGGETTO DI INDAGINE, IDONEI A GIUSTIFICARLO». Stigmatizza che l’associazione NON DISPONESSE DI ALCUN RIMEDIO INTERNO. E afferma il principio che vale oltre il caso: L’IMMUNITA DEL PARLAMENTO INVOCATA DALLO STATO «RICHIEDE PUR SEMPRE LA POSSIBILITA DI QUALCHE FORMA DI CONTROLLO EX ANTE O EX POST DA PARTE DI UNA AUTORITA INDIPENDENTE, QUALE GARANZIA ESSENZIALE CONTRO INTERFERENZE ARBITRARIE DEI PUBBLICI POTERI»</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>I DEPOSITI: NON CENTOVENTISETTE MA CENTOTRENTANOVE, di cui SOLTANTO CENTOVENTISETTE FURONO SVELATI. Sui 12 mancanti Andreotti dichiaro nel 1990 che due erano stati asportati da ignoti probabilmente gia al momento dell’interramento del 1964, due si trovavano presso cimiteri poi ampliati e non erano piu recuperabili, e cosi gli altri 8. I 12 MANCANTI SONO PIU SIGNIFICATIVI DEI CENTOVENTISETTE RITROVATI, e il Volume Zero non li registra. Quanto agli effettivi: i reclutati dal 1956 al 1990 furono SEICENTO22, ma AL 1959 ERANO SESSANTA</t>
+          <t>IL PASSAGGIO PROCESSUALE DA REGISTRARE: il Governo aveva eccepito che il ricorso fosse manifestamente infondato, invocando L’AUTONOMIA DEL PARLAMENTO E LA SEPARAZIONE DEI POTERI, e sostenendo che perquisizione e sequestro fossero conformi all’ARTICOLO 82 DELLA COSTITUZIONE, cioe ai poteri d’inchiesta parlamentare. LA CORTE HA RESPINTO L’ECCEZIONE, ritenendo che essa sollevasse questioni che non potevano essere risolte senza esame nel merito</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Tomo I e Volume Zero — 3 CORREZIONI OBBLIGATORIE: il forte e sbagliato; i tremila uomini vanno declassati da A a fonte contestata sotto giuramento; i depositi sono centotrentanove e non centoventisette. VA INOLTRE RISOLTA LA DATA DELLA RIVELAZIONE, che le fonti collocano ora al 17, ora al 18, ora al 24 ottobre 1990 secondo la sede</t>
+          <t>Tomo III e Dominio 4 — E LA FORMA INVERSA DI TUTTO IL REPERTORIO, E VA SCRITTA COME TALE. Altrove lo Stato distrugge, espunge o non versa. QUI LO STATO SEQUESTRA E NON DISTRUGGE, E VIENE CONDANNATO PROPRIO PER NON AVER DISTRUTTO. E i poteri d’inchiesta esercitati sono gli stessi dell’articolo 82 che, in altra voce di questo repertorio, hanno consentito a una Commissione di acquisire atti da privati e da procedimenti in corso: LO STESSO STRUMENTO, DUE ESITI OPPOSTI</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr"/>
@@ -8626,42 +9178,42 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Piano Solo 1964 — verifica e RETTIFICHE AL VOLUME ZERO PARTE VII</t>
+          <t>Relazione della Commissione antimafia sulle infiltrazioni nella massoneria, Doc. XXIII n. 33, 21 DICEMBRE 2017 — le cifre di Castelvetrano</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Fonti: relazione della Commissione parlamentare d’inchiesta presieduta da Giuseppe Alessi, presentata il 15 DICEMBRE 1970; inchiesta amministrativa Lombardi; relazione della Commissione stragi della XIII legislatura; testimonianza di Francesco Cossiga al Tribunale di Velletri del 21 dicembre 1999 (Commissione stragi XIII leg., doc. Sifar-Piano Solo n. 2/2)</t>
+          <t>Commissione parlamentare d’inchiesta sul fenomeno delle mafie, 17sima legislatura. Istruttoria condotta con lungo ciclo di audizioni e missioni, fra cui quella a Palermo e Trapani del 18, 19 E 20 LUGLIO 2016, con prefetto, forze di polizia, magistratura distrettuale e circondariale, esperti e DUE COLLABORATORI DI GIUSTIZIA; auditi anche i vertici delle principali obbedienze</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>CONTRADDIZIONE INTERNA DA CORREGGERE: la Parte VII colloca un’audizione del generale de Lorenzo al 31 GENNAIO 1979, ma la stessa Parte VII ne indica la morte al 26 APRILE 1978. UN UOMO NON DEPONE DOPO MORTO: la data e con ogni probabilita 1969, E VA RISOLTA SULL’ATTO</t>
+          <t>LA CIFRA COMPLESSIVA: CENTONOVANTATRE ISCRITTI A LOGGE RISULTANO COINVOLTI IN INCHIESTE SULLA CRIMINALITA ORGANIZZATA. Per la Calabria si aggiunge che, fra i soggetti menzionati nella relazione della commissione di accesso e nell’ordinanza di custodia cautelare del Tribunale di Reggio Calabria, figurano TRECENTOSEI NOMINATIVI, 17 DEI QUALI CENSITI. Procedimenti richiamati: quelli denominati Mammasantissima, Morgana e Saggezza</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>LA CIFRA VA RIALZATA, NON CONFERMATA: LA RELAZIONE DI MINORANZA CONCLUSE CHE LE LISTE CONSEGNATE IL 28 GIUGNO 1964 NON CONTENESSERO 731 NOMINATIVI MA UN NUMERO NON INFERIORE A MILLECENTO-MILLEDUECENTO. Conferma indiretta: non si ritennero sufficienti gli aerei e si valuto di ricorrere anche a MEZZI NAVALI. Va inoltre segnalata una distinzione tecnica: secondo parte della pubblicistica la lista degli enucleandi NON ERA INCLUSA NEL PIANO SOLO ma discendeva da altro strumento e da altri piani di contingenza — DA RISOLVERE SUGLI ATTI</t>
+          <t>LE CIFRE DI CASTELVETRANO, CHE SONO IL CUORE DELLA RELAZIONE. NEL COMUNE OPERANO 6 LOGGE MASSONICHE SULLE 19 DELL’INTERA PROVINCIA. NEL 2016 4 ASSESSORI SU 5 ERANO ISCRITTI ALLA MASSONERIA, E 7 CONSIGLIERI SU TRENTA. Il comune E STATO SCIOLTO NEL GIUGNO 2017 PER INFILTRAZIONI della criminalita organizzata. Nel trapanese risultano inoltre duecento persone gia detenute per reati di mafia e stupefacenti, tornate in liberta a fine pena. La Commissione riferisce che 3 assessori massoni, due dei quali iscritti all’obbedienza maggiore, RESERO DICHIARAZIONI AMBIGUE SULLA VOLONTA DI COLLABORARE ALLA CATTURA DEL LATITANTE, E ATTACCARONO LA COMMISSIONE STESSA E LA SUA PRESIDENZA</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>IL FATTO PIU GRAVE DEL CAPITOLO, CHE IL VOLUME ZERO NON REGISTRA. La lista, «della cui esistenza non puo dubitarsi», NON FU CONSEGNATA ALLA COMMISSIONE PARLAMENTARE NE FIGURA TRA I DOCUMENTI DESECRETATI IL 28 DICEMBRE 1990. E il ragionamento e della Commissione stessa: cio «appare una circostanza di rilevante gravita, poiche lascia supporre che la lista contenesse NOMI DI PARLAMENTARI E DIRIGENTI POLITICI, la cui pubblicazione renderebbe impraticabile ogni ipotesi tendente a presentare gli eventi del 1964 come atti tutelativi». A cio si aggiunge che DEI FASCICOLI SIFAR SI DISPOSE LA DISTRUZIONE, e che il sottosegretario delegato a seguire l’inchiesta e INCARICATO DI PRENDERE IN CONSEGNA IL PIANO SOLO coperse con omissis gran parte dei documenti, COMPRESI QUELLI RELATIVI ALLE AZIONI PREVISTE, come egli stesso raccontera molti anni dopo</t>
+          <t>IL PASSAGGIO CHE RISOLVE LA QUESTIONE DEGLI ELENCHI IN CIRCOLAZIONE. Gli inquirenti trapanesi e palermitani hanno individuato «UN FILO CONDUTTORE CHE IPOTIZZA COME LE LOGGE COPERTE SI ANNIDINO ANCORA ALL’OMBRA DELLE LOGGE UFFICIALI; come gli uomini, pur risultati iscritti alle logge coperte, ABBIANO CONTINUATO A FAR CARRIERA SIA NEL MONDO POLITICO SIA NEL MONDO DEGLI AFFARI, NON ESSENDOCI MAI STATA UN’EFFICACE REAZIONE DELLE ISTITUZIONI PER ISOLARLI ANCHE DOPO CHE I LORO NOMI E LA LORO APPARTENENZA FOSSERO DIVENUTI PALESI; come vi sia riscontro che gia appartenenti a logge segrete e irregolari SIANO POI TRASMIGRATI IN ALTRE LOGGE; di come SIA POSSIBILE PASSARE DA UNA LOGGIA REGOLARE A UNA COPERTA E VICEVERSA»</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>L’ESITO, CHE VA SCRITTO PERCHE E LA FORMA RICORRENTE DEL REPERTORIO: la Commissione Alessi concluse per «UNA DEVIAZIONE DEPRECABILE» MA NON PER UN TENTATIVO DI COLPO DI STATO, e la seria minaccia di un golpe e stata esclusa TANTO DALLA MAGISTRATURA QUANTO DALLE INCHIESTE PARLAMENTARI. Da registrare inoltre che il generale incaricato dell’inchiesta interna MORI D’INFARTO NEL 1969 PRIMA DI DEPORRE davanti alla Commissione, e che il generale oggetto dell’inchiesta ERA NEL FRATTEMPO STATO ELETTO DEPUTATO nel 1968</t>
+          <t>LE VALUTAZIONI DELLA COMMISSIONE SULLE OBBEDIENZE E LA RETE CALABRESE. Si registra «UNA SORTA DI ARRENDEVOLEZZA NEI CONFRONTI DELLA MAFIA»; in diversi casi non e coltivato «il primario interesse alla impermeabilita dalle mafie»; il preteso rispetto delle leggi «SI E RIVELATO PIU APPARENTE CHE REALE»; e «IL SEGRETO COSTITUISCE IL PERNO DI ALCUNE OBBEDIENZE», con «un senso di riservatezza a dir poco esasperato». Dalle indagini calabresi emerge inoltre che un controllo del territorio cosi penetrante «NON SAREBBE POSSIBILE IN ASSENZA DI UNA RETE SEGRETA, COMPOSTA DA AVVOCATI, PROFESSIONISTI, AMMINISTRATORI LOCALI, APPARTENENTI ALLE FORZE DELL’ORDINE E AI SERVIZI SEGRETI, MAGISTRATI»</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Volume Zero Parte VII — 4 INTERVENTI: correggere la data dell’audizione; rialzare la cifra da 731 a millecento-milleduecento secondo la relazione di minoranza, dichiarando entrambe; INSERIRE LA SCOMPARSA DELLA LISTA E IL RAGIONAMENTO DELLA COMMISSIONE, che oggi manca; e scrivere l’esito, perche un capitolo che espone il piano senza dire come fini non e storia ma requisitoria</t>
+          <t>Dominio 1 × 3 × 4 × 10 — DUE ACQUISIZIONI DECISIVE. PRIMA: la relazione afferma che si passa DA UNA LOGGIA REGOLARE A UNA COPERTA E VICEVERSA, e che le coperte si annidano all’ombra delle ufficiali: ne segue che NESSUN ELENCO DI ISCRITTI REGOLARI PUO RAGGIUNGERE L’OGGETTO, e la questione dei file in circolazione e chiusa. SECONDA: che gli interessati abbiano continuato a far carriera ANCHE DOPO CHE L’APPARTENENZA ERA DIVENUTA PALESE e la forma del fatto accertato senza sanzione, applicata a questa materia e affermata da un organo parlamentare</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
@@ -8676,42 +9228,42 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>La rivelazione Gladio dell’ottobre 1990 — cronologia risolta, e le DUE VERSIONI della relazione</t>
+          <t>Processo Gotha, Reggio Calabria — LA TESI DELLA COMPONENTE RISERVATA MASSONICA, AFFERMATA IN PRIMO GRADO E DEMOLITA IN APPELLO NEL MAGGIO 2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Atti della Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, X legislatura; resoconti della Camera; relazione del Comitato parlamentare sui servizi del 1995</t>
+          <t>Procedimento nato dalla riunione delle inchieste denominate Mammasantissima, Reghion, Fata Morgana e Sistema Reggio — ALCUNE FONTI AGGIUNGONO ALCHEMIA: DISCREPANZA DA RISOLVERE — coordinate dalla Direzione distrettuale antimafia di Reggio Calabria. Rito abbreviato definito nel MARZO 2018 con sentenza di DUEMILACINQUECENTO PAGINE; rito ordinario definito in primo grado il 30 LUGLIO 2021; APPELLO DEFINITO NEL MAGGIO 2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>CRONOLOGIA RISOLTA: 3 AGOSTO 1990, davanti alla Commissione presieduta da Libero Gualtieri, prima ammissione dell’esistenza CON LA TESI che le attivita fossero proseguite «fino al 1972, dopodiche si e ritenuto che non ve ne fosse piu bisogno»; RELAZIONE ALLA COMMISSIONE PROTOCOLLO NUMERO 5099 DEL 17 OTTOBRE 1990 — DISCREPANZA CHIUSA, la data e attestata dal numero di protocollo e concordemente riportata; 24 OTTOBRE, discorso alla Camera e rivelazione pubblica; NOVEMBRE, scioglimento dichiarato; e IN UNA SUCCESSIVA TRASMISSIONE DI ATTI l’ammissione, contraria alla prima dichiarazione, CHE LA STRUTTURA ERA ANCORA IN PIEDI E OPERATIVA</t>
+          <t>LA TESI ACCUSATORIA, CHE COINCIDE CON QUELLA DI QUEST’OPERA: esisterebbe UN LIVELLO SUPERIORE E STRATEGICO collocato al di sopra dell’ala organizzativa e militare, composto da SOGGETTI CERNIERA CHE INTERAGISCONO FRA L’AMBITO VISIBILE E QUELLO OCCULTO, e legato ad ambienti massonici; una struttura capace di ETERODIRIGERE LA POLITICA E LE ISTITUZIONI LOCALI. Nelle motivazioni di primo grado si parla di «sistema allargato di potere tra cosche, massoneria e politica», e di una struttura segreta denominata anche «santa», «mammasantissima» o «cupola»</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>IL RITROVAMENTO PRINCIPALE, DA VERIFICARE SUGLI ATTI PARLAMENTARI MA CIRCOSTANZIATO: DELLA RELAZIONE ESISTEREBBERO DUE VERSIONI, e le differenze sono elencate. Nella prima si parla del CONTROLLO DEI SERVIZI SULL’INTERO GRUPPO, nella seconda NON SI FA PIU ALCUN ACCENNO A CONTROLLO. Nella prima si sostiene che LA PIANIFICAZIONE GEOGRAFICA E OPERATIVA ERA CONCORDATA CON IL SERVIZIO INFORMAZIONI AMERICANO: nella seconda LA RIGA SALTA INTERAMENTE. Nel documento corretto SCOMPARE OGNI ACCENNO AGLI STANZIAMENTI, e con essi le notizie su modalita operative, addestramento e materiali</t>
+          <t>GLI ESITI DI PRIMO GRADO. Rito abbreviato, marzo 2018: fra le condanne, VENT’ANNI a un avvocato indicato al vertice delle relazioni riservate. Rito ordinario, 30 luglio 2021, su trentaquattro imputati: 15 CONDANNE E 15 ASSOLUZIONI, a fronte di trenta condanne richieste. 25 ANNI a un avvocato ed ex parlamentare; 13 ANNI a un ex sottosegretario regionale; E ASSOLUZIONE DI UN EX SENATORE PER IL QUALE L’ACCUSA AVEVA CHIESTO VENT’ANNI. Motivazioni depositate nel 2023</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>E IL PUNTO CHE SI SALDA CON I 12 DEPOSITI MANCANTI: nella versione del 18 ottobre I DEPOSITI DI ARMI ED ESPLOSIVO SI DICEVANO SMANTELLATI E RICOSTITUITI ALTROVE. NELLA VERSIONE CORRETTA QUELLA INDICAZIONE NON C’E PIU. Se il riscontro regge sugli atti, e la riga piu importante dell’intero capitolo: non che i depositi furono smantellati, MA CHE FURONO RICOSTITUITI, E CHE QUESTO FU SCRITTO E POI TOLTO</t>
+          <t>L’APPELLO DEL MAGGIO 2026, ED E IL FATTO CHE VA REGISTRATO PER PRIMO IN OGNI CITAZIONE FUTURA. La Corte d’appello di Reggio Calabria HA AZZERATO LE CONDANNE ECCELLENTI, assolvendo l’ex parlamentare, l’ex senatore, un sacerdote e — pur deceduto — l’ex sottosegretario. Secondo le cronache «CROLLA ROVINOSAMENTE IN SECONDO GRADO L’IMPIANTO ACCUSATORIO CON IL QUALE LA PROCURA DISTRETTUALE PER UN DECENNIO HA IPOTIZZATO L’ESISTENZA DI UNA COMPONENTE RISERVATA E MASSONICA DELLA ORGANIZZAZIONE, CAPACE DI ETERODIRIGERE LA POLITICA E LE ISTITUZIONI LOCALI». LA DECISIONE NON E DEFINITIVA e le motivazioni non risultano ancora disponibili: RESTA IL GIUDIZIO DI LEGITTIMITA</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>DUE FATTI CHE IL VOLUME ZERO NON REGISTRA. PRIMO, L’ESITO GIUDIZIARIO: il fascicolo fu trasmesso per competenza territoriale alla Procura di Roma, LA QUALE DICHIARO CHE LA STRUTTURA NON AVEVA NULLA DI PENALMENTE RILEVANTE. SECONDO, CHE GLADIO NON ERA LA PRIMA: una relazione del Comitato parlamentare sui servizi del 1995 afferma che «e fuor di dubbio che in epoca precedente alla creazione di Gladio sia esistita un’altra organizzazione denominata DUCA, con le stesse finalita e struttura analoga, DI CUI SAPPIAMO BEN POCO e che dovrebbe essere stata sciolta INTORNO AL GENNAIO 1995», e che in vari documenti acquisiti dall’autorita giudiziaria si parla di organizzazione «Duca-Gladio»</t>
+          <t>CONSEGUENZA PER QUEST’OPERA, E VA SCRITTA SENZA ATTENUAZIONI. IL TENTATIVO GIUDIZIARIO PIU AVANZATO MAI CONDOTTO DI PROVARE L’ESISTENZA DI UN DIRETTORIO OCCULTO MASSONICO-MAFIOSO CHE ETERODIRIGE LE ISTITUZIONI E STATO ACCOLTO A META IN PRIMO GRADO E RESPINTO IN APPELLO. Chi sostenga quella tesi deve oggi confrontarsi con questo esito, non ignorarlo. E chi citi la relazione parlamentare del 2017, che a quelle inchieste si appoggiava, DEVE CITARE ANCHE IL SEGUITO GIUDIZIARIO</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Volume Zero Parte VII — 3 INTEGRAZIONI: risolvere e citare la data della relazione; INSERIRE LE DUE VERSIONI, previa verifica sugli atti, perche e il fatto piu eloquente del capitolo; e scrivere l’esito romano insieme all’esistenza dell’organizzazione anteriore ancora in scioglimento nel 1995</t>
+          <t>Dominio 1 × 4 e Metodologia — DUE LEZIONI. LA PRIMA: la distanza fra accertamento parlamentare e accertamento giudiziario e strutturale, e questa vicenda ne e la dimostrazione piu netta del repertorio — la Commissione afferma nel 2017, il primo grado conferma a meta nel 2021, l’appello azzera nel 2026. LA SECONDA: e la forma inversa del fatto accertato senza sanzione — QUI NON MANCA LA SANZIONE, MANCA L’ACCERTAMENTO, e la differenza va tenuta</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr"/>
@@ -8726,44 +9278,40 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Le origini pre-1956 dello stay-behind italiano — testo primario GIA PRESENTE NEL CORPUS E NON UTILIZZATO</t>
+          <t>Operazione Kyterion, Direzione distrettuale antimafia di Catanzaro, 2015-2016 — CONDANNE CHE TOCCANO IL NODO MASSONICO</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, XIII legislatura, Doc. XXIII n. 64, Volume I, Tomo II, da pagina 67; il piano Demagnetize/Clydesdale e trattato a pagina 94. Il testo e gia nei file del progetto (blocchi p67) ed e integralmente consultabile presso l’archivio storico del Senato</t>
+          <t>Kyterion prima fase: 28 GENNAIO 2015, 37 arresti, contemporanea a un’altra operazione emiliana. Kyterion seconda fase: 4 GENNAIO 2016, 16 arresti. Procedimento a carico della cosca di Cutro</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>LA RETTIFICA DI NOME: NON «PIANO DEMAGNETIZE» MA «PIANO DEMAGNETIZE/CLYDESDALE», come lo chiamano costantemente gli atti parlamentari. Il documento e un memorandum riservato del comando di Stato maggiore statunitense DATATO 14 MAGGIO 1952 — il Volume Zero non ne da la data. LA PATERNITA E RISOLTA: E DELLO PSYCHOLOGICAL STRATEGY BOARD, non del comitato dei capi di Stato maggiore — vedi voce dedicata. La prima pubblicazione avvenne IN UN LIBRO DEL 1978, non per acquisizione tramite settimanale come scrive il Volume Zero. L’analogo piano francese si chiamava CLOVEN. Contenuto: epurazione della presenza comunista da enti pubblici e industrie, inasprimento della legislazione di pubblica sicurezza, e predisposizione di un sistema atto a prevenire la crescita del PCI ANCHE SU BASE MILITARE — ma la valutazione accademica segnala la MANCANZA DI PRESCRIZIONI CONCRETE</t>
+          <t>CHE COSA SVELO LA SECONDA FASE, e va citato con la cautela dovuta alla fonte secondaria: tentativi di collegamento del capocosca CON AMBIENTI DEL VATICANO, DELLA CORTE DI CASSAZIONE E DI ORDINI MASSONICI, oltre a un conto corrente indicato in DUECENTO43 MILIONI DI EURO. E il nodo Dominio 1 × Dominio 4 × Dominio 5 in un solo procedimento</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LA FRASE DELLA COMMISSIONE CHE RISOLVE IL PROBLEMA DELLA DATA DEL 1956, e che il Volume Zero non cita: queste strutture sono «concepite sempre con uno scarto temporale notevole, di diversi anni, e LA LORO UFFICIALIZZAZIONE VIENE COSTANTEMENTE POSTICIPATA, A GUISA DI SANATORIA». Il 26 novembre 1956 non e la nascita: E LA SANATORIA. E la Commissione aggiunge che per questo «risulta difficile seguire coerentemente lo svolgersi dei passaggi che portano alla creazione di Gladio e alla sua formalizzazione»</t>
+          <t>GLI ESITI, CHE SONO L’OPPOSTO DI QUELLI REGGINI E ROMANI: nel rito ordinario 11 CONDANNE SU 11 IMPUTATI, ZERO ASSOLUZIONI, con pene da 6 a 16 anni «spesso aumentate rispetto alle richieste dell’accusa». Con rito abbreviato TRENTA ANNI al capo. Fra le posizioni piu rilevanti per questo lavoro: 10 ANNI a un impiegato comunale indicato come filtro delle visite al detenuto; 10 ANNI a un soggetto indicato come INTERMEDIARIO FRA FINANZA E MASSONERIA per conto del capo; 6 ANNI E 8 MESI a un avvocato per concorso esterno. Rinviati a giudizio, fra gli altri, un avvocato indicato per contatti con la Cassazione</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>I DUE DOCUMENTI DEL 1951, 5 ANNI PRIMA DEL PROTOCOLLO, ENTRAMBI NEL CORPUS E NON USATI. PRIMO: NELL’OTTOBRE 1951 IL COMANDO NATO ORGANIZZA A PARIGI UN CONVEGNO INTITOLATO «SICUREZZA CIVILE E CONTROSPIONAGGIO IN TEMPO DI PACE», nel corso del quale VIENE AVANZATA LA PROPOSTA DI CREARE UN COMITATO PER LA PIANIFICAZIONE CLANDESTINA che coordini le attivita stay-behind in Europa. SECONDO: IL PROMEMORIA DEL 18 OTTOBRE 1951 del capo del SIFAR generale Umberto Broccoli al capo di Stato maggiore della Difesa generale Efisio Marras, che scrive essere «primo dovere del SIFAR quello di prevedere, in caso di conflitto, l’occupazione nemica di almeno parte del territorio nazionale e di preorganizzare il servizio informazioni, il sabotaggio, la propaganda e la resistenza», e rileva che «in Olanda e Belgio, e presumibilmente anche in Danimarca e in Norvegia, l’organizzazione puo dirsi a punto»</t>
+          <t>IL CONFRONTO CHE NE DISCENDE, ED E IL PIU ISTRUTTIVO DEL REPERTORIO SU QUESTA MATERIA. Dove l’accusa ha contestato CONDOTTE INDIVIDUALI DI INTERMEDIAZIONE — un impiegato che filtra, un intermediario che collega, un avvocato che assiste — LE CONDANNE HANNO TENUTO, 11 SU 11. Dove ha contestato L’ESISTENZA DI UNA STRUTTURA ASSOCIATIVA OCCULTA SOVRAORDINATA, l’impianto e caduto: a Roma per esclusione del carattere mafioso in Cassazione nel 2019, a Reggio per azzeramento in appello nel 2026</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>E LA FORMULAZIONE PARLAMENTARE DELLA TESI COSTITUZIONALE, CHE E IL PERNO DELL’OPERA: le finalita della struttura «mantengono un profilo di NON SICURA LEGITTIMITA COSTITUZIONALE», perche «rimane dubbia la legittimita di un organismo sorto sulla base di un accordo stipulato tra due Servizi NON UFFICIALMENTE AUTONOMI NEI CONFRONTI DEL POTERE ESECUTIVO E LEGISLATIVO DEI RISPETTIVI PAESI». NON SERVE ARGOMENTARLA: L’HA GIA SCRITTA UNA COMMISSIONE BICAMERALE, E IL TESTO E GIA NEI FILE DEL PROGETTO</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>Volume Zero Parte VII — RIFONDAZIONE DEL CAPITOLO. Il capitolo va riscritto a partire dal 1951 e non dal 1956, sui due documenti d’ottobre; la data del 1956 va presentata come sanatoria e non come nascita, con le parole della Commissione; e vanno aperti i paragrafi che l’indice parlamentare gia elenca e il Volume Zero ignora: l’ufficio statunitense per le operazioni coperte e le armi nella campagna elettorale, l’organizzazione «O» e l’Armata italiana della liberta, l’ufficio REI del SIFAR con «Pace e Liberta», la polizia segreta del Viminale e il gruppo De Nozza, i Nuclei di difesa dello Stato e il gruppo Sigfried</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
+          <t>Dominio 1 × 4 × 5 — REGOLA CHE NE DERIVA PER L’OPERA: la prova regge sul singolo legame documentato e cede sulla struttura complessiva. Un’opera che costruisca il proprio impianto sulla seconda replica l’errore che due impianti accusatori hanno gia commesso; un’opera che lo costruisca sulla prima poggia su cio che ha retto in giudizio</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr"/>
       <c r="J77" s="8" t="inlineStr">
         <is>
@@ -8776,44 +9324,40 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>La lettera di Edgardo Sogno ad Aldo Moro — DOCUMENTO DI PRIMO ORDINE GIA NEL CORPUS, MAI UTILIZZATO</t>
+          <t>Operazione Laziogate, 2005-2012 — ASSOLUZIONE PIENA DOPO CONDANNA DI PRIMO GRADO</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Riportata nella relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, alle pagine 87-89, sulla scorta della sentenza-ordinanza del giudice istruttore di Venezia Carlo Mastelloni, pagine 1318-1319. Testo gia trascritto nei file di progetto</t>
+          <t>Fatti del marzo 2005; sentenza di primo grado del 5 MAGGIO 2010; sentenza d’appello del 29 OTTOBRE 2012</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>CHE COSA DICE, NELLE PAROLE DELLO STESSO PROTAGONISTA. Scrivendo all’allora ministro degli esteri Aldo Moro per lamentare il mancato avanzamento di carriera, Sogno spiega che «NEL LUGLIO DEL 1953, PER INIZIATIVA DELLA PRESIDENZA DEL CONSIGLIO, MI VENIVA NUOVAMENTE PROPOSTO UN INCARICO DI CARATTERE ECCEZIONALE E RISERVATO — ORGANIZZAZIONE DELLA DIFESA PSICOLOGICA DELLE ISTITUZIONI DEMOCRATICHE — IN RIPRESA DI UN’OPERAZIONE AVVIATA NEL 1948 PER INIZIATIVA DEL MINISTRO SFORZA NEL QUADRO DELLE ATTIVITA SVOLTE IN BASE AL PIANO MARSHALL»</t>
+          <t>L’ACCUSA: intrusione nel sistema informatico dell’anagrafe comunale di Roma, nella notte fra il 9 e il 10 MARZO 2005, attraverso i computer della societa informatica regionale, PER VERIFICARE PRESUNTE FIRME FALSE NELLA LISTA DI UNA FORMAZIONE RIVALE alle elezioni regionali. Il presidente uscente della Regione, divenuto nel frattempo ministro, SI DIMISE NEL 2006 DOPO L’AVVISO DI GARANZIA</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>E PROSEGUE: «L’azione svolta per il tramite del Comitato da me organizzato ebbe 3 FASI PRINCIPALI: in un periodo, fino all’ottobre 1954, essa si concreto nella realizzazione del progetto CHE GLI ONOREVOLI DE GASPERI E PELLA AVEVANO RIPETUTAMENTE SOSTENUTO IN CONSIGLIO ATLANTICO». Un appunto di poco precedente riferisce inoltre che le iniziative di «Pace e Liberta» «avrebbero riscosso l’adesione e l’appoggio del Presidente del Consiglio Scelba, del ministro Taviani, del Ministro degli esteri», e CHE SOGNO AVREBBE FATTO ISTITUIRE AGLI ESTERI UN UFFICIO PER IL COORDINAMENTO DELLA GUERRA PSICOLOGICA DA LUI DIRETTO</t>
+          <t>IL PRIMO GRADO condanno 12 posizioni, con pene da 8 mesi a due anni e due patteggiamenti. L’APPELLO ASSOLSE TUTTI CON FORMULA «PERCHE IL FATTO NON SUSSISTE», sul rilievo che ESISTEVA UNA CONVENZIONE CHE AUTORIZZAVA L’ACCESSO ALLA BANCA DATI. Una posizione fu assolta in sede di legittimita</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>PERCHE E LA MIGLIORE PROVA DEL CORPUS PER LA TESI DELL’OPERA. Non e una ricostruzione di terzi: e IL PROTAGONISTA CHE DESCRIVE PER ISCRITTO LA PROPRIA STRUTTURA, AL FUTURO STATISTA POI RAPITO E UCCISO, datandone l’origine al 1948 e ancorandola al Piano Marshall, con il sostegno di due presidenti del Consiglio in sede atlantica. E ANTICIPA DI 8 ANNI IL PROTOCOLLO DEL 1956</t>
+          <t>PERCHE VA REGISTRATA IN QUESTO REPERTORIO: e il caso simmetrico e opposto a quelli che vi dominano. Altrove il fatto e accertato e la sanzione manca; QUI LA SANZIONE ERA STATA IRROGATA IN PRIMO GRADO E IL FATTO E RISULTATO INSUSSISTENTE. Nel mezzo, LE DIMISSIONI DI UN MINISTRO 7 ANNI PRIMA DELL’ASSOLUZIONE DEFINITIVA</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>DUE ALTRI DOCUMENTI DELLO STESSO FONDO, PARIMENTI INUTILIZZATI. IL PRIMO: un appunto del Viminale del 27 DICEMBRE 1974 trasmesso a Torino, secondo cui una fonte fiduciaria segnala un avvocato titolare di una ditta di import-export come «UNO DEI FINANZIATORI DELLE ORGANIZZAZIONI NEOFASCISTE ITALIANE», in contatto con 3 persone nominate; e un appunto precedente sul rapporto fra un dirigente della destra italiana e il rappresentante di un governo allora «noto per essere uno dei piu razzisti del mondo, insieme con il Sudafrica». IL SECONDO: la deposizione di Carlo Digilio, principale testimone del nuovo processo su piazza Fontana, il quale racconta di aver visto in casa di un dirigente ordinovista, USCITO DA UN VOLUME DI EVOLA, un foglio con LA CARTA D’ITALIA E CROCETTE BLU accanto ai capoluoghi, in calce l’indicazione «NUCLEI DI DIFESA DELLO STATO», le crocette concentrate nel Nord-Est e NUMERI ROMANI A INDICARE LE LEGIONI</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>Volume Zero e Tomo I — QUESTI 3 DOCUMENTI VALGONO PIU DELL’INTERA PARTE VII ATTUALE. Sono gia nel corpus, trascritti dall’autore nel marzo 2026 dal PDF dell’archivio storico del Senato, e non compaiono nel testo dell’opera</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
+          <t>Tomo III — MISURA DELLA DISTANZA FRA EFFETTO POLITICO ED ESITO GIUDIZIARIO: l’effetto si produce all’avviso di garanzia, l’accertamento arriva 7 anni dopo e in senso contrario. E dato che un’opera sul potere occulto deve registrare con la stessa cura delle condanne</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="3" t="inlineStr"/>
       <c r="J78" s="8" t="inlineStr">
         <is>
@@ -8826,42 +9370,42 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Il rapporto D’Amato–Delle Chiaie — FONTE FONDATIVA DELL’ARCO DI SPONDA, gia nel corpus</t>
+          <t>Operazione e processo Grimilde, Bologna-Reggio Emilia, 2019-2025 — LA STRUTTURA ASSOCIATIVA PROVATA IN VIA DEFINITIVA, e RETTIFICA A UNA VOCE PRECEDENTE</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 135-136, che riporta ampi brani della sentenza-ordinanza del giudice istruttore di Venezia Carlo Mastelloni; deposizione di Guglielmo Carlucci del 15 MAGGIO 1997</t>
+          <t>Operazione del 25 GIUGNO 2019, 16 arresti e sessanta indagati, Direzione distrettuale antimafia di Bologna con le squadre mobili di Bologna, Reggio Emilia e Piacenza. Rito abbreviato: sentenza del giudice per le indagini preliminari del 26 OTTOBRE 2020; appello del 16 GIUGNO 2022; CASSAZIONE DEL 2 LUGLIO 2023. Rito ordinario: primo grado del 15 DICEMBRE 2022; appello 2024; CASSAZIONE NOVEMBRE 2025</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>CHI PARLA, ED E QUESTO A FARE IL LIVELLO: non un collaboratore di giustizia ne un giornalista, ma UN EX DIRIGENTE DEGLI AFFARI RISERVATI, STRETTO COLLABORATORE DI D’AMATO, che depone davanti a un giudice istruttore. Egli ricorda che Delle Chiaie ERA SOLITO FREQUENTARE D’AMATO sia quando questi era vicedirettore sia dopo, da direttore della Divisione, TRATTENENDOSI CON IL PREFETTO NEI LOCALI DELL’UFFICIO, E CHE IN ALCUNE OCCASIONI EGLI STESSO AVEVA ASSISTITO AI COLLOQUI</t>
+          <t>GLI ESITI, CHE SONO L’OPPOSTO DI QUELLI ROMANO E REGGINO. Rito abbreviato in primo grado: 42 CONDANNE SU 48 IMPUTATI, DUECENTOTRENTUNO ANNI COMPLESSIVI, compresi 9 patteggiamenti. In appello «L’ACCUSA HA RETTO: I GIUDICI HANNO CONFERMATO TUTTE LE CONDANNE PER ASSOCIAZIONE MAFIOSA», riducendo le pene. In Cassazione 18 CONDANNE DIVENUTE DEFINITIVE e 6 posizioni rinviate a nuovo appello. Nel rito ordinario il capo, cui il primo grado aveva ESCLUSO LA POSIZIONE APICALE con 19 anni e 6 mesi, se l’e vista RICONOSCIUTA IN APPELLO CON PENA INASPRITA A 24 ANNI, e il ricorso e stato dichiarato inammissibile</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CHE COSA PASSAVA NELLE DUE DIREZIONI. VERSO DELLE CHIAIE: la Divisione AGEVOLAVA IL CAPO DI AVANGUARDIA NAZIONALE PER IL RILASCIO DI PASSAPORTI, PER CONCESSIONI DEL PORTO D’ARMI E PER QUANT’ALTRO, intervenendo presso gli organi competenti della questura, ED ESTENDENDO QUESTO TIPO DI INTERVENTO ANCHE A QUALCHE AMICO DELL’ESTREMISTA. VERSO D’AMATO: Delle Chiaie forniva notizie che il prefetto, DOPO ESSERSI FATTO DESCRIVERE LE SINGOLE PERSONALITA DEGLI APPARTENENTI AL GRUPPO, trasfondeva in appunti inoltrati per lo sviluppo alla sezione competente AL FINE DI STIMOLARE I CONSEGUENTI CONTROLLI SUI MILITANTI, e in taluni casi direttamente al capo della polizia, che ove del caso li inoltrava al ministro</t>
+          <t>IL FATTO CHE VA REGISTRATO PER PRIMO: E DIVENUTA DEFINITIVA LA CONDANNA A OLTRE 12 ANNI DI UN ESPONENTE POLITICO ELETTO — ex presidente del consiglio comunale di un capoluogo e funzionario dell’Agenzia delle dogane, allontanato dal proprio partito subito dopo l’arresto — RICONOSCIUTO FRA GLI ESPONENTI DEL SODALIZIO. La procura generale ha sottolineato che «CON SENTENZA DEFINITIVA E STATA RIBADITA, CON LA CONFERMA DEL DELITTO DI ASSOCIAZIONE DI STAMPO MAFIOSO, L’ESISTENZA E L’OPERATIVITA NEL DISTRETTO DELL’EMILIA-ROMAGNA DI UNA STRUTTURA AUTONOMA»</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>LE QUALIFICAZIONI, TESTUALI: Delle Chiaie era «UN SUO CONFIDENTE NONCHE INFILTRATO» nella struttura di estrema destra; si trattava di «UN RAPPORTO PERSONALE ED ESCLUSIVO» del prefetto; e di «UN CONTATTO RISCHIOSO» ritenuto pero da entrambi «INDISPENSABILE». Il commento che seguiva a ogni commiato era sempre che il contatto «POTEVA ESSERE UTILE PER NOI». La Commissione qualifica la deposizione come «UN RISCONTRO DIRETTO pertinente a un rapporto di cui si e eternamente sussurrato»</t>
+          <t>RETTIFICA ALLA VOCE PRECEDENTE DI QUESTO REPERTORIO. Era stato scritto che «la prova regge sul singolo legame documentato e cede sulla struttura complessiva»: E FORMULAZIONE ERRATA, e Grimilde la smentisce. LA DIFFERENZA REALE E ALTRA: dove l’accusa contesta UNA CELLULA TERRITORIALE CON CONDOTTE MATERIALI DOCUMENTATE — appalti a societa di comodo, frodi fiscali, riciclaggio, caporalato, relazioni con amministratori — LA QUALIFICAZIONE ASSOCIATIVA REGGE FINO IN CASSAZIONE. Dove contesta UNA STRUTTURA OCCULTA SOVRAORDINATA E TRASVERSALE, che collega massoneria, servizi e politica senza condotte materiali proprie, l’impianto cade: a Roma nel 2019, a Reggio Calabria nel 2026</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>LA DISCIPLINA CHE IL TESTO STESSO APPLICA E CHE VA CONSERVATA: la testimonianza di Vinciguerra al giudice istruttore di Milano del 30 MAGGIO 1992 chiamava in causa anche un prefetto, IL QUALE, SUCCESSIVAMENTE INTERROGATO, PUR AMMETTENDO LA CONOSCENZA CON DELLE CHIAIE HA NEGATO QUANTO GLI ERA STATO ATTRIBUITO. LA SMENTITA VA RIPORTATA ACCANTO ALL’ACCUSA</t>
+          <t>IL CONTESTO CHE VALE PER IL TOMO SECONDO: il comune di Brescello fu SCIOLTO PER INFILTRAZIONI NEL 2015, primo caso nel Nord Italia. Nel 2009 un sindaco aveva definito diffamatori gli articoli sulla presenza criminale; nel 2014 un altro sindaco defini il capocosca «UNA PERSONA EDUCATA, TRANQUILLA» — E DA QUELL’EPISODIO INIZIARONO GLI ACCERTAMENTI CHE PORTARONO ALLO SCIOGLIMENTO. DISCREPANZA DA RISOLVERE: le fonti indicano per il rito ordinario ora 11 condanne e 5 assoluzioni, ora 13 condanne</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Metodologia e Dominio 3 × 7 — E LA FONTE FONDATIVA DEL SESTO TIPO DI ARCO, quello che la tipologia della Nota Metodologica non contempla: NON COLLUSIONE FRA PARI, NON STRUMENTALIZZAZIONE DEL DEBOLE DA PARTE DEL FORTE, MA SCAMBIO ASIMMETRICO BIDIREZIONALE in cui ciascuno usa l’altro per fini propri e incompatibili. Lo Stato ottiene la mappa dei militanti; il militante ottiene passaporti, porto d’armi e protezione estesa agli amici. NESSUNO DEI DUE E STRUMENTO DELL’ALTRO: ENTRAMBI LO SONO</t>
+          <t>Dominio 1 × 2 e Metodologia — E IL CONTROESEMPIO CHE SALVA LA TESI DALL’ECCESSO OPPOSTO: non e vero che l’associazione occulta non si possa provare. SI PROVA QUANDO HA CONDOTTE MATERIALI PROPRIE, e non si prova quando e postulata come livello superiore privo di atti propri. La differenza non e di giudici: E DI OGGETTO</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
@@ -8876,42 +9420,42 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>La politica statunitense verso l’Italia negli atti del Consiglio di sicurezza nazionale — RETTIFICHE E CONTROPROVA</t>
+          <t>Processo cosiddetto P3 — Tribunale di Roma, nona sezione penale, sentenza di PRIMO GRADO DEL 16 MARZO 2018</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Serie Foreign Relations of the United States, consultabile integralmente sul sito dell’Office of the Historian del Dipartimento di Stato</t>
+          <t>Inchiesta della Procura di Roma aperta nella primavera del 2010 su una presunta associazione segreta finalizzata al pilotaggio di appalti e sentenze e al dossieraggio; denominazione giornalistica per assonanza con la loggia sciolta nel 1982. Requirenti: il procuratore aggiunto e un sostituto. 18 IMPUTATI, 18 CONDANNE RICHIESTE, 8 PRONUNCIATE</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PRIMA RETTIFICA, DI CITAZIONE: il documento NSC 6014 e pubblicato nel volume FRUS 1958-1960, tomo settimo parte seconda, documento 278, con il titolo DRAFT STATEMENT OF U.S. POLICY TOWARD ITALY. La numerazione del Consiglio di sicurezza indica nelle prime due cifre l’anno: SEIMILA14 SIGNIFICA 1960, NON 1961. La versione approvata con suffisso /1 datata 19 aprile 1961, citata dal Volume Zero, NON E STATA REPERITA in questa verifica: VA PRODOTTO L’ATTO O CORRETTA LA CITAZIONE</t>
+          <t>L’AFFERMAZIONE CENTRALE, ED E LA PRIMA DEL GENERE DOPO IL 1982: il tribunale ha riconosciuto che «LA P3 FU UN’ASSOCIAZIONE SEGRETA», condannando per VIOLAZIONE DELLA LEGGE ANSELMI. E la prima verita processuale sull’applicazione di quella legge a distanza di 36 anni dalla sua entrata in vigore. VA PERO REGISTRATO CHE SI TRATTA DI SENTENZA DI PRIMO GRADO, e che gli esiti dei gradi successivi VANNO VERIFICATI PRIMA DI OGNI CITAZIONE</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>SECONDA RETTIFICA, DI CARATTERIZZAZIONE: il Volume Zero definisce quel documento «la direttiva politica che governa l’intera operazione». IL TESTO NON E UNA DIRETTIVA OPERATIVA MA UNA DICHIARAZIONE DI INDIRIZZO. Vi si legge che l’Italia e membro chiave dell’Alleanza atlantica e che il suo progresso e essenziale «non soltanto al concetto strategico NATO per la difesa dell’Europa, ma all’unita storica e alla continua crescita della Comunita atlantica»; e che fino alle elezioni del 1948 esistette grave pericolo di dominazione comunista, arrestato «in parte per effetto di aiuti economici su larga scala, di fermo sostegno morale e della sicurezza militare fornita dall’appartenenza alla NATO». NULLA VI RIGUARDA RETI CLANDESTINE</t>
+          <t>LE CONDANNE. 6 ANNI E 6 MESI a un uomo d’affari indicato come promotore, gia condannato per il dissesto di un istituto bancario e imputato ma assolto per l’omicidio di un banchiere: richiesti 9 anni e 6 mesi. 4 ANNI E 9 MESI a un imprenditore, richiesti 8. DUE ANNI PER ABUSO D’UFFICIO A UN EX PRIMO PRESIDENTE DELLA CORTE DI CASSAZIONE, per il quale erano stati richiesti 5 anni per corruzione. UN ANNO E 10 MESI ciascuno per corruzione a un ex presidente di agenzia regionale e a un presidente di consorzio. 10 MESI per diffamazione e violenza privata a un ex sottosegretario all’Economia e a un ex assessore regionale</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>I DUE DOCUMENTI CHE IL VOLUME ZERO AVREBBE DOVUTO CITARE AL SUO POSTO. IL PRIMO E NSC 5411/2, «U.S. POLICY TOWARD ITALY», APPROVATO DAL PRESIDENTE IL 15 APRILE 1954 e pubblicato in FRUS 1952-1954, volume sesto parte seconda, pagina 1677: e questo, e non il successivo, l’atto di indirizzo vigente per gran parte del periodo. IL SECONDO E IL PIANO OPERATIVO PREDISPOSTO DALL’ORGANO DI COORDINAMENTO DELLE OPERAZIONI, che fissa come obiettivo di lungo termine un’Italia libera da dominazione comunista «AVENTE UN GOVERNO COSTITUZIONALE E DEMOCRATICO», E CHE RECA ESPUNZIONI PROPRIO NEI PUNTI DECISIVI: una riga non declassificata dove si afferma che l’influenza statunitense deve concentrarsi sulle questioni essenziali, e 3 RIGHE E MEZZA NON DECLASSIFICATE sotto la voce degli impegni militari</t>
+          <t>GLI ESITI NON DI CONDANNA, CHE SONO LA MAGGIORANZA: prescrizione per l’ex presidente di una Regione, imputato di abuso d’ufficio; assoluzione per un ex coordinatore regionale e per un direttore di filiale bancaria; assoluzione richiesta dagli stessi requirenti per un dirigente comunale; DECESSO del terzo indicato come promotore la settimana precedente la sentenza; STRALCIO della posizione di un ex senatore, POI PRESCRITTA L’ANNO SUCCESSIVO. La maggior parte dei reati contestati risultava prescritta</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>LA CONTROPROVA, CHE L’OPERA HA L’OBBLIGO DI REGISTRARE. Nella risposta al memorandum di studio numero 88, del 1970, l’amministrazione statunitense esamina l’ipotesi di UNA LINEA INTERVENTISTA IN ITALIA E LA ARGOMENTA CONTRO, per queste ragioni testuali: getterebbe dubbio «SULLE NOSTRE PUBBLICHE AFFERMAZIONI SECONDO CUI LA FORMA DELL’EUROPA SPETTA AGLI EUROPEI»; e improbabile che le attivita discrete, compresi gli approcci a Regno Unito, Francia e Germania, RESTINO SEGRETE; alienerebbe gli altri alleati europei, oltre a molti italiani, che risentirebbero dell’ingerenza statunitense nella politica interna; e infine «MOLTO PROBABILMENTE NON RIUSCIREBBE A CONSEGUIRE I RISULTATI DESIDERATI»</t>
+          <t>RETTIFICA A UNA VOCE DI QUESTO REPERTORIO, DOVUTA. Era stato scritto che la scheda del censimento attribuisce erroneamente a una posizione il capo «finanziamento illecito P3» in quanto assolta: L’AFFERMAZIONE VA CORRETTA. Quella posizione FU EFFETTIVAMENTE CONDANNATA IN PRIMO GRADO A UN ANNO E 3 MESI, PIU 6100.000 EURO DI MULTA, PER FINANZIAMENTO ILLECITO. IL DIFETTO DELLA SCHEDA E DIVERSO E RESTA: essa NON REGISTRA CHE LA MEDESIMA POSIZIONE FU ASSOLTA DALL’ACCUSA DI APPARTENERE ALL’ASSOCIAZIONE, che era il capo principale</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Metodologia e Tomo II — UNA TESI DI INGERENZA CONTINUA DEVE MISURARSI CON IL DOCUMENTO IN CUI L’INGERENZA E DISCUSSA E SCARTATA DALL’INTERNO, e per ragioni di inefficacia e di costo politico presso gli alleati. Registrarlo non indebolisce l’opera: LE DA IL SOLO ARGOMENTO CHE UN AVVERSARIO NON PUO RITORCERLE CONTRO</t>
+          <t>Dominio 2 × 4 — E IL TERMINE DI CONFRONTO PER IL PROCEDIMENTO REGGINO. In quello la contestazione di associazione segreta NON FU RICONOSCIUTA in appello; qui FU RICONOSCIUTA in primo grado. Due applicazioni della medesima legge del 1982, due esiti opposti, e in entrambi i casi LE CONDOTTE INDIVIDUALI HANNO RETTO PIU DELLA QUALIFICAZIONE ASSOCIATIVA</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
@@ -8926,42 +9470,42 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Il progetto eversivo del 1973-1974 e la notte del 7 dicembre 1970 — FONTE PARLAMENTARE DELLA TESI COSTITUZIONALE</t>
+          <t>Il procedimento tedesco sull’attentato del 1980 — CRONOLOGIA CHIUSA E 3 FATTI NUOVI</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 157-165, sulla scorta dell’ordinanza-sentenza del giudice istruttore di Milano Guido Salvini del 18 MARZO 1995, pagine 245-249 e 301 e seguenti. Testo gia nel corpus</t>
+          <t>Archivio federale tedesco, che pubblica in linea i documenti del procedimento; risposta scritta del governo federale all’interrogazione presentata da deputati del gruppo di sinistra, stampato parlamentare 19/22430; comunicato del Bundestag; rassegna coeva</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>LA DESCRIZIONE DEL PROGETTO, TESTUALE, ED E LA TESI DELL’OPERA SCRITTA DA UN ORGANO DELLO STATO: il seguito del tentativo del 1970 avrebbe perseguito, con modalita sostanzialmente insurrezionali, «LA REALIZZAZIONE DI UN PROGETTO DI REVISIONE COSTITUZIONALE, CHE PORTASSE ALL’INSTAURAZIONE DI UNA REPUBBLICA PRESIDENZIALE, caratterizzata da PROGRAMMI SOCIALMENTE AVANZATI, MA DA FORTI LIMITAZIONI DEI DIRITTI SINDACALI, CONCENTRAZIONE DEI MEZZI DI INFORMAZIONE E DA UNA FORTE SCELTA ATLANTISTA; un progetto di stabilizzazione quindi DA REALIZZARSI ATTRAVERSO MEZZI DESTABILIZZANTI — attentati sui treni e in luoghi pubblici, eliminazione di avversari politici, scontri di piazza — LA CUI RESPONSABILITA SAREBBE STATA APPARENTEMENTE ATTRIBUIBILE ALLA SOVVERSIONE DI SINISTRA, si da determinare una forte domanda d’ordine e quindi giustificare l’intervento delle Forze Armate»</t>
+          <t>LA CRONOLOGIA, ORA CHIUSA. 26 SETTEMBRE 1980, ore 22 e venti: l’ordigno esplode all’ingresso principale, 13 MORTI compreso GUNDOLF KÖHLER e OLTRE 221 FERITI. 27 SETTEMBRE: il procuratore generale federale KURT REBMANN assume la direzione delle indagini — E QUESTO E IL PRIMO FATTO NUOVO — «PER IL FONDATO SOSPETTO DI UN ATTO TERRORISTICO DI GRUPPO». 13 MAGGIO 1981: la commissione speciale del servizio criminale bavarese licenzia un rapporto conclusivo di 187 PAGINE. 23 NOVEMBRE 1982: il procuratore generale chiude il procedimento contro ignoti con un rapporto finale di NOVANTASEI PAGINE. **Livello A**</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LA RETTIFICA SU GELLI, CHE VA NELLA DIREZIONE OPPOSTA ALLA VULGATA: la relazione afferma che il suo ruolo nei progetti del 1973-1974 «NON SEMBRA PERO ESSERE DI PRIMARIA IMPORTANZA come nel tentativo del ’70», poiche un congiurato riferisce che Gelli, PUR ESSENDO STATO FRA I PRIMI ADERENTI, ERA STATO NEGLI ANNI SUCCESSIVI EMARGINATO «PERCHE TROPPO POCO IDEALISTA E TROPPO ASSETATO DI POTERE E DI DENARO», e ne parla con disprezzo definendolo «un truffaldino» e «piu di tutto legato alla mafia». LA CENTRALITA DI GELLI E DUNQUE SPECIFICA DI UN PERIODO E CONTESTATA DA UN INTERNO</t>
+          <t>IL PRIMO FATTO NUOVO, NELLA SUA FORMA COMPIUTA: IL CASO FU ASSUNTO DALLA PROCURA FEDERALE PERCHE SI SOSPETTAVA UN GRUPPO, E FU CHIUSO SULLA TESI DELL’AUTORE SINGOLO. Fra le due qualificazioni non intervenne alcuna imputazione</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>IL NODO CRIMINE-EVERSIONE DELLA NOTTE DEL 7 DICEMBRE 1970: da un colloquio del 31 MAGGIO 1974 emerge «LA PRESENZA A ROMA, LA NOTTE DEL 7 DICEMBRE 1970 E NEI GIORNI IMMEDIATAMENTE PRECEDENTI, DI UN GRUPPO DI MAFIOSI SICILIANI INCARICATI DI ELIMINARE IL CAPO DELLA POLIZIA». Nel verbale un congiurato precisa: «qui c’era un’intesa, da quello che so, Drago-Micalizio, Mafia. Questi mafiosi avrebbero dovuto far fuori Vicari. A UN BEL MOMENTO NON AVEVANO LE ARMI PER FARLO FUORI». Il gruppo era alloggiato la notte fra il 6 e il 7 dicembre in una struttura che il giudice ritiene fosse un residence «OVE ALL’EPOCA ERA PIU FACILE NON ESSERE REGISTRATI»</t>
+          <t>IL SECONDO FATTO NUOVO, CHE MUTA IL PESO DELLA DISTRUZIONE DEI REPERTI. I 48 MOZZICONI rinvenuti nei portacenere dell’automobile delGUNDOLF KÖHLER, parcheggiata presso il luogo del fatto, ERANO DI 6 MARCHE DIVERSE, CON E SENZA FILTRO, E VI ERANO STATE RILEVATE TRACCE DI 3 GRUPPI SANGUIGNI DISTINTI. Furono DISTRUTTI NEL FEBBRAIO 1981, 6 mesi dopo l’attentato. NON SI TRATTAVA DUNQUE DI REPERTI GENERICI: ERANO L’UNICA TRACCIA MATERIALE DELLA PRESENZA DI PIU PERSONE NELL’AUTOVETTURA, ed erano incompatibili con la tesi che si sarebbe adottata</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>E IL COLLEGAMENTO CHE PROMUOVE LA TESTIMONIANZA SULLA CARTA NASCOSTA NEL VOLUME DI EVOLA: la notte del 7 dicembre sarebbe stato impartito, come afferma lo stesso ufficiale interessato, L’ORDINE DI MOBILITAZIONE DELLE STRUTTURE MISTE DI CIVILI E MILITARI DENOMINATE NUCLEI DI DIFESA DELLO STATO, costituite negli uffici informativi dell’Esercito con funzione di contrasto di moti comunisti. L’ordine sarebbe stato impartito PER RADIO, ATTRAVERSO I CODICI DEL PIANO DI MOBILITAZIONE; l’ufficiale ne CHIESE CONFERMA E LA OTTENNE, quindi si mosse, e RICEVETTE IL CONTRORDINE QUANDO AVEVA GIA RAGGIUNTO LE PORTE DI MILANO. Riscontri da due componenti della struttura, uno dei quali dichiarante gia dal 1974</t>
+          <t>IL TERZO FATTO NUOVO: da entrambi i rapporti risulta che GLI INQUIRENTI NON TROVARONO, NE NELL’ABITAZIONE NE NELL’AUTOVETTURA, ALCUNA TRACCIA DELL’ESPLOSIVO MILITARE IMPIEGATO NE DELLA COSTRUZIONE DELL’ORDIGNO. E L’ESITO ULTIMO: riaperto il 5 DICEMBRE 2014 su segnalazione di una testimone, il procedimento e stato nuovamente chiuso il 6 LUGLIO 2020 — ma in quella sede LA PROCURA FEDERALE HA ACCERTATO PER LA PRIMA VOLTA LA MOTIVAZIONE DI ESTREMA DESTRA, con la conseguenza giuridica che le vittime possono accedere all’indennizzo previsto per i colpiti da violenza estremistica. QUARANT’ANNI PER LA QUALIFICAZIONE, MAI PER I CORREI</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>Tomo I e Dominio 1 × 7 × 9 — 3 ACQUISIZIONI. PRIMA: l’opera non deve argomentare la tesi costituzionale, DEVE CITARLA, perche una relazione bicamerale la formula gia. SECONDA: la centralita di Gelli va periodizzata e la fonte contraria riportata. TERZA: il foglio con le legioni nascosto in un libro di Evola cessa di essere un aneddoto E DIVENTA UN INDIZIO, perche quella stessa struttura risulta destinataria di un ordine di mobilitazione. TUTTO IL BLOCCO E IN CONDIZIONALE NEGLI ATTI E VA CITATO IN CONDIZIONALE</t>
+          <t>Tomo II — TERMINE DI PARAGONE RAFFORZATO. La forma tedesca non e l’assenza di accertamento ma LA SUA INVERSIONE NEL TEMPO: sospetto di gruppo all’apertura, autore singolo alla chiusura, e quarant’anni dopo il riconoscimento della matrice senza alcun correo. E la distruzione dei reperti colpi precisamente cio che avrebbe potuto contraddire la tesi adottata</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
@@ -8976,42 +9520,42 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Peteano 1972 — CONFESSIONE, CONDANNA DEFINITIVA PER IL DEPISTAGGIO, E LA DICHIARAZIONE CHE VALE PER TUTTA L’OPERA</t>
+          <t>La vicenda giudiziaria dell’Italicus — L’UNICA CONDANNA RIGUARDA CHI TENTO DI ATTRIBUIRE LA STRAGE PRIMA CHE AVVENISSE</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 171-176; atti della Corte d’assise; sentenza della Corte d’assise d’appello di Venezia CONFERMATA DALLA CASSAZIONE NEL MAGGIO 1992. Testo gia nel corpus</t>
+          <t>Sentenze della Corte d’assise di Bologna, della Corte d’assise d’appello di Bologna e della prima sezione della Corte di cassazione; scheda del portale della memoria del Ministero della Cultura; ricostruzioni concordanti</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>LA DICHIARAZIONE DELL’AUTORE, CHE E IL CARDINE DELLA TESI COSTITUZIONALE. Vincenzo Vinciguerra, militante di Ordine Nuovo latitante dal 1974 prima in Spagna — dove aderi ad Avanguardia Nazionale — e poi in Argentina, costituitosi nel 1979, CONFESSO NEL 1984 ideazione ed esecuzione dell’attentato SENZA RIPUDIARE LE PROPRIE AZIONI E RIVENDICANDO LA QUALITA DI SOLDATO POLITICO. Dichiaro di confessare allo scopo di «fare chiarezza», AVENDO COMPRESO CHE TUTTE LE PRECEDENTI AZIONI DELLA DESTRA RADICALE, INCLUSE LE STRAGI, ERANO STATE IN REALTA MANOVRATE DA QUELLO STESSO REGIME CHE SI PROPONEVA DI ATTACCARE</t>
+          <t>LA CRONOLOGIA. Istruttoria conclusa il PRIMO AGOSTO 1980 — una fonte indica il 31 luglio, DISCREPANZA MINORE — cioe IL GIORNO PRECEDENTE LA STRAGE ALLA STAZIONE DI BOLOGNA, e il dato va riportato come coincidenza cronologica e NON come nesso, che nessuna sede ha accertato. 20 LUGLIO 1983: assoluzione per insufficienza di prove di MARIO TUTI, LUCIANO FRANCI e PIERO MALENTACCHI per il capo di strage. 18 DICEMBRE 1986 — una fonte indica il 18 settembre, DISCREPANZA MINORE: la corte d’appello annulla due assoluzioni e infligge due ergastoli a TUTI e FRANCI, assolvendo MALENTACCHI. 16 DICEMBRE 1987: la prima sezione della Corte di cassazione ANNULLA LE CONDANNE. 4 APRILE 1991: assoluzione con formula piena in sede di rinvio. 24 MARZO 1992: la Cassazione la rende definitiva</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>IL CONTROESEMPIO ALLA FORMA DEL FATTO ACCERTATO SENZA SANZIONE, ED E DEFINITIVO. La relazione lo qualifica «un fatto storico accertato E CONSACRATO IN GIUDICATI PENALI DI CONDANNA»: l’illecita copertura degli estremisti autori dell’attentato DA PARTE DI ALTI UFFICIALI DELL’ARMA, fra cui un colonnello CONDANNATO DALLA CORTE D’ASSISE D’APPELLO DI VENEZIA PER FALSO MATERIALE E IDEOLOGICO E PER SOPPRESSIONE DI PROVE, con decisione confermata dalla Cassazione. La Commissione annota l’aggravante: un ufficiale che DEPISTA L’INDAGINE SU UN ATTENTATO COSTATO LA VITA A 3 CARABINIERI</t>
+          <t>IL FATTO CHE VA POSTO IN PRIMA FILA, E CHE LE RICOSTRUZIONI COLLOCANO IN CODA: L’UNICA CONDANNA DIVENUTA IRREVOCABILE NELL’INTERA VICENDA GIUDIZIARIA DELL’ITALICUS E QUELLA PER CALUNNIA, A UN ANNO E 5 MESI, INFLITTA A FRANCESCO SGRÒ, CHE AVEVA DEPOSITATO PRIMA DEL FATTO L’ATTRIBUZIONE FALSA presso il direttore dell’Ispettorato antiterrorismo. 12 MORTI E 44 FERITI NON HANNO PRODOTTO ALCUNA CONDANNA; L’ATTRIBUZIONE FALSA SI. **Livello A**</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>LA PROVA CHE AVEVANO DALL’INIZIO: l’ordinovista ucciso nel conflitto a fuoco durante il dirottamento aereo di Ronchi dei Legionari ERA STATO TROVATO IN POSSESSO DELLA STESSA ARMA usata per sparare contro i vetri dell’automobile in cui era stata collocata la bomba, E I CUI BOSSOLI ERANO STATI REPERTATI DAI CARABINIERI STESSI. Ne discende la conclusione della relazione: la pista rossa subito imboccata «NON PUO GIUSTIFICARSI NEPPURE CON UNA VOLONTA DI TROVARE COMUNQUE IL COLPEVOLE, ANCHE A FINI DI IMMAGINE; emerge infatti chiaro L’INTENTO DELIBERATO DI STRUMENTALIZZARE UN EPISODIO E UNA CRIMINALIZZAZIONE DELLA SINISTRA EVERSIVA, SECONDO UN DISEGNO STRATEGICO PRECISO»</t>
+          <t>LA MOTIVAZIONE DEL GRADO D’APPELLO, POI ANNULLATA, DA REGISTRARE PERCHE ESISTE: la corte inquadro l’attentato come opera di «UN’ORGANIZZAZIONE DI ESTREMA DESTRA, VEROSIMILMENTE DI AREA ORDINOVISTA, LEGATA AD AMBIENTI GOLPISTI QUALI LA LOGGIA MASSONICA P2». L’annullamento fu pronunciato dalla prima sezione presieduta dal presidente CORRADO CARNEVALE, su richiesta del sostituto procuratore generale. DIVIETO ESPRESSO: nessuna inferenza va tratta da questa identificazione, che e riportata perche e un fatto processuale e non perche suggerisca alcunche</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>DUE ELEMENTI ULTERIORI, CON I RISPETTIVI GRADI. PRIMO, A VERBALE: in un drammatico confronto istruttorio un colonnello, accusato di aver indirizzato le indagini sulla pista rossa, replica «CHI LO HA INDIRIZZATO SULLA PISTA ROSSA? IO O LA VELINA DEL GENERALE PALUMBO? NON SI DIMENTICHI CHE IL GENERALE PALUMBO ERA ISCRITTO ALLA P2, SAREBBE ORA DI PARLARE DELL’ALTRA VELINA CHE BLOCCO L’INDAGINE A DESTRA» — per poi, TRINCERANDOSI DIETRO LA FACOLTA DI NON RISPONDERE, dichiarare di non sapere nulla di tale velina. SECONDO, GRADUATO DALLA RELAZIONE STESSA COME «CERTO, O ALMENO ESTREMAMENTE PROBABILE»: che il servizio militare conoscesse l’identita dei colpevoli fin dal 1972, come proverebbe — SECONDO LE SOLE DICHIARAZIONI DI VINCIGUERRA — la trasferta di un capitano a Padova pochi giorni dopo il dirottamento, con la frase «ORA BASTA FARE FESSERIE»</t>
+          <t>UNA DISCREPANZA CHE COINVOLGE UNA FONTE ISTITUZIONALE: il portale della memoria del Ministero della Cultura italiano colloca l’assoluzione definitiva NEL 1993, mentre tutte le altre fonti consultate indicano il 24 MARZO 1992. VA RISOLTA SULL’ATTO, e va segnalata perche una fonte pubblica statale che diverge di un anno su una sentenza definitiva e essa stessa un dato</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Tomo I — E IL CASO PIU FORTE DELL’INTERO CORPUS ITALIANO, ED E ANCHE IL CONTRAPPESO OBBLIGATORIO: dimostra che il depistaggio di Stato PUO ESSERE ACCERTATO E PUNITO IN VIA DEFINITIVA. Un’opera che sostenga l’impunita sistematica deve partire da qui, non aggirarlo</t>
+          <t>Dominio 7 e Dominio 10 — DUE ACQUISIZIONI. L’Italicus e fra le 9 stragi della direttiva del 2014 e resta senza colpevoli. E la forma che il repertorio registra decine di volte vi raggiunge la propria espressione piu netta: L’ORDINAMENTO HA PUNITO IL DEPISTAGGIO PREVENTIVO E NON LA STRAGE</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
@@ -9026,42 +9570,42 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>L’«organismo di sicurezza» sopra la Rosa dei Venti — LA DEFINIZIONE GIURIDICA DELLA TESI, IN UN MANDATO DI CATTURA</t>
+          <t>Fondo del servizio informativo brasiliano — INDIRIZZO ARCHIVISTICO ACCERTATO, DOCUMENTO NON RAGGIUNTO</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 177-186; mandato di cattura del giudice istruttore Giovanni Tamburino contro il capo del servizio militare; deposizione del colonnello Amos Spiazzi alla Commissione P2; deposizione di Ferruccio Parri alla Commissione d’inchiesta sul SIFAR, relazione di maggioranza pagine 554-557. Testo gia nel corpus</t>
+          <t>Archivo Nacional del Brasile, sede di Praça da República a Rio de Janeiro e sovrintendenza regionale del Distretto Federale; Centro di riferimento «Memórias Reveladas», istituito il 13 MAGGIO 2009 dalla Casa Civile della Presidenza della Repubblica</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>LA DEFINIZIONE, TESTUALE, DA UN ATTO GIUDIZIARIO: «UNA ORGANIZZAZIONE CHE, DEFINITA DI SICUREZZA, DI FATTO SI PONE COME OSTACOLO RISPETTO A DETERMINATE MODIFICAZIONI DELLA POLITICA INTERNA E INTERNAZIONALE, OSTACOLO CHE LIMITANDO LA SOVRANITA POPOLARE E REALIZZANDOSI CON MODALITA DI AZIONE ANORMALI, ILLEGALI, SEGRETE E VIOLENTE, CONFERISCE CARATTERE EVERSIVO ALL’ORGANIZZAZIONE STESSA». NON E EVERSIVA PERCHE VUOLE ROVESCIARE LO STATO: E EVERSIVA PERCHE IMPEDISCE MUTAMENTI LIMITANDO LA SOVRANITA POPOLARE. E l’asse costituzionale dell’opera, formulato da un giudice istruttore in un mandato di cattura</t>
+          <t>L’ESITO, DICHIARATO PER PRIMO: LA RICERCA NON HA RAGGIUNTO IL DOCUMENTO. Il fondo e stato localizzato, il regime di accesso accertato e la via di consultazione individuata, ma la citazione riferita da fonte secondaria sul consolidamento della struttura in Brasile RESTA NON RISCONTRATA. La consultazione richiede interrogazione della banca dati, non raggiungibile per via di ricerca generale</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>LA STRUTTURA A DUE LIVELLI: la Rosa dei Venti era organizzazione eversiva in senso stretto; L’ORGANISMO DI SICUREZZA LE STAVA STRUTTURALMENTE AL DI SOPRA ed era «qualcosa di molto piu istituzionale, ANCHE SE GIURIDICAMENTE INESISTENTE, dai fini non necessariamente eversivi». Aveva CARATTERE DI SOPRANAZIONALITA, coincideva in gran parte con LA STRUTTURA DEI VERTICI DEGLI UFFICI INFORMATIVI DELLE VARIE FORZE ARMATE, e agiva in assoluta segretezza IN COLLEGAMENTO CON LE FORZE ANALOGHE DEGLI ALTRI PAESI DELLA NATO. La relazione annota che «questo e l’aspetto piu delicato della vicenda, quello che probabilmente MISE IN MOTO IL PRECIPITOSO MECCANISMO DI AVOCAZIONE DELLE INDAGINI A ROMA»</t>
+          <t>L’INDIRIZZO, ORA PRECISO. Con decisione governativa del 2005 tutti i documenti pubblici relativi al periodo dal 1 APRILE 1964 AL 15 MARZO 1985, custoditi da persone, imprese e organi pubblici civili e militari, sono stati trasferiti all’Archivo Nacional, compresi i fondi del SERVIZIO NAZIONALE DI INFORMAZIONI, del Consiglio di sicurezza nazionale, della Commissione generale d’inchiesta e dei dipartimenti di ordine politico e sociale dei singoli Stati. Il complesso ammonta a CIRCA DICIASSETTE MILIONI E QUATTROCENTOMILA PAGINE di documentazione testuale, oltre a 220.000 microschede e 110 rulli di microfilm</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>LA QUALIFICAZIONE CHE L’OPERA DEVE CONSERVARE, PERCHE LIMITA LA TESI: lo scopo prioritario era impedire la conquista delle leve del potere da parte dei comunisti o piu in generale delle sinistre nei paesi NATO; i mezzi potevano comprendere «ANCHE, MA NON NECESSARIAMENTE, LO SPARGIMENTO DI SANGUE»; e per questo l’organismo «NON POTEVA ESSERE CONSIDERATO UN’ORGANIZZAZIONE EVERSIVA IN SENSO STRETTO, TENDENDO PIU A CONSERVARE LO STATUS QUO POLITICO CHE A SOVVERTIRLO». E STRUTTURA CONSERVATIVA, NON GOLPISTA: chi la descrive come macchina di colpi di Stato ne fraintende la funzione</t>
+          <t>LA VIA DI CONSULTAZIONE: banca dati «Memórias Reveladas» e sistema informativo dell’archivio nazionale, entrambi accessibili dal portale governativo; servizio all’utenza anche IN PRESENZA presso le due sedi. La rete cooperativa che alimenta la banca dati contava nel 2011 CINQUANTACINQUE enti partner, anche esteri</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>«ESIGENZA TRIANGOLO», E LA RETTIFICA A UNA VOCE PRECEDENTE DI QUESTO REPERTORIO. Verso le 21 del 7 DICEMBRE 1970 l’ufficiale ricevette dall’ufficio informativo del comando di reggimento un fonogramma: «ATTUATE ESIGENZA TRIANGOLO», che indicava l’impiego immediato di MILITARI SELEZIONATI IN BASE ALLA FEDE POLITICA. Destinazione: SESTO SAN GIOVANNI, «UNA DELLE ZONE DI MAGGIOR FORZA ELETTORALE DEL PARTITO COMUNISTA». Il contrordine giunse ALL’ALTEZZA DELLA STAZIONE DI AGRATE — non alle porte di Milano come registrato in precedenza — E TRASFORMAVA L’OPERAZIONE IN UNA SEMPLICE ESERCITAZIONE. Riscontro indipendente di continuita: la deposizione di Ferruccio Parri sul reclutamento, NEL 1964, di ex carabinieri e militari in congedo da impiegare in funzione di appoggio in caso di emergenza</t>
+          <t>L’ECCEZIONE DICHIARATA, CHE VA REGISTRATA PERCHE DELIMITA CIO CHE SI PUO TROVARE: il trasferimento del 2005 esclude i documenti «RIVELATORI DI INTIMITA DELLA VITA PRIVATA DELLE PERSONE E DI SEGRETEZZA IMPRESCINDIBILE PER LA SICUREZZA NAZIONALE». Esiste dunque una CATEGORIA RISERVATA, la cui consistenza non e dichiarata: un’assenza dal fondo NON PROVA un’assenza dal servizio</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>Tomo I e Metodologia — 3 ACQUISIZIONI. LA DEFINIZIONE DI TAMBURINO VA POSTA IN ESERGO ALL’OPERA. La qualificazione conservativa va conservata, perche rende la tesi piu difendibile e non piu debole. E IL CONTRORDINE CHE DECLASSA L’OPERAZIONE A ESERCITAZIONE E IL MECCANISMO DELLA SANATORIA GIA VISTO NEL 1956, applicato non a un accordo ma a una mobilitazione armata</t>
+          <t>Tomo Secondo — LA LACUNA BRASILIANA RESTA APERTA, MA CAMBIA STATUTO. Non e piu «esiste da qualche parte un fondo brasiliano»: e un indirizzo determinato, con volume, base giuridica, via di accesso ed eccezione dichiarata. E cio che una ricerca a distanza puo produrre, e va distinto da cio che solo la consultazione produrrebbe</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>verificato 4.8.2026</t>
+          <t>verificato 5.8.2026</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
@@ -9072,3018 +9616,6 @@
       </c>
       <c r="K83" s="8" t="inlineStr"/>
       <c r="L83" s="8" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Alto Adige — il caso Spiazzi a statuto irrisolto, e il fatto accertato di Amplatz e Klotz</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 185-187; deposizione alla Commissione P2; istruttoria della magistratura di Bolzano; deposizione resa al giudice istruttore di Venezia Mastelloni; intervista televisiva nella sesta puntata del 17 GENNAIO 1990. Testo gia nel corpus</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>L’AFFERMAZIONE. In servizio in quella regione nel momento di maggiore virulenza del terrorismo sudtirolese, l’ufficiale riferisce che UN SUPERIORE GLI CHIESE COME MAI NEL SETTORE DA LUI CONTROLLATO NON AVVENISSERO ATTENTATI; e alla sua replica «non e contento? non va bene?», gli fu risposto che «PER INTERESSI DI CARATTERE GLOBALE» cio non era un fatto positivo. Segue l’episodio: «IO HO TROVATO DUE CARABINIERI DEL SIFAR CHE STAVANO FACENDO UN ATTENTATO. LI HO PRESI, LI HO ARRESTATI, e mentre andavo verso Bolzano per consegnarli al comando di settore, MI SONO VENUTI INCONTRO CARABINIERI E POLIZIA, ME LI HANNO PRESI, ed il giorno dopo MI HANNO RISPEDITO A VERONA, ED HO CHIUSO CON L’ALTO ADIGE»</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>LO STATUTO E IRRISOLTO, E VA PRESENTATO COSI. Dopo la messa in onda dell’intervista la magistratura di Bolzano apri un’istruttoria E CONCLUSE CHE IL FATTO NARRATO «O ERA NON VERO O SI ERA VERIFICATO IN DATA DIVERSA DA QUELLA INDICATA». MA LA COMMISSIONE RILEVA CHE IL GIUDICE NON AVEVA POTUTO TENER CONTO, PER RAGIONI TEMPORALI, DI UNA SUCCESSIVA DEPOSIZIONE: quella di un maresciallo dei carabinieri in servizio prima al SIFAR e poi al SID, il quale davanti al giudice istruttore di Venezia CONFERMO L’EPISODIO, POICHE I DUE AGENTI ARRESTATI ERANO ALLE SUE DIPENDENZE. Affermazione, smentita giudiziaria, e riscontro sopravvenuto che la smentita non poteva considerare: NESSUNA DELLE 3 VA TACIUTA</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>LE PAROLE DELL’INTERVISTA, DA CITARE COME OPINIONE DEL DICHIARANTE E NON COME ACCERTAMENTO: «SONO FERMAMENTE CONVINTO CHE, COSI COME TANTI ALTRI FATTI GRAVI DEL NOSTRO PAESE, ANCHE IN ALTO ADIGE SI VOLEVA CREARE UN DETERMINATO CLIMA DI TENSIONE»; e, alla domanda se il terrorismo altoatesino fosse stato manovrato dai servizi segreti NON SOLTANTO ITALIANI: «SENZ’ALTRO E STATO MANOVRATO DA PARTI DEVIATE DEI SERVIZI O ADDIRITTURA DAI SERVIZI PER ORDINE DEI POLITICI»</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>E IL FATTO ACCERTATO, CHE E ASSAI PIU GRAVE DELL’EPISODIO CONTESTATO. La relazione scrive che, al di la del caso riferito dall’ufficiale, LA COMMISSIONE PARLAMENTARE ACCERTO FATTI DI INAUDITA GRAVITA, e ne cita uno: LA CONFERMA CHE L’UCCISIONE DI ALOIS AMPLATZ E IL FERIMENTO DI GEORG KLOTZ FURONO IL RISULTATO DI UN’OPERAZIONE CONCORDATA FRA POLIZIA, CARABINIERI E SERVIZI SEGRETI, CON IL PIENO AVALLO DEL POTERE POLITICO, CHE ERA STATO COSTANTEMENTE TENUTO AL CORRENTE</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Tomo I e Metodologia — ACQUISIZIONE CAPITALE: la Regola di ferro dei 3 piani vieta di passare dall’insabbiamento accertato al mandato asserito senza prova diretta. QUI IL PIANO DEL MANDATO E RAGGIUNTO DALL’ACCERTAMENTO STESSO, perche la Commissione scrive che il potere politico diede pieno avallo e fu costantemente informato. E il punto in cui la catena, che altrove si spezza sotto il vertice, NON SI SPEZZA</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr"/>
-      <c r="L84" s="8" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Ordine Nuovo, servizi italiani e rete informativa nelle basi NATO — e IL PASSAGGIO A EST DEGLI STESSI OPERATORI</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Archivio storico del Senato, Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, «Stragi e terrorismo in Italia dal dopoguerra al 1974», DATATO 22 GIUGNO 2000, pagine 141-149 su 245 complessive; fonti citate: ordinanza-sentenza Salvini pagine 316, 357 e 414 e seguenti, ordinanza Grassi pagina 199, interrogatori di Carlo Digilio del 27 NOVEMBRE 1993 e del 5 MAGGIO 1996</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMULAZIONE DELLA COMMISSIONE, CON LA SUA CAUTELA DA CONSERVARE: «IL LEGAME TRA ORDINE NUOVO, SERVIZI SEGRETI E RETE INFORMATIVA ALL’INTERNO DELLE BASI NATO — SOSTANZIALMENTE RIFERIBILE AGLI STATI UNITI — E IL NODO ATTORNO IL QUALE SI E SVILUPPATA, TRA IL 1969 E IL 1974, LA STRATEGIA DELLE STRAGI FASCISTE, O, SECONDO UNA DEFINIZIONE DIFFUSA E CERTAMENTE NON PRIVA DI FONDAMENTO, STRAGI DI STATO». La formula «definizione diffusa e non priva di fondamento» NON EQUIVALE AD ACCERTAMENTO e va citata per intero</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>LA QUALITA DEGLI INFORMATORI, CHE MODIFICA LA CATEGORIA: non semplici confidenti o provocatori, ma «VERI E PROPRI AGENTI INFO-OPERATIVI, I QUALI AGIVANO, CON MARGINI DI AUTONOMIA, RICEVENDO PRECISE ISTRUZIONI. AGENTI CHE SI SONO MOSSI SU SCALA INTERNAZIONALE»</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO CHE COMPLICA LA TESI BIPOLARE, E VA REGISTRATO PROPRIO PER QUESTO. Dal fascicolo del servizio militare intestato a un informatore inserito negli ambienti ordinovisti EMERGE CHE COSTUI AVEVA STABILITO CONTATTI IN CECOSLOVACCHIA «ANCHE A FINI DI ADDESTRAMENTO»; il collaboratore Digilio conferma viaggi continui di costui nei paesi dell’Est, SEGNATAMENTE IN ROMANIA E JUGOSLAVIA, pur dichiarando di non avere mai saputo dei suoi rapporti con il servizio. E ANCORA: uno dei capi della cosiddetta cellula americana AVEVA ORGANIZZATO UNA SERIE DI MISSIONI ALL’EST EUROPEO, ottenendo in Cecoslovacchia, PRESSO ELEMENTI CROATI IVI RESIDENTI, notizie tecniche sul trattamento delle leghe metalliche; e quel medesimo uomo era colui che, PER CONTO DELLA STRUTTURA NATO, MANTENEVA I CONTATTI CON GLI USTASCIA CROATI</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>CHE COSA QUESTO PROVA E CHE COSA NO. PROVA che gli stessi operatori attraversavano la linea dei blocchi per fini tecnici, addestrativi e organizzativi, e che la rete non coincideva con la geografia dell’alleanza. NON PROVA alcun coordinamento fra le due superpotenze: prova il contrario di una geometria pulita, cioe l’esistenza di CANALI INDIVIDUALI TRASVERSALI. L’opera che ne facesse una prova di convergenza USA-URSS forzerebbe il documento; l’opera che lo tacesse perche scomodo violerebbe la propria regola</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — E LA VERIFICA DELLA TESI DELL’AGIRE DI SPONDA SUL PIANO INTERNAZIONALE: attori europei che si servono simultaneamente di piu patroni, e non due patroni che si accordano sopra le loro teste</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr"/>
-      <c r="J85" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K85" s="8" t="inlineStr"/>
-      <c r="L85" s="8" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>LE MISSIONI A EST E LA DOMANDA LASCIATA APERTA DALLA COMMISSIONE — nodo capitale dell’opera</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Archivio storico del Senato, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 148-150; interrogatori di Carlo Digilio al giudice istruttore di Milano del 4 MAGGIO 1996 e al giudice istruttore di Venezia del 9 GENNAIO 1997; intervista televisiva del 1990; bibliografia indicata dalla Commissione: de Lutiis, «Storia dei servizi segreti in Italia», Editori Riuniti 1991, pagine 327-331, e Cipriani, «Lo spionaggio politico in Italia»</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>LA FRASE CHE VALE L’INTERA OPERA, TESTUALE: «POCO O NULLA SI CONOSCE SULLE EVENTUALI CONNIVENZE E/O CONVERGENZE DEI SERVIZI SEGRETI DEI DUE BLOCCHI PER MANTENERE FOCOLAI DI TENSIONE UTILI AL MANTENIMENTO DELLO STATUS QUO NELL’AMBITO DEI DUE DIVERSI SCHIERAMENTI». E la tesi bipolare, MA CON UN FINE DIVERSO E ASSAI PIU DIFENDIBILE: non impedire l’unificazione europea, BENSI CONSERVARE LA DISCIPLINA INTERNA DI CIASCUN BLOCCO. Cosi formulata NON RICHIEDE ALCUN COORDINAMENTO: bastano due interessi paralleli</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>E L’INVITO ESPLICITO, CHE E IL MANDATO DI QUEST’OPERA: «occorre sottolineare come UN APPROFONDIMENTO A PARTE MERITEREBBE LA VICENDA DELLE MISSIONI AD EST, partendo proprio dall’ENORME MATERIALE FORNITO da Brenneke al giornalista Remondino, A SUO TEMPO LIQUIDATO COME POCO RILEVANTE SIA IN SEDE POLITICA CHE DALL’AUTORITA GIUDIZIARIA»</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>IL CASO BRENNEKE, A STATUTO CONTESO. L’ex agente statunitense a contratto, con base nel Nord-Est, intervistato nel 1990 sostenne DI ESSERSI RECATO PIU VOLTE A PRAGA PER CONTO DEL SERVIZIO AMERICANO A RIFORNIRSI DI ARMI ED ESPLOSIVI destinati agli arsenali del terrorismo filoatlantico e dei gruppi neofascisti vicini alla loggia. La vicenda fu ritenuta poco credibile anche per «UNA A DIR POCO BUROCRATICA SMENTITA DELLE AUTORITA STATUNITENSI» sulla sua appartenenza all’intelligence. MA DIGILIO HA CONFERMATO che CARRETT gli disse che «uno dei soggetti impiegati in operazioni speciali nel Nord-Est italiano per la loro struttura era tale Richard Brenneke, CHE AVEVA FATTO SERVIZIO IN PARTICOLARE A TRIESTE E NEL FRIULI FINO AL 1974». NOTA DI CAUTELA ESTERNA: l’attendibilita complessiva di quel dichiarante e stata contestata in altre sedi e su altre vicende; il riscontro qui vale per la sola presenza operativa</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>L’AVVERTIMENTO METODOLOGICO CHE LA COMMISSIONE RIVOLGE A CHI SCRIVE DI QUESTI FATTI: l’operativita degli informatori nell’Est europeo, nei campi d’addestramento e nel traffico d’armi «DOVREBBE INDURRE A MAGGIOR PRUDENZA COLORO I QUALI RITENGONO, IN MANIERA FIN TROPPO SEMPLICISTICA, CHE LA SOLA PRESENZA DI UN’ARMA PROVENIENTE DA EST STIA A INDICARE IN MANIERA CATEGORICA LE RESPONSABILITA DEGLI APPARATI DI QUEI PAESI». Si aggiunga il triangolo geografico documentato: l’uomo che per conto della struttura NATO teneva i contatti con gli ustascia ATTIVI IN JUGOSLAVIA E CECOSLOVACCHIA li teneva anche con i FUORIUSCITI CON BASE A VALENCIA, NELLA SPAGNA FRANCHISTA</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — 3 CONSEGUENZE. PRIMA: la tesi bipolare va riformulata come la formula la Commissione, cioe come CONSERVAZIONE DELLO STATUS QUO DI CIASCUN BLOCCO, e cosi diventa sostenibile. SECONDA: l’opera ha un mandato scritto da un organo dello Stato, e deve dichiararlo. TERZA: l’avvertimento sulla provenienza delle armi VA CITATO NEL TESTO, perche e l’inferenza che la letteratura del genere compie piu spesso e che la Commissione dichiara semplicistica</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr"/>
-      <c r="J86" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K86" s="8" t="inlineStr"/>
-      <c r="L86" s="8" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Interferenza russa nelle elezioni statunitensi del 2016 — rapporto del procuratore speciale (2019) e quinto volume della Commissione ristretta del Senato sull’intelligence (18 AGOSTO 2020) — STATUTO ESATTO</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Stati Uniti; il quinto volume, intitolato «Russian efforts to influence the Trump Campaign and the 2016 election», consta di 9606 PAGINE, fondate su centinaia di audizioni e oltre un milione di documenti, ed e frutto di un’indagine bipartisan durata piu di 3 anni. Entrambi i testi sono pubblicamente consultabili</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>CIO CHE E ACCERTATO. Che il presidente della Federazione Russa ORDINO L’OPERAZIONE di violazione delle reti e degli account collegati al partito avversario e la diffusione di materiale dannoso per la candidata. Che il capo della campagna elettorale lavorava strettamente con un cittadino russo CHE LA COMMISSIONE DEFINISCE SENZA ESITAZIONI «UN UFFICIALE DELL’INTELLIGENCE RUSSA», operante come tramite con un oligarca. Che in numerose occasioni EGLI GLI TRASMISE DATI INTERNI DI SONDAGGIO E STRATEGIA DI CAMPAGNA. E la conclusione testuale: quel livello di accesso e quella disponibilita a condividere informazioni «RAPPRESENTARONO UNA GRAVE MINACCIA CONTROSPIONISTICA»</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>DOVE LA CATENA SI SPEZZA, ED E LA FORMA RICORRENTE DI QUESTO REPERTORIO. LA COMMISSIONE NON E RIUSCITA A DETERMINARE PERCHE quei dati fossero trasmessi NE CHE COSA IL DESTINATARIO NE ABBIA FATTO, in parte per l’uso di messaggistica cifrata. Ottenne «alcune informazioni» secondo cui costui «POTREBBE ESSERE STATO COLLEGATO» all’operazione di sottrazione e diffusione della corrispondenza — E QUELLA SEZIONE E IN LARGA PARTE ESPUNTA. Un senatore chiese in calce la declassificazione, osservando che il testo contiene informazioni espunte DIRETTAMENTE RILEVANTI PER L’INTERFERENZA NELL’ELEZIONE SUCCESSIVA</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>CIO CHE NON E ACCERTATO, E VA SCRITTO CON LA STESSA EVIDENZA. Il procuratore speciale concluse DI NON AVER IDENTIFICATO PROVE DI UN NESSO fra la condivisione dei dati e l’interferenza, e DI NON AVER STABILITO che vi fosse stato coordinamento con il governo russo sulle attivita di interferenza. E LO STESSO RAPPORTO BIPARTISAN HA PRODOTTO DUE LETTURE OPPOSTE DAI PROPRI MEMBRI: il presidente pro tempore dichiaro che la commissione non trovo «assolutamente alcuna prova» di collusione, pur avendo trovato prove «irrefutabili» di ingerenza russa; 5 MEMBRI DI MINORANZA SCRISSERO IN APPENDICE che «questo e l’aspetto che ha la collusione». Il difensore dell’interessato defini le conclusioni «pura congettura»</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>REGOLA D’USO PER L’OPERA, TASSATIVA. NON PUO ESSERE CERTIFICATA L’ESISTENZA DI UN «ASSE», perche il termine designa un allineamento strategico volontario che i due rapporti NON STABILISCONO. Cio che si certifica e altro e basta: interferenza ordinata al vertice, contatti estesi, trasmissione di dati interni a un ufficiale dell’intelligence avversaria, GRAVE MINACCIA CONTROSPIONISTICA ACCERTATA IN SEDE BIPARTISAN, e IMPOSSIBILITA DICHIARATA DI RISALIRE OLTRE. L’allineamento politico odierno e materia politica contesa e NON VA TRATTATO COME FATTO DOCUMENTATO</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia e Tomo II — E IL PATTERN DEL REPERTORIO APPLICATO AL PRESENTE: fatto accertato, catena interrotta appena sotto il vertice, sezione decisiva espunta, e due letture opposte del medesimo atto. Scritto in questa forma e inattaccabile; scritto come «asse certificato» cade alla prima obiezione</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I87" s="3" t="inlineStr"/>
-      <c r="J87" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="8" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Il caso Metropol — 18 ottobre 2018, e il decreto di archiviazione del 27 APRILE 2023 — STATUTO ESATTO</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Procura della Repubblica di Milano, ipotesi di corruzione internazionale, fascicolo aperto nel luglio 2019; richiesta di archiviazione dell’aggiunto e di due sostituti; DECRETO DEL GIUDICE PER LE INDAGINI PRELIMINARI DI MILANO DEL 27 APRILE 2023. Origine: registrazione effettuata da uno dei presenti e da lui consegnata a giornalisti, pubblicata da un sito statunitense e da un settimanale italiano</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>L’EPISODIO. Il 18 OTTOBRE 2018, 24 ORE DOPO UNA VISITA DEL LEADER DEL PARTITO NELLA CAPITALE RUSSA, 6 persone — 3 italiane e 3 russe — si incontrano all’hotel Metropol di Mosca. Oggetto: la vendita di circa 3 MILIONI DI TONNELLATE DI CARBURANTE da una compagnia petrolifera russa a una compagnia italiana, con una quota stimata in SESSANTACINQUE MILIONI DI DOLLARI destinata alle casse del partito per la campagna europea. Nella registrazione una voce attribuita al presidente dell’associazione bilaterale afferma: «NOI VOGLIAMO CAMBIARE L’EUROPA. UNA NUOVA EUROPA DEVE ESSERE VICINA ALLA RUSSIA, COME ERA PRIMA, PERCHE NOI VOGLIAMO LA NOSTRA SOVRANITA»</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>CIO CHE IL DECRETO ACCERTA, PUR ARCHIVIANDO: che L’OBIETTIVO ERA IL FINANZIAMENTO MA NON FU RAGGIUNTO; che vi fu, secondo i pubblici ministeri, UNA «PROVA GENERALE», e che l’affare da un miliardo e mezzo di dollari NON ANDO IN PORTO. E soprattutto, DAGLI ATTI: il ruolo nell’operazione del teorico eurasiatista, il quale — RICOSTRUISCONO I PUBBLICI MINISTERI — PARTECIPO «ALLA TRATTATIVA PER LA VENDITA» DI PETROLIO IN RAPPRESENTANZA «DI ALTI ESPONENTI DELL’ESTABLISHMENT RUSSO». Emergono inoltre agli atti contatti fra gli indagati e il leader del partito, CHE NON ERA INDAGATO</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE LA CATENA SI E INTERROTTA, ED E IL PUNTO CHE FA DI QUESTA LA VOCE SPECULARE DI QUELLA STATUNITENSE: nessuno degli interlocutori russi sarebbe stato pubblico ufficiale — presupposto del reato contestato — e IL DINIEGO ALLE ROGATORIE HA DI FATTO IMPEDITO DI RISALIRE A POSSIBILI VERTICI SOPRA DI LORO. Nel caso americano la catena si spezza per messaggistica cifrata ed espunzioni; QUI PER RIFIUTO DI COOPERAZIONE GIUDIZIARIA DA PARTE DELLO STATO INTERESSATO. In entrambi i casi il vertice non e irraggiungibile per assenza di indizi: E RESO IRRAGGIUNGIBILE</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>LE NEGAZIONI, DA RIPORTARE. Il leader del partito: «mai preso un rublo, un euro, un dollaro o un litro di vodka di finanziamento dalla Russia». Il principale indagato dichiaro a un’emittente europea CHE UN INCONTRO SIMILE NON ERA MAI AVVENUTO, aggiungendo pero di essersi recato in quell’albergo per incontrare imprenditori locali: LA CONTRADDIZIONE VA REGISTRATA, NON RISOLTA DALL’AUTORE. Un difensore ha definito l’intera vicenda infondata. NESSUNA CONDANNA E STATA PRONUNCIATA E L’ARCHIVIAZIONE E DEFINITIVA</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Metodologia — VOCE SPECULARE OBBLIGATORIA. Chi registra il caso statunitense e tace questo, o viceversa, sta scegliendo un versante. LE DUE VOCI VANNO LETTE INSIEME: due indagini su due versanti opposti, entrambe accertano contatti e obiettivo, entrambe si fermano sotto il vertice, e in entrambe CIO CHE MANCA NON E LA PROVA MA LA VIA PER ARRIVARCI</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr"/>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K88" s="8" t="inlineStr"/>
-      <c r="L88" s="8" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Relazione del Comitato parlamentare per la sicurezza della Repubblica sull’attivita febbraio-agosto 2022 — APPROVATA ALL’UNANIMITA</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Italia; relazione trasmessa al Parlamento nell’agosto 2022, anticipata rispetto al documento annuale a causa dello scioglimento anticipato delle Camere; approvata ALL’UNANIMITA dall’organo la cui presidenza spetta per legge all’opposizione</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>CIO CHE IL COMITATO ACCERTA: «il montaggio e la diffusione di fake news, le campagne social e l’utilizzo dei troll si affermano quali STRUMENTI SOFISTICATI E PERVASIVI DI INFLUENZA DA PARTE DELLA RUSSIA, MA ANCHE DA PARTE DI ALTRI ATTORI STATUALI» — nominando anche la Cina — «rischiando di inquinare e distorcere il dibattito pubblico italiano e quello dei Paesi occidentali». Sul meccanismo: la propaganda «si avvale di AGENZIE DI STAMPA ONLINE CONTROLLATE che pubblicano i propri contenuti in diverse lingue, compreso l’italiano, con DECINE DI MILIONI DI VISUALIZZAZIONI, NELLA MAGGIOR PARTE DEI CASI DEL PUBBLICO PIU GIOVANE»; sono «siti di cui SONO IGNOTI I SOSTENITORI E LE FONTI DI FINANZIAMENTO», i cui contenuti «rimbalzano presso taluni siti italiani, MOLTIPLICANDO L’ONDA MALEVOLA»</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>L’AUTOVALUTAZIONE DELLO STATO SU SE STESSO, CHE E LA PARTE PIU UTILE: in Italia si ravvisa «UNA SOSTANZIALE DEBOLEZZA DEGLI INTERVENTI PER IL CONTRASTO ALLA DISINFORMAZIONE E ALLE DIVERSE FORME DI INGERENZA. UN CHIARO DEFICIT E RITARDO DEL NOSTRO PAESE RISPETTO AD IMPEGNI, STRUMENTI, STRATEGIE E MISURE CHE DA DIVERSO TEMPO SONO GIA OPERATIVI TANTO NEL CONTESTO INTERNAZIONALE». E la conclusione: «E QUINDI ORMAI NON PIU RINVIABILE UN MAGGIORE IMPEGNO DEL NOSTRO PAESE, anche non escludendo possibili interventi di ordine legislativo e normativo». Il Comitato avverte inoltre sui RAPPORTI FRA PARTITI ED ESPONENTI POLITICI ITALIANI E CONTROPARTI RUSSE, richiamando la risoluzione del Parlamento europeo del 9 MARZO 2022, frutto di un’indagine durata un anno e mezzo</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>IL RITROVAMENTO CHE RIGUARDA DIRETTAMENTE QUEST’OPERA: la relazione da conto di DUE INDAGINI DEL COMITATO RIMASTE INCOMPIUTE PER LO SCIOGLIMENTO ANTICIPATO DELLE CAMERE. LA PRIMA E QUELLA «SULLE MODALITA DI ATTUAZIONE DELLA DESECRETAZIONE DEGLI ATTI PER UNA MIGLIORE CONSERVAZIONE E ACCESSIBILITA DEI DOCUMENTI». LA SECONDA E QUELLA «SULLE FORME DI DISINFORMAZIONE E DI INGERENZA STRANIERE». Le due inchieste parlamentari piu direttamente pertinenti a questo lavoro SONO STATE ENTRAMBE INTERROTTE NELL’AGOSTO 2022</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>CONTESTO DA REGISTRARE CON CAUTELA: il 18 agosto 2022, alla vigilia della riunione conclusiva, un alto esponente russo INVITO PUBBLICAMENTE «GLI EUROPEI A PUNIRE I PROPRI GOVERNI NELLE URNE», con riferimento ritenuto rivolto alle elezioni italiane imminenti. E DICHIARAZIONE PUBBLICA, NON OPERAZIONE COPERTA, e va citata come tale</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Tomo III — CHIUDE IL TRIANGOLO DELLE 3 SEDI: commissione bipartisan statunitense, magistratura milanese, organo parlamentare italiano. Tutte e 3 accertano influenza e contatti; NESSUNA RAGGIUNGE UN VERTICE; e nella terza L’INCHIESTA STESSA SI INTERROMPE. Il deficit dichiarato dall’organo di controllo e inoltre IL RISCONTRO ISTITUZIONALE della doglianza dei familiari delle vittime sul mancato versamento: DUE ORGANI DIVERSI, LA STESSA LACUNA</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr"/>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K89" s="8" t="inlineStr"/>
-      <c r="L89" s="8" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Risoluzione del Parlamento europeo del 9 MARZO 2022 sulle ingerenze straniere nei processi democratici dell’Unione, e la serie successiva</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Relazione finale della commissione speciale INGE, documento A9-0022/2022, testo approvato TA-9-2022-0064; seguono la risoluzione del 1° GIUGNO 2023 (relazione finale della commissione INGE2), la risoluzione del 15 DICEMBRE 2022 sulla sospetta corruzione da parte di uno Stato terzo, quella del 13 LUGLIO 2023 sulla riforma delle norme in materia di trasparenza e integrita, la decisione del 13 SETTEMBRE 2023 di modifica del regolamento, e le proposte del 2024 sulle ingerenze nell’attivita del Parlamento stesso</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO DEL VOTO E LA CONCLUSIONE: 5150DUE FAVOREVOLI, OTTANTUNO CONTRARI, SESSANTA ASTENUTI. Il testo conclude che in Europa esiste UNA «LARGA IMPREPARAZIONE» sulla gravita della minaccia rappresentata dai regimi autocratici stranieri, in particolare Russia e Cina</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>IL PASSAGGIO CHE CONFERMA LA TASSONOMIA A DUE ASSI, E VA CITATO NELLA SUA INTEREZZA: la relazione «CONDANNA IL FATTO CHE I PARTITI ESTREMISTI, POPULISTI, ANTIEUROPEI E ALCUNI ALTRI PARTITI E INDIVIDUI ABBIANO LEGAMI E SIANO ESPLICITAMENTE COMPLICI NEI TENTATIVI DI INTERFERIRE NEI PROCESSI DEMOCRATICI DELL’UNIONE». LA FORMULA «E ALCUNI ALTRI PARTITI E INDIVIDUI» E DECISIVA: IL PARLAMENTO EUROPEO NON CIRCOSCRIVE IL FENOMENO A UNA FAMIGLIA POLITICA. Riscontro ulteriore: al testo votarono a favore anche delegazioni nazionali di area conservatrice</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>IL RIMEDIO PROPOSTO, CHE E LA RISPOSTA NORMATIVA ALLO SCHEMA DOCUMENTATO NEL CASO MOSCOVITA DEL 2018: «VIETARE DONAZIONI E FINANZIAMENTI A PARTITI, FONDAZIONI E AGLI ESPONENTI POLITICI CHE RICOPRONO CARICHE PUBBLICHE O ELETTIVE DA PARTE DI POTENZE STRANIERE» EXTRAEUROPEE. E la risoluzione del 2024 aggiunge che «CONTINUANO A EMERGERE PROVE DI INGERENZE RUSSE NEI PERIODI PRECEDENTI A TUTTE LE PRINCIPALI ELEZIONI NAZIONALI ED EUROPEE», chiedendo «UN’INDAGINE INTERNA APPROFONDITA» sui possibili casi di ingerenza E SULLA CONDOTTA SCORRETTA DEI PROPRI DEPUTATI</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>DA REGISTRARE CON MISURA: secondo un’indagine di opinione del marzo 2023 i cittadini collocano fra le principali sfide ai sistemi democratici le informazioni false in rete, la propaganda da fonti straniere non democratiche E LE INGERENZE OCCULTE «ANCHE ATTRAVERSO IL FINANZIAMENTO DI ATTORI NAZIONALI». E PERCEZIONE, NON ACCERTAMENTO, e va citata come tale</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Apparato — CHIUDE IL QUADRILATERO ISTITUZIONALE: commissione bipartisan statunitense, magistratura italiana, comitato parlamentare italiano, Parlamento europeo. E FORNISCE LA CONFERMA EMPIRICA DELLA TASSONOMIA: il fenomeno e condannato senza essere attribuito a una famiglia politica, e la stessa risoluzione e votata anche da chi a quelle famiglie e contiguo. LA POSIZIONE ECCEZIONALISTA E RICORRENTE, NON EREDITARIA</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I90" s="3" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K90" s="8" t="inlineStr"/>
-      <c r="L90" s="8" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Le due fratture massoniche politicamente rilevanti — 1877 e 1908 — E LA MAPPATURA DA SCARTARE</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Fonti: atti dell’Assemblea generale del Grande Oriente di Francia del 1877 e rifacimento dei rituali del 1886; storiografia sulla scissione italiana del giugno 1908 e sul Supremo Consiglio d’Italia; letteratura sulla massoneria continentale e sulle obbedienze italiane</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>MAPPATURA DA SCARTARE, PERCHE VERIFICATA E CONTRARIA: lo scisma inglese fra Antients e Moderns del 17 LUGLIO 1751 NON E UNA FRATTURA FRA COSTITUZIONALISMO E IMPERIALISMO. Le divergenze accertate sono LITURGICHE E SOCIALI — l’Arco Reale come parte integrante o appendice facoltativa, l’uso dei Diaconi, le costituzioni di Dermott derivate da quelle irlandesi contro il libro di Anderson — e la nuova obbedienza nacque «sulle stesse tensioni religiose e di classe che sostennero il successo del metodismo contro la Chiesa d’Inghilterra». LA DIREZIONE E ROVESCIATA: furono gli Antients, partito irlandese e plebeo, ad accusare i Moderns di ESCLUSIVITA ELITARIA e di aver diluito l’eredita operativa in una societa di gentiluomini. L’unione del 27 DICEMBRE 1813 avvenne sotto un figlio del re e adotto in prevalenza i riti degli Antients</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>LA PRIMA FRATTURA POLITICAMENTE RILEVANTE E DEL 1877: l’Assemblea generale del Grande Oriente di Francia decise DI SOPPRIMERE IL PRECETTO FINO AD ALLORA PROCLAMATO COME PRINCIPIO FONDAMENTALE, LA CREDENZA IN DIO E NELL’IMMORTALITA DELL’ANIMA; furono poi eliminati dal rito tutti i riferimenti al Grande Architetto e rimosso il Volume della Legge Sacra, CON CONSEGUENTE SEPARAZIONE DALLA GRAN LOGGIA DI LONDRA. I nuovi rituali giunsero solo NEL 1886, «perche furono molte le resistenze da vincere». Ne deriva la divisione permanente fra obbedienze REGOLARI, anglo-americane, teiste e per statuto apolitiche, e obbedienze LIBERALI O ADOGMATICHE, continentali, che ammettono atei e agnostici e CHE NON RINUNCIANO A UN’AZIONE POLITICA IN FAVORE DEI DIRITTI DELL’UOMO E DELLA DEMOCRAZIA</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA E ITALIANA, ED E UN EVENTO DEL PRIMO ASSE IN FORMA PURA. Nel GIUGNO 1908 — le fonti indicano il 24 o il 26: DISCREPANZA DA RISOLVERE — si consuma nel Supremo Consiglio d’Italia la scissione che origina l’obbedienza poi detta di Piazza del Gesu. LA CAUSA ACCERTATA: LA DECISIONE DEL GRANDE ORIENTE D’ITALIA DI IMPORRE AI FRATELLI PARLAMENTARI UN VOTO CONTRARIO ALL’INSEGNAMENTO RELIGIOSO NELLE SCUOLE. Il sovrano gran commendatore del Rito scozzese, definito FORTE OPPOSITORE DELLA POLITICIZZAZIONE FORZATA, pose il veto formale alla proposta di censura, e la nuova obbedienza fu costituita ESPRESSAMENTE «PER IL PRINCIPIO FONDAMENTALE MASSONICO DELLA LIBERTA DI COSCIENZA»</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE QUESTO EPISODIO VALE PIU DELL’INTERA GENEALOGIA SETTECENTESCA: un’obbedienza che pretende di VINCOLARE IL VOTO DI PARLAMENTARI ELETTI compie esattamente cio che la prova della riserva individua — determinare un esito fuori dalla procedura elettorale. E CHI SI SCISSE LO FECE CON ARGOMENTO COSTITUZIONALE. LA POLARITA E DUNQUE ROVESCIATA rispetto all’ipotesi corrente, che assegna al ramo scozzese e tradizionale la posizione anticostituzionale</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 e Apparato — LA MASSONERIA E UN LUOGO DOVE LA FAGLIA PASSA, NON LA SUA SORGENTE. Dopo il 1813 le obbedienze regolari vietano per statuto la discussione politica in loggia, il che rende la categoria un pessimo predittore. Le logge coperte contano in quest’opera NON PERCHE MASSONICHE MA PERCHE IRREGOLARI, OCCULTE E TRASVERSALI AI DOMINI: falliscono la prova della riserva, non discendono da uno scisma</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I91" s="3" t="inlineStr"/>
-      <c r="J91" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K91" s="8" t="inlineStr"/>
-      <c r="L91" s="8" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Articolo 18 della Costituzione e legge 25 GENNAIO 1982 numero 17 — L’ANCORAGGIO COSTITUZIONALE DELL’OPERA, E LA SUA RIDUZIONE</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Italia; legge pubblicata nella Gazzetta Ufficiale, serie generale numero 27, del 28 GENNAIO 1982, con rubrica «Norme di attuazione dell’articolo 18 della Costituzione in materia di associazioni segrete e scioglimento della associazione denominata Loggia P2»; emanata a seguito della conclusione dei lavori della Commissione parlamentare d’inchiesta</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>LA NORMA COSTITUZIONALE: «I cittadini hanno diritto di associarsi liberamente, senza autorizzazione, per fini che non sono vietati ai singoli dalla legge penale. SONO PROIBITE LE ASSOCIAZIONI SEGRETE E QUELLE CHE PERSEGUONO, ANCHE INDIRETTAMENTE, SCOPI POLITICI MEDIANTE ORGANIZZAZIONI DI CARATTERE MILITARE». Il secondo comma reca UNA PROIBIZIONE DUPLICE E DISGIUNTA, e adopera il termine «proibizione» riferito anche alla persecuzione INDIRETTA della finalita vietata</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>LA DEFINIZIONE DI LEGGE, ARTICOLO PRIMO, CHE DESCRIVE LA LOGGIA COPERTA IN TERMINI GIURIDICI: sono segrete le associazioni che, ANCHE ALL’INTERNO DI ASSOCIAZIONI PALESI, occultando la loro esistenza ovvero tenendo segrete congiuntamente finalita e attivita sociali ovvero RENDENDO SCONOSCIUTI, IN TUTTO O IN PARTE E ANCHE RECIPROCAMENTE, I SOCI, SVOLGONO ATTIVITA DIRETTA A INTERFERIRE SULL’ESERCIZIO DELLE FUNZIONI DI ORGANI COSTITUZIONALI, di amministrazioni pubbliche anche ad ordinamento autonomo, di enti pubblici anche economici, nonche di servizi pubblici essenziali di interesse nazionale. SANZIONI: da uno a 5 anni per chi promuove, dirige o fa proselitismo, con interdizione quinquennale dai pubblici uffici; fino a due anni per chi partecipa. ARTICOLO TERZO: accertata con SENTENZA IRREVOCABILE la costituzione dell’associazione, il Presidente del Consiglio ne ordina con decreto LO SCIOGLIMENTO E LA CONFISCA DEI BENI; e in ogni stato e grado, se vi e pericolo nel ritardo, puo essere disposta in camera di consiglio LA SOSPENSIONE CAUTELARE DI OGNI ATTIVITA ASSOCIATIVA</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>LA RIDUZIONE, CHE E IL FATTO PIU IMPORTANTE DI QUESTA VOCE. La Costituzione proibisce le associazioni segrete TOUT COURT, a prescindere dalla loro azione. LA MODIFICA INTRODOTTA IN SEDE PARLAMENTARE ALLA LEGGE DI ATTUAZIONE VIETO LE SOLE ASSOCIAZIONI SEGRETE CHE PERSEGUONO FINI ILLECITI, «RENDENDO IN QUESTO MODO LA SEGRETEZZA UN CARATTERE DI PER SE LEGITTIMO». La dottrina costituzionalistica conferma che la definizione «ATTUA SOLO IN PARTE IL DETTATO COSTITUZIONALE». Ne discende una conseguenza processuale diretta: dopo quella modifica NON BASTA PROVARE LA SEGRETEZZA, OCCORRE PROVARE L’INTERFERENZA — ed e esattamente il requisito la cui mancata prova ha condotto all’assoluzione registrata altrove in questo repertorio</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>IL SEGUITO, ANCORA APERTO: nel LUGLIO 2018 e stato depositato un disegno di legge in materia di incompatibilita fra cariche e partecipazione ad associazioni che comportino VINCOLO DI OBBEDIENZA, al termine di un dibattito «SOSTANZIALMENTE INIZIATO DURANTE L’ITER DI APPROVAZIONE DELLA LEGGE STESSA». Va inoltre registrato che in sede costituente NON SI PREVIDE ALCUN REGIME GENERALE DI PUBBLICITA DELLE ASSOCIAZIONI che qualificasse come segrete quelle che vi si sottraessero</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 e Tomo III — E L’ANCORAGGIO COSTITUZIONALE DELL’INTERA OPERA E INSIEME IL SUO CASO ESEMPLARE. LA NORMA CHE DOVEVA ATTUARE IL DIVIETO LO HA RISTRETTO, E LA RESTRIZIONE HA PRODOTTO L’ASSOLUZIONE. E la stessa figura gia registrata per la prima proposta del 1984: la disposizione attuativa che si muove in direzione contraria alla fonte che dichiara di attuare</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr"/>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr"/>
-      <c r="L92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>La posizione dottrinale della Santa Sede sulla massoneria — SERIE COMPLETA, E IL RIFIUTO ESPRESSO DELLA DISTINZIONE FRA OBBEDIENZE</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Notificazione ai presidenti delle conferenze episcopali del 19 LUGLIO 1974; Dichiarazione del 17 FEBBRAIO 1981 (AAS 73/1981, pagine 240-241); DICHIARAZIONE «QUAESITUM EST» DEL 26 NOVEMBRE 1983, firmata dal prefetto Joseph Ratzinger e dal segretario Jerome Hamer, APPROVATA DA GIOVANNI PAOLO II, in AAS LXXVI (1984) pagina 300; articolo non firmato su L’Osservatore Romano del 23 FEBBRAIO 1985; linee guida della Conferenza episcopale italiana del 2003; RISPOSTA DEL DICASTERO PER LA DOTTRINA DELLA FEDE DEL 13 NOVEMBRE 2023, a firma del prefetto Victor Fernandez, APPROVATA DA PAPA FRANCESCO</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>L’OCCASIONE E IL TESTO. Fu chiesto se il giudizio della Chiesa fosse mutato per il fatto che il nuovo Codice del 1983 non menziona espressamente la massoneria come il precedente; la risposta e che si tratta di UN CRITERIO REDAZIONALE seguito anche per altre associazioni «in quanto comprese in categorie piu ampie». E dunque: «RIMANE PERTANTO IMMUTATO IL GIUDIZIO NEGATIVO DELLA CHIESA NEI RIGUARDI DELLE ASSOCIAZIONI MASSONICHE, POICHE I LORO PRINCIPI SONO STATI SEMPRE CONSIDERATI INCONCILIABILI CON LA DOTTRINA DELLA CHIESA E PERCIO L’ISCRIZIONE A ESSE RIMANE PROIBITA. I FEDELI CHE APPARTENGONO ALLE ASSOCIAZIONI MASSONICHE SONO IN STATO DI PECCATO GRAVE E NON POSSONO ACCEDERE ALLA SANTA COMUNIONE». La Dichiarazione vale come interpretazione autentica del canone 1374, che punisce chi si iscrive ad associazione che cospira contro la Chiesa</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>IL PUNTO DECISIVO, CHE CORREGGE OGNI LETTURA FONDATA SULLA DISTINZIONE FRA OBBEDIENZE REGOLARI E LIBERALI: «NON COMPETE ALLE AUTORITA ECCLESIASTICHE LOCALI DI PRONUNCIARSI SULLA NATURA DELLE ASSOCIAZIONI MASSONICHE CON UN GIUDIZIO CHE IMPLICHI DEROGA A QUANTO SOPRA STABILITO». E la spiegazione ufficiosa del 1985 lo esplicita: «MALGRADO LA DIVERSITA CHE PUO SUSSISTERE FRA LE OBBEDIENZE MASSONICHE, IN PARTICOLARE NEL LORO ATTEGGIAMENTO DICHIARATO VERSO LA CHIESA, LA SEDE APOSTOLICA VI RISCONTRA ALCUNI PRINCIPI COMUNI, CHE RICHIEDONO UNA MEDESIMA VALUTAZIONE DA PARTE DI TUTTE LE AUTORITA ECCLESIASTICHE». LA DISTINZIONE FRA REGOLARI E ADOGMATICHE, DECISIVA SUL PIANO POLITICO, E DICHIARATA IRRILEVANTE SUL PIANO DOTTRINALE</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>LA CONFERMA RECENTE, A QUARANT’ANNI ESATTI: la risposta del 13 novembre 2023, sollecitata da un vescovo delle Filippine e approvata dal Pontefice, ribadisce che «L’ISCRIZIONE ATTIVA ALLA MASSONERIA DA PARTE DI UN FEDELE E PROIBITA, A CAUSA DELL’INCONCILIABILITA TRA DOTTRINA CATTOLICA E MASSONERIA», e precisa che vi ricadono coloro che «FORMALMENTE E CONSAPEVOLMENTE» si sono iscritti e ne hanno abbracciato i principi, aggiungendo che LE MEDESIME MISURE SI APPLICANO AGLI ECCLESIASTICI ISCRITTI</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>IL LIMITE DA NON OLTREPASSARE, E LA CONTROPROVA STA NEL CORPUS STESSO. La posizione dottrinale NON SI TRADUCE AUTOMATICAMENTE IN COMPORTAMENTO POLITICO NE ELETTORALE: dedurre che partiti ed elettori di area cattolica condividano per cio stesso quella posizione e UN’INFERENZA, NON UN FATTO. E l’elenco sequestrato nel 1981, oggetto di questo repertorio, CONTIENE ISCRITTI DI PARTITI DI ISPIRAZIONE CATTOLICA: la proibizione dottrinale, per quanto reiterata e mai revocata, NON IMPEDI L’ISCRIZIONE</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 × Dominio 5 e Apparato — TERZA DIMENSIONE DA AGGIUNGERE ALLA TASSONOMIA: accanto alla fonte della legittimita e alla sede della sovranita va posto IL RAPPORTO CON L’AUTORITA RELIGIOSA, che e indipendente dalle prime due e che nessuna delle due predice. E la Santa Sede giudica il fenomeno TOUT COURT, cosi come il primo comma dell’articolo 18 proibiva le associazioni segrete tout court PRIMA CHE LA LEGGE DI ATTUAZIONE LO RESTRINGESSE</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="8" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Profilo statistico dell’elenco sequestrato nel 1981 — ELABORAZIONE SUI 960 RECORD DEL CORPUS</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Elaborazione condotta sul file tabellare presente nei file di progetto, che riporta 960 record su novecentosettantadue dichiarati, ordinati per numero di fascicolo, con lacuna dichiarata di 3 fascicoli attribuita alla copia utilizzata e non necessariamente alla fonte originale</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>RETTIFICA A UNA VOCE PRECEDENTE DI QUESTO REPERTORIO, DOVUTA. Era stato affermato che l’elenco contiene iscritti di partiti d’ispirazione cattolica: L’ELENCO NON RECA ALCUN DATO DI APPARTENENZA PARTITICA. Reca 41 record con titolo parlamentare, ma senza indicazione di partito. L’affermazione, che poggia su altre fonti, NON PUO ESSERE RICAVATA DA QUESTO DOCUMENTO e va attribuita alla sede in cui e stata accertata</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>ACCERTAMENTO NEGATIVO CERTIFICATO, sulla copia utilizzata: LA RICERCA DI TITOLI ECCLESIASTICI — don, monsignore, padre, reverendo, fra, sacerdote, cardinale, abate — RESTITUISCE ZERO OCCORRENZE SU 960 RECORD. Il dato va enunciato con il proprio limite: riguarda i titoli riportati nell’elenco, non l’eventuale appartenenza di ecclesiastici priva di titolo nel documento</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>LA COMPOSIZIONE PER TITOLO, non esclusiva: 475 recano titolo dottorale, pari al 49 per cento; 205 RECANO UN GRADO MILITARE, PARI AL 21 PER CENTO — e nel dettaglio 82 COLONNELLI, 49 GENERALI, 48 CAPITANI, 37 TENENTI COLONNELLI, 16 MAGGIORI, 9 AMMIRAGLI. Seguono 50due professori, 44 avvocati, 41 fra deputati e senatori, 22 ragionieri, venti ingegneri, 12 geometri. UN ISCRITTO SU 5 PORTAVA UN GRADO MILITARE</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>GEOGRAFIA E STATO. Roma 31503 e Firenze 119: 472 SU 960, PARI AL 49 PER CENTO, IN DUE SOLE CITTA. Fuori d’Italia: Brasile 19, Buenos Aires 13, Argentina 8, Uruguay due, Stati Uniti due, Liberia due, Dakar uno — 42 VOCI SUDAMERICANE, che vanno lette accanto agli atti del processo romano sull’asse continentale. Quanto allo stato dell’affiliazione, SOLTANTO 101 RECORD RECANO ANNOTAZIONE: 42 in sonno, 36 deceduti, 10 PASSATI AL GRANDE ORIENTE, 8 passati ad altra loggia, 4 sospesi, uno espulso. AVVERTENZA TECNICA: alcuni campi contengono rumore d’estrazione</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Cerniera e Dominio 9 — DUE ACQUISIZIONI. I 10 PASSAGGI ALL’OBBEDIENZA REGOLARE documentano il transito fra struttura coperta e associazione palese, che e precisamente la fattispecie descritta dall’articolo primo della legge del 1982. E LA QUOTA MILITARE DEL 21 PER CENTO, con 9 ammiragli e 49 generali, va misurata contro il secondo comma dell’articolo 18 della Costituzione, che proibisce le associazioni perseguenti anche indirettamente scopi politici MEDIANTE ORGANIZZAZIONI DI CARATTERE MILITARE</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K94" s="8" t="inlineStr"/>
-      <c r="L94" s="8" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Test di adiacenza numerica sull’elenco del 1981 — RISULTATO POSITIVO E SIGNIFICATIVO</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Elaborazione originale sui 960 record del file tabellare presente nei file di progetto, ordinati per numero di fascicolo. Metodo: conteggio delle coppie a numerazione consecutiva che condividono un attributo, e confronto con un modello nullo costruito su duemila permutazioni casuali dell’attributo a sequenza numerica invariata</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>IL DISEGNO, FISSATO PRIMA DEL CALCOLO. Se il numero di fascicolo rispecchia l’ordine di affiliazione, e se il reclutamento avvenne per coorti anziche per adesioni individuali, allora due iscritti con numeri consecutivi devono condividere la citta piu spesso di quanto il caso consenta. L’ipotesi nulla e che l’attributo sia distribuito indipendentemente dalla sequenza numerica</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO SULLA CITTA: su 955 coppie a numerazione consecutiva, 296 condividono la citta, pari al TRENTUNO PER CENTO, contro un valore atteso per puro caso di 150 E 6 DECIMI. L’osservato e quasi il doppio dell’atteso e la probabilita che si verifichi per caso e inferiore a una su 10mila. IL RECLUTAMENTO PROCEDETTE PER COORTI TERRITORIALI, E LA NUMERAZIONE NE CONSERVA L’ORDINE</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>I BLOCCHI PIU LUNGHI, CHE SONO IL DATO PIU ELOQUENTE: 24 FASCICOLI CONSECUTIVI, DAL 6099 AL SETTECENTO22, TUTTI FIORENTINI; 11 consecutivi romani dal quattrocentonovanta al cinquecento; e soprattutto 11 CONSECUTIVI BRASILIANI dal 597 al 607, seguiti da 6 CONSECUTIVI BRASILIANI dal 611 al 616. 17 DEI 19 RECORD BRASILIANI STANNO IN DUE BLOCCHI RAVVICINATI: l’affiliazione brasiliana non fu un accumulo di adesioni individuali ma UNA O DUE OPERAZIONI DATABILI NELLA SEQUENZA</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>IL RISULTATO SUL GRADO MILITARE VA LETTO AL CONTRARIO, ED E ALTRETTANTO UTILE: le coppie consecutive che condividono la condizione militare sono 674 SU 955, pari al settanta e 6 decimi per cento, contro un atteso di 636 e 4 decimi. LA DIFFERENZA E STATISTICAMENTE SIGNIFICATIVA MA MINIMA. NE SEGUE CHE LA LOGGIA NON RECLUTAVA UNA CATEGORIA PROFESSIONALE: RECLUTAVA LUOGHI, E I MILITARI ARRIVAVANO CON I LUOGHI</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Cerniera e Metodologia — 3 AVVERTENZE E UNA CONSEGUENZA. Che il numero di fascicolo corrisponda all’ordine di affiliazione E UN’INFERENZA, sostenuta dall’addensamento ma non dimostrata altrimenti; 3 fascicoli mancano nella copia utilizzata; alcuni campi contengono rumore d’estrazione. LA CONSEGUENZA E CHE IL PATTERN DELL’ADDENSAMENTO, CHE SULLE 9 STRAGI AVEVA DATO ESITO NULLO, QUI DA ESITO POSITIVO CON LO STESSO METODO E LO STESSO MODELLO NULLO: lo strumento non e tarato per produrre negazioni</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr"/>
-      <c r="J95" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K95" s="8" t="inlineStr"/>
-      <c r="L95" s="8" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>LE VOCI ESTERE DELL’ELENCO DEL 1981 — struttura a blocchi ed elaborazione originale, fondamento del Tomo Secondo</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Elaborazione sui 960 record del file tabellare di progetto; riscontri sull’elenco alfabetico pubblicato dalla Presidenza del Consiglio il 21 MAGGIO 1981 e sulla relazione della Commissione d’inchiesta comunicata alle Camere il 12 LUGLIO 1984</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>LA STRUTTURA, CHE E IL RITROVAMENTO. Le voci con localizzazione extraitaliana sono 51 — e non 44 come indicato nell’indice generale dell’opera: DISCREPANZA DA RISOLVERE, verosimilmente per diverso criterio di inclusione. Di esse, TRENTA STANNO IN UN SOLO BLOCCO DI 33 NUMERI CONSECUTIVI, dal fascicolo 589 al 621, con soli 3 salti: 18 brasiliane, 8 argentine, due uruguaiane, due liberiane. IL 509 PER CENTO DELLE VOCI ESTERE OCCUPA IL 3 PER CENTO DELLA NUMERAZIONE. Non e un accumulo di adesioni: E UN’OPERAZIONE UNICA, COLLOCABILE NELLA SEQUENZA</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>LE IDENTIFICAZIONI, RISCONTRATE SU FONTI INDIPENDENTI. Al fascicolo 478, Buenos Aires, figura l’ammiraglio EMILIO EDUARDO MASSERA, membro della giunta militare insediatasi con il colpo di Stato del 1976 — con AVVERTENZA DI TRASCRIZIONE: il file tabellare lo qualifica come generale, mentre l’elenco pubblicato reca «amm». Al fascicolo 591, Argentina, figura JOSÉ LÓPEZ REGA, comandante dell’Alleanza Anticomunista Argentina e poi ministro, CHE SI ISCRISSE PERO IN SPAGNA. Al fascicolo SEICENTONOVE, Argentina, figura il generale CARLOS GUILLERMO SUÁREZ MASON. Nel medesimo blocco figurano inoltre un ammiraglio al 617 e un ufficiale brasiliano al 601</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>IL NESSO ACCERTATO IN SEDE GIUDIZIARIA: i giudici di Bologna hanno ricordato che dopo il colpo di Stato il capo della loggia «AVREBBE SCRITTO A MASSERA COMPLIMENTANDOSI PER IL BUON ESITO DELL’OPERAZIONE E PERCHE TUTTO SI ERA SVOLTO SECONDO I PIANI PRESTABILITI», e la Corte segnala che quel nome comparira negli elenchi sequestrati. E documentato inoltre che Massera si reco a visitare Gelli NELLO STABILIMENTO DI CASTIGLION FIBOCCHI. IL BLOCCO VA DUNQUE LETTO ACCANTO AGLI ERGASTOLI DEFINITIVI PRONUNCIATI A ROMA NEL 2021 PER L’ASSE CONTINENTALE SUDAMERICANO</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>LE AVVERTENZE DELLA COMMISSIONE, DA RIPORTARE SEMPRE. Le liste furono giudicate AUTENTICHE e ATTENDIBILI, ma la Commissione accerto che alcuni erano iscritti da prima della gestione contestata, che MOLTI NEGARONO LA PARTECIPAZIONE o sostennero di essere stati iscritti a loro insaputa, e AVANZO L’IPOTESI CHE LA LISTA NON FOSSE COMPLETA. Convergenza che valida l’estrazione: il computo qui condotto da 205 titoli militari e 41 parlamentari, contro i 208 e 44 delle fonti coeve</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — E IL FONDAMENTO DEL TOMO, E VA APERTO DA QUI: non dall’elenco delle voci estere, MA DALLA LORO DISPOSIZIONE. trenta affiliazioni sudamericane in 33 numeri consecutivi documentano un atto singolo; e fra esse un membro della giunta, il fondatore della Triplice A e un generale poi condannato</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="8" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>La posizione argentina di Licio Gelli, 1973-1981 — accertamenti parlamentari e giudiziari</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Relazione della Commissione parlamentare d’inchiesta; motivazioni della sentenza della Corte d’assise di Bologna nel procedimento Bellini, che ha acquisito sentenze sul Piano Condor; testimonianza resa alla Commissione da un dirigente massonico; Boletin Oficial argentino del 24 OTTOBRE 1973</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>LA CRONOLOGIA DOCUMENTATA. 4 FEBBRAIO 1973: Licio Gelli chiede al gran maestro dell’obbedienza italiana di essere nominato rappresentante massonico argentino presso di essa, e due giorni dopo il gran maestro scrive al gran segretario della Gran Loggia dell’Argentina trasmettendo la richiesta. 28 GIUGNO 1973, un mese dopo l’insediamento del nuovo presidente argentino: gli e concesso PASSAPORTO DIPLOMATICO NUMERO ZEROZEROMILLEOTTOCENTO47 in qualita di «delegato in missione speciale» — E L’ACCERTAMENTO E DELLA COMMISSIONE PARLAMENTARE. 18 OTTOBRE 1973: con decreto numero trentaquattro, firmato dal presidente e dal ministro degli Esteri, gli e conferita la massima onorificenza nazionale argentina, PUBBLICATA NEL BOLLETTINO UFFICIALE IL 24 OTTOBRE E NON DIFFUSA DALLA STAMPA</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>LA POSIZIONE ISTITUZIONALE. 13 SETTEMBRE 1974: cittadinanza argentina. SETTEMBRE 1974, con decreto: designazione a CONSIGLIERE ECONOMICO DELL’AMBASCIATA ARGENTINA IN ITALIA — DISCREPANZA CHIUSA MA CON ANOMALIA: l’atto e il DECRETO NUMERO SETTANTATRE DEL 2 SETTEMBRE 1974, emesso dal governo succeduto alla morte del presidente; una fonte anticipa la designazione all’agosto attribuendola a un decreto redatto con quel presidente, il quale era pero gia morto — vedi voce dedicata. In successione gli furono rilasciati 4 PASSAPORTI ARGENTINI, che gli consentirono di accreditarsi come diplomatico PER OLTRE 8 ANNI, DAL 1973 AL 19 MAGGIO 1981 — cioe FINO A DUE GIORNI PRIMA DELLA PUBBLICAZIONE DELLE LISTE DA PARTE DELLA PRESIDENZA DEL CONSIGLIO</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>L’ACCERTAMENTO GIUDIZIARIO, CHE SALDA LA LOGGIA ALL’ASSE CONTINENTALE. Le motivazioni della sentenza di Bologna, riprendendo le conclusioni della Commissione, parlano del suo «RUOLO INCREDIBILE NELL’AMBITO DELLE GIUNTE MILITARI CHE NEGLI ANNI SETTANTA PRENDONO IL POTERE IN ARGENTINA, URUGUAY, BRASILE, PARAGUAY», e affermano che egli «E IL PRINCIPALE RAPPRESENTANTE DI QUESTI PAESI IN ITALIA E COSTRUISCE UNA FORTUNA PERSONALE IN TALI STATI». La medesima sentenza lo qualifica come consigliere economico presso l’ambasciata che «TRAFFICA IN ARMAMENTI E INFLUENZE». E i giudici, AVENDO ACQUISITO SENTENZE SUL PIANO CONDOR, scrivono che «LA P2 E PARTE COMUNE IN QUEL PERIODO DELLA VITA POLITICA IN ARGENTINA, COSI COME IN ITALIA»</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>DUE INDIRIZZI DI RICERCA CHE NE DISCENDONO. PRIMO: la corrispondenza fra Licio Gelli e la massoneria argentina RISULTA CONSERVATA PRESSO LE BIBLIOTECHE DEL PARLAMENTO ITALIANO A ROMA, ed e consultabile. SECONDO: e stata riferita in sede processuale l’esistenza di ARCHIVI URUGUAIANI del medesimo, con l’affermazione che LA COMMISSIONE PARLAMENTARE NON FOSSE A CONOSCENZA DELL’INTERVENTO DEL SERVIZIO STATUNITENSE SU DI ESSI: circostanza DA VERIFICARE SUGLI ATTI, riferita da chi fu per anni collaboratrice della presidenza di quella Commissione</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — SPIEGA LA STRUTTURA A BLOCCHI. Le trenta affiliazioni sudamericane consecutive non sono un fenomeno massonico: SONO IL PRODOTTO DI UNA POSIZIONE DIPLOMATICA E COMMERCIALE DOCUMENTATA, esercitata con passaporto di Stato per 8 anni. E il blocco va datato entro quell’arco</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr"/>
-      <c r="J97" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K97" s="8" t="inlineStr"/>
-      <c r="L97" s="8" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>Il blocco brasiliano dell’elenco — LACUNA DICHIARATA, indirizzo archivistico, e incoerenza delle cifre pubblicate</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Per la ricerca: fondo del Servizio nazionale di informazioni brasiliano, custodito dall’Archivio nazionale e accessibile tramite il portale governativo delle memorie rivelate; il servizio fu istituito con legge del 13 GIUGNO 1964 e produceva anche relazioni esterne su paesi definiti antagonisti e amici</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>LO STATO DELLA QUESTIONE, DICHIARATO COME LACUNA. Le 18 affiliazioni brasiliane, disposte in due blocchi consecutivi fra i fascicoli 597 e 616, NON HANNO A TUTT’OGGI UNA SPIEGAZIONE DOCUMENTATA nella letteratura consultata. E il piu numeroso fra i gruppi esteri dell’elenco ed e il meno studiato: la ricerca si e concentrata sull’Argentina, dove il capo della loggia aveva posizione diplomatica, e ha lasciato il Brasile sullo sfondo. QUESTA E UNA LACUNA DELLA RICERCA, NON UNA LACUNA DELLE FONTI</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>LA TRACCIA DA VERIFICARE, DI LIVELLO C: fonte secondaria riferisce che ANALISTI DELL’INTELLIGENCE BRASILIANA avrebbero scritto che, «con l’ambiente sfavorevole in Uruguay e il suo indebolimento in Argentina, IL SISTEMA P2 E I SUOI SOTTOSISTEMI STAREBBERO CONSOLIDANDO LE PROPRIE ATTIVITA NEL NOSTRO PAESE». La citazione, se autentica, spiegherebbe lo spostamento del baricentro ma non l’epoca delle affiliazioni, che precede il periodo indicato. VA CERCATO IL DOCUMENTO ORIGINALE NEL FONDO SOPRA INDICATO. E riferito parimenti che l’Uruguay era «divenuto un vero e proprio centro per gli affari della loggia, grazie alla copertura del regime militare», e che un mutamento alla presidenza porto un titolare ostile</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>LA SCOPERTA COLLATERALE, CHE RIGUARDA OGNI CITAZIONE FUTURA: LE CIFRE RIASSUNTIVE IN CIRCOLAZIONE NON CONCORDANO FRA LORO. Una fonte indica 208 militari, 8 ammiragli, 11 questori, 5 prefetti, 44 parlamentari e due ministri; un’altra 119 alti ufficiali, 22 dirigenti di polizia, 509 PARLAMENTARI, 8 direttori di giornali, 22 giornalisti e 4 editori; una terza 4 MINISTRI O EX MINISTRI. Una fonte indica inoltre 992 nominativi anziche 962. Il computo diretto condotto su questo repertorio da 205 TITOLI MILITARI E 41 PARLAMENTARI</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>REGOLA CHE NE DISCENDE: NESSUNA CIFRA RIASSUNTIVA VA CITATA DA FONTE SECONDARIA. Chi voglia usare un numero deve contarlo sull’elenco e dichiarare il criterio di conteggio, perche i titoli sono ambigui — un medesimo nominativo puo recare piu qualifiche — e le fonti coeve adottano criteri diversi senza dichiararli. VA INOLTRE REGISTRATA, COME IPOTESI NON VERIFICATA, l’esistenza riferita di un archivio esteso di circa 2.400 NOMI, mai rinvenuto e attestato dalle sole testimonianze</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — 3 COMPITI. Interrogare il fondo del servizio brasiliano per il documento sul consolidamento; interrogare la corrispondenza massonica argentina conservata presso le biblioteche parlamentari italiane; e ricontare l’elenco dichiarando il criterio, poiche nessuna delle cifre pubblicate e riproducibile</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr"/>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K98" s="8" t="inlineStr"/>
-      <c r="L98" s="8" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Conteggio riproducibile dell’elenco del 1981 — CRITERIO DICHIARATO E CIFRA CONFERMATA</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Elaborazione sui 960 record del file tabellare di progetto. CRITERIO DICHIARATO, senza il quale nessuna cifra e verificabile: si cerca il titolo come parola isolata, ignorando punteggiatura e maiuscole, NELLA SOLA PORZIONE INIZIALE DEL CAMPO NOME — i primi quaranta caratteri — per evitare falsi positivi su cognomi. Il conteggio e NON ESCLUSIVO: un medesimo record puo ricadere in piu categorie</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>IL RISULTATO PRINCIPALE, CHE CONFERMA LA CIFRA COEVA PER VIA INDIPENDENTE: 208 RECORD RECANO ALMENO UN GRADO MILITARE, pari al 21 E 7 DECIMI PER CENTO DELL’UNIVERSO. E esattamente la cifra riportata dalle fonti del tempo, qui riottenuta da un conteggio diretto e ripetibile. Nel dettaglio: 82 COLONNELLI, 49 GENERALI, 48 CAPITANI, 44 fra brigadieri, sottotenenti, tenenti, sergenti e marescialli, 37 TENENTI COLONNELLI, 16 MAGGIORI, 9 AMMIRAGLI</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>LE QUALIFICHE CIVILI: 475 dottori, 50due professori, 44 avvocati, 41 PARLAMENTARI, 22 ragionieri, venti ingegneri, 12 geometri, 6 commendatori. E 85 RECORD, PARI ALL’8 E 9 DECIMI PER CENTO, SONO PRIVI DI QUALSIASI TITOLO RICONOSCIUTO</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>LA DIMOSTRAZIONE DEL PERCHE LE CIFRE PUBBLICATE DIVERGONO, E NON E UN SOSPETTO MA UN CALCOLO: 50 RECORD RECANO DUE O PIU QUALIFICHE RICONOSCIUTE. Ne segue che chi conta per qualifica ottiene una somma superiore all’universo, mentre chi assegna una sola categoria per record ottiene numeri inferiori — E NESSUNA DELLE FONTI COEVE DICHIARA QUALE DEI DUE CRITERI ABBIA ADOTTATO. Le divergenze fra le cifre in circolazione NON SONO ERRORI: SONO CRITERI DIVERSI NON DICHIARATI</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>SCARTI RESIDUI DA RISOLVERE SULL’ATTO: le fonti coeve indicano 43 generali distinti per forza armata contro i 49 qui contati, 8 ammiragli contro 9, 44 parlamentari contro 41. Gli scarti sono compatibili con criteri di inclusione diversi — per esempio il computo dei soli generali di 4 forze specificate — MA VANNO VERIFICATI SULLA RELAZIONE ORIGINALE. Va inoltre ricordato che l’estrazione poggia su 960 RECORD SU 962 DICHIARATI</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Cerniera e Metodologia — CHIUDE IL COMPITO ENUNCIATO NELLA VOCE PRECEDENTE. L’opera puo ora citare una cifra propria, ottenuta con criterio esplicito e ripetibile da chiunque disponga del medesimo file. E LA REGOLA GENERALE: OGNI NUMERO PUBBLICATO IN QUEST’OPERA DEVE PORTARE CON SE IL CRITERIO CHE LO HA PRODOTTO, altrimenti condivide la sorte delle cifre coeve, che divergono fra loro senza che nessuno sappia perche</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I99" s="3" t="inlineStr"/>
-      <c r="J99" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="8" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Il capitolo su mafia e massoneria deviata — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 292-311, GIA NEL CORPUS E MAI APERTO</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Relazione della Commissione stragi, XIII legislatura, DATATA 22 GIUGNO 2000, firmata da 4 senatori e 5 deputati; blocco conclusivo della trascrizione presente nei file di progetto, pagine duecento26-245 su 245</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>LA DEFINIZIONE DELLA STRAGE, TESTUALE, CHE COINCIDE CON IL PRIMO ASSE DELLA TASSONOMIA: «Uccidere persone a caso, vecchi e bambini, clienti di una banca o passeggeri di un treno, in una parola la strage, E STATO UN ATTO POLITICO: un modo violento, barbaro, inaudito, per incidere sugli equilibri del paese e sulle sue istituzioni nell’ambito di strategie TALVOLTA PRECISE — OSTACOLARE L’ALTERNANZA DELLE FORZE AL GOVERNO — e in altri casi piu confuse, indebolire lo Stato e ridurne la capacita di contrasto nella lotta alla criminalita organizzata». LA COMMISSIONE NOMINA COME FINE PRECISO DELLE STRAGI ESATTAMENTE CIO CHE LA PROVA DELL’ALTERNANZA INDIVIDUA COME CRITERIO DELL’ECCEZIONALISMO</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>LA STRUTTURA DEL FENOMENO, E LA CAUTELA CHE VA CONSERVATA: «La cosiddetta strategia della tensione e stata la PARTE ARMATA DI UN PROGETTO POLITICO, O DI PIU PROGETTI POLITICI, messi in atto da soggetti diversi via via spinti a collaborare e ad integrarsi tra loro per colpire lo Stato democratico. Cosi l’eversione di destra si e saldata con parti importanti della mafia, di Cosa Nostra e della Ndrangheta, SPESSO ATTRAVERSO LA MEDIAZIONE ATTIVA DI LOGGE MASSONICHE DEVIATE DIVENUTE IL PUNTO DI INCONTRO DI CAPI DELL’EVERSIONE E DI BOSS MAFIOSI». L’inciso «o di piu progetti politici» E DELLA COMMISSIONE, e sostiene la lettura per progetti rivali anziche per disegno unico. E la loggia vi figura COME PUNTO DI INCONTRO, non come mandante: e ruolo di intermediazione, cioe di betweenness</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>LA FONTE PRINCIPALE E LA SUA GRADUAZIONE: nell’audizione alla Commissione antimafia della XI legislatura del 16 NOVEMBRE 1992, Tommaso Buscetta dichiaro che NEL 1970 3 CAPI MAFIOSI ERANO INTERESSATI A CREARE IN SICILIA UN «CLIMA DI TENSIONE» CHE AVREBBE DOVUTO FAVORIRE UN COLPO DI STATO, e che il contatto fra uomini d’onore e il promotore del tentativo sarebbe avvenuto ATTRAVERSO ESPONENTI DI ALCUNE LOGGE MASSONICHE. La Commissione grada le proprie fonti: i due dichiaranti erano «PUR MOTIVATI DA INTENTI DIVERSI, l’uno dall’intento di collaborare con la giustizia, l’altro FORSE PER LANCIARE OSCURI MESSAGGI». E conclude con formula misurata: «e oggi possibile affermare che la mafia e la cosiddetta massoneria deviata SONO STATE COINVOLTE A VARIO TITOLO nella stagione eversiva 1969-1974»</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>DUE ELEMENTI ULTERIORI DEL MEDESIMO CAPITOLO. PRIMO: vi si trattano LOGGE RISERVATE AI MILITARI DELL’ALLEANZA ATLANTICA SFUGGITE AL CONTROLLO MASSONICO ITALIANO, e logge costituite ad hoc per militari, con la segnalazione della peculiarita di logge legate ad ambienti massonici e politici internazionali. SECONDO, ED E UN SECONDO MANDATO SCRITTO PER QUEST’OPERA: la Commissione enuncia L’ESIGENZA DI APPROFONDIRE IL RUOLO DELLA MASSONERIA NELLA STRATEGIA DELLA TENSIONE, definendolo UN PROBLEMA «DIMENTICATO» DALLA COMMISSIONE P2 IN POI, e osserva che le informazioni disponibili si sono moltiplicate negli ultimi anni. Il paragrafo che precede tratta inoltre DEI FINANZIAMENTI STATUNITENSI AI DIRIGENTI DEL PARTITO DELLA DESTRA PARLAMENTARE</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 4 × 7 — COLMA LA PRINCIPALE LACUNA DICHIARATA NELL’AUDIT. Era il blocco conclusivo del fondo, trascritto dall’autore nell’aprile 2026 e mai aperto; contiene la definizione politica della strage, la struttura a piu progetti, il ruolo di intermediazione della loggia e un invito espresso all’approfondimento</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K100" s="8" t="inlineStr"/>
-      <c r="L100" s="8" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>LA CHIUSA DELLA RELAZIONE — pagina 311, le ultime parole del documento, e la domanda che vi resta</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, PAGINA 311, ultima del documento; trascrizione integrale gia presente nei file di progetto</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>LE LOGGE PER I MILITARI DELL’ALLEANZA, TESTUALE: e anomala «l’esistenza nel passato, nel nostro paese, DI STRUTTURE MASSONICHE TRASVERSALI COSTITUITE AD HOC PER POTER RISERVATAMENTE ACCOGLIERE ALCUNE TIPOLOGIE DI FRATELLI, I MILITARI AD ESEMPIO», e cosi «l’esistenza di LOGGE RISERVATE AI MILITARI DELLA NATO, LOGGE CHE PER STESSA AMMISSIONE DEI RESPONSABILI MASSONICI ITALIANI SONO SFUGGITE A QUALSIASI FORMA DI CONTROLLO DELL’ATTIVITA SVOLTA». Sono i vertici dell’obbedienza ad ammettere di non avere controllato</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>GLI ALTRI ELEMENTI ELENCATI NELLA MEDESIMA FRASE: la peculiarita di alcune logge «LEGATE A BEN PRECISI AMBIENTI MASSONICI E POLITICI INTERNAZIONALI»; il configurarsi di alcune di esse come «VERE E PROPRIE ASSOCIAZIONI SEGRETE»; i «COMPROVATI FINANZIAMENTI» di Licio Gelli a un militante dell’eversione di destra; e la «COMPROVATA APPARTENENZA A LOGGE DEVIATE DI PROTAGONISTI DI VICENDE EVERSIVE E DI MILITANTI DI ORGANIZZAZIONI DELLA DESTRA EVERSIVA». La Commissione qualifica due di questi elementi come COMPROVATI e gli altri come motivi che avvalorano l’esigenza di approfondimento: LA GRADUAZIONE E SUA</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>LA FRASE CHE CHIUDE IL DOCUMENTO, E CHE DOVREBBE CHIUDERE UN CAPITOLO DI QUEST’OPERA: «IL PROBLEMA RESTA QUELLO DI COMPRENDERE SE TUTTO CIO SIA STATO O MENO CASUALE». E la domanda popperiana posta dallo Stato su se stesso, alla fine di 245 pagine: non una conclusione, MA LA DICHIARAZIONE CHE LA CONCLUSIONE NON C’E</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>LA CAUTELA CHE LA COMMISSIONE STESSA APPLICA, E CHE VA ADOTTATA NEL DOMINIO QUARTO: essa distingue espressamente «la stessa massoneria italiana, QUELLA DEL TUTTO ESTRANEA A QUESTE VICENDE E CHE PERCIO HA IL DIRITTO DI NON VEDERSI CONFUSA CON L’ATTIVITA DELLE LOGGE ATIPICHE». E il terzo mandato scritto: «DAI TEMPI DELLA COMMISSIONE SULLA LOGGIA P2, SE SI ECCETTUA IL LAVORO DELLA COMMISSIONE ANTIMAFIA DELLA XI LEGISLATURA, NON SI E PIU CERCATO DI APPROFONDIRE QUESTO PROBLEMA», e le informazioni disponibili, MOLTIPLICATESI NEGLI ULTIMI ANNI, consentirebbero di esaminare «con serieta e rigore un aspetto della strategia della tensione PER TROPPO TEMPO DIMENTICATO»</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 e Metodologia — CHIUDE IL FONDO E CHIUDE L’AUDIT SU QUESTA LACUNA. Il documento non termina con una tesi ma con una domanda, e distingue i propri gradi: due elementi comprovati, gli altri motivi di approfondimento, e una questione dichiarata aperta. UN’OPERA CHE SI CHIUDESSE CON PIU CERTEZZA DI QUANTA NE ABBIA LA FONTE SU CUI POGGIA SAREBBE, IN QUEL PUNTO, MENO RIGOROSA DELLO STATO</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="inlineStr"/>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K101" s="8" t="inlineStr"/>
-      <c r="L101" s="8" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>«Non la restaurazione di un regime fascista, bensi una democrazia autoritaria» — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 267-268</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>AVVERTENZA PRELIMINARE CHE NE DETERMINA L’USO: il documento reca nel titolo i nomi di 5 deputati e 4 senatori ed e una PROPOSTA DI RELAZIONE DI UN GRUPPO DI COMMISSARI, non la conclusione unanime della Commissione. VA CITATO COME TESI DI QUEI COMMISSARI, non come accertamento dell’organo. Datato 22 giugno 2000; trascrizione integrale gia nei file di progetto</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMULA CENTRALE, TESTUALE: «Non si puo scrivere la storia, anche sul piano giudiziario, della strategia della tensione se non si accetta la realta che vuole la destra neofascista italiana TATTICAMENTE DIVISA E STRATEGICAMENTE UNITA, in una SUDDIVISIONE STRUMENTALE DI RUOLI E DI COMPITI che doveva permettere L’UTILIZZO INCONSAPEVOLE DI CENTINAIA DI MIGLIAIA DI PERSONE allo scopo di portare contro la sinistra italiana quell’affondo decisivo che avrebbe consentito LA TRASFORMAZIONE DEL REGIME DA DEMOCRAZIA PARLAMENTARE A REPUBBLICA PRESIDENZIALE. NON LA RESTAURAZIONE DI UN REGIME FASCISTA, BENSI L’INSTAURAZIONE DI UNA DEMOCRAZIA AUTORITARIA NELLA QUALE I COMUNISTI NON AVESSERO SPAZIO E CITTADINANZA LEGALE»</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE E LA DEFINIZIONE ESATTA DELL’ECCEZIONALISMO: non rivoluzione e non restaurazione, ma UNA DEMOCRAZIA CON UN’ESCLUSIONE PERMANENTE. Un esito e precluso in anticipo alla competizione, e una categoria di cittadini e privata di «spazio e cittadinanza legale». E la PROVA DELLA RISERVA nella sua forma piu pura, e non e formulata da questo repertorio ma da 9 parlamentari nel duemila</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA FORMULA, CHE ROVESCIA IL NOME STESSO DEL FENOMENO: «NON C’E STATA UNA STRATEGIA STRAGISTA, c’e stata una strategia che aveva preventivato gli attentati, gli agguati, i disordini, i feriti e i morti, che li ha cercati e li ha provocati, COSI DA MANTENERE IL PAESE IN UN EQUILIBRIO TANTO PRECARIO CHE IN OGNI MOMENTO, NEL CORSO DEGLI ANNI FRA IL 1965-66 E IL 1981-82, UN INTERVENTO AUTORITARIO COMPIUTO DA FORZE POLITICHE DI GOVERNO SOSTENUTE DALLE FORZE ARMATE E DAI CORPI DI POLIZIA SAREBBE STATO ACCOLTO COME UNA LIBERAZIONE dalla popolazione stanca, nauseata, impaurita da anni e anni di violenza estremistica di segno ora fascista, ora comunista». LE STRAGI NON SONO IL FINE MA IL MEZZO PER PRODURRE UNA DOMANDA D’ORDINE, e la finestra dichiarata e 1965-1982</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>SULLA STRUTTURA, CON LE CAUTELE DEL TESTO: le scissioni fra le organizzazioni della destra radicale sarebbero state «PIU CHE ALTRO STRUMENTALI» e avrebbero garantito il controllo dell’estremismo «DA PARTE DI POCHI UOMINI CHE A LIVELLO DI VERTICE SONO SEMPRE STATI IN CONTATTO FRA LORO, PEGGIO ANCORA IN ACCORDO FRA LORO, ALMENO FINO ALLA META DEGLI ANNI SETTANTA». Del partito parlamentare si afferma che della violenza estremistica «NON FU SOLO IL BENEFICIARIO IN TERMINI POLITICI, MA ANCHE IL PROMOTORE E IL COORDINATORE». E del suo segretario che faceva da mediatore fra le istanze nazional-rivoluzionarie e quelle moderate, presentandosi come uomo capace di conciliare la lotta senza compromessi con «LA MIMETIZZAZIONE NECESSARIA PER NON FARSI PORRE FUORI LEGGE». TUTTE AFFERMAZIONI DI PARTE, DA CITARE COME TALI</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Primo e Apparato — 3 CONSEGUENZE. LA TESI DELL’OPERA HA UNA FORMULAZIONE PARLAMENTARE MIGLIORE DI QUALSIASI RIFORMULAZIONE D’AUTORE, e va citata. LA DATAZIONE 1965-1982 va confrontata con la finestra del test di densita, che copriva 1969-1985: IL TEST ANDREBBE RIESEGUITO SULLA FINESTRA DICHIARATA DALLA FONTE. E LA QUALIFICA DI PROPOSTA DI GRUPPO VA RIPETUTA A OGNI CITAZIONE, perche e cio che distingue l’uso corretto dall’abuso</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr"/>
-      <c r="J102" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K102" s="8" t="inlineStr"/>
-      <c r="L102" s="8" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Verifica di robustezza del test di densita — RIESECUZIONE SULLA FINESTRA DICHIARATA DALLA FONTE</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Rielaborazione del test pre-registrato, con la sola modifica della finestra di osservazione: dal periodo scelto dal ricercatore (1969-1985) a QUELLO DICHIARATO DAI COMMISSARI NELLA PROPOSTA DI RELAZIONE DEL 2000, cioe 1965-1982. 100.000 estrazioni per ciascun raggio</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>LA MODIFICA E LE SUE CONSEGUENZE MECCANICHE: la finestra passa a SEIMILACINQUECENTOSETTANTATRE GIORNI; le tappe dell’integrazione comprese diventano 15, includendo il compromesso di Lussemburgo del 1966, il secondo veto del 1967 e il completamento dell’unione doganale del 1968; E UNO DEGLI EVENTI ESCE DALL’INSIEME, poiche la strage del 1984 cade fuori dalla finestra dichiarata. Gli eventi testati sono dunque 8</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO E IDENTICO. Al raggio primario di novanta giorni: 3 EVENTI PROSSIMI SU 8, contro DUE E OTTANTASETTE CENTESIMI attesi per puro caso, con probabilita pari a ZERO VIRGOLA 509. Nessun raggio raggiunge la significativita: a trenta giorni uno osservato contro uno virgola zerocinque atteso; a sessanta due contro uno virgola novantanove; a centottanta 6 contro 5 virgola zerodue; a trecentosessantacinque 8 SU 8 contro 7 virgola trentuno attesi</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>LA RIGA CHE VALE LA VERIFICA: al raggio di un anno TUTTI E 8 GLI EVENTI RISULTANO PROSSIMI A UNA TAPPA, MA LA COPERTURA DELLA LINEA TEMPORALE E DEL NOVANTUNO E 4 DECIMI PER CENTO. In quella condizione «tutto e vicino a qualcosa» NON E UN RISULTATO MA UNA TAUTOLOGIA, e la probabilita che il caso produca lo stesso esito e quasi una su due</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>LA CONCLUSIONE METODOLOGICA, CHE E LA PIU IMPORTANTE. L’esito nullo NON E UN ARTEFATTO DELLA FINESTRA SCELTA: sopravvive alla sostituzione della finestra con quella dichiarata dalla fonte. MA VA LETTO CON PRECISIONE: la tesi dei commissari NON RICHIEDE ADDENSAMENTO ATTORNO A DATE EUROPEE, poiche descrive una strategia CONTINUA di mantenimento di un equilibrio precario. IL RISULTATO NULLO DUNQUE NON CONFUTA LA LORO TESI: CONFUTA QUELLA DA CUI L’OPERA ERA PARTITA, cioe la convergenza bipolare orientata contro le tappe dell’unificazione</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — LA VERIFICA CHIUDE IL PRIMO CAPITOLO METODOLOGICO. L’argomento della coincidenza temporale con il calendario europeo VA ABBANDONATO; l’opera deve reggersi sui legami documentali, che il repertorio sostiene, e sulla strategia continua descritta dalla fonte, che non e misurabile con questo strumento</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr"/>
-      <c r="J103" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K103" s="8" t="inlineStr"/>
-      <c r="L103" s="8" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Il riconoscimento inglese delle obbedienze italiane — 1972, 1993, 2023 — LACUNA COLMATA</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Fonti: comunicazioni trimestrali della Gran Loggia Unita d’Inghilterra; comunicato ufficiale del Grande Oriente d’Italia del 2023; ricostruzioni giornalistiche coeve. LA VOCE COLMA LA PRIMA LACUNA DICHIARATA NELL’AUDIT</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>LA PRIMA DATA, CHE E QUELLA CHE RIGUARDA IL TOMO PRIMO. IL 13 SETTEMBRE 1972 la Gran Loggia Unita d’Inghilterra riconosce la regolarita del Grande Oriente d’Italia. Il riconoscimento e attribuito all’opera dei gran maestri Giordano Gamberini e poi LINO SALVINI, «con l’opera sotto traccia» di un alto funzionario della Ragioneria generale dello Stato. VA LETTA ACCANTO A UNA VOCE GIA REGISTRATA: e lo stesso gran maestro che, NEL FEBBRAIO 1973, accolse la richiesta di Licio Gelli coperta di essere nominato rappresentante massonico argentino presso l’obbedienza italiana. IL RICONOSCIMENTO INGLESE PRECEDE QUELLA NOMINA DI 5 MESI</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA DATA. L’8 DICEMBRE 1993, nella comunicazione trimestrale, la Gran Loggia Unita d’Inghilterra CONFERISCE IL RICONOSCIMENTO ALLA GRAN LOGGIA REGOLARE D’ITALIA SOTTRAENDOLO AL GRANDE ORIENTE. Seguono a breve la Gran Loggia Nazionale Francese, quella d’Irlanda e quella di Scozia, poi Israele, Turchia, Brasile e diverse obbedienze africane. La nuova obbedienza era stata fondata da chi aveva lasciato la guida del Grande Oriente NELLO STESSO 1993, secondo la ricostruzione giornalistica «SULL’ONDA DELLE DENUNCE DELLE INFILTRAZIONI MAFIOSE». IL RITIRO DEL RICONOSCIMENTO E DUNQUE COLLEGATO, DALLE FONTI, ALLA QUESTIONE DELLE INFILTRAZIONI</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>LA TERZA DATA E LA CONDIZIONE POSTA. L’8 MARZO 2023, dopo trent’anni esatti, il riconoscimento e ripristinato al Grande Oriente, che lo commenta definendo quello del 1993 «UN INGIUSTO PROVVEDIMENTO». Ma le costituzioni inglesi PREVEDONO CHE DUE OBBEDIENZE DEL MEDESIMO PAESE POSSANO ESSERE RICONOSCIUTE SOLTANTO SE SI RICONOSCONO FRA LORO, e la pregiudiziale posta e che le due convivano fraternamente: CONDIZIONE CHE AL MOMENTO DELLE FONTI NON RISULTAVA SODDISFATTA</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>E LA RISPOSTA A UNA DOMANDA RIMASTA APERTA IN QUESTO LAVORO: NON ESISTE ALCUN «RITO DI KENT». ESISTE UN GRAN MAESTRO DI KENT — il duca di Kent, gran maestro della Gran Loggia Unita d’Inghilterra dal 1967 — ed e in quella veste che il nome ricorre nelle cronache del riconoscimento italiano. UNA FONTE PARLA DI «MICHELE DI KENT»: la denominazione va verificata, poiche esistono due membri di quella casa con ruoli massonici distinti. IL NOME DESIGNA UNA PERSONA E UNA CARICA, NON UN RITO</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 e Tomo I — 3 ACQUISIZIONI. La regolarita internazionale del Grande Oriente COPRE ESATTAMENTE IL PERIODO 1972-1993, cioe l’arco in cui si colloca la vicenda della loggia coperta e il suo scioglimento per legge. IL RITIRO NON AVVIENE NEL 1981 CON LA SCOPERTA DELLE LISTE, NE NEL 1982 CON LA LEGGE, MA NEL 1993 — dato che va spiegato e non presunto. E il riconoscimento inglese si conferma, come gia registrato, IL VERO ASSE DELLA GEOGRAFIA MASSONICA: non il rito praticato, ma chi riconosce chi</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr"/>
-      <c r="J104" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K104" s="8" t="inlineStr"/>
-      <c r="L104" s="8" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Perche il ritiro del riconoscimento avviene nel 1993 — e il filone che ne discende fino al 2024</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Fonti: audizione dell’ex gran maestro dinanzi alla Commissione antimafia (2017); relazione della Commissione antimafia del 21 DICEMBRE 2017, Doc. XXIII n. 33; sezione ventesima della relazione della legislatura successiva; sentenza della Corte europea dei diritti dell’uomo DEPOSITATA IL 19 DICEMBRE 2024</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>LA SPIEGAZIONE, E NON RIGUARDA IL 1981. L’ex gran maestro si dimise dal Grande Oriente NELL’APRILE 1993, a 3 anni dall’insediamento, e ha poi riferito in sede parlamentare due ordini di fatti. PRIMO: che VERSO LA FINE DEL 1991 E NELLA PRIMAVERA SUCCESSIVA il capo della loggia coperta approfitto della sua elezione PER CHIEDERGLI DI RIENTRARE FORMALMENTE NELL’OBBEDIENZA, prospettandogli tramite un emissario LA POSSIBILITA DI OTTENERE IN CAMBIO DEL DENARO; le profferte furono respinte. SECONDO: rapporti con le organizzazioni criminali siciliana e calabrese, fra cui una riunione a Palermo in cui IL VERTICE DELLA MASSONERIA SICILIANA GLI DISSE DI NON ACCETTARE L’INVITO DEL PRESIDENTE DEL COLLEGIO REGIONALE «PERCHE AVEVA A CHE FARE CON LA MAFIA»</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>NE SEGUE CHE IL RITIRO DEL RICONOSCIMENTO DEL DICEMBRE 1993 NON E LA CONSEGUENZA TARDIVA DELLE LISTE DEL 1981, ma di due fatti del 1991-1993: un tentativo di rientro di Licio Gelli disciolta, e l’emersione delle infiltrazioni mafiose. E si colloca nel medesimo periodo dei lavori della Commissione antimafia della legislatura undicesima sui rapporti fra organizzazioni mafiose e massoneria — la sola indagine che, secondo la relazione sulle stragi del 2000, avesse ripreso il problema dopo la Commissione sulla loggia coperta</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>IL FILONE PROSEGUE E SI INASPRISCE. Nell’APRILE 2017 la Commissione antimafia invito la Guardia di finanza a SEQUESTRARE GLI ELENCHI DI TRENTACINQUEMILA ISCRITTI delle 4 principali obbedienze italiane; furono sequestrati TRENTANOVE FALDONI relativi a SEIMILA ISCRITTI delle logge di Sicilia e Calabria. Il 21 DICEMBRE 2017 la Commissione approvo una relazione sulle infiltrazioni delle due organizzazioni nella massoneria delle due regioni, CHE FU OGGETTO DI DENUNCIA PENALE DA PARTE DELL’OBBEDIENZA MAGGIORE. Vi si legge che il progetto dei massimi esponenti della organizzazione calabrese, GIA PRESENTI IN LOGGE MASSONICHE, di conquistare posizioni di potere pubblico nella Regione, e stato definito dall’indagine «UN VERO CAPOLAVORO»</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>E IL FATTO CHE CHIUDE IL CICLO: CON SENTENZA DEPOSITATA IL 19 DICEMBRE 2024 LA CORTE EUROPEA DEI DIRITTI DELL’UOMO HA CONDANNATO L’ITALIA per quella perquisizione e per quel sequestro. La relazione del 2017 aveva inoltre dichiarato LA LACUNOSITA DELLA NORMATIVA VIGENTE, con riferimento «sia alle disposizioni della legge del 1982, CHE PREVEDE UNA FATTISPECIE MOLTO RESTRITTIVA DI ASSOCIAZIONE SEGRETA, sia alle norme che dovrebbero impedire a magistrati, pubblici dipendenti, militari e forze dell’ordine di aderire ad associazioni massoniche», ritenendo essenziale un adeguamento</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 4 e Tomo III — 3 ACQUISIZIONI. La restrizione della fattispecie introdotta nel 1982, gia registrata in questo repertorio, E DENUNCIATA DALLA COMMISSIONE ANTIMAFIA TRENTACINQUE ANNI DOPO COME LACUNA ANCORA APERTA. Il ciclo si chiude con UNA CONDANNA SOVRANAZIONALE ALLO STATO CHE INDAGAVA: e la forma inversa di quella registrata altrove, e va scritta come tale. E il tentativo di rientro del 1991-1992, se riscontrato sugli atti dell’audizione, COLLEGA LA VICENDA DELLA LOGGIA DISCIOLTA AL RITIRO DEL RICONOSCIMENTO DI UN DECENNIO DOPO</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K105" s="8" t="inlineStr"/>
-      <c r="L105" s="8" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>Corte europea dei diritti dell’uomo, Grande Oriente d’Italia contro Italia — ricorso 29550/17, sentenza 19 DICEMBRE 2024</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>TESTO INTEGRALE IN TRADUZIONE ITALIANA UFFICIALE SUL SITO DEL MINISTERO DELLA GIUSTIZIA, sezione delle sentenze della Corte europea; comunicato stampa della cancelleria in lingua inglese. Ricorso proposto il 13 APRILE 2017, poche settimane dopo i fatti; decisione di Camera ALL’UNANIMITA</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>I FATTI ACCERTATI. Nel MARZO 2017, su ordine della Commissione parlamentare antimafia della 17sima legislatura, il nucleo speciale della Guardia di finanza per il contrasto alla criminalita organizzata perquisi la sede dell’obbedienza. L’associazione si era rifiutata di consegnare gli elenchi spontaneamente per due ragioni: NON RISULTAVA CHE ALCUN ISCRITTO FOSSE INDAGATO dalla magistratura, e la consegna avrebbe violato la normativa sulla protezione dei dati personali. LA PERQUISIZIONE DURO 14 ORE e si estese all’intera struttura, COMPRESI L’APPARTAMENTO PRIVATO DEL GRAN MAESTRO E IL CAPANNO DEGLI ATTREZZI. Furono sequestrati TRENTANOVE FALDONI di schede relative a SEIMILA ISCRITTI delle logge di Sicilia e Calabria</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>LA RISPOSTA ALLA DOMANDA SU DOVE SIANO I FASCICOLI, E VIENE DALLA SENTENZA: SI TRATTA DI «INTERFERENZA PERMANENTE IN QUANTO LA DOCUMENTAZIONE SEQUESTRATA NON E STATA DISTRUTTA AL TERMINE DELL’ATTIVITA DELLA COMMISSIONE». I trentanove faldoni non risultano dunque distrutti, e la Corte qualifica proprio questo come il carattere permanente della violazione. QUANTO AI TRENTACINQUEMILA NOMINATIVI DELLE 4 OBBEDIENZE, ESSI SONO L’OGGETTO DELL’INVITO DELL’APRILE 2017, NON DEL SEQUESTRO ACCERTATO: la sorte degli elenchi delle altre 3 obbedienze NON RISULTA DA QUESTE FONTI E RESTA DA VERIFICARE</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>LE MOTIVAZIONI, CHE INTERESSANO IL TOMO TERZO. La Corte accerta violazione dell’articolo 8 della Convenzione, e conclude che il provvedimento fu adottato «IN ASSENZA DI PROVE O DI RAGIONEVOLI SOSPETTI DEL COINVOLGIMENTO NEI FATTI OGGETTO DI INDAGINE, IDONEI A GIUSTIFICARLO». Stigmatizza che l’associazione NON DISPONESSE DI ALCUN RIMEDIO INTERNO. E afferma il principio che vale oltre il caso: L’IMMUNITA DEL PARLAMENTO INVOCATA DALLO STATO «RICHIEDE PUR SEMPRE LA POSSIBILITA DI QUALCHE FORMA DI CONTROLLO EX ANTE O EX POST DA PARTE DI UNA AUTORITA INDIPENDENTE, QUALE GARANZIA ESSENZIALE CONTRO INTERFERENZE ARBITRARIE DEI PUBBLICI POTERI»</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>IL PASSAGGIO PROCESSUALE DA REGISTRARE: il Governo aveva eccepito che il ricorso fosse manifestamente infondato, invocando L’AUTONOMIA DEL PARLAMENTO E LA SEPARAZIONE DEI POTERI, e sostenendo che perquisizione e sequestro fossero conformi all’ARTICOLO 82 DELLA COSTITUZIONE, cioe ai poteri d’inchiesta parlamentare. LA CORTE HA RESPINTO L’ECCEZIONE, ritenendo che essa sollevasse questioni che non potevano essere risolte senza esame nel merito</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III e Dominio 4 — E LA FORMA INVERSA DI TUTTO IL REPERTORIO, E VA SCRITTA COME TALE. Altrove lo Stato distrugge, espunge o non versa. QUI LO STATO SEQUESTRA E NON DISTRUGGE, E VIENE CONDANNATO PROPRIO PER NON AVER DISTRUTTO. E i poteri d’inchiesta esercitati sono gli stessi dell’articolo 82 che, in altra voce di questo repertorio, hanno consentito a una Commissione di acquisire atti da privati e da procedimenti in corso: LO STESSO STRUMENTO, DUE ESITI OPPOSTI</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="inlineStr"/>
-      <c r="J106" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K106" s="8" t="inlineStr"/>
-      <c r="L106" s="8" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>La circolazione degli elenchi nominativi massonici italiani, 2010-2022 — OGGETTO DOCUMENTABILE, NON FONTE UTILIZZABILE</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Accertamento condotto sui due file esaminati e su fonti pubbliche. Il documento del 2010 risulta accessibile in rete presso il sito di un centro studi, in cartella datata marzo 2010, coerente con la data di creazione del file (1° aprile 2010); il documento del 2022 ne e la versione ampliata</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>LA CATENA DI CIRCOLAZIONE, ACCERTATA. Una redazione dichiarata in 26MILAQUATTROCENTO10 nominativi circola su piattaforme di condivisione ed e stata rivendicata da un organo di stampa; il file del 2010 e in rete da 15 ANNI; quello del 2022 conta circa TRENTADUEMILATRECENTO coppie distinte e ne contiene il NOVANTASEI VIRGOLA 3 PER CENTO. Termine di confronto dichiarato all’epoca dal gran maestro dell’obbedienza maggiore: 18MILACINQUECENTO iscritti — l’elenco copre dunque piu obbedienze</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CHE NE DETERMINA L’INUTILIZZABILITA PER QUEST’OPERA, E LO DICHIARA LA FONTE STESSA CHE LI DIFFUSE: gli elenchi «NON COMPRENDONO LOGGE OCCULTE NE LE LISTE DEGLI AFFILIATI ALL’ESTERO». Per costruzione, dunque, NON CONTENGONO CIO CHE QUESTA RICERCA CERCA. La medesima fonte formula inoltre l’ipotesi che chi assurge a cariche pubbliche elevate sposti il proprio nome «in elenchi maggiormente riservati, spesso di logge estere»: E CONGETTURA NON PROVATA e va marcata come tale</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>IL QUADRO GIURIDICO, DUE AUTORITA A 3 ANNI DI DISTANZA. Il Garante per la protezione dei dati personali, nel parere del 14 GENNAIO 2021, ha stabilito che i dati riferiti all’appartenenza ad associazioni private RIENTRANO FRA LE CATEGORIE PARTICOLARI cui il Regolamento riserva le piu elevate garanzie quando idonei a rivelare opinioni politiche o convinzioni religiose e filosofiche, richiamando i principi di LIMITAZIONE DELLA FINALITA e MINIMIZZAZIONE DEI DATI oltre alla liberta di associazione costituzionalmente riconosciuta. E la Corte europea, nel DICEMBRE 2024, ha condannato lo Stato per il sequestro di elenchi analoghi</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>LA PRASSI GIORNALISTICA DOCUMENTATA, CHE COINCIDE CON IL CRITERIO ADOTTATO IN QUESTO REPERTORIO: nel caso siciliano del 2022, pubblicati elenchi comprendenti logge di piu obbedienze — fra cui una di Castelvetrano aderente all’obbedienza francese — il cronista, PUR APPLICANDO OMISSIS, riporto per esteso i soli nominativi «dei piu importanti, o comunque di coloro che ricoprono o hanno ricoperto un ruolo politico». OMISSIS PER I PRIVATI, NOME PER CHI ESERCITA FUNZIONI PUBBLICHE</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 e Metodologia — L’ESISTENZA E LA CIRCOLAZIONE DI QUESTI ELENCHI SONO UN FATTO REGISTRABILE; il loro contenuto non e una fonte utilizzabile, sia perche la catena documentale manca dell’anello iniziale, sia perche PER AMMISSIONE DI CHI LI DIFFUSE ESSI ESCLUDONO LE STRUTTURE COPERTE. Un elenco che dichiara di non contenere le logge occulte non puo provare nulla su di esse</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr"/>
-      <c r="J107" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K107" s="8" t="inlineStr"/>
-      <c r="L107" s="8" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Relazione della Commissione antimafia sulle infiltrazioni nella massoneria, Doc. XXIII n. 33, 21 DICEMBRE 2017 — le cifre di Castelvetrano</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Commissione parlamentare d’inchiesta sul fenomeno delle mafie, 17sima legislatura. Istruttoria condotta con lungo ciclo di audizioni e missioni, fra cui quella a Palermo e Trapani del 18, 19 E 20 LUGLIO 2016, con prefetto, forze di polizia, magistratura distrettuale e circondariale, esperti e DUE COLLABORATORI DI GIUSTIZIA; auditi anche i vertici delle principali obbedienze</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>LA CIFRA COMPLESSIVA: CENTONOVANTATRE ISCRITTI A LOGGE RISULTANO COINVOLTI IN INCHIESTE SULLA CRIMINALITA ORGANIZZATA. Per la Calabria si aggiunge che, fra i soggetti menzionati nella relazione della commissione di accesso e nell’ordinanza di custodia cautelare del Tribunale di Reggio Calabria, figurano TRECENTOSEI NOMINATIVI, 17 DEI QUALI CENSITI. Procedimenti richiamati: quelli denominati Mammasantissima, Morgana e Saggezza</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>LE CIFRE DI CASTELVETRANO, CHE SONO IL CUORE DELLA RELAZIONE. NEL COMUNE OPERANO 6 LOGGE MASSONICHE SULLE 19 DELL’INTERA PROVINCIA. NEL 2016 4 ASSESSORI SU 5 ERANO ISCRITTI ALLA MASSONERIA, E 7 CONSIGLIERI SU TRENTA. Il comune E STATO SCIOLTO NEL GIUGNO 2017 PER INFILTRAZIONI della criminalita organizzata. Nel trapanese risultano inoltre duecento persone gia detenute per reati di mafia e stupefacenti, tornate in liberta a fine pena. La Commissione riferisce che 3 assessori massoni, due dei quali iscritti all’obbedienza maggiore, RESERO DICHIARAZIONI AMBIGUE SULLA VOLONTA DI COLLABORARE ALLA CATTURA DEL LATITANTE, E ATTACCARONO LA COMMISSIONE STESSA E LA SUA PRESIDENZA</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>IL PASSAGGIO CHE RISOLVE LA QUESTIONE DEGLI ELENCHI IN CIRCOLAZIONE. Gli inquirenti trapanesi e palermitani hanno individuato «UN FILO CONDUTTORE CHE IPOTIZZA COME LE LOGGE COPERTE SI ANNIDINO ANCORA ALL’OMBRA DELLE LOGGE UFFICIALI; come gli uomini, pur risultati iscritti alle logge coperte, ABBIANO CONTINUATO A FAR CARRIERA SIA NEL MONDO POLITICO SIA NEL MONDO DEGLI AFFARI, NON ESSENDOCI MAI STATA UN’EFFICACE REAZIONE DELLE ISTITUZIONI PER ISOLARLI ANCHE DOPO CHE I LORO NOMI E LA LORO APPARTENENZA FOSSERO DIVENUTI PALESI; come vi sia riscontro che gia appartenenti a logge segrete e irregolari SIANO POI TRASMIGRATI IN ALTRE LOGGE; di come SIA POSSIBILE PASSARE DA UNA LOGGIA REGOLARE A UNA COPERTA E VICEVERSA»</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>LE VALUTAZIONI DELLA COMMISSIONE SULLE OBBEDIENZE E LA RETE CALABRESE. Si registra «UNA SORTA DI ARRENDEVOLEZZA NEI CONFRONTI DELLA MAFIA»; in diversi casi non e coltivato «il primario interesse alla impermeabilita dalle mafie»; il preteso rispetto delle leggi «SI E RIVELATO PIU APPARENTE CHE REALE»; e «IL SEGRETO COSTITUISCE IL PERNO DI ALCUNE OBBEDIENZE», con «un senso di riservatezza a dir poco esasperato». Dalle indagini calabresi emerge inoltre che un controllo del territorio cosi penetrante «NON SAREBBE POSSIBILE IN ASSENZA DI UNA RETE SEGRETA, COMPOSTA DA AVVOCATI, PROFESSIONISTI, AMMINISTRATORI LOCALI, APPARTENENTI ALLE FORZE DELL’ORDINE E AI SERVIZI SEGRETI, MAGISTRATI»</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 3 × 4 × 10 — DUE ACQUISIZIONI DECISIVE. PRIMA: la relazione afferma che si passa DA UNA LOGGIA REGOLARE A UNA COPERTA E VICEVERSA, e che le coperte si annidano all’ombra delle ufficiali: ne segue che NESSUN ELENCO DI ISCRITTI REGOLARI PUO RAGGIUNGERE L’OGGETTO, e la questione dei file in circolazione e chiusa. SECONDA: che gli interessati abbiano continuato a far carriera ANCHE DOPO CHE L’APPARTENENZA ERA DIVENUTA PALESE e la forma del fatto accertato senza sanzione, applicata a questa materia e affermata da un organo parlamentare</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="inlineStr"/>
-      <c r="J108" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K108" s="8" t="inlineStr"/>
-      <c r="L108" s="8" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Processo Gotha, Reggio Calabria — LA TESI DELLA COMPONENTE RISERVATA MASSONICA, AFFERMATA IN PRIMO GRADO E DEMOLITA IN APPELLO NEL MAGGIO 2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Procedimento nato dalla riunione delle inchieste denominate Mammasantissima, Reghion, Fata Morgana e Sistema Reggio — ALCUNE FONTI AGGIUNGONO ALCHEMIA: DISCREPANZA DA RISOLVERE — coordinate dalla Direzione distrettuale antimafia di Reggio Calabria. Rito abbreviato definito nel MARZO 2018 con sentenza di DUEMILACINQUECENTO PAGINE; rito ordinario definito in primo grado il 30 LUGLIO 2021; APPELLO DEFINITO NEL MAGGIO 2026</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>LA TESI ACCUSATORIA, CHE COINCIDE CON QUELLA DI QUEST’OPERA: esisterebbe UN LIVELLO SUPERIORE E STRATEGICO collocato al di sopra dell’ala organizzativa e militare, composto da SOGGETTI CERNIERA CHE INTERAGISCONO FRA L’AMBITO VISIBILE E QUELLO OCCULTO, e legato ad ambienti massonici; una struttura capace di ETERODIRIGERE LA POLITICA E LE ISTITUZIONI LOCALI. Nelle motivazioni di primo grado si parla di «sistema allargato di potere tra cosche, massoneria e politica», e di una struttura segreta denominata anche «santa», «mammasantissima» o «cupola»</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>GLI ESITI DI PRIMO GRADO. Rito abbreviato, marzo 2018: fra le condanne, VENT’ANNI a un avvocato indicato al vertice delle relazioni riservate. Rito ordinario, 30 luglio 2021, su trentaquattro imputati: 15 CONDANNE E 15 ASSOLUZIONI, a fronte di trenta condanne richieste. 25 ANNI a un avvocato ed ex parlamentare; 13 ANNI a un ex sottosegretario regionale; E ASSOLUZIONE DI UN EX SENATORE PER IL QUALE L’ACCUSA AVEVA CHIESTO VENT’ANNI. Motivazioni depositate nel 2023</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>L’APPELLO DEL MAGGIO 2026, ED E IL FATTO CHE VA REGISTRATO PER PRIMO IN OGNI CITAZIONE FUTURA. La Corte d’appello di Reggio Calabria HA AZZERATO LE CONDANNE ECCELLENTI, assolvendo l’ex parlamentare, l’ex senatore, un sacerdote e — pur deceduto — l’ex sottosegretario. Secondo le cronache «CROLLA ROVINOSAMENTE IN SECONDO GRADO L’IMPIANTO ACCUSATORIO CON IL QUALE LA PROCURA DISTRETTUALE PER UN DECENNIO HA IPOTIZZATO L’ESISTENZA DI UNA COMPONENTE RISERVATA E MASSONICA DELLA ORGANIZZAZIONE, CAPACE DI ETERODIRIGERE LA POLITICA E LE ISTITUZIONI LOCALI». LA DECISIONE NON E DEFINITIVA e le motivazioni non risultano ancora disponibili: RESTA IL GIUDIZIO DI LEGITTIMITA</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>CONSEGUENZA PER QUEST’OPERA, E VA SCRITTA SENZA ATTENUAZIONI. IL TENTATIVO GIUDIZIARIO PIU AVANZATO MAI CONDOTTO DI PROVARE L’ESISTENZA DI UN DIRETTORIO OCCULTO MASSONICO-MAFIOSO CHE ETERODIRIGE LE ISTITUZIONI E STATO ACCOLTO A META IN PRIMO GRADO E RESPINTO IN APPELLO. Chi sostenga quella tesi deve oggi confrontarsi con questo esito, non ignorarlo. E chi citi la relazione parlamentare del 2017, che a quelle inchieste si appoggiava, DEVE CITARE ANCHE IL SEGUITO GIUDIZIARIO</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 4 e Metodologia — DUE LEZIONI. LA PRIMA: la distanza fra accertamento parlamentare e accertamento giudiziario e strutturale, e questa vicenda ne e la dimostrazione piu netta del repertorio — la Commissione afferma nel 2017, il primo grado conferma a meta nel 2021, l’appello azzera nel 2026. LA SECONDA: e la forma inversa del fatto accertato senza sanzione — QUI NON MANCA LA SANZIONE, MANCA L’ACCERTAMENTO, e la differenza va tenuta</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr"/>
-      <c r="J109" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K109" s="8" t="inlineStr"/>
-      <c r="L109" s="8" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Censimento delle condanne definitive di parlamentari — IMPOSTAZIONE DEL CRITERIO E FONTE ISTITUZIONALE</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Fonte normativa: decreto legislativo 31 DICEMBRE 2012 numero 235, in attuazione della delega contenuta nella legge 6 novembre 2012 numero 190. Fonte documentale: deliberazioni delle Giunte delle elezioni e delle immunita parlamentari e voti delle rispettive Assemblee, atti pubblici</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>LA CATEGORIA GIURIDICA CHE RENDE IL CENSIMENTO POSSIBILE. La norma prevede l’incandidabilita EX LEGE per 3 classi di condannati CON SENTENZA DEFINITIVA A PENE SUPERIORI A DUE ANNI: per i delitti di cui all’articolo 51 commi 3-bis e 3-quater del codice di procedura penale, cioe DI STAMPO MAFIOSO E CON FINALITA DI TERRORISMO; per i DELITTI CONTRO LA PUBBLICA AMMINISTRAZIONE; e per i delitti non colposi puniti con reclusione non inferiore nel massimo a 4 anni. MECCANISMO: se la condanna diviene definitiva durante il mandato, LA DECADENZA E DICHIARATA DALLA GIUNTA DELLE ELEZIONI E CONFERMATA DALL’AULA. Precedente documentato: Giunta del 4 OTTOBRE 2013, Assemblea del 27 NOVEMBRE 2013, con deliberazione a voto palese. LA CORTE EUROPEA HA ESCLUSO IL CARATTERE PENALE DELL’INCANDIDABILITA</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE QUESTA E LA SOLA FONTE UTILIZZABILE: la decadenza parlamentare consegue ESCLUSIVAMENTE A CONDANNA DEFINITIVA, e la deliberazione che la dichiara e un atto pubblico verbalizzato. Non richiede rassegne stampa, non contiene imputazioni, e non e selezionata per parte. E IL CORRISPETTIVO, PER LA SECONDA REPUBBLICA, DI CIO CHE LA DIRETTIVA DEL 2014 E PER LE STRAGI: UN ELENCO PRODOTTO DALLO STATO PER ALTRI FINI</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>IL DIFETTO EREDITATO, ACCERTATO. Il censimento giornalistico piu citato, pubblicato alla vigilia delle elezioni del 2022, conta 101 CANDIDATI e poi QUARANTA ELETTI, ma dichiara espressamente di comprendere «INDAGINI A CARICO, PROCESSI IN CORSO O CONDANNE PASSATE IN GIUDICATO» — CIOE FONDE LE 3 CATEGORIE ESATTAMENTE COME FA IL REGISTRO DEL CORPUS. Ne segue che l’errore di standard probatorio rilevato nel registro NON E ORIGINALE: E EREDITATO DALLA FONTE. Il medesimo articolo presenta inoltre UN’INCOERENZA INTERNA, indicando in un punto ventisette deputati e 11 senatori e in un altro 25 e 15, a fronte di un totale dichiarato di quaranta</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CHE VA REGISTRATO PER INTERO, PERCHE E TRASVERSALE: la ripartizione di quei quaranta e indicata in 12 per la Lega, 8 per Fratelli d’Italia, 7 per Forza Italia, 5 PER IL PARTITO DEMOCRATICO, 4 PER ITALIA VIVA, DUE PER IL MOVIMENTO 5 STELLE e due per un’altra lista — con 26 SU QUARANTA nella coalizione allora vincente. UN CENSIMENTO CHE SELEZIONASSE UNA SOLA PARTE PERDEREBBE 14 CASI SU QUARANTA E CON ESSI LA PROPRIA DIFENDIBILITA</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — IL CRITERIO DA ADOTTARE, DICHIARATO: condanne DEFINITIVE di parlamentari, TUTTE LE AREE, dal 1994, con estremi della sentenza, capo d’imputazione e data della deliberazione di decadenza dove intervenuta; categoria separata e distinta per imputazioni e procedimenti pendenti, MAI FUSA CON LA PRIMA. Se il risultato mostrasse uno squilibrio fra le aree, LO SQUILIBRIO SAREBBE IL RITROVAMENTO — e nessuno potrebbe attribuirlo alla selezione</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="inlineStr"/>
-      <c r="J110" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K110" s="8" t="inlineStr"/>
-      <c r="L110" s="8" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Atlante giudiziario della politica italiana 1994-2026 — compilazione trasversale, e LE DUE CORREZIONI CHE APPORTA AL REGISTRO DEL CORPUS</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Documento di oltre 3150 schede, organizzato per operazione giudiziaria e per appartenenza politica, con indicazione di esito definitivo, patteggiamento, assoluzione o rinvio a giudizio distinti fra loro. STATUTO: E COMPILAZIONE SECONDARIA FONDATA SU FONTI GIORNALISTICHE, NON SU SENTENZE LETTE IN ORIGINALE: vale come indice verso gli atti, non come atto</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>LA PRIMA CORREZIONE, CHE RISOLVE L’ERRORE GIA RILEVATO: il documento tiene distinte la condanna definitiva di Marcello Dell’Utri a 7 ANNI e l’esito del procedimento sulla cosiddetta trattativa, nel quale «HA VISTO ASSOLTI TUTTI GLI IMPUTATI ISTITUZIONALI». Il registro del corpus li fondeva in una frase sola, attribuendo la condanna al processo sbagliato e dandola per annullata: VA RISCRITTA SU QUESTA BASE E POI VERIFICATA SULLE SENTENZE</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA CORREZIONE, CHE VALE PER LA TESI GENERALE. Nel procedimento su Roma la CASSAZIONE, CON DECISIONE DEL 22 OTTOBRE 2019, HA ESCLUSO DEFINITIVAMENTE L’ASSOCIAZIONE DI STAMPO MAFIOSO, riqualificando il fatto in associazione a delinquere semplice, sul rilievo che LA CAPACITA INTIMIDATRICE APPARTENEVA AL SOLO CAPO PERSONALMENTE E NON AL GRUPPO IN MODO IMPERSONALE. Le condanne restano — 10 anni al capo, 12 anni e 10 mesi al vertice della componente economica, definitive nel settembre 2022 — MA LA QUALIFICAZIONE ASSOCIATIVA MAFIOSA E CADUTA</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CHE SMENTISCE OGNI CENSIMENTO DI PARTE, E VIENE DAL DOCUMENTO STESSO. Fra i politici condannati nel procedimento romano figurano 4 ESPONENTI DEL PARTITO DEMOCRATICO — con pene definitive fino a 5 anni — DUE DI AREA POPOLARE-FORZA ITALIA, UNO DI ALLEANZA NAZIONALE poi condannato in via definitiva a un anno e 10 mesi in procedimento separato, e UNO DI ALTRA LISTA. NEL PRINCIPALE PROCEDIMENTO ROMANO DEL PERIODO I CONDANNATI DI UNA PARTE SONO PIU NUMEROSI DI QUELLI DELL’ALTRA, E IN DIREZIONE OPPOSTA A QUELLA PRESUPPOSTA DALLA RICHIESTA INIZIALE</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>E IL PARALLELO CHE VA REGISTRATO. In due diversi procedimenti maggiori — quello romano e quello reggino — L’IMPIANTO ASSOCIATIVO E CADUTO: nel primo per esclusione definitiva del carattere mafioso in Cassazione nel 2019; nel secondo per azzeramento in appello delle condanne eccellenti nel maggio 2026. IN ENTRAMBI I CASI RESTANO CONDANNE INDIVIDUALI E CADE LA STRUTTURA. E il dato piu importante che questo repertorio abbia sulla tesi del sistema associativo occulto</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — IL DOCUMENTO E UTILIZZABILE COME INDICE, MAI COME PROVA: ogni scheda va risolta sulla sentenza citata. Ma il suo impianto e corretto dove il registro del corpus non lo era, perche DISTINGUE CONDANNA DEFINITIVA, PATTEGGIAMENTO, ASSOLUZIONE E RINVIO A GIUDIZIO, e perche non seleziona per parte</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="inlineStr"/>
-      <c r="J111" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K111" s="8" t="inlineStr"/>
-      <c r="L111" s="8" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Operazione Kyterion, Direzione distrettuale antimafia di Catanzaro, 2015-2016 — CONDANNE CHE TOCCANO IL NODO MASSONICO</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Kyterion prima fase: 28 GENNAIO 2015, 37 arresti, contemporanea a un’altra operazione emiliana. Kyterion seconda fase: 4 GENNAIO 2016, 16 arresti. Procedimento a carico della cosca di Cutro</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>CHE COSA SVELO LA SECONDA FASE, e va citato con la cautela dovuta alla fonte secondaria: tentativi di collegamento del capocosca CON AMBIENTI DEL VATICANO, DELLA CORTE DI CASSAZIONE E DI ORDINI MASSONICI, oltre a un conto corrente indicato in DUECENTO43 MILIONI DI EURO. E il nodo Dominio 1 × Dominio 4 × Dominio 5 in un solo procedimento</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>GLI ESITI, CHE SONO L’OPPOSTO DI QUELLI REGGINI E ROMANI: nel rito ordinario 11 CONDANNE SU 11 IMPUTATI, ZERO ASSOLUZIONI, con pene da 6 a 16 anni «spesso aumentate rispetto alle richieste dell’accusa». Con rito abbreviato TRENTA ANNI al capo. Fra le posizioni piu rilevanti per questo lavoro: 10 ANNI a un impiegato comunale indicato come filtro delle visite al detenuto; 10 ANNI a un soggetto indicato come INTERMEDIARIO FRA FINANZA E MASSONERIA per conto del capo; 6 ANNI E 8 MESI a un avvocato per concorso esterno. Rinviati a giudizio, fra gli altri, un avvocato indicato per contatti con la Cassazione</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>IL CONFRONTO CHE NE DISCENDE, ED E IL PIU ISTRUTTIVO DEL REPERTORIO SU QUESTA MATERIA. Dove l’accusa ha contestato CONDOTTE INDIVIDUALI DI INTERMEDIAZIONE — un impiegato che filtra, un intermediario che collega, un avvocato che assiste — LE CONDANNE HANNO TENUTO, 11 SU 11. Dove ha contestato L’ESISTENZA DI UNA STRUTTURA ASSOCIATIVA OCCULTA SOVRAORDINATA, l’impianto e caduto: a Roma per esclusione del carattere mafioso in Cassazione nel 2019, a Reggio per azzeramento in appello nel 2026</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 4 × 5 — REGOLA CHE NE DERIVA PER L’OPERA: la prova regge sul singolo legame documentato e cede sulla struttura complessiva. Un’opera che costruisca il proprio impianto sulla seconda replica l’errore che due impianti accusatori hanno gia commesso; un’opera che lo costruisca sulla prima poggia su cio che ha retto in giudizio</t>
-        </is>
-      </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="3" t="inlineStr"/>
-      <c r="J112" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K112" s="8" t="inlineStr"/>
-      <c r="L112" s="8" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Operazione Laziogate, 2005-2012 — ASSOLUZIONE PIENA DOPO CONDANNA DI PRIMO GRADO</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Fatti del marzo 2005; sentenza di primo grado del 5 MAGGIO 2010; sentenza d’appello del 29 OTTOBRE 2012</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>L’ACCUSA: intrusione nel sistema informatico dell’anagrafe comunale di Roma, nella notte fra il 9 e il 10 MARZO 2005, attraverso i computer della societa informatica regionale, PER VERIFICARE PRESUNTE FIRME FALSE NELLA LISTA DI UNA FORMAZIONE RIVALE alle elezioni regionali. Il presidente uscente della Regione, divenuto nel frattempo ministro, SI DIMISE NEL 2006 DOPO L’AVVISO DI GARANZIA</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>IL PRIMO GRADO condanno 12 posizioni, con pene da 8 mesi a due anni e due patteggiamenti. L’APPELLO ASSOLSE TUTTI CON FORMULA «PERCHE IL FATTO NON SUSSISTE», sul rilievo che ESISTEVA UNA CONVENZIONE CHE AUTORIZZAVA L’ACCESSO ALLA BANCA DATI. Una posizione fu assolta in sede di legittimita</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE VA REGISTRATA IN QUESTO REPERTORIO: e il caso simmetrico e opposto a quelli che vi dominano. Altrove il fatto e accertato e la sanzione manca; QUI LA SANZIONE ERA STATA IRROGATA IN PRIMO GRADO E IL FATTO E RISULTATO INSUSSISTENTE. Nel mezzo, LE DIMISSIONI DI UN MINISTRO 7 ANNI PRIMA DELL’ASSOLUZIONE DEFINITIVA</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — MISURA DELLA DISTANZA FRA EFFETTO POLITICO ED ESITO GIUDIZIARIO: l’effetto si produce all’avviso di garanzia, l’accertamento arriva 7 anni dopo e in senso contrario. E dato che un’opera sul potere occulto deve registrare con la stessa cura delle condanne</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="3" t="inlineStr"/>
-      <c r="J113" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K113" s="8" t="inlineStr"/>
-      <c r="L113" s="8" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>Operazione e processo Grimilde, Bologna-Reggio Emilia, 2019-2025 — LA STRUTTURA ASSOCIATIVA PROVATA IN VIA DEFINITIVA, e RETTIFICA A UNA VOCE PRECEDENTE</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Operazione del 25 GIUGNO 2019, 16 arresti e sessanta indagati, Direzione distrettuale antimafia di Bologna con le squadre mobili di Bologna, Reggio Emilia e Piacenza. Rito abbreviato: sentenza del giudice per le indagini preliminari del 26 OTTOBRE 2020; appello del 16 GIUGNO 2022; CASSAZIONE DEL 2 LUGLIO 2023. Rito ordinario: primo grado del 15 DICEMBRE 2022; appello 2024; CASSAZIONE NOVEMBRE 2025</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>GLI ESITI, CHE SONO L’OPPOSTO DI QUELLI ROMANO E REGGINO. Rito abbreviato in primo grado: 42 CONDANNE SU 48 IMPUTATI, DUECENTOTRENTUNO ANNI COMPLESSIVI, compresi 9 patteggiamenti. In appello «L’ACCUSA HA RETTO: I GIUDICI HANNO CONFERMATO TUTTE LE CONDANNE PER ASSOCIAZIONE MAFIOSA», riducendo le pene. In Cassazione 18 CONDANNE DIVENUTE DEFINITIVE e 6 posizioni rinviate a nuovo appello. Nel rito ordinario il capo, cui il primo grado aveva ESCLUSO LA POSIZIONE APICALE con 19 anni e 6 mesi, se l’e vista RICONOSCIUTA IN APPELLO CON PENA INASPRITA A 24 ANNI, e il ricorso e stato dichiarato inammissibile</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO CHE VA REGISTRATO PER PRIMO: E DIVENUTA DEFINITIVA LA CONDANNA A OLTRE 12 ANNI DI UN ESPONENTE POLITICO ELETTO — ex presidente del consiglio comunale di un capoluogo e funzionario dell’Agenzia delle dogane, allontanato dal proprio partito subito dopo l’arresto — RICONOSCIUTO FRA GLI ESPONENTI DEL SODALIZIO. La procura generale ha sottolineato che «CON SENTENZA DEFINITIVA E STATA RIBADITA, CON LA CONFERMA DEL DELITTO DI ASSOCIAZIONE DI STAMPO MAFIOSO, L’ESISTENZA E L’OPERATIVITA NEL DISTRETTO DELL’EMILIA-ROMAGNA DI UNA STRUTTURA AUTONOMA»</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>RETTIFICA ALLA VOCE PRECEDENTE DI QUESTO REPERTORIO. Era stato scritto che «la prova regge sul singolo legame documentato e cede sulla struttura complessiva»: E FORMULAZIONE ERRATA, e Grimilde la smentisce. LA DIFFERENZA REALE E ALTRA: dove l’accusa contesta UNA CELLULA TERRITORIALE CON CONDOTTE MATERIALI DOCUMENTATE — appalti a societa di comodo, frodi fiscali, riciclaggio, caporalato, relazioni con amministratori — LA QUALIFICAZIONE ASSOCIATIVA REGGE FINO IN CASSAZIONE. Dove contesta UNA STRUTTURA OCCULTA SOVRAORDINATA E TRASVERSALE, che collega massoneria, servizi e politica senza condotte materiali proprie, l’impianto cade: a Roma nel 2019, a Reggio Calabria nel 2026</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>IL CONTESTO CHE VALE PER IL TOMO SECONDO: il comune di Brescello fu SCIOLTO PER INFILTRAZIONI NEL 2015, primo caso nel Nord Italia. Nel 2009 un sindaco aveva definito diffamatori gli articoli sulla presenza criminale; nel 2014 un altro sindaco defini il capocosca «UNA PERSONA EDUCATA, TRANQUILLA» — E DA QUELL’EPISODIO INIZIARONO GLI ACCERTAMENTI CHE PORTARONO ALLO SCIOGLIMENTO. DISCREPANZA DA RISOLVERE: le fonti indicano per il rito ordinario ora 11 condanne e 5 assoluzioni, ora 13 condanne</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 2 e Metodologia — E IL CONTROESEMPIO CHE SALVA LA TESI DALL’ECCESSO OPPOSTO: non e vero che l’associazione occulta non si possa provare. SI PROVA QUANDO HA CONDOTTE MATERIALI PROPRIE, e non si prova quando e postulata come livello superiore privo di atti propri. La differenza non e di giudici: E DI OGGETTO</t>
-        </is>
-      </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr"/>
-      <c r="J114" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K114" s="8" t="inlineStr"/>
-      <c r="L114" s="8" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Processo Gotha — RICOSTRUZIONE CORRETTA DEI 3 TRONCONI, e rettifica a due affermazioni precedenti</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Ricostruzione condotta su fonti giornalistiche coeve e sulla voce enciclopedica; VA RISOLTA SUGLI ATTI. RETTIFICA ALLA VOCE PRECEDENTE DI QUESTO REPERTORIO, che presentava l’appello del maggio 2026 come esito unico: IL PROCEDIMENTO SI ARTICOLA IN ALMENO 3 TRONCONI CON ESITI DIVERSI E DATE DIVERSE</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>TRONCONE PRIMO, RITO ABBREVIATO. Primo grado MARZO 2018: vent’anni all’avvocato indicato come vertice delle relazioni riservate, e pene severe ad altri. Appello GENNAIO 2021: pena ridotta a 15 anni e 4 mesi. CASSAZIONE MARZO 2022: ANNULLA 10 CONDANNE — per quella principale, ANNULLAMENTO SENZA RINVIO per i fatti fino al 2005 perche gia coperti da giudicato, e ANNULLAMENTO CON RINVIO per la condotta successiva, sul rilievo che fosse «ILLOGICA» LA SOVRAPPOSIZIONE FRA RUOLO VISIBILE E RUOLO OCCULTO. Appello bis 15 NOVEMBRE 2024: 4 condanne rideterminate, 3 ASSOLUZIONI PIENE, una prescrizione; 10 ANNI all’imputato principale, qualificato come PARTECIPE E NON PROMOTORE</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>TRONCONE SECONDO, RITO ORDINARIO. Primo grado 30 LUGLIO 2021: 15 condanne e 15 assoluzioni; 25 anni all’avvocato ed ex parlamentare; motivazioni depositate circa due anni dopo. APPELLO MAGGIO 2026: assoluzioni delle posizioni maggiori</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>TRONCONE TERZO, ED E QUELLO CHE PIU INTERESSA QUEST’OPERA: uno stralcio in rito abbreviato relativo agli imputati accusati di far parte di UN’ASSOCIAZIONE SEGRETA ai sensi della legge del 1982. LA CORTE D’APPELLO NON HA RICONOSCIUTO L’ASSOCIAZIONE SEGRETA e ha assolto «PERCHE IL FATTO NON SUSSISTE» un ex consigliere di una finanziaria regionale e UN CANCELLIERE DELLA MEDESIMA CORTE D’APPELLO, in primo grado condannati a due e a 4 anni. Assolto dalla violazione della legge anche un commercialista, CHE PERO E STATO CONDANNATO A 10 ANNI E 8 MESI PER CONCORSO ESTERNO</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>LA CONFERMA DELLA REGOLA, SULLA MEDESIMA PERSONA: per lo stesso imputato LA CONDOTTA INDIVIDUALE DI CONCORSO ESTERNO HA RETTO E LA QUALIFICAZIONE DI ASSOCIAZIONE SEGRETA E CADUTA. E la dimostrazione piu netta che il repertorio possieda del fatto che la fattispecie introdotta nel 1982 — quella che richiede la prova dell’interferenza — E DI DIFFICILISSIMA APPLICAZIONE, esattamente come la Commissione antimafia denunciava nel 2017. SEGNALAZIONE SUL CORPUS: una sessione precedente di questo lavoro afferma l’esistenza di una «sentenza definitiva della Corte di cassazione del 5 settembre 2023» con 8 condanne definitive nel Gotha: TALE PRONUNCIA NON TROVA RISCONTRO nelle fonti qui verificate, che collocano l’intervento di legittimita nel MARZO 2022 con annullamento. VA VERIFICATA O CORRETTA</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 1 × 4 × 10 e Metodologia — 3 ACQUISIZIONI. Fra gli assolti figura UN CANCELLIERE DELLA CORTE D’APPELLO CHE LO GIUDICAVA, circostanza da registrare per se stessa. La valutazione di sintesi disponibile e che appello e legittimita abbiano «demolito in parte l’impianto accusatorio, decidendo per l’assoluzione di tutti i principali imputati e confermando la condanna soltanto per 4 profili minori». E NESSUNA CITAZIONE DI QUESTO PROCEDIMENTO E CORRETTA SE NON SPECIFICA IL TRONCONE E IL GRADO</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr"/>
-      <c r="J115" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K115" s="8" t="inlineStr"/>
-      <c r="L115" s="8" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Capitolo primo del censimento dei politici in procedimenti penali — MISURAZIONE DELLA COMPOSIZIONE E CERTIFICAZIONE DEI LIMITI</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Documento omnicomprensivo di compilazione dell’autore, aprile 2026: millecentotrentacinque paragrafi, 10 tabelle, DUECENTOSETTANTADUE RIGHE, quasi 16mila parole. Struttura: centotrentaquattro schede sintetiche in 5 sezioni, piu centotrentacinque schede dettagliate a 7 campi nelle sezioni A-E, piu appendice sui procedimenti emiliani e calabresi</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>LA COMPOSIZIONE REALE, MISURATA SULLA COLONNA ESITO DI TUTTE LE CENTOTRENTAQUATTRO RIGHE: 33 POSIZIONI DEFINITIVE, pari al 24 E 6 DECIMI PER CENTO; 42 PENDENTI, pari al TRENTUNO E 3 DECIMI PER CENTO; 28 NON DETERMINABILI DAL CAMPO, pari al VENTI E 9 DECIMI; 12 patteggiamenti; 7 ASSOLUZIONI O PROSCIOGLIMENTI; 6 prescrizioni; 3 posizioni con esiti misti fra condanna e assoluzione su capi diversi; 3 non definitive</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>LA CERTIFICAZIONE CHE NE SEGUE, E VA APPOSTA AL DOCUMENTO: MENO DI UN QUARTO DELLE POSIZIONI CENSITE E DEFINITIVA. Quasi un terzo riguarda procedimenti pendenti, cioe persone su cui NON ESISTE ALCUN ACCERTAMENTO. E un quinto reca un campo esito da cui lo stato processuale NON E RICAVABILE</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>IL MIGLIORAMENTO ACCERTATO RISPETTO ALLA PRIMA STESURA: la versione precedente dello stesso capitolo, su 43 schede, registrava UNA SOLA ASSOLUZIONE; questa ne registra 7, piu 6 prescrizioni e 3 esiti misti. LA STRUTTURA PREVEDE DUNQUE GLI ESITI FAVOREVOLI, e li registra. Resta che il 5 e due decimi per cento di assoluzioni E QUOTA IMPLAUSIBILE rispetto alla realta giudiziaria italiana, e va verificato se dipenda dal criterio di selezione</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>LA DISTINZIONE DECISIVA PER L’USO DEL DOCUMENTO. Il titolo dichiara «politici COINVOLTI IN PROCEDIMENTI PENALI»: rispetto a quel titolo l’inclusione di pendenti, assolti e prescritti E CORRETTA E DOVUTA. IL PROBLEMA NON E L’INCLUSIONE MA L’USO: nessuna riga di questo censimento puo sostenere un’affermazione di responsabilita se non reca esito definitivo, e le 33 che lo recano vanno tenute separate dalle altre 101</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — REGOLA DI CITAZIONE: dal censimento si cita l’esito, mai la presenza. E le 3 posizioni con esiti misti su capi diversi VANNO SCOMPOSTE CAPO PER CAPO, perche una scheda che registri insieme una condanna e un’assoluzione non e citabile in nessuna delle due direzioni</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr"/>
-      <c r="J116" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K116" s="8" t="inlineStr"/>
-      <c r="L116" s="8" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Verifica a campione delle posizioni definitive del capitolo primo — DUE RISCONTRI E UN PROBLEMA SISTEMICO</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>Verifica condotta su fonti giornalistiche coeve per due delle 33 posizioni indicate come definitive nel censimento</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>PRIMA VERIFICA, CONFERMATA MA DA COMPLETARE: la condanna a 6 ANNI per concorso esterno di un ex senatore ed ex sottosegretario all’Interno E DEFINITIVA DAL 13 DICEMBRE 2022. La scheda e esatta e priva di data. MA LA STORIA PROCESSUALE VA REGISTRATA PERCHE E ISTRUTTIVA: richiesta di rinvio a giudizio nell’OTTOBRE 2011; SETTEMBRE 2013, il giudice ASSOLVE per i fatti successivi al 1994 e dichiara prescritti i precedenti; SETTEMBRE 2016, L’APPELLO CONFERMA L’ASSOLUZIONE; 22 GENNAIO 2018, LA CASSAZIONE ANNULLA L’ASSOLUZIONE CON RINVIO; 21 LUGLIO 2021, l’appello bis CONDANNA A 6 ANNI; 13 DICEMBRE 2022, ricorso rigettato. 11 ANNI, ASSOLTO IN DUE GRADI E POI CONDANNATO IN VIA DEFINITIVA</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE QUESTO CASO VA ACCOSTATO AI PRECEDENTI: e la direzione opposta a quella del procedimento romano e di quello reggino. LI la condanna precede l’assoluzione, QUI L’ASSOLUZIONE PRECEDE LA CONDANNA. NON E VERO CHE I GRADI SUPERIORI ASSOLVANO: correggono in entrambe le direzioni, e un’opera che citasse solo i ribaltamenti favorevoli commetterebbe lo stesso errore di chi cita solo le condanne</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>SECONDA VERIFICA, CHE CORREGGE LA SCHEDA. Per l’ex presidente di regione la scheda indica «falso e abuso d’ufficio» con condanna definitiva del 2018: LA CASSAZIONE DEL 4 APRILE 2018 HA DICHIARATO PRESCRITTO L’ABUSO D’UFFICIO e confermato il solo FALSO IN ATTO PUBBLICO, rideterminando la pena da 5 anni a 4 ANNI E 7 MESI. Primo grado marzo 2014: 6 anni e interdizione perpetua; appello dicembre 2016: 5 anni. LA RIDETERMINAZIONE HA FATTO VENIR MENO L’INTERDIZIONE PERPETUA, limitandola a 5 anni. Condannati in via definitiva anche 3 revisori dei conti a due anni e 4 mesi ciascuno</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>IL PROBLEMA SISTEMICO CHE NE EMERGE, E RIGUARDA PIU SCHEDE: NEL 2024 IL DELITTO DI ABUSO D’UFFICIO E STATO ABROGATO — circostanza da riscontrare sull’atto legislativo. Nell’elenco delle posizioni definitive del capitolo figurano ALMENO 3 CONDANNE PER QUEL SOLO TITOLO, rispettivamente a 8 mesi, a 6 mesi e a un anno e 6 mesi. L’ABROGAZIONE NON CANCELLA IL GIUDICATO, ma un censimento che si estenda al 2026 DEVE REGISTRARE CHE IL REATO NON ESISTE PIU, altrimenti attribuisce oggi una qualificazione che l’ordinamento non prevede</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — 3 PRESCRIZIONI OPERATIVE. Ogni scheda deve recare LA DATA E L’AUTORITA della pronuncia definitiva, assenti in 28 delle 33. Deve DISTINGUERE I CAPI CONFERMATI DA QUELLI PRESCRITTI, perche la scheda verificata li fondeva. E deve SEGNALARE I TITOLI DI REATO ABROGATI</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="inlineStr"/>
-      <c r="J117" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K117" s="8" t="inlineStr"/>
-      <c r="L117" s="8" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Terza verifica sul capitolo primo — SCHEDA CHE ATTRIBUISCE FRA I REATI DUE CAPI CON ESITO ASSOLUTORIO</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Verifica condotta su fonti giornalistiche coeve sulla posizione che il censimento indica con il totale di pena piu elevato del capitolo</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>CIO CHE RISULTA CONFERMATO: la posizione reca effettivamente 3 CONDANNE DEFINITIVE PER BANCAROTTA. La prima, per il dissesto di un istituto di credito cooperativo di cui l’interessato fu presidente per circa vent’anni, e definitiva dal 3 NOVEMBRE 2020 in 6 ANNI E 6 MESI — primo grado 9 anni, ridotti in appello a 6 anni e 10 mesi e poi in legittimita per prescrizioni parziali. La seconda, per il fallimento di una societa editrice, e definitiva dal 28 NOVEMBRE 2023 in 5 ANNI E 6 MESI. La terza riguarda il fallimento di un’impresa edile</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>L’ERRORE, ED E IL PIU GRAVE FINORA RILEVATO NEL CENSIMENTO: la scheda elenca fra i reati anche «FINANZIAMENTO ILLECITO (P3)». MA LE FONTI ATTESTANO CHE L’INTERESSATO FU RICONOSCIUTO NON COLPEVOLE DELL’ACCUSA DI APPARTENERE ALLA COSIDDETTA P3, E FU ASSOLTO nell’inchiesta romana sulla compravendita di un immobile, nella quale era accusato proprio di finanziamento illecito. LA SCHEDA ATTRIBUISCE DUNQUE FRA I REATI DUE CAPI CON ESITO ASSOLUTORIO, e classifica poi l’intera riga come condanna definitiva</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMA DELL’ERRORE, CHE E STRUTTURALE E NON ISOLATA: il campo «reato o accusa» raccoglie indistintamente CAPI CON CONDANNA DEFINITIVA E CAPI CON ASSOLUZIONE, e il campo «esito» riporta soltanto i primi. CHI LEGGA LA RIGA RICAVA CHE L’INTERESSATO SIA STATO CONDANNATO ANCHE PER I FATTI DAI QUALI E STATO ASSOLTO. E il medesimo difetto gia rilevato su altra scheda, dove un capo prescritto era fuso con uno confermato</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>SECONDO RILIEVO, DI METODO: la scheda somma le 3 pene in un totale di circa 15 ANNI E 10 MESI. LA SOMMA ARITMETICA DI CONDANNE DISTINTE NON CORRISPONDE ALLA PENA DA ESPIARE, che si determina con provvedimento di cumulo secondo le regole del concorso. Un totale sommato senza provvedimento di cumulo E DATO PRIVO DI SIGNIFICATO GIURIDICO, ancorche aritmeticamente esatto</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — REGOLA CHE NE DISCENDE, E VA APPLICATA A TUTTE LE SCHEDE: OGNI CAPO D’IMPUTAZIONE DEVE PORTARE IL PROPRIO ESITO. Non si elencano i capi in un campo e gli esiti in un altro, perche l’accostamento produce attribuzioni false. E NON SI SOMMANO LE PENE senza il provvedimento che le cumula</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="inlineStr"/>
-      <c r="J118" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K118" s="8" t="inlineStr"/>
-      <c r="L118" s="8" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Processo cosiddetto P3 — Tribunale di Roma, nona sezione penale, sentenza di PRIMO GRADO DEL 16 MARZO 2018</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Inchiesta della Procura di Roma aperta nella primavera del 2010 su una presunta associazione segreta finalizzata al pilotaggio di appalti e sentenze e al dossieraggio; denominazione giornalistica per assonanza con la loggia sciolta nel 1982. Requirenti: il procuratore aggiunto e un sostituto. 18 IMPUTATI, 18 CONDANNE RICHIESTE, 8 PRONUNCIATE</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>L’AFFERMAZIONE CENTRALE, ED E LA PRIMA DEL GENERE DOPO IL 1982: il tribunale ha riconosciuto che «LA P3 FU UN’ASSOCIAZIONE SEGRETA», condannando per VIOLAZIONE DELLA LEGGE ANSELMI. E la prima verita processuale sull’applicazione di quella legge a distanza di 36 anni dalla sua entrata in vigore. VA PERO REGISTRATO CHE SI TRATTA DI SENTENZA DI PRIMO GRADO, e che gli esiti dei gradi successivi VANNO VERIFICATI PRIMA DI OGNI CITAZIONE</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>LE CONDANNE. 6 ANNI E 6 MESI a un uomo d’affari indicato come promotore, gia condannato per il dissesto di un istituto bancario e imputato ma assolto per l’omicidio di un banchiere: richiesti 9 anni e 6 mesi. 4 ANNI E 9 MESI a un imprenditore, richiesti 8. DUE ANNI PER ABUSO D’UFFICIO A UN EX PRIMO PRESIDENTE DELLA CORTE DI CASSAZIONE, per il quale erano stati richiesti 5 anni per corruzione. UN ANNO E 10 MESI ciascuno per corruzione a un ex presidente di agenzia regionale e a un presidente di consorzio. 10 MESI per diffamazione e violenza privata a un ex sottosegretario all’Economia e a un ex assessore regionale</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>GLI ESITI NON DI CONDANNA, CHE SONO LA MAGGIORANZA: prescrizione per l’ex presidente di una Regione, imputato di abuso d’ufficio; assoluzione per un ex coordinatore regionale e per un direttore di filiale bancaria; assoluzione richiesta dagli stessi requirenti per un dirigente comunale; DECESSO del terzo indicato come promotore la settimana precedente la sentenza; STRALCIO della posizione di un ex senatore, POI PRESCRITTA L’ANNO SUCCESSIVO. La maggior parte dei reati contestati risultava prescritta</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>RETTIFICA A UNA VOCE DI QUESTO REPERTORIO, DOVUTA. Era stato scritto che la scheda del censimento attribuisce erroneamente a una posizione il capo «finanziamento illecito P3» in quanto assolta: L’AFFERMAZIONE VA CORRETTA. Quella posizione FU EFFETTIVAMENTE CONDANNATA IN PRIMO GRADO A UN ANNO E 3 MESI, PIU 6100.000 EURO DI MULTA, PER FINANZIAMENTO ILLECITO. IL DIFETTO DELLA SCHEDA E DIVERSO E RESTA: essa NON REGISTRA CHE LA MEDESIMA POSIZIONE FU ASSOLTA DALL’ACCUSA DI APPARTENERE ALL’ASSOCIAZIONE, che era il capo principale</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 2 × 4 — E IL TERMINE DI CONFRONTO PER IL PROCEDIMENTO REGGINO. In quello la contestazione di associazione segreta NON FU RICONOSCIUTA in appello; qui FU RICONOSCIUTA in primo grado. Due applicazioni della medesima legge del 1982, due esiti opposti, e in entrambi i casi LE CONDOTTE INDIVIDUALI HANNO RETTO PIU DELLA QUALIFICAZIONE ASSOCIATIVA</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="inlineStr"/>
-      <c r="J119" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K119" s="8" t="inlineStr"/>
-      <c r="L119" s="8" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>CHIUSURA DI DUE DISCREPANZE DI DATA, E IL PRINCIPIO CHE NE EMERGE</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Per la prima: articolo su rivista giuridica statunitense, National Security Archive, e voce enciclopedica divergente. Per la seconda: 7 testate e organizzazioni di parte civile che seguirono l’udienza</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>PRIMA — LA DIRETTIVA STATUNITENSE DEL 1973. Le fonti davano 7 oppure 9 maggio. LA DISCREPANZA SI RISOLVE COME DOPPIO ATTO E NON COME ERRORE: JAMES SCHLESINGER SOTTOSCRISSE la direttiva ai vertici operativi IL 7 MAGGIO, e IL 9 MAGGIO diramo il memorandum a tutto il personale dell’agenzia invitando anche gli ex dipendenti a riferire. Le fonti che indicano la prima data descrivono la firma; quelle che indicano la seconda descrivono la diramazione. ENTRAMBE VANNO CITATE, ciascuna per il proprio atto. **Livello A**</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>SECONDA — LA SENTENZA DI LEGITTIMITA SULL’ASSE CONTINENTALE. Le fonti davano 8 oppure 9 luglio duemila21. ANCHE QUI DOPPIO ATTO: l’udienza si apri ALLE ORE 10 DELL’8 LUGLIO e prosegui per due giornate; LA SENTENZA FU LETTA NEL PRIMO POMERIGGIO DEL 9 LUGLIO dalla prima sezione penale. Chi data all’8 data l’inizio dell’udienza, chi data al 9 data la pronuncia. LA DATA DELLA SENTENZA E IL 9 LUGLIO DUEMILA21</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>SI RISOLVONO CONTESTUALMENTE LE DISCREPANZE DI CIFRA DEL MEDESIMO PROCEDIMENTO. Furono emessi 146 MANDATI D’ARRESTO; soltanto 37 divennero imputati, dei quali 4 brasiliani giudicati separatamente. Primo grado, 17 GENNAIO DUEMILA17: 8 ergastoli e 19 assoluzioni. Appello duemila19: 24 ERGASTOLI SU 25. Legittimita: 14 ERGASTOLI DEFINITIVI, essendo 7 imputati deceduti nel frattempo, PIU 3 gia irrevocabili per mancata impugnazione — 17 IN TOTALE</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>E SI RISOLVE LA DISCREPANZA SULLE VITTIME: le 43 sono le vittime di origine italiana comprese nel processo come aperto — 6 italo-argentini, 4 italo-cileni, 13 italo-uruguaiani e venti uruguaiani; le 23 sono quelle contemplate nei capi portati al giudicato definitivo. NON SONO CIFRE ALTERNATIVE MA CIFRE DI FASI DIVERSE. LA DISCREPANZA SULLA SENTENZA D’APPELLO E STATA CHIUSA NELLA MEDESIMA GIORNATA: LA DATA E L’8 LUGLIO 2019, un lunedi, attestata da 5 testate che riferirono quel giorno; il 10 luglio compare in una ricostruzione posteriore che, nel medesimo articolo, usa la stessa data anche per l’unificazione delle inchieste del 2006</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — IL PRINCIPIO GENERALE, CHE VALE PER LE 6 DISCREPANZE ANCORA APERTE. In entrambi i casi risolti, LA DIVERGENZA NON ERA UN ERRORE DI UNA FONTE MA LA REGISTRAZIONE DI DUE ATTI DISTINTI DA PARTE DI FONTI DIVERSE. Ne segue la regola di lavoro: davanti a due date vicine non si cerca quale sia falsa, MA QUALE ATTO CIASCUNA REGISTRI; e la discrepanza si chiude nominando entrambi. Chi sceglie una data e scarta l’altra perde un\’informazione anziche acquistarne una</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="inlineStr"/>
-      <c r="J120" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K120" s="8" t="inlineStr"/>
-      <c r="L120" s="8" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>CHIUSURA DELLA DISCREPANZA SULLA SCISSIONE DEL 1908 — E RETTIFICA A UN CAPITOLO GIA SCRITTO</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Fonte istituzionale per il fatto: relazione della Commissione parlamentare d’inchiesta sulla loggia P2, che registra «una scissione intervenuta nel 1908, in ragione di contrasti attinenti l’atteggiamento da assumere sulla legislazione concernente l’insegnamento religioso nelle scuole». Per la data: voce enciclopedica, enciclopedia massonica di lingua tedesca e ricostruzione giornalistica concordano; studio accademico sui fondi di Salamanca per il contesto</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>LA DATA E IL 24 GIUGNO 1908. 3 fonti indipendenti la indicano concordemente; il 26 giugno compare in un sito di un’obbedienza discendente dagli scissionisti, cioe FONTE DI PARTE E SUCCESSORE INTERESSATO. VI E INOLTRE UNA CORROBORAZIONE INTERNA CHE VALE PIU DEL COMPUTO DELLE FONTI: il 24 giugno e la festivita del santo precursore, data nella quale le obbedienze tengono per tradizione l’assemblea annuale — e la rottura si consumo appunto in quella sede. **Livello A**</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>LA RETTIFICA, CHE E SOSTANZIALE E RIGUARDA UN CAPITOLO GIA REDATTO DI QUEST’OPERA. Era stato scritto che l’obbedienza «aveva imposto ai propri affiliati parlamentari un indirizzo di voto». LA DINAMICA ACCERTATA E DIVERSA E PIU FORTE: nel corso della gran loggia annuale il gran maestro ETTORE FERRARI PROPOSE LA CENSURA nei confronti dei parlamentari massoni CHE SI ERANO RIFIUTATI DI VOTARE la mozione — presentata da LEONIDA BISSOLATI, deputato socialista riformista anch’egli massone — volta ad abolire l’insegnamento della religione nella scuola elementare. SAVERIO FERA, sovrano gran commendatore in pectore del rito scozzese, POSE IL VETO FORMALE CONTRO LA PROPOSTA DI CENSURA, e da li si giunse alla scissione</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE LA RETTIFICA RAFFORZA L’ARGOMENTO ANZICHE INDEBOLIRLO: non si trattava di un’istruzione di voto impartita in anticipo, MA DI UNA SANZIONE ASSOCIATIVA MINACCIATA A POSTERIORI CONTRO CHI AVEVA VOTATO SECONDO COSCIENZA. La questione sollevata dagli scissionisti non era dunque se l’associazione potesse indirizzare, ma SE POTESSE PUNIRE UN ELETTO PER IL VOTO ESPRESSO. E la prova del vincolo di coscienza, quarto criterio del terzo asse della tassonomia, VA RIFORMULATA DI CONSEGUENZA in termini di sanzione e non di indirizzo</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>ELEMENTI ULTERIORI DA REGISTRARE: secondo le parole del gran maestro abbandonarono 9 LOGGE; gli scissionisti erano guidati da un pastore metodista wesleyano poi della chiesa evangelica italiana, deputato, e furono seguiti da 21 ALTI DIGNITARI che portarono con se sigilli e cassa del rito; all’inizio del 1909 la nuova obbedienza contava CIRCA 15MILA ISCRITTI. Lo studio accademico avverte che la questione scolastica «AVEVA FUNTO DA DETONATORE PER UNA SITUAZIONE INTERNA CHE GIA VIVEVA FORTI CRITICITA E DIVISIONI»: la causa dichiarata non esaurisce la causa</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 4 — DUE CONSEGUENZE OPERATIVE. Il capitolo sul dominio quarto va corretto nel passaggio sul millenovecentotto. E il fatto ha ora una fonte parlamentare italiana, che e preferibile alle fonti massoniche di parte finora usate per esso</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr"/>
-      <c r="J121" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K121" s="8" t="inlineStr"/>
-      <c r="L121" s="8" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>La soppressione della relazione parlamentare statunitense del 1976 — CRONOLOGIA CHIUSA E DOCUMENTI MAI RITROVATI</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Rivista interna dell’agenzia informativa statunitense, numero invernale 1998-1999; archivio universitario di sicurezza nazionale; edizione integrale della relazione trafugata, pubblicata all’estero</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>LA CRONOLOGIA, ORA COMPLETA. 15 GENNAIO 1976: il presidente scrive al presidente della commissione negando la declassificazione delle informazioni sulle operazioni coperte. 19 GENNAIO: la commissione trasmette all’agenzia la bozza finale, 338 PAGINE. 26 GENNAIO: il maggiore esponente repubblicano della commissione dichiara in aula che la diffusione metterebbe in pericolo la sicurezza nazionale. 29 GENNAIO 1976, 3 GIORNI DOPO: la camera vota 246 CONTRO 124 per vietare alla propria commissione di diffondere la relazione finche non sia «CERTIFICATA DAL PRESIDENTE COME NON CONTENENTE INFORMAZIONI CHE POSSANO PREGIUDICARE LE ATTIVITA INFORMATIVE DELL’AGENZIA». **Livello A**</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>LA REPLICA DI OTIS PIKE, DA CITARE NEL TOMO TERZO: «LA CAMERA HA APPENA VOTATO PER NON DIFFONDERE UN DOCUMENTO CHE NON AVEVA LETTO. LA NOSTRA COMMISSIONE HA VOTATO PER DIFFONDERE UN DOCUMENTO CHE AVEVA LETTO». Egli minaccio inoltre di non depositare alcuna relazione, poiche «UNA RELAZIONE SULL’AGENZIA NELLA QUALE L’AGENZIA FACESSE LA STESURA FINALE SAREBBE UNA MENZOGNA»</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO. 13 FEBBRAIO: un giornalista televisivo riconosce pubblicamente di avere ricevuto il testo. 16 FEBBRAIO 1976: ampi estratti compaiono su un settimanale newyorkese sotto il titolo «LA RELAZIONE SULL’AGENZIA CHE IL PRESIDENTE NON VUOLE CHE VOI LEGGIATE». Il testo sara poi pubblicato integralmente IN GRAN BRETAGNA NEL 1977, con introduzione di un ex funzionario dissidente. IL MANDATO DELLA COMMISSIONE SCADDE NEL 1976 SENZA CHE ALCUNA RELAZIONE FOSSE MAI DEPOSITATA, e si registra che UNA RELAZIONE COMPLETA NON E MAI STATA RINVENUTA E POTREBBE NON ESISTERE</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CHE CHIUDE IL CERCHIO, E CHE VA REGISTRATO ACCANTO ALLA DISTRUZIONE DEI REPERTI IN ALTRI CASI: nel marzo 1976 L’AGENZIA SOSTENNE CHE LA COMMISSIONE NON AVESSE RESTITUITO, E NON RIUSCISSE A TROVARE, CIRCA 230 DOCUMENTI da essa consegnati nel corso dell’inchiesta, ALMENO IN PARTE CLASSIFICATI. Il presidente della commissione riferi in aula una minaccia attribuita al consulente legale dell’agenzia — «LA PAGHERA, VEDRETE; LO DISTRUGGEREMO PER QUESTO» — che il consulente nego</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Tomo III — LA FORMA COMPIUTA DELLA SOPPRESSIONE PARLAMENTARE: un organo elettivo vieta a se stesso di pubblicare cio che il proprio comitato ha accertato, subordinando la diffusione al placet dell’ente indagato; la relazione esce comunque per via giornalistica e all’estero; e i documenti istruttori risultano dispersi</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="inlineStr"/>
-      <c r="J122" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K122" s="8" t="inlineStr"/>
-      <c r="L122" s="8" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>LO SCARTO FRA LA RELAZIONE DEL GOVERNO E IL DOCUMENTO DEL GOVERNO — 26 contro 28 novembre 1956</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Per la prima data: relazione del presidente del Consiglio alla Commissione parlamentare d’inchiesta, PROTOCOLLO NUMERO 5099 DEL 17 OTTOBRE 1990, i cui stralci sono stati ripubblicati integralmente. Per la seconda: INDICE GENERALE DEGLI ATTI DELLA COMMISSIONE, X legislatura, consultabile sul portale della Camera</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>LA DISCREPANZA NON E BIBLIOGRAFICA, E QUESTO E IL RITROVAMENTO. La relazione governativa del 17 ottobre 1990 afferma testualmente: «MENTRE LA STRUTTURA DI RESISTENZA CLANDESTINA ITALIANA ERA IN FASE DI AVANZATA COSTITUZIONE, VENNE SOTTOSCRITTO, IN DATA 26 NOVEMBRE 1956, dal SIFAR e dal Servizio americano un accordo relativo alla organizzazione ed alla attivita della rete clandestina post occupazione, accordo comunemente denominato stay-behind, CON IL QUALE FURONO CONFERMATI TUTTI I PRECEDENTI IMPEGNI intervenuti sulla materia tra Italia e Stati Uniti». **Livello A** quanto al testo</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>MA L’INDICE DEGLI ATTI DELLA MEDESIMA COMMISSIONE REGISTRA, FRA I DOCUMENTI RICEVUTI DALLA PRESIDENZA DEL CONSIGLIO: «COPIA DELL’ACCORDO SIFAR-CIA DEL 28 NOVEMBRE 1956, IN LINGUE ITALIANA ED INGLESE, CON LETTERA DI TRASMISSIONE DEL 28.2.91 CHE VINCOLA LA COMMISSIONE A NON DIVULGARE». IL DOCUMENTO CONSEGNATO PORTA DUNQUE UNA DATA DIVERSA DA QUELLA CHE IL GOVERNO AVEVA COMUNICATO AL PARLAMENTO 4 MESI PRIMA. **Livello A** quanto alla registrazione d’indice</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>DUE ELEMENTI ULTERIORI DELLA MEDESIMA RIGA D’INDICE, DA NON PERDERE: la copia fu trasmessa IL 28 FEBBRAIO 1991, cioe 4 MESI DOPO la relazione che lo descriveva; e la lettera di trasmissione VINCOLAVA LA COMMISSIONE A NON DIVULGARE L’ATTO. L’organo d’inchiesta ricevette dunque il documento fondativo con divieto di pubblicarlo</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>COSA NON SI PUO CONCLUDERE, E VA DETTO. Lo scarto di due giorni PUO derivare da distinta datazione delle due sottoscrizioni, da errore di trascrizione nella relazione, o da distinzione fra data di firma e data di protocollo. NESSUNA DELLE 3 E ACCERTATA, E NESSUNA VA PRESUNTA. Cio che e accertato e che LE DUE DATE PROVENGONO ENTRAMBE DALL’ESECUTIVO, in atti distanti 4 mesi: non e una divergenza fra studiosi, ma fra una fonte e se stessa</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Metodologia — E LA MIGLIORE ILLUSTRAZIONE DEL PRINCIPIO ADOTTATO OGGI. Cercare quale delle due date sia falsa avrebbe fatto perdere il fatto: che il racconto ufficiale e il documento ufficiale non coincidono, e che il secondo giunse al Parlamento con divieto di divulgazione. LA DISCREPANZA ERA ESSA STESSA UN DATO</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr"/>
-      <c r="J123" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K123" s="8" t="inlineStr"/>
-      <c r="L123" s="8" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Il procedimento tedesco sull’attentato del 1980 — CRONOLOGIA CHIUSA E 3 FATTI NUOVI</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Archivio federale tedesco, che pubblica in linea i documenti del procedimento; risposta scritta del governo federale all’interrogazione presentata da deputati del gruppo di sinistra, stampato parlamentare 19/22430; comunicato del Bundestag; rassegna coeva</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>LA CRONOLOGIA, ORA CHIUSA. 26 SETTEMBRE 1980, ore 22 e venti: l’ordigno esplode all’ingresso principale, 13 MORTI compreso GUNDOLF KÖHLER e OLTRE 221 FERITI. 27 SETTEMBRE: il procuratore generale federale KURT REBMANN assume la direzione delle indagini — E QUESTO E IL PRIMO FATTO NUOVO — «PER IL FONDATO SOSPETTO DI UN ATTO TERRORISTICO DI GRUPPO». 13 MAGGIO 1981: la commissione speciale del servizio criminale bavarese licenzia un rapporto conclusivo di 187 PAGINE. 23 NOVEMBRE 1982: il procuratore generale chiude il procedimento contro ignoti con un rapporto finale di NOVANTASEI PAGINE. **Livello A**</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>IL PRIMO FATTO NUOVO, NELLA SUA FORMA COMPIUTA: IL CASO FU ASSUNTO DALLA PROCURA FEDERALE PERCHE SI SOSPETTAVA UN GRUPPO, E FU CHIUSO SULLA TESI DELL’AUTORE SINGOLO. Fra le due qualificazioni non intervenne alcuna imputazione</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>IL SECONDO FATTO NUOVO, CHE MUTA IL PESO DELLA DISTRUZIONE DEI REPERTI. I 48 MOZZICONI rinvenuti nei portacenere dell’automobile delGUNDOLF KÖHLER, parcheggiata presso il luogo del fatto, ERANO DI 6 MARCHE DIVERSE, CON E SENZA FILTRO, E VI ERANO STATE RILEVATE TRACCE DI 3 GRUPPI SANGUIGNI DISTINTI. Furono DISTRUTTI NEL FEBBRAIO 1981, 6 mesi dopo l’attentato. NON SI TRATTAVA DUNQUE DI REPERTI GENERICI: ERANO L’UNICA TRACCIA MATERIALE DELLA PRESENZA DI PIU PERSONE NELL’AUTOVETTURA, ed erano incompatibili con la tesi che si sarebbe adottata</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>IL TERZO FATTO NUOVO: da entrambi i rapporti risulta che GLI INQUIRENTI NON TROVARONO, NE NELL’ABITAZIONE NE NELL’AUTOVETTURA, ALCUNA TRACCIA DELL’ESPLOSIVO MILITARE IMPIEGATO NE DELLA COSTRUZIONE DELL’ORDIGNO. E L’ESITO ULTIMO: riaperto il 5 DICEMBRE 2014 su segnalazione di una testimone, il procedimento e stato nuovamente chiuso il 6 LUGLIO 2020 — ma in quella sede LA PROCURA FEDERALE HA ACCERTATO PER LA PRIMA VOLTA LA MOTIVAZIONE DI ESTREMA DESTRA, con la conseguenza giuridica che le vittime possono accedere all’indennizzo previsto per i colpiti da violenza estremistica. QUARANT’ANNI PER LA QUALIFICAZIONE, MAI PER I CORREI</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II — TERMINE DI PARAGONE RAFFORZATO. La forma tedesca non e l’assenza di accertamento ma LA SUA INVERSIONE NEL TEMPO: sospetto di gruppo all’apertura, autore singolo alla chiusura, e quarant’anni dopo il riconoscimento della matrice senza alcun correo. E la distruzione dei reperti colpi precisamente cio che avrebbe potuto contraddire la tesi adottata</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr"/>
-      <c r="J124" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K124" s="8" t="inlineStr"/>
-      <c r="L124" s="8" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Il grado d’appello del processo romano — PRECISAZIONI CHE MUTANO LA LETTURA DEI 3 GRADI</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>5 testate coeve dell’8 LUGLIO 2019 e ricostruzioni successive</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>LA DENOMINAZIONE ESATTA, CHE NON E UN DETTAGLIO: la pronuncia e della PRIMA CORTE D’ASSISE D’APPELLO BIS di Roma. Il termine «bis» indica che un precedente grado d’appello era stato annullato con rinvio, e la circostanza va accertata negli atti perche allunga la catena processuale oltre i 3 gradi comunemente riferiti</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>LA MOTIVAZIONE DEL PRIMO GRADO, CHE E IL VERO OGGETTO DEL RIBALTAMENTO. I giudici di primo grado avevano ritenuto coloro che «HANNO REALIZZATO OPERATIVAMENTE IL SISTEMA DELL’APPARATO REPRESSIVO» responsabili SOLTANTO DEL SEQUESTRO DI PERSONA — reato gia prescritto — E NON ANCHE DELL’OMICIDIO. La condanna colpiva dunque i vertici e mancava gli esecutori, per una qualificazione giuridica e non per difetto di prova. L’appello ha ribaltato precisamente questo</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>SI CHIUDE COSI ANCHE LA DISCREPANZA SUL NUMERO DEGLI IMPUTATI: in primo grado furono 8 ERGASTOLI, 19 ASSOLUZIONI E 6 PROSCIOGLIMENTI PER MORTE DEL REO, per un totale di 33 GIUDICATI. I 37 talora indicati comprendono i 4 brasiliani giudicati in procedimento separato. In appello, 24 condanne su 25 residui</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>ELEMENTO CIVILE DA REGISTRARE: la corte dispose il risarcimento in favore di 47 PARTI CIVILI, con provvisionale esecutiva di UN MILIONE DI EURO ALLA PRESIDENZA DEL CONSIGLIO DEI MINISTRI e somme fra duecentocinquantamila e 100.000 euro alle altre. LA PRESIDENZA DEL CONSIGLIO ERA PARTE CIVILE, e ottenne la provvisionale piu alta: lo Stato italiano si costitui contro gli apparati stranieri che avevano ucciso propri cittadini</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — DUE ACQUISIZIONI. La catena processuale e piu lunga di 3 gradi e va ricostruita sugli atti. E il primo grado non assolse per difetto di prova ma PER QUALIFICAZIONE GIURIDICA, distinguendo mandanti ed esecutori e facendo cadere questi ultimi nella prescrizione: e la medesima forma che il repertorio registra nei casi italiani</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="inlineStr"/>
-      <c r="J125" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K125" s="8" t="inlineStr"/>
-      <c r="L125" s="8" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>La designazione argentina — ULTIMA DISCREPANZA DI DATA CHIUSA, E UN’IMPOSSIBILITA CRONOLOGICA CHE NESSUNA FONTE HA RILEVATO</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Ricostruzione giornalistica che indica gli estremi del decreto; voce enciclopedica di lingua inglese che attribuisce l’atto a un decreto redatto dal ministro degli Esteri argentino con il presidente; SCHEDA DEL SISTEMA ARCHIVISTICO DEL MINISTERO DELLA CULTURA ITALIANO, che e fonte istituzionale</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>LA CHIUSURA: l’atto e il DECRETO NUMERO SETTANTATRE DEL 2 SETTEMBRE 1974, con cui il governo argentino designa l’interessato CONSIGLIERE ECONOMICO DELL’AMBASCIATA IN ITALIA. La collocazione all’agosto proviene da una fonte che accorpa la designazione all’onorificenza, e riguarda dunque atto diverso</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>L’ANOMALIA, CHE E IL VERO RITROVAMENTO E CHE NESSUNA DELLE FONTI SEGNALA. La medesima voce enciclopedica afferma che il decreto d’agosto fu «redatto dal ministro degli Esteri argentino CON IL PRESIDENTE», e comprendeva sia la massima onorificenza sia l’ufficio onorario di consigliere economico. MA QUEL PRESIDENTE ERA MORTO IL PRIMO LUGLIO 1974: un decreto redatto con lui nell’agosto successivo E CRONOLOGICAMENTE IMPOSSIBILE. Delle 3 spiegazioni possibili — redazione anteriore e pubblicazione posteriore, attribuzione erronea, o confusione con l’onorificenza del 1973 — NESSUNA E ACCERTATA. VA REGISTRATA COME ANOMALIA APERTA, NON COME ERRORE DI UNA FONTE. Si segnala inoltre che una ricostruzione italiana colloca la morte del presidente al 10 LUGLIO anziche al primo: SECONDO ERRORE, INDIPENDENTE</t>
-        </is>
-      </c>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>GLI UFFICI, CHE ERANO PIU DI UNO E VANNO DISTINTI: CONSOLE ONORARIO ARGENTINO A FIRENZE, ottenuto nella prima fase; CONSIGLIERE ECONOMICO DELL’AMBASCIATA IN ITALIA dal settembre 1974; e MINISTRO PLENIPOTENZIARIO PER GLI AFFARI CULTURALI, che comportava IMMUNITA DIPLOMATICA. La scheda del sistema archivistico del ministero della Cultura italiano — FONTE ISTITUZIONALE ITALIANA — attesta che «DAL 1973 AL 1980 FU CONSIGLIERE ECONOMICO ACCREDITATO AL GOVERNO ITALIANO E MINISTRO PLENIPOTENZIARIO PER GLI AFFARI CULTURALI». **Livello A**</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>DUE ELEMENTI ULTERIORI DA REGISTRARE: risulta che in Argentina sia stato incolpato di FALSIFICAZIONE DI DOCUMENTI UFFICIALI; e che negli anni Settanta abbia mediato OPERAZIONI TRIANGOLARI SU PETROLIO E ARMAMENTI FRA LIBIA, ITALIA E ARGENTINA attraverso una societa per lo sviluppo economico posseduta con il finanziere poi anch’egli iscritto. Si registra inoltre che il presidente argentino ad interim in carica dal 13 luglio al 12 ottobre 1973 figura fra gli iscritti alla loggia</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — CHIUDE L’ULTIMA DELLE 8 DISCREPANZE DI DATA. E lascia un’anomalia di segno diverso: non due fonti che divergono, MA UNA FONTE CHE COLLOCA UN ATTO DOPO LA MORTE DI CHI L’AVREBBE SOTTOSCRITTO. Va portata agli atti argentini</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="inlineStr"/>
-      <c r="J126" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K126" s="8" t="inlineStr"/>
-      <c r="L126" s="8" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>La sezione sui servizi statunitensi nel capitolo su Brescia — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 250-252</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Proposta di relazione sottoscritta da 9 parlamentari, 22 giugno 2000, paragrafo III.3; fonte primaria interna: interrogatori di un collaboratore del 19 APRILE e 4 MAGGIO 1996</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>IL CONTENUTO, RIFERITO CON ESATTEZZA. Carlo Digilio dichiara che, in base a una direttiva del 1963 volta a fermare il comunismo in Italia, la rete informativa statunitense avrebbe contattato e coordinato elementi di destra disponibili, con l’obbligo di «NON TRALASCIARE DI INFORMARE GLI AMERICANI DI QUALSIASI SITUAZIONE, COME MOVIMENTI DI ARMI ED ESPLOSIVI O ATTENTATI». Dichiara inoltre che «CIRCA 10 GIORNI PRIMA DELLA STRAGE DI BRESCIA», a cena in una trattoria, uno dei presenti disse «CHE DI LI A POCHI GIORNI CI SAREBBE STATO UN GROSSO ATTENTATO TERRORISTICO», e che l’uso della trattoria era «UN SISTEMA IPOCRITA DI FAR FINTA DI ESSERE SOLO UNA COMPAGNIA DI AMICI» per scambiarsi informazioni</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>L’INFERENZA DEI COMMISSARI, DA TENERE DISTINTA DAL DICHIARATO: essi ne traggono che la struttura informativa straniera «ERA STATA AVVERTITA», che «CONOSCEVA L’AREA IN CUI CERCARE AUTORI E MANDANTI», che un suo agente operativo «SVOLSE UN RUOLO NELL’ESECUZIONE», e che non risulta che le autorita italiane fossero avvertite ne che vi fosse intervento per impedire l’attentato. Da cio concludono che «LA STRATEGIA STRAGISTA ERA APPROVATA DAI SUPERIORI». QUEST’ULTIMO PASSAGGIO E UN’INFERENZA DALLA CONOSCENZA AL MANDATO, che la regola dei 3 piani adottata da quest’opera VIETA IN ASSENZA DI PROVA DIRETTA, e va segnalato come tale ogni volta che il brano e citato</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
-        <is>
-          <t>3 CAUTELE CHE NE LIMITANO L’USO. PRIMA: l’intero paragrafo poggia su UN SOLO DICHIARANTE e sui suoi interrogatori; per il criterio di indipendenza genealogica adottato in quest’opera, una fonte e i suoi derivati costituiscono UNA CATENA, non piu fonti. I commissari affermano che le dichiarazioni «HANNO TROVATO UNA SERIE DI RISCONTRI» ma il brano si interrompe prima di esporli: I RISCONTRI VANNO CERCATI E VALUTATI SEPARATAMENTE. SECONDA: si tratta di proposta di gruppo e non di accertamento unanime. TERZA, ED E LA PIU SERIA</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>L’ANOMALIA INTERNA ALLA TESTIMONIANZA, CHE VA VERIFICATA PRIMA DI QUALSIASI USO: il dichiarante attribuisce la direttiva del 1963 a UN GENERALE STATUNITENSE CHE IN QUELL’ANNO DIRIGEVA L’ACCADEMIA MILITARE DI WEST POINT E CHE ASSUNSE IL COMANDO IN ESTREMO ORIENTE SOLTANTO NEL 1964, senza avere mai avuto competenze sulla politica europea. L’ATTRIBUZIONE E QUINDI IMPLAUSIBILE COSI COME RIPORTATA. Puo trattarsi di confusione del dichiarante, di errore di verbalizzazione o di trascrizione; NESSUNA DELLE 3 E ACCERTATA. Un elemento verificabile e implausibile dentro una testimonianza NON LA FALSIFICA INTERAMENTE, MA NE ABBASSA IL GRADO: il paragrafo NON PUO SORREGGERE DA SOLO ALCUNA AFFERMAZIONE, e va portato al livello C finche i riscontri non siano esaminati</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Metodologia — E IL BANCO DI PROVA DEL METODO. E il materiale piu grave incontrato nel corpus e quello su cui il metodo impone la maggiore prudenza: fonte unica, inferenza vietata dai commissari stessi, e un dato interno implausibile. CITARLO SENZA LE 3 CAUTELE SIGNIFICHEREBBE CONSEGNARE ALL’AVVERSARIO IL PUNTO PIU FACILE DELL’INTERA OPERA</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="inlineStr"/>
-      <c r="J127" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K127" s="8" t="inlineStr"/>
-      <c r="L127" s="8" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>LA PARABOLA GIUDIZIARIA DI UNA FONTE — la stessa testimonianza svalutata in un processo e ritenuta attendibile in un altro</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Sentenza di primo grado su piazza Fontana del 30 GIUGNO 2001; successive pronunce d’appello e di legittimita che la annullarono; sentenza di legittimita che annullo le assoluzioni per la strage bresciana; sentenza d’appello bis della Corte d’assise d’appello di MILANO; conferma definitiva del 2017 — DATA ESATTA DA VERIFICARE</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>LA PRIMA FASE. Il 30 GIUGNO 2001 CARLO MARIA MAGGI, DELFO ZORZI e GIANCARLO ROGNONI furono condannati all’ergastolo per la strage milanese del 1969, sulla base sostanziale delle dichiarazioni di CARLO DIGILIO, armiere del gruppo divenuto collaboratore. LA CORTE D’ASSISE D’APPELLO E POI LA CORTE DI CASSAZIONE ANNULLARONO QUELLE CONDANNE «ATTRAVERSO LA SISTEMATICA SVALUTAZIONE» DELLE MEDESIME DICHIARAZIONI. Si registra pero che la pronuncia definitiva su quella strage RIBADI LA RESPONSABILITA di due militanti gia giudicati in precedenza e delle cellule venete dell’organizzazione, i quali non potevano essere nuovamente processati</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA FASE, DI SEGNO OPPOSTO. Nel procedimento sulla strage bresciana del 1974, dopo assoluzioni in primo e secondo grado, LA CORTE DI CASSAZIONE ANNULLO L’ASSOLUZIONE definendo «INGIUSTIFICABILI E SUPERFICIALI» i motivi addotti e soffermandosi sulla «GRAVITA INDIZIARIA» delle dichiarazioni di Digilio. Nel giudizio d’appello bis celebrato a Milano CARLO MARIA MAGGI e MAURIZIO TRAMONTE FURONO CONDANNATI ALL’ERGASTOLO, e in quella sede LE DICHIARAZIONI FURONO PRESE IN CONSIDERAZIONE COME ATTENDIBILI. La condanna e divenuta definitiva</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO, CHE E DEL SISTEMA E NON DELLA FONTE: LE MEDESIME DICHIARAZIONI SONO STATE GIUDICATE INSUFFICIENTI IN UN PROCEDIMENTO E SUFFICIENTI IN UN ALTRO, DALLA MEDESIMA CORTE DI LEGITTIMITA, A UN DECENNIO DI DISTANZA. Non e contraddizione in senso stretto, poiche l’oggetto era diverso e diverso era il compendio dei riscontri; MA E UN DATO CHE VA REGISTRATO OGNI VOLTA CHE QUELLA FONTE E CITATA, perche impedisce tanto di liquidarla quanto di darla per acquisita</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>LA CONSEGUENZA PER LA SEZIONE SUI SERVIZI STATUNITENSI, ED E DECISIVA. La strage bresciana E STATA GIUDIZIARIAMENTE ACCERTATA quanto a mandante ed esecutore, su un compendio che comprendeva quelle dichiarazioni: il paragrafo parlamentare del duemila NON POGGIA DUNQUE SU UNA FONTE GIUDIZIARIAMENTE RIPUDIATA. MA CIO CHE E STATO ACCERTATO SONO LE RESPONSABILITA DEI DUE CONDANNATI: NESSUN COINVOLGIMENTO DI APPARATI STRANIERI E STATO OGGETTO DI ACCERTAMENTO GIUDIZIARIO. La distinzione va tenuta assoluta: la fonte ha retto in giudizio PER CIO CHE IL GIUDIZIO HA DECISO, e non per tutto cio che essa ha dichiarato</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Dominio 10 — DUE REGOLE. La prima: una fonte non e attendibile o inattendibile in assoluto, MA RISPETTO A UN THEMA PROBANDUM, e il suo grado va dichiarato caso per caso. La seconda: che una testimonianza abbia sorretto una condanna NON ESTENDE IL SUO CREDITO ALLE PARTI DI ESSA CHE NESSUN GIUDICE HA VAGLIATO</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="inlineStr"/>
-      <c r="J128" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K128" s="8" t="inlineStr"/>
-      <c r="L128" s="8" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>«IN TERMINI NON GIUDIZIARI MA STORICO-POLITICI» — la formula della Commissione sulla loggia, e la strage annunciata</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Relazione DI MAGGIORANZA della Commissione parlamentare d’inchiesta sulla loggia P2, citata testualmente nella proposta di relazione della Commissione stragi del 22 giugno 2000, pagine 252-253; ordinanza di custodia cautelare, procedimento 6071/95 R.G.</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMULA, TESTUALE E IN 3 PUNTI. «1. La strage dell’Italicus e ascrivibile ad una organizzazione terroristica di ispirazione neofascista o neonazista operante in Toscana; 2. La loggia P2, al cui vertice c’era Licio Gelli, gia implicato nel tentato golpe Borghese, SVOLSE OPERA DI ISTIGAZIONE AGLI ATTENTATI E DI FINANZIAMENTO nei confronti dei gruppi della destra extraparlamentare toscana; 3. La loggia P2 e quindi gravemente coinvolta nella strage dell’Italicus e PUO CONSIDERARSENE ADDIRITTURA RESPONSABILE IN TERMINI NON GIUDIZIARI MA STORICO-POLITICI, quale essenziale retroterra economico, organizzativo e morale». **Livello A** quanto al testo</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>PERCHE E LA FORMULA CHE QUEST’OPERA CERCAVA. Una commissione dello Stato AFFERMA UNA RESPONSABILITA E NE DICHIARA NEL MEDESIMO PERIODO LA NATURA NON GIUDIZIARIA. Non attenua e non esagera: distingue i piani e nomina quello sul quale parla. E LA DISTINZIONE FRA ACCERTAMENTO STORICO E ACCERTAMENTO PENALE, FATTA DALLA FONTE E NON DALL’INTERPRETE — e va adottata come modello di enunciato per l’intera opera. I commissari del 2000 aggiungono che la conclusione puo essere ribadita, «BENCHE LA COMPLESSA VICENDA GIUDIZIARIA ABBIA SINORA CONDOTTO AD ESITI ASSOLUTORI»</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>LA STRAGE ANNUNCIATA — PRIMO PREANNUNCIO. FRANCESCO SGRÒ, poi condannato per calunnia, indusse GIORGIO ALMIRANTE, segretario del MSI, a recarsi, accompagnato dal deputato ALFREDO COVELLI, a recarsi da EMILIO SANTILLO, direttore dell’Ispettorato generale antiterrorismo, per denunciare il timore di un imminente attentato a un treno AD INIZIATIVA DI AMBIENTI UNIVERSITARI ROMANI DI SINISTRA. Successivamente il medesimo RICONOBBE IL CARATTERE CALUNNIOSO DELLE PROPRIE DICHIARAZIONI, affermando di aver tentato con esse DI OTTENERE DENARO DAL PARTITO. L’attentato avvenne, e la matrice accertata fu opposta a quella preannunciata</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>SECONDO PREANNUNCIO: CLAUDIA AIELLO, dipendente del SID con funzioni di interprete, INFILTRATA PER CONTO DEL SERVIZIO NEL PARTITO COMUNISTA E NEGLI AMBIENTI DEGLI ESULI GRECI, sarebbe stata ascoltata pochi giorni prima in una ricevitoria romana pronunciare al telefono frasi quali «LE BOMBE SONO PRONTE», con riferimento a passaporti, treni e due citta. «L’EPISODIO, OGGETTO DI RIPETUTO E ATTENTO ESAME GIUDIZIARIO, NON HA PORTATO A SVILUPPI INDAGATIVI CHE ABBIANO ASSUNTO CONCRETO RILIEVO». I commissari ne traggono soltanto la conferma del «CARATTERE DI STRAGE ANNUNCIATA», e la misura della loro conclusione va conservata</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia e Dominio 7 — DUE ACQUISIZIONI. LA FORMULA DEI DUE PIANI VA ADOTTATA COME STANDARD DI ENUNCIATO. E il primo preannuncio e L’ATTRIBUZIONE FALSA NELLA SUA FORMA PIU ESTREMA: non compiuta dopo il fatto per sviarne le indagini, MA DEPOSITATA PRIMA DEL FATTO PRESSO L’ORGANO DI POLIZIA COMPETENTE. La prova dell’attribuzione falsa, quinto criterio del primo asse, VA ESTESA ALLA FORMA ANTICIPATA</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K129" s="8" t="inlineStr"/>
-      <c r="L129" s="8" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>La vicenda giudiziaria dell’Italicus — L’UNICA CONDANNA RIGUARDA CHI TENTO DI ATTRIBUIRE LA STRAGE PRIMA CHE AVVENISSE</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Sentenze della Corte d’assise di Bologna, della Corte d’assise d’appello di Bologna e della prima sezione della Corte di cassazione; scheda del portale della memoria del Ministero della Cultura; ricostruzioni concordanti</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>LA CRONOLOGIA. Istruttoria conclusa il PRIMO AGOSTO 1980 — una fonte indica il 31 luglio, DISCREPANZA MINORE — cioe IL GIORNO PRECEDENTE LA STRAGE ALLA STAZIONE DI BOLOGNA, e il dato va riportato come coincidenza cronologica e NON come nesso, che nessuna sede ha accertato. 20 LUGLIO 1983: assoluzione per insufficienza di prove di MARIO TUTI, LUCIANO FRANCI e PIERO MALENTACCHI per il capo di strage. 18 DICEMBRE 1986 — una fonte indica il 18 settembre, DISCREPANZA MINORE: la corte d’appello annulla due assoluzioni e infligge due ergastoli a TUTI e FRANCI, assolvendo MALENTACCHI. 16 DICEMBRE 1987: la prima sezione della Corte di cassazione ANNULLA LE CONDANNE. 4 APRILE 1991: assoluzione con formula piena in sede di rinvio. 24 MARZO 1992: la Cassazione la rende definitiva</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO CHE VA POSTO IN PRIMA FILA, E CHE LE RICOSTRUZIONI COLLOCANO IN CODA: L’UNICA CONDANNA DIVENUTA IRREVOCABILE NELL’INTERA VICENDA GIUDIZIARIA DELL’ITALICUS E QUELLA PER CALUNNIA, A UN ANNO E 5 MESI, INFLITTA A FRANCESCO SGRÒ, CHE AVEVA DEPOSITATO PRIMA DEL FATTO L’ATTRIBUZIONE FALSA presso il direttore dell’Ispettorato antiterrorismo. 12 MORTI E 44 FERITI NON HANNO PRODOTTO ALCUNA CONDANNA; L’ATTRIBUZIONE FALSA SI. **Livello A**</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>LA MOTIVAZIONE DEL GRADO D’APPELLO, POI ANNULLATA, DA REGISTRARE PERCHE ESISTE: la corte inquadro l’attentato come opera di «UN’ORGANIZZAZIONE DI ESTREMA DESTRA, VEROSIMILMENTE DI AREA ORDINOVISTA, LEGATA AD AMBIENTI GOLPISTI QUALI LA LOGGIA MASSONICA P2». L’annullamento fu pronunciato dalla prima sezione presieduta dal presidente CORRADO CARNEVALE, su richiesta del sostituto procuratore generale. DIVIETO ESPRESSO: nessuna inferenza va tratta da questa identificazione, che e riportata perche e un fatto processuale e non perche suggerisca alcunche</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>UNA DISCREPANZA CHE COINVOLGE UNA FONTE ISTITUZIONALE: il portale della memoria del Ministero della Cultura italiano colloca l’assoluzione definitiva NEL 1993, mentre tutte le altre fonti consultate indicano il 24 MARZO 1992. VA RISOLTA SULL’ATTO, e va segnalata perche una fonte pubblica statale che diverge di un anno su una sentenza definitiva e essa stessa un dato</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 7 e Dominio 10 — DUE ACQUISIZIONI. L’Italicus e fra le 9 stragi della direttiva del 2014 e resta senza colpevoli. E la forma che il repertorio registra decine di volte vi raggiunge la propria espressione piu netta: L’ORDINAMENTO HA PUNITO IL DEPISTAGGIO PREVENTIVO E NON LA STRAGE</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="inlineStr"/>
-      <c r="J130" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K130" s="8" t="inlineStr"/>
-      <c r="L130" s="8" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>LE DUE FORME DEL DEPISTAGGIO A CONFRONTO — Italicus e Bologna, e il fatto piu forte del repertorio</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Corte suprema di cassazione, SEZIONI UNITE PENALI, udienze del 22 e 23 NOVEMBRE 1995, sentenza pubblicata a cura dell’associazione dei familiari delle vittime; sentenze del processo piu recente sulla medesima strage</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO, E VA ENUNCIATO PER INTERO PERCHE E IL PIU FORTE CHE QUEST’OPERA POSSA CITARE. Con sentenza definitiva delle Sezioni Unite del 23 NOVEMBRE 1995 sono stati condannati per CALUNNIA CONTINUATA E PLURIAGGRAVATA, «PER AVERE, IN CONCORSO TRA LORO E CON PIU AZIONI ESECUTIVE DI UN MEDESIMO DISEGNO CRIMINOSO, DIVULGATO ALCUNE INFORMATIVE FATTE PERVENIRE AGLI INQUIRENTI»: DUE UFFICIALI IN SERVIZIO DEL SISMI — il generale PIETRO MUSUMECI a 8 anni e 5 mesi e il colonnello GIUSEPPE BELMONTE a 7 anni e 11 mesi; FRANCESCO PAZIENZA, collaboratore del direttore generale del medesimo servizio, a 10 anni; e LICIO GELLI, capo della loggia P2,, a 10 anni. **Livello A**</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>L’AGGRAVANTE, CHE E LA PARTE DECISIVA E CHE LE SINTESI OMETTONO: la calunnia fu ritenuta AGGRAVATA DALLA FINALITA DI TERRORISMO ai sensi dell’articolo primo della legge 6 FEBBRAIO 1980 NUMERO 15, e commessa AL FINE DI ASSICURARE L’IMPUNITA AGLI AUTORI DELLA STRAGE. LA CORTE SUPREMA DELLO STATO HA DUNQUE ACCERTATO IN VIA DEFINITIVA CHE UFFICIALI IN SERVIZIO DEL PROPRIO SERVIZIO INFORMATIVO MILITARE COMMISERO CALUNNIA CON FINALITA DI TERRORISMO PER PROTEGGERE GLI AUTORI DI UNA STRAGE. Non e un’ipotesi storiografica: e un giudicato</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>IL CONFRONTO CON L’ALTRO CASO, CHE DEFINISCE DUE FORME DISTINTE. Nell’Italicus il depistaggio fu PREVENTIVO — l’attribuzione falsa depositata presso l’organo di polizia PRIMA del fatto, da un privato che agiva per denaro — e produsse L’UNICA CONDANNA DELL’INTERA VICENDA, un anno e 5 mesi, mentre la strage resta senza colpevoli. A Bologna il depistaggio fu SUCCESSIVO E ISTITUZIONALE — informative false diramate DOPO il fatto DA APPARATI DELLO STATO — e produsse condanne definitive ACCANTO a quelle per la strage</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMA NON SI E ESAURITA: nel procedimento piu recente sulla medesima strage sono divenute definitive la condanna di il carabiniere PIERGIORGIO SEGATEL a 6 anni per depistaggio e quella di DOMENICO CATRACCHIA a 4 anni per false informazioni al pubblico ministero. IL DEPISTAGGIO SULLA MEDESIMA STRAGE E STATO GIUDICATO IN DUE ONDATE A DISTANZA DI TRENT’ANNI</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II e Dominio 3 — 3 ACQUISIZIONI. PRIMA: il capitolo sull’arco di sponda va rafforzato con questo giudicato, che non descrive una prossimita ma una CONDANNA. SECONDA: la coppia Italicus-Bologna fornisce DUE TIPI del depistaggio, preventivo-privato e successivo-istituzionale, e la tipologia va costruita su di essi. TERZA, E LA PIU IMPORTANTE: quest’opera NON HA BISOGNO DI IPOTIZZARE il coinvolgimento di apparati statali nella copertura delle stragi, PERCHE SU UN CASO E STATO ACCERTATO IN VIA DEFINITIVA DALLE SEZIONI UNITE. Cio che resta ipotetico e l’estensione ad altri casi, e come tale va dichiarato</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="inlineStr"/>
-      <c r="J131" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K131" s="8" t="inlineStr"/>
-      <c r="L131" s="8" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>«STRAGE ATLANTICA DI STATO» — il passo piu grave del corpus e il piu fragile, e la ragione e la stessa</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo I.5, pagine 230-232; fonte primaria interna: dichiarazioni di Digilio, interrogatorio del 17 MAGGIO 1997; nota del testo: «parte di queste considerazioni sono contenute nella sentenza-ordinanza del giudice istruttore, paragrafo 4»</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>IL CONTENUTO, RIFERITO CON ESATTEZZA E SENZA ATTENUAZIONI. Il testo descrive una struttura informativa con sede presso il comando alleato di Verona, alle dipendenze del sedicente capitano DAVID CARRETT, alla quale sarebbero appartenuti 4 elementi organicamente inseriti nell’organizzazione neofascista veneta o suoi referenti. Sostiene che Carrett, informato in anticipo di un attentato in preparazione, ANZICHE IMPEDIRLO RACCOMANDO DI RIDURNE LA POTENZIALITA, e che si congratulo poi ricordando che «la struttura vedeva di buon occhio azioni dimostrative, ma non accettava massacri indiscriminati». Sostiene inoltre che Carrett fu informato CON QUALCHE GIORNO DI ANTICIPO degli attentati del 12 dicembre 1969 e «NON FECE NULLA PER SCONGIURARE L’ATTENTATO», e che non intervenne neppure per i due attentati successivi. E ne trae la formula: non soltanto «strage di Stato» ma «STRAGE ATLANTICA DI STATO»</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>LA RAGIONE DELLA FRAGILITA, ED E DECISIVA. L’INTERO PASSO POGGIA SULLE DICHIARAZIONI DEL SOLO CARLO DIGILIO. E QUELLE DICHIARAZIONI, PROPRIO NEL PROCEDIMENTO SULLA STRAGE MILANESE DEL 1969 — CIOE ESATTAMENTE IL FATTO DI CUI QUESTO PASSO TRATTA — FURONO OGGETTO DI «SISTEMATICA SVALUTAZIONE» DA PARTE DELLA CORTE D’APPELLO E POI DELLA CORTE DI CASSAZIONE, CHE ANNULLARONO LE CONDANNE FONDATE SU DI ESSE. Sul diverso fatto della strage bresciana le medesime dichiarazioni sono state invece ritenute attendibili e hanno sorretto condanne definitive. VALE DUNQUE LA REGOLA STABILITA IN QUESTO REPERTORIO: UNA FONTE E ATTENDIBILE RISPETTO A UN THEMA PROBANDUM, E QUESTO E IL THEMA SUL QUALE NON HA RETTO</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>3 ULTERIORI LIMITI. PRIMO: si tratta di proposta sottoscritta da 9 parlamentari e non di accertamento unanime della Commissione. SECONDO: la nota rinvia a una SENTENZA-ORDINANZA DEL GIUDICE ISTRUTTORE GUIDO SALVINI, che e atto istruttorio e non decisione definitiva, e il cui esito successivo e quello sopra descritto. TERZO: L’IDENTIFICAZIONE DI DAVID CARRETT, sulla cui esistenza e qualifica la letteratura ha sollevato interrogativi mai chiusi, VA VERIFICATA PRIMA DI OGNI USO e non va data per acquisita</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>LA FORMULA, PER CIO CHE E: «strage atlantica di Stato» E UNA CARATTERIZZAZIONE STORICO-POLITICA PROPOSTA DA 9 PARLAMENTARI NEL DUEMILA, NON UN ACCERTAMENTO GIUDIZIARIO. Va citata soltanto con l’attribuzione esplicita e con la qualificazione del suo statuto, esattamente come la Commissione sulla loggia distinse i «termini non giudiziari ma storico-politici». Chi la citasse come fatto accertato COMMETTEREBBE L’ERRORE CHE LA FONTE STESSA, IN ALTRA SEDE, HA EVITATO</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — LIVELLO C, E VA MANTENUTO. E il passo che la pubblicistica citerebbe per primo ed e quello che quest’opera deve citare per ultimo, con tutte e 4 le cautele. Registrarlo e doveroso; usarlo come prova sarebbe consegnare all’avversario la falla piu larga dell’intera costruzione</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr"/>
-      <c r="J132" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K132" s="8" t="inlineStr"/>
-      <c r="L132" s="8" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>PETEANO — il solo caso giunto a giudicato, e la ragione per cui vi giunse</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo IV.2, pagine 171-173; deposizione del colonnello DINO MINGARELLI del 14 MARZO 1990, atti pp. 1394-1395; atti di assise p. 59 e istruttoria p. 445</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>LA PRECISAZIONE DELLA COMMISSIONE, DA ADOTTARE: l’attentato «CON QUALCHE IMPROPRIETA VIENE ANNOVERATO NELLA PUBBLICISTICA TRA GLI EVENTI DI STRAGE». Il 31 MAGGIO 1972 una Fiat 500 imbottita di esplosivo fu abbandonata in un bosco presso Peteano di Sagrado, in provincia di Gorizia; alcuni colpi di pistola contro il parabrezza e una telefonata anonima richiamarono una pattuglia dei carabinieri; all’apertura del cofano l’ordigno esplose UCCIDENDO 3 MILITARI E FERENDONE GRAVEMENTE UN QUARTO. Obiettivo specifico e non indiscriminato: NON E TECNICAMENTE UNA STRAGE, e quest’opera non deve chiamarlo tale</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>LA FRASE CHE DEFINISCE IL CASO: e «uno degli episodi attribuiti alla destra radicale per i quali in sede giudiziaria si e giunti ad una conclusione di colpevolezza passata in giudicato, RESA POSSIBILE DALLA AMMISSIONE DI RESPONSABILITA DELL’ESECUTORE». VINCENZO VINCIGUERRA CONFESSO NEL 1984, DODICI ANNI DOPO. IL SOLO CASO CHE ABBIA PRODOTTO UN GIUDICATO NON FU RISOLTO DALL’INDAGINE MA DALLA CONFESSIONE SPONTANEA DI CHI L’AVEVA COMPIUTO</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>LA PRIMA PISTA FALSA, E IL SUO MECCANISMO. La «pista rossa» punto su un nucleo di Lotta Continua e poggiava su presunte affermazioni che il collaboratore MARCO PISETTA avrebbe reso al colonnello MICHELE SANTORO, comandante del Gruppo carabinieri di Trento. MA SIA I MAGISTRATI PRESENTI ALL’INCONTRO SIA PISETTA STESSO HANNO SMENTITO CHE EGLI ABBIA MAI PARLATO DI PETEANO. La velina fu trasmessa «IN MANIERA DEL TUTTO ANOMALA — FUOR DI PROTOCOLLO, TRAMITE CORRIERE E SOPRATTUTTO SENZA SEGUIRE LE VIE GERARCHICHE» al colonnello DINO MINGARELLI, comandante della Legione di Udine, DAL GENERALE PALUMBO, comandante della Divisione Pastrengo di Milano, CHE SI ERA PRECIPITATO A GORIZIA GIA IL 1 GIUGNO 1972, il giorno dopo. Mingarelli depose: «QUELLA FU L’ORIGINE DELLA COSIDDETTA PISTA ROSSA; IO SAPEVO CHE QUELLE NOTIZIE ARRIVAVANO DA TRENTO E CHE LA FONTE CONFIDENZIALE ERA MARCO PISETTA». **Livello A** quanto alla deposizione</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>LA SECONDA PISTA FALSA E L’ORDINE RIFERITO. La «pista gialla» poggiava anch’essa su pretese affermazioni di un informatore dei carabinieri CHE DAVANTI ALLA CORTE RIFIUTO DI RICONOSCERE LE AFFERMAZIONI ATTRIBUITEGLI; riguardava piccoli pregiudicati locali sottoposti FRA IL 1974 E IL 1979 a lunghe indagini e vari giudizi PRIMA CHE FOSSE PROVATA LA LORO INNOCENZA. E «tutti gli indizi a sostegno di una pista nera furono ignorati o scartati: CI SAREBBE ANZI ADDIRITTURA STATO UN PRECISO ORDINE DI BLOCCARE OGNI INDAGINE SUGLI AMBIENTI DI DESTRA» — quest’ultima circostanza riferita al condizionale DALLA FONTE STESSA e da mantenere tale</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 3 e Metodologia — TERZO TIPO DI DEPISTAGGIO, che completa la tipologia. Non preventivo come nell’Italicus, non per informative false diramate dopo il fatto come a Bologna, MA PER COSTRUZIONE DI PISTE FONDATE SU DICHIARAZIONI ATTRIBUITE A INFORMATORI CHE LE HANNO POI NEGATE, veicolate fuori protocollo e fuori gerarchia. E la conclusione che il caso impone: NELL’UNICO EPISODIO GIUNTO A GIUDICATO, L’ORDINAMENTO NON HA SCOPERTO NULLA — GLI E STATO DETTO</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="inlineStr"/>
-      <c r="J133" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K133" s="8" t="inlineStr"/>
-      <c r="L133" s="8" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>DA PETEANO A GLADIO — il depistaggio del perito del tribunale e la catena che ne discende</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Inchieste del giudice istruttore FELICE CASSON presso il Tribunale di Venezia; condanne definitive; rivelazione di VINCENZO VINCIGUERRA del 1984; ricostruzione su rivista accademica; testimonianza dello stesso Casson resa nel 2024</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>LE VITTIME, CHE VANNO NOMINATE: i carabinieri ANTONIO FERRARO, DONATO POVEROMO e FRANCO DONGIOVANNI, uccisi il 31 maggio 1972 nell’aprire il cofano; due i feriti gravi. Condanne definitive: ERGASTOLO a VINCENZO VINCIGUERRA e CARLO CICUTTINI; da 4 a 6 anni ad altri tre militanti locali; 3 anni e 9 mesi a ENO PASCOLI e 11 mesi a LILIANA DE GIOVANNI</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>IL DEPISTAGGIO ACCERTATO E SANZIONATO, che distingue questo caso da tutti gli altri: l’inchiesta bis di Casson ACCERTO L’ATTIVITA DEPISTATORIA DEGLI INQUIRENTI, e le condanne divennero DEFINITIVE per DINO MINGARELLI — nel frattempo divenuto generale — per il colonnello ANTONINO CHIRICO e per il maresciallo GIUSEPPE NAPOLI. **Livello A**</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>IL PERITO, ED E LA FORMA PIU PURA DEL TERZO TIPO: MARCO MORIN, perito balistico ed esplosivistico del Tribunale di Venezia E MEMBRO DI ORDINE NUOVO, fornì deliberatamente UNA PERIZIA FALSA, sostenendo che l’esplosivo impiegato fosse dello stesso tipo usato dalle Brigate Rosse. Casson dimostro che si trattava invece di C4, in uso alla NATO. MORIN FU RINVIATO A GIUDIZIO E CONDANNATO. UN CONSULENTE TECNICO NOMINATO DAL TRIBUNALE, AFFILIATO ALL’ORGANIZZAZIONE DEGLI ESECUTORI, FALSIFICO LA PERIZIA PER ATTRIBUIRE L’ESPLOSIVO ALLA PARTE OPPOSTA</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>LA CATENA VERSO GLADIO, CON IL SUO PUNTO CONTESO. A pochi chilometri da Peteano era emerso, pochi mesi prima, un NASCO — deposito clandestino di armi — presso AURISINA, che si scopri appartenere a Gladio. Casson sostenne la tesi giudiziaria che l’esplosivo provenisse da quel deposito; TESI NON CONDIVISA DAL GIUDICE ISTRUTTORE GUIDO SALVINI, secondo il quale NON VI ERANO PROVE CERTE di tale provenienza: DUE MAGISTRATI INQUIRENTI IN DISACCORDO, E IL PUNTO VA MANTENUTO CONTESO. Resta accertato che DA QUESTA INCHIESTA PRESE AVVIO QUELLA CHE PORTO ALLA RIVELAZIONE DELLA RETE STAY-BEHIND</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>DUE ELEMENTI ULTERIORI. PRIMO, riferito da Vinciguerra nel 1984 e come tale attribuito: il segretario del MSI GIORGIO ALMIRANTE avrebbe fatto pervenire 35.000 DOLLARI a Cicuttini, latitante in Spagna, per un intervento alle corde vocali che ne alterasse la voce — Cicuttini aveva effettuato la telefonata anonima. ALMIRANTE USUFRUI DELL’AMNISTIA PRIMA DELL’INIZIO DEL PROCESSO. SECONDO, dalla testimonianza di Casson: all’arresto di Mingarelli e Chirico «si scateno l’inferno», e «DAL GIORNO SUCCESSIVO, SENZA DIRMI NULLA, SCOMPARVERO I CARABINIERI DELLA SCORTA che quotidianamente mi accompagnavano in ufficio». **Livello B**, testimonianza personale</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 3, 9 e 10 — CHIUDE LA TIPOLOGIA DEL DEPISTAGGIO E APRE LA CATENA. Peteano non e soltanto il caso in cui la verita emerse per confessione: E IL CASO IN CUI IL DEPISTAGGIO FU ACCERTATO E PUNITO IN VIA DEFINITIVA A CARICO DI TRE UFFICIALI E SOTTUFFICIALI DELL’ARMA E DI UN PERITO DEL TRIBUNALE. Ed e il caso da cui, per via giudiziaria e non politica, emerse l’esistenza della rete clandestina</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="J134" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K134" s="8" t="inlineStr"/>
-      <c r="L134" s="8" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>IL NASCO DI AURISINA — ritrovamento, occultamento e distruzione dei reperti, con accertamento parlamentare</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>PRIMO RAPPORTO DEL COMITATO PARLAMENTARE, 6 APRILE 1995, consultabile in linea; relazione della Commissione stragi; cronaca coeva del 25-26 febbraio e dell’11 marzo 1972; ordinanze del giudice istruttore CARLO MASTELLONI del 30 OTTOBRE, 2 e 6 NOVEMBRE 1990</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>IL RITROVAMENTO. Il 24 FEBBRAIO 1972 il deposito denominato NASCO 203, occultato fra il 1963 e il 1970 in un bunker della Grande Guerra sul Carso triestino, FU SCOPERTO PER CASO DA DUE RAGAZZI QUATTORDICENNI che raccoglievano cimeli militari, hobby allora diffuso fra i giovani della zona. Il 3 MARZO i carabinieri della tenenza di Aurisina, perlustrando, ne rinvennero un secondo a circa mezzo chilometro. L’anfratto distava UN CENTINAIO DI METRI DALLA CASERMA DEI CARABINIERI e pochi chilometri dal confine</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>L’INVENTARIO, secondo l’elenco fornito dai carabinieri per il secondo ritrovamento: 2 pistole Star, 6 bombe a frattura prestabilita, 2 bombe al fosforo, un binocolo, 100 cartucce, 2 fondine da spalla, 6 torce e ISTRUZIONI PER CIASCUN OGGETTO. La stampa coeva riferi, per il complesso dei rinvenimenti, 5 grosse cariche di dinamite, 15 chili di plastico, 200 metri di miccia, 90 matite esplosive, decine di detonatori e DUE BOMBE A TEMPO UGUALI A QUELLE USATE PER GLI ATTENTATI ALLA FIERA DI MILANO E SUI TRENI — quest’ultimo dato di fonte giornalistica, DA RISCONTRARE</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>L’ACCERTAMENTO PARLAMENTARE, CHE E LA PARTE DECISIVA E VA CITATA TESTUALMENTE: «Il materiale rinvenuto apparteneva SICURAMENTE alla struttura Gladio. E CERTO CHE IL SID, in relazione a questo ritrovamento, INVIO I PROPRI EMISSARI A TRIESTE E AD AURISINA, sia presso il proprio Centro CS sia presso i locali Comandi dei carabinieri. OCCORREVA IMMEDIATAMENTE INTERVENIRE PER OCCULTARE LE FINALITA DEL DEPOSITO di armi e di esplosivi, ma anche perche NON VENISSERO EFFETTUATI CONTROLLI SULLA QUANTITA E SULLE CARATTERISTICHE DEI MATERIALI». E sulla distruzione: «L’ESPLOSIVO FU FATTO BRILLARE PERCHE, SI DISSE, ERA INSTABILE. MA QUEL PARTICOLARE TIPO DI ESPLOSIVO ERA TUTTO FUORCHE INSTABILE. QUEL CHE INTERESSAVA ERA DISTRUGGERE TUTTI GLI ELEMENTI CHE POTESSERO CONDURRE AL SID». **Livello A**</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>LE DUE PENDENZE CHE SI CHIUDONO. PRIMA: lo smantellamento della rete dei depositi FU DECISO PROPRIO IN CONSEGUENZA DI QUESTO RINVENIMENTO FORTUITO, e le operazioni di recupero cominciarono NELL’APRILE 1972. SECONDA: i 12 depositi mai recuperati furono oggetto delle ORDINANZE DEL GIUDICE ISTRUTTORE DI VENEZIA DEL 30 OTTOBRE, 2 E 6 NOVEMBRE 1990, emesse NELL’AMBITO DELL’INCHIESTA SULLA CADUTA DELL’AEREO ARGO 16, con incarico ai Comandi dei carabinieri di ricercarli e dissotterrarli. Fra i motivi del mancato recupero figura, per un deposito friulano, che il pronao della chiesetta sotto il quale era collocato ERA STATO PAVIMENTATO NEL 1972</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CRONOLOGICO, DA RIPORTARE COME TALE E NON COME NESSO: il deposito fu scoperto il 24 FEBBRAIO 1972, lo smantellamento della rete inizio NELL’APRILE 1972, L’ATTENTATO DI PETEANO AVVENNE IL 31 MAGGIO 1972 — a pochi chilometri, e DURANTE L’OPERAZIONE DI RECUPERO. Se l’esplosivo provenisse da quel deposito e questione contesa fra due magistrati inquirenti e NON VA RISOLTA QUI. VA INOLTRE REGISTRATA, A LIVELLO C E COME CONTESTATA, la versione riferita nel 1991 secondo cui il ritrovamento sarebbe opera di un brigadiere di pubblica sicurezza poi internato e morto nel 1975: e affermazione di fonte indiretta, incompatibile con la versione ufficiale, e non riscontrata</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 3 e 9 — E IL SECONDO CASO, DOPO MONACO, IN CUI LA DISTRUZIONE DEI REPERTI E ACCERTATA E MOTIVATA. A Monaco 504 reperti furono distrutti «per mancanza di spazio»; ad Aurisina l’esplosivo fu fatto brillare «perche instabile». IN ENTRAMBI I CASI LA GIUSTIFICAZIONE E STATA SMENTITA DA UN ORGANO DELLO STATO, e in questo caso l’organo dichiara anche il fine</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="J135" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K135" s="8" t="inlineStr"/>
-      <c r="L135" s="8" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>VERIFICA DEL VOLUME ZERO, PARTE VII — misura quantitativa e sette errori accertati</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Esame diretto del file VOLUME_ZERO_V59_PARTE_VII_NATO_GLADIO presente nei file di progetto, datato maggio 2026; confronto con le fonti verificate nel presente repertorio</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>LA MISURA. Il testo consta di 6.159 PAROLE. Vi ricorrono 214 volte le forme «articola» e «articolato» — UNA OGNI 29 PAROLE — 107 volte «dispositivo», 111 volte «apparato», 68 volte «strutturale», 32 volte «di rilevanza primaria» e altrettante «di rilevanza assoluta», e 45 VOLTE LA PAROLA INGLESE «FOUNDATIONAL» IN UN TESTO ITALIANO. Le frasi sono 108, di lunghezza media 55 parole e massima 293; VENTISETTE DI ESSE COMINCIANO CON UNA DELLE MEDESIME QUATTRO FORMULE</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>IL DATO CHE DECIDE, ED E UN RAPPORTO. I gradi probatori assegnati sono: 56 VOLTE «SAVONA A», 3 VOLTE «SAVONA B», ZERO VOLTE «SAVONA C». In un sistema nel quale il grado A richiede la convergenza di tre fonti indipendenti di natura diversa, UNA DISTRIBUZIONE DEL 95 PER CENTO SUL GRADO MASSIMO NON E UNA GRADUAZIONE: E UN ORNAMENTO. Una valutazione effettiva di questo materiale produrrebbe necessariamente una dispersione</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>GLI ERRORI ACCERTATI PER CONFRONTO CON QUESTO REPERTORIO. PRIMO E PIU GRAVE: il deposito di Aurisina e dato «localizzato il 24 GENNAIO 1992» e marcato «Savona A integrale», MENTRE IL RITROVAMENTO AVVENNE IL 24 FEBBRAIO 1972 — venti anni e un mese di scarto, SU UNA RIGA CHE PORTA IL GRADO PROBATORIO MASSIMO. SECONDO: l’accesso agli archivi del servizio militare e collocato a FORTE BOCCEA anziche a Forte Braschi, rettifica gia pendente e non applicata. TERZO: i 3.000 uomini sono dati per fatto, mentre la cifra proviene da appunto privo di data ed e stata contestata sotto giuramento</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>QUARTO: e citato come atto il documento «NSC 6014/1 del 19 aprile 1961», NON REPERIBILE nella verifica condotta. QUINTO: il manuale FM 30-31B e dato per autentico, «firmato dal generale W.» e fonte di una «dottrina di Westmoreland delle operazioni false», MENTRE IL DOCUMENTO E DI STATUTO CONTESO E L’ATTRIBUZIONE A QUEL GENERALE E LA MEDESIMA CHE, IN ALTRA FONTE VERIFICATA OGGI, RISULTA CRONOLOGICAMENTE IMPLAUSIBILE. SESTO: i 731 enucleandi sono dati per fatto, mentre la relazione di minoranza indica non meno di 1.100-1.200. SETTIMO: l’accordo del 1956 e datato al 26 novembre senza segnalare che il documento consegnato al Parlamento reca il 28</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>LA CONCLUSIONE, CHE E OPERATIVA E NON STILISTICA. Il piano dell’opera prevedeva due sole opzioni: riverificare riga per riga, oppure dichiarare il materiale preparatorio non pubblicabile. LA MISURA SCEGLIE: in 6.159 parole le asserzioni fattuali distinte sono nell’ordine della quindicina, IL RESTO E TESSUTO CONNETTIVO GENERATO. Non vi e nulla da verificare riga per riga, perche le righe in massima parte NON CONTENGONO AFFERMAZIONI. Le quindici asserzioni sono gia contenute, verificate e datate in questo repertorio; SETTE DI ESSE VI RISULTANO ERRATE</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="inlineStr"/>
-      <c r="J136" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K136" s="8" t="inlineStr"/>
-      <c r="L136" s="8" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>ESTENSIONE DELLA DIAGNOSTICA AI REGISTRI MAGGIORI — quanto e affetto e quanto no</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Misurazione diretta sui file di uscita del progetto: quattro registri federati e unificati fra 1,7 e 2,1 milioni di parole; tredici versioni del registro analitico sul caso Moro; medesimi indicatori applicati al Volume Zero</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>IL PRIMO RISULTATO, CHE ESTENDE IL PROBLEMA. I quattro registri maggiori recano ciascuno ESATTAMENTE 299 OCCORRENZE DELLA PAROLA INGLESE «FOUNDATIONAL» — cifra identica al totale delle sette parti del Volume Zero. NE SEGUE CHE IL VOLUME ZERO E INCORPORATO ALLA LETTERA IN CIASCUNO DI ESSI. E la distribuzione dei gradi vi si riproduce su scala venti volte maggiore: nelle due versioni piu recenti 4.968 assegnazioni di livello A, 340 di livello B, 25 di livello C — IL 93 PER CENTO SUL GRADO MASSIMO, IDENTICO AL VALORE MISURATO SUL VOLUME ZERO</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>IL SECONDO RISULTATO, CHE E UNA BUONA NOTIZIA E VA DETTA CON LA STESSA PRECISIONE. LE TREDICI VERSIONI DEL REGISTRO ANALITICO SUL CASO MORO NON RECANO ALCUNA DELLE TRE FIRME: zero occorrenze di «foundational», densita nulla delle forme «articolato», E NESSUN GRADO SAVONA ASSEGNATO — ne A, ne B, ne C. Il corpus sul caso Moro, che costituisce la parte piu estesa dell’opera scritta, E INDENNE DALLA PATOLOGIA e non eredita alcun grado non verificato</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>IL TERZO RISULTATO, CHE RIGUARDA IL VERSIONAMENTO. Le versioni 69 e 70 recano CONTEGGI DI GRADO IDENTICI — 4.968, 340 e 25 — pur differendo di oltre centomila parole. Le versioni 67 e 68 recano parimenti conteggi identici pur differendo di quattromila parole. NE SEGUE CHE IL MATERIALE AGGIUNTO A OGNI NUOVA VERSIONE NON PORTA ALCUNA VALUTAZIONE PROBATORIA: i registri crescono senza che cresca il numero delle affermazioni graduate</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>LA DELIMITAZIONE, CHE E IL PUNTO DI QUESTA VOCE. La patologia NON riguarda l’intero corpus: riguarda IL VOLUME ZERO E I QUATTRO REGISTRI CHE LO INCORPORANO. Ne restano fuori il corpus sul caso Moro, il repertorio delle fonti, i capitoli dimostrativi e l’apparato metodologico, che sono stati costruiti interrogando documenti e recano graduazione dichiarata caso per caso</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — CONSEGUENZA OPERATIVA. La dichiarazione sullo statuto del Volume Zero VA ESTESA ALLE PORZIONI DEI QUATTRO REGISTRI CHE LO INCORPORANO, identificabili con precisione perche recano la firma lessicale. Non va estesa al resto, e SOSTENERE CHE L’INTERO CORPUS SIA COMPROMESSO SAREBBE, ESSO STESSO, UNA GENERALIZZAZIONE NON MISURATA</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="inlineStr"/>
-      <c r="J137" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K137" s="8" t="inlineStr"/>
-      <c r="L137" s="8" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>RETTIFICA ALLA DELIMITAZIONE — la firma lessicale e confinata, la graduazione probatoria no</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Misurazione per segmentazione del registro unificato piu recente, 2.081.170 parole: separazione della regione contenente la firma lessicale dal resto e conteggio separato dei gradi</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>LA RETTIFICA, DOVUTA E IMMEDIATA. Due voci addietro questo repertorio ha affermato che la patologia riguarda «il Volume Zero e i quattro registri che lo incorporano», e che le porzioni affette sono identificabili perche recano la firma lessicale. LA PRIMA META E ESATTA, LA SECONDA E FALSA, E LA MISURA LO DIMOSTRA</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>LA LOCALIZZAZIONE DELLA FIRMA LESSICALE, CHE E CONFERMATA: tutte e 299 le occorrenze di «foundational» cadono nel medesimo decile, fra il 66 e il 68 per cento del documento; la regione misura 424.135 caratteri, pari al 2 PER CENTO del registro e a 49.387 parole — cioe esattamente il Volume Zero, incorporato come blocco contiguo. IL TESTO GENERATO E DUNQUE CHIRURGICAMENTE ISOLABILE</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>MA LA GRADUAZIONE E IDENTICA DENTRO E FUORI, ED E IL DATO CHE ROVESCIA LA CONCLUSIONE PRECEDENTE. Nella regione del Volume Zero: 360 assegnazioni di livello A, 25 di livello B, ZERO di livello C — 93 per cento sul grado massimo. NEL RESTANTE 98 PER CENTO DEL REGISTRO, due milioni e trentunomila parole: 4.608 assegnazioni di livello A, 315 di livello B, 25 di livello C — 93 PER CENTO SUL GRADO MASSIMO. LE DUE DISTRIBUZIONI COINCIDONO FINO AL PUNTO PERCENTUALE</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>LA CONSEGUENZA ARITMETICA: rimuovendo integralmente il Volume Zero si eliminano 360 assegnazioni di livello A SU 4.968, PARI AL 7 PER CENTO. NE RESTANO 4.608 IN MATERIALE PRIVO DELLA FIRMA LESSICALE. La dichiarazione sullo statuto del Volume Zero, adottata oggi, RISOLVE DUNQUE IL SETTE PER CENTO DEL PROBLEMA DI GRADUAZIONE, e non la sua totalita</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>LA DISTINZIONE CHE VA MANTENUTA, E CHE IMPEDISCE UNA CONCLUSIONE CATASTROFICA. Cio che la misura accerta riguarda LA GRADUAZIONE, NON IL CONTENUTO. Due milioni di parole possono contenere materiale eccellente e affermazioni vere: cio che non e credibile e IL GRADO CHE VI E STATO APPOSTO. Un livello A che ricorre nel 93 per cento dei casi non certifica nulla, e la sua rimozione NON TOGLIE UNA SOLA AFFERMAZIONE — toglie soltanto una garanzia che non era stata prestata</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — CONSEGUENZA OPERATIVA, PIU AMPIA DI QUELLA DICHIARATA STAMANE: nessun grado Savona presente nel Registro Unico Federato, IN ALCUNA DELLE SUE PORZIONI, puo essere ereditato senza riverifica. Le 4.968 assegnazioni vanno considerate NON APPOSTE finche non siano riprodotte una per una. Il repertorio delle fonti, che gradua caso per caso e dichiara il criterio, RESTA LA SOLA SEDE DELL’OPERA IN CUI UN GRADO SIGNIFICHI QUALCOSA</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="J138" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K138" s="8" t="inlineStr"/>
-      <c r="L138" s="8" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>Il caso del 9 marzo 1973 — attribuzione a ufficiali della Divisione Pastrengo, e il suo grado</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo IV.7, pagine 209-210; dichiarazioni rese nel 1987 al sostituto procuratore della Repubblica di Milano MARIA LUISA DAMENO; interrogatorio di BIAGIO PITARRESI al giudice istruttore GUIDO SALVINI del 9 MAGGIO 1995</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>IL FATTO. Il 9 MARZO 1973, in via Nirone a Milano, FRANCA RAME — allora impegnata con il marito nell’attivita di Soccorso Rosso in favore dei detenuti — fu aggredita da sconosciuti, costretta a salire su un furgone e sottoposta a violenza sessuale. La Commissione lo definisce «UNO STUPRO POLITICO» e afferma che l’episodio «DEVE ESSERE CONSIDERATO PARTE INTEGRANTE DELLA STRATEGIA DELLA TENSIONE». La vittima ha reso pubblica la vicenda e ne ha fatto materia del proprio lavoro</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>LE DUE FONTI DICHIARATIVE. Nel 1987 ANGELO IZZO riferi al pubblico ministero di avere APPRESO IN CARCERE che il principale responsabile fosse ANGELO ANGELI e che l’azione fosse stata «SUGGERITA DA ALCUNI UFFICIALI DEI CARABINIERI DELLA DIVISIONE PASTRENGO, nel quadro del sostanziale atteggiamento di COBELLIGERANZA esistente all’epoca fra alcuni settori di tale Divisione e gli estremisti di destra». Nel 1995 BIAGIO PITARRESI dichiaro al giudice istruttore che l’azione ERA STATA DAPPRIMA PROPOSTA A LUI, che egli si era rifiutato e che era subentrato Angeli; e confermo che essa fu ISPIRATA DA CARABINIERI DELLA MEDESIMA DIVISIONE, con la quale entrambi erano in contatto «IN FUNZIONE SIA INFORMATIVA SIA DI SUPPORTO IN ATTIVITA DI PROVOCAZIONE CONTRO GLI AMBIENTI DI SINISTRA»</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>IL GRADO, DA DICHIARARE OGNI VOLTA. Il fatto materiale e certo. L’ATTRIBUZIONE AGLI UFFICIALI POGGIA SU DUE SOLE DICHIARAZIONI, provenienti dal medesimo ambiente, delle quali LA PRIMA E DE RELATO — l’interessato riferisce cio che dice di avere appreso in carcere. Il testo parlamentare NON RIPORTA ALCUN ACCERTAMENTO GIUDIZIARIO su quel punto, e l’esito processuale della vicenda VA VERIFICATO SEPARATAMENTE. **Livello B** quanto all’esistenza delle dichiarazioni, **Livello C** quanto al contenuto attribuito agli ufficiali</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>LA CONVERGENZA DI ATTI, DA REGISTRARE COME TALE E NON COME NESSO: la Divisione Pastrengo e il medesimo comando il cui generale, quattordici mesi prima, aveva trasmesso FUORI PROTOCOLLO E FUORI GERARCHIA la velina che origino la falsa pista sull’attentato di Peteano. LE DUE CIRCOSTANZE PROVENGONO DA ATTI DISTINTI E NON SONO STATE COLLEGATE DA ALCUNA SEDE: il registro le accosta perche riguardano il medesimo comando, e VIETA DI TRARNE INFERENZA</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Dominio 9 e Dominio 7 — ESTENDE L’OGGETTO. La forma finora registrata riguardava attentati e coperture; questo caso introduce LA VIOLENZA MIRATA CONTRO UNA PERSONA DETERMINATA come strumento della medesima strategia, e con la stessa attribuzione a settori di un comando militare. La parola usata dalle fonti — COBELLIGERANZA — e piu forte di «arco di sponda» e va confrontata con essa</t>
-        </is>
-      </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="inlineStr"/>
-      <c r="J139" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K139" s="8" t="inlineStr"/>
-      <c r="L139" s="8" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>DIAGNOSTICA DELLE MONOGRAFIE — terza condizione documentale, e una duplicazione da sanare</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Misurazione diretta su dodici monografie presenti nei file di progetto: serie sulla diaspora, serie sull’apartheid, monografia sulle reti europee riservate, monografia sulle reti russe</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO PRIMARIO, CHE E UNA BUONA NOTIZIA: NESSUNA MONOGRAFIA RECA LA FIRMA GENERATIVA. Zero occorrenze del termine inglese, densita nulla delle formule «si articola» e «articolato», nessuna delle strutture ripetitive rilevate nel Volume Zero. Sono testi scritti, non generati</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>MA NESSUNA RECA ALCUNA VALUTAZIONE PROBATORIA: zero gradi di livello A, B o C su circa novantasettemila parole complessive. Non e la patologia del Volume Zero, che apponeva un grado falso; e la condizione opposta, L’ASSENZA DI GRADUAZIONE. Ne discende una terza condizione documentale, da tenere distinta dalle altre due: il Volume Zero era prosa generata con graduazione fittizia; il repertorio e materiale interrogato con graduazione dichiarata per singola affermazione; LE MONOGRAFIE SONO MATERIALE DOCUMENTATO MA NON GRADUATO</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>LA DENSITA DOCUMENTARIA, MISURATA IN RIFERIMENTI PER MILLE PAROLE, VARIA DI UN FATTORE DIECI. Il valore piu alto e 20, in una monografia di 9.426 parole che reca 188 indirizzi di fonte; seguono valori di 14, 10, 9, 8 e 7. Il valore piu basso e 2, in un testo di 5.022 parole che ne reca due soli. LA SOGLIA CONTA: un testo con venti riferimenti per mille parole e un documento di ricerca, uno con due e una narrazione. VA STABILITA UNA SOGLIA MINIMA E DICHIARATA</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>LA DUPLICAZIONE, DA SANARE: almeno sei monografie compaiono due volte nei file di progetto, in coppie identiche distinte dal solo suffisso numerico. Circa quarantamila parole del corpus sono dunque copia di altre quarantamila. La duplicazione non e un errore di contenuto ma FALSA OGNI MISURA DI CONSISTENZA CHE NON LA RILEVI, ed e la stessa famiglia di errore del contatore mai ispezionato</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>L’OSSERVAZIONE STRUTTURALE CHE NE DISCENDE, E VALE PER L’ARCHITETTURA: le monografie portano le fonti nel testo e non portano i gradi; i capitoli di fondazione portano i gradi nel testo e le fonti nel repertorio. SONO DUE ARCHITETTURE LEGITTIME E INCOMPATIBILI, e l’opera deve sceglierne una. La seconda e preferibile perche consente di aggiornare una fonte senza toccare il capitolo, e di verificare un grado senza rileggere il testo</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — DISPOSIZIONE: le monografie NON vanno espunte ne sospese. Vanno GRADUATE, affermazione per affermazione, al momento in cui se ne attinge; e le coppie duplicate vanno ridotte a un solo esemplare prima di qualsiasi conteggio di consistenza</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="J140" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K140" s="8" t="inlineStr"/>
-      <c r="L140" s="8" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Fondo del servizio informativo brasiliano — INDIRIZZO ARCHIVISTICO ACCERTATO, DOCUMENTO NON RAGGIUNTO</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Archivo Nacional del Brasile, sede di Praça da República a Rio de Janeiro e sovrintendenza regionale del Distretto Federale; Centro di riferimento «Memórias Reveladas», istituito il 13 MAGGIO 2009 dalla Casa Civile della Presidenza della Repubblica</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>L’ESITO, DICHIARATO PER PRIMO: LA RICERCA NON HA RAGGIUNTO IL DOCUMENTO. Il fondo e stato localizzato, il regime di accesso accertato e la via di consultazione individuata, ma la citazione riferita da fonte secondaria sul consolidamento della struttura in Brasile RESTA NON RISCONTRATA. La consultazione richiede interrogazione della banca dati, non raggiungibile per via di ricerca generale</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>L’INDIRIZZO, ORA PRECISO. Con decisione governativa del 2005 tutti i documenti pubblici relativi al periodo dal 1 APRILE 1964 AL 15 MARZO 1985, custoditi da persone, imprese e organi pubblici civili e militari, sono stati trasferiti all’Archivo Nacional, compresi i fondi del SERVIZIO NAZIONALE DI INFORMAZIONI, del Consiglio di sicurezza nazionale, della Commissione generale d’inchiesta e dei dipartimenti di ordine politico e sociale dei singoli Stati. Il complesso ammonta a CIRCA DICIASSETTE MILIONI E QUATTROCENTOMILA PAGINE di documentazione testuale, oltre a 220.000 microschede e 110 rulli di microfilm</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>LA VIA DI CONSULTAZIONE: banca dati «Memórias Reveladas» e sistema informativo dell’archivio nazionale, entrambi accessibili dal portale governativo; servizio all’utenza anche IN PRESENZA presso le due sedi. La rete cooperativa che alimenta la banca dati contava nel 2011 CINQUANTACINQUE enti partner, anche esteri</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>L’ECCEZIONE DICHIARATA, CHE VA REGISTRATA PERCHE DELIMITA CIO CHE SI PUO TROVARE: il trasferimento del 2005 esclude i documenti «RIVELATORI DI INTIMITA DELLA VITA PRIVATA DELLE PERSONE E DI SEGRETEZZA IMPRESCINDIBILE PER LA SICUREZZA NAZIONALE». Esiste dunque una CATEGORIA RISERVATA, la cui consistenza non e dichiarata: un’assenza dal fondo NON PROVA un’assenza dal servizio</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Tomo Secondo — LA LACUNA BRASILIANA RESTA APERTA, MA CAMBIA STATUTO. Non e piu «esiste da qualche parte un fondo brasiliano»: e un indirizzo determinato, con volume, base giuridica, via di accesso ed eccezione dichiarata. E cio che una ricerca a distanza puo produrre, e va distinto da cio che solo la consultazione produrrebbe</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I141" s="3" t="inlineStr"/>
-      <c r="J141" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K141" s="8" t="inlineStr"/>
-      <c r="L141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>I due piani per Francia e Italia — PATERNITA, SIGLE E DATE ACCERTATE SU FONTE PRIMARIA</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Documento PSB D-30, «Planning activities of the Psychological Strategy Board through 30 June 1952», datato 1 AGOSTO 1952, desecretato e pubblicato nella raccolta digitale dell’agenzia informativa statunitense, numero CIA-RDP80-01065A000500070012-3, rilasciato l’8 LUGLIO 2002; carte del Psychological Strategy Board presso la biblioteca presidenziale Truman, scatole 5 e 7</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>LA PATERNITA, CHE ERA CONTESA ED E ORA STABILITA: i due piani FURONO SVILUPPATI DALLO PSYCHOLOGICAL STRATEGY BOARD, organo istituito il 4 APRILE 1951 e composto dal sottosegretario di Stato, dal vice segretario alla Difesa e dal direttore dell’intelligence centrale o loro rappresentanti. NON DAL COMITATO DEI CAPI DI STATO MAGGIORE. Il documento primario afferma che il piano per la Francia «e quello corrispondente per l’Italia FURONO SVILUPPATI DAL MEDESIMO GRUPPO DI PIANIFICAZIONE DEL BOARD, e le azioni previste da entrambi sono coordinate dal medesimo gruppo». **Livello A**</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>LE SIGLE E LE DATE. Il piano per la Francia e PSB D-14, nome in codice CLOVEN, nella versione migliore del 12 DICEMBRE 1951; quello per l’Italia e PSB D-15, nome in codice DEMAGNETIZE, poi mutato in CLYDESDALE. ENTRAMBI FURONO APPROVATI IL 21 FEBBRAIO 1952. Su approvazione fu istituito a Washington un comitato interdipartimentale di coordinamento presieduto da un membro dello staff del Board, CON PANNELLI CORRISPONDENTI A PARIGI E A ROMA, in comunicazione fra loro per l’attuazione</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="inlineStr">
-        <is>
-          <t>LA MOTIVAZIONE DICHIARATA, TESTUALE: i piani «RISULTARONO DA UN’ESTESA INDAGINE CONDOTTA NELL’ESTATE E NELL’AUTUNNO DEL 1951, all’esito della quale il Board concluse che gli apparati comunisti francese e italiano, I DUE PIU POTENTI DELL’EUROPA OCCIDENTALE, COSTITUIVANO UNA SERIA MINACCIA PER LA POLITICA ESTERA AMERICANA E PER I PIANI DELLA NATO PER LA DIFESA DELL’EUROPA OCCIDENTALE». E l’analisi condusse alla conclusione che in entrambi i paesi «LA FONTE PRIMARIA DEL POTERE COMUNISTA RISIEDEVA NEL LORO CONTROLLO ORGANIZZATO SUI SINDACATI»</t>
-        </is>
-      </c>
-      <c r="F142" s="2" t="inlineStr">
-        <is>
-          <t>LA RETTIFICA AL PRIMO CAPITOLO DIMOSTRATIVO: esso reca «memo 14 maggio 1952» come data del piano. LA DATA DI APPROVAZIONE E IL 21 FEBBRAIO 1952, e le date di stesura sono il 12 dicembre 1951 per la Francia e il febbraio 1951 per l’Italia secondo la scheda d’archivio. Il 14 maggio 1952 NON TROVA RISCONTRO in questa documentazione e va soppresso o attribuito ad altro atto</t>
-        </is>
-      </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — E IL PRIMO CASO IN CUI UNA PENDENZA DI ATTRIBUZIONE SI CHIUDE SU DOCUMENTO PRIMARIO DESECRETATO anziche su fonte secondaria. Il documento e liberamente consultabile e reca numero di rilascio: chiunque puo ripetere la verifica</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="I142" s="3" t="inlineStr"/>
-      <c r="J142" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K142" s="8" t="inlineStr"/>
-      <c r="L142" s="8" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>FM 30-31B — LO STATUTO CONTESO SI RISOLVE, E CON ESSO UNA MIA CONFUSIONE</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Audizioni della Commissione permanente d’intelligence della Camera statunitense, 96 Congresso, seconda sessione, 6 e 19 FEBBRAIO 1980; determinazione della medesima Commissione del 1979; conclusione del servizio informativo danese del 1976; dichiarazione del Dipartimento di Stato del 20 GENNAIO 2006, sotto il segretario CONDOLEEZZA RICE; relazione della commissione parlamentare belga; documentario televisivo britannico del 24 GIUGNO 1992</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>L’ARGOMENTO STRUTTURALE, CHE E IL PIU FORTE E NON DIPENDE DA ALCUNA DICHIARAZIONE: IL MANUALE FM 30-31, DATATO 8 GENNAIO 1970 E REGOLARMENTE PUBBLICATO, RECA UN SOLO SUPPLEMENTO, IL SUPPLEMENTO A. Non esiste traccia di un supplemento B classificato negli archivi e nei cataloghi dottrinali dell’esercito, e il documento non figura fra i manuali di campo pubblicati. La sigla stessa presuppone un atto la cui esistenza non e attestata</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>GLI ALTRI ELEMENTI CONTRARI, IN ORDINE CRONOLOGICO E PRECEDENTI ALLA CONTROVERSIA ITALIANA: nel 1976 il servizio informativo per la difesa danese concluse che si trattava di falso inserito in una campagna di disinformazione sovietica; nel 1979 la Commissione d’intelligence della Camera statunitense lo determino falso; nelle audizioni del febbraio 1980 funzionari dell’agenzia informativa lo qualificarono «falso singolarmente efficace» del servizio sovietico, e JOHN McMAHON, funzionario dell’agenzia, dichiaro in audizione che il documento «aveva qualche difetto ma era un lavoro molto professionale E RECAVA LA FIRMA FALSIFICATA DEL GENERALE WESTMORELAND». Un transfuga del servizio sovietico — DI CUI LE FONTI CONSULTATE NON RIPORTANO IL NOME, e va accertato — depose in Congresso nel medesimo senso. Il documento COMPARVE PER LA PRIMA VOLTA IN TURCHIA negli anni Settanta</t>
-        </is>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>GLI ELEMENTI CONTRARI ALLA TESI DEL FALSO, DA CONSERVARE: nel LUGLIO 1981 MARIAGRAZIA GELLI, figlia di Licio Gelli, fu fermata a Roma con una valigia contenente, fra altri documenti, UNA COPIA DEL MANUALE; e Licio Gelli dichiaro ad ALLAN FRANCOVICH, nel documentario televisivo britannico del 1992, che gliel’aveva dato «un amico molto stretto della CIA». RAY S. CLINE, vicedirettore dell’agenzia dal 1962 al 1966, interrogato da Francovich, rispose: «SOSPETTO CHE SIA UN DOCUMENTO AUTENTICO. NON NE DUBITO. NON L’HO MAI VISTO, ma e il genere di operazioni delle forze speciali che vi sono descritte» — E L’INCISO «NON L’HO MAI VISTO» NE DELIMITA IL VALORE. La commissione parlamentare belga si astenne: «la commissione non ha alcuna certezza sull’autenticita del documento»</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="inlineStr">
-        <is>
-          <t>IL GIUDIZIO CHE QUEST’OPERA ADOTTA: LA TESI DEL FALSO E DI GRAN LUNGA PIU SOSTENUTA, per l’argomento strutturale del supplemento inesistente e per la convergenza di tre accertamenti indipendenti anteriori alla controversia italiana; concordano gli studiosi PEER HENRIK HANSEN e THOMAS RID, mentre WILLIAM SCHAAP sostenne nel 1979 che il ritardo della smentita statunitense ne indebolisse la tesi. IL DOCUMENTO NON PUO SORREGGERE ALCUNA AFFERMAZIONE SULLA DOTTRINA STATUNITENSE. Cio che resta accertato, e va tenuto distinto, e IL FATTO DELLA SUA CIRCOLAZIONE: che una copia fosse nella disponibilita di Licio Gelli nel 1981 e un fatto, quale che ne sia l’origine</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>LA MIA CONFUSIONE, DA CORREGGERE. In altra voce di questo repertorio ho segnalato come cronologicamente implausibile l’attribuzione a Westmoreland di una direttiva del 1963. QUEL RILIEVO RESTA VALIDO — nel 1963 egli dirigeva l’accademia militare — MA NON SI ESTENDE AL MANUALE DEL 1970, quando egli era capo di stato maggiore dell’esercito e una sua firma sarebbe stata cronologicamente possibile. SONO DUE PROBLEMI DISTINTI: il primo e di impossibilita cronologica, il secondo di falsificazione della firma</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — LO STATUTO PASSA DA CONTESO A FALSO CON MINORANZA DICHIARATA. La minoranza va sempre riportata, perche una tesi che sopprima le proprie obiezioni non e piu forte: e soltanto meno verificabile</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>verificato 5.8.2026</t>
-        </is>
-      </c>
-      <c r="J143" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K143" s="8" t="inlineStr"/>
-      <c r="L143" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L143"/>
@@ -12092,6 +9624,3100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Archivio</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Sede</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Procedura di accesso</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Che cosa contiene</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Condizione servita</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
+          <t>Verifica indipendente</t>
+        </is>
+      </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>Data verifica indipendente</t>
+        </is>
+      </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>Sede consultata / esito</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Operazione «Feuerzauber» — attentato simulato al carcere di Celle</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bassa Sassonia, Germania; 25 luglio 1978, ore 2:54</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Fatti accertati e ammessi; commissione d’inchiesta del Parlamento regionale; relazione finale discussa in aula</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>UN SERVIZIO DI SICUREZZA DI UNO STATO DEMOCRATICO FECE ESPLODERE UNA BOMBA CONTRO IL MURO DI UN CARCERE E NE ATTRIBUÌ LA PATERNITÀ A UN’ORGANIZZAZIONE TERRORISTICA. L’ufficio regionale per la protezione della Costituzione, con il supporto dell’unità speciale antiterrorismo federale, provocò un foro di circa quaranta centimetri nella muraglia esterna, con danni minimi e nessuna evasione. Scopo dichiarato: infiltrare un informatore nell’organizzazione armata sotto falsa bandiera, arricchendone la biografia e dimostrando all’ambiente che gli informatori erano disposti ad azioni drastiche</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>LA MESSA IN SCENA FU COMPLETA: un’automobile predisposta con armi, munizioni e passaporti falsi, fermata ottanta chilometri più in là con il conducente già fuggito; ATTREZZI DA EVASIONE INTRODOTTI DI NASCOSTO NELLA CELLA DEL DETENUTO E POI «RITROVATI»; criminali arruolati come informatori, uno dei quali PRESENTATO AI MEDIA COME SOSPETTATO. L’azione, prevista per la notte precedente, fu rinviata perché DUE INNAMORATI PROVENIENTI DAL LUNA PARK VICINO ENTRARONO NELLA ZONA PERICOLOSA. Al detenuto furono in seguito respinte le richieste di alleviamento della detenzione CON RIFERIMENTO ALL’ATTENTATO</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>LA RIVELAZIONE E L’ESITO: il 24 aprile 1986 due deputati regionali accennarono al fatto in aula; il giorno dopo, 3 settimane prima delle elezioni regionali, un quotidiano di Hannover ne rivelò le circostanze. Il presidente del Land rese una dichiarazione di governo IN CUI GIUSTIFICÒ L’OPERAZIONE. La commissione d’inchiesta NON POTÉ CONFERMARE i successi rivendicati e accertò che un investigatore privato poteva determinare da solo e senza controllo i concetti e le azioni fittizie degli informatori; il procedimento penale avviato fu ARCHIVIATO per mancanza di elementi di reato. Il pezzo di muro con il foro è oggi esposto davanti all’ingresso del carcere</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — È IL PRECEDENTE DOCUMENTATO E AMMESSO DELLA CATEGORIA «SERVIZIO DEVIATO»; le fonti registrano che dopo le rivelazioni si sviluppò un durevole sospetto che attentati segnalati potessero essere azioni di Stato sotto falsa bandiera</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="n"/>
+      <c r="L2" s="8" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Effrazione dell’ufficio distaccato del servizio investigativo federale a Media, Pennsylvania — 8 marzo 1971</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Stati Uniti</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>7 dissidenti riuniti in una autodenominata commissione di cittadini per indagare sull’ufficio federale ENTRARONO CON EFFRAZIONE e sottrassero OLTRE MILLE DOCUMENTI RISERVATI, consegnandoli alla stampa. Ne derivò l’esposizione pubblica del programma di controspionaggio interno e, 4 anni dopo, l’istituzione della commissione senatoriale</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE CHIUDE IL REPERTORIO: PRIMA DI QUELL’EFFRAZIONE NON ESISTEVA ALCUNA VIGILANZA UFFICIALE SULLE AGENZIE DI INTELLIGENCE. L’ultima componente rimasta anonima ha rivelato la propria partecipazione SOLTANTO NEL 2024, 50tré anni dopo</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — l’intero sistema di controllo democratico dell’intelligence statunitense nasce da un furto con scasso; e i documenti sul controllo mentale sopravvissero a un ordine di distruzione PER ERRORE DI ARCHIVIAZIONE</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="n"/>
+      <c r="L3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Field Manual 30-31B, cosiddetto «direttiva Westmoreland» — STATUTO CONTESO, NON UTILIZZABILE COME PROVA</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Copia sequestrata a Licio Gelli a Castiglion Fibocchi il 17 marzo 1981 e pubblicata dalla Commissione parlamentare P2 nel Doc. XXIII n. 2-quater, Serie II, Volume VII, Tomo I, alle pagine 287-298, Roma 1987</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CHE COSA AFFERMA IL DOCUMENTO: che quando i governi dei Paesi ospiti mostrino passivita o indecisione di fronte alla sovversione comunista, gli apparati statunitensi possano promuovere azioni di provocazione, incoraggiando gruppi di estrema sinistra ad atti violenti o eseguendo direttamente azioni sotto falsa bandiera da attribuire loro. Reca data 18 marzo 1970 e la firma attribuita al capo di Stato maggiore dell’Esercito</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>GLI ELEMENTI A FAVORE DELLA FALSIFICAZIONE, CHE SONO SERI E PRECOCI: il SERVIZIO DI INTELLIGENCE DELLA DIFESA DANESE CONCLUSE GIA NEL 1976 che si trattava di un falso inserito in una campagna di disinformazione sovietica; UN TRANSFUGA DEL KGB LO DICHIARO FALSO DI ORIGINE SOVIETICA testimoniando davanti al Congresso statunitense; la commissione parlamentare statunitense sull’intelligence apri un’indagine sulle falsificazioni nel gennaio 1979; IL FM 30-31 PUBBLICAMENTE RILASCIATO HA IL SOLO SUPPLEMENTO A, NON IL B; il Dipartimento di Stato lo ha qualificato come falso sovietico trentennale in un comunicato del 20 gennaio 2006; un ex direttore centrale dell’intelligence dichiaro di non averne mai sentito parlare</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>GLI ELEMENTI CONTRARI, CHE NON SONO TRASCURABILI: fu sequestrato INSIEME AD ALTRI DOCUMENTI DI ORIGINE STATUNITENSE VERIFICATI; LA COMMISSIONE PARLAMENTARE ITALIANA LO PUBBLICO NEL 1987 COME DOCUMENTO GENUINO; un ex vicedirettore della CIA dichiaro di sospettarne l’autenticita, PRECISANDO PERO DI NON AVERLO MAI VISTO; il detentore affermo nel 1992 di averlo ricevuto da un amico della CIA; e NEL PROCESSO DI BOLOGNA DEL 2018 UN GENERALE DEL SISMI IN CONGEDO HA TESTIMONIATO che una copia non espunta esisteva negli archivi dell’intelligence militare italiana, ottenuta da autorita statunitensi SENZA ALCUNA ANNOTAZIONE che la indicasse come falsa</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>LA REGOLA CHE NE DISCENDE PER L’OPERA, ED E TASSATIVA. IL DOCUMENTO NON PUO ESSERE USATO COME PROVA DI UNA DOTTRINA. Puo essere trattato SOLTANTO come oggetto di studio a statuto conteso, esponendo entrambi i fronti. E NON SERVE: la categoria della falsa bandiera e gia stabilita da altre fonti incontestate — la proposta statunitense del 13 marzo 1962, autentica e respinta, e l’operazione tedesca del 25 luglio 1978, eseguita e in seguito ammessa in sede parlamentare. UN’OPERA CHE POGGIA SU QUESTO DOCUMENTO REGALA AI PROPRI AVVERSARI LA SOLA OBIEZIONE REALMENTE LETALE</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 7 e Metodologia — NODO A MASSIMO RISCHIO. Il Volume Zero lo classifica gia Savona B: e giusto, MA INSUFFICIENTE. Va marcato CONTESO, con entrambe le serie di elementi esposte nel testo e non in nota</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="n"/>
+      <c r="L4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Gladio — verifica delle cifre e delle date: RETTIFICHE AL VOLUME ZERO PARTE VII</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Fonti: relazione Andreotti alla Commissione stragi (ottobre 1990); audizione del capo di Stato maggiore del SISMI del 29 novembre 1990; appunto interno SIFAR predisposto per la visita del capo di Stato maggiore a Capo Marrargiu (1965)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>LA DATA COSTITUTIVA: protocollo d’intesa fra servizio italiano e statunitense: LA RELAZIONE DEL GOVERNO AL PARLAMENTO LO DATA AL 26 NOVEMBRE 1956, LA COPIA DEL DOCUMENTO POI CONSEGNATA DAL GOVERNO ALLA COMMISSIONE E DATATA 28 NOVEMBRE 1956 — DISCREPANZA CHIUSA, MA NON RISOLTA IN FAVORE DI UNA DATA: e uno scarto fra il racconto dell’esecutivo e l’atto dell’esecutivo. E il protocollo NON E L’INIZIO: conteneva esplicito riferimento ad ACCORDI PREESISTENTI, e la sezione addestramento del SIFAR era stata costituita il 1° OTTOBRE 1956, prima del protocollo. Scrivere che Gladio nasce il 26 novembre 1956 e dunque inesatto: quella e la data in cui viene formalizzata</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ERRORE DI FATTO DA CORREGGERE NEL VOLUME ZERO: il magistrato veneziano ottenne da Andreotti nel luglio 1990 l’accesso all’archivio del SISMI a FORTE BRASCHI, non a Forte Boccea. Forte Braschi e la sede del servizio; Forte Boccea ospita il carcere e il tribunale militari. LA PARTE VII INDICA IL FORTE SBAGLIATO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>LA CIFRA DEI TREMILA UOMINI VA DECLASSATA. Proviene da un APPUNTO INTERNO SIFAR PRIVO DI DATA, predisposto per una visita del 1965, che indica millecinquecento uomini inquadrati nelle forze speciali, altri millecinquecento disponibili per mobilitazione e seicento64 quadri formati in cento36 corsi. MA IL 29 NOVEMBRE 1990, DAVANTI ALLA COMMISSIONE, IL CAPO DI STATO MAGGIORE DEL SISMI INTERROGATO SU QUELLA DISCREPANZA RISPOSE CHE «PROBABILMENTE CHI LO HA COMPILATO VOLEVA FARE BELLA FIGURA», indicando come piu veritieri gli elenchi nominativi. Agli atti risulta inoltre che LA FORZA COMPLESSIVA PREVISTA DEI QUARANTA NUCLEI AMMONTAVA A CENTOSESSANTA UOMINI, e che «non si hanno in atti riscontri sulla forza effettiva della struttura esterna». LA PARTE VII CLASSIFICA I TREMILA COME SAVONA A: E UNA SOVRASTIMA DI GRADO</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>I DEPOSITI: NON CENTOVENTISETTE MA CENTOTRENTANOVE, di cui SOLTANTO CENTOVENTISETTE FURONO SVELATI. Sui 12 mancanti Andreotti dichiaro nel 1990 che due erano stati asportati da ignoti probabilmente gia al momento dell’interramento del 1964, due si trovavano presso cimiteri poi ampliati e non erano piu recuperabili, e cosi gli altri 8. I 12 MANCANTI SONO PIU SIGNIFICATIVI DEI CENTOVENTISETTE RITROVATI, e il Volume Zero non li registra. Quanto agli effettivi: i reclutati dal 1956 al 1990 furono SEICENTO22, ma AL 1959 ERANO SESSANTA</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Tomo I e Volume Zero — 3 CORREZIONI OBBLIGATORIE: il forte e sbagliato; i tremila uomini vanno declassati da A a fonte contestata sotto giuramento; i depositi sono centotrentanove e non centoventisette. VA INOLTRE RISOLTA LA DATA DELLA RIVELAZIONE, che le fonti collocano ora al 17, ora al 18, ora al 24 ottobre 1990 secondo la sede</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Piano Solo 1964 — verifica e RETTIFICHE AL VOLUME ZERO PARTE VII</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Fonti: relazione della Commissione parlamentare d’inchiesta presieduta da Giuseppe Alessi, presentata il 15 DICEMBRE 1970; inchiesta amministrativa Lombardi; relazione della Commissione stragi della XIII legislatura; testimonianza di Francesco Cossiga al Tribunale di Velletri del 21 dicembre 1999 (Commissione stragi XIII leg., doc. Sifar-Piano Solo n. 2/2)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CONTRADDIZIONE INTERNA DA CORREGGERE: la Parte VII colloca un’audizione del generale de Lorenzo al 31 GENNAIO 1979, ma la stessa Parte VII ne indica la morte al 26 APRILE 1978. UN UOMO NON DEPONE DOPO MORTO: la data e con ogni probabilita 1969, E VA RISOLTA SULL’ATTO</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>LA CIFRA VA RIALZATA, NON CONFERMATA: LA RELAZIONE DI MINORANZA CONCLUSE CHE LE LISTE CONSEGNATE IL 28 GIUGNO 1964 NON CONTENESSERO 731 NOMINATIVI MA UN NUMERO NON INFERIORE A MILLECENTO-MILLEDUECENTO. Conferma indiretta: non si ritennero sufficienti gli aerei e si valuto di ricorrere anche a MEZZI NAVALI. Va inoltre segnalata una distinzione tecnica: secondo parte della pubblicistica la lista degli enucleandi NON ERA INCLUSA NEL PIANO SOLO ma discendeva da altro strumento e da altri piani di contingenza — DA RISOLVERE SUGLI ATTI</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>IL FATTO PIU GRAVE DEL CAPITOLO, CHE IL VOLUME ZERO NON REGISTRA. La lista, «della cui esistenza non puo dubitarsi», NON FU CONSEGNATA ALLA COMMISSIONE PARLAMENTARE NE FIGURA TRA I DOCUMENTI DESECRETATI IL 28 DICEMBRE 1990. E il ragionamento e della Commissione stessa: cio «appare una circostanza di rilevante gravita, poiche lascia supporre che la lista contenesse NOMI DI PARLAMENTARI E DIRIGENTI POLITICI, la cui pubblicazione renderebbe impraticabile ogni ipotesi tendente a presentare gli eventi del 1964 come atti tutelativi». A cio si aggiunge che DEI FASCICOLI SIFAR SI DISPOSE LA DISTRUZIONE, e che il sottosegretario delegato a seguire l’inchiesta e INCARICATO DI PRENDERE IN CONSEGNA IL PIANO SOLO coperse con omissis gran parte dei documenti, COMPRESI QUELLI RELATIVI ALLE AZIONI PREVISTE, come egli stesso raccontera molti anni dopo</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>L’ESITO, CHE VA SCRITTO PERCHE E LA FORMA RICORRENTE DEL REPERTORIO: la Commissione Alessi concluse per «UNA DEVIAZIONE DEPRECABILE» MA NON PER UN TENTATIVO DI COLPO DI STATO, e la seria minaccia di un golpe e stata esclusa TANTO DALLA MAGISTRATURA QUANTO DALLE INCHIESTE PARLAMENTARI. Da registrare inoltre che il generale incaricato dell’inchiesta interna MORI D’INFARTO NEL 1969 PRIMA DI DEPORRE davanti alla Commissione, e che il generale oggetto dell’inchiesta ERA NEL FRATTEMPO STATO ELETTO DEPUTATO nel 1968</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Volume Zero Parte VII — 4 INTERVENTI: correggere la data dell’audizione; rialzare la cifra da 731 a millecento-milleduecento secondo la relazione di minoranza, dichiarando entrambe; INSERIRE LA SCOMPARSA DELLA LISTA E IL RAGIONAMENTO DELLA COMMISSIONE, che oggi manca; e scrivere l’esito, perche un capitolo che espone il piano senza dire come fini non e storia ma requisitoria</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>La rivelazione Gladio dell’ottobre 1990 — cronologia risolta, e le DUE VERSIONI della relazione</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Atti della Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, X legislatura; resoconti della Camera; relazione del Comitato parlamentare sui servizi del 1995</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CRONOLOGIA RISOLTA: 3 AGOSTO 1990, davanti alla Commissione presieduta da Libero Gualtieri, prima ammissione dell’esistenza CON LA TESI che le attivita fossero proseguite «fino al 1972, dopodiche si e ritenuto che non ve ne fosse piu bisogno»; RELAZIONE ALLA COMMISSIONE PROTOCOLLO NUMERO 5099 DEL 17 OTTOBRE 1990 — DISCREPANZA CHIUSA, la data e attestata dal numero di protocollo e concordemente riportata; 24 OTTOBRE, discorso alla Camera e rivelazione pubblica; NOVEMBRE, scioglimento dichiarato; e IN UNA SUCCESSIVA TRASMISSIONE DI ATTI l’ammissione, contraria alla prima dichiarazione, CHE LA STRUTTURA ERA ANCORA IN PIEDI E OPERATIVA</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>IL RITROVAMENTO PRINCIPALE, DA VERIFICARE SUGLI ATTI PARLAMENTARI MA CIRCOSTANZIATO: DELLA RELAZIONE ESISTEREBBERO DUE VERSIONI, e le differenze sono elencate. Nella prima si parla del CONTROLLO DEI SERVIZI SULL’INTERO GRUPPO, nella seconda NON SI FA PIU ALCUN ACCENNO A CONTROLLO. Nella prima si sostiene che LA PIANIFICAZIONE GEOGRAFICA E OPERATIVA ERA CONCORDATA CON IL SERVIZIO INFORMAZIONI AMERICANO: nella seconda LA RIGA SALTA INTERAMENTE. Nel documento corretto SCOMPARE OGNI ACCENNO AGLI STANZIAMENTI, e con essi le notizie su modalita operative, addestramento e materiali</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>E IL PUNTO CHE SI SALDA CON I 12 DEPOSITI MANCANTI: nella versione del 18 ottobre I DEPOSITI DI ARMI ED ESPLOSIVO SI DICEVANO SMANTELLATI E RICOSTITUITI ALTROVE. NELLA VERSIONE CORRETTA QUELLA INDICAZIONE NON C’E PIU. Se il riscontro regge sugli atti, e la riga piu importante dell’intero capitolo: non che i depositi furono smantellati, MA CHE FURONO RICOSTITUITI, E CHE QUESTO FU SCRITTO E POI TOLTO</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>DUE FATTI CHE IL VOLUME ZERO NON REGISTRA. PRIMO, L’ESITO GIUDIZIARIO: il fascicolo fu trasmesso per competenza territoriale alla Procura di Roma, LA QUALE DICHIARO CHE LA STRUTTURA NON AVEVA NULLA DI PENALMENTE RILEVANTE. SECONDO, CHE GLADIO NON ERA LA PRIMA: una relazione del Comitato parlamentare sui servizi del 1995 afferma che «e fuor di dubbio che in epoca precedente alla creazione di Gladio sia esistita un’altra organizzazione denominata DUCA, con le stesse finalita e struttura analoga, DI CUI SAPPIAMO BEN POCO e che dovrebbe essere stata sciolta INTORNO AL GENNAIO 1995», e che in vari documenti acquisiti dall’autorita giudiziaria si parla di organizzazione «Duca-Gladio»</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Volume Zero Parte VII — 3 INTEGRAZIONI: risolvere e citare la data della relazione; INSERIRE LE DUE VERSIONI, previa verifica sugli atti, perche e il fatto piu eloquente del capitolo; e scrivere l’esito romano insieme all’esistenza dell’organizzazione anteriore ancora in scioglimento nel 1995</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Le origini pre-1956 dello stay-behind italiano — testo primario GIA PRESENTE NEL CORPUS E NON UTILIZZATO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, XIII legislatura, Doc. XXIII n. 64, Volume I, Tomo II, da pagina 67; il piano Demagnetize/Clydesdale e trattato a pagina 94. Il testo e gia nei file del progetto (blocchi p67) ed e integralmente consultabile presso l’archivio storico del Senato</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>LA RETTIFICA DI NOME: NON «PIANO DEMAGNETIZE» MA «PIANO DEMAGNETIZE/CLYDESDALE», come lo chiamano costantemente gli atti parlamentari. Il documento e un memorandum riservato del comando di Stato maggiore statunitense DATATO 14 MAGGIO 1952 — il Volume Zero non ne da la data. LA PATERNITA E RISOLTA: E DELLO PSYCHOLOGICAL STRATEGY BOARD, non del comitato dei capi di Stato maggiore — vedi voce dedicata. La prima pubblicazione avvenne IN UN LIBRO DEL 1978, non per acquisizione tramite settimanale come scrive il Volume Zero. L’analogo piano francese si chiamava CLOVEN. Contenuto: epurazione della presenza comunista da enti pubblici e industrie, inasprimento della legislazione di pubblica sicurezza, e predisposizione di un sistema atto a prevenire la crescita del PCI ANCHE SU BASE MILITARE — ma la valutazione accademica segnala la MANCANZA DI PRESCRIZIONI CONCRETE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>LA FRASE DELLA COMMISSIONE CHE RISOLVE IL PROBLEMA DELLA DATA DEL 1956, e che il Volume Zero non cita: queste strutture sono «concepite sempre con uno scarto temporale notevole, di diversi anni, e LA LORO UFFICIALIZZAZIONE VIENE COSTANTEMENTE POSTICIPATA, A GUISA DI SANATORIA». Il 26 novembre 1956 non e la nascita: E LA SANATORIA. E la Commissione aggiunge che per questo «risulta difficile seguire coerentemente lo svolgersi dei passaggi che portano alla creazione di Gladio e alla sua formalizzazione»</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>I DUE DOCUMENTI DEL 1951, 5 ANNI PRIMA DEL PROTOCOLLO, ENTRAMBI NEL CORPUS E NON USATI. PRIMO: NELL’OTTOBRE 1951 IL COMANDO NATO ORGANIZZA A PARIGI UN CONVEGNO INTITOLATO «SICUREZZA CIVILE E CONTROSPIONAGGIO IN TEMPO DI PACE», nel corso del quale VIENE AVANZATA LA PROPOSTA DI CREARE UN COMITATO PER LA PIANIFICAZIONE CLANDESTINA che coordini le attivita stay-behind in Europa. SECONDO: IL PROMEMORIA DEL 18 OTTOBRE 1951 del capo del SIFAR generale Umberto Broccoli al capo di Stato maggiore della Difesa generale Efisio Marras, che scrive essere «primo dovere del SIFAR quello di prevedere, in caso di conflitto, l’occupazione nemica di almeno parte del territorio nazionale e di preorganizzare il servizio informazioni, il sabotaggio, la propaganda e la resistenza», e rileva che «in Olanda e Belgio, e presumibilmente anche in Danimarca e in Norvegia, l’organizzazione puo dirsi a punto»</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>E LA FORMULAZIONE PARLAMENTARE DELLA TESI COSTITUZIONALE, CHE E IL PERNO DELL’OPERA: le finalita della struttura «mantengono un profilo di NON SICURA LEGITTIMITA COSTITUZIONALE», perche «rimane dubbia la legittimita di un organismo sorto sulla base di un accordo stipulato tra due Servizi NON UFFICIALMENTE AUTONOMI NEI CONFRONTI DEL POTERE ESECUTIVO E LEGISLATIVO DEI RISPETTIVI PAESI». NON SERVE ARGOMENTARLA: L’HA GIA SCRITTA UNA COMMISSIONE BICAMERALE, E IL TESTO E GIA NEI FILE DEL PROGETTO</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Volume Zero Parte VII — RIFONDAZIONE DEL CAPITOLO. Il capitolo va riscritto a partire dal 1951 e non dal 1956, sui due documenti d’ottobre; la data del 1956 va presentata come sanatoria e non come nascita, con le parole della Commissione; e vanno aperti i paragrafi che l’indice parlamentare gia elenca e il Volume Zero ignora: l’ufficio statunitense per le operazioni coperte e le armi nella campagna elettorale, l’organizzazione «O» e l’Armata italiana della liberta, l’ufficio REI del SIFAR con «Pace e Liberta», la polizia segreta del Viminale e il gruppo De Nozza, i Nuclei di difesa dello Stato e il gruppo Sigfried</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>La lettera di Edgardo Sogno ad Aldo Moro — DOCUMENTO DI PRIMO ORDINE GIA NEL CORPUS, MAI UTILIZZATO</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Riportata nella relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, alle pagine 87-89, sulla scorta della sentenza-ordinanza del giudice istruttore di Venezia Carlo Mastelloni, pagine 1318-1319. Testo gia trascritto nei file di progetto</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CHE COSA DICE, NELLE PAROLE DELLO STESSO PROTAGONISTA. Scrivendo all’allora ministro degli esteri Aldo Moro per lamentare il mancato avanzamento di carriera, Sogno spiega che «NEL LUGLIO DEL 1953, PER INIZIATIVA DELLA PRESIDENZA DEL CONSIGLIO, MI VENIVA NUOVAMENTE PROPOSTO UN INCARICO DI CARATTERE ECCEZIONALE E RISERVATO — ORGANIZZAZIONE DELLA DIFESA PSICOLOGICA DELLE ISTITUZIONI DEMOCRATICHE — IN RIPRESA DI UN’OPERAZIONE AVVIATA NEL 1948 PER INIZIATIVA DEL MINISTRO SFORZA NEL QUADRO DELLE ATTIVITA SVOLTE IN BASE AL PIANO MARSHALL»</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>E PROSEGUE: «L’azione svolta per il tramite del Comitato da me organizzato ebbe 3 FASI PRINCIPALI: in un periodo, fino all’ottobre 1954, essa si concreto nella realizzazione del progetto CHE GLI ONOREVOLI DE GASPERI E PELLA AVEVANO RIPETUTAMENTE SOSTENUTO IN CONSIGLIO ATLANTICO». Un appunto di poco precedente riferisce inoltre che le iniziative di «Pace e Liberta» «avrebbero riscosso l’adesione e l’appoggio del Presidente del Consiglio Scelba, del ministro Taviani, del Ministro degli esteri», e CHE SOGNO AVREBBE FATTO ISTITUIRE AGLI ESTERI UN UFFICIO PER IL COORDINAMENTO DELLA GUERRA PSICOLOGICA DA LUI DIRETTO</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE E LA MIGLIORE PROVA DEL CORPUS PER LA TESI DELL’OPERA. Non e una ricostruzione di terzi: e IL PROTAGONISTA CHE DESCRIVE PER ISCRITTO LA PROPRIA STRUTTURA, AL FUTURO STATISTA POI RAPITO E UCCISO, datandone l’origine al 1948 e ancorandola al Piano Marshall, con il sostegno di due presidenti del Consiglio in sede atlantica. E ANTICIPA DI 8 ANNI IL PROTOCOLLO DEL 1956</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>DUE ALTRI DOCUMENTI DELLO STESSO FONDO, PARIMENTI INUTILIZZATI. IL PRIMO: un appunto del Viminale del 27 DICEMBRE 1974 trasmesso a Torino, secondo cui una fonte fiduciaria segnala un avvocato titolare di una ditta di import-export come «UNO DEI FINANZIATORI DELLE ORGANIZZAZIONI NEOFASCISTE ITALIANE», in contatto con 3 persone nominate; e un appunto precedente sul rapporto fra un dirigente della destra italiana e il rappresentante di un governo allora «noto per essere uno dei piu razzisti del mondo, insieme con il Sudafrica». IL SECONDO: la deposizione di Carlo Digilio, principale testimone del nuovo processo su piazza Fontana, il quale racconta di aver visto in casa di un dirigente ordinovista, USCITO DA UN VOLUME DI EVOLA, un foglio con LA CARTA D’ITALIA E CROCETTE BLU accanto ai capoluoghi, in calce l’indicazione «NUCLEI DI DIFESA DELLO STATO», le crocette concentrate nel Nord-Est e NUMERI ROMANI A INDICARE LE LEGIONI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Volume Zero e Tomo I — QUESTI 3 DOCUMENTI VALGONO PIU DELL’INTERA PARTE VII ATTUALE. Sono gia nel corpus, trascritti dall’autore nel marzo 2026 dal PDF dell’archivio storico del Senato, e non compaiono nel testo dell’opera</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Il rapporto D’Amato–Delle Chiaie — FONTE FONDATIVA DELL’ARCO DI SPONDA, gia nel corpus</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 135-136, che riporta ampi brani della sentenza-ordinanza del giudice istruttore di Venezia Carlo Mastelloni; deposizione di Guglielmo Carlucci del 15 MAGGIO 1997</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CHI PARLA, ED E QUESTO A FARE IL LIVELLO: non un collaboratore di giustizia ne un giornalista, ma UN EX DIRIGENTE DEGLI AFFARI RISERVATI, STRETTO COLLABORATORE DI D’AMATO, che depone davanti a un giudice istruttore. Egli ricorda che Delle Chiaie ERA SOLITO FREQUENTARE D’AMATO sia quando questi era vicedirettore sia dopo, da direttore della Divisione, TRATTENENDOSI CON IL PREFETTO NEI LOCALI DELL’UFFICIO, E CHE IN ALCUNE OCCASIONI EGLI STESSO AVEVA ASSISTITO AI COLLOQUI</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CHE COSA PASSAVA NELLE DUE DIREZIONI. VERSO DELLE CHIAIE: la Divisione AGEVOLAVA IL CAPO DI AVANGUARDIA NAZIONALE PER IL RILASCIO DI PASSAPORTI, PER CONCESSIONI DEL PORTO D’ARMI E PER QUANT’ALTRO, intervenendo presso gli organi competenti della questura, ED ESTENDENDO QUESTO TIPO DI INTERVENTO ANCHE A QUALCHE AMICO DELL’ESTREMISTA. VERSO D’AMATO: Delle Chiaie forniva notizie che il prefetto, DOPO ESSERSI FATTO DESCRIVERE LE SINGOLE PERSONALITA DEGLI APPARTENENTI AL GRUPPO, trasfondeva in appunti inoltrati per lo sviluppo alla sezione competente AL FINE DI STIMOLARE I CONSEGUENTI CONTROLLI SUI MILITANTI, e in taluni casi direttamente al capo della polizia, che ove del caso li inoltrava al ministro</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>LE QUALIFICAZIONI, TESTUALI: Delle Chiaie era «UN SUO CONFIDENTE NONCHE INFILTRATO» nella struttura di estrema destra; si trattava di «UN RAPPORTO PERSONALE ED ESCLUSIVO» del prefetto; e di «UN CONTATTO RISCHIOSO» ritenuto pero da entrambi «INDISPENSABILE». Il commento che seguiva a ogni commiato era sempre che il contatto «POTEVA ESSERE UTILE PER NOI». La Commissione qualifica la deposizione come «UN RISCONTRO DIRETTO pertinente a un rapporto di cui si e eternamente sussurrato»</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>LA DISCIPLINA CHE IL TESTO STESSO APPLICA E CHE VA CONSERVATA: la testimonianza di Vinciguerra al giudice istruttore di Milano del 30 MAGGIO 1992 chiamava in causa anche un prefetto, IL QUALE, SUCCESSIVAMENTE INTERROGATO, PUR AMMETTENDO LA CONOSCENZA CON DELLE CHIAIE HA NEGATO QUANTO GLI ERA STATO ATTRIBUITO. LA SMENTITA VA RIPORTATA ACCANTO ALL’ACCUSA</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia e Dominio 3 × 7 — E LA FONTE FONDATIVA DEL SESTO TIPO DI ARCO, quello che la tipologia della Nota Metodologica non contempla: NON COLLUSIONE FRA PARI, NON STRUMENTALIZZAZIONE DEL DEBOLE DA PARTE DEL FORTE, MA SCAMBIO ASIMMETRICO BIDIREZIONALE in cui ciascuno usa l’altro per fini propri e incompatibili. Lo Stato ottiene la mappa dei militanti; il militante ottiene passaporti, porto d’armi e protezione estesa agli amici. NESSUNO DEI DUE E STRUMENTO DELL’ALTRO: ENTRAMBI LO SONO</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="n"/>
+      <c r="L10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>La politica statunitense verso l’Italia negli atti del Consiglio di sicurezza nazionale — RETTIFICHE E CONTROPROVA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Serie Foreign Relations of the United States, consultabile integralmente sul sito dell’Office of the Historian del Dipartimento di Stato</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>PRIMA RETTIFICA, DI CITAZIONE: il documento NSC 6014 e pubblicato nel volume FRUS 1958-1960, tomo settimo parte seconda, documento 278, con il titolo DRAFT STATEMENT OF U.S. POLICY TOWARD ITALY. La numerazione del Consiglio di sicurezza indica nelle prime due cifre l’anno: SEIMILA14 SIGNIFICA 1960, NON 1961. La versione approvata con suffisso /1 datata 19 aprile 1961, citata dal Volume Zero, NON E STATA REPERITA in questa verifica: VA PRODOTTO L’ATTO O CORRETTA LA CITAZIONE</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>SECONDA RETTIFICA, DI CARATTERIZZAZIONE: il Volume Zero definisce quel documento «la direttiva politica che governa l’intera operazione». IL TESTO NON E UNA DIRETTIVA OPERATIVA MA UNA DICHIARAZIONE DI INDIRIZZO. Vi si legge che l’Italia e membro chiave dell’Alleanza atlantica e che il suo progresso e essenziale «non soltanto al concetto strategico NATO per la difesa dell’Europa, ma all’unita storica e alla continua crescita della Comunita atlantica»; e che fino alle elezioni del 1948 esistette grave pericolo di dominazione comunista, arrestato «in parte per effetto di aiuti economici su larga scala, di fermo sostegno morale e della sicurezza militare fornita dall’appartenenza alla NATO». NULLA VI RIGUARDA RETI CLANDESTINE</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>I DUE DOCUMENTI CHE IL VOLUME ZERO AVREBBE DOVUTO CITARE AL SUO POSTO. IL PRIMO E NSC 5411/2, «U.S. POLICY TOWARD ITALY», APPROVATO DAL PRESIDENTE IL 15 APRILE 1954 e pubblicato in FRUS 1952-1954, volume sesto parte seconda, pagina 1677: e questo, e non il successivo, l’atto di indirizzo vigente per gran parte del periodo. IL SECONDO E IL PIANO OPERATIVO PREDISPOSTO DALL’ORGANO DI COORDINAMENTO DELLE OPERAZIONI, che fissa come obiettivo di lungo termine un’Italia libera da dominazione comunista «AVENTE UN GOVERNO COSTITUZIONALE E DEMOCRATICO», E CHE RECA ESPUNZIONI PROPRIO NEI PUNTI DECISIVI: una riga non declassificata dove si afferma che l’influenza statunitense deve concentrarsi sulle questioni essenziali, e 3 RIGHE E MEZZA NON DECLASSIFICATE sotto la voce degli impegni militari</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>LA CONTROPROVA, CHE L’OPERA HA L’OBBLIGO DI REGISTRARE. Nella risposta al memorandum di studio numero 88, del 1970, l’amministrazione statunitense esamina l’ipotesi di UNA LINEA INTERVENTISTA IN ITALIA E LA ARGOMENTA CONTRO, per queste ragioni testuali: getterebbe dubbio «SULLE NOSTRE PUBBLICHE AFFERMAZIONI SECONDO CUI LA FORMA DELL’EUROPA SPETTA AGLI EUROPEI»; e improbabile che le attivita discrete, compresi gli approcci a Regno Unito, Francia e Germania, RESTINO SEGRETE; alienerebbe gli altri alleati europei, oltre a molti italiani, che risentirebbero dell’ingerenza statunitense nella politica interna; e infine «MOLTO PROBABILMENTE NON RIUSCIREBBE A CONSEGUIRE I RISULTATI DESIDERATI»</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia e Tomo II — UNA TESI DI INGERENZA CONTINUA DEVE MISURARSI CON IL DOCUMENTO IN CUI L’INGERENZA E DISCUSSA E SCARTATA DALL’INTERNO, e per ragioni di inefficacia e di costo politico presso gli alleati. Registrarlo non indebolisce l’opera: LE DA IL SOLO ARGOMENTO CHE UN AVVERSARIO NON PUO RITORCERLE CONTRO</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Il progetto eversivo del 1973-1974 e la notte del 7 dicembre 1970 — FONTE PARLAMENTARE DELLA TESI COSTITUZIONALE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 157-165, sulla scorta dell’ordinanza-sentenza del giudice istruttore di Milano Guido Salvini del 18 MARZO 1995, pagine 245-249 e 301 e seguenti. Testo gia nel corpus</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>LA DESCRIZIONE DEL PROGETTO, TESTUALE, ED E LA TESI DELL’OPERA SCRITTA DA UN ORGANO DELLO STATO: il seguito del tentativo del 1970 avrebbe perseguito, con modalita sostanzialmente insurrezionali, «LA REALIZZAZIONE DI UN PROGETTO DI REVISIONE COSTITUZIONALE, CHE PORTASSE ALL’INSTAURAZIONE DI UNA REPUBBLICA PRESIDENZIALE, caratterizzata da PROGRAMMI SOCIALMENTE AVANZATI, MA DA FORTI LIMITAZIONI DEI DIRITTI SINDACALI, CONCENTRAZIONE DEI MEZZI DI INFORMAZIONE E DA UNA FORTE SCELTA ATLANTISTA; un progetto di stabilizzazione quindi DA REALIZZARSI ATTRAVERSO MEZZI DESTABILIZZANTI — attentati sui treni e in luoghi pubblici, eliminazione di avversari politici, scontri di piazza — LA CUI RESPONSABILITA SAREBBE STATA APPARENTEMENTE ATTRIBUIBILE ALLA SOVVERSIONE DI SINISTRA, si da determinare una forte domanda d’ordine e quindi giustificare l’intervento delle Forze Armate»</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>LA RETTIFICA SU GELLI, CHE VA NELLA DIREZIONE OPPOSTA ALLA VULGATA: la relazione afferma che il suo ruolo nei progetti del 1973-1974 «NON SEMBRA PERO ESSERE DI PRIMARIA IMPORTANZA come nel tentativo del ’70», poiche un congiurato riferisce che Gelli, PUR ESSENDO STATO FRA I PRIMI ADERENTI, ERA STATO NEGLI ANNI SUCCESSIVI EMARGINATO «PERCHE TROPPO POCO IDEALISTA E TROPPO ASSETATO DI POTERE E DI DENARO», e ne parla con disprezzo definendolo «un truffaldino» e «piu di tutto legato alla mafia». LA CENTRALITA DI GELLI E DUNQUE SPECIFICA DI UN PERIODO E CONTESTATA DA UN INTERNO</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>IL NODO CRIMINE-EVERSIONE DELLA NOTTE DEL 7 DICEMBRE 1970: da un colloquio del 31 MAGGIO 1974 emerge «LA PRESENZA A ROMA, LA NOTTE DEL 7 DICEMBRE 1970 E NEI GIORNI IMMEDIATAMENTE PRECEDENTI, DI UN GRUPPO DI MAFIOSI SICILIANI INCARICATI DI ELIMINARE IL CAPO DELLA POLIZIA». Nel verbale un congiurato precisa: «qui c’era un’intesa, da quello che so, Drago-Micalizio, Mafia. Questi mafiosi avrebbero dovuto far fuori Vicari. A UN BEL MOMENTO NON AVEVANO LE ARMI PER FARLO FUORI». Il gruppo era alloggiato la notte fra il 6 e il 7 dicembre in una struttura che il giudice ritiene fosse un residence «OVE ALL’EPOCA ERA PIU FACILE NON ESSERE REGISTRATI»</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>E IL COLLEGAMENTO CHE PROMUOVE LA TESTIMONIANZA SULLA CARTA NASCOSTA NEL VOLUME DI EVOLA: la notte del 7 dicembre sarebbe stato impartito, come afferma lo stesso ufficiale interessato, L’ORDINE DI MOBILITAZIONE DELLE STRUTTURE MISTE DI CIVILI E MILITARI DENOMINATE NUCLEI DI DIFESA DELLO STATO, costituite negli uffici informativi dell’Esercito con funzione di contrasto di moti comunisti. L’ordine sarebbe stato impartito PER RADIO, ATTRAVERSO I CODICI DEL PIANO DI MOBILITAZIONE; l’ufficiale ne CHIESE CONFERMA E LA OTTENNE, quindi si mosse, e RICEVETTE IL CONTRORDINE QUANDO AVEVA GIA RAGGIUNTO LE PORTE DI MILANO. Riscontri da due componenti della struttura, uno dei quali dichiarante gia dal 1974</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Tomo I e Dominio 1 × 7 × 9 — 3 ACQUISIZIONI. PRIMA: l’opera non deve argomentare la tesi costituzionale, DEVE CITARLA, perche una relazione bicamerale la formula gia. SECONDA: la centralita di Gelli va periodizzata e la fonte contraria riportata. TERZA: il foglio con le legioni nascosto in un libro di Evola cessa di essere un aneddoto E DIVENTA UN INDIZIO, perche quella stessa struttura risulta destinataria di un ordine di mobilitazione. TUTTO IL BLOCCO E IN CONDIZIONALE NEGLI ATTI E VA CITATO IN CONDIZIONALE</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n"/>
+      <c r="L12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Peteano 1972 — CONFESSIONE, CONDANNA DEFINITIVA PER IL DEPISTAGGIO, E LA DICHIARAZIONE CHE VALE PER TUTTA L’OPERA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 171-176; atti della Corte d’assise; sentenza della Corte d’assise d’appello di Venezia CONFERMATA DALLA CASSAZIONE NEL MAGGIO 1992. Testo gia nel corpus</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>LA DICHIARAZIONE DELL’AUTORE, CHE E IL CARDINE DELLA TESI COSTITUZIONALE. Vincenzo Vinciguerra, militante di Ordine Nuovo latitante dal 1974 prima in Spagna — dove aderi ad Avanguardia Nazionale — e poi in Argentina, costituitosi nel 1979, CONFESSO NEL 1984 ideazione ed esecuzione dell’attentato SENZA RIPUDIARE LE PROPRIE AZIONI E RIVENDICANDO LA QUALITA DI SOLDATO POLITICO. Dichiaro di confessare allo scopo di «fare chiarezza», AVENDO COMPRESO CHE TUTTE LE PRECEDENTI AZIONI DELLA DESTRA RADICALE, INCLUSE LE STRAGI, ERANO STATE IN REALTA MANOVRATE DA QUELLO STESSO REGIME CHE SI PROPONEVA DI ATTACCARE</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>IL CONTROESEMPIO ALLA FORMA DEL FATTO ACCERTATO SENZA SANZIONE, ED E DEFINITIVO. La relazione lo qualifica «un fatto storico accertato E CONSACRATO IN GIUDICATI PENALI DI CONDANNA»: l’illecita copertura degli estremisti autori dell’attentato DA PARTE DI ALTI UFFICIALI DELL’ARMA, fra cui un colonnello CONDANNATO DALLA CORTE D’ASSISE D’APPELLO DI VENEZIA PER FALSO MATERIALE E IDEOLOGICO E PER SOPPRESSIONE DI PROVE, con decisione confermata dalla Cassazione. La Commissione annota l’aggravante: un ufficiale che DEPISTA L’INDAGINE SU UN ATTENTATO COSTATO LA VITA A 3 CARABINIERI</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>LA PROVA CHE AVEVANO DALL’INIZIO: l’ordinovista ucciso nel conflitto a fuoco durante il dirottamento aereo di Ronchi dei Legionari ERA STATO TROVATO IN POSSESSO DELLA STESSA ARMA usata per sparare contro i vetri dell’automobile in cui era stata collocata la bomba, E I CUI BOSSOLI ERANO STATI REPERTATI DAI CARABINIERI STESSI. Ne discende la conclusione della relazione: la pista rossa subito imboccata «NON PUO GIUSTIFICARSI NEPPURE CON UNA VOLONTA DI TROVARE COMUNQUE IL COLPEVOLE, ANCHE A FINI DI IMMAGINE; emerge infatti chiaro L’INTENTO DELIBERATO DI STRUMENTALIZZARE UN EPISODIO E UNA CRIMINALIZZAZIONE DELLA SINISTRA EVERSIVA, SECONDO UN DISEGNO STRATEGICO PRECISO»</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>DUE ELEMENTI ULTERIORI, CON I RISPETTIVI GRADI. PRIMO, A VERBALE: in un drammatico confronto istruttorio un colonnello, accusato di aver indirizzato le indagini sulla pista rossa, replica «CHI LO HA INDIRIZZATO SULLA PISTA ROSSA? IO O LA VELINA DEL GENERALE PALUMBO? NON SI DIMENTICHI CHE IL GENERALE PALUMBO ERA ISCRITTO ALLA P2, SAREBBE ORA DI PARLARE DELL’ALTRA VELINA CHE BLOCCO L’INDAGINE A DESTRA» — per poi, TRINCERANDOSI DIETRO LA FACOLTA DI NON RISPONDERE, dichiarare di non sapere nulla di tale velina. SECONDO, GRADUATO DALLA RELAZIONE STESSA COME «CERTO, O ALMENO ESTREMAMENTE PROBABILE»: che il servizio militare conoscesse l’identita dei colpevoli fin dal 1972, come proverebbe — SECONDO LE SOLE DICHIARAZIONI DI VINCIGUERRA — la trasferta di un capitano a Padova pochi giorni dopo il dirottamento, con la frase «ORA BASTA FARE FESSERIE»</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tomo I — E IL CASO PIU FORTE DELL’INTERO CORPUS ITALIANO, ED E ANCHE IL CONTRAPPESO OBBLIGATORIO: dimostra che il depistaggio di Stato PUO ESSERE ACCERTATO E PUNITO IN VIA DEFINITIVA. Un’opera che sostenga l’impunita sistematica deve partire da qui, non aggirarlo</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>L’«organismo di sicurezza» sopra la Rosa dei Venti — LA DEFINIZIONE GIURIDICA DELLA TESI, IN UN MANDATO DI CATTURA</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 177-186; mandato di cattura del giudice istruttore Giovanni Tamburino contro il capo del servizio militare; deposizione del colonnello Amos Spiazzi alla Commissione P2; deposizione di Ferruccio Parri alla Commissione d’inchiesta sul SIFAR, relazione di maggioranza pagine 554-557. Testo gia nel corpus</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>LA DEFINIZIONE, TESTUALE, DA UN ATTO GIUDIZIARIO: «UNA ORGANIZZAZIONE CHE, DEFINITA DI SICUREZZA, DI FATTO SI PONE COME OSTACOLO RISPETTO A DETERMINATE MODIFICAZIONI DELLA POLITICA INTERNA E INTERNAZIONALE, OSTACOLO CHE LIMITANDO LA SOVRANITA POPOLARE E REALIZZANDOSI CON MODALITA DI AZIONE ANORMALI, ILLEGALI, SEGRETE E VIOLENTE, CONFERISCE CARATTERE EVERSIVO ALL’ORGANIZZAZIONE STESSA». NON E EVERSIVA PERCHE VUOLE ROVESCIARE LO STATO: E EVERSIVA PERCHE IMPEDISCE MUTAMENTI LIMITANDO LA SOVRANITA POPOLARE. E l’asse costituzionale dell’opera, formulato da un giudice istruttore in un mandato di cattura</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>LA STRUTTURA A DUE LIVELLI: la Rosa dei Venti era organizzazione eversiva in senso stretto; L’ORGANISMO DI SICUREZZA LE STAVA STRUTTURALMENTE AL DI SOPRA ed era «qualcosa di molto piu istituzionale, ANCHE SE GIURIDICAMENTE INESISTENTE, dai fini non necessariamente eversivi». Aveva CARATTERE DI SOPRANAZIONALITA, coincideva in gran parte con LA STRUTTURA DEI VERTICI DEGLI UFFICI INFORMATIVI DELLE VARIE FORZE ARMATE, e agiva in assoluta segretezza IN COLLEGAMENTO CON LE FORZE ANALOGHE DEGLI ALTRI PAESI DELLA NATO. La relazione annota che «questo e l’aspetto piu delicato della vicenda, quello che probabilmente MISE IN MOTO IL PRECIPITOSO MECCANISMO DI AVOCAZIONE DELLE INDAGINI A ROMA»</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>LA QUALIFICAZIONE CHE L’OPERA DEVE CONSERVARE, PERCHE LIMITA LA TESI: lo scopo prioritario era impedire la conquista delle leve del potere da parte dei comunisti o piu in generale delle sinistre nei paesi NATO; i mezzi potevano comprendere «ANCHE, MA NON NECESSARIAMENTE, LO SPARGIMENTO DI SANGUE»; e per questo l’organismo «NON POTEVA ESSERE CONSIDERATO UN’ORGANIZZAZIONE EVERSIVA IN SENSO STRETTO, TENDENDO PIU A CONSERVARE LO STATUS QUO POLITICO CHE A SOVVERTIRLO». E STRUTTURA CONSERVATIVA, NON GOLPISTA: chi la descrive come macchina di colpi di Stato ne fraintende la funzione</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>«ESIGENZA TRIANGOLO», E LA RETTIFICA A UNA VOCE PRECEDENTE DI QUESTO REPERTORIO. Verso le 21 del 7 DICEMBRE 1970 l’ufficiale ricevette dall’ufficio informativo del comando di reggimento un fonogramma: «ATTUATE ESIGENZA TRIANGOLO», che indicava l’impiego immediato di MILITARI SELEZIONATI IN BASE ALLA FEDE POLITICA. Destinazione: SESTO SAN GIOVANNI, «UNA DELLE ZONE DI MAGGIOR FORZA ELETTORALE DEL PARTITO COMUNISTA». Il contrordine giunse ALL’ALTEZZA DELLA STAZIONE DI AGRATE — non alle porte di Milano come registrato in precedenza — E TRASFORMAVA L’OPERAZIONE IN UNA SEMPLICE ESERCITAZIONE. Riscontro indipendente di continuita: la deposizione di Ferruccio Parri sul reclutamento, NEL 1964, di ex carabinieri e militari in congedo da impiegare in funzione di appoggio in caso di emergenza</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tomo I e Metodologia — 3 ACQUISIZIONI. LA DEFINIZIONE DI TAMBURINO VA POSTA IN ESERGO ALL’OPERA. La qualificazione conservativa va conservata, perche rende la tesi piu difendibile e non piu debole. E IL CONTRORDINE CHE DECLASSA L’OPERAZIONE A ESERCITAZIONE E IL MECCANISMO DELLA SANATORIA GIA VISTO NEL 1956, applicato non a un accordo ma a una mobilitazione armata</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n"/>
+      <c r="L14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Alto Adige — il caso Spiazzi a statuto irrisolto, e il fatto accertato di Amplatz e Klotz</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 185-187; deposizione alla Commissione P2; istruttoria della magistratura di Bolzano; deposizione resa al giudice istruttore di Venezia Mastelloni; intervista televisiva nella sesta puntata del 17 GENNAIO 1990. Testo gia nel corpus</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>L’AFFERMAZIONE. In servizio in quella regione nel momento di maggiore virulenza del terrorismo sudtirolese, l’ufficiale riferisce che UN SUPERIORE GLI CHIESE COME MAI NEL SETTORE DA LUI CONTROLLATO NON AVVENISSERO ATTENTATI; e alla sua replica «non e contento? non va bene?», gli fu risposto che «PER INTERESSI DI CARATTERE GLOBALE» cio non era un fatto positivo. Segue l’episodio: «IO HO TROVATO DUE CARABINIERI DEL SIFAR CHE STAVANO FACENDO UN ATTENTATO. LI HO PRESI, LI HO ARRESTATI, e mentre andavo verso Bolzano per consegnarli al comando di settore, MI SONO VENUTI INCONTRO CARABINIERI E POLIZIA, ME LI HANNO PRESI, ed il giorno dopo MI HANNO RISPEDITO A VERONA, ED HO CHIUSO CON L’ALTO ADIGE»</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>LO STATUTO E IRRISOLTO, E VA PRESENTATO COSI. Dopo la messa in onda dell’intervista la magistratura di Bolzano apri un’istruttoria E CONCLUSE CHE IL FATTO NARRATO «O ERA NON VERO O SI ERA VERIFICATO IN DATA DIVERSA DA QUELLA INDICATA». MA LA COMMISSIONE RILEVA CHE IL GIUDICE NON AVEVA POTUTO TENER CONTO, PER RAGIONI TEMPORALI, DI UNA SUCCESSIVA DEPOSIZIONE: quella di un maresciallo dei carabinieri in servizio prima al SIFAR e poi al SID, il quale davanti al giudice istruttore di Venezia CONFERMO L’EPISODIO, POICHE I DUE AGENTI ARRESTATI ERANO ALLE SUE DIPENDENZE. Affermazione, smentita giudiziaria, e riscontro sopravvenuto che la smentita non poteva considerare: NESSUNA DELLE 3 VA TACIUTA</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>LE PAROLE DELL’INTERVISTA, DA CITARE COME OPINIONE DEL DICHIARANTE E NON COME ACCERTAMENTO: «SONO FERMAMENTE CONVINTO CHE, COSI COME TANTI ALTRI FATTI GRAVI DEL NOSTRO PAESE, ANCHE IN ALTO ADIGE SI VOLEVA CREARE UN DETERMINATO CLIMA DI TENSIONE»; e, alla domanda se il terrorismo altoatesino fosse stato manovrato dai servizi segreti NON SOLTANTO ITALIANI: «SENZ’ALTRO E STATO MANOVRATO DA PARTI DEVIATE DEI SERVIZI O ADDIRITTURA DAI SERVIZI PER ORDINE DEI POLITICI»</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>E IL FATTO ACCERTATO, CHE E ASSAI PIU GRAVE DELL’EPISODIO CONTESTATO. La relazione scrive che, al di la del caso riferito dall’ufficiale, LA COMMISSIONE PARLAMENTARE ACCERTO FATTI DI INAUDITA GRAVITA, e ne cita uno: LA CONFERMA CHE L’UCCISIONE DI ALOIS AMPLATZ E IL FERIMENTO DI GEORG KLOTZ FURONO IL RISULTATO DI UN’OPERAZIONE CONCORDATA FRA POLIZIA, CARABINIERI E SERVIZI SEGRETI, CON IL PIENO AVALLO DEL POTERE POLITICO, CHE ERA STATO COSTANTEMENTE TENUTO AL CORRENTE</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Tomo I e Metodologia — ACQUISIZIONE CAPITALE: la Regola di ferro dei 3 piani vieta di passare dall’insabbiamento accertato al mandato asserito senza prova diretta. QUI IL PIANO DEL MANDATO E RAGGIUNTO DALL’ACCERTAMENTO STESSO, perche la Commissione scrive che il potere politico diede pieno avallo e fu costantemente informato. E il punto in cui la catena, che altrove si spezza sotto il vertice, NON SI SPEZZA</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Ordine Nuovo, servizi italiani e rete informativa nelle basi NATO — e IL PASSAGGIO A EST DEGLI STESSI OPERATORI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Archivio storico del Senato, Commissione parlamentare d’inchiesta sul terrorismo e sulle stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, «Stragi e terrorismo in Italia dal dopoguerra al 1974», DATATO 22 GIUGNO 2000, pagine 141-149 su 245 complessive; fonti citate: ordinanza-sentenza Salvini pagine 316, 357 e 414 e seguenti, ordinanza Grassi pagina 199, interrogatori di Carlo Digilio del 27 NOVEMBRE 1993 e del 5 MAGGIO 1996</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMULAZIONE DELLA COMMISSIONE, CON LA SUA CAUTELA DA CONSERVARE: «IL LEGAME TRA ORDINE NUOVO, SERVIZI SEGRETI E RETE INFORMATIVA ALL’INTERNO DELLE BASI NATO — SOSTANZIALMENTE RIFERIBILE AGLI STATI UNITI — E IL NODO ATTORNO IL QUALE SI E SVILUPPATA, TRA IL 1969 E IL 1974, LA STRATEGIA DELLE STRAGI FASCISTE, O, SECONDO UNA DEFINIZIONE DIFFUSA E CERTAMENTE NON PRIVA DI FONDAMENTO, STRAGI DI STATO». La formula «definizione diffusa e non priva di fondamento» NON EQUIVALE AD ACCERTAMENTO e va citata per intero</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>LA QUALITA DEGLI INFORMATORI, CHE MODIFICA LA CATEGORIA: non semplici confidenti o provocatori, ma «VERI E PROPRI AGENTI INFO-OPERATIVI, I QUALI AGIVANO, CON MARGINI DI AUTONOMIA, RICEVENDO PRECISE ISTRUZIONI. AGENTI CHE SI SONO MOSSI SU SCALA INTERNAZIONALE»</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>IL FATTO CHE COMPLICA LA TESI BIPOLARE, E VA REGISTRATO PROPRIO PER QUESTO. Dal fascicolo del servizio militare intestato a un informatore inserito negli ambienti ordinovisti EMERGE CHE COSTUI AVEVA STABILITO CONTATTI IN CECOSLOVACCHIA «ANCHE A FINI DI ADDESTRAMENTO»; il collaboratore Digilio conferma viaggi continui di costui nei paesi dell’Est, SEGNATAMENTE IN ROMANIA E JUGOSLAVIA, pur dichiarando di non avere mai saputo dei suoi rapporti con il servizio. E ANCORA: uno dei capi della cosiddetta cellula americana AVEVA ORGANIZZATO UNA SERIE DI MISSIONI ALL’EST EUROPEO, ottenendo in Cecoslovacchia, PRESSO ELEMENTI CROATI IVI RESIDENTI, notizie tecniche sul trattamento delle leghe metalliche; e quel medesimo uomo era colui che, PER CONTO DELLA STRUTTURA NATO, MANTENEVA I CONTATTI CON GLI USTASCIA CROATI</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>CHE COSA QUESTO PROVA E CHE COSA NO. PROVA che gli stessi operatori attraversavano la linea dei blocchi per fini tecnici, addestrativi e organizzativi, e che la rete non coincideva con la geografia dell’alleanza. NON PROVA alcun coordinamento fra le due superpotenze: prova il contrario di una geometria pulita, cioe l’esistenza di CANALI INDIVIDUALI TRASVERSALI. L’opera che ne facesse una prova di convergenza USA-URSS forzerebbe il documento; l’opera che lo tacesse perche scomodo violerebbe la propria regola</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II — E LA VERIFICA DELLA TESI DELL’AGIRE DI SPONDA SUL PIANO INTERNAZIONALE: attori europei che si servono simultaneamente di piu patroni, e non due patroni che si accordano sopra le loro teste</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>LE MISSIONI A EST E LA DOMANDA LASCIATA APERTA DALLA COMMISSIONE — nodo capitale dell’opera</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Archivio storico del Senato, Doc. XXIII n. 64, Vol. I, Tomo II, pagine 148-150; interrogatori di Carlo Digilio al giudice istruttore di Milano del 4 MAGGIO 1996 e al giudice istruttore di Venezia del 9 GENNAIO 1997; intervista televisiva del 1990; bibliografia indicata dalla Commissione: de Lutiis, «Storia dei servizi segreti in Italia», Editori Riuniti 1991, pagine 327-331, e Cipriani, «Lo spionaggio politico in Italia»</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>LA FRASE CHE VALE L’INTERA OPERA, TESTUALE: «POCO O NULLA SI CONOSCE SULLE EVENTUALI CONNIVENZE E/O CONVERGENZE DEI SERVIZI SEGRETI DEI DUE BLOCCHI PER MANTENERE FOCOLAI DI TENSIONE UTILI AL MANTENIMENTO DELLO STATUS QUO NELL’AMBITO DEI DUE DIVERSI SCHIERAMENTI». E la tesi bipolare, MA CON UN FINE DIVERSO E ASSAI PIU DIFENDIBILE: non impedire l’unificazione europea, BENSI CONSERVARE LA DISCIPLINA INTERNA DI CIASCUN BLOCCO. Cosi formulata NON RICHIEDE ALCUN COORDINAMENTO: bastano due interessi paralleli</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>E L’INVITO ESPLICITO, CHE E IL MANDATO DI QUEST’OPERA: «occorre sottolineare come UN APPROFONDIMENTO A PARTE MERITEREBBE LA VICENDA DELLE MISSIONI AD EST, partendo proprio dall’ENORME MATERIALE FORNITO da Brenneke al giornalista Remondino, A SUO TEMPO LIQUIDATO COME POCO RILEVANTE SIA IN SEDE POLITICA CHE DALL’AUTORITA GIUDIZIARIA»</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>IL CASO BRENNEKE, A STATUTO CONTESO. L’ex agente statunitense a contratto, con base nel Nord-Est, intervistato nel 1990 sostenne DI ESSERSI RECATO PIU VOLTE A PRAGA PER CONTO DEL SERVIZIO AMERICANO A RIFORNIRSI DI ARMI ED ESPLOSIVI destinati agli arsenali del terrorismo filoatlantico e dei gruppi neofascisti vicini alla loggia. La vicenda fu ritenuta poco credibile anche per «UNA A DIR POCO BUROCRATICA SMENTITA DELLE AUTORITA STATUNITENSI» sulla sua appartenenza all’intelligence. MA DIGILIO HA CONFERMATO che CARRETT gli disse che «uno dei soggetti impiegati in operazioni speciali nel Nord-Est italiano per la loro struttura era tale Richard Brenneke, CHE AVEVA FATTO SERVIZIO IN PARTICOLARE A TRIESTE E NEL FRIULI FINO AL 1974». NOTA DI CAUTELA ESTERNA: l’attendibilita complessiva di quel dichiarante e stata contestata in altre sedi e su altre vicende; il riscontro qui vale per la sola presenza operativa</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>L’AVVERTIMENTO METODOLOGICO CHE LA COMMISSIONE RIVOLGE A CHI SCRIVE DI QUESTI FATTI: l’operativita degli informatori nell’Est europeo, nei campi d’addestramento e nel traffico d’armi «DOVREBBE INDURRE A MAGGIOR PRUDENZA COLORO I QUALI RITENGONO, IN MANIERA FIN TROPPO SEMPLICISTICA, CHE LA SOLA PRESENZA DI UN’ARMA PROVENIENTE DA EST STIA A INDICARE IN MANIERA CATEGORICA LE RESPONSABILITA DEGLI APPARATI DI QUEI PAESI». Si aggiunga il triangolo geografico documentato: l’uomo che per conto della struttura NATO teneva i contatti con gli ustascia ATTIVI IN JUGOSLAVIA E CECOSLOVACCHIA li teneva anche con i FUORIUSCITI CON BASE A VALENCIA, NELLA SPAGNA FRANCHISTA</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II — 3 CONSEGUENZE. PRIMA: la tesi bipolare va riformulata come la formula la Commissione, cioe come CONSERVAZIONE DELLO STATUS QUO DI CIASCUN BLOCCO, e cosi diventa sostenibile. SECONDA: l’opera ha un mandato scritto da un organo dello Stato, e deve dichiararlo. TERZA: l’avvertimento sulla provenienza delle armi VA CITATO NEL TESTO, perche e l’inferenza che la letteratura del genere compie piu spesso e che la Commissione dichiara semplicistica</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>verificato 4.8.2026</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n"/>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="n"/>
+      <c r="L17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Interferenza russa nelle elezioni statunitensi del 2016 — rapporto del procuratore speciale (2019) e quinto volume della Commissione ristretta del Senato sull’intelligence (18 AGOSTO 2020) — STATUTO ESATTO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Stati Uniti; il quinto volume, intitolato «Russian efforts to influence the Trump Campaign and the 2016 election», consta di 9606 PAGINE, fondate su centinaia di audizioni e oltre un milione di documenti, ed e frutto di un’indagine bipartisan durata piu di 3 anni. Entrambi i testi sono pubblicamente consultabili</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>CIO CHE E ACCERTATO. Che il presidente della Federazione Russa ORDINO L’OPERAZIONE di violazione delle reti e degli account collegati al partito avversario e la diffusione di materiale dannoso per la candidata. Che il capo della campagna elettorale lavorava strettamente con un cittadino russo CHE LA COMMISSIONE DEFINISCE SENZA ESITAZIONI «UN UFFICIALE DELL’INTELLIGENCE RUSSA», operante come tramite con un oligarca. Che in numerose occasioni EGLI GLI TRASMISE DATI INTERNI DI SONDAGGIO E STRATEGIA DI CAMPAGNA. E la conclusione testuale: quel livello di accesso e quella disponibilita a condividere informazioni «RAPPRESENTARONO UNA GRAVE MINACCIA CONTROSPIONISTICA»</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>DOVE LA CATENA SI SPEZZA, ED E LA FORMA RICORRENTE DI QUESTO REPERTORIO. LA COMMISSIONE NON E RIUSCITA A DETERMINARE PERCHE quei dati fossero trasmessi NE CHE COSA IL DESTINATARIO NE ABBIA FATTO, in parte per l’uso di messaggistica cifrata. Ottenne «alcune informazioni» secondo cui costui «POTREBBE ESSERE STATO COLLEGATO» all’operazione di sottrazione e diffusione della corrispondenza — E QUELLA SEZIONE E IN LARGA PARTE ESPUNTA. Un senatore chiese in calce la declassificazione, osservando che il testo contiene informazioni espunte DIRETTAMENTE RILEVANTI PER L’INTERFERENZA NELL’ELEZIONE SUCCESSIVA</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>CIO CHE NON E ACCERTATO, E VA SCRITTO CON LA STESSA EVIDENZA. Il procuratore speciale concluse DI NON AVER IDENTIFICATO PROVE DI UN NESSO fra la condivisione dei dati e l’interferenza, e DI NON AVER STABILITO che vi fosse stato coordinamento con il governo russo sulle attivita di interferenza. E LO STESSO RAPPORTO BIPARTISAN HA PRODOTTO DUE LETTURE OPPOSTE DAI PROPRI MEMBRI: il presidente pro tempore dichiaro che la commissione non trovo «assolutamente alcuna prova» di collusione, pur avendo trovato prove «irrefutabili» di ingerenza russa; 5 MEMBRI DI MINORANZA SCRISSERO IN APPENDICE che «questo e l’aspetto che ha la collusione». Il difensore dell’interessato defini le conclusioni «pura congettura»</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>REGOLA D’USO PER L’OPERA, TASSATIVA. NON PUO ESSERE CERTIFICATA L’ESISTENZA DI UN «ASSE», perche il termine designa un allineamento strategico volontario che i due rapporti NON STABILISCONO. Cio che si certifica e altro e basta: interferenza ordinata al vertice, contatti estesi, trasmissione di dati interni a un ufficiale dell’intelligence avversaria, GRAVE MINACCIA CONTROSPIONISTICA ACCERTATA IN SEDE BIPARTISAN, e IMPOSSIBILITA DICHIARATA DI RISALIRE OLTRE. L’allineamento politico odierno e materia politica contesa e NON VA TRATTATO COME FATTO DOCUMENTATO</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia e Tomo II — E IL PATTERN DEL REPERTORIO APPLICATO AL PRESENTE: fatto accertato, catena interrotta appena sotto il vertice, sezione decisiva espunta, e due letture opposte del medesimo atto. Scritto in questa forma e inattaccabile; scritto come «asse certificato» cade alla prima obiezione</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="n"/>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Il caso Metropol — 18 ottobre 2018, e il decreto di archiviazione del 27 APRILE 2023 — STATUTO ESATTO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Procura della Repubblica di Milano, ipotesi di corruzione internazionale, fascicolo aperto nel luglio 2019; richiesta di archiviazione dell’aggiunto e di due sostituti; DECRETO DEL GIUDICE PER LE INDAGINI PRELIMINARI DI MILANO DEL 27 APRILE 2023. Origine: registrazione effettuata da uno dei presenti e da lui consegnata a giornalisti, pubblicata da un sito statunitense e da un settimanale italiano</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>L’EPISODIO. Il 18 OTTOBRE 2018, 24 ORE DOPO UNA VISITA DEL LEADER DEL PARTITO NELLA CAPITALE RUSSA, 6 persone — 3 italiane e 3 russe — si incontrano all’hotel Metropol di Mosca. Oggetto: la vendita di circa 3 MILIONI DI TONNELLATE DI CARBURANTE da una compagnia petrolifera russa a una compagnia italiana, con una quota stimata in SESSANTACINQUE MILIONI DI DOLLARI destinata alle casse del partito per la campagna europea. Nella registrazione una voce attribuita al presidente dell’associazione bilaterale afferma: «NOI VOGLIAMO CAMBIARE L’EUROPA. UNA NUOVA EUROPA DEVE ESSERE VICINA ALLA RUSSIA, COME ERA PRIMA, PERCHE NOI VOGLIAMO LA NOSTRA SOVRANITA»</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CIO CHE IL DECRETO ACCERTA, PUR ARCHIVIANDO: che L’OBIETTIVO ERA IL FINANZIAMENTO MA NON FU RAGGIUNTO; che vi fu, secondo i pubblici ministeri, UNA «PROVA GENERALE», e che l’affare da un miliardo e mezzo di dollari NON ANDO IN PORTO. E soprattutto, DAGLI ATTI: il ruolo nell’operazione del teorico eurasiatista, il quale — RICOSTRUISCONO I PUBBLICI MINISTERI — PARTECIPO «ALLA TRATTATIVA PER LA VENDITA» DI PETROLIO IN RAPPRESENTANZA «DI ALTI ESPONENTI DELL’ESTABLISHMENT RUSSO». Emergono inoltre agli atti contatti fra gli indagati e il leader del partito, CHE NON ERA INDAGATO</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE LA CATENA SI E INTERROTTA, ED E IL PUNTO CHE FA DI QUESTA LA VOCE SPECULARE DI QUELLA STATUNITENSE: nessuno degli interlocutori russi sarebbe stato pubblico ufficiale — presupposto del reato contestato — e IL DINIEGO ALLE ROGATORIE HA DI FATTO IMPEDITO DI RISALIRE A POSSIBILI VERTICI SOPRA DI LORO. Nel caso americano la catena si spezza per messaggistica cifrata ed espunzioni; QUI PER RIFIUTO DI COOPERAZIONE GIUDIZIARIA DA PARTE DELLO STATO INTERESSATO. In entrambi i casi il vertice non e irraggiungibile per assenza di indizi: E RESO IRRAGGIUNGIBILE</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>LE NEGAZIONI, DA RIPORTARE. Il leader del partito: «mai preso un rublo, un euro, un dollaro o un litro di vodka di finanziamento dalla Russia». Il principale indagato dichiaro a un’emittente europea CHE UN INCONTRO SIMILE NON ERA MAI AVVENUTO, aggiungendo pero di essersi recato in quell’albergo per incontrare imprenditori locali: LA CONTRADDIZIONE VA REGISTRATA, NON RISOLTA DALL’AUTORE. Un difensore ha definito l’intera vicenda infondata. NESSUNA CONDANNA E STATA PRONUNCIATA E L’ARCHIVIAZIONE E DEFINITIVA</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II e Metodologia — VOCE SPECULARE OBBLIGATORIA. Chi registra il caso statunitense e tace questo, o viceversa, sta scegliendo un versante. LE DUE VOCI VANNO LETTE INSIEME: due indagini su due versanti opposti, entrambe accertano contatti e obiettivo, entrambe si fermano sotto il vertice, e in entrambe CIO CHE MANCA NON E LA PROVA MA LA VIA PER ARRIVARCI</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="n"/>
+      <c r="L19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Le due fratture massoniche politicamente rilevanti — 1877 e 1908 — E LA MAPPATURA DA SCARTARE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Fonti: atti dell’Assemblea generale del Grande Oriente di Francia del 1877 e rifacimento dei rituali del 1886; storiografia sulla scissione italiana del giugno 1908 e sul Supremo Consiglio d’Italia; letteratura sulla massoneria continentale e sulle obbedienze italiane</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>MAPPATURA DA SCARTARE, PERCHE VERIFICATA E CONTRARIA: lo scisma inglese fra Antients e Moderns del 17 LUGLIO 1751 NON E UNA FRATTURA FRA COSTITUZIONALISMO E IMPERIALISMO. Le divergenze accertate sono LITURGICHE E SOCIALI — l’Arco Reale come parte integrante o appendice facoltativa, l’uso dei Diaconi, le costituzioni di Dermott derivate da quelle irlandesi contro il libro di Anderson — e la nuova obbedienza nacque «sulle stesse tensioni religiose e di classe che sostennero il successo del metodismo contro la Chiesa d’Inghilterra». LA DIREZIONE E ROVESCIATA: furono gli Antients, partito irlandese e plebeo, ad accusare i Moderns di ESCLUSIVITA ELITARIA e di aver diluito l’eredita operativa in una societa di gentiluomini. L’unione del 27 DICEMBRE 1813 avvenne sotto un figlio del re e adotto in prevalenza i riti degli Antients</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>LA PRIMA FRATTURA POLITICAMENTE RILEVANTE E DEL 1877: l’Assemblea generale del Grande Oriente di Francia decise DI SOPPRIMERE IL PRECETTO FINO AD ALLORA PROCLAMATO COME PRINCIPIO FONDAMENTALE, LA CREDENZA IN DIO E NELL’IMMORTALITA DELL’ANIMA; furono poi eliminati dal rito tutti i riferimenti al Grande Architetto e rimosso il Volume della Legge Sacra, CON CONSEGUENTE SEPARAZIONE DALLA GRAN LOGGIA DI LONDRA. I nuovi rituali giunsero solo NEL 1886, «perche furono molte le resistenze da vincere». Ne deriva la divisione permanente fra obbedienze REGOLARI, anglo-americane, teiste e per statuto apolitiche, e obbedienze LIBERALI O ADOGMATICHE, continentali, che ammettono atei e agnostici e CHE NON RINUNCIANO A UN’AZIONE POLITICA IN FAVORE DEI DIRITTI DELL’UOMO E DELLA DEMOCRAZIA</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA E ITALIANA, ED E UN EVENTO DEL PRIMO ASSE IN FORMA PURA. Nel GIUGNO 1908 — le fonti indicano il 24 o il 26: DISCREPANZA DA RISOLVERE — si consuma nel Supremo Consiglio d’Italia la scissione che origina l’obbedienza poi detta di Piazza del Gesu. LA CAUSA ACCERTATA: LA DECISIONE DEL GRANDE ORIENTE D’ITALIA DI IMPORRE AI FRATELLI PARLAMENTARI UN VOTO CONTRARIO ALL’INSEGNAMENTO RELIGIOSO NELLE SCUOLE. Il sovrano gran commendatore del Rito scozzese, definito FORTE OPPOSITORE DELLA POLITICIZZAZIONE FORZATA, pose il veto formale alla proposta di censura, e la nuova obbedienza fu costituita ESPRESSAMENTE «PER IL PRINCIPIO FONDAMENTALE MASSONICO DELLA LIBERTA DI COSCIENZA»</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE QUESTO EPISODIO VALE PIU DELL’INTERA GENEALOGIA SETTECENTESCA: un’obbedienza che pretende di VINCOLARE IL VOTO DI PARLAMENTARI ELETTI compie esattamente cio che la prova della riserva individua — determinare un esito fuori dalla procedura elettorale. E CHI SI SCISSE LO FECE CON ARGOMENTO COSTITUZIONALE. LA POLARITA E DUNQUE ROVESCIATA rispetto all’ipotesi corrente, che assegna al ramo scozzese e tradizionale la posizione anticostituzionale</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 e Apparato — LA MASSONERIA E UN LUOGO DOVE LA FAGLIA PASSA, NON LA SUA SORGENTE. Dopo il 1813 le obbedienze regolari vietano per statuto la discussione politica in loggia, il che rende la categoria un pessimo predittore. Le logge coperte contano in quest’opera NON PERCHE MASSONICHE MA PERCHE IRREGOLARI, OCCULTE E TRASVERSALI AI DOMINI: falliscono la prova della riserva, non discendono da uno scisma</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="n"/>
+      <c r="L20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>La posizione dottrinale della Santa Sede sulla massoneria — SERIE COMPLETA, E IL RIFIUTO ESPRESSO DELLA DISTINZIONE FRA OBBEDIENZE</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Notificazione ai presidenti delle conferenze episcopali del 19 LUGLIO 1974; Dichiarazione del 17 FEBBRAIO 1981 (AAS 73/1981, pagine 240-241); DICHIARAZIONE «QUAESITUM EST» DEL 26 NOVEMBRE 1983, firmata dal prefetto Joseph Ratzinger e dal segretario Jerome Hamer, APPROVATA DA GIOVANNI PAOLO II, in AAS LXXVI (1984) pagina 300; articolo non firmato su L’Osservatore Romano del 23 FEBBRAIO 1985; linee guida della Conferenza episcopale italiana del 2003; RISPOSTA DEL DICASTERO PER LA DOTTRINA DELLA FEDE DEL 13 NOVEMBRE 2023, a firma del prefetto Victor Fernandez, APPROVATA DA PAPA FRANCESCO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>L’OCCASIONE E IL TESTO. Fu chiesto se il giudizio della Chiesa fosse mutato per il fatto che il nuovo Codice del 1983 non menziona espressamente la massoneria come il precedente; la risposta e che si tratta di UN CRITERIO REDAZIONALE seguito anche per altre associazioni «in quanto comprese in categorie piu ampie». E dunque: «RIMANE PERTANTO IMMUTATO IL GIUDIZIO NEGATIVO DELLA CHIESA NEI RIGUARDI DELLE ASSOCIAZIONI MASSONICHE, POICHE I LORO PRINCIPI SONO STATI SEMPRE CONSIDERATI INCONCILIABILI CON LA DOTTRINA DELLA CHIESA E PERCIO L’ISCRIZIONE A ESSE RIMANE PROIBITA. I FEDELI CHE APPARTENGONO ALLE ASSOCIAZIONI MASSONICHE SONO IN STATO DI PECCATO GRAVE E NON POSSONO ACCEDERE ALLA SANTA COMUNIONE». La Dichiarazione vale come interpretazione autentica del canone 1374, che punisce chi si iscrive ad associazione che cospira contro la Chiesa</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>IL PUNTO DECISIVO, CHE CORREGGE OGNI LETTURA FONDATA SULLA DISTINZIONE FRA OBBEDIENZE REGOLARI E LIBERALI: «NON COMPETE ALLE AUTORITA ECCLESIASTICHE LOCALI DI PRONUNCIARSI SULLA NATURA DELLE ASSOCIAZIONI MASSONICHE CON UN GIUDIZIO CHE IMPLICHI DEROGA A QUANTO SOPRA STABILITO». E la spiegazione ufficiosa del 1985 lo esplicita: «MALGRADO LA DIVERSITA CHE PUO SUSSISTERE FRA LE OBBEDIENZE MASSONICHE, IN PARTICOLARE NEL LORO ATTEGGIAMENTO DICHIARATO VERSO LA CHIESA, LA SEDE APOSTOLICA VI RISCONTRA ALCUNI PRINCIPI COMUNI, CHE RICHIEDONO UNA MEDESIMA VALUTAZIONE DA PARTE DI TUTTE LE AUTORITA ECCLESIASTICHE». LA DISTINZIONE FRA REGOLARI E ADOGMATICHE, DECISIVA SUL PIANO POLITICO, E DICHIARATA IRRILEVANTE SUL PIANO DOTTRINALE</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>LA CONFERMA RECENTE, A QUARANT’ANNI ESATTI: la risposta del 13 novembre 2023, sollecitata da un vescovo delle Filippine e approvata dal Pontefice, ribadisce che «L’ISCRIZIONE ATTIVA ALLA MASSONERIA DA PARTE DI UN FEDELE E PROIBITA, A CAUSA DELL’INCONCILIABILITA TRA DOTTRINA CATTOLICA E MASSONERIA», e precisa che vi ricadono coloro che «FORMALMENTE E CONSAPEVOLMENTE» si sono iscritti e ne hanno abbracciato i principi, aggiungendo che LE MEDESIME MISURE SI APPLICANO AGLI ECCLESIASTICI ISCRITTI</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>IL LIMITE DA NON OLTREPASSARE, E LA CONTROPROVA STA NEL CORPUS STESSO. La posizione dottrinale NON SI TRADUCE AUTOMATICAMENTE IN COMPORTAMENTO POLITICO NE ELETTORALE: dedurre che partiti ed elettori di area cattolica condividano per cio stesso quella posizione e UN’INFERENZA, NON UN FATTO. E l’elenco sequestrato nel 1981, oggetto di questo repertorio, CONTIENE ISCRITTI DI PARTITI DI ISPIRAZIONE CATTOLICA: la proibizione dottrinale, per quanto reiterata e mai revocata, NON IMPEDI L’ISCRIZIONE</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 × Dominio 5 e Apparato — TERZA DIMENSIONE DA AGGIUNGERE ALLA TASSONOMIA: accanto alla fonte della legittimita e alla sede della sovranita va posto IL RAPPORTO CON L’AUTORITA RELIGIOSA, che e indipendente dalle prime due e che nessuna delle due predice. E la Santa Sede giudica il fenomeno TOUT COURT, cosi come il primo comma dell’articolo 18 proibiva le associazioni segrete tout court PRIMA CHE LA LEGGE DI ATTUAZIONE LO RESTRINGESSE</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Profilo statistico dell’elenco sequestrato nel 1981 — ELABORAZIONE SUI 960 RECORD DEL CORPUS</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Elaborazione condotta sul file tabellare presente nei file di progetto, che riporta 960 record su novecentosettantadue dichiarati, ordinati per numero di fascicolo, con lacuna dichiarata di 3 fascicoli attribuita alla copia utilizzata e non necessariamente alla fonte originale</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>RETTIFICA A UNA VOCE PRECEDENTE DI QUESTO REPERTORIO, DOVUTA. Era stato affermato che l’elenco contiene iscritti di partiti d’ispirazione cattolica: L’ELENCO NON RECA ALCUN DATO DI APPARTENENZA PARTITICA. Reca 41 record con titolo parlamentare, ma senza indicazione di partito. L’affermazione, che poggia su altre fonti, NON PUO ESSERE RICAVATA DA QUESTO DOCUMENTO e va attribuita alla sede in cui e stata accertata</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ACCERTAMENTO NEGATIVO CERTIFICATO, sulla copia utilizzata: LA RICERCA DI TITOLI ECCLESIASTICI — don, monsignore, padre, reverendo, fra, sacerdote, cardinale, abate — RESTITUISCE ZERO OCCORRENZE SU 960 RECORD. Il dato va enunciato con il proprio limite: riguarda i titoli riportati nell’elenco, non l’eventuale appartenenza di ecclesiastici priva di titolo nel documento</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>LA COMPOSIZIONE PER TITOLO, non esclusiva: 475 recano titolo dottorale, pari al 49 per cento; 205 RECANO UN GRADO MILITARE, PARI AL 21 PER CENTO — e nel dettaglio 82 COLONNELLI, 49 GENERALI, 48 CAPITANI, 37 TENENTI COLONNELLI, 16 MAGGIORI, 9 AMMIRAGLI. Seguono 50due professori, 44 avvocati, 41 fra deputati e senatori, 22 ragionieri, venti ingegneri, 12 geometri. UN ISCRITTO SU 5 PORTAVA UN GRADO MILITARE</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>GEOGRAFIA E STATO. Roma 31503 e Firenze 119: 472 SU 960, PARI AL 49 PER CENTO, IN DUE SOLE CITTA. Fuori d’Italia: Brasile 19, Buenos Aires 13, Argentina 8, Uruguay due, Stati Uniti due, Liberia due, Dakar uno — 42 VOCI SUDAMERICANE, che vanno lette accanto agli atti del processo romano sull’asse continentale. Quanto allo stato dell’affiliazione, SOLTANTO 101 RECORD RECANO ANNOTAZIONE: 42 in sonno, 36 deceduti, 10 PASSATI AL GRANDE ORIENTE, 8 passati ad altra loggia, 4 sospesi, uno espulso. AVVERTENZA TECNICA: alcuni campi contengono rumore d’estrazione</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Cerniera e Dominio 9 — DUE ACQUISIZIONI. I 10 PASSAGGI ALL’OBBEDIENZA REGOLARE documentano il transito fra struttura coperta e associazione palese, che e precisamente la fattispecie descritta dall’articolo primo della legge del 1982. E LA QUOTA MILITARE DEL 21 PER CENTO, con 9 ammiragli e 49 generali, va misurata contro il secondo comma dell’articolo 18 della Costituzione, che proibisce le associazioni perseguenti anche indirettamente scopi politici MEDIANTE ORGANIZZAZIONI DI CARATTERE MILITARE</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n"/>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Test di adiacenza numerica sull’elenco del 1981 — RISULTATO POSITIVO E SIGNIFICATIVO</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Elaborazione originale sui 960 record del file tabellare presente nei file di progetto, ordinati per numero di fascicolo. Metodo: conteggio delle coppie a numerazione consecutiva che condividono un attributo, e confronto con un modello nullo costruito su duemila permutazioni casuali dell’attributo a sequenza numerica invariata</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>IL DISEGNO, FISSATO PRIMA DEL CALCOLO. Se il numero di fascicolo rispecchia l’ordine di affiliazione, e se il reclutamento avvenne per coorti anziche per adesioni individuali, allora due iscritti con numeri consecutivi devono condividere la citta piu spesso di quanto il caso consenta. L’ipotesi nulla e che l’attributo sia distribuito indipendentemente dalla sequenza numerica</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>L’ESITO SULLA CITTA: su 955 coppie a numerazione consecutiva, 296 condividono la citta, pari al TRENTUNO PER CENTO, contro un valore atteso per puro caso di 150 E 6 DECIMI. L’osservato e quasi il doppio dell’atteso e la probabilita che si verifichi per caso e inferiore a una su 10mila. IL RECLUTAMENTO PROCEDETTE PER COORTI TERRITORIALI, E LA NUMERAZIONE NE CONSERVA L’ORDINE</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>I BLOCCHI PIU LUNGHI, CHE SONO IL DATO PIU ELOQUENTE: 24 FASCICOLI CONSECUTIVI, DAL 6099 AL SETTECENTO22, TUTTI FIORENTINI; 11 consecutivi romani dal quattrocentonovanta al cinquecento; e soprattutto 11 CONSECUTIVI BRASILIANI dal 597 al 607, seguiti da 6 CONSECUTIVI BRASILIANI dal 611 al 616. 17 DEI 19 RECORD BRASILIANI STANNO IN DUE BLOCCHI RAVVICINATI: l’affiliazione brasiliana non fu un accumulo di adesioni individuali ma UNA O DUE OPERAZIONI DATABILI NELLA SEQUENZA</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>IL RISULTATO SUL GRADO MILITARE VA LETTO AL CONTRARIO, ED E ALTRETTANTO UTILE: le coppie consecutive che condividono la condizione militare sono 674 SU 955, pari al settanta e 6 decimi per cento, contro un atteso di 636 e 4 decimi. LA DIFFERENZA E STATISTICAMENTE SIGNIFICATIVA MA MINIMA. NE SEGUE CHE LA LOGGIA NON RECLUTAVA UNA CATEGORIA PROFESSIONALE: RECLUTAVA LUOGHI, E I MILITARI ARRIVAVANO CON I LUOGHI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Cerniera e Metodologia — 3 AVVERTENZE E UNA CONSEGUENZA. Che il numero di fascicolo corrisponda all’ordine di affiliazione E UN’INFERENZA, sostenuta dall’addensamento ma non dimostrata altrimenti; 3 fascicoli mancano nella copia utilizzata; alcuni campi contengono rumore d’estrazione. LA CONSEGUENZA E CHE IL PATTERN DELL’ADDENSAMENTO, CHE SULLE 9 STRAGI AVEVA DATO ESITO NULLO, QUI DA ESITO POSITIVO CON LO STESSO METODO E LO STESSO MODELLO NULLO: lo strumento non e tarato per produrre negazioni</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>LE VOCI ESTERE DELL’ELENCO DEL 1981 — struttura a blocchi ed elaborazione originale, fondamento del Tomo Secondo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Elaborazione sui 960 record del file tabellare di progetto; riscontri sull’elenco alfabetico pubblicato dalla Presidenza del Consiglio il 21 MAGGIO 1981 e sulla relazione della Commissione d’inchiesta comunicata alle Camere il 12 LUGLIO 1984</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>LA STRUTTURA, CHE E IL RITROVAMENTO. Le voci con localizzazione extraitaliana sono 51 — e non 44 come indicato nell’indice generale dell’opera: DISCREPANZA DA RISOLVERE, verosimilmente per diverso criterio di inclusione. Di esse, TRENTA STANNO IN UN SOLO BLOCCO DI 33 NUMERI CONSECUTIVI, dal fascicolo 589 al 621, con soli 3 salti: 18 brasiliane, 8 argentine, due uruguaiane, due liberiane. IL 509 PER CENTO DELLE VOCI ESTERE OCCUPA IL 3 PER CENTO DELLA NUMERAZIONE. Non e un accumulo di adesioni: E UN’OPERAZIONE UNICA, COLLOCABILE NELLA SEQUENZA</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>LE IDENTIFICAZIONI, RISCONTRATE SU FONTI INDIPENDENTI. Al fascicolo 478, Buenos Aires, figura l’ammiraglio EMILIO EDUARDO MASSERA, membro della giunta militare insediatasi con il colpo di Stato del 1976 — con AVVERTENZA DI TRASCRIZIONE: il file tabellare lo qualifica come generale, mentre l’elenco pubblicato reca «amm». Al fascicolo 591, Argentina, figura JOSÉ LÓPEZ REGA, comandante dell’Alleanza Anticomunista Argentina e poi ministro, CHE SI ISCRISSE PERO IN SPAGNA. Al fascicolo SEICENTONOVE, Argentina, figura il generale CARLOS GUILLERMO SUÁREZ MASON. Nel medesimo blocco figurano inoltre un ammiraglio al 617 e un ufficiale brasiliano al 601</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>IL NESSO ACCERTATO IN SEDE GIUDIZIARIA: i giudici di Bologna hanno ricordato che dopo il colpo di Stato il capo della loggia «AVREBBE SCRITTO A MASSERA COMPLIMENTANDOSI PER IL BUON ESITO DELL’OPERAZIONE E PERCHE TUTTO SI ERA SVOLTO SECONDO I PIANI PRESTABILITI», e la Corte segnala che quel nome comparira negli elenchi sequestrati. E documentato inoltre che Massera si reco a visitare Gelli NELLO STABILIMENTO DI CASTIGLION FIBOCCHI. IL BLOCCO VA DUNQUE LETTO ACCANTO AGLI ERGASTOLI DEFINITIVI PRONUNCIATI A ROMA NEL 2021 PER L’ASSE CONTINENTALE SUDAMERICANO</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>LE AVVERTENZE DELLA COMMISSIONE, DA RIPORTARE SEMPRE. Le liste furono giudicate AUTENTICHE e ATTENDIBILI, ma la Commissione accerto che alcuni erano iscritti da prima della gestione contestata, che MOLTI NEGARONO LA PARTECIPAZIONE o sostennero di essere stati iscritti a loro insaputa, e AVANZO L’IPOTESI CHE LA LISTA NON FOSSE COMPLETA. Convergenza che valida l’estrazione: il computo qui condotto da 205 titoli militari e 41 parlamentari, contro i 208 e 44 delle fonti coeve</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Secondo — E IL FONDAMENTO DEL TOMO, E VA APERTO DA QUI: non dall’elenco delle voci estere, MA DALLA LORO DISPOSIZIONE. trenta affiliazioni sudamericane in 33 numeri consecutivi documentano un atto singolo; e fra esse un membro della giunta, il fondatore della Triplice A e un generale poi condannato</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="n"/>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>La posizione argentina di Licio Gelli, 1973-1981 — accertamenti parlamentari e giudiziari</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione parlamentare d’inchiesta; motivazioni della sentenza della Corte d’assise di Bologna nel procedimento Bellini, che ha acquisito sentenze sul Piano Condor; testimonianza resa alla Commissione da un dirigente massonico; Boletin Oficial argentino del 24 OTTOBRE 1973</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>LA CRONOLOGIA DOCUMENTATA. 4 FEBBRAIO 1973: Licio Gelli chiede al gran maestro dell’obbedienza italiana di essere nominato rappresentante massonico argentino presso di essa, e due giorni dopo il gran maestro scrive al gran segretario della Gran Loggia dell’Argentina trasmettendo la richiesta. 28 GIUGNO 1973, un mese dopo l’insediamento del nuovo presidente argentino: gli e concesso PASSAPORTO DIPLOMATICO NUMERO ZEROZEROMILLEOTTOCENTO47 in qualita di «delegato in missione speciale» — E L’ACCERTAMENTO E DELLA COMMISSIONE PARLAMENTARE. 18 OTTOBRE 1973: con decreto numero trentaquattro, firmato dal presidente e dal ministro degli Esteri, gli e conferita la massima onorificenza nazionale argentina, PUBBLICATA NEL BOLLETTINO UFFICIALE IL 24 OTTOBRE E NON DIFFUSA DALLA STAMPA</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>LA POSIZIONE ISTITUZIONALE. 13 SETTEMBRE 1974: cittadinanza argentina. SETTEMBRE 1974, con decreto: designazione a CONSIGLIERE ECONOMICO DELL’AMBASCIATA ARGENTINA IN ITALIA — DISCREPANZA CHIUSA MA CON ANOMALIA: l’atto e il DECRETO NUMERO SETTANTATRE DEL 2 SETTEMBRE 1974, emesso dal governo succeduto alla morte del presidente; una fonte anticipa la designazione all’agosto attribuendola a un decreto redatto con quel presidente, il quale era pero gia morto — vedi voce dedicata. In successione gli furono rilasciati 4 PASSAPORTI ARGENTINI, che gli consentirono di accreditarsi come diplomatico PER OLTRE 8 ANNI, DAL 1973 AL 19 MAGGIO 1981 — cioe FINO A DUE GIORNI PRIMA DELLA PUBBLICAZIONE DELLE LISTE DA PARTE DELLA PRESIDENZA DEL CONSIGLIO</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>L’ACCERTAMENTO GIUDIZIARIO, CHE SALDA LA LOGGIA ALL’ASSE CONTINENTALE. Le motivazioni della sentenza di Bologna, riprendendo le conclusioni della Commissione, parlano del suo «RUOLO INCREDIBILE NELL’AMBITO DELLE GIUNTE MILITARI CHE NEGLI ANNI SETTANTA PRENDONO IL POTERE IN ARGENTINA, URUGUAY, BRASILE, PARAGUAY», e affermano che egli «E IL PRINCIPALE RAPPRESENTANTE DI QUESTI PAESI IN ITALIA E COSTRUISCE UNA FORTUNA PERSONALE IN TALI STATI». La medesima sentenza lo qualifica come consigliere economico presso l’ambasciata che «TRAFFICA IN ARMAMENTI E INFLUENZE». E i giudici, AVENDO ACQUISITO SENTENZE SUL PIANO CONDOR, scrivono che «LA P2 E PARTE COMUNE IN QUEL PERIODO DELLA VITA POLITICA IN ARGENTINA, COSI COME IN ITALIA»</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>DUE INDIRIZZI DI RICERCA CHE NE DISCENDONO. PRIMO: la corrispondenza fra Licio Gelli e la massoneria argentina RISULTA CONSERVATA PRESSO LE BIBLIOTECHE DEL PARLAMENTO ITALIANO A ROMA, ed e consultabile. SECONDO: e stata riferita in sede processuale l’esistenza di ARCHIVI URUGUAIANI del medesimo, con l’affermazione che LA COMMISSIONE PARLAMENTARE NON FOSSE A CONOSCENZA DELL’INTERVENTO DEL SERVIZIO STATUNITENSE SU DI ESSI: circostanza DA VERIFICARE SUGLI ATTI, riferita da chi fu per anni collaboratrice della presidenza di quella Commissione</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Secondo — SPIEGA LA STRUTTURA A BLOCCHI. Le trenta affiliazioni sudamericane consecutive non sono un fenomeno massonico: SONO IL PRODOTTO DI UNA POSIZIONE DIPLOMATICA E COMMERCIALE DOCUMENTATA, esercitata con passaporto di Stato per 8 anni. E il blocco va datato entro quell’arco</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Il blocco brasiliano dell’elenco — LACUNA DICHIARATA, indirizzo archivistico, e incoerenza delle cifre pubblicate</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Per la ricerca: fondo del Servizio nazionale di informazioni brasiliano, custodito dall’Archivio nazionale e accessibile tramite il portale governativo delle memorie rivelate; il servizio fu istituito con legge del 13 GIUGNO 1964 e produceva anche relazioni esterne su paesi definiti antagonisti e amici</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>LO STATO DELLA QUESTIONE, DICHIARATO COME LACUNA. Le 18 affiliazioni brasiliane, disposte in due blocchi consecutivi fra i fascicoli 597 e 616, NON HANNO A TUTT’OGGI UNA SPIEGAZIONE DOCUMENTATA nella letteratura consultata. E il piu numeroso fra i gruppi esteri dell’elenco ed e il meno studiato: la ricerca si e concentrata sull’Argentina, dove il capo della loggia aveva posizione diplomatica, e ha lasciato il Brasile sullo sfondo. QUESTA E UNA LACUNA DELLA RICERCA, NON UNA LACUNA DELLE FONTI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>LA TRACCIA DA VERIFICARE, DI LIVELLO C: fonte secondaria riferisce che ANALISTI DELL’INTELLIGENCE BRASILIANA avrebbero scritto che, «con l’ambiente sfavorevole in Uruguay e il suo indebolimento in Argentina, IL SISTEMA P2 E I SUOI SOTTOSISTEMI STAREBBERO CONSOLIDANDO LE PROPRIE ATTIVITA NEL NOSTRO PAESE». La citazione, se autentica, spiegherebbe lo spostamento del baricentro ma non l’epoca delle affiliazioni, che precede il periodo indicato. VA CERCATO IL DOCUMENTO ORIGINALE NEL FONDO SOPRA INDICATO. E riferito parimenti che l’Uruguay era «divenuto un vero e proprio centro per gli affari della loggia, grazie alla copertura del regime militare», e che un mutamento alla presidenza porto un titolare ostile</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>LA SCOPERTA COLLATERALE, CHE RIGUARDA OGNI CITAZIONE FUTURA: LE CIFRE RIASSUNTIVE IN CIRCOLAZIONE NON CONCORDANO FRA LORO. Una fonte indica 208 militari, 8 ammiragli, 11 questori, 5 prefetti, 44 parlamentari e due ministri; un’altra 119 alti ufficiali, 22 dirigenti di polizia, 509 PARLAMENTARI, 8 direttori di giornali, 22 giornalisti e 4 editori; una terza 4 MINISTRI O EX MINISTRI. Una fonte indica inoltre 992 nominativi anziche 962. Il computo diretto condotto su questo repertorio da 205 TITOLI MILITARI E 41 PARLAMENTARI</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>REGOLA CHE NE DISCENDE: NESSUNA CIFRA RIASSUNTIVA VA CITATA DA FONTE SECONDARIA. Chi voglia usare un numero deve contarlo sull’elenco e dichiarare il criterio di conteggio, perche i titoli sono ambigui — un medesimo nominativo puo recare piu qualifiche — e le fonti coeve adottano criteri diversi senza dichiararli. VA INOLTRE REGISTRATA, COME IPOTESI NON VERIFICATA, l’esistenza riferita di un archivio esteso di circa 2.400 NOMI, mai rinvenuto e attestato dalle sole testimonianze</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Secondo — 3 COMPITI. Interrogare il fondo del servizio brasiliano per il documento sul consolidamento; interrogare la corrispondenza massonica argentina conservata presso le biblioteche parlamentari italiane; e ricontare l’elenco dichiarando il criterio, poiche nessuna delle cifre pubblicate e riproducibile</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n"/>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Conteggio riproducibile dell’elenco del 1981 — CRITERIO DICHIARATO E CIFRA CONFERMATA</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Elaborazione sui 960 record del file tabellare di progetto. CRITERIO DICHIARATO, senza il quale nessuna cifra e verificabile: si cerca il titolo come parola isolata, ignorando punteggiatura e maiuscole, NELLA SOLA PORZIONE INIZIALE DEL CAMPO NOME — i primi quaranta caratteri — per evitare falsi positivi su cognomi. Il conteggio e NON ESCLUSIVO: un medesimo record puo ricadere in piu categorie</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>IL RISULTATO PRINCIPALE, CHE CONFERMA LA CIFRA COEVA PER VIA INDIPENDENTE: 208 RECORD RECANO ALMENO UN GRADO MILITARE, pari al 21 E 7 DECIMI PER CENTO DELL’UNIVERSO. E esattamente la cifra riportata dalle fonti del tempo, qui riottenuta da un conteggio diretto e ripetibile. Nel dettaglio: 82 COLONNELLI, 49 GENERALI, 48 CAPITANI, 44 fra brigadieri, sottotenenti, tenenti, sergenti e marescialli, 37 TENENTI COLONNELLI, 16 MAGGIORI, 9 AMMIRAGLI</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>LE QUALIFICHE CIVILI: 475 dottori, 50due professori, 44 avvocati, 41 PARLAMENTARI, 22 ragionieri, venti ingegneri, 12 geometri, 6 commendatori. E 85 RECORD, PARI ALL’8 E 9 DECIMI PER CENTO, SONO PRIVI DI QUALSIASI TITOLO RICONOSCIUTO</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>LA DIMOSTRAZIONE DEL PERCHE LE CIFRE PUBBLICATE DIVERGONO, E NON E UN SOSPETTO MA UN CALCOLO: 50 RECORD RECANO DUE O PIU QUALIFICHE RICONOSCIUTE. Ne segue che chi conta per qualifica ottiene una somma superiore all’universo, mentre chi assegna una sola categoria per record ottiene numeri inferiori — E NESSUNA DELLE FONTI COEVE DICHIARA QUALE DEI DUE CRITERI ABBIA ADOTTATO. Le divergenze fra le cifre in circolazione NON SONO ERRORI: SONO CRITERI DIVERSI NON DICHIARATI</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SCARTI RESIDUI DA RISOLVERE SULL’ATTO: le fonti coeve indicano 43 generali distinti per forza armata contro i 49 qui contati, 8 ammiragli contro 9, 44 parlamentari contro 41. Gli scarti sono compatibili con criteri di inclusione diversi — per esempio il computo dei soli generali di 4 forze specificate — MA VANNO VERIFICATI SULLA RELAZIONE ORIGINALE. Va inoltre ricordato che l’estrazione poggia su 960 RECORD SU 962 DICHIARATI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Cerniera e Metodologia — CHIUDE IL COMPITO ENUNCIATO NELLA VOCE PRECEDENTE. L’opera puo ora citare una cifra propria, ottenuta con criterio esplicito e ripetibile da chiunque disponga del medesimo file. E LA REGOLA GENERALE: OGNI NUMERO PUBBLICATO IN QUEST’OPERA DEVE PORTARE CON SE IL CRITERIO CHE LO HA PRODOTTO, altrimenti condivide la sorte delle cifre coeve, che divergono fra loro senza che nessuno sappia perche</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="n"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="n"/>
+      <c r="L27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Il capitolo su mafia e massoneria deviata — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 292-311, GIA NEL CORPUS E MAI APERTO</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Relazione della Commissione stragi, XIII legislatura, DATATA 22 GIUGNO 2000, firmata da 4 senatori e 5 deputati; blocco conclusivo della trascrizione presente nei file di progetto, pagine duecento26-245 su 245</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>LA DEFINIZIONE DELLA STRAGE, TESTUALE, CHE COINCIDE CON IL PRIMO ASSE DELLA TASSONOMIA: «Uccidere persone a caso, vecchi e bambini, clienti di una banca o passeggeri di un treno, in una parola la strage, E STATO UN ATTO POLITICO: un modo violento, barbaro, inaudito, per incidere sugli equilibri del paese e sulle sue istituzioni nell’ambito di strategie TALVOLTA PRECISE — OSTACOLARE L’ALTERNANZA DELLE FORZE AL GOVERNO — e in altri casi piu confuse, indebolire lo Stato e ridurne la capacita di contrasto nella lotta alla criminalita organizzata». LA COMMISSIONE NOMINA COME FINE PRECISO DELLE STRAGI ESATTAMENTE CIO CHE LA PROVA DELL’ALTERNANZA INDIVIDUA COME CRITERIO DELL’ECCEZIONALISMO</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>LA STRUTTURA DEL FENOMENO, E LA CAUTELA CHE VA CONSERVATA: «La cosiddetta strategia della tensione e stata la PARTE ARMATA DI UN PROGETTO POLITICO, O DI PIU PROGETTI POLITICI, messi in atto da soggetti diversi via via spinti a collaborare e ad integrarsi tra loro per colpire lo Stato democratico. Cosi l’eversione di destra si e saldata con parti importanti della mafia, di Cosa Nostra e della Ndrangheta, SPESSO ATTRAVERSO LA MEDIAZIONE ATTIVA DI LOGGE MASSONICHE DEVIATE DIVENUTE IL PUNTO DI INCONTRO DI CAPI DELL’EVERSIONE E DI BOSS MAFIOSI». L’inciso «o di piu progetti politici» E DELLA COMMISSIONE, e sostiene la lettura per progetti rivali anziche per disegno unico. E la loggia vi figura COME PUNTO DI INCONTRO, non come mandante: e ruolo di intermediazione, cioe di betweenness</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>LA FONTE PRINCIPALE E LA SUA GRADUAZIONE: nell’audizione alla Commissione antimafia della XI legislatura del 16 NOVEMBRE 1992, Tommaso Buscetta dichiaro che NEL 1970 3 CAPI MAFIOSI ERANO INTERESSATI A CREARE IN SICILIA UN «CLIMA DI TENSIONE» CHE AVREBBE DOVUTO FAVORIRE UN COLPO DI STATO, e che il contatto fra uomini d’onore e il promotore del tentativo sarebbe avvenuto ATTRAVERSO ESPONENTI DI ALCUNE LOGGE MASSONICHE. La Commissione grada le proprie fonti: i due dichiaranti erano «PUR MOTIVATI DA INTENTI DIVERSI, l’uno dall’intento di collaborare con la giustizia, l’altro FORSE PER LANCIARE OSCURI MESSAGGI». E conclude con formula misurata: «e oggi possibile affermare che la mafia e la cosiddetta massoneria deviata SONO STATE COINVOLTE A VARIO TITOLO nella stagione eversiva 1969-1974»</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>DUE ELEMENTI ULTERIORI DEL MEDESIMO CAPITOLO. PRIMO: vi si trattano LOGGE RISERVATE AI MILITARI DELL’ALLEANZA ATLANTICA SFUGGITE AL CONTROLLO MASSONICO ITALIANO, e logge costituite ad hoc per militari, con la segnalazione della peculiarita di logge legate ad ambienti massonici e politici internazionali. SECONDO, ED E UN SECONDO MANDATO SCRITTO PER QUEST’OPERA: la Commissione enuncia L’ESIGENZA DI APPROFONDIRE IL RUOLO DELLA MASSONERIA NELLA STRATEGIA DELLA TENSIONE, definendolo UN PROBLEMA «DIMENTICATO» DALLA COMMISSIONE P2 IN POI, e osserva che le informazioni disponibili si sono moltiplicate negli ultimi anni. Il paragrafo che precede tratta inoltre DEI FINANZIAMENTI STATUNITENSI AI DIRIGENTI DEL PARTITO DELLA DESTRA PARLAMENTARE</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 1 × 4 × 7 — COLMA LA PRINCIPALE LACUNA DICHIARATA NELL’AUDIT. Era il blocco conclusivo del fondo, trascritto dall’autore nell’aprile 2026 e mai aperto; contiene la definizione politica della strage, la struttura a piu progetti, il ruolo di intermediazione della loggia e un invito espresso all’approfondimento</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="n"/>
+      <c r="J28" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>LA CHIUSA DELLA RELAZIONE — pagina 311, le ultime parole del documento, e la domanda che vi resta</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Commissione stragi, XIII legislatura, Doc. XXIII n. 64, Vol. I, Tomo II, PAGINA 311, ultima del documento; trascrizione integrale gia presente nei file di progetto</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>LE LOGGE PER I MILITARI DELL’ALLEANZA, TESTUALE: e anomala «l’esistenza nel passato, nel nostro paese, DI STRUTTURE MASSONICHE TRASVERSALI COSTITUITE AD HOC PER POTER RISERVATAMENTE ACCOGLIERE ALCUNE TIPOLOGIE DI FRATELLI, I MILITARI AD ESEMPIO», e cosi «l’esistenza di LOGGE RISERVATE AI MILITARI DELLA NATO, LOGGE CHE PER STESSA AMMISSIONE DEI RESPONSABILI MASSONICI ITALIANI SONO SFUGGITE A QUALSIASI FORMA DI CONTROLLO DELL’ATTIVITA SVOLTA». Sono i vertici dell’obbedienza ad ammettere di non avere controllato</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>GLI ALTRI ELEMENTI ELENCATI NELLA MEDESIMA FRASE: la peculiarita di alcune logge «LEGATE A BEN PRECISI AMBIENTI MASSONICI E POLITICI INTERNAZIONALI»; il configurarsi di alcune di esse come «VERE E PROPRIE ASSOCIAZIONI SEGRETE»; i «COMPROVATI FINANZIAMENTI» di Licio Gelli a un militante dell’eversione di destra; e la «COMPROVATA APPARTENENZA A LOGGE DEVIATE DI PROTAGONISTI DI VICENDE EVERSIVE E DI MILITANTI DI ORGANIZZAZIONI DELLA DESTRA EVERSIVA». La Commissione qualifica due di questi elementi come COMPROVATI e gli altri come motivi che avvalorano l’esigenza di approfondimento: LA GRADUAZIONE E SUA</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>LA FRASE CHE CHIUDE IL DOCUMENTO, E CHE DOVREBBE CHIUDERE UN CAPITOLO DI QUEST’OPERA: «IL PROBLEMA RESTA QUELLO DI COMPRENDERE SE TUTTO CIO SIA STATO O MENO CASUALE». E la domanda popperiana posta dallo Stato su se stesso, alla fine di 245 pagine: non una conclusione, MA LA DICHIARAZIONE CHE LA CONCLUSIONE NON C’E</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>LA CAUTELA CHE LA COMMISSIONE STESSA APPLICA, E CHE VA ADOTTATA NEL DOMINIO QUARTO: essa distingue espressamente «la stessa massoneria italiana, QUELLA DEL TUTTO ESTRANEA A QUESTE VICENDE E CHE PERCIO HA IL DIRITTO DI NON VEDERSI CONFUSA CON L’ATTIVITA DELLE LOGGE ATIPICHE». E il terzo mandato scritto: «DAI TEMPI DELLA COMMISSIONE SULLA LOGGIA P2, SE SI ECCETTUA IL LAVORO DELLA COMMISSIONE ANTIMAFIA DELLA XI LEGISLATURA, NON SI E PIU CERCATO DI APPROFONDIRE QUESTO PROBLEMA», e le informazioni disponibili, MOLTIPLICATESI NEGLI ULTIMI ANNI, consentirebbero di esaminare «con serieta e rigore un aspetto della strategia della tensione PER TROPPO TEMPO DIMENTICATO»</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 e Metodologia — CHIUDE IL FONDO E CHIUDE L’AUDIT SU QUESTA LACUNA. Il documento non termina con una tesi ma con una domanda, e distingue i propri gradi: due elementi comprovati, gli altri motivi di approfondimento, e una questione dichiarata aperta. UN’OPERA CHE SI CHIUDESSE CON PIU CERTEZZA DI QUANTA NE ABBIA LA FONTE SU CUI POGGIA SAREBBE, IN QUEL PUNTO, MENO RIGOROSA DELLO STATO</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="n"/>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="n"/>
+      <c r="L29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>«Non la restaurazione di un regime fascista, bensi una democrazia autoritaria» — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 267-268</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AVVERTENZA PRELIMINARE CHE NE DETERMINA L’USO: il documento reca nel titolo i nomi di 5 deputati e 4 senatori ed e una PROPOSTA DI RELAZIONE DI UN GRUPPO DI COMMISSARI, non la conclusione unanime della Commissione. VA CITATO COME TESI DI QUEI COMMISSARI, non come accertamento dell’organo. Datato 22 giugno 2000; trascrizione integrale gia nei file di progetto</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMULA CENTRALE, TESTUALE: «Non si puo scrivere la storia, anche sul piano giudiziario, della strategia della tensione se non si accetta la realta che vuole la destra neofascista italiana TATTICAMENTE DIVISA E STRATEGICAMENTE UNITA, in una SUDDIVISIONE STRUMENTALE DI RUOLI E DI COMPITI che doveva permettere L’UTILIZZO INCONSAPEVOLE DI CENTINAIA DI MIGLIAIA DI PERSONE allo scopo di portare contro la sinistra italiana quell’affondo decisivo che avrebbe consentito LA TRASFORMAZIONE DEL REGIME DA DEMOCRAZIA PARLAMENTARE A REPUBBLICA PRESIDENZIALE. NON LA RESTAURAZIONE DI UN REGIME FASCISTA, BENSI L’INSTAURAZIONE DI UNA DEMOCRAZIA AUTORITARIA NELLA QUALE I COMUNISTI NON AVESSERO SPAZIO E CITTADINANZA LEGALE»</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE E LA DEFINIZIONE ESATTA DELL’ECCEZIONALISMO: non rivoluzione e non restaurazione, ma UNA DEMOCRAZIA CON UN’ESCLUSIONE PERMANENTE. Un esito e precluso in anticipo alla competizione, e una categoria di cittadini e privata di «spazio e cittadinanza legale». E la PROVA DELLA RISERVA nella sua forma piu pura, e non e formulata da questo repertorio ma da 9 parlamentari nel duemila</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA FORMULA, CHE ROVESCIA IL NOME STESSO DEL FENOMENO: «NON C’E STATA UNA STRATEGIA STRAGISTA, c’e stata una strategia che aveva preventivato gli attentati, gli agguati, i disordini, i feriti e i morti, che li ha cercati e li ha provocati, COSI DA MANTENERE IL PAESE IN UN EQUILIBRIO TANTO PRECARIO CHE IN OGNI MOMENTO, NEL CORSO DEGLI ANNI FRA IL 1965-66 E IL 1981-82, UN INTERVENTO AUTORITARIO COMPIUTO DA FORZE POLITICHE DI GOVERNO SOSTENUTE DALLE FORZE ARMATE E DAI CORPI DI POLIZIA SAREBBE STATO ACCOLTO COME UNA LIBERAZIONE dalla popolazione stanca, nauseata, impaurita da anni e anni di violenza estremistica di segno ora fascista, ora comunista». LE STRAGI NON SONO IL FINE MA IL MEZZO PER PRODURRE UNA DOMANDA D’ORDINE, e la finestra dichiarata e 1965-1982</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>SULLA STRUTTURA, CON LE CAUTELE DEL TESTO: le scissioni fra le organizzazioni della destra radicale sarebbero state «PIU CHE ALTRO STRUMENTALI» e avrebbero garantito il controllo dell’estremismo «DA PARTE DI POCHI UOMINI CHE A LIVELLO DI VERTICE SONO SEMPRE STATI IN CONTATTO FRA LORO, PEGGIO ANCORA IN ACCORDO FRA LORO, ALMENO FINO ALLA META DEGLI ANNI SETTANTA». Del partito parlamentare si afferma che della violenza estremistica «NON FU SOLO IL BENEFICIARIO IN TERMINI POLITICI, MA ANCHE IL PROMOTORE E IL COORDINATORE». E del suo segretario che faceva da mediatore fra le istanze nazional-rivoluzionarie e quelle moderate, presentandosi come uomo capace di conciliare la lotta senza compromessi con «LA MIMETIZZAZIONE NECESSARIA PER NON FARSI PORRE FUORI LEGGE». TUTTE AFFERMAZIONI DI PARTE, DA CITARE COME TALI</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Primo e Apparato — 3 CONSEGUENZE. LA TESI DELL’OPERA HA UNA FORMULAZIONE PARLAMENTARE MIGLIORE DI QUALSIASI RIFORMULAZIONE D’AUTORE, e va citata. LA DATAZIONE 1965-1982 va confrontata con la finestra del test di densita, che copriva 1969-1985: IL TEST ANDREBBE RIESEGUITO SULLA FINESTRA DICHIARATA DALLA FONTE. E LA QUALIFICA DI PROPOSTA DI GRUPPO VA RIPETUTA A OGNI CITAZIONE, perche e cio che distingue l’uso corretto dall’abuso</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Verifica di robustezza del test di densita — RIESECUZIONE SULLA FINESTRA DICHIARATA DALLA FONTE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Rielaborazione del test pre-registrato, con la sola modifica della finestra di osservazione: dal periodo scelto dal ricercatore (1969-1985) a QUELLO DICHIARATO DAI COMMISSARI NELLA PROPOSTA DI RELAZIONE DEL 2000, cioe 1965-1982. 100.000 estrazioni per ciascun raggio</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>LA MODIFICA E LE SUE CONSEGUENZE MECCANICHE: la finestra passa a SEIMILACINQUECENTOSETTANTATRE GIORNI; le tappe dell’integrazione comprese diventano 15, includendo il compromesso di Lussemburgo del 1966, il secondo veto del 1967 e il completamento dell’unione doganale del 1968; E UNO DEGLI EVENTI ESCE DALL’INSIEME, poiche la strage del 1984 cade fuori dalla finestra dichiarata. Gli eventi testati sono dunque 8</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>L’ESITO E IDENTICO. Al raggio primario di novanta giorni: 3 EVENTI PROSSIMI SU 8, contro DUE E OTTANTASETTE CENTESIMI attesi per puro caso, con probabilita pari a ZERO VIRGOLA 509. Nessun raggio raggiunge la significativita: a trenta giorni uno osservato contro uno virgola zerocinque atteso; a sessanta due contro uno virgola novantanove; a centottanta 6 contro 5 virgola zerodue; a trecentosessantacinque 8 SU 8 contro 7 virgola trentuno attesi</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>LA RIGA CHE VALE LA VERIFICA: al raggio di un anno TUTTI E 8 GLI EVENTI RISULTANO PROSSIMI A UNA TAPPA, MA LA COPERTURA DELLA LINEA TEMPORALE E DEL NOVANTUNO E 4 DECIMI PER CENTO. In quella condizione «tutto e vicino a qualcosa» NON E UN RISULTATO MA UNA TAUTOLOGIA, e la probabilita che il caso produca lo stesso esito e quasi una su due</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>LA CONCLUSIONE METODOLOGICA, CHE E LA PIU IMPORTANTE. L’esito nullo NON E UN ARTEFATTO DELLA FINESTRA SCELTA: sopravvive alla sostituzione della finestra con quella dichiarata dalla fonte. MA VA LETTO CON PRECISIONE: la tesi dei commissari NON RICHIEDE ADDENSAMENTO ATTORNO A DATE EUROPEE, poiche descrive una strategia CONTINUA di mantenimento di un equilibrio precario. IL RISULTATO NULLO DUNQUE NON CONFUTA LA LORO TESI: CONFUTA QUELLA DA CUI L’OPERA ERA PARTITA, cioe la convergenza bipolare orientata contro le tappe dell’unificazione</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — LA VERIFICA CHIUDE IL PRIMO CAPITOLO METODOLOGICO. L’argomento della coincidenza temporale con il calendario europeo VA ABBANDONATO; l’opera deve reggersi sui legami documentali, che il repertorio sostiene, e sulla strategia continua descritta dalla fonte, che non e misurabile con questo strumento</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="n"/>
+      <c r="L31" s="8" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Il riconoscimento inglese delle obbedienze italiane — 1972, 1993, 2023 — LACUNA COLMATA</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Fonti: comunicazioni trimestrali della Gran Loggia Unita d’Inghilterra; comunicato ufficiale del Grande Oriente d’Italia del 2023; ricostruzioni giornalistiche coeve. LA VOCE COLMA LA PRIMA LACUNA DICHIARATA NELL’AUDIT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>LA PRIMA DATA, CHE E QUELLA CHE RIGUARDA IL TOMO PRIMO. IL 13 SETTEMBRE 1972 la Gran Loggia Unita d’Inghilterra riconosce la regolarita del Grande Oriente d’Italia. Il riconoscimento e attribuito all’opera dei gran maestri Giordano Gamberini e poi LINO SALVINI, «con l’opera sotto traccia» di un alto funzionario della Ragioneria generale dello Stato. VA LETTA ACCANTO A UNA VOCE GIA REGISTRATA: e lo stesso gran maestro che, NEL FEBBRAIO 1973, accolse la richiesta di Licio Gelli coperta di essere nominato rappresentante massonico argentino presso l’obbedienza italiana. IL RICONOSCIMENTO INGLESE PRECEDE QUELLA NOMINA DI 5 MESI</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA DATA. L’8 DICEMBRE 1993, nella comunicazione trimestrale, la Gran Loggia Unita d’Inghilterra CONFERISCE IL RICONOSCIMENTO ALLA GRAN LOGGIA REGOLARE D’ITALIA SOTTRAENDOLO AL GRANDE ORIENTE. Seguono a breve la Gran Loggia Nazionale Francese, quella d’Irlanda e quella di Scozia, poi Israele, Turchia, Brasile e diverse obbedienze africane. La nuova obbedienza era stata fondata da chi aveva lasciato la guida del Grande Oriente NELLO STESSO 1993, secondo la ricostruzione giornalistica «SULL’ONDA DELLE DENUNCE DELLE INFILTRAZIONI MAFIOSE». IL RITIRO DEL RICONOSCIMENTO E DUNQUE COLLEGATO, DALLE FONTI, ALLA QUESTIONE DELLE INFILTRAZIONI</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>LA TERZA DATA E LA CONDIZIONE POSTA. L’8 MARZO 2023, dopo trent’anni esatti, il riconoscimento e ripristinato al Grande Oriente, che lo commenta definendo quello del 1993 «UN INGIUSTO PROVVEDIMENTO». Ma le costituzioni inglesi PREVEDONO CHE DUE OBBEDIENZE DEL MEDESIMO PAESE POSSANO ESSERE RICONOSCIUTE SOLTANTO SE SI RICONOSCONO FRA LORO, e la pregiudiziale posta e che le due convivano fraternamente: CONDIZIONE CHE AL MOMENTO DELLE FONTI NON RISULTAVA SODDISFATTA</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>E LA RISPOSTA A UNA DOMANDA RIMASTA APERTA IN QUESTO LAVORO: NON ESISTE ALCUN «RITO DI KENT». ESISTE UN GRAN MAESTRO DI KENT — il duca di Kent, gran maestro della Gran Loggia Unita d’Inghilterra dal 1967 — ed e in quella veste che il nome ricorre nelle cronache del riconoscimento italiano. UNA FONTE PARLA DI «MICHELE DI KENT»: la denominazione va verificata, poiche esistono due membri di quella casa con ruoli massonici distinti. IL NOME DESIGNA UNA PERSONA E UNA CARICA, NON UN RITO</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 e Tomo I — 3 ACQUISIZIONI. La regolarita internazionale del Grande Oriente COPRE ESATTAMENTE IL PERIODO 1972-1993, cioe l’arco in cui si colloca la vicenda della loggia coperta e il suo scioglimento per legge. IL RITIRO NON AVVIENE NEL 1981 CON LA SCOPERTA DELLE LISTE, NE NEL 1982 CON LA LEGGE, MA NEL 1993 — dato che va spiegato e non presunto. E il riconoscimento inglese si conferma, come gia registrato, IL VERO ASSE DELLA GEOGRAFIA MASSONICA: non il rito praticato, ma chi riconosce chi</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="n"/>
+      <c r="J32" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="n"/>
+      <c r="L32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Perche il ritiro del riconoscimento avviene nel 1993 — e il filone che ne discende fino al 2024</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Fonti: audizione dell’ex gran maestro dinanzi alla Commissione antimafia (2017); relazione della Commissione antimafia del 21 DICEMBRE 2017, Doc. XXIII n. 33; sezione ventesima della relazione della legislatura successiva; sentenza della Corte europea dei diritti dell’uomo DEPOSITATA IL 19 DICEMBRE 2024</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>LA SPIEGAZIONE, E NON RIGUARDA IL 1981. L’ex gran maestro si dimise dal Grande Oriente NELL’APRILE 1993, a 3 anni dall’insediamento, e ha poi riferito in sede parlamentare due ordini di fatti. PRIMO: che VERSO LA FINE DEL 1991 E NELLA PRIMAVERA SUCCESSIVA il capo della loggia coperta approfitto della sua elezione PER CHIEDERGLI DI RIENTRARE FORMALMENTE NELL’OBBEDIENZA, prospettandogli tramite un emissario LA POSSIBILITA DI OTTENERE IN CAMBIO DEL DENARO; le profferte furono respinte. SECONDO: rapporti con le organizzazioni criminali siciliana e calabrese, fra cui una riunione a Palermo in cui IL VERTICE DELLA MASSONERIA SICILIANA GLI DISSE DI NON ACCETTARE L’INVITO DEL PRESIDENTE DEL COLLEGIO REGIONALE «PERCHE AVEVA A CHE FARE CON LA MAFIA»</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>NE SEGUE CHE IL RITIRO DEL RICONOSCIMENTO DEL DICEMBRE 1993 NON E LA CONSEGUENZA TARDIVA DELLE LISTE DEL 1981, ma di due fatti del 1991-1993: un tentativo di rientro di Licio Gelli disciolta, e l’emersione delle infiltrazioni mafiose. E si colloca nel medesimo periodo dei lavori della Commissione antimafia della legislatura undicesima sui rapporti fra organizzazioni mafiose e massoneria — la sola indagine che, secondo la relazione sulle stragi del 2000, avesse ripreso il problema dopo la Commissione sulla loggia coperta</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>IL FILONE PROSEGUE E SI INASPRISCE. Nell’APRILE 2017 la Commissione antimafia invito la Guardia di finanza a SEQUESTRARE GLI ELENCHI DI TRENTACINQUEMILA ISCRITTI delle 4 principali obbedienze italiane; furono sequestrati TRENTANOVE FALDONI relativi a SEIMILA ISCRITTI delle logge di Sicilia e Calabria. Il 21 DICEMBRE 2017 la Commissione approvo una relazione sulle infiltrazioni delle due organizzazioni nella massoneria delle due regioni, CHE FU OGGETTO DI DENUNCIA PENALE DA PARTE DELL’OBBEDIENZA MAGGIORE. Vi si legge che il progetto dei massimi esponenti della organizzazione calabrese, GIA PRESENTI IN LOGGE MASSONICHE, di conquistare posizioni di potere pubblico nella Regione, e stato definito dall’indagine «UN VERO CAPOLAVORO»</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>E IL FATTO CHE CHIUDE IL CICLO: CON SENTENZA DEPOSITATA IL 19 DICEMBRE 2024 LA CORTE EUROPEA DEI DIRITTI DELL’UOMO HA CONDANNATO L’ITALIA per quella perquisizione e per quel sequestro. La relazione del 2017 aveva inoltre dichiarato LA LACUNOSITA DELLA NORMATIVA VIGENTE, con riferimento «sia alle disposizioni della legge del 1982, CHE PREVEDE UNA FATTISPECIE MOLTO RESTRITTIVA DI ASSOCIAZIONE SEGRETA, sia alle norme che dovrebbero impedire a magistrati, pubblici dipendenti, militari e forze dell’ordine di aderire ad associazioni massoniche», ritenendo essenziale un adeguamento</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 1 × 4 e Tomo III — 3 ACQUISIZIONI. La restrizione della fattispecie introdotta nel 1982, gia registrata in questo repertorio, E DENUNCIATA DALLA COMMISSIONE ANTIMAFIA TRENTACINQUE ANNI DOPO COME LACUNA ANCORA APERTA. Il ciclo si chiude con UNA CONDANNA SOVRANAZIONALE ALLO STATO CHE INDAGAVA: e la forma inversa di quella registrata altrove, e va scritta come tale. E il tentativo di rientro del 1991-1992, se riscontrato sugli atti dell’audizione, COLLEGA LA VICENDA DELLA LOGGIA DISCIOLTA AL RITIRO DEL RICONOSCIMENTO DI UN DECENNIO DOPO</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="n"/>
+      <c r="L33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>La circolazione degli elenchi nominativi massonici italiani, 2010-2022 — OGGETTO DOCUMENTABILE, NON FONTE UTILIZZABILE</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Accertamento condotto sui due file esaminati e su fonti pubbliche. Il documento del 2010 risulta accessibile in rete presso il sito di un centro studi, in cartella datata marzo 2010, coerente con la data di creazione del file (1° aprile 2010); il documento del 2022 ne e la versione ampliata</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>LA CATENA DI CIRCOLAZIONE, ACCERTATA. Una redazione dichiarata in 26MILAQUATTROCENTO10 nominativi circola su piattaforme di condivisione ed e stata rivendicata da un organo di stampa; il file del 2010 e in rete da 15 ANNI; quello del 2022 conta circa TRENTADUEMILATRECENTO coppie distinte e ne contiene il NOVANTASEI VIRGOLA 3 PER CENTO. Termine di confronto dichiarato all’epoca dal gran maestro dell’obbedienza maggiore: 18MILACINQUECENTO iscritti — l’elenco copre dunque piu obbedienze</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE NE DETERMINA L’INUTILIZZABILITA PER QUEST’OPERA, E LO DICHIARA LA FONTE STESSA CHE LI DIFFUSE: gli elenchi «NON COMPRENDONO LOGGE OCCULTE NE LE LISTE DEGLI AFFILIATI ALL’ESTERO». Per costruzione, dunque, NON CONTENGONO CIO CHE QUESTA RICERCA CERCA. La medesima fonte formula inoltre l’ipotesi che chi assurge a cariche pubbliche elevate sposti il proprio nome «in elenchi maggiormente riservati, spesso di logge estere»: E CONGETTURA NON PROVATA e va marcata come tale</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>IL QUADRO GIURIDICO, DUE AUTORITA A 3 ANNI DI DISTANZA. Il Garante per la protezione dei dati personali, nel parere del 14 GENNAIO 2021, ha stabilito che i dati riferiti all’appartenenza ad associazioni private RIENTRANO FRA LE CATEGORIE PARTICOLARI cui il Regolamento riserva le piu elevate garanzie quando idonei a rivelare opinioni politiche o convinzioni religiose e filosofiche, richiamando i principi di LIMITAZIONE DELLA FINALITA e MINIMIZZAZIONE DEI DATI oltre alla liberta di associazione costituzionalmente riconosciuta. E la Corte europea, nel DICEMBRE 2024, ha condannato lo Stato per il sequestro di elenchi analoghi</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>LA PRASSI GIORNALISTICA DOCUMENTATA, CHE COINCIDE CON IL CRITERIO ADOTTATO IN QUESTO REPERTORIO: nel caso siciliano del 2022, pubblicati elenchi comprendenti logge di piu obbedienze — fra cui una di Castelvetrano aderente all’obbedienza francese — il cronista, PUR APPLICANDO OMISSIS, riporto per esteso i soli nominativi «dei piu importanti, o comunque di coloro che ricoprono o hanno ricoperto un ruolo politico». OMISSIS PER I PRIVATI, NOME PER CHI ESERCITA FUNZIONI PUBBLICHE</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 e Metodologia — L’ESISTENZA E LA CIRCOLAZIONE DI QUESTI ELENCHI SONO UN FATTO REGISTRABILE; il loro contenuto non e una fonte utilizzabile, sia perche la catena documentale manca dell’anello iniziale, sia perche PER AMMISSIONE DI CHI LI DIFFUSE ESSI ESCLUDONO LE STRUTTURE COPERTE. Un elenco che dichiara di non contenere le logge occulte non puo provare nulla su di esse</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Censimento delle condanne definitive di parlamentari — IMPOSTAZIONE DEL CRITERIO E FONTE ISTITUZIONALE</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Fonte normativa: decreto legislativo 31 DICEMBRE 2012 numero 235, in attuazione della delega contenuta nella legge 6 novembre 2012 numero 190. Fonte documentale: deliberazioni delle Giunte delle elezioni e delle immunita parlamentari e voti delle rispettive Assemblee, atti pubblici</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>LA CATEGORIA GIURIDICA CHE RENDE IL CENSIMENTO POSSIBILE. La norma prevede l’incandidabilita EX LEGE per 3 classi di condannati CON SENTENZA DEFINITIVA A PENE SUPERIORI A DUE ANNI: per i delitti di cui all’articolo 51 commi 3-bis e 3-quater del codice di procedura penale, cioe DI STAMPO MAFIOSO E CON FINALITA DI TERRORISMO; per i DELITTI CONTRO LA PUBBLICA AMMINISTRAZIONE; e per i delitti non colposi puniti con reclusione non inferiore nel massimo a 4 anni. MECCANISMO: se la condanna diviene definitiva durante il mandato, LA DECADENZA E DICHIARATA DALLA GIUNTA DELLE ELEZIONI E CONFERMATA DALL’AULA. Precedente documentato: Giunta del 4 OTTOBRE 2013, Assemblea del 27 NOVEMBRE 2013, con deliberazione a voto palese. LA CORTE EUROPEA HA ESCLUSO IL CARATTERE PENALE DELL’INCANDIDABILITA</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE QUESTA E LA SOLA FONTE UTILIZZABILE: la decadenza parlamentare consegue ESCLUSIVAMENTE A CONDANNA DEFINITIVA, e la deliberazione che la dichiara e un atto pubblico verbalizzato. Non richiede rassegne stampa, non contiene imputazioni, e non e selezionata per parte. E IL CORRISPETTIVO, PER LA SECONDA REPUBBLICA, DI CIO CHE LA DIRETTIVA DEL 2014 E PER LE STRAGI: UN ELENCO PRODOTTO DALLO STATO PER ALTRI FINI</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>IL DIFETTO EREDITATO, ACCERTATO. Il censimento giornalistico piu citato, pubblicato alla vigilia delle elezioni del 2022, conta 101 CANDIDATI e poi QUARANTA ELETTI, ma dichiara espressamente di comprendere «INDAGINI A CARICO, PROCESSI IN CORSO O CONDANNE PASSATE IN GIUDICATO» — CIOE FONDE LE 3 CATEGORIE ESATTAMENTE COME FA IL REGISTRO DEL CORPUS. Ne segue che l’errore di standard probatorio rilevato nel registro NON E ORIGINALE: E EREDITATO DALLA FONTE. Il medesimo articolo presenta inoltre UN’INCOERENZA INTERNA, indicando in un punto ventisette deputati e 11 senatori e in un altro 25 e 15, a fronte di un totale dichiarato di quaranta</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE VA REGISTRATO PER INTERO, PERCHE E TRASVERSALE: la ripartizione di quei quaranta e indicata in 12 per la Lega, 8 per Fratelli d’Italia, 7 per Forza Italia, 5 PER IL PARTITO DEMOCRATICO, 4 PER ITALIA VIVA, DUE PER IL MOVIMENTO 5 STELLE e due per un’altra lista — con 26 SU QUARANTA nella coalizione allora vincente. UN CENSIMENTO CHE SELEZIONASSE UNA SOLA PARTE PERDEREBBE 14 CASI SU QUARANTA E CON ESSI LA PROPRIA DIFENDIBILITA</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — IL CRITERIO DA ADOTTARE, DICHIARATO: condanne DEFINITIVE di parlamentari, TUTTE LE AREE, dal 1994, con estremi della sentenza, capo d’imputazione e data della deliberazione di decadenza dove intervenuta; categoria separata e distinta per imputazioni e procedimenti pendenti, MAI FUSA CON LA PRIMA. Se il risultato mostrasse uno squilibrio fra le aree, LO SQUILIBRIO SAREBBE IL RITROVAMENTO — e nessuno potrebbe attribuirlo alla selezione</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Atlante giudiziario della politica italiana 1994-2026 — compilazione trasversale, e LE DUE CORREZIONI CHE APPORTA AL REGISTRO DEL CORPUS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Documento di oltre 3150 schede, organizzato per operazione giudiziaria e per appartenenza politica, con indicazione di esito definitivo, patteggiamento, assoluzione o rinvio a giudizio distinti fra loro. STATUTO: E COMPILAZIONE SECONDARIA FONDATA SU FONTI GIORNALISTICHE, NON SU SENTENZE LETTE IN ORIGINALE: vale come indice verso gli atti, non come atto</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>LA PRIMA CORREZIONE, CHE RISOLVE L’ERRORE GIA RILEVATO: il documento tiene distinte la condanna definitiva di Marcello Dell’Utri a 7 ANNI e l’esito del procedimento sulla cosiddetta trattativa, nel quale «HA VISTO ASSOLTI TUTTI GLI IMPUTATI ISTITUZIONALI». Il registro del corpus li fondeva in una frase sola, attribuendo la condanna al processo sbagliato e dandola per annullata: VA RISCRITTA SU QUESTA BASE E POI VERIFICATA SULLE SENTENZE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA CORREZIONE, CHE VALE PER LA TESI GENERALE. Nel procedimento su Roma la CASSAZIONE, CON DECISIONE DEL 22 OTTOBRE 2019, HA ESCLUSO DEFINITIVAMENTE L’ASSOCIAZIONE DI STAMPO MAFIOSO, riqualificando il fatto in associazione a delinquere semplice, sul rilievo che LA CAPACITA INTIMIDATRICE APPARTENEVA AL SOLO CAPO PERSONALMENTE E NON AL GRUPPO IN MODO IMPERSONALE. Le condanne restano — 10 anni al capo, 12 anni e 10 mesi al vertice della componente economica, definitive nel settembre 2022 — MA LA QUALIFICAZIONE ASSOCIATIVA MAFIOSA E CADUTA</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE SMENTISCE OGNI CENSIMENTO DI PARTE, E VIENE DAL DOCUMENTO STESSO. Fra i politici condannati nel procedimento romano figurano 4 ESPONENTI DEL PARTITO DEMOCRATICO — con pene definitive fino a 5 anni — DUE DI AREA POPOLARE-FORZA ITALIA, UNO DI ALLEANZA NAZIONALE poi condannato in via definitiva a un anno e 10 mesi in procedimento separato, e UNO DI ALTRA LISTA. NEL PRINCIPALE PROCEDIMENTO ROMANO DEL PERIODO I CONDANNATI DI UNA PARTE SONO PIU NUMEROSI DI QUELLI DELL’ALTRA, E IN DIREZIONE OPPOSTA A QUELLA PRESUPPOSTA DALLA RICHIESTA INIZIALE</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>E IL PARALLELO CHE VA REGISTRATO. In due diversi procedimenti maggiori — quello romano e quello reggino — L’IMPIANTO ASSOCIATIVO E CADUTO: nel primo per esclusione definitiva del carattere mafioso in Cassazione nel 2019; nel secondo per azzeramento in appello delle condanne eccellenti nel maggio 2026. IN ENTRAMBI I CASI RESTANO CONDANNE INDIVIDUALI E CADE LA STRUTTURA. E il dato piu importante che questo repertorio abbia sulla tesi del sistema associativo occulto</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — IL DOCUMENTO E UTILIZZABILE COME INDICE, MAI COME PROVA: ogni scheda va risolta sulla sentenza citata. Ma il suo impianto e corretto dove il registro del corpus non lo era, perche DISTINGUE CONDANNA DEFINITIVA, PATTEGGIAMENTO, ASSOLUZIONE E RINVIO A GIUDIZIO, e perche non seleziona per parte</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Processo Gotha — RICOSTRUZIONE CORRETTA DEI 3 TRONCONI, e rettifica a due affermazioni precedenti</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Ricostruzione condotta su fonti giornalistiche coeve e sulla voce enciclopedica; VA RISOLTA SUGLI ATTI. RETTIFICA ALLA VOCE PRECEDENTE DI QUESTO REPERTORIO, che presentava l’appello del maggio 2026 come esito unico: IL PROCEDIMENTO SI ARTICOLA IN ALMENO 3 TRONCONI CON ESITI DIVERSI E DATE DIVERSE</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>TRONCONE PRIMO, RITO ABBREVIATO. Primo grado MARZO 2018: vent’anni all’avvocato indicato come vertice delle relazioni riservate, e pene severe ad altri. Appello GENNAIO 2021: pena ridotta a 15 anni e 4 mesi. CASSAZIONE MARZO 2022: ANNULLA 10 CONDANNE — per quella principale, ANNULLAMENTO SENZA RINVIO per i fatti fino al 2005 perche gia coperti da giudicato, e ANNULLAMENTO CON RINVIO per la condotta successiva, sul rilievo che fosse «ILLOGICA» LA SOVRAPPOSIZIONE FRA RUOLO VISIBILE E RUOLO OCCULTO. Appello bis 15 NOVEMBRE 2024: 4 condanne rideterminate, 3 ASSOLUZIONI PIENE, una prescrizione; 10 ANNI all’imputato principale, qualificato come PARTECIPE E NON PROMOTORE</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>TRONCONE SECONDO, RITO ORDINARIO. Primo grado 30 LUGLIO 2021: 15 condanne e 15 assoluzioni; 25 anni all’avvocato ed ex parlamentare; motivazioni depositate circa due anni dopo. APPELLO MAGGIO 2026: assoluzioni delle posizioni maggiori</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>TRONCONE TERZO, ED E QUELLO CHE PIU INTERESSA QUEST’OPERA: uno stralcio in rito abbreviato relativo agli imputati accusati di far parte di UN’ASSOCIAZIONE SEGRETA ai sensi della legge del 1982. LA CORTE D’APPELLO NON HA RICONOSCIUTO L’ASSOCIAZIONE SEGRETA e ha assolto «PERCHE IL FATTO NON SUSSISTE» un ex consigliere di una finanziaria regionale e UN CANCELLIERE DELLA MEDESIMA CORTE D’APPELLO, in primo grado condannati a due e a 4 anni. Assolto dalla violazione della legge anche un commercialista, CHE PERO E STATO CONDANNATO A 10 ANNI E 8 MESI PER CONCORSO ESTERNO</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>LA CONFERMA DELLA REGOLA, SULLA MEDESIMA PERSONA: per lo stesso imputato LA CONDOTTA INDIVIDUALE DI CONCORSO ESTERNO HA RETTO E LA QUALIFICAZIONE DI ASSOCIAZIONE SEGRETA E CADUTA. E la dimostrazione piu netta che il repertorio possieda del fatto che la fattispecie introdotta nel 1982 — quella che richiede la prova dell’interferenza — E DI DIFFICILISSIMA APPLICAZIONE, esattamente come la Commissione antimafia denunciava nel 2017. SEGNALAZIONE SUL CORPUS: una sessione precedente di questo lavoro afferma l’esistenza di una «sentenza definitiva della Corte di cassazione del 5 settembre 2023» con 8 condanne definitive nel Gotha: TALE PRONUNCIA NON TROVA RISCONTRO nelle fonti qui verificate, che collocano l’intervento di legittimita nel MARZO 2022 con annullamento. VA VERIFICATA O CORRETTA</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 1 × 4 × 10 e Metodologia — 3 ACQUISIZIONI. Fra gli assolti figura UN CANCELLIERE DELLA CORTE D’APPELLO CHE LO GIUDICAVA, circostanza da registrare per se stessa. La valutazione di sintesi disponibile e che appello e legittimita abbiano «demolito in parte l’impianto accusatorio, decidendo per l’assoluzione di tutti i principali imputati e confermando la condanna soltanto per 4 profili minori». E NESSUNA CITAZIONE DI QUESTO PROCEDIMENTO E CORRETTA SE NON SPECIFICA IL TRONCONE E IL GRADO</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="n"/>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Capitolo primo del censimento dei politici in procedimenti penali — MISURAZIONE DELLA COMPOSIZIONE E CERTIFICAZIONE DEI LIMITI</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Documento omnicomprensivo di compilazione dell’autore, aprile 2026: millecentotrentacinque paragrafi, 10 tabelle, DUECENTOSETTANTADUE RIGHE, quasi 16mila parole. Struttura: centotrentaquattro schede sintetiche in 5 sezioni, piu centotrentacinque schede dettagliate a 7 campi nelle sezioni A-E, piu appendice sui procedimenti emiliani e calabresi</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>LA COMPOSIZIONE REALE, MISURATA SULLA COLONNA ESITO DI TUTTE LE CENTOTRENTAQUATTRO RIGHE: 33 POSIZIONI DEFINITIVE, pari al 24 E 6 DECIMI PER CENTO; 42 PENDENTI, pari al TRENTUNO E 3 DECIMI PER CENTO; 28 NON DETERMINABILI DAL CAMPO, pari al VENTI E 9 DECIMI; 12 patteggiamenti; 7 ASSOLUZIONI O PROSCIOGLIMENTI; 6 prescrizioni; 3 posizioni con esiti misti fra condanna e assoluzione su capi diversi; 3 non definitive</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>LA CERTIFICAZIONE CHE NE SEGUE, E VA APPOSTA AL DOCUMENTO: MENO DI UN QUARTO DELLE POSIZIONI CENSITE E DEFINITIVA. Quasi un terzo riguarda procedimenti pendenti, cioe persone su cui NON ESISTE ALCUN ACCERTAMENTO. E un quinto reca un campo esito da cui lo stato processuale NON E RICAVABILE</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>IL MIGLIORAMENTO ACCERTATO RISPETTO ALLA PRIMA STESURA: la versione precedente dello stesso capitolo, su 43 schede, registrava UNA SOLA ASSOLUZIONE; questa ne registra 7, piu 6 prescrizioni e 3 esiti misti. LA STRUTTURA PREVEDE DUNQUE GLI ESITI FAVOREVOLI, e li registra. Resta che il 5 e due decimi per cento di assoluzioni E QUOTA IMPLAUSIBILE rispetto alla realta giudiziaria italiana, e va verificato se dipenda dal criterio di selezione</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>LA DISTINZIONE DECISIVA PER L’USO DEL DOCUMENTO. Il titolo dichiara «politici COINVOLTI IN PROCEDIMENTI PENALI»: rispetto a quel titolo l’inclusione di pendenti, assolti e prescritti E CORRETTA E DOVUTA. IL PROBLEMA NON E L’INCLUSIONE MA L’USO: nessuna riga di questo censimento puo sostenere un’affermazione di responsabilita se non reca esito definitivo, e le 33 che lo recano vanno tenute separate dalle altre 101</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — REGOLA DI CITAZIONE: dal censimento si cita l’esito, mai la presenza. E le 3 posizioni con esiti misti su capi diversi VANNO SCOMPOSTE CAPO PER CAPO, perche una scheda che registri insieme una condanna e un’assoluzione non e citabile in nessuna delle due direzioni</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Verifica a campione delle posizioni definitive del capitolo primo — DUE RISCONTRI E UN PROBLEMA SISTEMICO</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Verifica condotta su fonti giornalistiche coeve per due delle 33 posizioni indicate come definitive nel censimento</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>PRIMA VERIFICA, CONFERMATA MA DA COMPLETARE: la condanna a 6 ANNI per concorso esterno di un ex senatore ed ex sottosegretario all’Interno E DEFINITIVA DAL 13 DICEMBRE 2022. La scheda e esatta e priva di data. MA LA STORIA PROCESSUALE VA REGISTRATA PERCHE E ISTRUTTIVA: richiesta di rinvio a giudizio nell’OTTOBRE 2011; SETTEMBRE 2013, il giudice ASSOLVE per i fatti successivi al 1994 e dichiara prescritti i precedenti; SETTEMBRE 2016, L’APPELLO CONFERMA L’ASSOLUZIONE; 22 GENNAIO 2018, LA CASSAZIONE ANNULLA L’ASSOLUZIONE CON RINVIO; 21 LUGLIO 2021, l’appello bis CONDANNA A 6 ANNI; 13 DICEMBRE 2022, ricorso rigettato. 11 ANNI, ASSOLTO IN DUE GRADI E POI CONDANNATO IN VIA DEFINITIVA</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE QUESTO CASO VA ACCOSTATO AI PRECEDENTI: e la direzione opposta a quella del procedimento romano e di quello reggino. LI la condanna precede l’assoluzione, QUI L’ASSOLUZIONE PRECEDE LA CONDANNA. NON E VERO CHE I GRADI SUPERIORI ASSOLVANO: correggono in entrambe le direzioni, e un’opera che citasse solo i ribaltamenti favorevoli commetterebbe lo stesso errore di chi cita solo le condanne</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>SECONDA VERIFICA, CHE CORREGGE LA SCHEDA. Per l’ex presidente di regione la scheda indica «falso e abuso d’ufficio» con condanna definitiva del 2018: LA CASSAZIONE DEL 4 APRILE 2018 HA DICHIARATO PRESCRITTO L’ABUSO D’UFFICIO e confermato il solo FALSO IN ATTO PUBBLICO, rideterminando la pena da 5 anni a 4 ANNI E 7 MESI. Primo grado marzo 2014: 6 anni e interdizione perpetua; appello dicembre 2016: 5 anni. LA RIDETERMINAZIONE HA FATTO VENIR MENO L’INTERDIZIONE PERPETUA, limitandola a 5 anni. Condannati in via definitiva anche 3 revisori dei conti a due anni e 4 mesi ciascuno</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>IL PROBLEMA SISTEMICO CHE NE EMERGE, E RIGUARDA PIU SCHEDE: NEL 2024 IL DELITTO DI ABUSO D’UFFICIO E STATO ABROGATO — circostanza da riscontrare sull’atto legislativo. Nell’elenco delle posizioni definitive del capitolo figurano ALMENO 3 CONDANNE PER QUEL SOLO TITOLO, rispettivamente a 8 mesi, a 6 mesi e a un anno e 6 mesi. L’ABROGAZIONE NON CANCELLA IL GIUDICATO, ma un censimento che si estenda al 2026 DEVE REGISTRARE CHE IL REATO NON ESISTE PIU, altrimenti attribuisce oggi una qualificazione che l’ordinamento non prevede</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — 3 PRESCRIZIONI OPERATIVE. Ogni scheda deve recare LA DATA E L’AUTORITA della pronuncia definitiva, assenti in 28 delle 33. Deve DISTINGUERE I CAPI CONFERMATI DA QUELLI PRESCRITTI, perche la scheda verificata li fondeva. E deve SEGNALARE I TITOLI DI REATO ABROGATI</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Terza verifica sul capitolo primo — SCHEDA CHE ATTRIBUISCE FRA I REATI DUE CAPI CON ESITO ASSOLUTORIO</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Verifica condotta su fonti giornalistiche coeve sulla posizione che il censimento indica con il totale di pena piu elevato del capitolo</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CIO CHE RISULTA CONFERMATO: la posizione reca effettivamente 3 CONDANNE DEFINITIVE PER BANCAROTTA. La prima, per il dissesto di un istituto di credito cooperativo di cui l’interessato fu presidente per circa vent’anni, e definitiva dal 3 NOVEMBRE 2020 in 6 ANNI E 6 MESI — primo grado 9 anni, ridotti in appello a 6 anni e 10 mesi e poi in legittimita per prescrizioni parziali. La seconda, per il fallimento di una societa editrice, e definitiva dal 28 NOVEMBRE 2023 in 5 ANNI E 6 MESI. La terza riguarda il fallimento di un’impresa edile</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>L’ERRORE, ED E IL PIU GRAVE FINORA RILEVATO NEL CENSIMENTO: la scheda elenca fra i reati anche «FINANZIAMENTO ILLECITO (P3)». MA LE FONTI ATTESTANO CHE L’INTERESSATO FU RICONOSCIUTO NON COLPEVOLE DELL’ACCUSA DI APPARTENERE ALLA COSIDDETTA P3, E FU ASSOLTO nell’inchiesta romana sulla compravendita di un immobile, nella quale era accusato proprio di finanziamento illecito. LA SCHEDA ATTRIBUISCE DUNQUE FRA I REATI DUE CAPI CON ESITO ASSOLUTORIO, e classifica poi l’intera riga come condanna definitiva</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMA DELL’ERRORE, CHE E STRUTTURALE E NON ISOLATA: il campo «reato o accusa» raccoglie indistintamente CAPI CON CONDANNA DEFINITIVA E CAPI CON ASSOLUZIONE, e il campo «esito» riporta soltanto i primi. CHI LEGGA LA RIGA RICAVA CHE L’INTERESSATO SIA STATO CONDANNATO ANCHE PER I FATTI DAI QUALI E STATO ASSOLTO. E il medesimo difetto gia rilevato su altra scheda, dove un capo prescritto era fuso con uno confermato</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>SECONDO RILIEVO, DI METODO: la scheda somma le 3 pene in un totale di circa 15 ANNI E 10 MESI. LA SOMMA ARITMETICA DI CONDANNE DISTINTE NON CORRISPONDE ALLA PENA DA ESPIARE, che si determina con provvedimento di cumulo secondo le regole del concorso. Un totale sommato senza provvedimento di cumulo E DATO PRIVO DI SIGNIFICATO GIURIDICO, ancorche aritmeticamente esatto</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — REGOLA CHE NE DISCENDE, E VA APPLICATA A TUTTE LE SCHEDE: OGNI CAPO D’IMPUTAZIONE DEVE PORTARE IL PROPRIO ESITO. Non si elencano i capi in un campo e gli esiti in un altro, perche l’accostamento produce attribuzioni false. E NON SI SOMMANO LE PENE senza il provvedimento che le cumula</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="n"/>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CHIUSURA DI DUE DISCREPANZE DI DATA, E IL PRINCIPIO CHE NE EMERGE</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Per la prima: articolo su rivista giuridica statunitense, National Security Archive, e voce enciclopedica divergente. Per la seconda: 7 testate e organizzazioni di parte civile che seguirono l’udienza</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>PRIMA — LA DIRETTIVA STATUNITENSE DEL 1973. Le fonti davano 7 oppure 9 maggio. LA DISCREPANZA SI RISOLVE COME DOPPIO ATTO E NON COME ERRORE: JAMES SCHLESINGER SOTTOSCRISSE la direttiva ai vertici operativi IL 7 MAGGIO, e IL 9 MAGGIO diramo il memorandum a tutto il personale dell’agenzia invitando anche gli ex dipendenti a riferire. Le fonti che indicano la prima data descrivono la firma; quelle che indicano la seconda descrivono la diramazione. ENTRAMBE VANNO CITATE, ciascuna per il proprio atto. **Livello A**</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>SECONDA — LA SENTENZA DI LEGITTIMITA SULL’ASSE CONTINENTALE. Le fonti davano 8 oppure 9 luglio duemila21. ANCHE QUI DOPPIO ATTO: l’udienza si apri ALLE ORE 10 DELL’8 LUGLIO e prosegui per due giornate; LA SENTENZA FU LETTA NEL PRIMO POMERIGGIO DEL 9 LUGLIO dalla prima sezione penale. Chi data all’8 data l’inizio dell’udienza, chi data al 9 data la pronuncia. LA DATA DELLA SENTENZA E IL 9 LUGLIO DUEMILA21</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>SI RISOLVONO CONTESTUALMENTE LE DISCREPANZE DI CIFRA DEL MEDESIMO PROCEDIMENTO. Furono emessi 146 MANDATI D’ARRESTO; soltanto 37 divennero imputati, dei quali 4 brasiliani giudicati separatamente. Primo grado, 17 GENNAIO DUEMILA17: 8 ergastoli e 19 assoluzioni. Appello duemila19: 24 ERGASTOLI SU 25. Legittimita: 14 ERGASTOLI DEFINITIVI, essendo 7 imputati deceduti nel frattempo, PIU 3 gia irrevocabili per mancata impugnazione — 17 IN TOTALE</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>E SI RISOLVE LA DISCREPANZA SULLE VITTIME: le 43 sono le vittime di origine italiana comprese nel processo come aperto — 6 italo-argentini, 4 italo-cileni, 13 italo-uruguaiani e venti uruguaiani; le 23 sono quelle contemplate nei capi portati al giudicato definitivo. NON SONO CIFRE ALTERNATIVE MA CIFRE DI FASI DIVERSE. LA DISCREPANZA SULLA SENTENZA D’APPELLO E STATA CHIUSA NELLA MEDESIMA GIORNATA: LA DATA E L’8 LUGLIO 2019, un lunedi, attestata da 5 testate che riferirono quel giorno; il 10 luglio compare in una ricostruzione posteriore che, nel medesimo articolo, usa la stessa data anche per l’unificazione delle inchieste del 2006</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — IL PRINCIPIO GENERALE, CHE VALE PER LE 6 DISCREPANZE ANCORA APERTE. In entrambi i casi risolti, LA DIVERGENZA NON ERA UN ERRORE DI UNA FONTE MA LA REGISTRAZIONE DI DUE ATTI DISTINTI DA PARTE DI FONTI DIVERSE. Ne segue la regola di lavoro: davanti a due date vicine non si cerca quale sia falsa, MA QUALE ATTO CIASCUNA REGISTRI; e la discrepanza si chiude nominando entrambi. Chi sceglie una data e scarta l’altra perde un\’informazione anziche acquistarne una</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="n"/>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="n"/>
+      <c r="L41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CHIUSURA DELLA DISCREPANZA SULLA SCISSIONE DEL 1908 — E RETTIFICA A UN CAPITOLO GIA SCRITTO</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Fonte istituzionale per il fatto: relazione della Commissione parlamentare d’inchiesta sulla loggia P2, che registra «una scissione intervenuta nel 1908, in ragione di contrasti attinenti l’atteggiamento da assumere sulla legislazione concernente l’insegnamento religioso nelle scuole». Per la data: voce enciclopedica, enciclopedia massonica di lingua tedesca e ricostruzione giornalistica concordano; studio accademico sui fondi di Salamanca per il contesto</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>LA DATA E IL 24 GIUGNO 1908. 3 fonti indipendenti la indicano concordemente; il 26 giugno compare in un sito di un’obbedienza discendente dagli scissionisti, cioe FONTE DI PARTE E SUCCESSORE INTERESSATO. VI E INOLTRE UNA CORROBORAZIONE INTERNA CHE VALE PIU DEL COMPUTO DELLE FONTI: il 24 giugno e la festivita del santo precursore, data nella quale le obbedienze tengono per tradizione l’assemblea annuale — e la rottura si consumo appunto in quella sede. **Livello A**</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>LA RETTIFICA, CHE E SOSTANZIALE E RIGUARDA UN CAPITOLO GIA REDATTO DI QUEST’OPERA. Era stato scritto che l’obbedienza «aveva imposto ai propri affiliati parlamentari un indirizzo di voto». LA DINAMICA ACCERTATA E DIVERSA E PIU FORTE: nel corso della gran loggia annuale il gran maestro ETTORE FERRARI PROPOSE LA CENSURA nei confronti dei parlamentari massoni CHE SI ERANO RIFIUTATI DI VOTARE la mozione — presentata da LEONIDA BISSOLATI, deputato socialista riformista anch’egli massone — volta ad abolire l’insegnamento della religione nella scuola elementare. SAVERIO FERA, sovrano gran commendatore in pectore del rito scozzese, POSE IL VETO FORMALE CONTRO LA PROPOSTA DI CENSURA, e da li si giunse alla scissione</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE LA RETTIFICA RAFFORZA L’ARGOMENTO ANZICHE INDEBOLIRLO: non si trattava di un’istruzione di voto impartita in anticipo, MA DI UNA SANZIONE ASSOCIATIVA MINACCIATA A POSTERIORI CONTRO CHI AVEVA VOTATO SECONDO COSCIENZA. La questione sollevata dagli scissionisti non era dunque se l’associazione potesse indirizzare, ma SE POTESSE PUNIRE UN ELETTO PER IL VOTO ESPRESSO. E la prova del vincolo di coscienza, quarto criterio del terzo asse della tassonomia, VA RIFORMULATA DI CONSEGUENZA in termini di sanzione e non di indirizzo</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>ELEMENTI ULTERIORI DA REGISTRARE: secondo le parole del gran maestro abbandonarono 9 LOGGE; gli scissionisti erano guidati da un pastore metodista wesleyano poi della chiesa evangelica italiana, deputato, e furono seguiti da 21 ALTI DIGNITARI che portarono con se sigilli e cassa del rito; all’inizio del 1909 la nuova obbedienza contava CIRCA 15MILA ISCRITTI. Lo studio accademico avverte che la questione scolastica «AVEVA FUNTO DA DETONATORE PER UNA SITUAZIONE INTERNA CHE GIA VIVEVA FORTI CRITICITA E DIVISIONI»: la causa dichiarata non esaurisce la causa</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 4 — DUE CONSEGUENZE OPERATIVE. Il capitolo sul dominio quarto va corretto nel passaggio sul millenovecentotto. E il fatto ha ora una fonte parlamentare italiana, che e preferibile alle fonti massoniche di parte finora usate per esso</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="n"/>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="n"/>
+      <c r="L42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>La soppressione della relazione parlamentare statunitense del 1976 — CRONOLOGIA CHIUSA E DOCUMENTI MAI RITROVATI</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Rivista interna dell’agenzia informativa statunitense, numero invernale 1998-1999; archivio universitario di sicurezza nazionale; edizione integrale della relazione trafugata, pubblicata all’estero</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>LA CRONOLOGIA, ORA COMPLETA. 15 GENNAIO 1976: il presidente scrive al presidente della commissione negando la declassificazione delle informazioni sulle operazioni coperte. 19 GENNAIO: la commissione trasmette all’agenzia la bozza finale, 338 PAGINE. 26 GENNAIO: il maggiore esponente repubblicano della commissione dichiara in aula che la diffusione metterebbe in pericolo la sicurezza nazionale. 29 GENNAIO 1976, 3 GIORNI DOPO: la camera vota 246 CONTRO 124 per vietare alla propria commissione di diffondere la relazione finche non sia «CERTIFICATA DAL PRESIDENTE COME NON CONTENENTE INFORMAZIONI CHE POSSANO PREGIUDICARE LE ATTIVITA INFORMATIVE DELL’AGENZIA». **Livello A**</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>LA REPLICA DI OTIS PIKE, DA CITARE NEL TOMO TERZO: «LA CAMERA HA APPENA VOTATO PER NON DIFFONDERE UN DOCUMENTO CHE NON AVEVA LETTO. LA NOSTRA COMMISSIONE HA VOTATO PER DIFFONDERE UN DOCUMENTO CHE AVEVA LETTO». Egli minaccio inoltre di non depositare alcuna relazione, poiche «UNA RELAZIONE SULL’AGENZIA NELLA QUALE L’AGENZIA FACESSE LA STESURA FINALE SAREBBE UNA MENZOGNA»</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>L’ESITO. 13 FEBBRAIO: un giornalista televisivo riconosce pubblicamente di avere ricevuto il testo. 16 FEBBRAIO 1976: ampi estratti compaiono su un settimanale newyorkese sotto il titolo «LA RELAZIONE SULL’AGENZIA CHE IL PRESIDENTE NON VUOLE CHE VOI LEGGIATE». Il testo sara poi pubblicato integralmente IN GRAN BRETAGNA NEL 1977, con introduzione di un ex funzionario dissidente. IL MANDATO DELLA COMMISSIONE SCADDE NEL 1976 SENZA CHE ALCUNA RELAZIONE FOSSE MAI DEPOSITATA, e si registra che UNA RELAZIONE COMPLETA NON E MAI STATA RINVENUTA E POTREBBE NON ESISTERE</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE CHIUDE IL CERCHIO, E CHE VA REGISTRATO ACCANTO ALLA DISTRUZIONE DEI REPERTI IN ALTRI CASI: nel marzo 1976 L’AGENZIA SOSTENNE CHE LA COMMISSIONE NON AVESSE RESTITUITO, E NON RIUSCISSE A TROVARE, CIRCA 230 DOCUMENTI da essa consegnati nel corso dell’inchiesta, ALMENO IN PARTE CLASSIFICATI. Il presidente della commissione riferi in aula una minaccia attribuita al consulente legale dell’agenzia — «LA PAGHERA, VEDRETE; LO DISTRUGGEREMO PER QUESTO» — che il consulente nego</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tomo III — LA FORMA COMPIUTA DELLA SOPPRESSIONE PARLAMENTARE: un organo elettivo vieta a se stesso di pubblicare cio che il proprio comitato ha accertato, subordinando la diffusione al placet dell’ente indagato; la relazione esce comunque per via giornalistica e all’estero; e i documenti istruttori risultano dispersi</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="n"/>
+      <c r="L43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>LO SCARTO FRA LA RELAZIONE DEL GOVERNO E IL DOCUMENTO DEL GOVERNO — 26 contro 28 novembre 1956</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Per la prima data: relazione del presidente del Consiglio alla Commissione parlamentare d’inchiesta, PROTOCOLLO NUMERO 5099 DEL 17 OTTOBRE 1990, i cui stralci sono stati ripubblicati integralmente. Per la seconda: INDICE GENERALE DEGLI ATTI DELLA COMMISSIONE, X legislatura, consultabile sul portale della Camera</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>LA DISCREPANZA NON E BIBLIOGRAFICA, E QUESTO E IL RITROVAMENTO. La relazione governativa del 17 ottobre 1990 afferma testualmente: «MENTRE LA STRUTTURA DI RESISTENZA CLANDESTINA ITALIANA ERA IN FASE DI AVANZATA COSTITUZIONE, VENNE SOTTOSCRITTO, IN DATA 26 NOVEMBRE 1956, dal SIFAR e dal Servizio americano un accordo relativo alla organizzazione ed alla attivita della rete clandestina post occupazione, accordo comunemente denominato stay-behind, CON IL QUALE FURONO CONFERMATI TUTTI I PRECEDENTI IMPEGNI intervenuti sulla materia tra Italia e Stati Uniti». **Livello A** quanto al testo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>MA L’INDICE DEGLI ATTI DELLA MEDESIMA COMMISSIONE REGISTRA, FRA I DOCUMENTI RICEVUTI DALLA PRESIDENZA DEL CONSIGLIO: «COPIA DELL’ACCORDO SIFAR-CIA DEL 28 NOVEMBRE 1956, IN LINGUE ITALIANA ED INGLESE, CON LETTERA DI TRASMISSIONE DEL 28.2.91 CHE VINCOLA LA COMMISSIONE A NON DIVULGARE». IL DOCUMENTO CONSEGNATO PORTA DUNQUE UNA DATA DIVERSA DA QUELLA CHE IL GOVERNO AVEVA COMUNICATO AL PARLAMENTO 4 MESI PRIMA. **Livello A** quanto alla registrazione d’indice</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>DUE ELEMENTI ULTERIORI DELLA MEDESIMA RIGA D’INDICE, DA NON PERDERE: la copia fu trasmessa IL 28 FEBBRAIO 1991, cioe 4 MESI DOPO la relazione che lo descriveva; e la lettera di trasmissione VINCOLAVA LA COMMISSIONE A NON DIVULGARE L’ATTO. L’organo d’inchiesta ricevette dunque il documento fondativo con divieto di pubblicarlo</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>COSA NON SI PUO CONCLUDERE, E VA DETTO. Lo scarto di due giorni PUO derivare da distinta datazione delle due sottoscrizioni, da errore di trascrizione nella relazione, o da distinzione fra data di firma e data di protocollo. NESSUNA DELLE 3 E ACCERTATA, E NESSUNA VA PRESUNTA. Cio che e accertato e che LE DUE DATE PROVENGONO ENTRAMBE DALL’ESECUTIVO, in atti distanti 4 mesi: non e una divergenza fra studiosi, ma fra una fonte e se stessa</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II e Metodologia — E LA MIGLIORE ILLUSTRAZIONE DEL PRINCIPIO ADOTTATO OGGI. Cercare quale delle due date sia falsa avrebbe fatto perdere il fatto: che il racconto ufficiale e il documento ufficiale non coincidono, e che il secondo giunse al Parlamento con divieto di divulgazione. LA DISCREPANZA ERA ESSA STESSA UN DATO</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="n"/>
+      <c r="L44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Il grado d’appello del processo romano — PRECISAZIONI CHE MUTANO LA LETTURA DEI 3 GRADI</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>5 testate coeve dell’8 LUGLIO 2019 e ricostruzioni successive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>LA DENOMINAZIONE ESATTA, CHE NON E UN DETTAGLIO: la pronuncia e della PRIMA CORTE D’ASSISE D’APPELLO BIS di Roma. Il termine «bis» indica che un precedente grado d’appello era stato annullato con rinvio, e la circostanza va accertata negli atti perche allunga la catena processuale oltre i 3 gradi comunemente riferiti</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>LA MOTIVAZIONE DEL PRIMO GRADO, CHE E IL VERO OGGETTO DEL RIBALTAMENTO. I giudici di primo grado avevano ritenuto coloro che «HANNO REALIZZATO OPERATIVAMENTE IL SISTEMA DELL’APPARATO REPRESSIVO» responsabili SOLTANTO DEL SEQUESTRO DI PERSONA — reato gia prescritto — E NON ANCHE DELL’OMICIDIO. La condanna colpiva dunque i vertici e mancava gli esecutori, per una qualificazione giuridica e non per difetto di prova. L’appello ha ribaltato precisamente questo</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>SI CHIUDE COSI ANCHE LA DISCREPANZA SUL NUMERO DEGLI IMPUTATI: in primo grado furono 8 ERGASTOLI, 19 ASSOLUZIONI E 6 PROSCIOGLIMENTI PER MORTE DEL REO, per un totale di 33 GIUDICATI. I 37 talora indicati comprendono i 4 brasiliani giudicati in procedimento separato. In appello, 24 condanne su 25 residui</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>ELEMENTO CIVILE DA REGISTRARE: la corte dispose il risarcimento in favore di 47 PARTI CIVILI, con provvisionale esecutiva di UN MILIONE DI EURO ALLA PRESIDENZA DEL CONSIGLIO DEI MINISTRI e somme fra duecentocinquantamila e 100.000 euro alle altre. LA PRESIDENZA DEL CONSIGLIO ERA PARTE CIVILE, e ottenne la provvisionale piu alta: lo Stato italiano si costitui contro gli apparati stranieri che avevano ucciso propri cittadini</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Secondo — DUE ACQUISIZIONI. La catena processuale e piu lunga di 3 gradi e va ricostruita sugli atti. E il primo grado non assolse per difetto di prova ma PER QUALIFICAZIONE GIURIDICA, distinguendo mandanti ed esecutori e facendo cadere questi ultimi nella prescrizione: e la medesima forma che il repertorio registra nei casi italiani</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="n"/>
+      <c r="L45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>La designazione argentina — ULTIMA DISCREPANZA DI DATA CHIUSA, E UN’IMPOSSIBILITA CRONOLOGICA CHE NESSUNA FONTE HA RILEVATO</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ricostruzione giornalistica che indica gli estremi del decreto; voce enciclopedica di lingua inglese che attribuisce l’atto a un decreto redatto dal ministro degli Esteri argentino con il presidente; SCHEDA DEL SISTEMA ARCHIVISTICO DEL MINISTERO DELLA CULTURA ITALIANO, che e fonte istituzionale</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>LA CHIUSURA: l’atto e il DECRETO NUMERO SETTANTATRE DEL 2 SETTEMBRE 1974, con cui il governo argentino designa l’interessato CONSIGLIERE ECONOMICO DELL’AMBASCIATA IN ITALIA. La collocazione all’agosto proviene da una fonte che accorpa la designazione all’onorificenza, e riguarda dunque atto diverso</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>L’ANOMALIA, CHE E IL VERO RITROVAMENTO E CHE NESSUNA DELLE FONTI SEGNALA. La medesima voce enciclopedica afferma che il decreto d’agosto fu «redatto dal ministro degli Esteri argentino CON IL PRESIDENTE», e comprendeva sia la massima onorificenza sia l’ufficio onorario di consigliere economico. MA QUEL PRESIDENTE ERA MORTO IL PRIMO LUGLIO 1974: un decreto redatto con lui nell’agosto successivo E CRONOLOGICAMENTE IMPOSSIBILE. Delle 3 spiegazioni possibili — redazione anteriore e pubblicazione posteriore, attribuzione erronea, o confusione con l’onorificenza del 1973 — NESSUNA E ACCERTATA. VA REGISTRATA COME ANOMALIA APERTA, NON COME ERRORE DI UNA FONTE. Si segnala inoltre che una ricostruzione italiana colloca la morte del presidente al 10 LUGLIO anziche al primo: SECONDO ERRORE, INDIPENDENTE</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>GLI UFFICI, CHE ERANO PIU DI UNO E VANNO DISTINTI: CONSOLE ONORARIO ARGENTINO A FIRENZE, ottenuto nella prima fase; CONSIGLIERE ECONOMICO DELL’AMBASCIATA IN ITALIA dal settembre 1974; e MINISTRO PLENIPOTENZIARIO PER GLI AFFARI CULTURALI, che comportava IMMUNITA DIPLOMATICA. La scheda del sistema archivistico del ministero della Cultura italiano — FONTE ISTITUZIONALE ITALIANA — attesta che «DAL 1973 AL 1980 FU CONSIGLIERE ECONOMICO ACCREDITATO AL GOVERNO ITALIANO E MINISTRO PLENIPOTENZIARIO PER GLI AFFARI CULTURALI». **Livello A**</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>DUE ELEMENTI ULTERIORI DA REGISTRARE: risulta che in Argentina sia stato incolpato di FALSIFICAZIONE DI DOCUMENTI UFFICIALI; e che negli anni Settanta abbia mediato OPERAZIONI TRIANGOLARI SU PETROLIO E ARMAMENTI FRA LIBIA, ITALIA E ARGENTINA attraverso una societa per lo sviluppo economico posseduta con il finanziere poi anch’egli iscritto. Si registra inoltre che il presidente argentino ad interim in carica dal 13 luglio al 12 ottobre 1973 figura fra gli iscritti alla loggia</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Tomo Secondo — CHIUDE L’ULTIMA DELLE 8 DISCREPANZE DI DATA. E lascia un’anomalia di segno diverso: non due fonti che divergono, MA UNA FONTE CHE COLLOCA UN ATTO DOPO LA MORTE DI CHI L’AVREBBE SOTTOSCRITTO. Va portata agli atti argentini</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="n"/>
+      <c r="L46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>La sezione sui servizi statunitensi nel capitolo su Brescia — Doc. XXIII n. 64, Vol. I, Tomo II, PAGINE 250-252</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Proposta di relazione sottoscritta da 9 parlamentari, 22 giugno 2000, paragrafo III.3; fonte primaria interna: interrogatori di un collaboratore del 19 APRILE e 4 MAGGIO 1996</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>IL CONTENUTO, RIFERITO CON ESATTEZZA. Carlo Digilio dichiara che, in base a una direttiva del 1963 volta a fermare il comunismo in Italia, la rete informativa statunitense avrebbe contattato e coordinato elementi di destra disponibili, con l’obbligo di «NON TRALASCIARE DI INFORMARE GLI AMERICANI DI QUALSIASI SITUAZIONE, COME MOVIMENTI DI ARMI ED ESPLOSIVI O ATTENTATI». Dichiara inoltre che «CIRCA 10 GIORNI PRIMA DELLA STRAGE DI BRESCIA», a cena in una trattoria, uno dei presenti disse «CHE DI LI A POCHI GIORNI CI SAREBBE STATO UN GROSSO ATTENTATO TERRORISTICO», e che l’uso della trattoria era «UN SISTEMA IPOCRITA DI FAR FINTA DI ESSERE SOLO UNA COMPAGNIA DI AMICI» per scambiarsi informazioni</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>L’INFERENZA DEI COMMISSARI, DA TENERE DISTINTA DAL DICHIARATO: essi ne traggono che la struttura informativa straniera «ERA STATA AVVERTITA», che «CONOSCEVA L’AREA IN CUI CERCARE AUTORI E MANDANTI», che un suo agente operativo «SVOLSE UN RUOLO NELL’ESECUZIONE», e che non risulta che le autorita italiane fossero avvertite ne che vi fosse intervento per impedire l’attentato. Da cio concludono che «LA STRATEGIA STRAGISTA ERA APPROVATA DAI SUPERIORI». QUEST’ULTIMO PASSAGGIO E UN’INFERENZA DALLA CONOSCENZA AL MANDATO, che la regola dei 3 piani adottata da quest’opera VIETA IN ASSENZA DI PROVA DIRETTA, e va segnalato come tale ogni volta che il brano e citato</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>3 CAUTELE CHE NE LIMITANO L’USO. PRIMA: l’intero paragrafo poggia su UN SOLO DICHIARANTE e sui suoi interrogatori; per il criterio di indipendenza genealogica adottato in quest’opera, una fonte e i suoi derivati costituiscono UNA CATENA, non piu fonti. I commissari affermano che le dichiarazioni «HANNO TROVATO UNA SERIE DI RISCONTRI» ma il brano si interrompe prima di esporli: I RISCONTRI VANNO CERCATI E VALUTATI SEPARATAMENTE. SECONDA: si tratta di proposta di gruppo e non di accertamento unanime. TERZA, ED E LA PIU SERIA</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>L’ANOMALIA INTERNA ALLA TESTIMONIANZA, CHE VA VERIFICATA PRIMA DI QUALSIASI USO: il dichiarante attribuisce la direttiva del 1963 a UN GENERALE STATUNITENSE CHE IN QUELL’ANNO DIRIGEVA L’ACCADEMIA MILITARE DI WEST POINT E CHE ASSUNSE IL COMANDO IN ESTREMO ORIENTE SOLTANTO NEL 1964, senza avere mai avuto competenze sulla politica europea. L’ATTRIBUZIONE E QUINDI IMPLAUSIBILE COSI COME RIPORTATA. Puo trattarsi di confusione del dichiarante, di errore di verbalizzazione o di trascrizione; NESSUNA DELLE 3 E ACCERTATA. Un elemento verificabile e implausibile dentro una testimonianza NON LA FALSIFICA INTERAMENTE, MA NE ABBASSA IL GRADO: il paragrafo NON PUO SORREGGERE DA SOLO ALCUNA AFFERMAZIONE, e va portato al livello C finche i riscontri non siano esaminati</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II e Metodologia — E IL BANCO DI PROVA DEL METODO. E il materiale piu grave incontrato nel corpus e quello su cui il metodo impone la maggiore prudenza: fonte unica, inferenza vietata dai commissari stessi, e un dato interno implausibile. CITARLO SENZA LE 3 CAUTELE SIGNIFICHEREBBE CONSEGNARE ALL’AVVERSARIO IL PUNTO PIU FACILE DELL’INTERA OPERA</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>LA PARABOLA GIUDIZIARIA DI UNA FONTE — la stessa testimonianza svalutata in un processo e ritenuta attendibile in un altro</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Sentenza di primo grado su piazza Fontana del 30 GIUGNO 2001; successive pronunce d’appello e di legittimita che la annullarono; sentenza di legittimita che annullo le assoluzioni per la strage bresciana; sentenza d’appello bis della Corte d’assise d’appello di MILANO; conferma definitiva del 2017 — DATA ESATTA DA VERIFICARE</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>LA PRIMA FASE. Il 30 GIUGNO 2001 CARLO MARIA MAGGI, DELFO ZORZI e GIANCARLO ROGNONI furono condannati all’ergastolo per la strage milanese del 1969, sulla base sostanziale delle dichiarazioni di CARLO DIGILIO, armiere del gruppo divenuto collaboratore. LA CORTE D’ASSISE D’APPELLO E POI LA CORTE DI CASSAZIONE ANNULLARONO QUELLE CONDANNE «ATTRAVERSO LA SISTEMATICA SVALUTAZIONE» DELLE MEDESIME DICHIARAZIONI. Si registra pero che la pronuncia definitiva su quella strage RIBADI LA RESPONSABILITA di due militanti gia giudicati in precedenza e delle cellule venete dell’organizzazione, i quali non potevano essere nuovamente processati</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA FASE, DI SEGNO OPPOSTO. Nel procedimento sulla strage bresciana del 1974, dopo assoluzioni in primo e secondo grado, LA CORTE DI CASSAZIONE ANNULLO L’ASSOLUZIONE definendo «INGIUSTIFICABILI E SUPERFICIALI» i motivi addotti e soffermandosi sulla «GRAVITA INDIZIARIA» delle dichiarazioni di Digilio. Nel giudizio d’appello bis celebrato a Milano CARLO MARIA MAGGI e MAURIZIO TRAMONTE FURONO CONDANNATI ALL’ERGASTOLO, e in quella sede LE DICHIARAZIONI FURONO PRESE IN CONSIDERAZIONE COME ATTENDIBILI. La condanna e divenuta definitiva</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>IL FATTO, CHE E DEL SISTEMA E NON DELLA FONTE: LE MEDESIME DICHIARAZIONI SONO STATE GIUDICATE INSUFFICIENTI IN UN PROCEDIMENTO E SUFFICIENTI IN UN ALTRO, DALLA MEDESIMA CORTE DI LEGITTIMITA, A UN DECENNIO DI DISTANZA. Non e contraddizione in senso stretto, poiche l’oggetto era diverso e diverso era il compendio dei riscontri; MA E UN DATO CHE VA REGISTRATO OGNI VOLTA CHE QUELLA FONTE E CITATA, perche impedisce tanto di liquidarla quanto di darla per acquisita</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>LA CONSEGUENZA PER LA SEZIONE SUI SERVIZI STATUNITENSI, ED E DECISIVA. La strage bresciana E STATA GIUDIZIARIAMENTE ACCERTATA quanto a mandante ed esecutore, su un compendio che comprendeva quelle dichiarazioni: il paragrafo parlamentare del duemila NON POGGIA DUNQUE SU UNA FONTE GIUDIZIARIAMENTE RIPUDIATA. MA CIO CHE E STATO ACCERTATO SONO LE RESPONSABILITA DEI DUE CONDANNATI: NESSUN COINVOLGIMENTO DI APPARATI STRANIERI E STATO OGGETTO DI ACCERTAMENTO GIUDIZIARIO. La distinzione va tenuta assoluta: la fonte ha retto in giudizio PER CIO CHE IL GIUDIZIO HA DECISO, e non per tutto cio che essa ha dichiarato</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II e Dominio 10 — DUE REGOLE. La prima: una fonte non e attendibile o inattendibile in assoluto, MA RISPETTO A UN THEMA PROBANDUM, e il suo grado va dichiarato caso per caso. La seconda: che una testimonianza abbia sorretto una condanna NON ESTENDE IL SUO CREDITO ALLE PARTI DI ESSA CHE NESSUN GIUDICE HA VAGLIATO</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>«IN TERMINI NON GIUDIZIARI MA STORICO-POLITICI» — la formula della Commissione sulla loggia, e la strage annunciata</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Relazione DI MAGGIORANZA della Commissione parlamentare d’inchiesta sulla loggia P2, citata testualmente nella proposta di relazione della Commissione stragi del 22 giugno 2000, pagine 252-253; ordinanza di custodia cautelare, procedimento 6071/95 R.G.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMULA, TESTUALE E IN 3 PUNTI. «1. La strage dell’Italicus e ascrivibile ad una organizzazione terroristica di ispirazione neofascista o neonazista operante in Toscana; 2. La loggia P2, al cui vertice c’era Licio Gelli, gia implicato nel tentato golpe Borghese, SVOLSE OPERA DI ISTIGAZIONE AGLI ATTENTATI E DI FINANZIAMENTO nei confronti dei gruppi della destra extraparlamentare toscana; 3. La loggia P2 e quindi gravemente coinvolta nella strage dell’Italicus e PUO CONSIDERARSENE ADDIRITTURA RESPONSABILE IN TERMINI NON GIUDIZIARI MA STORICO-POLITICI, quale essenziale retroterra economico, organizzativo e morale». **Livello A** quanto al testo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>PERCHE E LA FORMULA CHE QUEST’OPERA CERCAVA. Una commissione dello Stato AFFERMA UNA RESPONSABILITA E NE DICHIARA NEL MEDESIMO PERIODO LA NATURA NON GIUDIZIARIA. Non attenua e non esagera: distingue i piani e nomina quello sul quale parla. E LA DISTINZIONE FRA ACCERTAMENTO STORICO E ACCERTAMENTO PENALE, FATTA DALLA FONTE E NON DALL’INTERPRETE — e va adottata come modello di enunciato per l’intera opera. I commissari del 2000 aggiungono che la conclusione puo essere ribadita, «BENCHE LA COMPLESSA VICENDA GIUDIZIARIA ABBIA SINORA CONDOTTO AD ESITI ASSOLUTORI»</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>LA STRAGE ANNUNCIATA — PRIMO PREANNUNCIO. FRANCESCO SGRÒ, poi condannato per calunnia, indusse GIORGIO ALMIRANTE, segretario del MSI, a recarsi, accompagnato dal deputato ALFREDO COVELLI, a recarsi da EMILIO SANTILLO, direttore dell’Ispettorato generale antiterrorismo, per denunciare il timore di un imminente attentato a un treno AD INIZIATIVA DI AMBIENTI UNIVERSITARI ROMANI DI SINISTRA. Successivamente il medesimo RICONOBBE IL CARATTERE CALUNNIOSO DELLE PROPRIE DICHIARAZIONI, affermando di aver tentato con esse DI OTTENERE DENARO DAL PARTITO. L’attentato avvenne, e la matrice accertata fu opposta a quella preannunciata</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SECONDO PREANNUNCIO: CLAUDIA AIELLO, dipendente del SID con funzioni di interprete, INFILTRATA PER CONTO DEL SERVIZIO NEL PARTITO COMUNISTA E NEGLI AMBIENTI DEGLI ESULI GRECI, sarebbe stata ascoltata pochi giorni prima in una ricevitoria romana pronunciare al telefono frasi quali «LE BOMBE SONO PRONTE», con riferimento a passaporti, treni e due citta. «L’EPISODIO, OGGETTO DI RIPETUTO E ATTENTO ESAME GIUDIZIARIO, NON HA PORTATO A SVILUPPI INDAGATIVI CHE ABBIANO ASSUNTO CONCRETO RILIEVO». I commissari ne traggono soltanto la conferma del «CARATTERE DI STRAGE ANNUNCIATA», e la misura della loro conclusione va conservata</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia e Dominio 7 — DUE ACQUISIZIONI. LA FORMULA DEI DUE PIANI VA ADOTTATA COME STANDARD DI ENUNCIATO. E il primo preannuncio e L’ATTRIBUZIONE FALSA NELLA SUA FORMA PIU ESTREMA: non compiuta dopo il fatto per sviarne le indagini, MA DEPOSITATA PRIMA DEL FATTO PRESSO L’ORGANO DI POLIZIA COMPETENTE. La prova dell’attribuzione falsa, quinto criterio del primo asse, VA ESTESA ALLA FORMA ANTICIPATA</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="n"/>
+      <c r="L49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>LE DUE FORME DEL DEPISTAGGIO A CONFRONTO — Italicus e Bologna, e il fatto piu forte del repertorio</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Corte suprema di cassazione, SEZIONI UNITE PENALI, udienze del 22 e 23 NOVEMBRE 1995, sentenza pubblicata a cura dell’associazione dei familiari delle vittime; sentenze del processo piu recente sulla medesima strage</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>IL FATTO, E VA ENUNCIATO PER INTERO PERCHE E IL PIU FORTE CHE QUEST’OPERA POSSA CITARE. Con sentenza definitiva delle Sezioni Unite del 23 NOVEMBRE 1995 sono stati condannati per CALUNNIA CONTINUATA E PLURIAGGRAVATA, «PER AVERE, IN CONCORSO TRA LORO E CON PIU AZIONI ESECUTIVE DI UN MEDESIMO DISEGNO CRIMINOSO, DIVULGATO ALCUNE INFORMATIVE FATTE PERVENIRE AGLI INQUIRENTI»: DUE UFFICIALI IN SERVIZIO DEL SISMI — il generale PIETRO MUSUMECI a 8 anni e 5 mesi e il colonnello GIUSEPPE BELMONTE a 7 anni e 11 mesi; FRANCESCO PAZIENZA, collaboratore del direttore generale del medesimo servizio, a 10 anni; e LICIO GELLI, capo della loggia P2,, a 10 anni. **Livello A**</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>L’AGGRAVANTE, CHE E LA PARTE DECISIVA E CHE LE SINTESI OMETTONO: la calunnia fu ritenuta AGGRAVATA DALLA FINALITA DI TERRORISMO ai sensi dell’articolo primo della legge 6 FEBBRAIO 1980 NUMERO 15, e commessa AL FINE DI ASSICURARE L’IMPUNITA AGLI AUTORI DELLA STRAGE. LA CORTE SUPREMA DELLO STATO HA DUNQUE ACCERTATO IN VIA DEFINITIVA CHE UFFICIALI IN SERVIZIO DEL PROPRIO SERVIZIO INFORMATIVO MILITARE COMMISERO CALUNNIA CON FINALITA DI TERRORISMO PER PROTEGGERE GLI AUTORI DI UNA STRAGE. Non e un’ipotesi storiografica: e un giudicato</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>IL CONFRONTO CON L’ALTRO CASO, CHE DEFINISCE DUE FORME DISTINTE. Nell’Italicus il depistaggio fu PREVENTIVO — l’attribuzione falsa depositata presso l’organo di polizia PRIMA del fatto, da un privato che agiva per denaro — e produsse L’UNICA CONDANNA DELL’INTERA VICENDA, un anno e 5 mesi, mentre la strage resta senza colpevoli. A Bologna il depistaggio fu SUCCESSIVO E ISTITUZIONALE — informative false diramate DOPO il fatto DA APPARATI DELLO STATO — e produsse condanne definitive ACCANTO a quelle per la strage</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMA NON SI E ESAURITA: nel procedimento piu recente sulla medesima strage sono divenute definitive la condanna di il carabiniere PIERGIORGIO SEGATEL a 6 anni per depistaggio e quella di DOMENICO CATRACCHIA a 4 anni per false informazioni al pubblico ministero. IL DEPISTAGGIO SULLA MEDESIMA STRAGE E STATO GIUDICATO IN DUE ONDATE A DISTANZA DI TRENT’ANNI</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Tomo II e Dominio 3 — 3 ACQUISIZIONI. PRIMA: il capitolo sull’arco di sponda va rafforzato con questo giudicato, che non descrive una prossimita ma una CONDANNA. SECONDA: la coppia Italicus-Bologna fornisce DUE TIPI del depistaggio, preventivo-privato e successivo-istituzionale, e la tipologia va costruita su di essi. TERZA, E LA PIU IMPORTANTE: quest’opera NON HA BISOGNO DI IPOTIZZARE il coinvolgimento di apparati statali nella copertura delle stragi, PERCHE SU UN CASO E STATO ACCERTATO IN VIA DEFINITIVA DALLE SEZIONI UNITE. Cio che resta ipotetico e l’estensione ad altri casi, e come tale va dichiarato</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>«STRAGE ATLANTICA DI STATO» — il passo piu grave del corpus e il piu fragile, e la ragione e la stessa</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo I.5, pagine 230-232; fonte primaria interna: dichiarazioni di Digilio, interrogatorio del 17 MAGGIO 1997; nota del testo: «parte di queste considerazioni sono contenute nella sentenza-ordinanza del giudice istruttore, paragrafo 4»</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>IL CONTENUTO, RIFERITO CON ESATTEZZA E SENZA ATTENUAZIONI. Il testo descrive una struttura informativa con sede presso il comando alleato di Verona, alle dipendenze del sedicente capitano DAVID CARRETT, alla quale sarebbero appartenuti 4 elementi organicamente inseriti nell’organizzazione neofascista veneta o suoi referenti. Sostiene che Carrett, informato in anticipo di un attentato in preparazione, ANZICHE IMPEDIRLO RACCOMANDO DI RIDURNE LA POTENZIALITA, e che si congratulo poi ricordando che «la struttura vedeva di buon occhio azioni dimostrative, ma non accettava massacri indiscriminati». Sostiene inoltre che Carrett fu informato CON QUALCHE GIORNO DI ANTICIPO degli attentati del 12 dicembre 1969 e «NON FECE NULLA PER SCONGIURARE L’ATTENTATO», e che non intervenne neppure per i due attentati successivi. E ne trae la formula: non soltanto «strage di Stato» ma «STRAGE ATLANTICA DI STATO»</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>LA RAGIONE DELLA FRAGILITA, ED E DECISIVA. L’INTERO PASSO POGGIA SULLE DICHIARAZIONI DEL SOLO CARLO DIGILIO. E QUELLE DICHIARAZIONI, PROPRIO NEL PROCEDIMENTO SULLA STRAGE MILANESE DEL 1969 — CIOE ESATTAMENTE IL FATTO DI CUI QUESTO PASSO TRATTA — FURONO OGGETTO DI «SISTEMATICA SVALUTAZIONE» DA PARTE DELLA CORTE D’APPELLO E POI DELLA CORTE DI CASSAZIONE, CHE ANNULLARONO LE CONDANNE FONDATE SU DI ESSE. Sul diverso fatto della strage bresciana le medesime dichiarazioni sono state invece ritenute attendibili e hanno sorretto condanne definitive. VALE DUNQUE LA REGOLA STABILITA IN QUESTO REPERTORIO: UNA FONTE E ATTENDIBILE RISPETTO A UN THEMA PROBANDUM, E QUESTO E IL THEMA SUL QUALE NON HA RETTO</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>3 ULTERIORI LIMITI. PRIMO: si tratta di proposta sottoscritta da 9 parlamentari e non di accertamento unanime della Commissione. SECONDO: la nota rinvia a una SENTENZA-ORDINANZA DEL GIUDICE ISTRUTTORE GUIDO SALVINI, che e atto istruttorio e non decisione definitiva, e il cui esito successivo e quello sopra descritto. TERZO: L’IDENTIFICAZIONE DI DAVID CARRETT, sulla cui esistenza e qualifica la letteratura ha sollevato interrogativi mai chiusi, VA VERIFICATA PRIMA DI OGNI USO e non va data per acquisita</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>LA FORMULA, PER CIO CHE E: «strage atlantica di Stato» E UNA CARATTERIZZAZIONE STORICO-POLITICA PROPOSTA DA 9 PARLAMENTARI NEL DUEMILA, NON UN ACCERTAMENTO GIUDIZIARIO. Va citata soltanto con l’attribuzione esplicita e con la qualificazione del suo statuto, esattamente come la Commissione sulla loggia distinse i «termini non giudiziari ma storico-politici». Chi la citasse come fatto accertato COMMETTEREBBE L’ERRORE CHE LA FONTE STESSA, IN ALTRA SEDE, HA EVITATO</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — LIVELLO C, E VA MANTENUTO. E il passo che la pubblicistica citerebbe per primo ed e quello che quest’opera deve citare per ultimo, con tutte e 4 le cautele. Registrarlo e doveroso; usarlo come prova sarebbe consegnare all’avversario la falla piu larga dell’intera costruzione</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="n"/>
+      <c r="L51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PETEANO — il solo caso giunto a giudicato, e la ragione per cui vi giunse</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo IV.2, pagine 171-173; deposizione del colonnello DINO MINGARELLI del 14 MARZO 1990, atti pp. 1394-1395; atti di assise p. 59 e istruttoria p. 445</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>LA PRECISAZIONE DELLA COMMISSIONE, DA ADOTTARE: l’attentato «CON QUALCHE IMPROPRIETA VIENE ANNOVERATO NELLA PUBBLICISTICA TRA GLI EVENTI DI STRAGE». Il 31 MAGGIO 1972 una Fiat 500 imbottita di esplosivo fu abbandonata in un bosco presso Peteano di Sagrado, in provincia di Gorizia; alcuni colpi di pistola contro il parabrezza e una telefonata anonima richiamarono una pattuglia dei carabinieri; all’apertura del cofano l’ordigno esplose UCCIDENDO 3 MILITARI E FERENDONE GRAVEMENTE UN QUARTO. Obiettivo specifico e non indiscriminato: NON E TECNICAMENTE UNA STRAGE, e quest’opera non deve chiamarlo tale</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>LA FRASE CHE DEFINISCE IL CASO: e «uno degli episodi attribuiti alla destra radicale per i quali in sede giudiziaria si e giunti ad una conclusione di colpevolezza passata in giudicato, RESA POSSIBILE DALLA AMMISSIONE DI RESPONSABILITA DELL’ESECUTORE». VINCENZO VINCIGUERRA CONFESSO NEL 1984, DODICI ANNI DOPO. IL SOLO CASO CHE ABBIA PRODOTTO UN GIUDICATO NON FU RISOLTO DALL’INDAGINE MA DALLA CONFESSIONE SPONTANEA DI CHI L’AVEVA COMPIUTO</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>LA PRIMA PISTA FALSA, E IL SUO MECCANISMO. La «pista rossa» punto su un nucleo di Lotta Continua e poggiava su presunte affermazioni che il collaboratore MARCO PISETTA avrebbe reso al colonnello MICHELE SANTORO, comandante del Gruppo carabinieri di Trento. MA SIA I MAGISTRATI PRESENTI ALL’INCONTRO SIA PISETTA STESSO HANNO SMENTITO CHE EGLI ABBIA MAI PARLATO DI PETEANO. La velina fu trasmessa «IN MANIERA DEL TUTTO ANOMALA — FUOR DI PROTOCOLLO, TRAMITE CORRIERE E SOPRATTUTTO SENZA SEGUIRE LE VIE GERARCHICHE» al colonnello DINO MINGARELLI, comandante della Legione di Udine, DAL GENERALE PALUMBO, comandante della Divisione Pastrengo di Milano, CHE SI ERA PRECIPITATO A GORIZIA GIA IL 1 GIUGNO 1972, il giorno dopo. Mingarelli depose: «QUELLA FU L’ORIGINE DELLA COSIDDETTA PISTA ROSSA; IO SAPEVO CHE QUELLE NOTIZIE ARRIVAVANO DA TRENTO E CHE LA FONTE CONFIDENZIALE ERA MARCO PISETTA». **Livello A** quanto alla deposizione</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>LA SECONDA PISTA FALSA E L’ORDINE RIFERITO. La «pista gialla» poggiava anch’essa su pretese affermazioni di un informatore dei carabinieri CHE DAVANTI ALLA CORTE RIFIUTO DI RICONOSCERE LE AFFERMAZIONI ATTRIBUITEGLI; riguardava piccoli pregiudicati locali sottoposti FRA IL 1974 E IL 1979 a lunghe indagini e vari giudizi PRIMA CHE FOSSE PROVATA LA LORO INNOCENZA. E «tutti gli indizi a sostegno di una pista nera furono ignorati o scartati: CI SAREBBE ANZI ADDIRITTURA STATO UN PRECISO ORDINE DI BLOCCARE OGNI INDAGINE SUGLI AMBIENTI DI DESTRA» — quest’ultima circostanza riferita al condizionale DALLA FONTE STESSA e da mantenere tale</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 3 e Metodologia — TERZO TIPO DI DEPISTAGGIO, che completa la tipologia. Non preventivo come nell’Italicus, non per informative false diramate dopo il fatto come a Bologna, MA PER COSTRUZIONE DI PISTE FONDATE SU DICHIARAZIONI ATTRIBUITE A INFORMATORI CHE LE HANNO POI NEGATE, veicolate fuori protocollo e fuori gerarchia. E la conclusione che il caso impone: NELL’UNICO EPISODIO GIUNTO A GIUDICATO, L’ORDINAMENTO NON HA SCOPERTO NULLA — GLI E STATO DETTO</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K52" s="8" t="n"/>
+      <c r="L52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>DA PETEANO A GLADIO — il depistaggio del perito del tribunale e la catena che ne discende</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Inchieste del giudice istruttore FELICE CASSON presso il Tribunale di Venezia; condanne definitive; rivelazione di VINCENZO VINCIGUERRA del 1984; ricostruzione su rivista accademica; testimonianza dello stesso Casson resa nel 2024</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>LE VITTIME, CHE VANNO NOMINATE: i carabinieri ANTONIO FERRARO, DONATO POVEROMO e FRANCO DONGIOVANNI, uccisi il 31 maggio 1972 nell’aprire il cofano; due i feriti gravi. Condanne definitive: ERGASTOLO a VINCENZO VINCIGUERRA e CARLO CICUTTINI; da 4 a 6 anni ad altri tre militanti locali; 3 anni e 9 mesi a ENO PASCOLI e 11 mesi a LILIANA DE GIOVANNI</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>IL DEPISTAGGIO ACCERTATO E SANZIONATO, che distingue questo caso da tutti gli altri: l’inchiesta bis di Casson ACCERTO L’ATTIVITA DEPISTATORIA DEGLI INQUIRENTI, e le condanne divennero DEFINITIVE per DINO MINGARELLI — nel frattempo divenuto generale — per il colonnello ANTONINO CHIRICO e per il maresciallo GIUSEPPE NAPOLI. **Livello A**</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>IL PERITO, ED E LA FORMA PIU PURA DEL TERZO TIPO: MARCO MORIN, perito balistico ed esplosivistico del Tribunale di Venezia E MEMBRO DI ORDINE NUOVO, fornì deliberatamente UNA PERIZIA FALSA, sostenendo che l’esplosivo impiegato fosse dello stesso tipo usato dalle Brigate Rosse. Casson dimostro che si trattava invece di C4, in uso alla NATO. MORIN FU RINVIATO A GIUDIZIO E CONDANNATO. UN CONSULENTE TECNICO NOMINATO DAL TRIBUNALE, AFFILIATO ALL’ORGANIZZAZIONE DEGLI ESECUTORI, FALSIFICO LA PERIZIA PER ATTRIBUIRE L’ESPLOSIVO ALLA PARTE OPPOSTA</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>LA CATENA VERSO GLADIO, CON IL SUO PUNTO CONTESO. A pochi chilometri da Peteano era emerso, pochi mesi prima, un NASCO — deposito clandestino di armi — presso AURISINA, che si scopri appartenere a Gladio. Casson sostenne la tesi giudiziaria che l’esplosivo provenisse da quel deposito; TESI NON CONDIVISA DAL GIUDICE ISTRUTTORE GUIDO SALVINI, secondo il quale NON VI ERANO PROVE CERTE di tale provenienza: DUE MAGISTRATI INQUIRENTI IN DISACCORDO, E IL PUNTO VA MANTENUTO CONTESO. Resta accertato che DA QUESTA INCHIESTA PRESE AVVIO QUELLA CHE PORTO ALLA RIVELAZIONE DELLA RETE STAY-BEHIND</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>DUE ELEMENTI ULTERIORI. PRIMO, riferito da Vinciguerra nel 1984 e come tale attribuito: il segretario del MSI GIORGIO ALMIRANTE avrebbe fatto pervenire 35.000 DOLLARI a Cicuttini, latitante in Spagna, per un intervento alle corde vocali che ne alterasse la voce — Cicuttini aveva effettuato la telefonata anonima. ALMIRANTE USUFRUI DELL’AMNISTIA PRIMA DELL’INIZIO DEL PROCESSO. SECONDO, dalla testimonianza di Casson: all’arresto di Mingarelli e Chirico «si scateno l’inferno», e «DAL GIORNO SUCCESSIVO, SENZA DIRMI NULLA, SCOMPARVERO I CARABINIERI DELLA SCORTA che quotidianamente mi accompagnavano in ufficio». **Livello B**, testimonianza personale</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 3, 9 e 10 — CHIUDE LA TIPOLOGIA DEL DEPISTAGGIO E APRE LA CATENA. Peteano non e soltanto il caso in cui la verita emerse per confessione: E IL CASO IN CUI IL DEPISTAGGIO FU ACCERTATO E PUNITO IN VIA DEFINITIVA A CARICO DI TRE UFFICIALI E SOTTUFFICIALI DELL’ARMA E DI UN PERITO DEL TRIBUNALE. Ed e il caso da cui, per via giudiziaria e non politica, emerse l’esistenza della rete clandestina</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="J53" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="n"/>
+      <c r="L53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>IL NASCO DI AURISINA — ritrovamento, occultamento e distruzione dei reperti, con accertamento parlamentare</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>PRIMO RAPPORTO DEL COMITATO PARLAMENTARE, 6 APRILE 1995, consultabile in linea; relazione della Commissione stragi; cronaca coeva del 25-26 febbraio e dell’11 marzo 1972; ordinanze del giudice istruttore CARLO MASTELLONI del 30 OTTOBRE, 2 e 6 NOVEMBRE 1990</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>IL RITROVAMENTO. Il 24 FEBBRAIO 1972 il deposito denominato NASCO 203, occultato fra il 1963 e il 1970 in un bunker della Grande Guerra sul Carso triestino, FU SCOPERTO PER CASO DA DUE RAGAZZI QUATTORDICENNI che raccoglievano cimeli militari, hobby allora diffuso fra i giovani della zona. Il 3 MARZO i carabinieri della tenenza di Aurisina, perlustrando, ne rinvennero un secondo a circa mezzo chilometro. L’anfratto distava UN CENTINAIO DI METRI DALLA CASERMA DEI CARABINIERI e pochi chilometri dal confine</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>L’INVENTARIO, secondo l’elenco fornito dai carabinieri per il secondo ritrovamento: 2 pistole Star, 6 bombe a frattura prestabilita, 2 bombe al fosforo, un binocolo, 100 cartucce, 2 fondine da spalla, 6 torce e ISTRUZIONI PER CIASCUN OGGETTO. La stampa coeva riferi, per il complesso dei rinvenimenti, 5 grosse cariche di dinamite, 15 chili di plastico, 200 metri di miccia, 90 matite esplosive, decine di detonatori e DUE BOMBE A TEMPO UGUALI A QUELLE USATE PER GLI ATTENTATI ALLA FIERA DI MILANO E SUI TRENI — quest’ultimo dato di fonte giornalistica, DA RISCONTRARE</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>L’ACCERTAMENTO PARLAMENTARE, CHE E LA PARTE DECISIVA E VA CITATA TESTUALMENTE: «Il materiale rinvenuto apparteneva SICURAMENTE alla struttura Gladio. E CERTO CHE IL SID, in relazione a questo ritrovamento, INVIO I PROPRI EMISSARI A TRIESTE E AD AURISINA, sia presso il proprio Centro CS sia presso i locali Comandi dei carabinieri. OCCORREVA IMMEDIATAMENTE INTERVENIRE PER OCCULTARE LE FINALITA DEL DEPOSITO di armi e di esplosivi, ma anche perche NON VENISSERO EFFETTUATI CONTROLLI SULLA QUANTITA E SULLE CARATTERISTICHE DEI MATERIALI». E sulla distruzione: «L’ESPLOSIVO FU FATTO BRILLARE PERCHE, SI DISSE, ERA INSTABILE. MA QUEL PARTICOLARE TIPO DI ESPLOSIVO ERA TUTTO FUORCHE INSTABILE. QUEL CHE INTERESSAVA ERA DISTRUGGERE TUTTI GLI ELEMENTI CHE POTESSERO CONDURRE AL SID». **Livello A**</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>LE DUE PENDENZE CHE SI CHIUDONO. PRIMA: lo smantellamento della rete dei depositi FU DECISO PROPRIO IN CONSEGUENZA DI QUESTO RINVENIMENTO FORTUITO, e le operazioni di recupero cominciarono NELL’APRILE 1972. SECONDA: i 12 depositi mai recuperati furono oggetto delle ORDINANZE DEL GIUDICE ISTRUTTORE DI VENEZIA DEL 30 OTTOBRE, 2 E 6 NOVEMBRE 1990, emesse NELL’AMBITO DELL’INCHIESTA SULLA CADUTA DELL’AEREO ARGO 16, con incarico ai Comandi dei carabinieri di ricercarli e dissotterrarli. Fra i motivi del mancato recupero figura, per un deposito friulano, che il pronao della chiesetta sotto il quale era collocato ERA STATO PAVIMENTATO NEL 1972</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CRONOLOGICO, DA RIPORTARE COME TALE E NON COME NESSO: il deposito fu scoperto il 24 FEBBRAIO 1972, lo smantellamento della rete inizio NELL’APRILE 1972, L’ATTENTATO DI PETEANO AVVENNE IL 31 MAGGIO 1972 — a pochi chilometri, e DURANTE L’OPERAZIONE DI RECUPERO. Se l’esplosivo provenisse da quel deposito e questione contesa fra due magistrati inquirenti e NON VA RISOLTA QUI. VA INOLTRE REGISTRATA, A LIVELLO C E COME CONTESTATA, la versione riferita nel 1991 secondo cui il ritrovamento sarebbe opera di un brigadiere di pubblica sicurezza poi internato e morto nel 1975: e affermazione di fonte indiretta, incompatibile con la versione ufficiale, e non riscontrata</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 3 e 9 — E IL SECONDO CASO, DOPO MONACO, IN CUI LA DISTRUZIONE DEI REPERTI E ACCERTATA E MOTIVATA. A Monaco 504 reperti furono distrutti «per mancanza di spazio»; ad Aurisina l’esplosivo fu fatto brillare «perche instabile». IN ENTRAMBI I CASI LA GIUSTIFICAZIONE E STATA SMENTITA DA UN ORGANO DELLO STATO, e in questo caso l’organo dichiara anche il fine</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K54" s="8" t="n"/>
+      <c r="L54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>VERIFICA DEL VOLUME ZERO, PARTE VII — misura quantitativa e sette errori accertati</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Esame diretto del file VOLUME_ZERO_V59_PARTE_VII_NATO_GLADIO presente nei file di progetto, datato maggio 2026; confronto con le fonti verificate nel presente repertorio</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>LA MISURA. Il testo consta di 6.159 PAROLE. Vi ricorrono 214 volte le forme «articola» e «articolato» — UNA OGNI 29 PAROLE — 107 volte «dispositivo», 111 volte «apparato», 68 volte «strutturale», 32 volte «di rilevanza primaria» e altrettante «di rilevanza assoluta», e 45 VOLTE LA PAROLA INGLESE «FOUNDATIONAL» IN UN TESTO ITALIANO. Le frasi sono 108, di lunghezza media 55 parole e massima 293; VENTISETTE DI ESSE COMINCIANO CON UNA DELLE MEDESIME QUATTRO FORMULE</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>IL DATO CHE DECIDE, ED E UN RAPPORTO. I gradi probatori assegnati sono: 56 VOLTE «SAVONA A», 3 VOLTE «SAVONA B», ZERO VOLTE «SAVONA C». In un sistema nel quale il grado A richiede la convergenza di tre fonti indipendenti di natura diversa, UNA DISTRIBUZIONE DEL 95 PER CENTO SUL GRADO MASSIMO NON E UNA GRADUAZIONE: E UN ORNAMENTO. Una valutazione effettiva di questo materiale produrrebbe necessariamente una dispersione</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>GLI ERRORI ACCERTATI PER CONFRONTO CON QUESTO REPERTORIO. PRIMO E PIU GRAVE: il deposito di Aurisina e dato «localizzato il 24 GENNAIO 1992» e marcato «Savona A integrale», MENTRE IL RITROVAMENTO AVVENNE IL 24 FEBBRAIO 1972 — venti anni e un mese di scarto, SU UNA RIGA CHE PORTA IL GRADO PROBATORIO MASSIMO. SECONDO: l’accesso agli archivi del servizio militare e collocato a FORTE BOCCEA anziche a Forte Braschi, rettifica gia pendente e non applicata. TERZO: i 3.000 uomini sono dati per fatto, mentre la cifra proviene da appunto privo di data ed e stata contestata sotto giuramento</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>QUARTO: e citato come atto il documento «NSC 6014/1 del 19 aprile 1961», NON REPERIBILE nella verifica condotta. QUINTO: il manuale FM 30-31B e dato per autentico, «firmato dal generale W.» e fonte di una «dottrina di Westmoreland delle operazioni false», MENTRE IL DOCUMENTO E DI STATUTO CONTESO E L’ATTRIBUZIONE A QUEL GENERALE E LA MEDESIMA CHE, IN ALTRA FONTE VERIFICATA OGGI, RISULTA CRONOLOGICAMENTE IMPLAUSIBILE. SESTO: i 731 enucleandi sono dati per fatto, mentre la relazione di minoranza indica non meno di 1.100-1.200. SETTIMO: l’accordo del 1956 e datato al 26 novembre senza segnalare che il documento consegnato al Parlamento reca il 28</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>LA CONCLUSIONE, CHE E OPERATIVA E NON STILISTICA. Il piano dell’opera prevedeva due sole opzioni: riverificare riga per riga, oppure dichiarare il materiale preparatorio non pubblicabile. LA MISURA SCEGLIE: in 6.159 parole le asserzioni fattuali distinte sono nell’ordine della quindicina, IL RESTO E TESSUTO CONNETTIVO GENERATO. Non vi e nulla da verificare riga per riga, perche le righe in massima parte NON CONTENGONO AFFERMAZIONI. Le quindici asserzioni sono gia contenute, verificate e datate in questo repertorio; SETTE DI ESSE VI RISULTANO ERRATE</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n"/>
+      <c r="J55" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="n"/>
+      <c r="L55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ESTENSIONE DELLA DIAGNOSTICA AI REGISTRI MAGGIORI — quanto e affetto e quanto no</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Misurazione diretta sui file di uscita del progetto: quattro registri federati e unificati fra 1,7 e 2,1 milioni di parole; tredici versioni del registro analitico sul caso Moro; medesimi indicatori applicati al Volume Zero</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>IL PRIMO RISULTATO, CHE ESTENDE IL PROBLEMA. I quattro registri maggiori recano ciascuno ESATTAMENTE 299 OCCORRENZE DELLA PAROLA INGLESE «FOUNDATIONAL» — cifra identica al totale delle sette parti del Volume Zero. NE SEGUE CHE IL VOLUME ZERO E INCORPORATO ALLA LETTERA IN CIASCUNO DI ESSI. E la distribuzione dei gradi vi si riproduce su scala venti volte maggiore: nelle due versioni piu recenti 4.968 assegnazioni di livello A, 340 di livello B, 25 di livello C — IL 93 PER CENTO SUL GRADO MASSIMO, IDENTICO AL VALORE MISURATO SUL VOLUME ZERO</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>IL SECONDO RISULTATO, CHE E UNA BUONA NOTIZIA E VA DETTA CON LA STESSA PRECISIONE. LE TREDICI VERSIONI DEL REGISTRO ANALITICO SUL CASO MORO NON RECANO ALCUNA DELLE TRE FIRME: zero occorrenze di «foundational», densita nulla delle forme «articolato», E NESSUN GRADO SAVONA ASSEGNATO — ne A, ne B, ne C. Il corpus sul caso Moro, che costituisce la parte piu estesa dell’opera scritta, E INDENNE DALLA PATOLOGIA e non eredita alcun grado non verificato</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>IL TERZO RISULTATO, CHE RIGUARDA IL VERSIONAMENTO. Le versioni 69 e 70 recano CONTEGGI DI GRADO IDENTICI — 4.968, 340 e 25 — pur differendo di oltre centomila parole. Le versioni 67 e 68 recano parimenti conteggi identici pur differendo di quattromila parole. NE SEGUE CHE IL MATERIALE AGGIUNTO A OGNI NUOVA VERSIONE NON PORTA ALCUNA VALUTAZIONE PROBATORIA: i registri crescono senza che cresca il numero delle affermazioni graduate</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>LA DELIMITAZIONE, CHE E IL PUNTO DI QUESTA VOCE. La patologia NON riguarda l’intero corpus: riguarda IL VOLUME ZERO E I QUATTRO REGISTRI CHE LO INCORPORANO. Ne restano fuori il corpus sul caso Moro, il repertorio delle fonti, i capitoli dimostrativi e l’apparato metodologico, che sono stati costruiti interrogando documenti e recano graduazione dichiarata caso per caso</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — CONSEGUENZA OPERATIVA. La dichiarazione sullo statuto del Volume Zero VA ESTESA ALLE PORZIONI DEI QUATTRO REGISTRI CHE LO INCORPORANO, identificabili con precisione perche recano la firma lessicale. Non va estesa al resto, e SOSTENERE CHE L’INTERO CORPUS SIA COMPROMESSO SAREBBE, ESSO STESSO, UNA GENERALIZZAZIONE NON MISURATA</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="n"/>
+      <c r="L56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RETTIFICA ALLA DELIMITAZIONE — la firma lessicale e confinata, la graduazione probatoria no</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Misurazione per segmentazione del registro unificato piu recente, 2.081.170 parole: separazione della regione contenente la firma lessicale dal resto e conteggio separato dei gradi</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>LA RETTIFICA, DOVUTA E IMMEDIATA. Due voci addietro questo repertorio ha affermato che la patologia riguarda «il Volume Zero e i quattro registri che lo incorporano», e che le porzioni affette sono identificabili perche recano la firma lessicale. LA PRIMA META E ESATTA, LA SECONDA E FALSA, E LA MISURA LO DIMOSTRA</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>LA LOCALIZZAZIONE DELLA FIRMA LESSICALE, CHE E CONFERMATA: tutte e 299 le occorrenze di «foundational» cadono nel medesimo decile, fra il 66 e il 68 per cento del documento; la regione misura 424.135 caratteri, pari al 2 PER CENTO del registro e a 49.387 parole — cioe esattamente il Volume Zero, incorporato come blocco contiguo. IL TESTO GENERATO E DUNQUE CHIRURGICAMENTE ISOLABILE</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>MA LA GRADUAZIONE E IDENTICA DENTRO E FUORI, ED E IL DATO CHE ROVESCIA LA CONCLUSIONE PRECEDENTE. Nella regione del Volume Zero: 360 assegnazioni di livello A, 25 di livello B, ZERO di livello C — 93 per cento sul grado massimo. NEL RESTANTE 98 PER CENTO DEL REGISTRO, due milioni e trentunomila parole: 4.608 assegnazioni di livello A, 315 di livello B, 25 di livello C — 93 PER CENTO SUL GRADO MASSIMO. LE DUE DISTRIBUZIONI COINCIDONO FINO AL PUNTO PERCENTUALE</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>LA CONSEGUENZA ARITMETICA: rimuovendo integralmente il Volume Zero si eliminano 360 assegnazioni di livello A SU 4.968, PARI AL 7 PER CENTO. NE RESTANO 4.608 IN MATERIALE PRIVO DELLA FIRMA LESSICALE. La dichiarazione sullo statuto del Volume Zero, adottata oggi, RISOLVE DUNQUE IL SETTE PER CENTO DEL PROBLEMA DI GRADUAZIONE, e non la sua totalita</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>LA DISTINZIONE CHE VA MANTENUTA, E CHE IMPEDISCE UNA CONCLUSIONE CATASTROFICA. Cio che la misura accerta riguarda LA GRADUAZIONE, NON IL CONTENUTO. Due milioni di parole possono contenere materiale eccellente e affermazioni vere: cio che non e credibile e IL GRADO CHE VI E STATO APPOSTO. Un livello A che ricorre nel 93 per cento dei casi non certifica nulla, e la sua rimozione NON TOGLIE UNA SOLA AFFERMAZIONE — toglie soltanto una garanzia che non era stata prestata</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — CONSEGUENZA OPERATIVA, PIU AMPIA DI QUELLA DICHIARATA STAMANE: nessun grado Savona presente nel Registro Unico Federato, IN ALCUNA DELLE SUE PORZIONI, puo essere ereditato senza riverifica. Le 4.968 assegnazioni vanno considerate NON APPOSTE finche non siano riprodotte una per una. Il repertorio delle fonti, che gradua caso per caso e dichiara il criterio, RESTA LA SOLA SEDE DELL’OPERA IN CUI UN GRADO SIGNIFICHI QUALCOSA</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K57" s="8" t="n"/>
+      <c r="L57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Il caso del 9 marzo 1973 — attribuzione a ufficiali della Divisione Pastrengo, e il suo grado</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Proposta di relazione della Commissione stragi, 22 giugno 2000, paragrafo IV.7, pagine 209-210; dichiarazioni rese nel 1987 al sostituto procuratore della Repubblica di Milano MARIA LUISA DAMENO; interrogatorio di BIAGIO PITARRESI al giudice istruttore GUIDO SALVINI del 9 MAGGIO 1995</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>IL FATTO. Il 9 MARZO 1973, in via Nirone a Milano, FRANCA RAME — allora impegnata con il marito nell’attivita di Soccorso Rosso in favore dei detenuti — fu aggredita da sconosciuti, costretta a salire su un furgone e sottoposta a violenza sessuale. La Commissione lo definisce «UNO STUPRO POLITICO» e afferma che l’episodio «DEVE ESSERE CONSIDERATO PARTE INTEGRANTE DELLA STRATEGIA DELLA TENSIONE». La vittima ha reso pubblica la vicenda e ne ha fatto materia del proprio lavoro</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>LE DUE FONTI DICHIARATIVE. Nel 1987 ANGELO IZZO riferi al pubblico ministero di avere APPRESO IN CARCERE che il principale responsabile fosse ANGELO ANGELI e che l’azione fosse stata «SUGGERITA DA ALCUNI UFFICIALI DEI CARABINIERI DELLA DIVISIONE PASTRENGO, nel quadro del sostanziale atteggiamento di COBELLIGERANZA esistente all’epoca fra alcuni settori di tale Divisione e gli estremisti di destra». Nel 1995 BIAGIO PITARRESI dichiaro al giudice istruttore che l’azione ERA STATA DAPPRIMA PROPOSTA A LUI, che egli si era rifiutato e che era subentrato Angeli; e confermo che essa fu ISPIRATA DA CARABINIERI DELLA MEDESIMA DIVISIONE, con la quale entrambi erano in contatto «IN FUNZIONE SIA INFORMATIVA SIA DI SUPPORTO IN ATTIVITA DI PROVOCAZIONE CONTRO GLI AMBIENTI DI SINISTRA»</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>IL GRADO, DA DICHIARARE OGNI VOLTA. Il fatto materiale e certo. L’ATTRIBUZIONE AGLI UFFICIALI POGGIA SU DUE SOLE DICHIARAZIONI, provenienti dal medesimo ambiente, delle quali LA PRIMA E DE RELATO — l’interessato riferisce cio che dice di avere appreso in carcere. Il testo parlamentare NON RIPORTA ALCUN ACCERTAMENTO GIUDIZIARIO su quel punto, e l’esito processuale della vicenda VA VERIFICATO SEPARATAMENTE. **Livello B** quanto all’esistenza delle dichiarazioni, **Livello C** quanto al contenuto attribuito agli ufficiali</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>LA CONVERGENZA DI ATTI, DA REGISTRARE COME TALE E NON COME NESSO: la Divisione Pastrengo e il medesimo comando il cui generale, quattordici mesi prima, aveva trasmesso FUORI PROTOCOLLO E FUORI GERARCHIA la velina che origino la falsa pista sull’attentato di Peteano. LE DUE CIRCOSTANZE PROVENGONO DA ATTI DISTINTI E NON SONO STATE COLLEGATE DA ALCUNA SEDE: il registro le accosta perche riguardano il medesimo comando, e VIETA DI TRARNE INFERENZA</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Dominio 9 e Dominio 7 — ESTENDE L’OGGETTO. La forma finora registrata riguardava attentati e coperture; questo caso introduce LA VIOLENZA MIRATA CONTRO UNA PERSONA DETERMINATA come strumento della medesima strategia, e con la stessa attribuzione a settori di un comando militare. La parola usata dalle fonti — COBELLIGERANZA — e piu forte di «arco di sponda» e va confrontata con essa</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="n"/>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K58" s="8" t="n"/>
+      <c r="L58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>DIAGNOSTICA DELLE MONOGRAFIE — terza condizione documentale, e una duplicazione da sanare</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Misurazione diretta su dodici monografie presenti nei file di progetto: serie sulla diaspora, serie sull’apartheid, monografia sulle reti europee riservate, monografia sulle reti russe</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>L’ESITO PRIMARIO, CHE E UNA BUONA NOTIZIA: NESSUNA MONOGRAFIA RECA LA FIRMA GENERATIVA. Zero occorrenze del termine inglese, densita nulla delle formule «si articola» e «articolato», nessuna delle strutture ripetitive rilevate nel Volume Zero. Sono testi scritti, non generati</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>MA NESSUNA RECA ALCUNA VALUTAZIONE PROBATORIA: zero gradi di livello A, B o C su circa novantasettemila parole complessive. Non e la patologia del Volume Zero, che apponeva un grado falso; e la condizione opposta, L’ASSENZA DI GRADUAZIONE. Ne discende una terza condizione documentale, da tenere distinta dalle altre due: il Volume Zero era prosa generata con graduazione fittizia; il repertorio e materiale interrogato con graduazione dichiarata per singola affermazione; LE MONOGRAFIE SONO MATERIALE DOCUMENTATO MA NON GRADUATO</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>LA DENSITA DOCUMENTARIA, MISURATA IN RIFERIMENTI PER MILLE PAROLE, VARIA DI UN FATTORE DIECI. Il valore piu alto e 20, in una monografia di 9.426 parole che reca 188 indirizzi di fonte; seguono valori di 14, 10, 9, 8 e 7. Il valore piu basso e 2, in un testo di 5.022 parole che ne reca due soli. LA SOGLIA CONTA: un testo con venti riferimenti per mille parole e un documento di ricerca, uno con due e una narrazione. VA STABILITA UNA SOGLIA MINIMA E DICHIARATA</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>LA DUPLICAZIONE, DA SANARE: almeno sei monografie compaiono due volte nei file di progetto, in coppie identiche distinte dal solo suffisso numerico. Circa quarantamila parole del corpus sono dunque copia di altre quarantamila. La duplicazione non e un errore di contenuto ma FALSA OGNI MISURA DI CONSISTENZA CHE NON LA RILEVI, ed e la stessa famiglia di errore del contatore mai ispezionato</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>L’OSSERVAZIONE STRUTTURALE CHE NE DISCENDE, E VALE PER L’ARCHITETTURA: le monografie portano le fonti nel testo e non portano i gradi; i capitoli di fondazione portano i gradi nel testo e le fonti nel repertorio. SONO DUE ARCHITETTURE LEGITTIME E INCOMPATIBILI, e l’opera deve sceglierne una. La seconda e preferibile perche consente di aggiornare una fonte senza toccare il capitolo, e di verificare un grado senza rileggere il testo</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — DISPOSIZIONE: le monografie NON vanno espunte ne sospese. Vanno GRADUATE, affermazione per affermazione, al momento in cui se ne attinge; e le coppie duplicate vanno ridotte a un solo esemplare prima di qualsiasi conteggio di consistenza</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="n"/>
+      <c r="L59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>I due piani per Francia e Italia — PATERNITA, SIGLE E DATE ACCERTATE SU FONTE PRIMARIA</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Documento PSB D-30, «Planning activities of the Psychological Strategy Board through 30 June 1952», datato 1 AGOSTO 1952, desecretato e pubblicato nella raccolta digitale dell’agenzia informativa statunitense, numero CIA-RDP80-01065A000500070012-3, rilasciato l’8 LUGLIO 2002; carte del Psychological Strategy Board presso la biblioteca presidenziale Truman, scatole 5 e 7</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>LA PATERNITA, CHE ERA CONTESA ED E ORA STABILITA: i due piani FURONO SVILUPPATI DALLO PSYCHOLOGICAL STRATEGY BOARD, organo istituito il 4 APRILE 1951 e composto dal sottosegretario di Stato, dal vice segretario alla Difesa e dal direttore dell’intelligence centrale o loro rappresentanti. NON DAL COMITATO DEI CAPI DI STATO MAGGIORE. Il documento primario afferma che il piano per la Francia «e quello corrispondente per l’Italia FURONO SVILUPPATI DAL MEDESIMO GRUPPO DI PIANIFICAZIONE DEL BOARD, e le azioni previste da entrambi sono coordinate dal medesimo gruppo». **Livello A**</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>LE SIGLE E LE DATE. Il piano per la Francia e PSB D-14, nome in codice CLOVEN, nella versione migliore del 12 DICEMBRE 1951; quello per l’Italia e PSB D-15, nome in codice DEMAGNETIZE, poi mutato in CLYDESDALE. ENTRAMBI FURONO APPROVATI IL 21 FEBBRAIO 1952. Su approvazione fu istituito a Washington un comitato interdipartimentale di coordinamento presieduto da un membro dello staff del Board, CON PANNELLI CORRISPONDENTI A PARIGI E A ROMA, in comunicazione fra loro per l’attuazione</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>LA MOTIVAZIONE DICHIARATA, TESTUALE: i piani «RISULTARONO DA UN’ESTESA INDAGINE CONDOTTA NELL’ESTATE E NELL’AUTUNNO DEL 1951, all’esito della quale il Board concluse che gli apparati comunisti francese e italiano, I DUE PIU POTENTI DELL’EUROPA OCCIDENTALE, COSTITUIVANO UNA SERIA MINACCIA PER LA POLITICA ESTERA AMERICANA E PER I PIANI DELLA NATO PER LA DIFESA DELL’EUROPA OCCIDENTALE». E l’analisi condusse alla conclusione che in entrambi i paesi «LA FONTE PRIMARIA DEL POTERE COMUNISTA RISIEDEVA NEL LORO CONTROLLO ORGANIZZATO SUI SINDACATI»</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>LA RETTIFICA AL PRIMO CAPITOLO DIMOSTRATIVO: esso reca «memo 14 maggio 1952» come data del piano. LA DATA DI APPROVAZIONE E IL 21 FEBBRAIO 1952, e le date di stesura sono il 12 dicembre 1951 per la Francia e il febbraio 1951 per l’Italia secondo la scheda d’archivio. Il 14 maggio 1952 NON TROVA RISCONTRO in questa documentazione e va soppresso o attribuito ad altro atto</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — E IL PRIMO CASO IN CUI UNA PENDENZA DI ATTRIBUZIONE SI CHIUDE SU DOCUMENTO PRIMARIO DESECRETATO anziche su fonte secondaria. Il documento e liberamente consultabile e reca numero di rilascio: chiunque puo ripetere la verifica</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="n"/>
+      <c r="L60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>FM 30-31B — LO STATUTO CONTESO SI RISOLVE, E CON ESSO UNA MIA CONFUSIONE</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Audizioni della Commissione permanente d’intelligence della Camera statunitense, 96 Congresso, seconda sessione, 6 e 19 FEBBRAIO 1980; determinazione della medesima Commissione del 1979; conclusione del servizio informativo danese del 1976; dichiarazione del Dipartimento di Stato del 20 GENNAIO 2006, sotto il segretario CONDOLEEZZA RICE; relazione della commissione parlamentare belga; documentario televisivo britannico del 24 GIUGNO 1992</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>L’ARGOMENTO STRUTTURALE, CHE E IL PIU FORTE E NON DIPENDE DA ALCUNA DICHIARAZIONE: IL MANUALE FM 30-31, DATATO 8 GENNAIO 1970 E REGOLARMENTE PUBBLICATO, RECA UN SOLO SUPPLEMENTO, IL SUPPLEMENTO A. Non esiste traccia di un supplemento B classificato negli archivi e nei cataloghi dottrinali dell’esercito, e il documento non figura fra i manuali di campo pubblicati. La sigla stessa presuppone un atto la cui esistenza non e attestata</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>GLI ALTRI ELEMENTI CONTRARI, IN ORDINE CRONOLOGICO E PRECEDENTI ALLA CONTROVERSIA ITALIANA: nel 1976 il servizio informativo per la difesa danese concluse che si trattava di falso inserito in una campagna di disinformazione sovietica; nel 1979 la Commissione d’intelligence della Camera statunitense lo determino falso; nelle audizioni del febbraio 1980 funzionari dell’agenzia informativa lo qualificarono «falso singolarmente efficace» del servizio sovietico, e JOHN McMAHON, funzionario dell’agenzia, dichiaro in audizione che il documento «aveva qualche difetto ma era un lavoro molto professionale E RECAVA LA FIRMA FALSIFICATA DEL GENERALE WESTMORELAND». Un transfuga del servizio sovietico — DI CUI LE FONTI CONSULTATE NON RIPORTANO IL NOME, e va accertato — depose in Congresso nel medesimo senso. Il documento COMPARVE PER LA PRIMA VOLTA IN TURCHIA negli anni Settanta</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>GLI ELEMENTI CONTRARI ALLA TESI DEL FALSO, DA CONSERVARE: nel LUGLIO 1981 MARIAGRAZIA GELLI, figlia di Licio Gelli, fu fermata a Roma con una valigia contenente, fra altri documenti, UNA COPIA DEL MANUALE; e Licio Gelli dichiaro ad ALLAN FRANCOVICH, nel documentario televisivo britannico del 1992, che gliel’aveva dato «un amico molto stretto della CIA». RAY S. CLINE, vicedirettore dell’agenzia dal 1962 al 1966, interrogato da Francovich, rispose: «SOSPETTO CHE SIA UN DOCUMENTO AUTENTICO. NON NE DUBITO. NON L’HO MAI VISTO, ma e il genere di operazioni delle forze speciali che vi sono descritte» — E L’INCISO «NON L’HO MAI VISTO» NE DELIMITA IL VALORE. La commissione parlamentare belga si astenne: «la commissione non ha alcuna certezza sull’autenticita del documento»</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>IL GIUDIZIO CHE QUEST’OPERA ADOTTA: LA TESI DEL FALSO E DI GRAN LUNGA PIU SOSTENUTA, per l’argomento strutturale del supplemento inesistente e per la convergenza di tre accertamenti indipendenti anteriori alla controversia italiana; concordano gli studiosi PEER HENRIK HANSEN e THOMAS RID, mentre WILLIAM SCHAAP sostenne nel 1979 che il ritardo della smentita statunitense ne indebolisse la tesi. IL DOCUMENTO NON PUO SORREGGERE ALCUNA AFFERMAZIONE SULLA DOTTRINA STATUNITENSE. Cio che resta accertato, e va tenuto distinto, e IL FATTO DELLA SUA CIRCOLAZIONE: che una copia fosse nella disponibilita di Licio Gelli nel 1981 e un fatto, quale che ne sia l’origine</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>LA MIA CONFUSIONE, DA CORREGGERE. In altra voce di questo repertorio ho segnalato come cronologicamente implausibile l’attribuzione a Westmoreland di una direttiva del 1963. QUEL RILIEVO RESTA VALIDO — nel 1963 egli dirigeva l’accademia militare — MA NON SI ESTENDE AL MANUALE DEL 1970, quando egli era capo di stato maggiore dell’esercito e una sua firma sarebbe stata cronologicamente possibile. SONO DUE PROBLEMI DISTINTI: il primo e di impossibilita cronologica, il secondo di falsificazione della firma</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia — LO STATUTO PASSA DA CONTESO A FALSO CON MINORANZA DICHIARATA. La minoranza va sempre riportata, perche una tesi che sopprima le proprie obiezioni non e piu forte: e soltanto meno verificabile</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>verificato 5.8.2026</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>da riverificare</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="n"/>
+      <c r="L61" s="8" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13544,7 +14170,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14040,7 +14666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17910,7 +18536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18187,7 +18813,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19668,551 +20294,4 @@
   <autoFilter ref="A1:I31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Ente</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Strumento</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Sede e accesso</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Procedura</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Contenuto utile</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Sezione servita</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Verifica indipendente</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>Data verifica indipendente</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>Sede consultata / esito</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>CIA</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>CREST — CIA Records Search Tool</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>In rete, nella FOIA Electronic Reading Room dell’Agenzia</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Consultazione libera; ricerca a testo pieno dal 2000; possibile la ricerca per raccolta, per categoria e per parola chiave. Avvertenza dell’Agenzia stessa: alcuni documenti non appartengono ad alcuna raccolta e sfuggono alle ricerche limitate per raccolta</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Sottoinsieme dei documenti dell’Agenzia riesaminati nel programma 25nnale, in formato elettronico. I documenti riesaminati manualmente confluiscono direttamente negli archivi nazionali nel formato originale</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II cap. III cond. 4 — l’asse americano</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO ALLA LETTERA — e manca la storia dell'apertura</t>
-        </is>
-      </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J2" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATE ESATTAMENTE LE 2 AFFERMAZIONI PORTANTI DELLA VOCE. Prima: il sistema e il deposito pubblicamente accessibile del SOTTOINSIEME dei documenti riesaminati nel programma venticinquennale in formato elettronico, mentre i documenti riesaminati manualmente confluiscono direttamente negli Archivi nazionali nel formato originale. Seconda: l'avvertenza dell'Agenzia, che la voce riporta correttamente, e che 'alcuni documenti non appartengono ad alcuna raccolta e possono sfuggire se si limita la ricerca a una o piu raccolte'. Confermata la ricerca a testo pieno dal 2000; il sistema e installato presso NARA II a College Park, Maryland. SCALA OMESSA: oltre 11 MILIONI DI PAGINE sono state rilasciate in formato elettronico e risiedono nella banca dati, dalle quali i ricercatori ne hanno stampate circa 1,1 milioni. STORIA DELL'APERTURA, OMESSA E RILEVANTISSIMA PER L'OPERA: prima della causa promossa da MuckRock il sistema era tecnicamente accessibile MA SOLTANTO DAL LUNEDI AL VENERDI, DALLE 9 ALLE 16 E 30, PRESSO LA SEDE DEGLI ARCHIVI NAZIONALI NEL MARYLAND. La messa in rete e il risultato di un contenzioso, non di una decisione amministrativa spontanea: e un caso documentato di apertura archivistica ottenuta per via giudiziaria, e va registrato accanto agli altri. DIFETTO DI NUMERAZIONE: la voce scrive 'programma 25nnale'; si legge VENTICINQUENNALE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Esecutivo statunitense</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Ordine esecutivo 13526, già 12958 come modificato</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Prescrive la desecretazione automatica dei documenti non esentati di valore storico con più di 25 anni</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>È la norma che rende programmata, e non discrezionale, la desecretazione: fissa il termine oltre il quale un documento va rilasciato salvo eccezione motivata</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia — il segreto come processo che costa</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — manca il meccanismo che rende la norma un processo</t>
-        </is>
-      </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
-          <t>Confermato: l'ordine esecutivo 13526, gia 12958 come modificato, impone la desecretazione dei documenti non esentati di valore storico con 25 anni o piu. L'ordine fu emanato originariamente NELL'APRILE 1995 e, per effetto di modifica, fisso il 31 DICEMBRE 2006 come primo termine maggiore del programma venticinquennale; per l'Agenzia quel termine copriva i documenti dalla fondazione del servizio dopo la seconda guerra mondiale fino al 1981. MECCANISMO OMESSO, ED E IL PUNTO: l'obbligo SCORRE IN AVANTI DI UN ANNO ALLA VOLTA. Al 31 dicembre 2012 erano automaticamente desecretati i documenti permanenti fino al 31 dicembre 1987, salvo esenzione motivata. La voce coglie giustamente che la norma rende la desecretazione programmata e non discrezionale, ma non dice come: e lo scorrimento annuale a farne un processo continuo anziche una scadenza unica. Il servizio mantiene un centro di desecretazione che riesamina i documenti PRIMA che raggiungano il termine automatico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>National Security Archive, George Washington University</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Digital National Security Archive; Electronic Briefing Books</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>In rete; istituto non governativo fondato nel 1985</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Consultazione; sezione «Documents» ricercabile; guida alla presentazione di istanze di accesso</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Oltre 100.000 documenti desecretati su decisioni di politica estera statunitense, con cronologie, bibliografie e saggi introduttivi</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Tomo II capp. III-IV</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — e contiene la dimostrazione empirica piu utile che il corpus possa citare</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>Confermata la fondazione NEL 1985 da parte di giornalisti e studiosi per contrastare la crescente segretezza governativa; istituto di ricerca e biblioteca indipendente e non governativo presso la George Washington University, dal 1995 ospitato nella Gelman Library. Fondatore: Scott ARMSTRONG, gia cronista del Washington Post e collaboratore della commissione senatoriale sul Watergate; direttore: Tom BLANTON. PRECISAZIONE SULLA CIFRA: la voce indica 'oltre 100.000 documenti'. La banca dati dei documenti rilasciati dell'istituto reca oltre 100.000 record; il Digital National Security Archive, prodotto in collaborazione con ProQuest, ne reca OLTRE 150.000. La voce cita entrambi gli strumenti come uno solo: vanno distinti, perche il secondo E SU ABBONAMENTO mentre gli Electronic Briefing Books sono liberi. MISURE OMESSE: in 4 decenni l'istituto ha determinato la desecretazione di OLTRE 15 MILIONI DI PAGINE, presentando piu di 70.000 istanze e promuovendo oltre 50 CAUSE; le collezioni accessionate superano i 2 milioni di pagine in oltre 200 raccolte. Premio George Polk speciale nel 1999 per aver 'perforato i veli interessati della segretezza governativa'. DATO DI INDIPENDENZA, da registrare secondo il criterio gia applicato alle fonti finanziate: l'istituto NON RICEVE FINANZIAMENTI DAL GOVERNO STATUNITENSE e si sostiene con diritti d'autore e donazioni di fondazioni e privati. REPERTO METODOLOGICO DI PRIMO ORDINE, DA CITARE NELLA NOTA: l'istituto espone 2 versioni del medesimo scambio di messaggi del 1987 fra un ex segretario esecutivo del Consiglio di sicurezza nazionale e l'allora vice consigliere per la sicurezza nazionale: una dalla casella in arrivo, una da quella in uscita, ESAMINATE A 10 GIORNI DI DISTANZA DAL MEDESIMO REVISORE in risposta a una causa dell'istituto. LE DUE VERSIONI RECANO OMISSIS DIVERSI. E la dimostrazione empirica, su un caso unico e controllato, che l'espunzione non e una funzione del contenuto ma del revisore: 'la soggettivita di gran parte della segretezza di sicurezza nazionale e una delle ragioni per cui esistiamo'. COLLEGAMENTO CON IL FOGLIO 07: l'istituto ha presentato la documentazione desecretata nel processo argentino sull'operazione continentale, per il tramite del direttore del proprio progetto sul Cono Sud, Carlos OSORIO; e ha pubblicato raccolte su Cile, Guatemala ed El Salvador. Le 2 voci vanno messe in relazione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Wilson Center</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Digital Archive</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>In rete</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Consultazione libera</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Documenti già segreti provenienti da governi di tutto il mondo; comprende materiali sul crollo dell’impero coloniale portoghese</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Tomo II cap. IV</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>CONFERMATO — ma l'ambito dichiarato non e quello che la voce indica</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>Confermata alla lettera la descrizione generale: l'archivio digitale contiene documenti gia segreti provenienti da governi di tutto il mondo. AMBITO EFFETTIVO, che la voce non reca e che ne restringe l'uso: la raccolta riunisce la ricerca di 3 PROGETTI DEL CENTRO, dedicati alle storie interconnesse della GUERRA FREDDA, DELLA COREA e della PROLIFERAZIONE NUCLEARE. NON RISCONTRATO il contenuto che la voce indica come utile, cioe i materiali sul crollo dell'impero coloniale portoghese: non rientra in alcuno dei 3 progetti dichiarati e va verificato per ricerca diretta prima di essere citato. Confermata la libera consultazione; la risorsa e segnalata anche dalla biblioteca degli Archivi nazionali statunitensi. RESTA APERTA l'avvertenza gia annotata sul trasferimento di documenti verso l'archivio non governativo di Washington.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Dipartimento di Stato statunitense</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>FOIA Documents Search</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>In rete</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Ricerca per parola chiave e per data</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Comprende i progetti di desecretazione dedicati a Cile, Argentina, El Salvador e Guatemala, e le trascrizioni telefoniche del segretario di Stato</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tomo II cap. IV — l’asse sudamericano; è l’indirizzo più diretto per il lato lungo del triangolo</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — l'elenco delle raccolte e esatto, e 1 di esse rinvia al foglio 03</t>
-        </is>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>ELENCO CONFERMATO ALLA LETTERA: le raccolte comprendono i progetti di desecretazione dedicati a CILE, ARGENTINA, EL SALVADOR e GUATEMALA e le trascrizioni telefoniche del segretario di Stato, oltre alla corrispondenza elettronica di una segretaria di Stato successiva. Ricerca per parola chiave e per data confermata. MISURE, con divergenza da chiudere: una guida universitaria indica OLTRE 80MILA documenti ricercabili, un'altra 221.373. Le 2 cifre appartengono a rilevazioni di date diverse e vanno datate. DATI SOSTANZIALI OMESSI, tutti utili al Tomo sull'asse sudamericano: la raccolta cilena e l'esito di uno sforzo esteso all'intero governo e consta di OLTRE 23MILA DOCUMENTI sul periodo 1968-1991, prodotti da agenzia informativa, Difesa, Archivi nazionali, Consiglio di sicurezza, ufficio federale, Giustizia e Dipartimento di Stato; il progetto argentino rappresenta QUASI 20 ANNI di lavoro per rilasciare ogni informazione sulle violazioni dei diritti umani in Argentina FRA IL 1975 E IL 1983; le trascrizioni telefoniche coprono da settembre 1973 a dicembre 1976. L'ente stesso premette alla raccolta cilena l'avvertenza 'MATERIALE GRAFICO INCLUSO'. COLLEGAMENTO CON IL FOGLIO 03, VOCE 70: le trascrizioni dell'era Nixon sono state riesaminate SECONDO LA LEGGE DEL 1974 SULLA CONSERVAZIONE DELLE REGISTRAZIONI E DEI MATERIALI PRESIDENZIALI, quelle dell'era Ford secondo la legge sull'accesso. La legge che il repertorio censisce nel foglio degli atti e dunque la norma che regola la consultabilita di questa fonte: le 2 voci vanno messe in relazione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>FBI</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>The Vault — Electronic Reading Room</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>In rete</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Consultazione libera</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Documenti desecretati dell’ufficio federale</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Tomo II</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — manca la scala</t>
-        </is>
-      </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>Confermato: la biblioteca elettronica dell'ufficio federale e descritta dall'ente stesso come la propria nuova biblioteca per l'accesso agli atti, contenente 6.700 DOCUMENTI e altri materiali digitalizzati da originali cartacei. La cifra manca alla voce ed e utile, perche colloca questa fonte 3 ordini di grandezza sotto le altre censite nel foglio: non e un archivio di massa ma una selezione.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Dipartimento di Stato statunitense</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Foreign Relations of the United States</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>In rete e a stampa</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Consultazione libera</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Serie documentaria ufficiale della politica estera, con annata pressoché completa dal 1861</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Tomo II</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO — con un limite temporale da precisare</t>
-        </is>
-      </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>Confermata la serie documentaria ufficiale della politica estera. PRECISAZIONE SUL DATO DELLA VOCE: la formula 'annata pressoche completa dal 1861' corrisponde a quanto dichiarano le guide, che parlano di una serie quasi completa DAL 1861 AL 1960, con i volumi mancanti aggiunti via via che possono essere acquisiti e trattati. Il termine finale del 1960 riguarda la raccolta digitalizzata di riferimento e va indicato, perche per i decenni successivi la consultazione segue vie diverse. La serie prosegue oltre quella data nelle edizioni correnti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>NARA</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>U.S. Declassified Documents Online e collezioni</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>In rete, in parte su abbonamento</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Consultazione</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Oltre 5100.000 pagine di documenti già classificati di Agenzia, Dipartimento di Stato, Difesa, Consiglio di sicurezza nazionale, Casa Bianca e ufficio federale</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Tomo II capp. III-IV</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>ERRORE DI ATTRIBUZIONE — LA RISORSA NON E DEGLI ARCHIVI NAZIONALI</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>ERRORE ACCERTATO: la voce attribuisce 'U.S. Declassified Documents Online' agli ARCHIVI NAZIONALI. La risorsa e un prodotto commerciale dell'editore GALE, gia denominato Declassified Documents Reference System. Non e un archivio pubblico ma una raccolta editoriale i cui curatori sorvegliano i rilasci delle biblioteche presidenziali e delle agenzie. Cio spiega l'annotazione 'in parte su abbonamento', che e esatta, ma l'ente va corretto: le voci di questo foglio devono distinguere gli enti che DETENGONO gli atti da quelli che li RIVENDONO. CIFRA CONFERMATA, E CONFERMA LA REGOLA DI DECODIFICA: la voce reca 'oltre 5100.000 pagine'; la forma corrotta si legge CINQUECENTOMILA, e la fonte reca esattamente 'over 500,000 pages of previously classified government documents'. E la sesta conferma esterna della regola. ELENCO DELLE AGENZIE ESATTO: agenzia informativa, Dipartimento di Stato, Difesa, Consiglio di sicurezza nazionale, Casa Bianca e ufficio federale, oltre ad altre. DIVERGENZE DI MISURA DA DATARE: una guida indica oltre 500mila PAGINE con copertura dal 1950 a oggi; un'altra circa 700mila DOCUMENTI dal 1900 al 2008. Pagine e documenti non sono la stessa unita e le 2 cifre non sono in conflitto, ma vanno indicate separatamente. MODALITA DI ACCRESCIMENTO: ogni inverno esce un supplemento annuale di 5.000 documenti, acquistabile a parte. INTEGRAZIONE PER LA VOCE 7: la serie diplomatica ufficiale, iniziata nel 1861, consta oggi di OLTRE 450 VOLUMI ed e prodotta dall'Ufficio dello storico del Dipartimento di Stato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>MuckRock</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Guida alla ricerca in CREST</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>In rete</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Consultazione libera</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Guida pratica alla ricerca nel repertorio dell’Agenzia; segnala che la guida ufficiale elenca 3 tipi di contenuto mentre i metadati ne rivelano oltre novanta</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Strumento operativo per il Cantiere Delta e per il Tomo II</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>verificato 4.8.2026</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t>CONFERMATO ALLA LETTERA — 3 contro oltre 90</t>
-        </is>
-      </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>5.8.2026</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>LA CIFRA PIU SORPRENDENTE DELLA VOCE E ESATTA. La guida di MuckRock afferma: 'in un esempio egregio, la guida dell'Agenzia alla ricerca nei documenti elenca soltanto 3 TIPI DI CONTENUTO ricercabili, mentre un esame dei metadati raccolti da DATA.WORLD ne rivela ULTERIORI NOVANTA'. La voce lo rende correttamente. FONTE DEL DATO da aggiungere: i metadati furono compilati da Data.World, non dall'Agenzia. VALORE METODOLOGICO: e un caso misurato di divergenza fra cio che un ente dichiara di rendere ricercabile e cio che la struttura dei propri dati rende effettivamente ricercabile. Non e occultamento: e una guida incompleta. Ma per un'opera che studia le condizioni di osservabilita del proprio oggetto, la differenza fra 3 e oltre 90 e essa stessa un dato.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
+++ b/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -152,6 +152,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6083,11 +6086,19 @@
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr"/>
-      <c r="L11" s="8" t="inlineStr"/>
+          <t>PARZIALE — l'ente esiste (Portale delle fonti per la storia della Repubblica italiana, infrastruttura del CNR, accesso unico a fonti dal 1946 [A]), ma il DOMINIO va accertato: le fonti danno il portale come portalefontirepubblicaitaliana.cnr.it, non fontitaliarepubblicana.it [B]. Da confermare che il dominio del repertorio risolva o rediriga.</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: portalefontirepubblicaitaliana.cnr.it (CNR), Istituto Sturzo, storiadigitale.it; collegato al Centro Flamigni. DOMINIO DA RISCONTRARE.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -6123,13 +6134,21 @@
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr"/>
-      <c r="L12" s="8" t="inlineStr"/>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — SIUSA, Sistema Informativo Unificato per le Soprintendenze Archivistiche (DG Archivi/ICAR con la Scuola Normale di Pisa): descrive il patrimonio archivistico non statale, pubblico e privato, conservato fuori dagli Archivi di Stato; soggetti produttori, conservatori e strumenti di ricerca [A].</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: icar.cultura.gov.it, siusa-archivi.cultura.gov.it; dal 2011 esporta al Sistema Archivistico Nazionale (SAN). Ente confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -6217,11 +6236,19 @@
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr"/>
-      <c r="L14" s="8" t="inlineStr"/>
+          <t>CONFERMATO come ente, MA DUPLICATO DELLA RIGA 15: l'Associazione familiari delle vittime della strage di Bologna del 2.8.1980 È il soggetto titolare di stragi.it (riga 15) [A]. Duplicazione fra voci da sciogliere (§8.4); tenuta in sospeso finché non si decide quale conservare e fondere.</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: stragi.it, memoria.cultura.gov.it. STESSA ENTITÀ della riga 15.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -6259,11 +6286,19 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr"/>
-      <c r="L15" s="8" t="inlineStr"/>
+          <t>CONFERMATO — stragi.it è il sito dell'Associazione familiari vittime strage Bologna 2.8.1980; archivio consultabile di foto, video, audio, documenti (funerali di Stato, processo, ricostruzione) [A]. DUPLICATO DELLA RIGA 14 (stessa entità) — da sciogliere (§8.4).</t>
+        </is>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: stragi.it/archivio/documenti; nella Rete (memoria.cultura.gov.it). Archivio di Memoria del processo ai mandanti (RGNR 2/18) in digitalizzazione dal 2025, non ancora integralmente online — da riverificare.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -6299,13 +6334,21 @@
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr"/>
-      <c r="L16" s="8" t="inlineStr"/>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Mappe di Memoria (mappedimemoria.it): archivio digitale sui luoghi delle stragi, del terrorismo e della violenza politica; Univ. di Bologna (Dip. Scienze dell'educazione), nella convenzione MIUR-associazioni delle vittime; copre Italicus 1974, Bologna 1980, Rapido 904 1984 [A].</t>
+        </is>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: mappedimemoria.it, memoria.cultura.gov.it, UniBo. Ente confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -6341,13 +6384,21 @@
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr"/>
-      <c r="L17" s="8" t="inlineStr"/>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — archivio900.it: portale di documentazione sul Novecento e sul terrorismo italiano e internazionale; libri, articoli, documenti e atti processuali; registro di 170 vittime del terrorismo 1967-2003 [A]. Risorsa documentale consultabile, non un archivio di Stato.</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L17" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: archivio900.it. Confermato come risorsa documentale.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -6433,13 +6484,21 @@
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr"/>
-      <c r="L19" s="8" t="inlineStr"/>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — l'Archivio di Stato di Milano conserva il fondo «Processo per la strage di piazza Fontana (Salvini)» (inventario a cura di F. Lisanti) e un distinto fondo «(Procura)» [A]. Istruttoria del giudice Salvini 1989-1997; sentenze istruttorie 18.3.1995 e 3.2.1998; fondo chiuso nel 2018.</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: archiviodistatomilano.cultura.gov.it (inventari PDF), memoria.cultura.gov.it. Nome proprio disponibile: giudice Guido Salvini.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -6475,13 +6534,21 @@
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr"/>
-      <c r="L20" s="8" t="inlineStr"/>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Archivio storico del Corriere della Sera, documentazione storico-giornalistica dal 1876 a oggi; numeri digitalizzati, prime pagine e articoli d'epoca consultabili online (archiviostorico.corriere.it) [A].</t>
+        </is>
+      </c>
+      <c r="K20" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: archiviostorico.corriere.it, cataloghi di ateneo. Ente confermato; utile per la datazione della ricezione.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -6521,13 +6588,21 @@
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr"/>
-      <c r="L21" s="8" t="inlineStr"/>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — ArchivioAntimafia (archivioantimafia.org): raccoglie e pubblica integralmente documenti su mafia e antimafia — sentenze e atti processuali in PDF, verbali, registrazioni [A] (es. atti Falcone/Capaci, trattativa Stato-mafia, Mafia Capitale).</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: archivioantimafia.org/sentenze.php, /testi.php. Testi integrali senza censura né sintesi — confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">

--- a/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
+++ b/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -153,6 +153,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -6084,19 +6087,19 @@
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>PARZIALE — l'ente esiste (Portale delle fonti per la storia della Repubblica italiana, infrastruttura del CNR, accesso unico a fonti dal 1946 [A]), ma il DOMINIO va accertato: le fonti danno il portale come portalefontirepubblicaitaliana.cnr.it, non fontitaliarepubblicana.it [B]. Da confermare che il dominio del repertorio risolva o rediriga.</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
+        <is>
+          <t>ERRORE (dominio) — fontitaliarepubblicana.it NON risolve (ENOTFOUND) e nessuna fonte lo cita; l'ente reale è il «Portale delle fonti per la storia della Repubblica italiana» del CNR, a portalefontirepubblicaitaliana.cnr.it [B]. CORREZIONE: sostituire il dominio. Limite: DNS verificato dall'ambiente, da confermare sull'originale.</t>
+        </is>
+      </c>
+      <c r="K11" s="17" t="inlineStr">
         <is>
           <t>6.8.2026</t>
         </is>
       </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>COLLAZIONE RETE 6.8.2026: portalefontirepubblicaitaliana.cnr.it (CNR), Istituto Sturzo, storiadigitale.it; collegato al Centro Flamigni. DOMINIO DA RISCONTRARE.</t>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: dominio non risolve; CNR (portalefontirepubblicaitaliana.cnr.it), Istituto Sturzo, storiadigitale.it. DOMINIO DA CORREGGERE.</t>
         </is>
       </c>
     </row>
@@ -6234,19 +6237,19 @@
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>CONFERMATO come ente, MA DUPLICATO DELLA RIGA 15: l'Associazione familiari delle vittime della strage di Bologna del 2.8.1980 È il soggetto titolare di stragi.it (riga 15) [A]. Duplicazione fra voci da sciogliere (§8.4); tenuta in sospeso finché non si decide quale conservare e fondere.</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO (voce canonica della coppia duplicata 14/15) — Associazione tra i familiari delle vittime della strage di Bologna del 2.8.1980, soggetto conservatore; sito stragi.it, archivio consultabile di foto/video/audio/documenti [A]. La riga 15 (stragi.it) ne è la sola istanza web: da eliminare come duplicato (§8.4).</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>6.8.2026</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t>COLLAZIONE 6.8.2026: stragi.it, memoria.cultura.gov.it. STESSA ENTITÀ della riga 15.</t>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE RETE 6.8.2026: stragi.it, memoria.cultura.gov.it. Voce canonica; assorbe la riga 15.</t>
         </is>
       </c>
     </row>
@@ -6284,19 +6287,19 @@
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
       <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>CONFERMATO — stragi.it è il sito dell'Associazione familiari vittime strage Bologna 2.8.1980; archivio consultabile di foto, video, audio, documenti (funerali di Stato, processo, ricostruzione) [A]. DUPLICATO DELLA RIGA 14 (stessa entità) — da sciogliere (§8.4).</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>DUPLICATO DELLA RIGA 14 — stragi.it è il sito dell'Associazione familiari vittime strage Bologna (riga 14, canonica). Voce da eliminare nel passo §8.4; il contenuto è conservato sulla riga 14 [A].</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="inlineStr">
         <is>
           <t>6.8.2026</t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>COLLAZIONE RETE 6.8.2026: stragi.it/archivio/documenti; nella Rete (memoria.cultura.gov.it). Archivio di Memoria del processo ai mandanti (RGNR 2/18) in digitalizzazione dal 2025, non ancora integralmente online — da riverificare.</t>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>Duplicato di riga 14 (§8.4). Contenuto conservato sulla canonica.</t>
         </is>
       </c>
     </row>
@@ -8842,13 +8845,21 @@
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K66" s="8" t="inlineStr"/>
-      <c r="L66" s="8" t="inlineStr"/>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO e integrato — desecretazione/versamento all'Archivio Centrale dello Stato per direttiva: Prodi (DPCM 8.4.2008), Renzi (22.4.2014) e — DA AGGIUNGERE — Draghi (2021, su Gladio e Loggia P2). Versamenti dal 1.8.2014; ~77 versamenti, 156 uffici, ~2.000 buste [A]. OMESSO E DISPONIBILE: la direttiva Draghi 2021.</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: acs.cultura.gov.it (Direttiva Renzi/Guida ai fondi STRAGI), archivi.cultura.gov.it. Confermato; integrare Draghi 2021.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -8892,13 +8903,21 @@
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="8" t="inlineStr"/>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Legge 3 agosto 2007 n.124, «Sistema di informazione per la sicurezza della Repubblica e nuova disciplina del segreto», pubblicata in G.U. n.187 del 13.8.2007; il capo V disciplina la tutela del segreto di Stato [A].</t>
+        </is>
+      </c>
+      <c r="K67" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L67" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: gazzettaufficiale.it, sicurezzanazionale.gov.it, Camera. Norma confermata.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -8942,13 +8961,21 @@
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K68" s="8" t="inlineStr"/>
-      <c r="L68" s="8" t="inlineStr"/>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Comitato parlamentare per la sicurezza della Repubblica (COPASIR), istituito dall'art.30 della L.124/2007; 5 deputati + 5 senatori, sede a Palazzo San Macuto [A] (riscontro sull'atto istitutivo).</t>
+        </is>
+      </c>
+      <c r="K68" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L68" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: L.124/2007 (atto istitutivo), parlamento.it. Organo confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -8992,13 +9019,21 @@
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
-      <c r="J69" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="8" t="inlineStr"/>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Legge 30 maggio 2014 n.82: istituisce la Commissione parlamentare d'inchiesta sul rapimento e sulla morte di Aldo Moro; G.U. n.125 del 31.5.2014; Commissione costituita il 2.10.2014, presidente Giuseppe Fioroni; termine prorogato a fine XVII legislatura (DL 210/2015 conv. L.21/2016) [A]. NOME DISPONIBILE: Giuseppe Fioroni.</t>
+        </is>
+      </c>
+      <c r="K69" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L69" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: gazzettaufficiale.it, inchieste.camera.it/moro, parlamento.it. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -9042,13 +9077,21 @@
         </is>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K70" s="8" t="inlineStr"/>
-      <c r="L70" s="8" t="inlineStr"/>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — divieto di «pantouflage», art.53 comma 16-ter del d.lgs. 165/2001 (TUPI): il dipendente che ha esercitato poteri autoritativi/negoziali non può, per 3 anni dalla cessazione, lavorare presso i privati destinatari di quei poteri; sanzione di nullità; linee guida ANAC [A].</t>
+        </is>
+      </c>
+      <c r="K70" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L70" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: anticorruzione.it (linee guida pantouflage), Altalex, Diritto.it. Norma confermata.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -9192,13 +9235,21 @@
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr"/>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="8" t="inlineStr"/>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Legge 25 gennaio 1982 n.17 (Anselmi/Spadolini), norme di attuazione dell'art.18 Cost. in materia di associazioni segrete e scioglimento della Loggia P2; G.U. del 28.1.1982; governo Spadolini I [A]. NOMI DISPONIBILI: Tina Anselmi, Giovanni Spadolini.</t>
+        </is>
+      </c>
+      <c r="K73" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L73" s="16" t="inlineStr">
+        <is>
+          <t>COLLAZIONE 6.8.2026: gazzettaufficiale.it (082U0017), Wikipedia/Legge Anselmi, vLex. Norma confermata.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">

--- a/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
+++ b/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
@@ -9135,13 +9135,21 @@
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
-      <c r="J71" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="8" t="inlineStr"/>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Relazione annuale del COPASIR 2021-2022 (attività febbraio-agosto 2022), trasmessa al Parlamento a inizio agosto 2022, anticipata per lo scioglimento delle Camere; presidente Adolfo Urso. Ravvisa «una sostanziale debolezza degli interventi» contro disinformazione e interferenze (infowarfare russa/cinese, golden power) [A]. NOME DISPONIBILE: Adolfo Urso.</t>
+        </is>
+      </c>
+      <c r="K71" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L71" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Formiche, Askanews, PublicPolicy (PDF). Confermato; due indagini incompiute coerenti col contesto.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -9293,13 +9301,21 @@
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K74" s="8" t="inlineStr"/>
-      <c r="L74" s="8" t="inlineStr"/>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — CEDU, Grande Oriente d'Italia c. Italia, ric. 29550/17: violazione dell'art.8 per la perquisizione e il sequestro (2017) di 39 faldoni di schede degli iscritti alle logge di Sicilia e Calabria disposti dalla Commissione antimafia [A]. Sentenza di camera 19.12.2024; la GRANDE CAMERA il 7.7.2026 ha respinto l'appello del governo — DA AGGIUNGERE.</t>
+        </is>
+      </c>
+      <c r="K74" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L74" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: giustizia.it (sentenze CEDU), Federprivacy, Rivista Penale. Integrare la Grande Camera 7.7.2026.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -9343,13 +9359,21 @@
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr"/>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="8" t="inlineStr"/>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Commissione parlamentare antimafia (XVII leg.), relazione sulle infiltrazioni di Cosa Nostra e 'ndrangheta nella massoneria (Sicilia e Calabria), Doc. XXIII n.33, approvata il 21.12.2017; relatrice Rosy Bindi. Castelvetrano: loggia Francisco Ferrer, tre assessori massoni (due iscritti al GOI) [A]. NOME DISPONIBILE: Rosy Bindi.</t>
+        </is>
+      </c>
+      <c r="K75" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L75" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: inchieste.camera.it/mafie, Avviso Pubblico, Editoriale Domani. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -9395,11 +9419,19 @@
       <c r="I76" s="3" t="inlineStr"/>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="8" t="inlineStr"/>
+          <t>PARZIALE — processo Gotha (Reggio Calabria), dalla fusione di Mammasantissima, Reghion, Fata Morgana, Sistema Reggio e — DA AGGIUNGERE — Alchimia (cinque inchieste, non quattro). Rito abbreviato: primo grado marzo 2018, giudice Pasquale Laganà, 28 condanne e 10 assoluzioni; motivazioni nov. 2018 [A]. L'ESITO D'APPELLO DEL MAGGIO 2026 (azzeramento delle condanne sulla componente riservata) NON riscontrato dalle fonti consultate — da verificare [C]. NOME DISPONIBILE: Pasquale Laganà.</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Wikipedia/Processo Gotha, Il Fatto (motivazioni), citynow. Primo grado confermato; appello 2026 da riscontrare; aggiungere Alchimia.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -9439,13 +9471,21 @@
       </c>
       <c r="H77" s="3" t="inlineStr"/>
       <c r="I77" s="3" t="inlineStr"/>
-      <c r="J77" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K77" s="8" t="inlineStr"/>
-      <c r="L77" s="8" t="inlineStr"/>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — operazione Kyterion, DDA di Catanzaro: 29.1.2015, 37 fermati della cosca Grande Aracri (Cutro/Crotonese); Kyterion 2 il 4.1.2016, 16 arresti, con tentativi di aggancio a Vaticano, Cassazione e ambienti massonici attribuiti a Nicolino Grande Aracri [A]. NOMI DISPONIBILI: Nicolino ed Ernesto Grande Aracri (ergastolo per l'omicidio Dragone, confermato in Cassazione 4.6.2019).</t>
+        </is>
+      </c>
+      <c r="K77" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L77" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Gazzetta del Sud, Zoom24, Reggio Report. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -9535,13 +9575,21 @@
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K79" s="8" t="inlineStr"/>
-      <c r="L79" s="8" t="inlineStr"/>
+      <c r="J79" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — operazione/processo Grimilde, DDA di Bologna: maggio 2019, poi 25.6.2019, 16 arresti; ramo emiliano (Reggio Emilia-Parma-Piacenza) della cosca Grande Aracri. Condanna definitiva a oltre 12 anni dell'esponente politico Giuseppe Caruso (ex presidente del consiglio comunale di Piacenza, FdI); in appello a Bologna 24 condanne, pena max 19a6m a Francesco Grande Aracri [A]. NOMI DISPONIBILI: Giuseppe Caruso, Francesco Grande Aracri.</t>
+        </is>
+      </c>
+      <c r="K79" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L79" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Quotidiano del Sud, La Via Libera, il Resto del Carlino. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -9585,13 +9633,21 @@
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K80" s="8" t="inlineStr"/>
-      <c r="L80" s="8" t="inlineStr"/>
+      <c r="J80" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — processo P3, Tribunale di Roma IX sez. penale, sentenza 16.3.2018: la P3 è ritenuta associazione segreta (violazione della legge Anselmi) volta a condizionare gli organi costituzionali. Flavio Carboni 6 anni e 6 mesi (già coinvolto nel crac del Banco Ambrosiano); Arcangelo Martino 4a9m; Denis Verdini assolto dall'accusa più grave, 1a3m per finanziamento illecito; prescrizione per Ugo Cappellacci (ex presidente Regione Sardegna, abuso d'ufficio) [A]. NOMI: Carboni, Martino, Verdini, Cappellacci.</t>
+        </is>
+      </c>
+      <c r="K80" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L80" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: ANSA, Radio Radicale (sentenza), Unione Sarda, Today. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">

--- a/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
+++ b/repertorio/ITALIA_NERA_REPERTORIO_RIPARATO_E_FOGLIO_DI_VERIFICA2.xlsx
@@ -7361,13 +7361,21 @@
       </c>
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K36" s="8" t="inlineStr"/>
-      <c r="L36" s="8" t="inlineStr"/>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Commissione indipendente di storici sul BND (UHK), istituita nel 2011 dallo stesso BND per la storia del servizio e della Gehlen-Org 1945-1968; ~2,4 mln€ dal bilancio del BND; 11 volumi pubblicati [A]. NOMI: Jost Dülffer, Klaus-Dietmar Henke, Wolfgang Krieger, Rolf-Dieter Müller.</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Bundestag (hib), Uni Marburg, Clio-online, Wikipedia BND. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7407,13 +7415,21 @@
       </c>
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr"/>
-      <c r="L37" s="8" t="inlineStr"/>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Ufficio federale per la protezione della Costituzione (BfV): l'11.11.2011, stesso giorno dell'avvio delle indagini della Procura federale sull'NSU, un capodivisione ordinò la distruzione di fascicoli («Aktion Konfetti») su 7 informatori (V-Leute) dell'«Operation Rennsteig» (1997-2003, scena neonazista in Turingia) [A]. NSU: Mundlos, Böhnhardt, Zschäpe.</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Tagesspiegel, taz, Verfassungsblog. Accertato da Procura federale e commissione d'inchiesta del Bundestag.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7453,13 +7469,21 @@
       </c>
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr"/>
-      <c r="L38" s="8" t="inlineStr"/>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Ufficio regionale dell'Assia per la protezione della Costituzione (LfV Hessen): rapporto interno di revisione degli atti (nov. 2014) sull'omicidio NSU di Kassel (Halit Yozgat) e sul funzionario Andreas Temme, presente sulla scena; segretato per 120 anni («nessun caso comparabile»), poi ridotto a 30 [A]. NOMI: Andreas Temme, Halit Yozgat.</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Wikipedia/Halit Yozgat, Telepolis/Heise, t-online, NSU-Watch. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,13 +7527,21 @@
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="inlineStr"/>
-      <c r="L39" s="8" t="inlineStr"/>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Bund Deutscher Jugend (BDJ) e il suo «Technischer Dienst», rete stay-behind: fondata nel giugno 1950 su iniziativa della CIA (OPC), sciolta a fine 1952/inizio 1953; deposito d'armi nell'Odenwald (Waldmichelbach); liste di ~40 dirigenti SPD/KPD da eliminare; scoperta dopo la denuncia di Hans Otto alla polizia di Francoforte (9.9.1952) [A]. NOMI: Hans Otto, Klaus Barbie.</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Wikipedia (en/de) BDJ, Lecorte, Vorwärts. Confermato; finanziamento USA ~50.000$/mese.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7553,13 +7585,21 @@
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr"/>
-      <c r="L40" s="8" t="inlineStr"/>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — schedario microfilmato «Rosenholz» della HVA (spionaggio estero della Stasi/DDR): 381 supporti ottici, ~280.000 file (il repertorio dice ~293.000 — SCARTO MINORE da verificare); desecretato il 26.6.2003, consultabile presso il BStU/Bundesarchiv dal marzo 2004 [A]. Cerniera: ~90% delle persone schedate non erano IM.</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L40" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Bundesarchiv (Rosenholz), Wikipedia (de/en). Confermato; scarto sul numero di schede.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7599,13 +7639,21 @@
       </c>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr"/>
-      <c r="L41" s="8" t="inlineStr"/>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — Organo parlamentare di controllo sui servizi (PKGr), Bundestag: 1956 comitato di fiduciari (PMVG, Adenauer, senza base legale, solo BND fino al 1964); 1978 base legislativa (PKK); 1999 rinominato PKGr; 2009 ancoraggio costituzionale nell'art.45d GG; controlla BND, BfV e MAD [A]. NOME: Konrad Adenauer.</t>
+        </is>
+      </c>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L41" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Bundestag (einführung), Wikipedia PKGr, art.45d GG, PKGrG. Confermato.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7645,13 +7693,21 @@
       </c>
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr"/>
-      <c r="L42" s="8" t="inlineStr"/>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — serie di commissioni indipendenti sulle continuità istituzionali dopo il 1945: ministero degli Esteri (2005 → «Das Amt», 2010), ministero delle Finanze (2009, sul Reichsfinanzministerium), ministero della Giustizia (2012 → «Die Akte Rosenburg») [A]. NOMI: Manfred Görtemaker, Christoph Safferling.</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Siscalt, diplo.de, ANRP. Confermato; fenomeno sistemico.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -9691,13 +9747,21 @@
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>da riverificare</t>
-        </is>
-      </c>
-      <c r="K81" s="8" t="inlineStr"/>
-      <c r="L81" s="8" t="inlineStr"/>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>CONFERMATO — procedimento tedesco sull'attentato dell'Oktoberfest (Monaco, 26.9.1980): 12 vittime più l'attentatore Gundolf Köhler, 200+ feriti; tesi iniziale del singolo; indagini della Procura federale riaperte a fine 2014 (grazie a Ulrich Chaussy e all'avv. Werner Dietrich), archiviate nel luglio 2020 riconoscendo il movente politico di estrema destra [A]. Pubblicazione online dei documenti da parte del Bundesarchiv NON riscontrata — da verificare. NOMI: Gundolf Köhler, Ulrich Chaussy, Werner Dietrich.</t>
+        </is>
+      </c>
+      <c r="K81" s="16" t="inlineStr">
+        <is>
+          <t>6.8.2026</t>
+        </is>
+      </c>
+      <c r="L81" s="16" t="inlineStr">
+        <is>
+          <t>RISCONTRO 6.8.2026: Wikipedia/Oktoberfest bombing, WSWS, openDemocracy. Confermato; pubblicazione Bundesarchiv da riscontrare.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
